--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -1,96 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\klim\projects\chaos_redux\docs\spreadsheets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5163BE9E-6627-400F-8232-D874770B147A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Events" sheetId="1" r:id="rId1"/>
+    <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Events!$A$1:$I$2</definedName>
-  </definedNames>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Event Name</t>
-  </si>
-  <si>
-    <t>Details</t>
-  </si>
-  <si>
-    <t>Evolutions I</t>
-  </si>
-  <si>
-    <t>Evolutions II</t>
-  </si>
-  <si>
-    <t>Evolutions III</t>
-  </si>
-  <si>
-    <t>Evolutions IV</t>
-  </si>
-  <si>
-    <t>World end</t>
-  </si>
-  <si>
-    <t>Major Event</t>
-  </si>
-  <si>
-    <t>Zombie Outbreak</t>
-  </si>
-  <si>
-    <t>If the outbreak survives into the late chaos game, the Anti-Zombie League still exists, and the main horde grows large enough, the chain can end in a zombie apocalypse world-end. If the main horde is broken repeatedly instead, outbreaks slow down, the system shuts off after three collapses, and wiping out the last zombie territory triggers a final victory event that also lowers chaos.</t>
-  </si>
-  <si>
-    <t>The first major zombie adaptation makes the horde much harder to starve out and much stronger at night. It is the point where early containment starts slipping, and cure work begins getting harder.</t>
-  </si>
-  <si>
-    <t>The horde turns into a faster assault force with better attack pressure and even less reliance on supply. Finding the cure becomes harder again.</t>
-  </si>
-  <si>
-    <t>At this stage weak fronts can collapse fast, and the cure is at its hardest to finish.</t>
-  </si>
-  <si>
-    <t>The outbreak begins in one random populous state. Zombies use only manpower for their divisions, and thus depend a lot on the population of states they capture. If the horde gets momentum, it spreads fast and captured land is cored right away.
-Secondary outbreaks happen most likely in big, crowded, less developed. Chaos makes those outbreaks more common over time, and each zombie evolution makes the horde harder to contain.
-If you want to keep the event under control, the main things that matter are holding the front, cutting outbreak risk with prevention decisions, pushing cure research, and joining the Anti-Zombie League.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -179,17 +116,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -199,16 +136,15 @@
   <dxfs count="15">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <b val="1"/>
       </font>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -222,127 +158,127 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+      <border outline="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
@@ -356,7 +292,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -388,7 +324,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border>
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -405,39 +341,27 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Table Style 1" pivot="0" count="3" xr9:uid="{AEF72196-99EB-4E06-A5D6-D000DE4B8566}">
+    <tableStyle name="Table Style 1" pivot="0" count="3">
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
-  <colors>
-    <mruColors>
-      <color rgb="FF974833"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors/>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EBAC382B-E17D-41F3-A1DB-866849839D0B}" name="Table1" displayName="Table1" ref="A1:I2" totalsRowShown="0" headerRowDxfId="11" dataDxfId="1" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:I2" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I2" headerRowCount="1" totalsRowShown="0" headerRowDxfId="11" dataDxfId="1" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:I2"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{09E2E79E-E67D-4541-A2D5-F8050D248861}" name="ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{E2DB3495-3FA1-4BAF-ABC4-3336FF40B1A3}" name="Type" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{E51D2C0B-22E7-4DD5-BA6B-2748F28F33A5}" name="Event Name" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{65105D20-8E3E-4C88-8E75-99C37C2DDC6A}" name="Details" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{327BD53E-1708-423F-94BD-01326356CBB2}" name="Evolutions I" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{E340BC85-586F-472E-894E-0BD6324AE181}" name="Evolutions II" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{E5F8859C-CAB3-4B28-9E8E-6DAF156E9A96}" name="Evolutions III" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{04AB8C5F-0AA6-4E37-A01D-8E7237252C51}" name="Evolutions IV" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{C1AEC05A-475F-4D3C-A4DF-8E27DC0E5D0E}" name="World end" dataDxfId="2"/>
+    <tableColumn id="1" name="ID" dataDxfId="10"/>
+    <tableColumn id="2" name="Type" dataDxfId="9"/>
+    <tableColumn id="3" name="Event Name" dataDxfId="8"/>
+    <tableColumn id="4" name="Details" dataDxfId="7"/>
+    <tableColumn id="5" name="Evolutions I" dataDxfId="6"/>
+    <tableColumn id="6" name="Evolutions II" dataDxfId="5"/>
+    <tableColumn id="7" name="Evolutions III" dataDxfId="4"/>
+    <tableColumn id="8" name="Evolutions IV" dataDxfId="3"/>
+    <tableColumn id="9" name="World end" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -727,83 +651,156 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF188038"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="64" customWidth="1"/>
-    <col min="5" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="44" customWidth="1"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="7"/>
+    <col width="16.42578125" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" ht="27.95" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Event Name</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Evolutions I</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Evolutions II</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Evolutions III</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Evolutions IV</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>World end</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Major Event</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Communism Spread</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Communist influence now escalates through implemented support-driven stages inside the existing communism chain. As support rises, strikes become harsher, soft responses stop being enough, military repression becomes riskier, and rebel seizure plus civil-war pressure become much more dangerous.</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>International Coordination: suggested true evolution for chaos tier 2. Once world chaos reaches tier 2, active communism-spread countries above 15% support should get faster strike MTTH, weaker soft-response decisions, and renewed unrest after complete military failures.</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Insurrectionary Bloc: suggested true evolution for chaos tier 4. Once world chaos reaches tier 4, countries above 30% support should face looser civil-war triggers, rebound rebel outbreaks after suppression, and military complete failures that can directly push the uprising path.</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>No world-end branch planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="210" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6" t="s">
-        <v>11</v>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Major Event</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Zombie Outbreak</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>The outbreak begins in one random populous state. Zombies use only manpower for their divisions, and thus depend a lot on the population of states they capture. If the horde gets momentum, it spreads fast and captured land is cored right away.
+Secondary outbreaks happen most likely in big, crowded, less developed. Chaos makes those outbreaks more common over time, and each zombie evolution makes the horde harder to contain.
+If you want to keep the event under control, the main things that matter are holding the front, cutting outbreak risk with prevention decisions, pushing cure research, and joining the Anti-Zombie League.</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>The first major zombie adaptation makes the horde much harder to starve out and much stronger at night. It is the point where early containment starts slipping, and cure work begins getting harder.</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>The horde turns into a faster assault force with better attack pressure and even less reliance on supply. Finding the cure becomes harder again.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>At this stage weak fronts can collapse fast, and the cure is at its hardest to finish.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>If the outbreak survives into the late chaos game, the Anti-Zombie League still exists, and the main horde grows large enough, the chain can end in a zombie apocalypse world-end. If the main horde is broken repeatedly instead, outbreaks slow down, the system shuts off after three collapses, and wiping out the last zombie territory triggers a final victory event that also lowers chaos.</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -1,33 +1,99 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\klim\projects\chaos_redux\docs\spreadsheets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C506BCF-393F-4392-8F3D-339695CBC9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Events" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Events" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Event Name</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>Evolutions I</t>
+  </si>
+  <si>
+    <t>Evolutions II</t>
+  </si>
+  <si>
+    <t>Evolutions III</t>
+  </si>
+  <si>
+    <t>Evolutions IV</t>
+  </si>
+  <si>
+    <t>World end</t>
+  </si>
+  <si>
+    <t>Communism Spread</t>
+  </si>
+  <si>
+    <t>Zombie Outbreak</t>
+  </si>
+  <si>
+    <t>The outbreak begins in one random populous state. Zombies use only manpower for their divisions, and thus depend a lot on the population of states they capture. If the horde gets momentum, it spreads fast and captured land is cored right away.
+Secondary outbreaks happen most likely in big, crowded, less developed. Chaos makes those outbreaks more common over time, and each zombie evolution makes the horde harder to contain.
+If you want to keep the event under control, the main things that matter are holding the front, cutting outbreak risk with prevention decisions, pushing cure research, and joining the Anti-Zombie League.</t>
+  </si>
+  <si>
+    <t>The first major zombie adaptation makes the horde much harder to starve out and much stronger at night. It is the point where early containment starts slipping, and cure work begins getting harder.</t>
+  </si>
+  <si>
+    <t>The horde turns into a faster assault force with better attack pressure and even less reliance on supply. Finding the cure becomes harder again.</t>
+  </si>
+  <si>
+    <t>At this stage weak fronts can collapse fast, and the cure is at its hardest to finish.</t>
+  </si>
+  <si>
+    <t>If the outbreak survives into the late chaos game, the Anti-Zombie League still exists, and the main horde grows large enough, the chain can end in a zombie apocalypse world-end. If the main horde is broken repeatedly instead, outbreaks slow down, the system shuts off after three collapses, and wiping out the last zombie territory triggers a final victory event that also lowers chaos.</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>Fire-once</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -116,17 +182,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -135,14 +201,6 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" wrapText="1"/>
       <border outline="0">
         <left style="thin">
@@ -286,6 +344,39 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <border>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -310,58 +401,40 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <font>
+        <b/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Table Style 1" pivot="0" count="3">
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    <tableStyle name="Table Style 1" pivot="0" count="1" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
-  <colors/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I2" headerRowCount="1" totalsRowShown="0" headerRowDxfId="11" dataDxfId="1" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:I2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:I2" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:I2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
-    <tableColumn id="1" name="ID" dataDxfId="10"/>
-    <tableColumn id="2" name="Type" dataDxfId="9"/>
-    <tableColumn id="3" name="Event Name" dataDxfId="8"/>
-    <tableColumn id="4" name="Details" dataDxfId="7"/>
-    <tableColumn id="5" name="Evolutions I" dataDxfId="6"/>
-    <tableColumn id="6" name="Evolutions II" dataDxfId="5"/>
-    <tableColumn id="7" name="Evolutions III" dataDxfId="4"/>
-    <tableColumn id="8" name="Evolutions IV" dataDxfId="3"/>
-    <tableColumn id="9" name="World end" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Event Name" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Details" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evolutions I" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Evolutions II" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Evolutions III" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evolutions IV" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="World end" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -651,156 +724,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF188038"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="7"/>
-    <col width="16.42578125" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="64" customWidth="1"/>
+    <col min="5" max="7" width="33" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="9" max="9" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Details</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Evolutions I</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Evolutions II</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Evolutions III</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Evolutions IV</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>World end</t>
-        </is>
+    <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="5" t="n">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Major Event</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Communism Spread</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Communist influence now escalates through implemented support-driven stages inside the existing communism chain. As support rises, strikes become harsher, soft responses stop being enough, military repression becomes riskier, and rebel seizure plus civil-war pressure become much more dangerous.</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>International Coordination: suggested true evolution for chaos tier 2. Once world chaos reaches tier 2, active communism-spread countries above 15% support should get faster strike MTTH, weaker soft-response decisions, and renewed unrest after complete military failures.</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Insurrectionary Bloc: suggested true evolution for chaos tier 4. Once world chaos reaches tier 4, countries above 30% support should face looser civil-war triggers, rebound rebel outbreaks after suppression, and military complete failures that can directly push the uprising path.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>No world-end branch planned.</t>
-        </is>
-      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="6"/>
     </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
+    <row r="3" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Major Event</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Zombie Outbreak</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>The outbreak begins in one random populous state. Zombies use only manpower for their divisions, and thus depend a lot on the population of states they capture. If the horde gets momentum, it spreads fast and captured land is cored right away.
-Secondary outbreaks happen most likely in big, crowded, less developed. Chaos makes those outbreaks more common over time, and each zombie evolution makes the horde harder to contain.
-If you want to keep the event under control, the main things that matter are holding the front, cutting outbreak risk with prevention decisions, pushing cure research, and joining the Anti-Zombie League.</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>The first major zombie adaptation makes the horde much harder to starve out and much stronger at night. It is the point where early containment starts slipping, and cure work begins getting harder.</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>The horde turns into a faster assault force with better attack pressure and even less reliance on supply. Finding the cure becomes harder again.</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>At this stage weak fronts can collapse fast, and the cure is at its hardest to finish.</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>If the outbreak survives into the late chaos game, the Anti-Zombie League still exists, and the main horde grows large enough, the chain can end in a zombie apocalypse world-end. If the main horde is broken repeatedly instead, outbreaks slow down, the system shuts off after three collapses, and wiping out the last zombie territory triggers a final victory event that also lowers chaos.</t>
-        </is>
+      <c r="B3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="6" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\klim\projects\chaos_redux\docs\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C506BCF-393F-4392-8F3D-339695CBC9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A064293-9F89-4881-815E-93682BDC20B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,11 +16,12 @@
     <sheet name="Events" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>ID</t>
   </si>
@@ -49,7 +50,7 @@
     <t>World end</t>
   </si>
   <si>
-    <t>Communism Spread</t>
+    <t>Communist Insurgency</t>
   </si>
   <si>
     <t>Zombie Outbreak</t>
@@ -76,12 +77,51 @@
   </si>
   <si>
     <t>Fire-once</t>
+  </si>
+  <si>
+    <t>Communist organizers build national pressure while contesting control of individual states. The root event immediately seeds one Level 1 controlled state so the player sees the map layer and response decisions right away. The national spirit gives a small daily communist drift, and each communist-controlled state adds +0.01 daily communist support through dynamic pressure. States progress through Agitation Zone, Insurgent Stronghold, and Communist Lockdown levels; Level 3 creates a demilitarized revolutionary lockdown zone. Local military intervention works only on Levels 1-2; Disrupt Communist Organizing reduces national communist support; emergency national intervention affects all controlled states and can trigger a custom rebel country without vanilla stockpile splitting. A country-level defeat popup fires once controlled states are gone, rebels are not active, and communist support falls below the spread threshold. World Revolution stays locked until Whispers of the World Revolution is reached.</t>
+  </si>
+  <si>
+    <t>Unstable Revolutionary Activity: begins once any state is communist-controlled. Enables rare surprise revolts, including very rare one-state breakaway revolts with rebel armies scaled by state and country strength.</t>
+  </si>
+  <si>
+    <t>Dark Worker Rituals: begins once a Level 2 stronghold exists. Enables rare worker ritual incidents that disrupt a controlled state, raise intervention risk, improve later conversion chance, and slightly increase communist support.</t>
+  </si>
+  <si>
+    <t>Whispers of the World Revolution: begins once a Level 3 lockdown exists. Unlocks World Revolution for the major-event pool. Later whisper events add 200 World Revolution weight and mark states as more likely to join uprisings.</t>
+  </si>
+  <si>
+    <t>World Revolution later uses existing communist-controlled states as REV bases. Level 1, 2, and 3 states scale rebel strength differently, with extra units from industry, population, victory points, country strength, manpower, divisions, war status, and ideology pressure. Rebel unit templates include stronger armor, motorized, and cavalry formations, and names vary by major country plus shared regional and language pools where supported.</t>
+  </si>
+  <si>
+    <t>Evolution I Tier</t>
+  </si>
+  <si>
+    <t>Evolution II Tier</t>
+  </si>
+  <si>
+    <t>Evolution III Tier</t>
+  </si>
+  <si>
+    <t>Communist organizers build national pressure while contesting control of individual states. The root event immediately seeds one Level 1 controlled state so the player sees the map layer and response decisions right away. The national spirit gives a small daily communist drift, and each communist-controlled state adds +0.01 daily communist support through dynamic pressure. States progress through Agitation Zone, Insurgent Stronghold, and Communist Lockdown levels; Level 3 creates a demilitarized revolutionary lockdown zone. Local military intervention works only on Levels 1-2; Disrupt Communist Organizing reduces national communist support; emergency national intervention affects all controlled states and can trigger a custom rebel country without vanilla stockpile splitting. A country-level defeat popup can only fire after a 180-day country grace period, once controlled states are gone, rebels are not active, and communist support falls below the spread threshold. World Revolution stays locked until Whispers of the World Revolution is reached.</t>
+  </si>
+  <si>
+    <t>Gathering Storm</t>
+  </si>
+  <si>
+    <t>Rising Chaos</t>
+  </si>
+  <si>
+    <t>Chaos Tier</t>
+  </si>
+  <si>
+    <t>World Revolution later uses existing communist-controlled states as REV bases. Level 1, 2, and 3 states scale rebel strength differently, with extra units from industry, population, state priority, country strength, manpower, divisions, war status, and ideology pressure. Rebel unit templates include stronger armor, motorized, and cavalry formations, and names vary by major country plus shared regional and language pools where supported.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -91,12 +131,48 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4CCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="7">
@@ -181,7 +257,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -195,6 +271,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -407,34 +501,37 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Table Style 1" pivot="0" count="1" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Table Style 1" pivot="0" count="1" ns3:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="firstColumnStripe" dxfId="14"/>
     </tableStyle>
   </tableStyles>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:I2" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
-  <autoFilter ref="A1:I2" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Event Name" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Details" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Evolutions I" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Evolutions II" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Evolutions III" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Evolutions IV" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="World end" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:L3" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+  <autoFilter ref="A1:L3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000000000001}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000000000002}" name="Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000000000003}" name="Event Name"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000000000004}" name="Details"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000000000005}" name="Evolutions I"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000000000006}" name="Evolution I Tier"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000000000007}" name="Evolutions II"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000000000008}" name="Evolution II Tier"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000000000009}" name="Evolutions III"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-000000000010}" name="Evolution III Tier"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-000000000011}" name="Evolutions IV"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-000000000012}" name="World end"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="1" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -724,52 +821,66 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF188038"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="64" customWidth="1"/>
-    <col min="5" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="44" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="72" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="34" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="34" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="L1" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -779,14 +890,33 @@
       <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="6"/>
+      <c r="D2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="4"/>
+      <c r="L2" s="12" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="210" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -799,17 +929,26 @@
       <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="12" t="s">
         <v>15</v>
       </c>
     </row>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\klimp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\klim\projects\chaos_redux\docs\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{208223F6-78FE-4C7B-A1AD-9A8F9EDB59C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258FF301-4A1A-49CF-B218-A80F6D29A05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="611">
   <si>
     <t>ID</t>
   </si>
@@ -163,9 +163,6 @@
     <t>Final Silence is a world-end scenario only if the Holy Realm exists, is sovereign, has reached the final path, has armed the final doctrine through Ministry of Release authorization, has completed the warning chain, the year is 1945 or later, Chaos Meter is above 1000, the Holy Realm has the most factories in the world, strike capability exists, world-end settings allow it, and no other world-end is active. A 1947 thermonuclear variant applies if thermonuclear logic is available.</t>
   </si>
   <si>
-    <t>In progress</t>
-  </si>
-  <si>
     <t>Research (science)</t>
   </si>
   <si>
@@ -175,9 +172,6 @@
     <t>Random War</t>
   </si>
   <si>
-    <t>Random country declares war on another random country.</t>
-  </si>
-  <si>
     <t>Minor Repeatable</t>
   </si>
   <si>
@@ -193,9 +187,6 @@
     <t>Soviet Union Collapse</t>
   </si>
   <si>
-    <t xml:space="preserve">Soviet Union releases BLR and UKR, and some other countries. Those countries will get free divisions. Soviet Union gets decisions to reclaim the broken away states. The broken away states can form a coalition. </t>
-  </si>
-  <si>
     <t>Further collapse if the crisis is not managed.</t>
   </si>
   <si>
@@ -1811,6 +1802,60 @@
   </si>
   <si>
     <t>Happens on a friday,  everything is heavely discounted for one day. A rare event</t>
+  </si>
+  <si>
+    <t>Gathering Storm: Triangular Incident. Three declarations fire in one linked dispute.</t>
+  </si>
+  <si>
+    <t>Rising Chaos: Four Fronts. Four declarations fire in one conflict web, with a small chance for a compatible special country to appear.</t>
+  </si>
+  <si>
+    <t>Chaos Tier: Contagious Ultimatums. Five declarations fire, major countries and faction members become more likely, and special-country involvement becomes more common.</t>
+  </si>
+  <si>
+    <t>Totalen Chaos: The War Week. Six declarations fire in a short chain, with a strong chance of one compatible special country participating.</t>
+  </si>
+  <si>
+    <t>World Collapse: Open Season. Seven to eight declarations fire while normal random events still run. Compatible special countries are strongly favored when available.</t>
+  </si>
+  <si>
+    <t>SCN-001</t>
+  </si>
+  <si>
+    <t>Zombie Apocalypse</t>
+  </si>
+  <si>
+    <t>Triggerable scenario. Manual setup launched from the Chaos Redux scenario window. Type controls outbreak profile/structure; intensity controls outbreak count, starting affected states, divisions, and early pressure.</t>
+  </si>
+  <si>
+    <t>Manual triggerable scenario</t>
+  </si>
+  <si>
+    <t>Manual Scenario</t>
+  </si>
+  <si>
+    <t>Implemented</t>
+  </si>
+  <si>
+    <t>SCN-002</t>
+  </si>
+  <si>
+    <t>Army of Mengele Clones</t>
+  </si>
+  <si>
+    <t>Triggerable scenario. Manual setup launched from the Chaos Redux scenario window. Type switches between the standard clone army and the stronger Aryan variant; intensity controls starting territory, division count, army strength, equipment, and neighboring pressure.</t>
+  </si>
+  <si>
+    <t>A random eligible country declares war on another eligible country. Higher chaos stages create larger linked war webs. Compatible special countries can appear in later stages.</t>
+  </si>
+  <si>
+    <t>Repeatable Wars cluster.</t>
+  </si>
+  <si>
+    <t>4, (later add more)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soviet Union releases some countries inside its territory, and more countries through like crisis maybe if not contained. Those countries will get free divisions, so that the soviet union wouldn't be able to invade them easily right away. Soviet Union gets decisions to reclaim the broken away states. The broken away states can form a coalition (like a faction to fight the soviet union), their goal is to completely make every possible country inside soviet union a free democratic country. </t>
   </si>
 </sst>
 </file>
@@ -1891,22 +1936,6 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF9B3642"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF9B3642"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF9B3642"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF9B3642"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -1970,19 +1999,35 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9B3642"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9B3642"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9B3642"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9B3642"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="2">
     <tableStyle name="Main Sheet-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
-      <tableStyleElement type="firstRowStripe" dxfId="6"/>
-      <tableStyleElement type="secondRowStripe" dxfId="5"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="firstRowStripe" dxfId="5"/>
+      <tableStyleElement type="secondRowStripe" dxfId="4"/>
     </tableStyle>
     <tableStyle name="Main Sheet-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
-      <tableStyleElement type="headerRow" dxfId="3"/>
-      <tableStyleElement type="firstRowStripe" dxfId="2"/>
-      <tableStyleElement type="secondRowStripe" dxfId="1"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="0"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2427,10 +2472,10 @@
         <v>22</v>
       </c>
       <c r="L4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
@@ -2443,54 +2488,68 @@
     </row>
     <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>49</v>
-      </c>
       <c r="C5" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+        <v>607</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>597</v>
+      </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
+      <c r="O5" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>609</v>
+      </c>
       <c r="Q5" s="8">
         <v>2</v>
       </c>
       <c r="R5" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>56</v>
+        <v>610</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
@@ -2499,10 +2558,10 @@
         <v>22</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -2515,13 +2574,13 @@
     </row>
     <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -2531,13 +2590,13 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -2550,13 +2609,13 @@
     </row>
     <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -2566,16 +2625,16 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P8" s="8"/>
       <c r="Q8" s="8">
@@ -2587,13 +2646,13 @@
     </row>
     <row r="9" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -2603,13 +2662,13 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -2622,13 +2681,13 @@
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -2638,13 +2697,13 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -2657,13 +2716,13 @@
     </row>
     <row r="11" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -2676,13 +2735,13 @@
         <v>22</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="8">
@@ -2694,13 +2753,13 @@
     </row>
     <row r="12" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -2713,13 +2772,13 @@
         <v>22</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="8">
@@ -2731,13 +2790,13 @@
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -2750,10 +2809,10 @@
         <v>22</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -2766,31 +2825,31 @@
     </row>
     <row r="14" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -2803,13 +2862,13 @@
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -2819,16 +2878,16 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="8">
@@ -2840,13 +2899,13 @@
     </row>
     <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -2856,21 +2915,21 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -2883,18 +2942,18 @@
         <v>22</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -2904,21 +2963,21 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -2928,21 +2987,21 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="K19" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -2952,27 +3011,27 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
@@ -2981,18 +3040,18 @@
         <v>22</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -3002,24 +3061,24 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -3032,18 +3091,18 @@
         <v>22</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -3056,18 +3115,18 @@
         <v>22</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -3080,18 +3139,18 @@
         <v>22</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -3104,18 +3163,18 @@
         <v>34</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -3128,18 +3187,18 @@
         <v>22</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -3152,18 +3211,18 @@
         <v>22</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -3173,21 +3232,21 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -3197,27 +3256,27 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
@@ -3226,18 +3285,18 @@
         <v>34</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -3247,21 +3306,21 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
       <c r="K32" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -3271,21 +3330,21 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
       <c r="K33" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -3295,21 +3354,21 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -3319,21 +3378,21 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
       <c r="K35" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -3343,21 +3402,21 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
       <c r="K36" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -3367,21 +3426,21 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -3391,27 +3450,27 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
@@ -3420,18 +3479,18 @@
         <v>22</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -3441,21 +3500,21 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -3465,21 +3524,21 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -3489,21 +3548,21 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -3513,21 +3572,21 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -3537,21 +3596,21 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
@@ -3564,18 +3623,18 @@
         <v>34</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -3588,18 +3647,18 @@
         <v>22</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -3609,21 +3668,21 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="K47" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
@@ -3633,21 +3692,21 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -3660,18 +3719,18 @@
         <v>22</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -3684,18 +3743,18 @@
         <v>34</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
@@ -3705,21 +3764,21 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
       <c r="K51" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -3732,18 +3791,18 @@
         <v>22</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -3753,21 +3812,21 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -3780,18 +3839,18 @@
         <v>22</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -3801,21 +3860,21 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
       <c r="K55" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -3825,21 +3884,21 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
       <c r="K56" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
@@ -3849,21 +3908,21 @@
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
       <c r="K57" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -3873,21 +3932,21 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
       <c r="K58" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
@@ -3897,21 +3956,21 @@
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
@@ -3924,18 +3983,18 @@
         <v>22</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -3945,21 +4004,21 @@
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
       <c r="K61" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -3969,21 +4028,21 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
       <c r="K62" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -3993,21 +4052,21 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
       <c r="K63" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -4017,21 +4076,21 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
       <c r="K64" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -4041,21 +4100,21 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -4065,21 +4124,21 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
       <c r="K66" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -4089,21 +4148,21 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
       <c r="K67" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -4116,24 +4175,24 @@
         <v>22</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -4142,18 +4201,18 @@
         <v>22</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -4166,18 +4225,18 @@
         <v>22</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -4190,18 +4249,18 @@
         <v>34</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -4214,18 +4273,18 @@
         <v>22</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -4238,18 +4297,18 @@
         <v>22</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -4262,18 +4321,18 @@
         <v>22</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -4286,18 +4345,18 @@
         <v>22</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -4310,18 +4369,18 @@
         <v>22</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -4331,21 +4390,21 @@
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
       <c r="K77" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
@@ -4355,21 +4414,21 @@
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
       <c r="K78" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
@@ -4379,21 +4438,21 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
       <c r="K79" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -4403,21 +4462,21 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
       <c r="K80" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -4430,18 +4489,18 @@
         <v>34</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -4454,18 +4513,18 @@
         <v>22</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
@@ -4475,21 +4534,21 @@
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
       <c r="K83" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
@@ -4499,21 +4558,21 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
       <c r="K84" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
@@ -4523,21 +4582,21 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
       <c r="K85" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
@@ -4547,21 +4606,21 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
       <c r="K86" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
@@ -4574,18 +4633,18 @@
         <v>22</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -4595,21 +4654,21 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
       <c r="K88" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
@@ -4622,18 +4681,18 @@
         <v>22</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
@@ -4646,18 +4705,18 @@
         <v>22</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
@@ -4670,24 +4729,24 @@
         <v>22</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
@@ -4696,18 +4755,18 @@
         <v>34</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
@@ -4720,18 +4779,18 @@
         <v>22</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
@@ -4744,18 +4803,18 @@
         <v>22</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
@@ -4765,21 +4824,21 @@
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
       <c r="K95" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
@@ -4789,21 +4848,21 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
       <c r="K96" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
@@ -4813,21 +4872,21 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
       <c r="K97" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
@@ -4837,21 +4896,21 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
       <c r="K98" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
@@ -4864,18 +4923,18 @@
         <v>22</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
@@ -4888,18 +4947,18 @@
         <v>22</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
@@ -4915,13 +4974,13 @@
     </row>
     <row r="102" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
@@ -4937,13 +4996,13 @@
     </row>
     <row r="103" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
@@ -4959,13 +5018,13 @@
     </row>
     <row r="104" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
@@ -4981,13 +5040,13 @@
     </row>
     <row r="105" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
@@ -5003,13 +5062,13 @@
     </row>
     <row r="106" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
@@ -5025,13 +5084,13 @@
     </row>
     <row r="107" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
@@ -5047,13 +5106,13 @@
     </row>
     <row r="108" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
@@ -5069,13 +5128,13 @@
     </row>
     <row r="109" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
@@ -5091,13 +5150,13 @@
     </row>
     <row r="110" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
@@ -5113,13 +5172,13 @@
     </row>
     <row r="111" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
@@ -5135,13 +5194,13 @@
     </row>
     <row r="112" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
@@ -5157,13 +5216,13 @@
     </row>
     <row r="113" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
@@ -5179,13 +5238,13 @@
     </row>
     <row r="114" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
@@ -5201,13 +5260,13 @@
     </row>
     <row r="115" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
@@ -5223,13 +5282,13 @@
     </row>
     <row r="116" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
@@ -5245,13 +5304,13 @@
     </row>
     <row r="117" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
@@ -5267,13 +5326,13 @@
     </row>
     <row r="118" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
@@ -5289,13 +5348,13 @@
     </row>
     <row r="119" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
@@ -5311,13 +5370,13 @@
     </row>
     <row r="120" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
@@ -5333,13 +5392,13 @@
     </row>
     <row r="121" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
@@ -5355,13 +5414,13 @@
     </row>
     <row r="122" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
@@ -5377,13 +5436,13 @@
     </row>
     <row r="123" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
@@ -5399,13 +5458,13 @@
     </row>
     <row r="124" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
@@ -5421,13 +5480,13 @@
     </row>
     <row r="125" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
@@ -5443,13 +5502,13 @@
     </row>
     <row r="126" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
@@ -5465,13 +5524,13 @@
     </row>
     <row r="127" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
@@ -5487,13 +5546,13 @@
     </row>
     <row r="128" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
@@ -5509,13 +5568,13 @@
     </row>
     <row r="129" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
@@ -5531,13 +5590,13 @@
     </row>
     <row r="130" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
@@ -5553,13 +5612,13 @@
     </row>
     <row r="131" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
@@ -5575,13 +5634,13 @@
     </row>
     <row r="132" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
@@ -5597,13 +5656,13 @@
     </row>
     <row r="133" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
@@ -5619,13 +5678,13 @@
     </row>
     <row r="134" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
@@ -5641,13 +5700,13 @@
     </row>
     <row r="135" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
@@ -5663,13 +5722,13 @@
     </row>
     <row r="136" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
@@ -5685,13 +5744,13 @@
     </row>
     <row r="137" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
@@ -5707,13 +5766,13 @@
     </row>
     <row r="138" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
@@ -5729,13 +5788,13 @@
     </row>
     <row r="139" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
@@ -5751,13 +5810,13 @@
     </row>
     <row r="140" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
@@ -5773,13 +5832,13 @@
     </row>
     <row r="141" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
@@ -5795,13 +5854,13 @@
     </row>
     <row r="142" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
@@ -5817,13 +5876,13 @@
     </row>
     <row r="143" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -5839,13 +5898,13 @@
     </row>
     <row r="144" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
@@ -5861,13 +5920,13 @@
     </row>
     <row r="145" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
@@ -5883,13 +5942,13 @@
     </row>
     <row r="146" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
@@ -5905,13 +5964,13 @@
     </row>
     <row r="147" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
@@ -5927,13 +5986,13 @@
     </row>
     <row r="148" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
@@ -5949,13 +6008,13 @@
     </row>
     <row r="149" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
@@ -5971,13 +6030,13 @@
     </row>
     <row r="150" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
@@ -5993,13 +6052,13 @@
     </row>
     <row r="151" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
@@ -6015,19 +6074,19 @@
     </row>
     <row r="152" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
@@ -6039,13 +6098,13 @@
     </row>
     <row r="153" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
@@ -6061,13 +6120,13 @@
     </row>
     <row r="154" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
@@ -6083,13 +6142,13 @@
     </row>
     <row r="155" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
@@ -6105,13 +6164,13 @@
     </row>
     <row r="156" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
@@ -6127,13 +6186,13 @@
     </row>
     <row r="157" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
@@ -6149,13 +6208,13 @@
     </row>
     <row r="158" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
@@ -6171,13 +6230,13 @@
     </row>
     <row r="159" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
@@ -6193,13 +6252,13 @@
     </row>
     <row r="160" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
@@ -6215,13 +6274,13 @@
     </row>
     <row r="161" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
@@ -6237,19 +6296,19 @@
     </row>
     <row r="162" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
@@ -6261,13 +6320,13 @@
     </row>
     <row r="163" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
@@ -6283,13 +6342,13 @@
     </row>
     <row r="164" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
@@ -6305,13 +6364,13 @@
     </row>
     <row r="165" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
@@ -6327,13 +6386,13 @@
     </row>
     <row r="166" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
@@ -6349,13 +6408,13 @@
     </row>
     <row r="167" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
@@ -6374,10 +6433,10 @@
     <row r="168" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="5"/>
       <c r="B168" s="5" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
@@ -6392,10 +6451,10 @@
     <row r="169" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="5"/>
       <c r="B169" s="5" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
@@ -6410,10 +6469,10 @@
     <row r="170" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="5"/>
       <c r="B170" s="5" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
@@ -6428,10 +6487,10 @@
     <row r="171" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="5"/>
       <c r="B171" s="5" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
@@ -6446,10 +6505,10 @@
     <row r="172" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="5"/>
       <c r="B172" s="5" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
@@ -6464,16 +6523,16 @@
     <row r="173" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="5"/>
       <c r="B173" s="5" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
@@ -6484,10 +6543,10 @@
     <row r="174" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="5"/>
       <c r="B174" s="5" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
@@ -6502,10 +6561,10 @@
     <row r="175" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="5" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
@@ -6520,10 +6579,10 @@
     <row r="176" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="5" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
@@ -6538,10 +6597,10 @@
     <row r="177" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="5" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
@@ -6556,10 +6615,10 @@
     <row r="178" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
@@ -6574,10 +6633,10 @@
     <row r="179" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="5" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
@@ -6592,10 +6651,10 @@
     <row r="180" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="5" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
@@ -6610,10 +6669,10 @@
     <row r="181" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="5" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
@@ -6628,10 +6687,10 @@
     <row r="182" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="5" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
@@ -6646,10 +6705,10 @@
     <row r="183" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="5" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
@@ -18310,20 +18369,14 @@
       <c r="L1015" s="6"/>
     </row>
     <row r="1016" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1016" s="5" t="inlineStr">
-        <is>
-          <t>SCN-001</t>
-        </is>
-      </c>
-      <c r="B1016" s="5" t="inlineStr">
-        <is>
-          <t>Zombie Apocalypse</t>
-        </is>
-      </c>
-      <c r="C1016" s="5" t="inlineStr">
-        <is>
-          <t>Triggerable scenario. Manual setup launched from the Chaos Redux scenario window. Type controls outbreak profile/structure; intensity controls outbreak count, starting affected states, divisions, and early pressure.</t>
-        </is>
+      <c r="A1016" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="B1016" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="C1016" s="5" t="s">
+        <v>600</v>
       </c>
       <c r="D1016" s="6"/>
       <c r="E1016" s="6"/>
@@ -18331,37 +18384,25 @@
       <c r="G1016" s="6"/>
       <c r="H1016" s="6"/>
       <c r="I1016" s="6"/>
-      <c r="J1016" s="6" t="inlineStr">
-        <is>
-          <t>Manual triggerable scenario</t>
-        </is>
-      </c>
-      <c r="K1016" s="6" t="inlineStr">
-        <is>
-          <t>Manual Scenario</t>
-        </is>
-      </c>
-      <c r="L1016" s="6" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
+      <c r="J1016" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="K1016" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="L1016" s="6" t="s">
+        <v>603</v>
       </c>
     </row>
     <row r="1017" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1017" s="5" t="inlineStr">
-        <is>
-          <t>SCN-002</t>
-        </is>
-      </c>
-      <c r="B1017" s="5" t="inlineStr">
-        <is>
-          <t>Army of Mengele Clones</t>
-        </is>
-      </c>
-      <c r="C1017" s="5" t="inlineStr">
-        <is>
-          <t>Triggerable scenario. Manual setup launched from the Chaos Redux scenario window. Type switches between the standard clone army and the stronger Aryan variant; intensity controls starting territory, division count, army strength, equipment, and neighboring pressure.</t>
-        </is>
+      <c r="A1017" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="B1017" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="C1017" s="5" t="s">
+        <v>606</v>
       </c>
       <c r="D1017" s="6"/>
       <c r="E1017" s="6"/>
@@ -18369,20 +18410,14 @@
       <c r="G1017" s="6"/>
       <c r="H1017" s="6"/>
       <c r="I1017" s="6"/>
-      <c r="J1017" s="6" t="inlineStr">
-        <is>
-          <t>Manual triggerable scenario</t>
-        </is>
-      </c>
-      <c r="K1017" s="6" t="inlineStr">
-        <is>
-          <t>Manual Scenario</t>
-        </is>
-      </c>
-      <c r="L1017" s="6" t="inlineStr">
-        <is>
-          <t>Implemented</t>
-        </is>
+      <c r="J1017" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="K1017" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="L1017" s="6" t="s">
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\klim\projects\chaos_redux\docs\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{258FF301-4A1A-49CF-B218-A80F6D29A05D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654CBF13-214A-458E-AFA9-9C0DD2C2BB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="891" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="610">
   <si>
     <t>ID</t>
   </si>
@@ -187,9 +187,6 @@
     <t>Soviet Union Collapse</t>
   </si>
   <si>
-    <t>Further collapse if the crisis is not managed.</t>
-  </si>
-  <si>
     <t>Diseases</t>
   </si>
   <si>
@@ -199,9 +196,6 @@
     <t>Independence Wave</t>
   </si>
   <si>
-    <t>Three random countries that do not exist will declare their independence.</t>
-  </si>
-  <si>
     <t>Aliens</t>
   </si>
   <si>
@@ -1855,7 +1849,10 @@
     <t>4, (later add more)</t>
   </si>
   <si>
-    <t xml:space="preserve">Soviet Union releases some countries inside its territory, and more countries through like crisis maybe if not contained. Those countries will get free divisions, so that the soviet union wouldn't be able to invade them easily right away. Soviet Union gets decisions to reclaim the broken away states. The broken away states can form a coalition (like a faction to fight the soviet union), their goal is to completely make every possible country inside soviet union a free democratic country. </t>
+    <t>to be reworked</t>
+  </si>
+  <si>
+    <t>Liberations</t>
   </si>
 </sst>
 </file>
@@ -2062,7 +2059,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Event_Clusters" displayName="Event_Clusters" ref="N1:R15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Event_Clusters" displayName="Event_Clusters" ref="N1:R16">
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Cluster Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Details"/>
@@ -2494,22 +2491,22 @@
         <v>48</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>593</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>594</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>595</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>596</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>597</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
@@ -2523,10 +2520,10 @@
         <v>51</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="Q5" s="8">
         <v>2</v>
@@ -2543,14 +2540,12 @@
         <v>53</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="G6" s="6"/>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
@@ -2561,7 +2556,7 @@
         <v>50</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
@@ -2574,13 +2569,13 @@
     </row>
     <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C7" s="5" t="s">
-        <v>58</v>
+        <v>608</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -2596,7 +2591,7 @@
         <v>50</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -2609,13 +2604,13 @@
     </row>
     <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>62</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -2631,10 +2626,10 @@
         <v>50</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P8" s="8"/>
       <c r="Q8" s="8">
@@ -2646,13 +2641,13 @@
     </row>
     <row r="9" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>67</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -2668,7 +2663,7 @@
         <v>50</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -2681,13 +2676,13 @@
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>69</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>71</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -2703,7 +2698,7 @@
         <v>50</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -2716,13 +2711,13 @@
     </row>
     <row r="11" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -2738,10 +2733,10 @@
         <v>50</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="8">
@@ -2753,13 +2748,13 @@
     </row>
     <row r="12" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -2775,10 +2770,10 @@
         <v>50</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="8">
@@ -2790,13 +2785,13 @@
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -2812,7 +2807,7 @@
         <v>50</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -2825,19 +2820,19 @@
     </row>
     <row r="14" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -2849,7 +2844,7 @@
         <v>50</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -2862,13 +2857,13 @@
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>93</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -2884,10 +2879,10 @@
         <v>50</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="8">
@@ -2899,13 +2894,13 @@
     </row>
     <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -2920,16 +2915,25 @@
       <c r="L16" s="6" t="s">
         <v>50</v>
       </c>
+      <c r="N16" t="s">
+        <v>609</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
+      </c>
+      <c r="R16" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -2947,13 +2951,13 @@
     </row>
     <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>102</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>104</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -2971,13 +2975,13 @@
     </row>
     <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>105</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -2995,13 +2999,13 @@
     </row>
     <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>110</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -3019,19 +3023,19 @@
     </row>
     <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
@@ -3045,13 +3049,13 @@
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -3067,18 +3071,18 @@
         <v>50</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>121</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -3096,13 +3100,13 @@
     </row>
     <row r="24" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>122</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>124</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -3120,13 +3124,13 @@
     </row>
     <row r="25" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>127</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -3144,13 +3148,13 @@
     </row>
     <row r="26" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>128</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -3168,13 +3172,13 @@
     </row>
     <row r="27" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>131</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>133</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -3192,13 +3196,13 @@
     </row>
     <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -3216,13 +3220,13 @@
     </row>
     <row r="29" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>139</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -3240,13 +3244,13 @@
     </row>
     <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>140</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>142</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -3264,19 +3268,19 @@
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
@@ -3290,13 +3294,13 @@
     </row>
     <row r="32" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>147</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -3314,13 +3318,13 @@
     </row>
     <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>150</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -3338,13 +3342,13 @@
     </row>
     <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>155</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -3362,13 +3366,13 @@
     </row>
     <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>158</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -3386,13 +3390,13 @@
     </row>
     <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -3410,13 +3414,13 @@
     </row>
     <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>162</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -3434,13 +3438,13 @@
     </row>
     <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -3458,19 +3462,19 @@
     </row>
     <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
@@ -3484,13 +3488,13 @@
     </row>
     <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -3508,13 +3512,13 @@
     </row>
     <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -3532,13 +3536,13 @@
     </row>
     <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>180</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -3556,13 +3560,13 @@
     </row>
     <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>181</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>183</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -3580,13 +3584,13 @@
     </row>
     <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>184</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -3604,13 +3608,13 @@
     </row>
     <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>187</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
@@ -3628,13 +3632,13 @@
     </row>
     <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -3652,13 +3656,13 @@
     </row>
     <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>195</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -3676,13 +3680,13 @@
     </row>
     <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>198</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
@@ -3700,13 +3704,13 @@
     </row>
     <row r="49" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>199</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -3724,13 +3728,13 @@
     </row>
     <row r="50" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -3748,13 +3752,13 @@
     </row>
     <row r="51" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>205</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
@@ -3772,13 +3776,13 @@
     </row>
     <row r="52" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>208</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>210</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -3796,13 +3800,13 @@
     </row>
     <row r="53" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -3820,13 +3824,13 @@
     </row>
     <row r="54" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -3844,13 +3848,13 @@
     </row>
     <row r="55" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>219</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -3868,13 +3872,13 @@
     </row>
     <row r="56" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -3892,13 +3896,13 @@
     </row>
     <row r="57" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>225</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
@@ -3916,13 +3920,13 @@
     </row>
     <row r="58" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="C58" s="5" t="s">
-        <v>228</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -3940,13 +3944,13 @@
     </row>
     <row r="59" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>231</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
@@ -3964,13 +3968,13 @@
     </row>
     <row r="60" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
@@ -3988,13 +3992,13 @@
     </row>
     <row r="61" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -4012,13 +4016,13 @@
     </row>
     <row r="62" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>240</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -4036,13 +4040,13 @@
     </row>
     <row r="63" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>243</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -4060,13 +4064,13 @@
     </row>
     <row r="64" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>246</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -4084,13 +4088,13 @@
     </row>
     <row r="65" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -4108,13 +4112,13 @@
     </row>
     <row r="66" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>250</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -4132,13 +4136,13 @@
     </row>
     <row r="67" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>253</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>255</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -4156,13 +4160,13 @@
     </row>
     <row r="68" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -4180,19 +4184,19 @@
     </row>
     <row r="69" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>259</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>261</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -4206,13 +4210,13 @@
     </row>
     <row r="70" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>263</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C70" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -4230,13 +4234,13 @@
     </row>
     <row r="71" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>266</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -4254,13 +4258,13 @@
     </row>
     <row r="72" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>269</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -4278,13 +4282,13 @@
     </row>
     <row r="73" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>272</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>274</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -4302,13 +4306,13 @@
     </row>
     <row r="74" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>277</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -4326,13 +4330,13 @@
     </row>
     <row r="75" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -4350,13 +4354,13 @@
     </row>
     <row r="76" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -4374,13 +4378,13 @@
     </row>
     <row r="77" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>284</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>286</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -4398,13 +4402,13 @@
     </row>
     <row r="78" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>289</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
@@ -4422,13 +4426,13 @@
     </row>
     <row r="79" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>292</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
@@ -4446,13 +4450,13 @@
     </row>
     <row r="80" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>293</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>295</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -4470,13 +4474,13 @@
     </row>
     <row r="81" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>296</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>298</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -4494,13 +4498,13 @@
     </row>
     <row r="82" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="C82" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -4518,13 +4522,13 @@
     </row>
     <row r="83" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
@@ -4542,13 +4546,13 @@
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>305</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>307</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
@@ -4566,13 +4570,13 @@
     </row>
     <row r="85" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>308</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>310</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
@@ -4590,13 +4594,13 @@
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>313</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
@@ -4614,13 +4618,13 @@
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>314</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>316</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
@@ -4638,13 +4642,13 @@
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>317</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>319</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -4662,13 +4666,13 @@
     </row>
     <row r="89" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>320</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>322</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
@@ -4686,13 +4690,13 @@
     </row>
     <row r="90" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>323</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>325</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
@@ -4710,13 +4714,13 @@
     </row>
     <row r="91" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>326</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>328</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
@@ -4734,19 +4738,19 @@
     </row>
     <row r="92" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>329</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>331</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
@@ -4760,13 +4764,13 @@
     </row>
     <row r="93" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>333</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>335</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
@@ -4784,13 +4788,13 @@
     </row>
     <row r="94" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>336</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>338</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
@@ -4808,13 +4812,13 @@
     </row>
     <row r="95" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>341</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
@@ -4832,13 +4836,13 @@
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C96" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>344</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
@@ -4856,13 +4860,13 @@
     </row>
     <row r="97" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>345</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>347</v>
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
@@ -4880,13 +4884,13 @@
     </row>
     <row r="98" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>348</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>350</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
@@ -4904,13 +4908,13 @@
     </row>
     <row r="99" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>351</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>353</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
@@ -4928,13 +4932,13 @@
     </row>
     <row r="100" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C100" s="5" t="s">
         <v>354</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>356</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
@@ -4952,13 +4956,13 @@
     </row>
     <row r="101" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>357</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>359</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
@@ -4974,13 +4978,13 @@
     </row>
     <row r="102" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>360</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>362</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
@@ -4996,13 +5000,13 @@
     </row>
     <row r="103" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C103" s="5" t="s">
         <v>363</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>365</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
@@ -5018,13 +5022,13 @@
     </row>
     <row r="104" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="C104" s="5" t="s">
         <v>366</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>368</v>
       </c>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
@@ -5040,13 +5044,13 @@
     </row>
     <row r="105" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C105" s="5" t="s">
         <v>369</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>371</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
@@ -5062,13 +5066,13 @@
     </row>
     <row r="106" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>372</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>374</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
@@ -5084,13 +5088,13 @@
     </row>
     <row r="107" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>375</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>377</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
@@ -5106,13 +5110,13 @@
     </row>
     <row r="108" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>378</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>380</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
@@ -5128,13 +5132,13 @@
     </row>
     <row r="109" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>381</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>383</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
@@ -5150,13 +5154,13 @@
     </row>
     <row r="110" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>384</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>386</v>
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
@@ -5172,13 +5176,13 @@
     </row>
     <row r="111" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>387</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>389</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
@@ -5194,13 +5198,13 @@
     </row>
     <row r="112" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="C112" s="5" t="s">
         <v>390</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>392</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
@@ -5216,13 +5220,13 @@
     </row>
     <row r="113" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="C113" s="5" t="s">
         <v>393</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>395</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
@@ -5238,13 +5242,13 @@
     </row>
     <row r="114" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="C114" s="5" t="s">
         <v>396</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>398</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
@@ -5260,13 +5264,13 @@
     </row>
     <row r="115" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>399</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>401</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
@@ -5282,13 +5286,13 @@
     </row>
     <row r="116" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>402</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>404</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
@@ -5304,13 +5308,13 @@
     </row>
     <row r="117" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="C117" s="5" t="s">
         <v>405</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>407</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
@@ -5326,13 +5330,13 @@
     </row>
     <row r="118" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>407</v>
+      </c>
+      <c r="C118" s="5" t="s">
         <v>408</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>410</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
@@ -5348,13 +5352,13 @@
     </row>
     <row r="119" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C119" s="5" t="s">
         <v>411</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>413</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
@@ -5370,13 +5374,13 @@
     </row>
     <row r="120" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>414</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>416</v>
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
@@ -5392,13 +5396,13 @@
     </row>
     <row r="121" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C121" s="5" t="s">
         <v>417</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>419</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
@@ -5414,13 +5418,13 @@
     </row>
     <row r="122" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="C122" s="5" t="s">
         <v>420</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>422</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
@@ -5436,13 +5440,13 @@
     </row>
     <row r="123" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="C123" s="5" t="s">
         <v>423</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>425</v>
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
@@ -5458,13 +5462,13 @@
     </row>
     <row r="124" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="C124" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>428</v>
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
@@ -5480,13 +5484,13 @@
     </row>
     <row r="125" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>429</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>431</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
@@ -5502,13 +5506,13 @@
     </row>
     <row r="126" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="C126" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>434</v>
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
@@ -5524,13 +5528,13 @@
     </row>
     <row r="127" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="C127" s="5" t="s">
         <v>435</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>437</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
@@ -5546,13 +5550,13 @@
     </row>
     <row r="128" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="C128" s="5" t="s">
         <v>438</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>440</v>
       </c>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
@@ -5568,13 +5572,13 @@
     </row>
     <row r="129" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>441</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>443</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
@@ -5590,13 +5594,13 @@
     </row>
     <row r="130" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="C130" s="5" t="s">
         <v>444</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>446</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
@@ -5612,13 +5616,13 @@
     </row>
     <row r="131" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="C131" s="5" t="s">
         <v>447</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>449</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
@@ -5634,13 +5638,13 @@
     </row>
     <row r="132" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="C132" s="5" t="s">
         <v>450</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
@@ -5656,13 +5660,13 @@
     </row>
     <row r="133" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C133" s="5" t="s">
         <v>453</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>454</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>455</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
@@ -5678,13 +5682,13 @@
     </row>
     <row r="134" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C134" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>458</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
@@ -5700,13 +5704,13 @@
     </row>
     <row r="135" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="C135" s="5" t="s">
         <v>459</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>460</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>461</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
@@ -5722,13 +5726,13 @@
     </row>
     <row r="136" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>462</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>464</v>
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
@@ -5744,13 +5748,13 @@
     </row>
     <row r="137" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C137" s="5" t="s">
         <v>465</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>467</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
@@ -5766,13 +5770,13 @@
     </row>
     <row r="138" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="C138" s="5" t="s">
         <v>468</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>470</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
@@ -5788,13 +5792,13 @@
     </row>
     <row r="139" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>470</v>
+      </c>
+      <c r="C139" s="5" t="s">
         <v>471</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>472</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>473</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
@@ -5810,13 +5814,13 @@
     </row>
     <row r="140" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="C140" s="5" t="s">
         <v>474</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>475</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>476</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
@@ -5832,13 +5836,13 @@
     </row>
     <row r="141" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="C141" s="5" t="s">
         <v>477</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>478</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
@@ -5854,13 +5858,13 @@
     </row>
     <row r="142" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="C142" s="5" t="s">
         <v>480</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>481</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>482</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
@@ -5876,13 +5880,13 @@
     </row>
     <row r="143" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C143" s="5" t="s">
         <v>483</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>484</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>485</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -5898,13 +5902,13 @@
     </row>
     <row r="144" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="C144" s="5" t="s">
         <v>486</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>487</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>488</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
@@ -5920,13 +5924,13 @@
     </row>
     <row r="145" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>488</v>
+      </c>
+      <c r="C145" s="5" t="s">
         <v>489</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>490</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>491</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
@@ -5942,13 +5946,13 @@
     </row>
     <row r="146" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>491</v>
+      </c>
+      <c r="C146" s="5" t="s">
         <v>492</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>493</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>494</v>
       </c>
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
@@ -5964,13 +5968,13 @@
     </row>
     <row r="147" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>494</v>
+      </c>
+      <c r="C147" s="5" t="s">
         <v>495</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>497</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
@@ -5986,13 +5990,13 @@
     </row>
     <row r="148" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="C148" s="5" t="s">
         <v>498</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>500</v>
       </c>
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
@@ -6008,13 +6012,13 @@
     </row>
     <row r="149" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C149" s="5" t="s">
         <v>501</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>502</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>503</v>
       </c>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
@@ -6030,13 +6034,13 @@
     </row>
     <row r="150" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C150" s="5" t="s">
         <v>504</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>506</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
@@ -6052,13 +6056,13 @@
     </row>
     <row r="151" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="C151" s="5" t="s">
         <v>507</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>508</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>509</v>
       </c>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
@@ -6074,19 +6078,19 @@
     </row>
     <row r="152" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="C152" s="5" t="s">
         <v>510</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>511</v>
-      </c>
-      <c r="C152" s="5" t="s">
-        <v>512</v>
       </c>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
@@ -6098,13 +6102,13 @@
     </row>
     <row r="153" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="C153" s="5" t="s">
         <v>514</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>515</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>516</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
@@ -6120,13 +6124,13 @@
     </row>
     <row r="154" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="C154" s="5" t="s">
         <v>517</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>519</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
@@ -6142,13 +6146,13 @@
     </row>
     <row r="155" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="C155" s="5" t="s">
         <v>520</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>522</v>
       </c>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
@@ -6164,13 +6168,13 @@
     </row>
     <row r="156" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="C156" s="5" t="s">
         <v>523</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>525</v>
       </c>
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
@@ -6186,13 +6190,13 @@
     </row>
     <row r="157" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="C157" s="5" t="s">
         <v>526</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>528</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
@@ -6208,13 +6212,13 @@
     </row>
     <row r="158" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="C158" s="5" t="s">
         <v>529</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>531</v>
       </c>
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
@@ -6230,13 +6234,13 @@
     </row>
     <row r="159" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="C159" s="5" t="s">
         <v>532</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>534</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
@@ -6252,13 +6256,13 @@
     </row>
     <row r="160" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="C160" s="5" t="s">
         <v>535</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>537</v>
       </c>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
@@ -6274,13 +6278,13 @@
     </row>
     <row r="161" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="C161" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="B161" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>540</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
@@ -6296,19 +6300,19 @@
     </row>
     <row r="162" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="C162" s="5" t="s">
         <v>541</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>543</v>
       </c>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
@@ -6320,13 +6324,13 @@
     </row>
     <row r="163" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="C163" s="5" t="s">
         <v>545</v>
-      </c>
-      <c r="B163" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>547</v>
       </c>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
@@ -6342,13 +6346,13 @@
     </row>
     <row r="164" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="C164" s="5" t="s">
         <v>548</v>
-      </c>
-      <c r="B164" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>550</v>
       </c>
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
@@ -6364,13 +6368,13 @@
     </row>
     <row r="165" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="C165" s="5" t="s">
         <v>551</v>
-      </c>
-      <c r="B165" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="C165" s="5" t="s">
-        <v>553</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
@@ -6386,13 +6390,13 @@
     </row>
     <row r="166" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="C166" s="5" t="s">
         <v>554</v>
-      </c>
-      <c r="B166" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>556</v>
       </c>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
@@ -6408,13 +6412,13 @@
     </row>
     <row r="167" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="C167" s="5" t="s">
         <v>557</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>558</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>559</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
@@ -6433,10 +6437,10 @@
     <row r="168" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="5"/>
       <c r="B168" s="5" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
@@ -6451,10 +6455,10 @@
     <row r="169" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="5"/>
       <c r="B169" s="5" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
@@ -6469,10 +6473,10 @@
     <row r="170" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="5"/>
       <c r="B170" s="5" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
@@ -6487,10 +6491,10 @@
     <row r="171" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="5"/>
       <c r="B171" s="5" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
@@ -6505,10 +6509,10 @@
     <row r="172" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="5"/>
       <c r="B172" s="5" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
@@ -6523,16 +6527,16 @@
     <row r="173" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="5"/>
       <c r="B173" s="5" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
@@ -6543,10 +6547,10 @@
     <row r="174" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="5"/>
       <c r="B174" s="5" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
@@ -6561,10 +6565,10 @@
     <row r="175" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="5" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
@@ -6579,10 +6583,10 @@
     <row r="176" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="5" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
@@ -6597,10 +6601,10 @@
     <row r="177" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="5" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
@@ -6615,10 +6619,10 @@
     <row r="178" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="5" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
@@ -6633,10 +6637,10 @@
     <row r="179" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="5" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
@@ -6651,10 +6655,10 @@
     <row r="180" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
@@ -6669,10 +6673,10 @@
     <row r="181" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
@@ -6687,10 +6691,10 @@
     <row r="182" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="5" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
@@ -6705,10 +6709,10 @@
     <row r="183" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="5" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
@@ -18370,13 +18374,13 @@
     </row>
     <row r="1016" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1016" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="B1016" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="C1016" s="5" t="s">
         <v>598</v>
-      </c>
-      <c r="B1016" s="5" t="s">
-        <v>599</v>
-      </c>
-      <c r="C1016" s="5" t="s">
-        <v>600</v>
       </c>
       <c r="D1016" s="6"/>
       <c r="E1016" s="6"/>
@@ -18385,24 +18389,24 @@
       <c r="H1016" s="6"/>
       <c r="I1016" s="6"/>
       <c r="J1016" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="K1016" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="L1016" s="6" t="s">
         <v>601</v>
-      </c>
-      <c r="K1016" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="L1016" s="6" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="1017" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1017" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="B1017" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="C1017" s="5" t="s">
         <v>604</v>
-      </c>
-      <c r="B1017" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="C1017" s="5" t="s">
-        <v>606</v>
       </c>
       <c r="D1017" s="6"/>
       <c r="E1017" s="6"/>
@@ -18411,13 +18415,13 @@
       <c r="H1017" s="6"/>
       <c r="I1017" s="6"/>
       <c r="J1017" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="K1017" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="L1017" s="6" t="s">
         <v>601</v>
-      </c>
-      <c r="K1017" s="6" t="s">
-        <v>602</v>
-      </c>
-      <c r="L1017" s="6" t="s">
-        <v>603</v>
       </c>
     </row>
   </sheetData>
@@ -18425,14 +18429,14 @@
     <dataValidation type="list" allowBlank="1" sqref="K2:K1017" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Minor Repeatable,Minor Fire-Once,Major"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="Q2:Q15" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="N2:N15 A2:C1017" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="N2:N16 A2:C1017" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
     <dataValidation type="list" allowBlank="1" sqref="L2:L1017" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="R2:R15" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="R2:R16" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Implemented,New,In progress,Under review,Buggy"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\klim\projects\chaos_redux\docs\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654CBF13-214A-458E-AFA9-9C0DD2C2BB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B9DC280-3EAE-48C3-A93C-CFD43DD36E07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="611">
   <si>
     <t>ID</t>
   </si>
@@ -172,30 +172,63 @@
     <t>Random War</t>
   </si>
   <si>
+    <t>A random eligible country declares war on another eligible country. Higher chaos stages create larger linked war webs. Compatible special countries can appear in later stages.</t>
+  </si>
+  <si>
+    <t>Gathering Storm: Triangular Incident. Three declarations fire in one linked dispute.</t>
+  </si>
+  <si>
+    <t>Rising Chaos: Four Fronts. Four declarations fire in one conflict web, with a small chance for a compatible special country to appear.</t>
+  </si>
+  <si>
+    <t>Chaos Tier: Contagious Ultimatums. Five declarations fire, major countries and faction members become more likely, and special-country involvement becomes more common.</t>
+  </si>
+  <si>
+    <t>Totalen Chaos: The War Week. Six declarations fire in a short chain, with a strong chance of one compatible special country participating.</t>
+  </si>
+  <si>
+    <t>World Collapse: Open Season. Seven to eight declarations fire while normal random events still run. Compatible special countries are strongly favored when available.</t>
+  </si>
+  <si>
     <t>Minor Repeatable</t>
   </si>
   <si>
+    <t>Wars</t>
+  </si>
+  <si>
+    <t>Repeatable Wars cluster.</t>
+  </si>
+  <si>
+    <t>4, (later add more)</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Soviet Union Collapse</t>
+  </si>
+  <si>
+    <t>Needs Final Review</t>
+  </si>
+  <si>
+    <t>Liberations</t>
+  </si>
+  <si>
+    <t>Liberation and breakaway shocks centered on a collapsing Soviet Union. Republics can seek recognition, arms, volunteers, intelligence contacts, economic help, or regional partners while the old union tries to hold together.</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Independence Wave</t>
+  </si>
+  <si>
+    <t>to be reworked</t>
+  </si>
+  <si>
     <t>To Be Reworked</t>
   </si>
   <si>
-    <t>Wars</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Soviet Union Collapse</t>
-  </si>
-  <si>
-    <t>Diseases</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Independence Wave</t>
-  </si>
-  <si>
     <t>Aliens</t>
   </si>
   <si>
@@ -373,7 +406,7 @@
     <t>random country gets a civil war.</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t/>
   </si>
   <si>
     <t>22</t>
@@ -1798,21 +1831,6 @@
     <t>Happens on a friday,  everything is heavely discounted for one day. A rare event</t>
   </si>
   <si>
-    <t>Gathering Storm: Triangular Incident. Three declarations fire in one linked dispute.</t>
-  </si>
-  <si>
-    <t>Rising Chaos: Four Fronts. Four declarations fire in one conflict web, with a small chance for a compatible special country to appear.</t>
-  </si>
-  <si>
-    <t>Chaos Tier: Contagious Ultimatums. Five declarations fire, major countries and faction members become more likely, and special-country involvement becomes more common.</t>
-  </si>
-  <si>
-    <t>Totalen Chaos: The War Week. Six declarations fire in a short chain, with a strong chance of one compatible special country participating.</t>
-  </si>
-  <si>
-    <t>World Collapse: Open Season. Seven to eight declarations fire while normal random events still run. Compatible special countries are strongly favored when available.</t>
-  </si>
-  <si>
     <t>SCN-001</t>
   </si>
   <si>
@@ -1838,21 +1856,6 @@
   </si>
   <si>
     <t>Triggerable scenario. Manual setup launched from the Chaos Redux scenario window. Type switches between the standard clone army and the stronger Aryan variant; intensity controls starting territory, division count, army strength, equipment, and neighboring pressure.</t>
-  </si>
-  <si>
-    <t>A random eligible country declares war on another eligible country. Higher chaos stages create larger linked war webs. Compatible special countries can appear in later stages.</t>
-  </si>
-  <si>
-    <t>Repeatable Wars cluster.</t>
-  </si>
-  <si>
-    <t>4, (later add more)</t>
-  </si>
-  <si>
-    <t>to be reworked</t>
-  </si>
-  <si>
-    <t>Liberations</t>
   </si>
 </sst>
 </file>
@@ -2013,7 +2016,7 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2">
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Main Sheet-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" size="0" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
@@ -2491,39 +2494,39 @@
         <v>48</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>605</v>
+        <v>49</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>591</v>
+        <v>50</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>592</v>
+        <v>51</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>593</v>
+        <v>52</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>594</v>
+        <v>53</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>595</v>
+        <v>54</v>
       </c>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L5" s="6" t="s">
         <v>23</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>606</v>
+        <v>57</v>
       </c>
       <c r="P5" s="8" t="s">
-        <v>607</v>
+        <v>58</v>
       </c>
       <c r="Q5" s="8">
         <v>2</v>
@@ -2534,13 +2537,13 @@
     </row>
     <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>608</v>
+        <v>66</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -2553,29 +2556,33 @@
         <v>22</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8">
-        <v>3</v>
+        <v>62</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="R6" s="8" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>608</v>
+        <v>66</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
@@ -2585,13 +2592,13 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
@@ -2604,13 +2611,13 @@
     </row>
     <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -2620,16 +2627,16 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="P8" s="8"/>
       <c r="Q8" s="8">
@@ -2641,13 +2648,13 @@
     </row>
     <row r="9" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -2657,13 +2664,13 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
@@ -2676,13 +2683,13 @@
     </row>
     <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -2692,13 +2699,13 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
       <c r="K10" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
@@ -2711,13 +2718,13 @@
     </row>
     <row r="11" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -2730,13 +2737,13 @@
         <v>22</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="O11" s="8" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="P11" s="8"/>
       <c r="Q11" s="8">
@@ -2748,13 +2755,13 @@
     </row>
     <row r="12" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -2767,13 +2774,13 @@
         <v>22</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="P12" s="8"/>
       <c r="Q12" s="8">
@@ -2785,13 +2792,13 @@
     </row>
     <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -2804,10 +2811,10 @@
         <v>22</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
@@ -2820,31 +2827,31 @@
     </row>
     <row r="14" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="C14" s="5" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="O14" s="8"/>
       <c r="P14" s="8"/>
@@ -2857,13 +2864,13 @@
     </row>
     <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -2873,16 +2880,16 @@
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
       <c r="K15" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="P15" s="8"/>
       <c r="Q15" s="8">
@@ -2894,13 +2901,13 @@
     </row>
     <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -2910,13 +2917,13 @@
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N16" t="s">
-        <v>609</v>
+        <v>62</v>
       </c>
       <c r="Q16">
         <v>1</v>
@@ -2927,13 +2934,13 @@
     </row>
     <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -2946,18 +2953,18 @@
         <v>22</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -2967,21 +2974,21 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -2991,21 +2998,21 @@
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
       <c r="K19" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -3015,27 +3022,27 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
@@ -3044,18 +3051,18 @@
         <v>22</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -3065,24 +3072,24 @@
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -3095,18 +3102,18 @@
         <v>22</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -3119,18 +3126,18 @@
         <v>22</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
@@ -3143,18 +3150,18 @@
         <v>22</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -3167,18 +3174,18 @@
         <v>34</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
@@ -3191,18 +3198,18 @@
         <v>22</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -3215,18 +3222,18 @@
         <v>22</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -3236,21 +3243,21 @@
       <c r="I29" s="6"/>
       <c r="J29" s="6"/>
       <c r="K29" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -3260,27 +3267,27 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
       <c r="G31" s="6" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="H31" s="6"/>
       <c r="I31" s="6"/>
@@ -3289,18 +3296,18 @@
         <v>34</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -3310,21 +3317,21 @@
       <c r="I32" s="6"/>
       <c r="J32" s="6"/>
       <c r="K32" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -3334,21 +3341,21 @@
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
       <c r="K33" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="D34" s="6"/>
       <c r="E34" s="6"/>
@@ -3358,21 +3365,21 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
       <c r="K34" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -3382,21 +3389,21 @@
       <c r="I35" s="6"/>
       <c r="J35" s="6"/>
       <c r="K35" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="D36" s="6"/>
       <c r="E36" s="6"/>
@@ -3406,21 +3413,21 @@
       <c r="I36" s="6"/>
       <c r="J36" s="6"/>
       <c r="K36" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -3430,21 +3437,21 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -3454,27 +3461,27 @@
       <c r="I38" s="6"/>
       <c r="J38" s="6"/>
       <c r="K38" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
       <c r="G39" s="6" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6"/>
@@ -3483,18 +3490,18 @@
         <v>22</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="D40" s="6"/>
       <c r="E40" s="6"/>
@@ -3504,21 +3511,21 @@
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="D41" s="6"/>
       <c r="E41" s="6"/>
@@ -3528,21 +3535,21 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
       <c r="K41" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
@@ -3552,21 +3559,21 @@
       <c r="I42" s="6"/>
       <c r="J42" s="6"/>
       <c r="K42" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="D43" s="6"/>
       <c r="E43" s="6"/>
@@ -3576,21 +3583,21 @@
       <c r="I43" s="6"/>
       <c r="J43" s="6"/>
       <c r="K43" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D44" s="6"/>
       <c r="E44" s="6"/>
@@ -3600,21 +3607,21 @@
       <c r="I44" s="6"/>
       <c r="J44" s="6"/>
       <c r="K44" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D45" s="6"/>
       <c r="E45" s="6"/>
@@ -3627,18 +3634,18 @@
         <v>34</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D46" s="6"/>
       <c r="E46" s="6"/>
@@ -3651,18 +3658,18 @@
         <v>22</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D47" s="6"/>
       <c r="E47" s="6"/>
@@ -3672,21 +3679,21 @@
       <c r="I47" s="6"/>
       <c r="J47" s="6"/>
       <c r="K47" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="D48" s="6"/>
       <c r="E48" s="6"/>
@@ -3696,21 +3703,21 @@
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
       <c r="K48" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
@@ -3723,18 +3730,18 @@
         <v>22</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
@@ -3747,18 +3754,18 @@
         <v>34</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
@@ -3768,21 +3775,21 @@
       <c r="I51" s="6"/>
       <c r="J51" s="6"/>
       <c r="K51" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -3795,18 +3802,18 @@
         <v>22</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -3816,21 +3823,21 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6"/>
       <c r="K53" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -3843,18 +3850,18 @@
         <v>22</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -3864,21 +3871,21 @@
       <c r="I55" s="6"/>
       <c r="J55" s="6"/>
       <c r="K55" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -3888,21 +3895,21 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
       <c r="K56" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
@@ -3912,21 +3919,21 @@
       <c r="I57" s="6"/>
       <c r="J57" s="6"/>
       <c r="K57" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -3936,21 +3943,21 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
       <c r="K58" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
@@ -3960,21 +3967,21 @@
       <c r="I59" s="6"/>
       <c r="J59" s="6"/>
       <c r="K59" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
@@ -3987,18 +3994,18 @@
         <v>22</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -4008,21 +4015,21 @@
       <c r="I61" s="6"/>
       <c r="J61" s="6"/>
       <c r="K61" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -4032,21 +4039,21 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
       <c r="K62" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -4056,21 +4063,21 @@
       <c r="I63" s="6"/>
       <c r="J63" s="6"/>
       <c r="K63" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -4080,21 +4087,21 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
       <c r="K64" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -4104,21 +4111,21 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6"/>
       <c r="K65" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -4128,21 +4135,21 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
       <c r="K66" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L66" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -4152,21 +4159,21 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
       <c r="K67" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L67" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -4179,24 +4186,24 @@
         <v>22</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
       <c r="F69" s="6"/>
       <c r="G69" s="6" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="H69" s="6"/>
       <c r="I69" s="6"/>
@@ -4205,18 +4212,18 @@
         <v>22</v>
       </c>
       <c r="L69" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -4229,18 +4236,18 @@
         <v>22</v>
       </c>
       <c r="L70" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -4253,18 +4260,18 @@
         <v>34</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -4277,18 +4284,18 @@
         <v>22</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -4301,18 +4308,18 @@
         <v>22</v>
       </c>
       <c r="L73" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -4325,18 +4332,18 @@
         <v>22</v>
       </c>
       <c r="L74" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -4349,18 +4356,18 @@
         <v>22</v>
       </c>
       <c r="L75" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -4373,18 +4380,18 @@
         <v>22</v>
       </c>
       <c r="L76" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -4394,21 +4401,21 @@
       <c r="I77" s="6"/>
       <c r="J77" s="6"/>
       <c r="K77" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L77" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
@@ -4418,21 +4425,21 @@
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
       <c r="K78" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L78" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
@@ -4442,21 +4449,21 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6"/>
       <c r="K79" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L79" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
@@ -4466,21 +4473,21 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
       <c r="K80" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L80" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
@@ -4493,18 +4500,18 @@
         <v>34</v>
       </c>
       <c r="L81" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
@@ -4517,18 +4524,18 @@
         <v>22</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
@@ -4538,21 +4545,21 @@
       <c r="I83" s="6"/>
       <c r="J83" s="6"/>
       <c r="K83" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L83" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
@@ -4562,21 +4569,21 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
       <c r="K84" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
@@ -4586,21 +4593,21 @@
       <c r="I85" s="6"/>
       <c r="J85" s="6"/>
       <c r="K85" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L85" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
@@ -4610,21 +4617,21 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
       <c r="K86" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L86" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
@@ -4637,18 +4644,18 @@
         <v>22</v>
       </c>
       <c r="L87" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D88" s="6"/>
       <c r="E88" s="6"/>
@@ -4658,21 +4665,21 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
       <c r="K88" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L88" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D89" s="6"/>
       <c r="E89" s="6"/>
@@ -4685,18 +4692,18 @@
         <v>22</v>
       </c>
       <c r="L89" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D90" s="6"/>
       <c r="E90" s="6"/>
@@ -4709,18 +4716,18 @@
         <v>22</v>
       </c>
       <c r="L90" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="D91" s="6"/>
       <c r="E91" s="6"/>
@@ -4733,24 +4740,24 @@
         <v>22</v>
       </c>
       <c r="L91" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D92" s="6"/>
       <c r="E92" s="6"/>
       <c r="F92" s="6"/>
       <c r="G92" s="6" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="H92" s="6"/>
       <c r="I92" s="6"/>
@@ -4759,18 +4766,18 @@
         <v>34</v>
       </c>
       <c r="L92" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="D93" s="6"/>
       <c r="E93" s="6"/>
@@ -4783,18 +4790,18 @@
         <v>22</v>
       </c>
       <c r="L93" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="6"/>
@@ -4807,18 +4814,18 @@
         <v>22</v>
       </c>
       <c r="L94" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="D95" s="6"/>
       <c r="E95" s="6"/>
@@ -4828,21 +4835,21 @@
       <c r="I95" s="6"/>
       <c r="J95" s="6"/>
       <c r="K95" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L95" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="D96" s="6"/>
       <c r="E96" s="6"/>
@@ -4852,21 +4859,21 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
       <c r="K96" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L96" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="D97" s="6"/>
       <c r="E97" s="6"/>
@@ -4876,21 +4883,21 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6"/>
       <c r="K97" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L97" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="D98" s="6"/>
       <c r="E98" s="6"/>
@@ -4900,21 +4907,21 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
       <c r="K98" s="6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L98" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D99" s="6"/>
       <c r="E99" s="6"/>
@@ -4927,18 +4934,18 @@
         <v>22</v>
       </c>
       <c r="L99" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D100" s="6"/>
       <c r="E100" s="6"/>
@@ -4951,18 +4958,18 @@
         <v>22</v>
       </c>
       <c r="L100" s="6" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="D101" s="6"/>
       <c r="E101" s="6"/>
@@ -4978,13 +4985,13 @@
     </row>
     <row r="102" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="D102" s="6"/>
       <c r="E102" s="6"/>
@@ -5000,13 +5007,13 @@
     </row>
     <row r="103" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D103" s="6"/>
       <c r="E103" s="6"/>
@@ -5022,13 +5029,13 @@
     </row>
     <row r="104" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D104" s="6"/>
       <c r="E104" s="6"/>
@@ -5044,13 +5051,13 @@
     </row>
     <row r="105" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D105" s="6"/>
       <c r="E105" s="6"/>
@@ -5066,13 +5073,13 @@
     </row>
     <row r="106" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
@@ -5088,13 +5095,13 @@
     </row>
     <row r="107" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="D107" s="6"/>
       <c r="E107" s="6"/>
@@ -5110,13 +5117,13 @@
     </row>
     <row r="108" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="6"/>
@@ -5132,13 +5139,13 @@
     </row>
     <row r="109" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="D109" s="6"/>
       <c r="E109" s="6"/>
@@ -5154,13 +5161,13 @@
     </row>
     <row r="110" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="D110" s="6"/>
       <c r="E110" s="6"/>
@@ -5176,13 +5183,13 @@
     </row>
     <row r="111" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="D111" s="6"/>
       <c r="E111" s="6"/>
@@ -5198,13 +5205,13 @@
     </row>
     <row r="112" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="D112" s="6"/>
       <c r="E112" s="6"/>
@@ -5220,13 +5227,13 @@
     </row>
     <row r="113" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="D113" s="6"/>
       <c r="E113" s="6"/>
@@ -5242,13 +5249,13 @@
     </row>
     <row r="114" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="D114" s="6"/>
       <c r="E114" s="6"/>
@@ -5264,13 +5271,13 @@
     </row>
     <row r="115" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="D115" s="6"/>
       <c r="E115" s="6"/>
@@ -5286,13 +5293,13 @@
     </row>
     <row r="116" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="D116" s="6"/>
       <c r="E116" s="6"/>
@@ -5308,13 +5315,13 @@
     </row>
     <row r="117" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="D117" s="6"/>
       <c r="E117" s="6"/>
@@ -5330,13 +5337,13 @@
     </row>
     <row r="118" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="D118" s="6"/>
       <c r="E118" s="6"/>
@@ -5352,13 +5359,13 @@
     </row>
     <row r="119" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="6"/>
@@ -5374,13 +5381,13 @@
     </row>
     <row r="120" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="D120" s="6"/>
       <c r="E120" s="6"/>
@@ -5396,13 +5403,13 @@
     </row>
     <row r="121" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="6"/>
@@ -5418,13 +5425,13 @@
     </row>
     <row r="122" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="6"/>
@@ -5440,13 +5447,13 @@
     </row>
     <row r="123" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="D123" s="6"/>
       <c r="E123" s="6"/>
@@ -5462,13 +5469,13 @@
     </row>
     <row r="124" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="D124" s="6"/>
       <c r="E124" s="6"/>
@@ -5484,13 +5491,13 @@
     </row>
     <row r="125" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D125" s="6"/>
       <c r="E125" s="6"/>
@@ -5506,13 +5513,13 @@
     </row>
     <row r="126" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="D126" s="6"/>
       <c r="E126" s="6"/>
@@ -5528,13 +5535,13 @@
     </row>
     <row r="127" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="D127" s="6"/>
       <c r="E127" s="6"/>
@@ -5550,13 +5557,13 @@
     </row>
     <row r="128" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="D128" s="6"/>
       <c r="E128" s="6"/>
@@ -5572,13 +5579,13 @@
     </row>
     <row r="129" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D129" s="6"/>
       <c r="E129" s="6"/>
@@ -5594,13 +5601,13 @@
     </row>
     <row r="130" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="D130" s="6"/>
       <c r="E130" s="6"/>
@@ -5616,13 +5623,13 @@
     </row>
     <row r="131" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="D131" s="6"/>
       <c r="E131" s="6"/>
@@ -5638,13 +5645,13 @@
     </row>
     <row r="132" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="D132" s="6"/>
       <c r="E132" s="6"/>
@@ -5660,13 +5667,13 @@
     </row>
     <row r="133" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="D133" s="6"/>
       <c r="E133" s="6"/>
@@ -5682,13 +5689,13 @@
     </row>
     <row r="134" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="D134" s="6"/>
       <c r="E134" s="6"/>
@@ -5704,13 +5711,13 @@
     </row>
     <row r="135" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="D135" s="6"/>
       <c r="E135" s="6"/>
@@ -5726,13 +5733,13 @@
     </row>
     <row r="136" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="D136" s="6"/>
       <c r="E136" s="6"/>
@@ -5748,13 +5755,13 @@
     </row>
     <row r="137" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="D137" s="6"/>
       <c r="E137" s="6"/>
@@ -5770,13 +5777,13 @@
     </row>
     <row r="138" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="D138" s="6"/>
       <c r="E138" s="6"/>
@@ -5792,13 +5799,13 @@
     </row>
     <row r="139" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="D139" s="6"/>
       <c r="E139" s="6"/>
@@ -5814,13 +5821,13 @@
     </row>
     <row r="140" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="D140" s="6"/>
       <c r="E140" s="6"/>
@@ -5836,13 +5843,13 @@
     </row>
     <row r="141" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="D141" s="6"/>
       <c r="E141" s="6"/>
@@ -5858,13 +5865,13 @@
     </row>
     <row r="142" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="D142" s="6"/>
       <c r="E142" s="6"/>
@@ -5880,13 +5887,13 @@
     </row>
     <row r="143" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="D143" s="6"/>
       <c r="E143" s="6"/>
@@ -5902,13 +5909,13 @@
     </row>
     <row r="144" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="D144" s="6"/>
       <c r="E144" s="6"/>
@@ -5924,13 +5931,13 @@
     </row>
     <row r="145" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="D145" s="6"/>
       <c r="E145" s="6"/>
@@ -5946,13 +5953,13 @@
     </row>
     <row r="146" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="D146" s="6"/>
       <c r="E146" s="6"/>
@@ -5968,13 +5975,13 @@
     </row>
     <row r="147" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="D147" s="6"/>
       <c r="E147" s="6"/>
@@ -5990,13 +5997,13 @@
     </row>
     <row r="148" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="D148" s="6"/>
       <c r="E148" s="6"/>
@@ -6012,13 +6019,13 @@
     </row>
     <row r="149" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="D149" s="6"/>
       <c r="E149" s="6"/>
@@ -6034,13 +6041,13 @@
     </row>
     <row r="150" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="D150" s="6"/>
       <c r="E150" s="6"/>
@@ -6056,13 +6063,13 @@
     </row>
     <row r="151" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="D151" s="6"/>
       <c r="E151" s="6"/>
@@ -6078,19 +6085,19 @@
     </row>
     <row r="152" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="D152" s="6"/>
       <c r="E152" s="6"/>
       <c r="F152" s="6"/>
       <c r="G152" s="6" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="H152" s="6"/>
       <c r="I152" s="6"/>
@@ -6102,13 +6109,13 @@
     </row>
     <row r="153" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="D153" s="6"/>
       <c r="E153" s="6"/>
@@ -6124,13 +6131,13 @@
     </row>
     <row r="154" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="D154" s="6"/>
       <c r="E154" s="6"/>
@@ -6146,13 +6153,13 @@
     </row>
     <row r="155" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="D155" s="6"/>
       <c r="E155" s="6"/>
@@ -6168,13 +6175,13 @@
     </row>
     <row r="156" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="D156" s="6"/>
       <c r="E156" s="6"/>
@@ -6190,13 +6197,13 @@
     </row>
     <row r="157" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="D157" s="6"/>
       <c r="E157" s="6"/>
@@ -6212,13 +6219,13 @@
     </row>
     <row r="158" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="D158" s="6"/>
       <c r="E158" s="6"/>
@@ -6234,13 +6241,13 @@
     </row>
     <row r="159" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="D159" s="6"/>
       <c r="E159" s="6"/>
@@ -6256,13 +6263,13 @@
     </row>
     <row r="160" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="D160" s="6"/>
       <c r="E160" s="6"/>
@@ -6278,13 +6285,13 @@
     </row>
     <row r="161" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="D161" s="6"/>
       <c r="E161" s="6"/>
@@ -6300,19 +6307,19 @@
     </row>
     <row r="162" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="D162" s="6"/>
       <c r="E162" s="6"/>
       <c r="F162" s="6"/>
       <c r="G162" s="6" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="H162" s="6"/>
       <c r="I162" s="6"/>
@@ -6324,13 +6331,13 @@
     </row>
     <row r="163" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="D163" s="6"/>
       <c r="E163" s="6"/>
@@ -6346,13 +6353,13 @@
     </row>
     <row r="164" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="D164" s="6"/>
       <c r="E164" s="6"/>
@@ -6368,13 +6375,13 @@
     </row>
     <row r="165" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="D165" s="6"/>
       <c r="E165" s="6"/>
@@ -6390,13 +6397,13 @@
     </row>
     <row r="166" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="D166" s="6"/>
       <c r="E166" s="6"/>
@@ -6412,13 +6419,13 @@
     </row>
     <row r="167" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="D167" s="6"/>
       <c r="E167" s="6"/>
@@ -6437,10 +6444,10 @@
     <row r="168" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="5"/>
       <c r="B168" s="5" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
@@ -6455,10 +6462,10 @@
     <row r="169" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="5"/>
       <c r="B169" s="5" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="D169" s="6"/>
       <c r="E169" s="6"/>
@@ -6473,10 +6480,10 @@
     <row r="170" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="5"/>
       <c r="B170" s="5" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="D170" s="6"/>
       <c r="E170" s="6"/>
@@ -6491,10 +6498,10 @@
     <row r="171" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="5"/>
       <c r="B171" s="5" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="D171" s="6"/>
       <c r="E171" s="6"/>
@@ -6509,10 +6516,10 @@
     <row r="172" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="5"/>
       <c r="B172" s="5" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="D172" s="6"/>
       <c r="E172" s="6"/>
@@ -6527,16 +6534,16 @@
     <row r="173" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="5"/>
       <c r="B173" s="5" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
       <c r="D173" s="6"/>
       <c r="E173" s="6"/>
       <c r="F173" s="6"/>
       <c r="G173" s="6" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="H173" s="6"/>
       <c r="I173" s="6"/>
@@ -6547,10 +6554,10 @@
     <row r="174" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="5"/>
       <c r="B174" s="5" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="D174" s="6"/>
       <c r="E174" s="6"/>
@@ -6565,10 +6572,10 @@
     <row r="175" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="5" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="D175" s="6"/>
       <c r="E175" s="6"/>
@@ -6583,10 +6590,10 @@
     <row r="176" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="5" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="D176" s="6"/>
       <c r="E176" s="6"/>
@@ -6601,10 +6608,10 @@
     <row r="177" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="5" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="D177" s="6"/>
       <c r="E177" s="6"/>
@@ -6619,10 +6626,10 @@
     <row r="178" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="5" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="D178" s="6"/>
       <c r="E178" s="6"/>
@@ -6637,10 +6644,10 @@
     <row r="179" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="5" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="D179" s="6"/>
       <c r="E179" s="6"/>
@@ -6655,10 +6662,10 @@
     <row r="180" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="5" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="D180" s="6"/>
       <c r="E180" s="6"/>
@@ -6673,10 +6680,10 @@
     <row r="181" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="5" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="D181" s="6"/>
       <c r="E181" s="6"/>
@@ -6691,10 +6698,10 @@
     <row r="182" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="5" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="D182" s="6"/>
       <c r="E182" s="6"/>
@@ -6709,10 +6716,10 @@
     <row r="183" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="5" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="D183" s="6"/>
       <c r="E183" s="6"/>
@@ -18374,13 +18381,13 @@
     </row>
     <row r="1016" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1016" s="5" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B1016" s="5" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="C1016" s="5" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="D1016" s="6"/>
       <c r="E1016" s="6"/>
@@ -18389,24 +18396,24 @@
       <c r="H1016" s="6"/>
       <c r="I1016" s="6"/>
       <c r="J1016" s="6" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="K1016" s="6" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="L1016" s="6" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
     <row r="1017" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1017" s="5" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B1017" s="5" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="C1017" s="5" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="D1017" s="6"/>
       <c r="E1017" s="6"/>
@@ -18415,13 +18422,13 @@
       <c r="H1017" s="6"/>
       <c r="I1017" s="6"/>
       <c r="J1017" s="6" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="K1017" s="6" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="L1017" s="6" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -18432,7 +18439,7 @@
     <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="N2:N16 A2:C1017" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
     <dataValidation type="list" allowBlank="1" sqref="L2:L1017" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
     </dataValidation>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2271,13 +2271,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1C4587"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R1017"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
@@ -2296,7 +2296,7 @@
     <col min="18" max="18" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="99.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="111.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="90" customHeight="1" ns3:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
@@ -2535,15 +2535,17 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>66</v>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Collapsing Soviet Union crisis with event-created republic focus trees, playable intervention boards, high-chaos successors, and the Civilian Factory of Russia Construction Directorate package.</t>
+        </is>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -2574,7 +2576,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>64</v>
       </c>
@@ -2609,7 +2611,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>69</v>
       </c>
@@ -2646,7 +2648,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>74</v>
       </c>
@@ -2681,7 +2683,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>78</v>
       </c>
@@ -2716,7 +2718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>82</v>
       </c>
@@ -2753,7 +2755,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>87</v>
       </c>
@@ -2790,7 +2792,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>92</v>
       </c>
@@ -2825,7 +2827,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>96</v>
       </c>
@@ -2862,7 +2864,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>100</v>
       </c>
@@ -2899,7 +2901,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>105</v>
       </c>
@@ -2932,7 +2934,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>108</v>
       </c>
@@ -2956,7 +2958,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>111</v>
       </c>
@@ -2980,7 +2982,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>114</v>
       </c>
@@ -3004,7 +3006,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>117</v>
       </c>
@@ -3028,7 +3030,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>120</v>
       </c>
@@ -3054,7 +3056,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>124</v>
       </c>
@@ -3081,7 +3083,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>128</v>
       </c>
@@ -3105,7 +3107,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>131</v>
       </c>
@@ -3129,7 +3131,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>134</v>
       </c>
@@ -3153,7 +3155,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>137</v>
       </c>
@@ -3177,7 +3179,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>140</v>
       </c>
@@ -3201,7 +3203,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>143</v>
       </c>
@@ -3225,7 +3227,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>146</v>
       </c>
@@ -3249,7 +3251,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>149</v>
       </c>
@@ -3273,7 +3275,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>152</v>
       </c>
@@ -3299,7 +3301,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>156</v>
       </c>
@@ -3323,7 +3325,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>159</v>
       </c>
@@ -3347,7 +3349,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>162</v>
       </c>
@@ -3371,7 +3373,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>165</v>
       </c>
@@ -3395,7 +3397,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>168</v>
       </c>
@@ -3419,7 +3421,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>171</v>
       </c>
@@ -3443,7 +3445,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>174</v>
       </c>
@@ -3467,7 +3469,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>177</v>
       </c>
@@ -3493,7 +3495,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>181</v>
       </c>
@@ -3517,7 +3519,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>184</v>
       </c>
@@ -3541,7 +3543,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>187</v>
       </c>
@@ -3565,7 +3567,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>190</v>
       </c>
@@ -3589,7 +3591,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>193</v>
       </c>
@@ -3613,7 +3615,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>196</v>
       </c>
@@ -3637,7 +3639,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>199</v>
       </c>
@@ -3661,7 +3663,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>202</v>
       </c>
@@ -3685,7 +3687,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>205</v>
       </c>
@@ -3709,7 +3711,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>208</v>
       </c>
@@ -3733,7 +3735,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>211</v>
       </c>
@@ -3757,7 +3759,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>214</v>
       </c>
@@ -3781,7 +3783,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>217</v>
       </c>
@@ -3805,7 +3807,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>220</v>
       </c>
@@ -3829,7 +3831,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>223</v>
       </c>
@@ -3853,7 +3855,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>226</v>
       </c>
@@ -3877,7 +3879,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>229</v>
       </c>
@@ -3901,7 +3903,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>232</v>
       </c>
@@ -3925,7 +3927,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>235</v>
       </c>
@@ -3949,7 +3951,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>238</v>
       </c>
@@ -3973,7 +3975,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>241</v>
       </c>
@@ -3997,7 +3999,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>244</v>
       </c>
@@ -4021,7 +4023,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>247</v>
       </c>
@@ -4045,7 +4047,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>250</v>
       </c>
@@ -4069,7 +4071,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>253</v>
       </c>
@@ -4093,7 +4095,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>256</v>
       </c>
@@ -4117,7 +4119,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>259</v>
       </c>
@@ -4141,7 +4143,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>262</v>
       </c>
@@ -4165,7 +4167,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>265</v>
       </c>
@@ -4189,7 +4191,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>268</v>
       </c>
@@ -4215,7 +4217,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>272</v>
       </c>
@@ -4239,7 +4241,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>275</v>
       </c>
@@ -4263,7 +4265,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>278</v>
       </c>
@@ -4287,7 +4289,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>281</v>
       </c>
@@ -4311,7 +4313,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>284</v>
       </c>
@@ -4335,7 +4337,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>287</v>
       </c>
@@ -4359,7 +4361,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>290</v>
       </c>
@@ -4383,7 +4385,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>293</v>
       </c>
@@ -4407,7 +4409,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>296</v>
       </c>
@@ -4431,7 +4433,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>299</v>
       </c>
@@ -4455,7 +4457,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>302</v>
       </c>
@@ -4479,7 +4481,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>305</v>
       </c>
@@ -4503,7 +4505,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>308</v>
       </c>
@@ -4527,7 +4529,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>311</v>
       </c>
@@ -4551,7 +4553,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>314</v>
       </c>
@@ -4575,7 +4577,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>317</v>
       </c>
@@ -4599,7 +4601,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>320</v>
       </c>
@@ -4623,7 +4625,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>323</v>
       </c>
@@ -4647,7 +4649,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>326</v>
       </c>
@@ -4671,7 +4673,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>329</v>
       </c>
@@ -4695,7 +4697,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>332</v>
       </c>
@@ -4719,7 +4721,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>335</v>
       </c>
@@ -4743,7 +4745,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>338</v>
       </c>
@@ -4769,7 +4771,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>342</v>
       </c>
@@ -4793,7 +4795,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>345</v>
       </c>
@@ -4817,7 +4819,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>348</v>
       </c>
@@ -4841,7 +4843,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>351</v>
       </c>
@@ -4865,7 +4867,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>354</v>
       </c>
@@ -4889,7 +4891,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>357</v>
       </c>
@@ -4913,7 +4915,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>360</v>
       </c>
@@ -4937,7 +4939,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>363</v>
       </c>
@@ -4961,7 +4963,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>366</v>
       </c>
@@ -4983,7 +4985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>369</v>
       </c>
@@ -5005,7 +5007,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>372</v>
       </c>
@@ -5027,7 +5029,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>375</v>
       </c>
@@ -5049,7 +5051,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>378</v>
       </c>
@@ -5071,7 +5073,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>381</v>
       </c>
@@ -5093,7 +5095,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>384</v>
       </c>
@@ -5115,7 +5117,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>387</v>
       </c>
@@ -5137,7 +5139,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>390</v>
       </c>
@@ -5159,7 +5161,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>393</v>
       </c>
@@ -5181,7 +5183,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>396</v>
       </c>
@@ -5203,7 +5205,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>399</v>
       </c>
@@ -5225,7 +5227,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>402</v>
       </c>
@@ -5247,7 +5249,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>405</v>
       </c>
@@ -5269,7 +5271,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>408</v>
       </c>
@@ -5291,7 +5293,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>411</v>
       </c>
@@ -5313,7 +5315,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>414</v>
       </c>
@@ -5335,7 +5337,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>417</v>
       </c>
@@ -5357,7 +5359,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>420</v>
       </c>
@@ -5379,7 +5381,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>423</v>
       </c>
@@ -5401,7 +5403,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>426</v>
       </c>
@@ -5423,7 +5425,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>429</v>
       </c>
@@ -5445,7 +5447,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>432</v>
       </c>
@@ -5467,7 +5469,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>435</v>
       </c>
@@ -5489,7 +5491,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>438</v>
       </c>
@@ -5511,7 +5513,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>441</v>
       </c>
@@ -5533,7 +5535,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>444</v>
       </c>
@@ -5555,7 +5557,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>447</v>
       </c>
@@ -5577,7 +5579,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>450</v>
       </c>
@@ -5599,7 +5601,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>453</v>
       </c>
@@ -5621,7 +5623,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>456</v>
       </c>
@@ -5643,7 +5645,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>459</v>
       </c>
@@ -5665,7 +5667,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>462</v>
       </c>
@@ -5687,7 +5689,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>465</v>
       </c>
@@ -5709,7 +5711,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>468</v>
       </c>
@@ -5731,7 +5733,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>471</v>
       </c>
@@ -5753,7 +5755,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>474</v>
       </c>
@@ -5775,7 +5777,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>477</v>
       </c>
@@ -5797,7 +5799,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>480</v>
       </c>
@@ -5819,7 +5821,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>483</v>
       </c>
@@ -5841,7 +5843,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>486</v>
       </c>
@@ -5863,7 +5865,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>489</v>
       </c>
@@ -5885,7 +5887,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>492</v>
       </c>
@@ -5907,7 +5909,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>495</v>
       </c>
@@ -5929,7 +5931,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>498</v>
       </c>
@@ -5951,7 +5953,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>501</v>
       </c>
@@ -5973,7 +5975,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>504</v>
       </c>
@@ -5995,7 +5997,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>507</v>
       </c>
@@ -6017,7 +6019,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>510</v>
       </c>
@@ -6039,7 +6041,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>513</v>
       </c>
@@ -6061,7 +6063,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>516</v>
       </c>
@@ -6083,7 +6085,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>519</v>
       </c>
@@ -6107,7 +6109,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>523</v>
       </c>
@@ -6129,7 +6131,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>526</v>
       </c>
@@ -6151,7 +6153,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>529</v>
       </c>
@@ -6173,7 +6175,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>532</v>
       </c>
@@ -6195,7 +6197,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>535</v>
       </c>
@@ -6217,7 +6219,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>538</v>
       </c>
@@ -6239,7 +6241,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>541</v>
       </c>
@@ -6261,7 +6263,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>544</v>
       </c>
@@ -6283,7 +6285,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>547</v>
       </c>
@@ -6305,7 +6307,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>550</v>
       </c>
@@ -6329,7 +6331,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>554</v>
       </c>
@@ -6351,7 +6353,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>557</v>
       </c>
@@ -6373,7 +6375,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>560</v>
       </c>
@@ -6395,7 +6397,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>563</v>
       </c>
@@ -6417,7 +6419,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>566</v>
       </c>
@@ -6441,7 +6443,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A168" s="5"/>
       <c r="B168" s="5" t="s">
         <v>569</v>
@@ -6459,7 +6461,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A169" s="5"/>
       <c r="B169" s="5" t="s">
         <v>571</v>
@@ -6477,7 +6479,7 @@
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
     </row>
-    <row r="170" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A170" s="5"/>
       <c r="B170" s="5" t="s">
         <v>573</v>
@@ -6495,7 +6497,7 @@
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
     </row>
-    <row r="171" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A171" s="5"/>
       <c r="B171" s="5" t="s">
         <v>575</v>
@@ -6513,7 +6515,7 @@
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
     </row>
-    <row r="172" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A172" s="5"/>
       <c r="B172" s="5" t="s">
         <v>577</v>
@@ -6531,7 +6533,7 @@
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
     </row>
-    <row r="173" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A173" s="5"/>
       <c r="B173" s="5" t="s">
         <v>579</v>
@@ -6551,7 +6553,7 @@
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
     </row>
-    <row r="174" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A174" s="5"/>
       <c r="B174" s="5" t="s">
         <v>582</v>
@@ -6569,7 +6571,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="5" t="s">
         <v>584</v>
@@ -6587,7 +6589,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="5" t="s">
         <v>586</v>
@@ -6605,7 +6607,7 @@
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
     </row>
-    <row r="177" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="5" t="s">
         <v>588</v>
@@ -6623,7 +6625,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="5" t="s">
         <v>590</v>
@@ -6641,7 +6643,7 @@
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
     </row>
-    <row r="179" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="5" t="s">
         <v>592</v>
@@ -6659,7 +6661,7 @@
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
     </row>
-    <row r="180" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="5" t="s">
         <v>594</v>
@@ -6677,7 +6679,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="5" t="s">
         <v>596</v>
@@ -6695,7 +6697,7 @@
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
     </row>
-    <row r="182" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="5" t="s">
         <v>598</v>
@@ -6713,7 +6715,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="5" t="s">
         <v>600</v>
@@ -6731,7 +6733,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -6745,7 +6747,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -6759,7 +6761,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -6773,7 +6775,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -6787,7 +6789,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -6801,7 +6803,7 @@
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
     </row>
-    <row r="189" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -6815,7 +6817,7 @@
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
     </row>
-    <row r="190" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -6829,7 +6831,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -6843,7 +6845,7 @@
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
     </row>
-    <row r="192" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -6857,7 +6859,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -6871,7 +6873,7 @@
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
     </row>
-    <row r="194" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -6885,7 +6887,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -6899,7 +6901,7 @@
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
     </row>
-    <row r="196" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -6913,7 +6915,7 @@
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
     </row>
-    <row r="197" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -6927,7 +6929,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -6941,7 +6943,7 @@
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
     </row>
-    <row r="199" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -6955,7 +6957,7 @@
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
     </row>
-    <row r="200" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -6969,7 +6971,7 @@
       <c r="K200" s="6"/>
       <c r="L200" s="6"/>
     </row>
-    <row r="201" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -6983,7 +6985,7 @@
       <c r="K201" s="6"/>
       <c r="L201" s="6"/>
     </row>
-    <row r="202" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -6997,7 +6999,7 @@
       <c r="K202" s="6"/>
       <c r="L202" s="6"/>
     </row>
-    <row r="203" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -7011,7 +7013,7 @@
       <c r="K203" s="6"/>
       <c r="L203" s="6"/>
     </row>
-    <row r="204" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -7025,7 +7027,7 @@
       <c r="K204" s="6"/>
       <c r="L204" s="6"/>
     </row>
-    <row r="205" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -7039,7 +7041,7 @@
       <c r="K205" s="6"/>
       <c r="L205" s="6"/>
     </row>
-    <row r="206" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -7053,7 +7055,7 @@
       <c r="K206" s="6"/>
       <c r="L206" s="6"/>
     </row>
-    <row r="207" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -7067,7 +7069,7 @@
       <c r="K207" s="6"/>
       <c r="L207" s="6"/>
     </row>
-    <row r="208" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -7081,7 +7083,7 @@
       <c r="K208" s="6"/>
       <c r="L208" s="6"/>
     </row>
-    <row r="209" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -7095,7 +7097,7 @@
       <c r="K209" s="6"/>
       <c r="L209" s="6"/>
     </row>
-    <row r="210" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -7109,7 +7111,7 @@
       <c r="K210" s="6"/>
       <c r="L210" s="6"/>
     </row>
-    <row r="211" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -7123,7 +7125,7 @@
       <c r="K211" s="6"/>
       <c r="L211" s="6"/>
     </row>
-    <row r="212" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -7137,7 +7139,7 @@
       <c r="K212" s="6"/>
       <c r="L212" s="6"/>
     </row>
-    <row r="213" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -7151,7 +7153,7 @@
       <c r="K213" s="6"/>
       <c r="L213" s="6"/>
     </row>
-    <row r="214" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -7165,7 +7167,7 @@
       <c r="K214" s="6"/>
       <c r="L214" s="6"/>
     </row>
-    <row r="215" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -7179,7 +7181,7 @@
       <c r="K215" s="6"/>
       <c r="L215" s="6"/>
     </row>
-    <row r="216" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -7193,7 +7195,7 @@
       <c r="K216" s="6"/>
       <c r="L216" s="6"/>
     </row>
-    <row r="217" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -7207,7 +7209,7 @@
       <c r="K217" s="6"/>
       <c r="L217" s="6"/>
     </row>
-    <row r="218" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -7221,7 +7223,7 @@
       <c r="K218" s="6"/>
       <c r="L218" s="6"/>
     </row>
-    <row r="219" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -7235,7 +7237,7 @@
       <c r="K219" s="6"/>
       <c r="L219" s="6"/>
     </row>
-    <row r="220" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -7249,7 +7251,7 @@
       <c r="K220" s="6"/>
       <c r="L220" s="6"/>
     </row>
-    <row r="221" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -7263,7 +7265,7 @@
       <c r="K221" s="6"/>
       <c r="L221" s="6"/>
     </row>
-    <row r="222" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -7277,7 +7279,7 @@
       <c r="K222" s="6"/>
       <c r="L222" s="6"/>
     </row>
-    <row r="223" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -7291,7 +7293,7 @@
       <c r="K223" s="6"/>
       <c r="L223" s="6"/>
     </row>
-    <row r="224" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -7305,7 +7307,7 @@
       <c r="K224" s="6"/>
       <c r="L224" s="6"/>
     </row>
-    <row r="225" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -7319,7 +7321,7 @@
       <c r="K225" s="6"/>
       <c r="L225" s="6"/>
     </row>
-    <row r="226" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -7333,7 +7335,7 @@
       <c r="K226" s="6"/>
       <c r="L226" s="6"/>
     </row>
-    <row r="227" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -7347,7 +7349,7 @@
       <c r="K227" s="6"/>
       <c r="L227" s="6"/>
     </row>
-    <row r="228" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -7361,7 +7363,7 @@
       <c r="K228" s="6"/>
       <c r="L228" s="6"/>
     </row>
-    <row r="229" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -7375,7 +7377,7 @@
       <c r="K229" s="6"/>
       <c r="L229" s="6"/>
     </row>
-    <row r="230" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -7389,7 +7391,7 @@
       <c r="K230" s="6"/>
       <c r="L230" s="6"/>
     </row>
-    <row r="231" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -7403,7 +7405,7 @@
       <c r="K231" s="6"/>
       <c r="L231" s="6"/>
     </row>
-    <row r="232" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -7417,7 +7419,7 @@
       <c r="K232" s="6"/>
       <c r="L232" s="6"/>
     </row>
-    <row r="233" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -7431,7 +7433,7 @@
       <c r="K233" s="6"/>
       <c r="L233" s="6"/>
     </row>
-    <row r="234" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -7445,7 +7447,7 @@
       <c r="K234" s="6"/>
       <c r="L234" s="6"/>
     </row>
-    <row r="235" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -7459,7 +7461,7 @@
       <c r="K235" s="6"/>
       <c r="L235" s="6"/>
     </row>
-    <row r="236" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -7473,7 +7475,7 @@
       <c r="K236" s="6"/>
       <c r="L236" s="6"/>
     </row>
-    <row r="237" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -7487,7 +7489,7 @@
       <c r="K237" s="6"/>
       <c r="L237" s="6"/>
     </row>
-    <row r="238" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -7501,7 +7503,7 @@
       <c r="K238" s="6"/>
       <c r="L238" s="6"/>
     </row>
-    <row r="239" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -7515,7 +7517,7 @@
       <c r="K239" s="6"/>
       <c r="L239" s="6"/>
     </row>
-    <row r="240" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -7529,7 +7531,7 @@
       <c r="K240" s="6"/>
       <c r="L240" s="6"/>
     </row>
-    <row r="241" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -7543,7 +7545,7 @@
       <c r="K241" s="6"/>
       <c r="L241" s="6"/>
     </row>
-    <row r="242" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -7557,7 +7559,7 @@
       <c r="K242" s="6"/>
       <c r="L242" s="6"/>
     </row>
-    <row r="243" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -7571,7 +7573,7 @@
       <c r="K243" s="6"/>
       <c r="L243" s="6"/>
     </row>
-    <row r="244" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -7585,7 +7587,7 @@
       <c r="K244" s="6"/>
       <c r="L244" s="6"/>
     </row>
-    <row r="245" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -7599,7 +7601,7 @@
       <c r="K245" s="6"/>
       <c r="L245" s="6"/>
     </row>
-    <row r="246" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -7613,7 +7615,7 @@
       <c r="K246" s="6"/>
       <c r="L246" s="6"/>
     </row>
-    <row r="247" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -7627,7 +7629,7 @@
       <c r="K247" s="6"/>
       <c r="L247" s="6"/>
     </row>
-    <row r="248" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -7641,7 +7643,7 @@
       <c r="K248" s="6"/>
       <c r="L248" s="6"/>
     </row>
-    <row r="249" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -7655,7 +7657,7 @@
       <c r="K249" s="6"/>
       <c r="L249" s="6"/>
     </row>
-    <row r="250" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -7669,7 +7671,7 @@
       <c r="K250" s="6"/>
       <c r="L250" s="6"/>
     </row>
-    <row r="251" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -7683,7 +7685,7 @@
       <c r="K251" s="6"/>
       <c r="L251" s="6"/>
     </row>
-    <row r="252" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -7697,7 +7699,7 @@
       <c r="K252" s="6"/>
       <c r="L252" s="6"/>
     </row>
-    <row r="253" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -7711,7 +7713,7 @@
       <c r="K253" s="6"/>
       <c r="L253" s="6"/>
     </row>
-    <row r="254" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -7725,7 +7727,7 @@
       <c r="K254" s="6"/>
       <c r="L254" s="6"/>
     </row>
-    <row r="255" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -7739,7 +7741,7 @@
       <c r="K255" s="6"/>
       <c r="L255" s="6"/>
     </row>
-    <row r="256" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -7753,7 +7755,7 @@
       <c r="K256" s="6"/>
       <c r="L256" s="6"/>
     </row>
-    <row r="257" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -7767,7 +7769,7 @@
       <c r="K257" s="6"/>
       <c r="L257" s="6"/>
     </row>
-    <row r="258" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -7781,7 +7783,7 @@
       <c r="K258" s="6"/>
       <c r="L258" s="6"/>
     </row>
-    <row r="259" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -7795,7 +7797,7 @@
       <c r="K259" s="6"/>
       <c r="L259" s="6"/>
     </row>
-    <row r="260" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -7809,7 +7811,7 @@
       <c r="K260" s="6"/>
       <c r="L260" s="6"/>
     </row>
-    <row r="261" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -7823,7 +7825,7 @@
       <c r="K261" s="6"/>
       <c r="L261" s="6"/>
     </row>
-    <row r="262" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -7837,7 +7839,7 @@
       <c r="K262" s="6"/>
       <c r="L262" s="6"/>
     </row>
-    <row r="263" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -7851,7 +7853,7 @@
       <c r="K263" s="6"/>
       <c r="L263" s="6"/>
     </row>
-    <row r="264" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -7865,7 +7867,7 @@
       <c r="K264" s="6"/>
       <c r="L264" s="6"/>
     </row>
-    <row r="265" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -7879,7 +7881,7 @@
       <c r="K265" s="6"/>
       <c r="L265" s="6"/>
     </row>
-    <row r="266" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -7893,7 +7895,7 @@
       <c r="K266" s="6"/>
       <c r="L266" s="6"/>
     </row>
-    <row r="267" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -7907,7 +7909,7 @@
       <c r="K267" s="6"/>
       <c r="L267" s="6"/>
     </row>
-    <row r="268" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -7921,7 +7923,7 @@
       <c r="K268" s="6"/>
       <c r="L268" s="6"/>
     </row>
-    <row r="269" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -7935,7 +7937,7 @@
       <c r="K269" s="6"/>
       <c r="L269" s="6"/>
     </row>
-    <row r="270" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -7949,7 +7951,7 @@
       <c r="K270" s="6"/>
       <c r="L270" s="6"/>
     </row>
-    <row r="271" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -7963,7 +7965,7 @@
       <c r="K271" s="6"/>
       <c r="L271" s="6"/>
     </row>
-    <row r="272" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -7977,7 +7979,7 @@
       <c r="K272" s="6"/>
       <c r="L272" s="6"/>
     </row>
-    <row r="273" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -7991,7 +7993,7 @@
       <c r="K273" s="6"/>
       <c r="L273" s="6"/>
     </row>
-    <row r="274" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -8005,7 +8007,7 @@
       <c r="K274" s="6"/>
       <c r="L274" s="6"/>
     </row>
-    <row r="275" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -8019,7 +8021,7 @@
       <c r="K275" s="6"/>
       <c r="L275" s="6"/>
     </row>
-    <row r="276" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -8033,7 +8035,7 @@
       <c r="K276" s="6"/>
       <c r="L276" s="6"/>
     </row>
-    <row r="277" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -8047,7 +8049,7 @@
       <c r="K277" s="6"/>
       <c r="L277" s="6"/>
     </row>
-    <row r="278" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -8061,7 +8063,7 @@
       <c r="K278" s="6"/>
       <c r="L278" s="6"/>
     </row>
-    <row r="279" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -8075,7 +8077,7 @@
       <c r="K279" s="6"/>
       <c r="L279" s="6"/>
     </row>
-    <row r="280" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -8089,7 +8091,7 @@
       <c r="K280" s="6"/>
       <c r="L280" s="6"/>
     </row>
-    <row r="281" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -8103,7 +8105,7 @@
       <c r="K281" s="6"/>
       <c r="L281" s="6"/>
     </row>
-    <row r="282" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -8117,7 +8119,7 @@
       <c r="K282" s="6"/>
       <c r="L282" s="6"/>
     </row>
-    <row r="283" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -8131,7 +8133,7 @@
       <c r="K283" s="6"/>
       <c r="L283" s="6"/>
     </row>
-    <row r="284" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -8145,7 +8147,7 @@
       <c r="K284" s="6"/>
       <c r="L284" s="6"/>
     </row>
-    <row r="285" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -8159,7 +8161,7 @@
       <c r="K285" s="6"/>
       <c r="L285" s="6"/>
     </row>
-    <row r="286" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -8173,7 +8175,7 @@
       <c r="K286" s="6"/>
       <c r="L286" s="6"/>
     </row>
-    <row r="287" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -8187,7 +8189,7 @@
       <c r="K287" s="6"/>
       <c r="L287" s="6"/>
     </row>
-    <row r="288" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -8201,7 +8203,7 @@
       <c r="K288" s="6"/>
       <c r="L288" s="6"/>
     </row>
-    <row r="289" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -8215,7 +8217,7 @@
       <c r="K289" s="6"/>
       <c r="L289" s="6"/>
     </row>
-    <row r="290" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -8229,7 +8231,7 @@
       <c r="K290" s="6"/>
       <c r="L290" s="6"/>
     </row>
-    <row r="291" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -8243,7 +8245,7 @@
       <c r="K291" s="6"/>
       <c r="L291" s="6"/>
     </row>
-    <row r="292" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -8257,7 +8259,7 @@
       <c r="K292" s="6"/>
       <c r="L292" s="6"/>
     </row>
-    <row r="293" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -8271,7 +8273,7 @@
       <c r="K293" s="6"/>
       <c r="L293" s="6"/>
     </row>
-    <row r="294" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -8285,7 +8287,7 @@
       <c r="K294" s="6"/>
       <c r="L294" s="6"/>
     </row>
-    <row r="295" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -8299,7 +8301,7 @@
       <c r="K295" s="6"/>
       <c r="L295" s="6"/>
     </row>
-    <row r="296" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -8313,7 +8315,7 @@
       <c r="K296" s="6"/>
       <c r="L296" s="6"/>
     </row>
-    <row r="297" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -8327,7 +8329,7 @@
       <c r="K297" s="6"/>
       <c r="L297" s="6"/>
     </row>
-    <row r="298" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -8341,7 +8343,7 @@
       <c r="K298" s="6"/>
       <c r="L298" s="6"/>
     </row>
-    <row r="299" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -8355,7 +8357,7 @@
       <c r="K299" s="6"/>
       <c r="L299" s="6"/>
     </row>
-    <row r="300" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -8369,7 +8371,7 @@
       <c r="K300" s="6"/>
       <c r="L300" s="6"/>
     </row>
-    <row r="301" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -8383,7 +8385,7 @@
       <c r="K301" s="6"/>
       <c r="L301" s="6"/>
     </row>
-    <row r="302" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -8397,7 +8399,7 @@
       <c r="K302" s="6"/>
       <c r="L302" s="6"/>
     </row>
-    <row r="303" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -8411,7 +8413,7 @@
       <c r="K303" s="6"/>
       <c r="L303" s="6"/>
     </row>
-    <row r="304" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -8425,7 +8427,7 @@
       <c r="K304" s="6"/>
       <c r="L304" s="6"/>
     </row>
-    <row r="305" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -8439,7 +8441,7 @@
       <c r="K305" s="6"/>
       <c r="L305" s="6"/>
     </row>
-    <row r="306" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -8453,7 +8455,7 @@
       <c r="K306" s="6"/>
       <c r="L306" s="6"/>
     </row>
-    <row r="307" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -8467,7 +8469,7 @@
       <c r="K307" s="6"/>
       <c r="L307" s="6"/>
     </row>
-    <row r="308" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -8481,7 +8483,7 @@
       <c r="K308" s="6"/>
       <c r="L308" s="6"/>
     </row>
-    <row r="309" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -8495,7 +8497,7 @@
       <c r="K309" s="6"/>
       <c r="L309" s="6"/>
     </row>
-    <row r="310" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -8509,7 +8511,7 @@
       <c r="K310" s="6"/>
       <c r="L310" s="6"/>
     </row>
-    <row r="311" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -8523,7 +8525,7 @@
       <c r="K311" s="6"/>
       <c r="L311" s="6"/>
     </row>
-    <row r="312" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -8537,7 +8539,7 @@
       <c r="K312" s="6"/>
       <c r="L312" s="6"/>
     </row>
-    <row r="313" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -8551,7 +8553,7 @@
       <c r="K313" s="6"/>
       <c r="L313" s="6"/>
     </row>
-    <row r="314" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -8565,7 +8567,7 @@
       <c r="K314" s="6"/>
       <c r="L314" s="6"/>
     </row>
-    <row r="315" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -8579,7 +8581,7 @@
       <c r="K315" s="6"/>
       <c r="L315" s="6"/>
     </row>
-    <row r="316" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -8593,7 +8595,7 @@
       <c r="K316" s="6"/>
       <c r="L316" s="6"/>
     </row>
-    <row r="317" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -8607,7 +8609,7 @@
       <c r="K317" s="6"/>
       <c r="L317" s="6"/>
     </row>
-    <row r="318" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -8621,7 +8623,7 @@
       <c r="K318" s="6"/>
       <c r="L318" s="6"/>
     </row>
-    <row r="319" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -8635,7 +8637,7 @@
       <c r="K319" s="6"/>
       <c r="L319" s="6"/>
     </row>
-    <row r="320" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -8649,7 +8651,7 @@
       <c r="K320" s="6"/>
       <c r="L320" s="6"/>
     </row>
-    <row r="321" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -8663,7 +8665,7 @@
       <c r="K321" s="6"/>
       <c r="L321" s="6"/>
     </row>
-    <row r="322" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -8677,7 +8679,7 @@
       <c r="K322" s="6"/>
       <c r="L322" s="6"/>
     </row>
-    <row r="323" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -8691,7 +8693,7 @@
       <c r="K323" s="6"/>
       <c r="L323" s="6"/>
     </row>
-    <row r="324" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -8705,7 +8707,7 @@
       <c r="K324" s="6"/>
       <c r="L324" s="6"/>
     </row>
-    <row r="325" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -8719,7 +8721,7 @@
       <c r="K325" s="6"/>
       <c r="L325" s="6"/>
     </row>
-    <row r="326" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -8733,7 +8735,7 @@
       <c r="K326" s="6"/>
       <c r="L326" s="6"/>
     </row>
-    <row r="327" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -8747,7 +8749,7 @@
       <c r="K327" s="6"/>
       <c r="L327" s="6"/>
     </row>
-    <row r="328" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -8761,7 +8763,7 @@
       <c r="K328" s="6"/>
       <c r="L328" s="6"/>
     </row>
-    <row r="329" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -8775,7 +8777,7 @@
       <c r="K329" s="6"/>
       <c r="L329" s="6"/>
     </row>
-    <row r="330" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -8789,7 +8791,7 @@
       <c r="K330" s="6"/>
       <c r="L330" s="6"/>
     </row>
-    <row r="331" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -8803,7 +8805,7 @@
       <c r="K331" s="6"/>
       <c r="L331" s="6"/>
     </row>
-    <row r="332" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -8817,7 +8819,7 @@
       <c r="K332" s="6"/>
       <c r="L332" s="6"/>
     </row>
-    <row r="333" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -8831,7 +8833,7 @@
       <c r="K333" s="6"/>
       <c r="L333" s="6"/>
     </row>
-    <row r="334" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -8845,7 +8847,7 @@
       <c r="K334" s="6"/>
       <c r="L334" s="6"/>
     </row>
-    <row r="335" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -8859,7 +8861,7 @@
       <c r="K335" s="6"/>
       <c r="L335" s="6"/>
     </row>
-    <row r="336" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -8873,7 +8875,7 @@
       <c r="K336" s="6"/>
       <c r="L336" s="6"/>
     </row>
-    <row r="337" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -8887,7 +8889,7 @@
       <c r="K337" s="6"/>
       <c r="L337" s="6"/>
     </row>
-    <row r="338" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -8901,7 +8903,7 @@
       <c r="K338" s="6"/>
       <c r="L338" s="6"/>
     </row>
-    <row r="339" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -8915,7 +8917,7 @@
       <c r="K339" s="6"/>
       <c r="L339" s="6"/>
     </row>
-    <row r="340" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -8929,7 +8931,7 @@
       <c r="K340" s="6"/>
       <c r="L340" s="6"/>
     </row>
-    <row r="341" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -8943,7 +8945,7 @@
       <c r="K341" s="6"/>
       <c r="L341" s="6"/>
     </row>
-    <row r="342" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -8957,7 +8959,7 @@
       <c r="K342" s="6"/>
       <c r="L342" s="6"/>
     </row>
-    <row r="343" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -8971,7 +8973,7 @@
       <c r="K343" s="6"/>
       <c r="L343" s="6"/>
     </row>
-    <row r="344" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -8985,7 +8987,7 @@
       <c r="K344" s="6"/>
       <c r="L344" s="6"/>
     </row>
-    <row r="345" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -8999,7 +9001,7 @@
       <c r="K345" s="6"/>
       <c r="L345" s="6"/>
     </row>
-    <row r="346" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -9013,7 +9015,7 @@
       <c r="K346" s="6"/>
       <c r="L346" s="6"/>
     </row>
-    <row r="347" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -9027,7 +9029,7 @@
       <c r="K347" s="6"/>
       <c r="L347" s="6"/>
     </row>
-    <row r="348" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -9041,7 +9043,7 @@
       <c r="K348" s="6"/>
       <c r="L348" s="6"/>
     </row>
-    <row r="349" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -9055,7 +9057,7 @@
       <c r="K349" s="6"/>
       <c r="L349" s="6"/>
     </row>
-    <row r="350" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -9069,7 +9071,7 @@
       <c r="K350" s="6"/>
       <c r="L350" s="6"/>
     </row>
-    <row r="351" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -9083,7 +9085,7 @@
       <c r="K351" s="6"/>
       <c r="L351" s="6"/>
     </row>
-    <row r="352" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -9097,7 +9099,7 @@
       <c r="K352" s="6"/>
       <c r="L352" s="6"/>
     </row>
-    <row r="353" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -9111,7 +9113,7 @@
       <c r="K353" s="6"/>
       <c r="L353" s="6"/>
     </row>
-    <row r="354" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -9125,7 +9127,7 @@
       <c r="K354" s="6"/>
       <c r="L354" s="6"/>
     </row>
-    <row r="355" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -9139,7 +9141,7 @@
       <c r="K355" s="6"/>
       <c r="L355" s="6"/>
     </row>
-    <row r="356" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -9153,7 +9155,7 @@
       <c r="K356" s="6"/>
       <c r="L356" s="6"/>
     </row>
-    <row r="357" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -9167,7 +9169,7 @@
       <c r="K357" s="6"/>
       <c r="L357" s="6"/>
     </row>
-    <row r="358" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -9181,7 +9183,7 @@
       <c r="K358" s="6"/>
       <c r="L358" s="6"/>
     </row>
-    <row r="359" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -9195,7 +9197,7 @@
       <c r="K359" s="6"/>
       <c r="L359" s="6"/>
     </row>
-    <row r="360" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -9209,7 +9211,7 @@
       <c r="K360" s="6"/>
       <c r="L360" s="6"/>
     </row>
-    <row r="361" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -9223,7 +9225,7 @@
       <c r="K361" s="6"/>
       <c r="L361" s="6"/>
     </row>
-    <row r="362" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -9237,7 +9239,7 @@
       <c r="K362" s="6"/>
       <c r="L362" s="6"/>
     </row>
-    <row r="363" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -9251,7 +9253,7 @@
       <c r="K363" s="6"/>
       <c r="L363" s="6"/>
     </row>
-    <row r="364" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -9265,7 +9267,7 @@
       <c r="K364" s="6"/>
       <c r="L364" s="6"/>
     </row>
-    <row r="365" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -9279,7 +9281,7 @@
       <c r="K365" s="6"/>
       <c r="L365" s="6"/>
     </row>
-    <row r="366" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -9293,7 +9295,7 @@
       <c r="K366" s="6"/>
       <c r="L366" s="6"/>
     </row>
-    <row r="367" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -9307,7 +9309,7 @@
       <c r="K367" s="6"/>
       <c r="L367" s="6"/>
     </row>
-    <row r="368" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -9321,7 +9323,7 @@
       <c r="K368" s="6"/>
       <c r="L368" s="6"/>
     </row>
-    <row r="369" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -9335,7 +9337,7 @@
       <c r="K369" s="6"/>
       <c r="L369" s="6"/>
     </row>
-    <row r="370" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -9349,7 +9351,7 @@
       <c r="K370" s="6"/>
       <c r="L370" s="6"/>
     </row>
-    <row r="371" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -9363,7 +9365,7 @@
       <c r="K371" s="6"/>
       <c r="L371" s="6"/>
     </row>
-    <row r="372" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -9377,7 +9379,7 @@
       <c r="K372" s="6"/>
       <c r="L372" s="6"/>
     </row>
-    <row r="373" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -9391,7 +9393,7 @@
       <c r="K373" s="6"/>
       <c r="L373" s="6"/>
     </row>
-    <row r="374" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -9405,7 +9407,7 @@
       <c r="K374" s="6"/>
       <c r="L374" s="6"/>
     </row>
-    <row r="375" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -9419,7 +9421,7 @@
       <c r="K375" s="6"/>
       <c r="L375" s="6"/>
     </row>
-    <row r="376" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -9433,7 +9435,7 @@
       <c r="K376" s="6"/>
       <c r="L376" s="6"/>
     </row>
-    <row r="377" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -9447,7 +9449,7 @@
       <c r="K377" s="6"/>
       <c r="L377" s="6"/>
     </row>
-    <row r="378" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -9461,7 +9463,7 @@
       <c r="K378" s="6"/>
       <c r="L378" s="6"/>
     </row>
-    <row r="379" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -9475,7 +9477,7 @@
       <c r="K379" s="6"/>
       <c r="L379" s="6"/>
     </row>
-    <row r="380" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -9489,7 +9491,7 @@
       <c r="K380" s="6"/>
       <c r="L380" s="6"/>
     </row>
-    <row r="381" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -9503,7 +9505,7 @@
       <c r="K381" s="6"/>
       <c r="L381" s="6"/>
     </row>
-    <row r="382" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -9517,7 +9519,7 @@
       <c r="K382" s="6"/>
       <c r="L382" s="6"/>
     </row>
-    <row r="383" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -9531,7 +9533,7 @@
       <c r="K383" s="6"/>
       <c r="L383" s="6"/>
     </row>
-    <row r="384" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -9545,7 +9547,7 @@
       <c r="K384" s="6"/>
       <c r="L384" s="6"/>
     </row>
-    <row r="385" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -9559,7 +9561,7 @@
       <c r="K385" s="6"/>
       <c r="L385" s="6"/>
     </row>
-    <row r="386" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -9573,7 +9575,7 @@
       <c r="K386" s="6"/>
       <c r="L386" s="6"/>
     </row>
-    <row r="387" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -9587,7 +9589,7 @@
       <c r="K387" s="6"/>
       <c r="L387" s="6"/>
     </row>
-    <row r="388" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -9601,7 +9603,7 @@
       <c r="K388" s="6"/>
       <c r="L388" s="6"/>
     </row>
-    <row r="389" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -9615,7 +9617,7 @@
       <c r="K389" s="6"/>
       <c r="L389" s="6"/>
     </row>
-    <row r="390" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -9629,7 +9631,7 @@
       <c r="K390" s="6"/>
       <c r="L390" s="6"/>
     </row>
-    <row r="391" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -9643,7 +9645,7 @@
       <c r="K391" s="6"/>
       <c r="L391" s="6"/>
     </row>
-    <row r="392" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -9657,7 +9659,7 @@
       <c r="K392" s="6"/>
       <c r="L392" s="6"/>
     </row>
-    <row r="393" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -9671,7 +9673,7 @@
       <c r="K393" s="6"/>
       <c r="L393" s="6"/>
     </row>
-    <row r="394" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -9685,7 +9687,7 @@
       <c r="K394" s="6"/>
       <c r="L394" s="6"/>
     </row>
-    <row r="395" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -9699,7 +9701,7 @@
       <c r="K395" s="6"/>
       <c r="L395" s="6"/>
     </row>
-    <row r="396" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -9713,7 +9715,7 @@
       <c r="K396" s="6"/>
       <c r="L396" s="6"/>
     </row>
-    <row r="397" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -9727,7 +9729,7 @@
       <c r="K397" s="6"/>
       <c r="L397" s="6"/>
     </row>
-    <row r="398" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -9741,7 +9743,7 @@
       <c r="K398" s="6"/>
       <c r="L398" s="6"/>
     </row>
-    <row r="399" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -9755,7 +9757,7 @@
       <c r="K399" s="6"/>
       <c r="L399" s="6"/>
     </row>
-    <row r="400" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -9769,7 +9771,7 @@
       <c r="K400" s="6"/>
       <c r="L400" s="6"/>
     </row>
-    <row r="401" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -9783,7 +9785,7 @@
       <c r="K401" s="6"/>
       <c r="L401" s="6"/>
     </row>
-    <row r="402" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -9797,7 +9799,7 @@
       <c r="K402" s="6"/>
       <c r="L402" s="6"/>
     </row>
-    <row r="403" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -9811,7 +9813,7 @@
       <c r="K403" s="6"/>
       <c r="L403" s="6"/>
     </row>
-    <row r="404" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -9825,7 +9827,7 @@
       <c r="K404" s="6"/>
       <c r="L404" s="6"/>
     </row>
-    <row r="405" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -9839,7 +9841,7 @@
       <c r="K405" s="6"/>
       <c r="L405" s="6"/>
     </row>
-    <row r="406" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -9853,7 +9855,7 @@
       <c r="K406" s="6"/>
       <c r="L406" s="6"/>
     </row>
-    <row r="407" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -9867,7 +9869,7 @@
       <c r="K407" s="6"/>
       <c r="L407" s="6"/>
     </row>
-    <row r="408" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -9881,7 +9883,7 @@
       <c r="K408" s="6"/>
       <c r="L408" s="6"/>
     </row>
-    <row r="409" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -9895,7 +9897,7 @@
       <c r="K409" s="6"/>
       <c r="L409" s="6"/>
     </row>
-    <row r="410" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -9909,7 +9911,7 @@
       <c r="K410" s="6"/>
       <c r="L410" s="6"/>
     </row>
-    <row r="411" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -9923,7 +9925,7 @@
       <c r="K411" s="6"/>
       <c r="L411" s="6"/>
     </row>
-    <row r="412" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -9937,7 +9939,7 @@
       <c r="K412" s="6"/>
       <c r="L412" s="6"/>
     </row>
-    <row r="413" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -9951,7 +9953,7 @@
       <c r="K413" s="6"/>
       <c r="L413" s="6"/>
     </row>
-    <row r="414" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -9965,7 +9967,7 @@
       <c r="K414" s="6"/>
       <c r="L414" s="6"/>
     </row>
-    <row r="415" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -9979,7 +9981,7 @@
       <c r="K415" s="6"/>
       <c r="L415" s="6"/>
     </row>
-    <row r="416" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -9993,7 +9995,7 @@
       <c r="K416" s="6"/>
       <c r="L416" s="6"/>
     </row>
-    <row r="417" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -10007,7 +10009,7 @@
       <c r="K417" s="6"/>
       <c r="L417" s="6"/>
     </row>
-    <row r="418" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -10021,7 +10023,7 @@
       <c r="K418" s="6"/>
       <c r="L418" s="6"/>
     </row>
-    <row r="419" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -10035,7 +10037,7 @@
       <c r="K419" s="6"/>
       <c r="L419" s="6"/>
     </row>
-    <row r="420" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -10049,7 +10051,7 @@
       <c r="K420" s="6"/>
       <c r="L420" s="6"/>
     </row>
-    <row r="421" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -10063,7 +10065,7 @@
       <c r="K421" s="6"/>
       <c r="L421" s="6"/>
     </row>
-    <row r="422" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -10077,7 +10079,7 @@
       <c r="K422" s="6"/>
       <c r="L422" s="6"/>
     </row>
-    <row r="423" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -10091,7 +10093,7 @@
       <c r="K423" s="6"/>
       <c r="L423" s="6"/>
     </row>
-    <row r="424" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -10105,7 +10107,7 @@
       <c r="K424" s="6"/>
       <c r="L424" s="6"/>
     </row>
-    <row r="425" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -10119,7 +10121,7 @@
       <c r="K425" s="6"/>
       <c r="L425" s="6"/>
     </row>
-    <row r="426" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -10133,7 +10135,7 @@
       <c r="K426" s="6"/>
       <c r="L426" s="6"/>
     </row>
-    <row r="427" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -10147,7 +10149,7 @@
       <c r="K427" s="6"/>
       <c r="L427" s="6"/>
     </row>
-    <row r="428" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -10161,7 +10163,7 @@
       <c r="K428" s="6"/>
       <c r="L428" s="6"/>
     </row>
-    <row r="429" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -10175,7 +10177,7 @@
       <c r="K429" s="6"/>
       <c r="L429" s="6"/>
     </row>
-    <row r="430" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -10189,7 +10191,7 @@
       <c r="K430" s="6"/>
       <c r="L430" s="6"/>
     </row>
-    <row r="431" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -10203,7 +10205,7 @@
       <c r="K431" s="6"/>
       <c r="L431" s="6"/>
     </row>
-    <row r="432" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -10217,7 +10219,7 @@
       <c r="K432" s="6"/>
       <c r="L432" s="6"/>
     </row>
-    <row r="433" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -10231,7 +10233,7 @@
       <c r="K433" s="6"/>
       <c r="L433" s="6"/>
     </row>
-    <row r="434" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -10245,7 +10247,7 @@
       <c r="K434" s="6"/>
       <c r="L434" s="6"/>
     </row>
-    <row r="435" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -10259,7 +10261,7 @@
       <c r="K435" s="6"/>
       <c r="L435" s="6"/>
     </row>
-    <row r="436" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -10273,7 +10275,7 @@
       <c r="K436" s="6"/>
       <c r="L436" s="6"/>
     </row>
-    <row r="437" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -10287,7 +10289,7 @@
       <c r="K437" s="6"/>
       <c r="L437" s="6"/>
     </row>
-    <row r="438" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -10301,7 +10303,7 @@
       <c r="K438" s="6"/>
       <c r="L438" s="6"/>
     </row>
-    <row r="439" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -10315,7 +10317,7 @@
       <c r="K439" s="6"/>
       <c r="L439" s="6"/>
     </row>
-    <row r="440" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -10329,7 +10331,7 @@
       <c r="K440" s="6"/>
       <c r="L440" s="6"/>
     </row>
-    <row r="441" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -10343,7 +10345,7 @@
       <c r="K441" s="6"/>
       <c r="L441" s="6"/>
     </row>
-    <row r="442" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -10357,7 +10359,7 @@
       <c r="K442" s="6"/>
       <c r="L442" s="6"/>
     </row>
-    <row r="443" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -10371,7 +10373,7 @@
       <c r="K443" s="6"/>
       <c r="L443" s="6"/>
     </row>
-    <row r="444" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -10385,7 +10387,7 @@
       <c r="K444" s="6"/>
       <c r="L444" s="6"/>
     </row>
-    <row r="445" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -10399,7 +10401,7 @@
       <c r="K445" s="6"/>
       <c r="L445" s="6"/>
     </row>
-    <row r="446" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -10413,7 +10415,7 @@
       <c r="K446" s="6"/>
       <c r="L446" s="6"/>
     </row>
-    <row r="447" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -10427,7 +10429,7 @@
       <c r="K447" s="6"/>
       <c r="L447" s="6"/>
     </row>
-    <row r="448" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A448" s="5"/>
       <c r="B448" s="5"/>
       <c r="C448" s="5"/>
@@ -10441,7 +10443,7 @@
       <c r="K448" s="6"/>
       <c r="L448" s="6"/>
     </row>
-    <row r="449" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A449" s="5"/>
       <c r="B449" s="5"/>
       <c r="C449" s="5"/>
@@ -10455,7 +10457,7 @@
       <c r="K449" s="6"/>
       <c r="L449" s="6"/>
     </row>
-    <row r="450" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A450" s="5"/>
       <c r="B450" s="5"/>
       <c r="C450" s="5"/>
@@ -10469,7 +10471,7 @@
       <c r="K450" s="6"/>
       <c r="L450" s="6"/>
     </row>
-    <row r="451" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A451" s="5"/>
       <c r="B451" s="5"/>
       <c r="C451" s="5"/>
@@ -10483,7 +10485,7 @@
       <c r="K451" s="6"/>
       <c r="L451" s="6"/>
     </row>
-    <row r="452" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A452" s="5"/>
       <c r="B452" s="5"/>
       <c r="C452" s="5"/>
@@ -10497,7 +10499,7 @@
       <c r="K452" s="6"/>
       <c r="L452" s="6"/>
     </row>
-    <row r="453" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A453" s="5"/>
       <c r="B453" s="5"/>
       <c r="C453" s="5"/>
@@ -10511,7 +10513,7 @@
       <c r="K453" s="6"/>
       <c r="L453" s="6"/>
     </row>
-    <row r="454" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A454" s="5"/>
       <c r="B454" s="5"/>
       <c r="C454" s="5"/>
@@ -10525,7 +10527,7 @@
       <c r="K454" s="6"/>
       <c r="L454" s="6"/>
     </row>
-    <row r="455" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A455" s="5"/>
       <c r="B455" s="5"/>
       <c r="C455" s="5"/>
@@ -10539,7 +10541,7 @@
       <c r="K455" s="6"/>
       <c r="L455" s="6"/>
     </row>
-    <row r="456" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A456" s="5"/>
       <c r="B456" s="5"/>
       <c r="C456" s="5"/>
@@ -10553,7 +10555,7 @@
       <c r="K456" s="6"/>
       <c r="L456" s="6"/>
     </row>
-    <row r="457" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A457" s="5"/>
       <c r="B457" s="5"/>
       <c r="C457" s="5"/>
@@ -10567,7 +10569,7 @@
       <c r="K457" s="6"/>
       <c r="L457" s="6"/>
     </row>
-    <row r="458" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A458" s="5"/>
       <c r="B458" s="5"/>
       <c r="C458" s="5"/>
@@ -10581,7 +10583,7 @@
       <c r="K458" s="6"/>
       <c r="L458" s="6"/>
     </row>
-    <row r="459" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A459" s="5"/>
       <c r="B459" s="5"/>
       <c r="C459" s="5"/>
@@ -10595,7 +10597,7 @@
       <c r="K459" s="6"/>
       <c r="L459" s="6"/>
     </row>
-    <row r="460" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A460" s="5"/>
       <c r="B460" s="5"/>
       <c r="C460" s="5"/>
@@ -10609,7 +10611,7 @@
       <c r="K460" s="6"/>
       <c r="L460" s="6"/>
     </row>
-    <row r="461" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A461" s="5"/>
       <c r="B461" s="5"/>
       <c r="C461" s="5"/>
@@ -10623,7 +10625,7 @@
       <c r="K461" s="6"/>
       <c r="L461" s="6"/>
     </row>
-    <row r="462" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A462" s="5"/>
       <c r="B462" s="5"/>
       <c r="C462" s="5"/>
@@ -10637,7 +10639,7 @@
       <c r="K462" s="6"/>
       <c r="L462" s="6"/>
     </row>
-    <row r="463" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A463" s="5"/>
       <c r="B463" s="5"/>
       <c r="C463" s="5"/>
@@ -10651,7 +10653,7 @@
       <c r="K463" s="6"/>
       <c r="L463" s="6"/>
     </row>
-    <row r="464" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A464" s="5"/>
       <c r="B464" s="5"/>
       <c r="C464" s="5"/>
@@ -10665,7 +10667,7 @@
       <c r="K464" s="6"/>
       <c r="L464" s="6"/>
     </row>
-    <row r="465" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A465" s="5"/>
       <c r="B465" s="5"/>
       <c r="C465" s="5"/>
@@ -10679,7 +10681,7 @@
       <c r="K465" s="6"/>
       <c r="L465" s="6"/>
     </row>
-    <row r="466" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A466" s="5"/>
       <c r="B466" s="5"/>
       <c r="C466" s="5"/>
@@ -10693,7 +10695,7 @@
       <c r="K466" s="6"/>
       <c r="L466" s="6"/>
     </row>
-    <row r="467" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A467" s="5"/>
       <c r="B467" s="5"/>
       <c r="C467" s="5"/>
@@ -10707,7 +10709,7 @@
       <c r="K467" s="6"/>
       <c r="L467" s="6"/>
     </row>
-    <row r="468" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A468" s="5"/>
       <c r="B468" s="5"/>
       <c r="C468" s="5"/>
@@ -10721,7 +10723,7 @@
       <c r="K468" s="6"/>
       <c r="L468" s="6"/>
     </row>
-    <row r="469" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A469" s="5"/>
       <c r="B469" s="5"/>
       <c r="C469" s="5"/>
@@ -10735,7 +10737,7 @@
       <c r="K469" s="6"/>
       <c r="L469" s="6"/>
     </row>
-    <row r="470" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A470" s="5"/>
       <c r="B470" s="5"/>
       <c r="C470" s="5"/>
@@ -10749,7 +10751,7 @@
       <c r="K470" s="6"/>
       <c r="L470" s="6"/>
     </row>
-    <row r="471" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A471" s="5"/>
       <c r="B471" s="5"/>
       <c r="C471" s="5"/>
@@ -10763,7 +10765,7 @@
       <c r="K471" s="6"/>
       <c r="L471" s="6"/>
     </row>
-    <row r="472" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A472" s="5"/>
       <c r="B472" s="5"/>
       <c r="C472" s="5"/>
@@ -10777,7 +10779,7 @@
       <c r="K472" s="6"/>
       <c r="L472" s="6"/>
     </row>
-    <row r="473" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A473" s="5"/>
       <c r="B473" s="5"/>
       <c r="C473" s="5"/>
@@ -10791,7 +10793,7 @@
       <c r="K473" s="6"/>
       <c r="L473" s="6"/>
     </row>
-    <row r="474" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A474" s="5"/>
       <c r="B474" s="5"/>
       <c r="C474" s="5"/>
@@ -10805,7 +10807,7 @@
       <c r="K474" s="6"/>
       <c r="L474" s="6"/>
     </row>
-    <row r="475" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A475" s="5"/>
       <c r="B475" s="5"/>
       <c r="C475" s="5"/>
@@ -10819,7 +10821,7 @@
       <c r="K475" s="6"/>
       <c r="L475" s="6"/>
     </row>
-    <row r="476" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A476" s="5"/>
       <c r="B476" s="5"/>
       <c r="C476" s="5"/>
@@ -10833,7 +10835,7 @@
       <c r="K476" s="6"/>
       <c r="L476" s="6"/>
     </row>
-    <row r="477" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A477" s="5"/>
       <c r="B477" s="5"/>
       <c r="C477" s="5"/>
@@ -10847,7 +10849,7 @@
       <c r="K477" s="6"/>
       <c r="L477" s="6"/>
     </row>
-    <row r="478" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A478" s="5"/>
       <c r="B478" s="5"/>
       <c r="C478" s="5"/>
@@ -10861,7 +10863,7 @@
       <c r="K478" s="6"/>
       <c r="L478" s="6"/>
     </row>
-    <row r="479" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A479" s="5"/>
       <c r="B479" s="5"/>
       <c r="C479" s="5"/>
@@ -10875,7 +10877,7 @@
       <c r="K479" s="6"/>
       <c r="L479" s="6"/>
     </row>
-    <row r="480" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A480" s="5"/>
       <c r="B480" s="5"/>
       <c r="C480" s="5"/>
@@ -10889,7 +10891,7 @@
       <c r="K480" s="6"/>
       <c r="L480" s="6"/>
     </row>
-    <row r="481" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A481" s="5"/>
       <c r="B481" s="5"/>
       <c r="C481" s="5"/>
@@ -10903,7 +10905,7 @@
       <c r="K481" s="6"/>
       <c r="L481" s="6"/>
     </row>
-    <row r="482" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A482" s="5"/>
       <c r="B482" s="5"/>
       <c r="C482" s="5"/>
@@ -10917,7 +10919,7 @@
       <c r="K482" s="6"/>
       <c r="L482" s="6"/>
     </row>
-    <row r="483" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A483" s="5"/>
       <c r="B483" s="5"/>
       <c r="C483" s="5"/>
@@ -10931,7 +10933,7 @@
       <c r="K483" s="6"/>
       <c r="L483" s="6"/>
     </row>
-    <row r="484" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A484" s="5"/>
       <c r="B484" s="5"/>
       <c r="C484" s="5"/>
@@ -10945,7 +10947,7 @@
       <c r="K484" s="6"/>
       <c r="L484" s="6"/>
     </row>
-    <row r="485" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A485" s="5"/>
       <c r="B485" s="5"/>
       <c r="C485" s="5"/>
@@ -10959,7 +10961,7 @@
       <c r="K485" s="6"/>
       <c r="L485" s="6"/>
     </row>
-    <row r="486" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A486" s="5"/>
       <c r="B486" s="5"/>
       <c r="C486" s="5"/>
@@ -10973,7 +10975,7 @@
       <c r="K486" s="6"/>
       <c r="L486" s="6"/>
     </row>
-    <row r="487" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A487" s="5"/>
       <c r="B487" s="5"/>
       <c r="C487" s="5"/>
@@ -10987,7 +10989,7 @@
       <c r="K487" s="6"/>
       <c r="L487" s="6"/>
     </row>
-    <row r="488" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A488" s="5"/>
       <c r="B488" s="5"/>
       <c r="C488" s="5"/>
@@ -11001,7 +11003,7 @@
       <c r="K488" s="6"/>
       <c r="L488" s="6"/>
     </row>
-    <row r="489" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A489" s="5"/>
       <c r="B489" s="5"/>
       <c r="C489" s="5"/>
@@ -11015,7 +11017,7 @@
       <c r="K489" s="6"/>
       <c r="L489" s="6"/>
     </row>
-    <row r="490" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A490" s="5"/>
       <c r="B490" s="5"/>
       <c r="C490" s="5"/>
@@ -11029,7 +11031,7 @@
       <c r="K490" s="6"/>
       <c r="L490" s="6"/>
     </row>
-    <row r="491" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A491" s="5"/>
       <c r="B491" s="5"/>
       <c r="C491" s="5"/>
@@ -11043,7 +11045,7 @@
       <c r="K491" s="6"/>
       <c r="L491" s="6"/>
     </row>
-    <row r="492" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A492" s="5"/>
       <c r="B492" s="5"/>
       <c r="C492" s="5"/>
@@ -11057,7 +11059,7 @@
       <c r="K492" s="6"/>
       <c r="L492" s="6"/>
     </row>
-    <row r="493" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A493" s="5"/>
       <c r="B493" s="5"/>
       <c r="C493" s="5"/>
@@ -11071,7 +11073,7 @@
       <c r="K493" s="6"/>
       <c r="L493" s="6"/>
     </row>
-    <row r="494" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A494" s="5"/>
       <c r="B494" s="5"/>
       <c r="C494" s="5"/>
@@ -11085,7 +11087,7 @@
       <c r="K494" s="6"/>
       <c r="L494" s="6"/>
     </row>
-    <row r="495" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A495" s="5"/>
       <c r="B495" s="5"/>
       <c r="C495" s="5"/>
@@ -11099,7 +11101,7 @@
       <c r="K495" s="6"/>
       <c r="L495" s="6"/>
     </row>
-    <row r="496" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A496" s="5"/>
       <c r="B496" s="5"/>
       <c r="C496" s="5"/>
@@ -11113,7 +11115,7 @@
       <c r="K496" s="6"/>
       <c r="L496" s="6"/>
     </row>
-    <row r="497" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A497" s="5"/>
       <c r="B497" s="5"/>
       <c r="C497" s="5"/>
@@ -11127,7 +11129,7 @@
       <c r="K497" s="6"/>
       <c r="L497" s="6"/>
     </row>
-    <row r="498" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A498" s="5"/>
       <c r="B498" s="5"/>
       <c r="C498" s="5"/>
@@ -11141,7 +11143,7 @@
       <c r="K498" s="6"/>
       <c r="L498" s="6"/>
     </row>
-    <row r="499" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A499" s="5"/>
       <c r="B499" s="5"/>
       <c r="C499" s="5"/>
@@ -11155,7 +11157,7 @@
       <c r="K499" s="6"/>
       <c r="L499" s="6"/>
     </row>
-    <row r="500" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A500" s="5"/>
       <c r="B500" s="5"/>
       <c r="C500" s="5"/>
@@ -11169,7 +11171,7 @@
       <c r="K500" s="6"/>
       <c r="L500" s="6"/>
     </row>
-    <row r="501" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A501" s="5"/>
       <c r="B501" s="5"/>
       <c r="C501" s="5"/>
@@ -11183,7 +11185,7 @@
       <c r="K501" s="6"/>
       <c r="L501" s="6"/>
     </row>
-    <row r="502" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A502" s="5"/>
       <c r="B502" s="5"/>
       <c r="C502" s="5"/>
@@ -11197,7 +11199,7 @@
       <c r="K502" s="6"/>
       <c r="L502" s="6"/>
     </row>
-    <row r="503" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A503" s="5"/>
       <c r="B503" s="5"/>
       <c r="C503" s="5"/>
@@ -11211,7 +11213,7 @@
       <c r="K503" s="6"/>
       <c r="L503" s="6"/>
     </row>
-    <row r="504" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A504" s="5"/>
       <c r="B504" s="5"/>
       <c r="C504" s="5"/>
@@ -11225,7 +11227,7 @@
       <c r="K504" s="6"/>
       <c r="L504" s="6"/>
     </row>
-    <row r="505" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A505" s="5"/>
       <c r="B505" s="5"/>
       <c r="C505" s="5"/>
@@ -11239,7 +11241,7 @@
       <c r="K505" s="6"/>
       <c r="L505" s="6"/>
     </row>
-    <row r="506" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A506" s="5"/>
       <c r="B506" s="5"/>
       <c r="C506" s="5"/>
@@ -11253,7 +11255,7 @@
       <c r="K506" s="6"/>
       <c r="L506" s="6"/>
     </row>
-    <row r="507" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A507" s="5"/>
       <c r="B507" s="5"/>
       <c r="C507" s="5"/>
@@ -11267,7 +11269,7 @@
       <c r="K507" s="6"/>
       <c r="L507" s="6"/>
     </row>
-    <row r="508" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A508" s="5"/>
       <c r="B508" s="5"/>
       <c r="C508" s="5"/>
@@ -11281,7 +11283,7 @@
       <c r="K508" s="6"/>
       <c r="L508" s="6"/>
     </row>
-    <row r="509" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A509" s="5"/>
       <c r="B509" s="5"/>
       <c r="C509" s="5"/>
@@ -11295,7 +11297,7 @@
       <c r="K509" s="6"/>
       <c r="L509" s="6"/>
     </row>
-    <row r="510" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A510" s="5"/>
       <c r="B510" s="5"/>
       <c r="C510" s="5"/>
@@ -11309,7 +11311,7 @@
       <c r="K510" s="6"/>
       <c r="L510" s="6"/>
     </row>
-    <row r="511" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A511" s="5"/>
       <c r="B511" s="5"/>
       <c r="C511" s="5"/>
@@ -11323,7 +11325,7 @@
       <c r="K511" s="6"/>
       <c r="L511" s="6"/>
     </row>
-    <row r="512" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A512" s="5"/>
       <c r="B512" s="5"/>
       <c r="C512" s="5"/>
@@ -11337,7 +11339,7 @@
       <c r="K512" s="6"/>
       <c r="L512" s="6"/>
     </row>
-    <row r="513" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A513" s="5"/>
       <c r="B513" s="5"/>
       <c r="C513" s="5"/>
@@ -11351,7 +11353,7 @@
       <c r="K513" s="6"/>
       <c r="L513" s="6"/>
     </row>
-    <row r="514" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A514" s="5"/>
       <c r="B514" s="5"/>
       <c r="C514" s="5"/>
@@ -11365,7 +11367,7 @@
       <c r="K514" s="6"/>
       <c r="L514" s="6"/>
     </row>
-    <row r="515" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A515" s="5"/>
       <c r="B515" s="5"/>
       <c r="C515" s="5"/>
@@ -11379,7 +11381,7 @@
       <c r="K515" s="6"/>
       <c r="L515" s="6"/>
     </row>
-    <row r="516" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A516" s="5"/>
       <c r="B516" s="5"/>
       <c r="C516" s="5"/>
@@ -11393,7 +11395,7 @@
       <c r="K516" s="6"/>
       <c r="L516" s="6"/>
     </row>
-    <row r="517" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A517" s="5"/>
       <c r="B517" s="5"/>
       <c r="C517" s="5"/>
@@ -11407,7 +11409,7 @@
       <c r="K517" s="6"/>
       <c r="L517" s="6"/>
     </row>
-    <row r="518" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A518" s="5"/>
       <c r="B518" s="5"/>
       <c r="C518" s="5"/>
@@ -11421,7 +11423,7 @@
       <c r="K518" s="6"/>
       <c r="L518" s="6"/>
     </row>
-    <row r="519" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A519" s="5"/>
       <c r="B519" s="5"/>
       <c r="C519" s="5"/>
@@ -11435,7 +11437,7 @@
       <c r="K519" s="6"/>
       <c r="L519" s="6"/>
     </row>
-    <row r="520" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A520" s="5"/>
       <c r="B520" s="5"/>
       <c r="C520" s="5"/>
@@ -11449,7 +11451,7 @@
       <c r="K520" s="6"/>
       <c r="L520" s="6"/>
     </row>
-    <row r="521" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A521" s="5"/>
       <c r="B521" s="5"/>
       <c r="C521" s="5"/>
@@ -11463,7 +11465,7 @@
       <c r="K521" s="6"/>
       <c r="L521" s="6"/>
     </row>
-    <row r="522" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A522" s="5"/>
       <c r="B522" s="5"/>
       <c r="C522" s="5"/>
@@ -11477,7 +11479,7 @@
       <c r="K522" s="6"/>
       <c r="L522" s="6"/>
     </row>
-    <row r="523" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A523" s="5"/>
       <c r="B523" s="5"/>
       <c r="C523" s="5"/>
@@ -11491,7 +11493,7 @@
       <c r="K523" s="6"/>
       <c r="L523" s="6"/>
     </row>
-    <row r="524" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A524" s="5"/>
       <c r="B524" s="5"/>
       <c r="C524" s="5"/>
@@ -11505,7 +11507,7 @@
       <c r="K524" s="6"/>
       <c r="L524" s="6"/>
     </row>
-    <row r="525" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A525" s="5"/>
       <c r="B525" s="5"/>
       <c r="C525" s="5"/>
@@ -11519,7 +11521,7 @@
       <c r="K525" s="6"/>
       <c r="L525" s="6"/>
     </row>
-    <row r="526" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A526" s="5"/>
       <c r="B526" s="5"/>
       <c r="C526" s="5"/>
@@ -11533,7 +11535,7 @@
       <c r="K526" s="6"/>
       <c r="L526" s="6"/>
     </row>
-    <row r="527" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A527" s="5"/>
       <c r="B527" s="5"/>
       <c r="C527" s="5"/>
@@ -11547,7 +11549,7 @@
       <c r="K527" s="6"/>
       <c r="L527" s="6"/>
     </row>
-    <row r="528" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A528" s="5"/>
       <c r="B528" s="5"/>
       <c r="C528" s="5"/>
@@ -11561,7 +11563,7 @@
       <c r="K528" s="6"/>
       <c r="L528" s="6"/>
     </row>
-    <row r="529" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A529" s="5"/>
       <c r="B529" s="5"/>
       <c r="C529" s="5"/>
@@ -11575,7 +11577,7 @@
       <c r="K529" s="6"/>
       <c r="L529" s="6"/>
     </row>
-    <row r="530" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A530" s="5"/>
       <c r="B530" s="5"/>
       <c r="C530" s="5"/>
@@ -11589,7 +11591,7 @@
       <c r="K530" s="6"/>
       <c r="L530" s="6"/>
     </row>
-    <row r="531" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A531" s="5"/>
       <c r="B531" s="5"/>
       <c r="C531" s="5"/>
@@ -11603,7 +11605,7 @@
       <c r="K531" s="6"/>
       <c r="L531" s="6"/>
     </row>
-    <row r="532" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A532" s="5"/>
       <c r="B532" s="5"/>
       <c r="C532" s="5"/>
@@ -11617,7 +11619,7 @@
       <c r="K532" s="6"/>
       <c r="L532" s="6"/>
     </row>
-    <row r="533" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A533" s="5"/>
       <c r="B533" s="5"/>
       <c r="C533" s="5"/>
@@ -11631,7 +11633,7 @@
       <c r="K533" s="6"/>
       <c r="L533" s="6"/>
     </row>
-    <row r="534" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A534" s="5"/>
       <c r="B534" s="5"/>
       <c r="C534" s="5"/>
@@ -11645,7 +11647,7 @@
       <c r="K534" s="6"/>
       <c r="L534" s="6"/>
     </row>
-    <row r="535" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A535" s="5"/>
       <c r="B535" s="5"/>
       <c r="C535" s="5"/>
@@ -11659,7 +11661,7 @@
       <c r="K535" s="6"/>
       <c r="L535" s="6"/>
     </row>
-    <row r="536" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A536" s="5"/>
       <c r="B536" s="5"/>
       <c r="C536" s="5"/>
@@ -11673,7 +11675,7 @@
       <c r="K536" s="6"/>
       <c r="L536" s="6"/>
     </row>
-    <row r="537" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A537" s="5"/>
       <c r="B537" s="5"/>
       <c r="C537" s="5"/>
@@ -11687,7 +11689,7 @@
       <c r="K537" s="6"/>
       <c r="L537" s="6"/>
     </row>
-    <row r="538" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A538" s="5"/>
       <c r="B538" s="5"/>
       <c r="C538" s="5"/>
@@ -11701,7 +11703,7 @@
       <c r="K538" s="6"/>
       <c r="L538" s="6"/>
     </row>
-    <row r="539" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A539" s="5"/>
       <c r="B539" s="5"/>
       <c r="C539" s="5"/>
@@ -11715,7 +11717,7 @@
       <c r="K539" s="6"/>
       <c r="L539" s="6"/>
     </row>
-    <row r="540" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A540" s="5"/>
       <c r="B540" s="5"/>
       <c r="C540" s="5"/>
@@ -11729,7 +11731,7 @@
       <c r="K540" s="6"/>
       <c r="L540" s="6"/>
     </row>
-    <row r="541" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A541" s="5"/>
       <c r="B541" s="5"/>
       <c r="C541" s="5"/>
@@ -11743,7 +11745,7 @@
       <c r="K541" s="6"/>
       <c r="L541" s="6"/>
     </row>
-    <row r="542" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A542" s="5"/>
       <c r="B542" s="5"/>
       <c r="C542" s="5"/>
@@ -11757,7 +11759,7 @@
       <c r="K542" s="6"/>
       <c r="L542" s="6"/>
     </row>
-    <row r="543" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A543" s="5"/>
       <c r="B543" s="5"/>
       <c r="C543" s="5"/>
@@ -11771,7 +11773,7 @@
       <c r="K543" s="6"/>
       <c r="L543" s="6"/>
     </row>
-    <row r="544" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A544" s="5"/>
       <c r="B544" s="5"/>
       <c r="C544" s="5"/>
@@ -11785,7 +11787,7 @@
       <c r="K544" s="6"/>
       <c r="L544" s="6"/>
     </row>
-    <row r="545" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A545" s="5"/>
       <c r="B545" s="5"/>
       <c r="C545" s="5"/>
@@ -11799,7 +11801,7 @@
       <c r="K545" s="6"/>
       <c r="L545" s="6"/>
     </row>
-    <row r="546" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A546" s="5"/>
       <c r="B546" s="5"/>
       <c r="C546" s="5"/>
@@ -11813,7 +11815,7 @@
       <c r="K546" s="6"/>
       <c r="L546" s="6"/>
     </row>
-    <row r="547" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A547" s="5"/>
       <c r="B547" s="5"/>
       <c r="C547" s="5"/>
@@ -11827,7 +11829,7 @@
       <c r="K547" s="6"/>
       <c r="L547" s="6"/>
     </row>
-    <row r="548" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A548" s="5"/>
       <c r="B548" s="5"/>
       <c r="C548" s="5"/>
@@ -11841,7 +11843,7 @@
       <c r="K548" s="6"/>
       <c r="L548" s="6"/>
     </row>
-    <row r="549" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A549" s="5"/>
       <c r="B549" s="5"/>
       <c r="C549" s="5"/>
@@ -11855,7 +11857,7 @@
       <c r="K549" s="6"/>
       <c r="L549" s="6"/>
     </row>
-    <row r="550" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A550" s="5"/>
       <c r="B550" s="5"/>
       <c r="C550" s="5"/>
@@ -11869,7 +11871,7 @@
       <c r="K550" s="6"/>
       <c r="L550" s="6"/>
     </row>
-    <row r="551" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A551" s="5"/>
       <c r="B551" s="5"/>
       <c r="C551" s="5"/>
@@ -11883,7 +11885,7 @@
       <c r="K551" s="6"/>
       <c r="L551" s="6"/>
     </row>
-    <row r="552" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A552" s="5"/>
       <c r="B552" s="5"/>
       <c r="C552" s="5"/>
@@ -11897,7 +11899,7 @@
       <c r="K552" s="6"/>
       <c r="L552" s="6"/>
     </row>
-    <row r="553" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A553" s="5"/>
       <c r="B553" s="5"/>
       <c r="C553" s="5"/>
@@ -11911,7 +11913,7 @@
       <c r="K553" s="6"/>
       <c r="L553" s="6"/>
     </row>
-    <row r="554" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A554" s="5"/>
       <c r="B554" s="5"/>
       <c r="C554" s="5"/>
@@ -11925,7 +11927,7 @@
       <c r="K554" s="6"/>
       <c r="L554" s="6"/>
     </row>
-    <row r="555" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A555" s="5"/>
       <c r="B555" s="5"/>
       <c r="C555" s="5"/>
@@ -11939,7 +11941,7 @@
       <c r="K555" s="6"/>
       <c r="L555" s="6"/>
     </row>
-    <row r="556" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A556" s="5"/>
       <c r="B556" s="5"/>
       <c r="C556" s="5"/>
@@ -11953,7 +11955,7 @@
       <c r="K556" s="6"/>
       <c r="L556" s="6"/>
     </row>
-    <row r="557" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A557" s="5"/>
       <c r="B557" s="5"/>
       <c r="C557" s="5"/>
@@ -11967,7 +11969,7 @@
       <c r="K557" s="6"/>
       <c r="L557" s="6"/>
     </row>
-    <row r="558" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A558" s="5"/>
       <c r="B558" s="5"/>
       <c r="C558" s="5"/>
@@ -11981,7 +11983,7 @@
       <c r="K558" s="6"/>
       <c r="L558" s="6"/>
     </row>
-    <row r="559" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A559" s="5"/>
       <c r="B559" s="5"/>
       <c r="C559" s="5"/>
@@ -11995,7 +11997,7 @@
       <c r="K559" s="6"/>
       <c r="L559" s="6"/>
     </row>
-    <row r="560" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A560" s="5"/>
       <c r="B560" s="5"/>
       <c r="C560" s="5"/>
@@ -12009,7 +12011,7 @@
       <c r="K560" s="6"/>
       <c r="L560" s="6"/>
     </row>
-    <row r="561" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A561" s="5"/>
       <c r="B561" s="5"/>
       <c r="C561" s="5"/>
@@ -12023,7 +12025,7 @@
       <c r="K561" s="6"/>
       <c r="L561" s="6"/>
     </row>
-    <row r="562" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A562" s="5"/>
       <c r="B562" s="5"/>
       <c r="C562" s="5"/>
@@ -12037,7 +12039,7 @@
       <c r="K562" s="6"/>
       <c r="L562" s="6"/>
     </row>
-    <row r="563" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A563" s="5"/>
       <c r="B563" s="5"/>
       <c r="C563" s="5"/>
@@ -12051,7 +12053,7 @@
       <c r="K563" s="6"/>
       <c r="L563" s="6"/>
     </row>
-    <row r="564" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A564" s="5"/>
       <c r="B564" s="5"/>
       <c r="C564" s="5"/>
@@ -12065,7 +12067,7 @@
       <c r="K564" s="6"/>
       <c r="L564" s="6"/>
     </row>
-    <row r="565" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A565" s="5"/>
       <c r="B565" s="5"/>
       <c r="C565" s="5"/>
@@ -12079,7 +12081,7 @@
       <c r="K565" s="6"/>
       <c r="L565" s="6"/>
     </row>
-    <row r="566" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A566" s="5"/>
       <c r="B566" s="5"/>
       <c r="C566" s="5"/>
@@ -12093,7 +12095,7 @@
       <c r="K566" s="6"/>
       <c r="L566" s="6"/>
     </row>
-    <row r="567" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A567" s="5"/>
       <c r="B567" s="5"/>
       <c r="C567" s="5"/>
@@ -12107,7 +12109,7 @@
       <c r="K567" s="6"/>
       <c r="L567" s="6"/>
     </row>
-    <row r="568" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A568" s="5"/>
       <c r="B568" s="5"/>
       <c r="C568" s="5"/>
@@ -12121,7 +12123,7 @@
       <c r="K568" s="6"/>
       <c r="L568" s="6"/>
     </row>
-    <row r="569" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A569" s="5"/>
       <c r="B569" s="5"/>
       <c r="C569" s="5"/>
@@ -12135,7 +12137,7 @@
       <c r="K569" s="6"/>
       <c r="L569" s="6"/>
     </row>
-    <row r="570" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A570" s="5"/>
       <c r="B570" s="5"/>
       <c r="C570" s="5"/>
@@ -12149,7 +12151,7 @@
       <c r="K570" s="6"/>
       <c r="L570" s="6"/>
     </row>
-    <row r="571" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A571" s="5"/>
       <c r="B571" s="5"/>
       <c r="C571" s="5"/>
@@ -12163,7 +12165,7 @@
       <c r="K571" s="6"/>
       <c r="L571" s="6"/>
     </row>
-    <row r="572" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A572" s="5"/>
       <c r="B572" s="5"/>
       <c r="C572" s="5"/>
@@ -12177,7 +12179,7 @@
       <c r="K572" s="6"/>
       <c r="L572" s="6"/>
     </row>
-    <row r="573" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A573" s="5"/>
       <c r="B573" s="5"/>
       <c r="C573" s="5"/>
@@ -12191,7 +12193,7 @@
       <c r="K573" s="6"/>
       <c r="L573" s="6"/>
     </row>
-    <row r="574" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A574" s="5"/>
       <c r="B574" s="5"/>
       <c r="C574" s="5"/>
@@ -12205,7 +12207,7 @@
       <c r="K574" s="6"/>
       <c r="L574" s="6"/>
     </row>
-    <row r="575" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A575" s="5"/>
       <c r="B575" s="5"/>
       <c r="C575" s="5"/>
@@ -12219,7 +12221,7 @@
       <c r="K575" s="6"/>
       <c r="L575" s="6"/>
     </row>
-    <row r="576" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A576" s="5"/>
       <c r="B576" s="5"/>
       <c r="C576" s="5"/>
@@ -12233,7 +12235,7 @@
       <c r="K576" s="6"/>
       <c r="L576" s="6"/>
     </row>
-    <row r="577" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A577" s="5"/>
       <c r="B577" s="5"/>
       <c r="C577" s="5"/>
@@ -12247,7 +12249,7 @@
       <c r="K577" s="6"/>
       <c r="L577" s="6"/>
     </row>
-    <row r="578" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A578" s="5"/>
       <c r="B578" s="5"/>
       <c r="C578" s="5"/>
@@ -12261,7 +12263,7 @@
       <c r="K578" s="6"/>
       <c r="L578" s="6"/>
     </row>
-    <row r="579" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A579" s="5"/>
       <c r="B579" s="5"/>
       <c r="C579" s="5"/>
@@ -12275,7 +12277,7 @@
       <c r="K579" s="6"/>
       <c r="L579" s="6"/>
     </row>
-    <row r="580" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A580" s="5"/>
       <c r="B580" s="5"/>
       <c r="C580" s="5"/>
@@ -12289,7 +12291,7 @@
       <c r="K580" s="6"/>
       <c r="L580" s="6"/>
     </row>
-    <row r="581" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A581" s="5"/>
       <c r="B581" s="5"/>
       <c r="C581" s="5"/>
@@ -12303,7 +12305,7 @@
       <c r="K581" s="6"/>
       <c r="L581" s="6"/>
     </row>
-    <row r="582" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A582" s="5"/>
       <c r="B582" s="5"/>
       <c r="C582" s="5"/>
@@ -12317,7 +12319,7 @@
       <c r="K582" s="6"/>
       <c r="L582" s="6"/>
     </row>
-    <row r="583" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A583" s="5"/>
       <c r="B583" s="5"/>
       <c r="C583" s="5"/>
@@ -12331,7 +12333,7 @@
       <c r="K583" s="6"/>
       <c r="L583" s="6"/>
     </row>
-    <row r="584" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A584" s="5"/>
       <c r="B584" s="5"/>
       <c r="C584" s="5"/>
@@ -12345,7 +12347,7 @@
       <c r="K584" s="6"/>
       <c r="L584" s="6"/>
     </row>
-    <row r="585" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A585" s="5"/>
       <c r="B585" s="5"/>
       <c r="C585" s="5"/>
@@ -12359,7 +12361,7 @@
       <c r="K585" s="6"/>
       <c r="L585" s="6"/>
     </row>
-    <row r="586" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A586" s="5"/>
       <c r="B586" s="5"/>
       <c r="C586" s="5"/>
@@ -12373,7 +12375,7 @@
       <c r="K586" s="6"/>
       <c r="L586" s="6"/>
     </row>
-    <row r="587" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A587" s="5"/>
       <c r="B587" s="5"/>
       <c r="C587" s="5"/>
@@ -12387,7 +12389,7 @@
       <c r="K587" s="6"/>
       <c r="L587" s="6"/>
     </row>
-    <row r="588" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A588" s="5"/>
       <c r="B588" s="5"/>
       <c r="C588" s="5"/>
@@ -12401,7 +12403,7 @@
       <c r="K588" s="6"/>
       <c r="L588" s="6"/>
     </row>
-    <row r="589" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A589" s="5"/>
       <c r="B589" s="5"/>
       <c r="C589" s="5"/>
@@ -12415,7 +12417,7 @@
       <c r="K589" s="6"/>
       <c r="L589" s="6"/>
     </row>
-    <row r="590" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A590" s="5"/>
       <c r="B590" s="5"/>
       <c r="C590" s="5"/>
@@ -12429,7 +12431,7 @@
       <c r="K590" s="6"/>
       <c r="L590" s="6"/>
     </row>
-    <row r="591" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A591" s="5"/>
       <c r="B591" s="5"/>
       <c r="C591" s="5"/>
@@ -12443,7 +12445,7 @@
       <c r="K591" s="6"/>
       <c r="L591" s="6"/>
     </row>
-    <row r="592" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A592" s="5"/>
       <c r="B592" s="5"/>
       <c r="C592" s="5"/>
@@ -12457,7 +12459,7 @@
       <c r="K592" s="6"/>
       <c r="L592" s="6"/>
     </row>
-    <row r="593" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A593" s="5"/>
       <c r="B593" s="5"/>
       <c r="C593" s="5"/>
@@ -12471,7 +12473,7 @@
       <c r="K593" s="6"/>
       <c r="L593" s="6"/>
     </row>
-    <row r="594" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A594" s="5"/>
       <c r="B594" s="5"/>
       <c r="C594" s="5"/>
@@ -12485,7 +12487,7 @@
       <c r="K594" s="6"/>
       <c r="L594" s="6"/>
     </row>
-    <row r="595" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A595" s="5"/>
       <c r="B595" s="5"/>
       <c r="C595" s="5"/>
@@ -12499,7 +12501,7 @@
       <c r="K595" s="6"/>
       <c r="L595" s="6"/>
     </row>
-    <row r="596" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A596" s="5"/>
       <c r="B596" s="5"/>
       <c r="C596" s="5"/>
@@ -12513,7 +12515,7 @@
       <c r="K596" s="6"/>
       <c r="L596" s="6"/>
     </row>
-    <row r="597" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A597" s="5"/>
       <c r="B597" s="5"/>
       <c r="C597" s="5"/>
@@ -12527,7 +12529,7 @@
       <c r="K597" s="6"/>
       <c r="L597" s="6"/>
     </row>
-    <row r="598" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A598" s="5"/>
       <c r="B598" s="5"/>
       <c r="C598" s="5"/>
@@ -12541,7 +12543,7 @@
       <c r="K598" s="6"/>
       <c r="L598" s="6"/>
     </row>
-    <row r="599" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A599" s="5"/>
       <c r="B599" s="5"/>
       <c r="C599" s="5"/>
@@ -12555,7 +12557,7 @@
       <c r="K599" s="6"/>
       <c r="L599" s="6"/>
     </row>
-    <row r="600" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A600" s="5"/>
       <c r="B600" s="5"/>
       <c r="C600" s="5"/>
@@ -12569,7 +12571,7 @@
       <c r="K600" s="6"/>
       <c r="L600" s="6"/>
     </row>
-    <row r="601" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A601" s="5"/>
       <c r="B601" s="5"/>
       <c r="C601" s="5"/>
@@ -12583,7 +12585,7 @@
       <c r="K601" s="6"/>
       <c r="L601" s="6"/>
     </row>
-    <row r="602" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A602" s="5"/>
       <c r="B602" s="5"/>
       <c r="C602" s="5"/>
@@ -12597,7 +12599,7 @@
       <c r="K602" s="6"/>
       <c r="L602" s="6"/>
     </row>
-    <row r="603" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A603" s="5"/>
       <c r="B603" s="5"/>
       <c r="C603" s="5"/>
@@ -12611,7 +12613,7 @@
       <c r="K603" s="6"/>
       <c r="L603" s="6"/>
     </row>
-    <row r="604" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A604" s="5"/>
       <c r="B604" s="5"/>
       <c r="C604" s="5"/>
@@ -12625,7 +12627,7 @@
       <c r="K604" s="6"/>
       <c r="L604" s="6"/>
     </row>
-    <row r="605" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A605" s="5"/>
       <c r="B605" s="5"/>
       <c r="C605" s="5"/>
@@ -12639,7 +12641,7 @@
       <c r="K605" s="6"/>
       <c r="L605" s="6"/>
     </row>
-    <row r="606" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A606" s="5"/>
       <c r="B606" s="5"/>
       <c r="C606" s="5"/>
@@ -12653,7 +12655,7 @@
       <c r="K606" s="6"/>
       <c r="L606" s="6"/>
     </row>
-    <row r="607" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A607" s="5"/>
       <c r="B607" s="5"/>
       <c r="C607" s="5"/>
@@ -12667,7 +12669,7 @@
       <c r="K607" s="6"/>
       <c r="L607" s="6"/>
     </row>
-    <row r="608" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A608" s="5"/>
       <c r="B608" s="5"/>
       <c r="C608" s="5"/>
@@ -12681,7 +12683,7 @@
       <c r="K608" s="6"/>
       <c r="L608" s="6"/>
     </row>
-    <row r="609" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A609" s="5"/>
       <c r="B609" s="5"/>
       <c r="C609" s="5"/>
@@ -12695,7 +12697,7 @@
       <c r="K609" s="6"/>
       <c r="L609" s="6"/>
     </row>
-    <row r="610" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A610" s="5"/>
       <c r="B610" s="5"/>
       <c r="C610" s="5"/>
@@ -12709,7 +12711,7 @@
       <c r="K610" s="6"/>
       <c r="L610" s="6"/>
     </row>
-    <row r="611" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A611" s="5"/>
       <c r="B611" s="5"/>
       <c r="C611" s="5"/>
@@ -12723,7 +12725,7 @@
       <c r="K611" s="6"/>
       <c r="L611" s="6"/>
     </row>
-    <row r="612" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A612" s="5"/>
       <c r="B612" s="5"/>
       <c r="C612" s="5"/>
@@ -12737,7 +12739,7 @@
       <c r="K612" s="6"/>
       <c r="L612" s="6"/>
     </row>
-    <row r="613" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A613" s="5"/>
       <c r="B613" s="5"/>
       <c r="C613" s="5"/>
@@ -12751,7 +12753,7 @@
       <c r="K613" s="6"/>
       <c r="L613" s="6"/>
     </row>
-    <row r="614" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A614" s="5"/>
       <c r="B614" s="5"/>
       <c r="C614" s="5"/>
@@ -12765,7 +12767,7 @@
       <c r="K614" s="6"/>
       <c r="L614" s="6"/>
     </row>
-    <row r="615" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A615" s="5"/>
       <c r="B615" s="5"/>
       <c r="C615" s="5"/>
@@ -12779,7 +12781,7 @@
       <c r="K615" s="6"/>
       <c r="L615" s="6"/>
     </row>
-    <row r="616" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A616" s="5"/>
       <c r="B616" s="5"/>
       <c r="C616" s="5"/>
@@ -12793,7 +12795,7 @@
       <c r="K616" s="6"/>
       <c r="L616" s="6"/>
     </row>
-    <row r="617" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A617" s="5"/>
       <c r="B617" s="5"/>
       <c r="C617" s="5"/>
@@ -12807,7 +12809,7 @@
       <c r="K617" s="6"/>
       <c r="L617" s="6"/>
     </row>
-    <row r="618" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A618" s="5"/>
       <c r="B618" s="5"/>
       <c r="C618" s="5"/>
@@ -12821,7 +12823,7 @@
       <c r="K618" s="6"/>
       <c r="L618" s="6"/>
     </row>
-    <row r="619" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A619" s="5"/>
       <c r="B619" s="5"/>
       <c r="C619" s="5"/>
@@ -12835,7 +12837,7 @@
       <c r="K619" s="6"/>
       <c r="L619" s="6"/>
     </row>
-    <row r="620" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A620" s="5"/>
       <c r="B620" s="5"/>
       <c r="C620" s="5"/>
@@ -12849,7 +12851,7 @@
       <c r="K620" s="6"/>
       <c r="L620" s="6"/>
     </row>
-    <row r="621" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A621" s="5"/>
       <c r="B621" s="5"/>
       <c r="C621" s="5"/>
@@ -12863,7 +12865,7 @@
       <c r="K621" s="6"/>
       <c r="L621" s="6"/>
     </row>
-    <row r="622" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A622" s="5"/>
       <c r="B622" s="5"/>
       <c r="C622" s="5"/>
@@ -12877,7 +12879,7 @@
       <c r="K622" s="6"/>
       <c r="L622" s="6"/>
     </row>
-    <row r="623" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A623" s="5"/>
       <c r="B623" s="5"/>
       <c r="C623" s="5"/>
@@ -12891,7 +12893,7 @@
       <c r="K623" s="6"/>
       <c r="L623" s="6"/>
     </row>
-    <row r="624" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A624" s="5"/>
       <c r="B624" s="5"/>
       <c r="C624" s="5"/>
@@ -12905,7 +12907,7 @@
       <c r="K624" s="6"/>
       <c r="L624" s="6"/>
     </row>
-    <row r="625" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A625" s="5"/>
       <c r="B625" s="5"/>
       <c r="C625" s="5"/>
@@ -12919,7 +12921,7 @@
       <c r="K625" s="6"/>
       <c r="L625" s="6"/>
     </row>
-    <row r="626" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A626" s="5"/>
       <c r="B626" s="5"/>
       <c r="C626" s="5"/>
@@ -12933,7 +12935,7 @@
       <c r="K626" s="6"/>
       <c r="L626" s="6"/>
     </row>
-    <row r="627" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A627" s="5"/>
       <c r="B627" s="5"/>
       <c r="C627" s="5"/>
@@ -12947,7 +12949,7 @@
       <c r="K627" s="6"/>
       <c r="L627" s="6"/>
     </row>
-    <row r="628" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A628" s="5"/>
       <c r="B628" s="5"/>
       <c r="C628" s="5"/>
@@ -12961,7 +12963,7 @@
       <c r="K628" s="6"/>
       <c r="L628" s="6"/>
     </row>
-    <row r="629" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A629" s="5"/>
       <c r="B629" s="5"/>
       <c r="C629" s="5"/>
@@ -12975,7 +12977,7 @@
       <c r="K629" s="6"/>
       <c r="L629" s="6"/>
     </row>
-    <row r="630" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A630" s="5"/>
       <c r="B630" s="5"/>
       <c r="C630" s="5"/>
@@ -12989,7 +12991,7 @@
       <c r="K630" s="6"/>
       <c r="L630" s="6"/>
     </row>
-    <row r="631" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A631" s="5"/>
       <c r="B631" s="5"/>
       <c r="C631" s="5"/>
@@ -13003,7 +13005,7 @@
       <c r="K631" s="6"/>
       <c r="L631" s="6"/>
     </row>
-    <row r="632" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A632" s="5"/>
       <c r="B632" s="5"/>
       <c r="C632" s="5"/>
@@ -13017,7 +13019,7 @@
       <c r="K632" s="6"/>
       <c r="L632" s="6"/>
     </row>
-    <row r="633" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A633" s="5"/>
       <c r="B633" s="5"/>
       <c r="C633" s="5"/>
@@ -13031,7 +13033,7 @@
       <c r="K633" s="6"/>
       <c r="L633" s="6"/>
     </row>
-    <row r="634" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A634" s="5"/>
       <c r="B634" s="5"/>
       <c r="C634" s="5"/>
@@ -13045,7 +13047,7 @@
       <c r="K634" s="6"/>
       <c r="L634" s="6"/>
     </row>
-    <row r="635" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A635" s="5"/>
       <c r="B635" s="5"/>
       <c r="C635" s="5"/>
@@ -13059,7 +13061,7 @@
       <c r="K635" s="6"/>
       <c r="L635" s="6"/>
     </row>
-    <row r="636" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A636" s="5"/>
       <c r="B636" s="5"/>
       <c r="C636" s="5"/>
@@ -13073,7 +13075,7 @@
       <c r="K636" s="6"/>
       <c r="L636" s="6"/>
     </row>
-    <row r="637" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A637" s="5"/>
       <c r="B637" s="5"/>
       <c r="C637" s="5"/>
@@ -13087,7 +13089,7 @@
       <c r="K637" s="6"/>
       <c r="L637" s="6"/>
     </row>
-    <row r="638" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A638" s="5"/>
       <c r="B638" s="5"/>
       <c r="C638" s="5"/>
@@ -13101,7 +13103,7 @@
       <c r="K638" s="6"/>
       <c r="L638" s="6"/>
     </row>
-    <row r="639" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A639" s="5"/>
       <c r="B639" s="5"/>
       <c r="C639" s="5"/>
@@ -13115,7 +13117,7 @@
       <c r="K639" s="6"/>
       <c r="L639" s="6"/>
     </row>
-    <row r="640" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A640" s="5"/>
       <c r="B640" s="5"/>
       <c r="C640" s="5"/>
@@ -13129,7 +13131,7 @@
       <c r="K640" s="6"/>
       <c r="L640" s="6"/>
     </row>
-    <row r="641" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A641" s="5"/>
       <c r="B641" s="5"/>
       <c r="C641" s="5"/>
@@ -13143,7 +13145,7 @@
       <c r="K641" s="6"/>
       <c r="L641" s="6"/>
     </row>
-    <row r="642" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A642" s="5"/>
       <c r="B642" s="5"/>
       <c r="C642" s="5"/>
@@ -13157,7 +13159,7 @@
       <c r="K642" s="6"/>
       <c r="L642" s="6"/>
     </row>
-    <row r="643" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A643" s="5"/>
       <c r="B643" s="5"/>
       <c r="C643" s="5"/>
@@ -13171,7 +13173,7 @@
       <c r="K643" s="6"/>
       <c r="L643" s="6"/>
     </row>
-    <row r="644" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A644" s="5"/>
       <c r="B644" s="5"/>
       <c r="C644" s="5"/>
@@ -13185,7 +13187,7 @@
       <c r="K644" s="6"/>
       <c r="L644" s="6"/>
     </row>
-    <row r="645" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A645" s="5"/>
       <c r="B645" s="5"/>
       <c r="C645" s="5"/>
@@ -13199,7 +13201,7 @@
       <c r="K645" s="6"/>
       <c r="L645" s="6"/>
     </row>
-    <row r="646" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A646" s="5"/>
       <c r="B646" s="5"/>
       <c r="C646" s="5"/>
@@ -13213,7 +13215,7 @@
       <c r="K646" s="6"/>
       <c r="L646" s="6"/>
     </row>
-    <row r="647" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A647" s="5"/>
       <c r="B647" s="5"/>
       <c r="C647" s="5"/>
@@ -13227,7 +13229,7 @@
       <c r="K647" s="6"/>
       <c r="L647" s="6"/>
     </row>
-    <row r="648" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A648" s="5"/>
       <c r="B648" s="5"/>
       <c r="C648" s="5"/>
@@ -13241,7 +13243,7 @@
       <c r="K648" s="6"/>
       <c r="L648" s="6"/>
     </row>
-    <row r="649" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A649" s="5"/>
       <c r="B649" s="5"/>
       <c r="C649" s="5"/>
@@ -13255,7 +13257,7 @@
       <c r="K649" s="6"/>
       <c r="L649" s="6"/>
     </row>
-    <row r="650" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A650" s="5"/>
       <c r="B650" s="5"/>
       <c r="C650" s="5"/>
@@ -13269,7 +13271,7 @@
       <c r="K650" s="6"/>
       <c r="L650" s="6"/>
     </row>
-    <row r="651" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A651" s="5"/>
       <c r="B651" s="5"/>
       <c r="C651" s="5"/>
@@ -13283,7 +13285,7 @@
       <c r="K651" s="6"/>
       <c r="L651" s="6"/>
     </row>
-    <row r="652" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A652" s="5"/>
       <c r="B652" s="5"/>
       <c r="C652" s="5"/>
@@ -13297,7 +13299,7 @@
       <c r="K652" s="6"/>
       <c r="L652" s="6"/>
     </row>
-    <row r="653" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A653" s="5"/>
       <c r="B653" s="5"/>
       <c r="C653" s="5"/>
@@ -13311,7 +13313,7 @@
       <c r="K653" s="6"/>
       <c r="L653" s="6"/>
     </row>
-    <row r="654" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A654" s="5"/>
       <c r="B654" s="5"/>
       <c r="C654" s="5"/>
@@ -13325,7 +13327,7 @@
       <c r="K654" s="6"/>
       <c r="L654" s="6"/>
     </row>
-    <row r="655" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A655" s="5"/>
       <c r="B655" s="5"/>
       <c r="C655" s="5"/>
@@ -13339,7 +13341,7 @@
       <c r="K655" s="6"/>
       <c r="L655" s="6"/>
     </row>
-    <row r="656" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A656" s="5"/>
       <c r="B656" s="5"/>
       <c r="C656" s="5"/>
@@ -13353,7 +13355,7 @@
       <c r="K656" s="6"/>
       <c r="L656" s="6"/>
     </row>
-    <row r="657" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A657" s="5"/>
       <c r="B657" s="5"/>
       <c r="C657" s="5"/>
@@ -13367,7 +13369,7 @@
       <c r="K657" s="6"/>
       <c r="L657" s="6"/>
     </row>
-    <row r="658" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A658" s="5"/>
       <c r="B658" s="5"/>
       <c r="C658" s="5"/>
@@ -13381,7 +13383,7 @@
       <c r="K658" s="6"/>
       <c r="L658" s="6"/>
     </row>
-    <row r="659" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A659" s="5"/>
       <c r="B659" s="5"/>
       <c r="C659" s="5"/>
@@ -13395,7 +13397,7 @@
       <c r="K659" s="6"/>
       <c r="L659" s="6"/>
     </row>
-    <row r="660" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A660" s="5"/>
       <c r="B660" s="5"/>
       <c r="C660" s="5"/>
@@ -13409,7 +13411,7 @@
       <c r="K660" s="6"/>
       <c r="L660" s="6"/>
     </row>
-    <row r="661" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A661" s="5"/>
       <c r="B661" s="5"/>
       <c r="C661" s="5"/>
@@ -13423,7 +13425,7 @@
       <c r="K661" s="6"/>
       <c r="L661" s="6"/>
     </row>
-    <row r="662" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A662" s="5"/>
       <c r="B662" s="5"/>
       <c r="C662" s="5"/>
@@ -13437,7 +13439,7 @@
       <c r="K662" s="6"/>
       <c r="L662" s="6"/>
     </row>
-    <row r="663" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A663" s="5"/>
       <c r="B663" s="5"/>
       <c r="C663" s="5"/>
@@ -13451,7 +13453,7 @@
       <c r="K663" s="6"/>
       <c r="L663" s="6"/>
     </row>
-    <row r="664" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A664" s="5"/>
       <c r="B664" s="5"/>
       <c r="C664" s="5"/>
@@ -13465,7 +13467,7 @@
       <c r="K664" s="6"/>
       <c r="L664" s="6"/>
     </row>
-    <row r="665" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A665" s="5"/>
       <c r="B665" s="5"/>
       <c r="C665" s="5"/>
@@ -13479,7 +13481,7 @@
       <c r="K665" s="6"/>
       <c r="L665" s="6"/>
     </row>
-    <row r="666" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A666" s="5"/>
       <c r="B666" s="5"/>
       <c r="C666" s="5"/>
@@ -13493,7 +13495,7 @@
       <c r="K666" s="6"/>
       <c r="L666" s="6"/>
     </row>
-    <row r="667" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A667" s="5"/>
       <c r="B667" s="5"/>
       <c r="C667" s="5"/>
@@ -13507,7 +13509,7 @@
       <c r="K667" s="6"/>
       <c r="L667" s="6"/>
     </row>
-    <row r="668" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A668" s="5"/>
       <c r="B668" s="5"/>
       <c r="C668" s="5"/>
@@ -13521,7 +13523,7 @@
       <c r="K668" s="6"/>
       <c r="L668" s="6"/>
     </row>
-    <row r="669" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A669" s="5"/>
       <c r="B669" s="5"/>
       <c r="C669" s="5"/>
@@ -13535,7 +13537,7 @@
       <c r="K669" s="6"/>
       <c r="L669" s="6"/>
     </row>
-    <row r="670" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A670" s="5"/>
       <c r="B670" s="5"/>
       <c r="C670" s="5"/>
@@ -13549,7 +13551,7 @@
       <c r="K670" s="6"/>
       <c r="L670" s="6"/>
     </row>
-    <row r="671" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A671" s="5"/>
       <c r="B671" s="5"/>
       <c r="C671" s="5"/>
@@ -13563,7 +13565,7 @@
       <c r="K671" s="6"/>
       <c r="L671" s="6"/>
     </row>
-    <row r="672" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A672" s="5"/>
       <c r="B672" s="5"/>
       <c r="C672" s="5"/>
@@ -13577,7 +13579,7 @@
       <c r="K672" s="6"/>
       <c r="L672" s="6"/>
     </row>
-    <row r="673" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A673" s="5"/>
       <c r="B673" s="5"/>
       <c r="C673" s="5"/>
@@ -13591,7 +13593,7 @@
       <c r="K673" s="6"/>
       <c r="L673" s="6"/>
     </row>
-    <row r="674" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A674" s="5"/>
       <c r="B674" s="5"/>
       <c r="C674" s="5"/>
@@ -13605,7 +13607,7 @@
       <c r="K674" s="6"/>
       <c r="L674" s="6"/>
     </row>
-    <row r="675" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A675" s="5"/>
       <c r="B675" s="5"/>
       <c r="C675" s="5"/>
@@ -13619,7 +13621,7 @@
       <c r="K675" s="6"/>
       <c r="L675" s="6"/>
     </row>
-    <row r="676" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A676" s="5"/>
       <c r="B676" s="5"/>
       <c r="C676" s="5"/>
@@ -13633,7 +13635,7 @@
       <c r="K676" s="6"/>
       <c r="L676" s="6"/>
     </row>
-    <row r="677" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A677" s="5"/>
       <c r="B677" s="5"/>
       <c r="C677" s="5"/>
@@ -13647,7 +13649,7 @@
       <c r="K677" s="6"/>
       <c r="L677" s="6"/>
     </row>
-    <row r="678" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A678" s="5"/>
       <c r="B678" s="5"/>
       <c r="C678" s="5"/>
@@ -13661,7 +13663,7 @@
       <c r="K678" s="6"/>
       <c r="L678" s="6"/>
     </row>
-    <row r="679" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A679" s="5"/>
       <c r="B679" s="5"/>
       <c r="C679" s="5"/>
@@ -13675,7 +13677,7 @@
       <c r="K679" s="6"/>
       <c r="L679" s="6"/>
     </row>
-    <row r="680" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A680" s="5"/>
       <c r="B680" s="5"/>
       <c r="C680" s="5"/>
@@ -13689,7 +13691,7 @@
       <c r="K680" s="6"/>
       <c r="L680" s="6"/>
     </row>
-    <row r="681" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A681" s="5"/>
       <c r="B681" s="5"/>
       <c r="C681" s="5"/>
@@ -13703,7 +13705,7 @@
       <c r="K681" s="6"/>
       <c r="L681" s="6"/>
     </row>
-    <row r="682" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A682" s="5"/>
       <c r="B682" s="5"/>
       <c r="C682" s="5"/>
@@ -13717,7 +13719,7 @@
       <c r="K682" s="6"/>
       <c r="L682" s="6"/>
     </row>
-    <row r="683" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A683" s="5"/>
       <c r="B683" s="5"/>
       <c r="C683" s="5"/>
@@ -13731,7 +13733,7 @@
       <c r="K683" s="6"/>
       <c r="L683" s="6"/>
     </row>
-    <row r="684" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A684" s="5"/>
       <c r="B684" s="5"/>
       <c r="C684" s="5"/>
@@ -13745,7 +13747,7 @@
       <c r="K684" s="6"/>
       <c r="L684" s="6"/>
     </row>
-    <row r="685" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A685" s="5"/>
       <c r="B685" s="5"/>
       <c r="C685" s="5"/>
@@ -13759,7 +13761,7 @@
       <c r="K685" s="6"/>
       <c r="L685" s="6"/>
     </row>
-    <row r="686" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A686" s="5"/>
       <c r="B686" s="5"/>
       <c r="C686" s="5"/>
@@ -13773,7 +13775,7 @@
       <c r="K686" s="6"/>
       <c r="L686" s="6"/>
     </row>
-    <row r="687" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A687" s="5"/>
       <c r="B687" s="5"/>
       <c r="C687" s="5"/>
@@ -13787,7 +13789,7 @@
       <c r="K687" s="6"/>
       <c r="L687" s="6"/>
     </row>
-    <row r="688" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A688" s="5"/>
       <c r="B688" s="5"/>
       <c r="C688" s="5"/>
@@ -13801,7 +13803,7 @@
       <c r="K688" s="6"/>
       <c r="L688" s="6"/>
     </row>
-    <row r="689" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A689" s="5"/>
       <c r="B689" s="5"/>
       <c r="C689" s="5"/>
@@ -13815,7 +13817,7 @@
       <c r="K689" s="6"/>
       <c r="L689" s="6"/>
     </row>
-    <row r="690" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A690" s="5"/>
       <c r="B690" s="5"/>
       <c r="C690" s="5"/>
@@ -13829,7 +13831,7 @@
       <c r="K690" s="6"/>
       <c r="L690" s="6"/>
     </row>
-    <row r="691" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A691" s="5"/>
       <c r="B691" s="5"/>
       <c r="C691" s="5"/>
@@ -13843,7 +13845,7 @@
       <c r="K691" s="6"/>
       <c r="L691" s="6"/>
     </row>
-    <row r="692" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A692" s="5"/>
       <c r="B692" s="5"/>
       <c r="C692" s="5"/>
@@ -13857,7 +13859,7 @@
       <c r="K692" s="6"/>
       <c r="L692" s="6"/>
     </row>
-    <row r="693" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A693" s="5"/>
       <c r="B693" s="5"/>
       <c r="C693" s="5"/>
@@ -13871,7 +13873,7 @@
       <c r="K693" s="6"/>
       <c r="L693" s="6"/>
     </row>
-    <row r="694" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A694" s="5"/>
       <c r="B694" s="5"/>
       <c r="C694" s="5"/>
@@ -13885,7 +13887,7 @@
       <c r="K694" s="6"/>
       <c r="L694" s="6"/>
     </row>
-    <row r="695" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A695" s="5"/>
       <c r="B695" s="5"/>
       <c r="C695" s="5"/>
@@ -13899,7 +13901,7 @@
       <c r="K695" s="6"/>
       <c r="L695" s="6"/>
     </row>
-    <row r="696" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A696" s="5"/>
       <c r="B696" s="5"/>
       <c r="C696" s="5"/>
@@ -13913,7 +13915,7 @@
       <c r="K696" s="6"/>
       <c r="L696" s="6"/>
     </row>
-    <row r="697" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A697" s="5"/>
       <c r="B697" s="5"/>
       <c r="C697" s="5"/>
@@ -13927,7 +13929,7 @@
       <c r="K697" s="6"/>
       <c r="L697" s="6"/>
     </row>
-    <row r="698" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A698" s="5"/>
       <c r="B698" s="5"/>
       <c r="C698" s="5"/>
@@ -13941,7 +13943,7 @@
       <c r="K698" s="6"/>
       <c r="L698" s="6"/>
     </row>
-    <row r="699" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A699" s="5"/>
       <c r="B699" s="5"/>
       <c r="C699" s="5"/>
@@ -13955,7 +13957,7 @@
       <c r="K699" s="6"/>
       <c r="L699" s="6"/>
     </row>
-    <row r="700" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A700" s="5"/>
       <c r="B700" s="5"/>
       <c r="C700" s="5"/>
@@ -13969,7 +13971,7 @@
       <c r="K700" s="6"/>
       <c r="L700" s="6"/>
     </row>
-    <row r="701" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A701" s="5"/>
       <c r="B701" s="5"/>
       <c r="C701" s="5"/>
@@ -13983,7 +13985,7 @@
       <c r="K701" s="6"/>
       <c r="L701" s="6"/>
     </row>
-    <row r="702" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A702" s="5"/>
       <c r="B702" s="5"/>
       <c r="C702" s="5"/>
@@ -13997,7 +13999,7 @@
       <c r="K702" s="6"/>
       <c r="L702" s="6"/>
     </row>
-    <row r="703" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A703" s="5"/>
       <c r="B703" s="5"/>
       <c r="C703" s="5"/>
@@ -14011,7 +14013,7 @@
       <c r="K703" s="6"/>
       <c r="L703" s="6"/>
     </row>
-    <row r="704" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A704" s="5"/>
       <c r="B704" s="5"/>
       <c r="C704" s="5"/>
@@ -14025,7 +14027,7 @@
       <c r="K704" s="6"/>
       <c r="L704" s="6"/>
     </row>
-    <row r="705" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A705" s="5"/>
       <c r="B705" s="5"/>
       <c r="C705" s="5"/>
@@ -14039,7 +14041,7 @@
       <c r="K705" s="6"/>
       <c r="L705" s="6"/>
     </row>
-    <row r="706" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A706" s="5"/>
       <c r="B706" s="5"/>
       <c r="C706" s="5"/>
@@ -14053,7 +14055,7 @@
       <c r="K706" s="6"/>
       <c r="L706" s="6"/>
     </row>
-    <row r="707" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A707" s="5"/>
       <c r="B707" s="5"/>
       <c r="C707" s="5"/>
@@ -14067,7 +14069,7 @@
       <c r="K707" s="6"/>
       <c r="L707" s="6"/>
     </row>
-    <row r="708" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A708" s="5"/>
       <c r="B708" s="5"/>
       <c r="C708" s="5"/>
@@ -14081,7 +14083,7 @@
       <c r="K708" s="6"/>
       <c r="L708" s="6"/>
     </row>
-    <row r="709" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A709" s="5"/>
       <c r="B709" s="5"/>
       <c r="C709" s="5"/>
@@ -14095,7 +14097,7 @@
       <c r="K709" s="6"/>
       <c r="L709" s="6"/>
     </row>
-    <row r="710" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A710" s="5"/>
       <c r="B710" s="5"/>
       <c r="C710" s="5"/>
@@ -14109,7 +14111,7 @@
       <c r="K710" s="6"/>
       <c r="L710" s="6"/>
     </row>
-    <row r="711" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A711" s="5"/>
       <c r="B711" s="5"/>
       <c r="C711" s="5"/>
@@ -14123,7 +14125,7 @@
       <c r="K711" s="6"/>
       <c r="L711" s="6"/>
     </row>
-    <row r="712" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A712" s="5"/>
       <c r="B712" s="5"/>
       <c r="C712" s="5"/>
@@ -14137,7 +14139,7 @@
       <c r="K712" s="6"/>
       <c r="L712" s="6"/>
     </row>
-    <row r="713" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A713" s="5"/>
       <c r="B713" s="5"/>
       <c r="C713" s="5"/>
@@ -14151,7 +14153,7 @@
       <c r="K713" s="6"/>
       <c r="L713" s="6"/>
     </row>
-    <row r="714" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A714" s="5"/>
       <c r="B714" s="5"/>
       <c r="C714" s="5"/>
@@ -14165,7 +14167,7 @@
       <c r="K714" s="6"/>
       <c r="L714" s="6"/>
     </row>
-    <row r="715" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A715" s="5"/>
       <c r="B715" s="5"/>
       <c r="C715" s="5"/>
@@ -14179,7 +14181,7 @@
       <c r="K715" s="6"/>
       <c r="L715" s="6"/>
     </row>
-    <row r="716" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A716" s="5"/>
       <c r="B716" s="5"/>
       <c r="C716" s="5"/>
@@ -14193,7 +14195,7 @@
       <c r="K716" s="6"/>
       <c r="L716" s="6"/>
     </row>
-    <row r="717" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A717" s="5"/>
       <c r="B717" s="5"/>
       <c r="C717" s="5"/>
@@ -14207,7 +14209,7 @@
       <c r="K717" s="6"/>
       <c r="L717" s="6"/>
     </row>
-    <row r="718" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A718" s="5"/>
       <c r="B718" s="5"/>
       <c r="C718" s="5"/>
@@ -14221,7 +14223,7 @@
       <c r="K718" s="6"/>
       <c r="L718" s="6"/>
     </row>
-    <row r="719" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A719" s="5"/>
       <c r="B719" s="5"/>
       <c r="C719" s="5"/>
@@ -14235,7 +14237,7 @@
       <c r="K719" s="6"/>
       <c r="L719" s="6"/>
     </row>
-    <row r="720" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A720" s="5"/>
       <c r="B720" s="5"/>
       <c r="C720" s="5"/>
@@ -14249,7 +14251,7 @@
       <c r="K720" s="6"/>
       <c r="L720" s="6"/>
     </row>
-    <row r="721" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A721" s="5"/>
       <c r="B721" s="5"/>
       <c r="C721" s="5"/>
@@ -14263,7 +14265,7 @@
       <c r="K721" s="6"/>
       <c r="L721" s="6"/>
     </row>
-    <row r="722" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A722" s="5"/>
       <c r="B722" s="5"/>
       <c r="C722" s="5"/>
@@ -14277,7 +14279,7 @@
       <c r="K722" s="6"/>
       <c r="L722" s="6"/>
     </row>
-    <row r="723" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A723" s="5"/>
       <c r="B723" s="5"/>
       <c r="C723" s="5"/>
@@ -14291,7 +14293,7 @@
       <c r="K723" s="6"/>
       <c r="L723" s="6"/>
     </row>
-    <row r="724" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A724" s="5"/>
       <c r="B724" s="5"/>
       <c r="C724" s="5"/>
@@ -14305,7 +14307,7 @@
       <c r="K724" s="6"/>
       <c r="L724" s="6"/>
     </row>
-    <row r="725" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A725" s="5"/>
       <c r="B725" s="5"/>
       <c r="C725" s="5"/>
@@ -14319,7 +14321,7 @@
       <c r="K725" s="6"/>
       <c r="L725" s="6"/>
     </row>
-    <row r="726" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A726" s="5"/>
       <c r="B726" s="5"/>
       <c r="C726" s="5"/>
@@ -14333,7 +14335,7 @@
       <c r="K726" s="6"/>
       <c r="L726" s="6"/>
     </row>
-    <row r="727" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A727" s="5"/>
       <c r="B727" s="5"/>
       <c r="C727" s="5"/>
@@ -14347,7 +14349,7 @@
       <c r="K727" s="6"/>
       <c r="L727" s="6"/>
     </row>
-    <row r="728" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A728" s="5"/>
       <c r="B728" s="5"/>
       <c r="C728" s="5"/>
@@ -14361,7 +14363,7 @@
       <c r="K728" s="6"/>
       <c r="L728" s="6"/>
     </row>
-    <row r="729" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A729" s="5"/>
       <c r="B729" s="5"/>
       <c r="C729" s="5"/>
@@ -14375,7 +14377,7 @@
       <c r="K729" s="6"/>
       <c r="L729" s="6"/>
     </row>
-    <row r="730" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A730" s="5"/>
       <c r="B730" s="5"/>
       <c r="C730" s="5"/>
@@ -14389,7 +14391,7 @@
       <c r="K730" s="6"/>
       <c r="L730" s="6"/>
     </row>
-    <row r="731" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A731" s="5"/>
       <c r="B731" s="5"/>
       <c r="C731" s="5"/>
@@ -14403,7 +14405,7 @@
       <c r="K731" s="6"/>
       <c r="L731" s="6"/>
     </row>
-    <row r="732" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A732" s="5"/>
       <c r="B732" s="5"/>
       <c r="C732" s="5"/>
@@ -14417,7 +14419,7 @@
       <c r="K732" s="6"/>
       <c r="L732" s="6"/>
     </row>
-    <row r="733" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A733" s="5"/>
       <c r="B733" s="5"/>
       <c r="C733" s="5"/>
@@ -14431,7 +14433,7 @@
       <c r="K733" s="6"/>
       <c r="L733" s="6"/>
     </row>
-    <row r="734" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A734" s="5"/>
       <c r="B734" s="5"/>
       <c r="C734" s="5"/>
@@ -14445,7 +14447,7 @@
       <c r="K734" s="6"/>
       <c r="L734" s="6"/>
     </row>
-    <row r="735" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A735" s="5"/>
       <c r="B735" s="5"/>
       <c r="C735" s="5"/>
@@ -14459,7 +14461,7 @@
       <c r="K735" s="6"/>
       <c r="L735" s="6"/>
     </row>
-    <row r="736" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A736" s="5"/>
       <c r="B736" s="5"/>
       <c r="C736" s="5"/>
@@ -14473,7 +14475,7 @@
       <c r="K736" s="6"/>
       <c r="L736" s="6"/>
     </row>
-    <row r="737" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A737" s="5"/>
       <c r="B737" s="5"/>
       <c r="C737" s="5"/>
@@ -14487,7 +14489,7 @@
       <c r="K737" s="6"/>
       <c r="L737" s="6"/>
     </row>
-    <row r="738" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A738" s="5"/>
       <c r="B738" s="5"/>
       <c r="C738" s="5"/>
@@ -14501,7 +14503,7 @@
       <c r="K738" s="6"/>
       <c r="L738" s="6"/>
     </row>
-    <row r="739" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A739" s="5"/>
       <c r="B739" s="5"/>
       <c r="C739" s="5"/>
@@ -14515,7 +14517,7 @@
       <c r="K739" s="6"/>
       <c r="L739" s="6"/>
     </row>
-    <row r="740" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A740" s="5"/>
       <c r="B740" s="5"/>
       <c r="C740" s="5"/>
@@ -14529,7 +14531,7 @@
       <c r="K740" s="6"/>
       <c r="L740" s="6"/>
     </row>
-    <row r="741" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A741" s="5"/>
       <c r="B741" s="5"/>
       <c r="C741" s="5"/>
@@ -14543,7 +14545,7 @@
       <c r="K741" s="6"/>
       <c r="L741" s="6"/>
     </row>
-    <row r="742" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A742" s="5"/>
       <c r="B742" s="5"/>
       <c r="C742" s="5"/>
@@ -14557,7 +14559,7 @@
       <c r="K742" s="6"/>
       <c r="L742" s="6"/>
     </row>
-    <row r="743" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A743" s="5"/>
       <c r="B743" s="5"/>
       <c r="C743" s="5"/>
@@ -14571,7 +14573,7 @@
       <c r="K743" s="6"/>
       <c r="L743" s="6"/>
     </row>
-    <row r="744" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A744" s="5"/>
       <c r="B744" s="5"/>
       <c r="C744" s="5"/>
@@ -14585,7 +14587,7 @@
       <c r="K744" s="6"/>
       <c r="L744" s="6"/>
     </row>
-    <row r="745" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A745" s="5"/>
       <c r="B745" s="5"/>
       <c r="C745" s="5"/>
@@ -14599,7 +14601,7 @@
       <c r="K745" s="6"/>
       <c r="L745" s="6"/>
     </row>
-    <row r="746" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A746" s="5"/>
       <c r="B746" s="5"/>
       <c r="C746" s="5"/>
@@ -14613,7 +14615,7 @@
       <c r="K746" s="6"/>
       <c r="L746" s="6"/>
     </row>
-    <row r="747" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A747" s="5"/>
       <c r="B747" s="5"/>
       <c r="C747" s="5"/>
@@ -14627,7 +14629,7 @@
       <c r="K747" s="6"/>
       <c r="L747" s="6"/>
     </row>
-    <row r="748" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A748" s="5"/>
       <c r="B748" s="5"/>
       <c r="C748" s="5"/>
@@ -14641,7 +14643,7 @@
       <c r="K748" s="6"/>
       <c r="L748" s="6"/>
     </row>
-    <row r="749" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A749" s="5"/>
       <c r="B749" s="5"/>
       <c r="C749" s="5"/>
@@ -14655,7 +14657,7 @@
       <c r="K749" s="6"/>
       <c r="L749" s="6"/>
     </row>
-    <row r="750" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A750" s="5"/>
       <c r="B750" s="5"/>
       <c r="C750" s="5"/>
@@ -14669,7 +14671,7 @@
       <c r="K750" s="6"/>
       <c r="L750" s="6"/>
     </row>
-    <row r="751" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A751" s="5"/>
       <c r="B751" s="5"/>
       <c r="C751" s="5"/>
@@ -14683,7 +14685,7 @@
       <c r="K751" s="6"/>
       <c r="L751" s="6"/>
     </row>
-    <row r="752" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A752" s="5"/>
       <c r="B752" s="5"/>
       <c r="C752" s="5"/>
@@ -14697,7 +14699,7 @@
       <c r="K752" s="6"/>
       <c r="L752" s="6"/>
     </row>
-    <row r="753" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A753" s="5"/>
       <c r="B753" s="5"/>
       <c r="C753" s="5"/>
@@ -14711,7 +14713,7 @@
       <c r="K753" s="6"/>
       <c r="L753" s="6"/>
     </row>
-    <row r="754" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A754" s="5"/>
       <c r="B754" s="5"/>
       <c r="C754" s="5"/>
@@ -14725,7 +14727,7 @@
       <c r="K754" s="6"/>
       <c r="L754" s="6"/>
     </row>
-    <row r="755" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A755" s="5"/>
       <c r="B755" s="5"/>
       <c r="C755" s="5"/>
@@ -14739,7 +14741,7 @@
       <c r="K755" s="6"/>
       <c r="L755" s="6"/>
     </row>
-    <row r="756" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A756" s="5"/>
       <c r="B756" s="5"/>
       <c r="C756" s="5"/>
@@ -14753,7 +14755,7 @@
       <c r="K756" s="6"/>
       <c r="L756" s="6"/>
     </row>
-    <row r="757" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A757" s="5"/>
       <c r="B757" s="5"/>
       <c r="C757" s="5"/>
@@ -14767,7 +14769,7 @@
       <c r="K757" s="6"/>
       <c r="L757" s="6"/>
     </row>
-    <row r="758" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A758" s="5"/>
       <c r="B758" s="5"/>
       <c r="C758" s="5"/>
@@ -14781,7 +14783,7 @@
       <c r="K758" s="6"/>
       <c r="L758" s="6"/>
     </row>
-    <row r="759" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A759" s="5"/>
       <c r="B759" s="5"/>
       <c r="C759" s="5"/>
@@ -14795,7 +14797,7 @@
       <c r="K759" s="6"/>
       <c r="L759" s="6"/>
     </row>
-    <row r="760" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A760" s="5"/>
       <c r="B760" s="5"/>
       <c r="C760" s="5"/>
@@ -14809,7 +14811,7 @@
       <c r="K760" s="6"/>
       <c r="L760" s="6"/>
     </row>
-    <row r="761" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A761" s="5"/>
       <c r="B761" s="5"/>
       <c r="C761" s="5"/>
@@ -14823,7 +14825,7 @@
       <c r="K761" s="6"/>
       <c r="L761" s="6"/>
     </row>
-    <row r="762" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A762" s="5"/>
       <c r="B762" s="5"/>
       <c r="C762" s="5"/>
@@ -14837,7 +14839,7 @@
       <c r="K762" s="6"/>
       <c r="L762" s="6"/>
     </row>
-    <row r="763" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A763" s="5"/>
       <c r="B763" s="5"/>
       <c r="C763" s="5"/>
@@ -14851,7 +14853,7 @@
       <c r="K763" s="6"/>
       <c r="L763" s="6"/>
     </row>
-    <row r="764" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A764" s="5"/>
       <c r="B764" s="5"/>
       <c r="C764" s="5"/>
@@ -14865,7 +14867,7 @@
       <c r="K764" s="6"/>
       <c r="L764" s="6"/>
     </row>
-    <row r="765" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A765" s="5"/>
       <c r="B765" s="5"/>
       <c r="C765" s="5"/>
@@ -14879,7 +14881,7 @@
       <c r="K765" s="6"/>
       <c r="L765" s="6"/>
     </row>
-    <row r="766" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A766" s="5"/>
       <c r="B766" s="5"/>
       <c r="C766" s="5"/>
@@ -14893,7 +14895,7 @@
       <c r="K766" s="6"/>
       <c r="L766" s="6"/>
     </row>
-    <row r="767" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A767" s="5"/>
       <c r="B767" s="5"/>
       <c r="C767" s="5"/>
@@ -14907,7 +14909,7 @@
       <c r="K767" s="6"/>
       <c r="L767" s="6"/>
     </row>
-    <row r="768" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A768" s="5"/>
       <c r="B768" s="5"/>
       <c r="C768" s="5"/>
@@ -14921,7 +14923,7 @@
       <c r="K768" s="6"/>
       <c r="L768" s="6"/>
     </row>
-    <row r="769" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A769" s="5"/>
       <c r="B769" s="5"/>
       <c r="C769" s="5"/>
@@ -14935,7 +14937,7 @@
       <c r="K769" s="6"/>
       <c r="L769" s="6"/>
     </row>
-    <row r="770" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A770" s="5"/>
       <c r="B770" s="5"/>
       <c r="C770" s="5"/>
@@ -14949,7 +14951,7 @@
       <c r="K770" s="6"/>
       <c r="L770" s="6"/>
     </row>
-    <row r="771" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A771" s="5"/>
       <c r="B771" s="5"/>
       <c r="C771" s="5"/>
@@ -14963,7 +14965,7 @@
       <c r="K771" s="6"/>
       <c r="L771" s="6"/>
     </row>
-    <row r="772" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A772" s="5"/>
       <c r="B772" s="5"/>
       <c r="C772" s="5"/>
@@ -14977,7 +14979,7 @@
       <c r="K772" s="6"/>
       <c r="L772" s="6"/>
     </row>
-    <row r="773" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A773" s="5"/>
       <c r="B773" s="5"/>
       <c r="C773" s="5"/>
@@ -14991,7 +14993,7 @@
       <c r="K773" s="6"/>
       <c r="L773" s="6"/>
     </row>
-    <row r="774" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A774" s="5"/>
       <c r="B774" s="5"/>
       <c r="C774" s="5"/>
@@ -15005,7 +15007,7 @@
       <c r="K774" s="6"/>
       <c r="L774" s="6"/>
     </row>
-    <row r="775" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A775" s="5"/>
       <c r="B775" s="5"/>
       <c r="C775" s="5"/>
@@ -15019,7 +15021,7 @@
       <c r="K775" s="6"/>
       <c r="L775" s="6"/>
     </row>
-    <row r="776" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A776" s="5"/>
       <c r="B776" s="5"/>
       <c r="C776" s="5"/>
@@ -15033,7 +15035,7 @@
       <c r="K776" s="6"/>
       <c r="L776" s="6"/>
     </row>
-    <row r="777" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A777" s="5"/>
       <c r="B777" s="5"/>
       <c r="C777" s="5"/>
@@ -15047,7 +15049,7 @@
       <c r="K777" s="6"/>
       <c r="L777" s="6"/>
     </row>
-    <row r="778" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A778" s="5"/>
       <c r="B778" s="5"/>
       <c r="C778" s="5"/>
@@ -15061,7 +15063,7 @@
       <c r="K778" s="6"/>
       <c r="L778" s="6"/>
     </row>
-    <row r="779" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A779" s="5"/>
       <c r="B779" s="5"/>
       <c r="C779" s="5"/>
@@ -15075,7 +15077,7 @@
       <c r="K779" s="6"/>
       <c r="L779" s="6"/>
     </row>
-    <row r="780" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A780" s="5"/>
       <c r="B780" s="5"/>
       <c r="C780" s="5"/>
@@ -15089,7 +15091,7 @@
       <c r="K780" s="6"/>
       <c r="L780" s="6"/>
     </row>
-    <row r="781" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A781" s="5"/>
       <c r="B781" s="5"/>
       <c r="C781" s="5"/>
@@ -15103,7 +15105,7 @@
       <c r="K781" s="6"/>
       <c r="L781" s="6"/>
     </row>
-    <row r="782" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A782" s="5"/>
       <c r="B782" s="5"/>
       <c r="C782" s="5"/>
@@ -15117,7 +15119,7 @@
       <c r="K782" s="6"/>
       <c r="L782" s="6"/>
     </row>
-    <row r="783" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A783" s="5"/>
       <c r="B783" s="5"/>
       <c r="C783" s="5"/>
@@ -15131,7 +15133,7 @@
       <c r="K783" s="6"/>
       <c r="L783" s="6"/>
     </row>
-    <row r="784" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A784" s="5"/>
       <c r="B784" s="5"/>
       <c r="C784" s="5"/>
@@ -15145,7 +15147,7 @@
       <c r="K784" s="6"/>
       <c r="L784" s="6"/>
     </row>
-    <row r="785" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A785" s="5"/>
       <c r="B785" s="5"/>
       <c r="C785" s="5"/>
@@ -15159,7 +15161,7 @@
       <c r="K785" s="6"/>
       <c r="L785" s="6"/>
     </row>
-    <row r="786" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A786" s="5"/>
       <c r="B786" s="5"/>
       <c r="C786" s="5"/>
@@ -15173,7 +15175,7 @@
       <c r="K786" s="6"/>
       <c r="L786" s="6"/>
     </row>
-    <row r="787" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A787" s="5"/>
       <c r="B787" s="5"/>
       <c r="C787" s="5"/>
@@ -15187,7 +15189,7 @@
       <c r="K787" s="6"/>
       <c r="L787" s="6"/>
     </row>
-    <row r="788" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A788" s="5"/>
       <c r="B788" s="5"/>
       <c r="C788" s="5"/>
@@ -15201,7 +15203,7 @@
       <c r="K788" s="6"/>
       <c r="L788" s="6"/>
     </row>
-    <row r="789" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A789" s="5"/>
       <c r="B789" s="5"/>
       <c r="C789" s="5"/>
@@ -15215,7 +15217,7 @@
       <c r="K789" s="6"/>
       <c r="L789" s="6"/>
     </row>
-    <row r="790" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A790" s="5"/>
       <c r="B790" s="5"/>
       <c r="C790" s="5"/>
@@ -15229,7 +15231,7 @@
       <c r="K790" s="6"/>
       <c r="L790" s="6"/>
     </row>
-    <row r="791" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A791" s="5"/>
       <c r="B791" s="5"/>
       <c r="C791" s="5"/>
@@ -15243,7 +15245,7 @@
       <c r="K791" s="6"/>
       <c r="L791" s="6"/>
     </row>
-    <row r="792" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A792" s="5"/>
       <c r="B792" s="5"/>
       <c r="C792" s="5"/>
@@ -15257,7 +15259,7 @@
       <c r="K792" s="6"/>
       <c r="L792" s="6"/>
     </row>
-    <row r="793" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A793" s="5"/>
       <c r="B793" s="5"/>
       <c r="C793" s="5"/>
@@ -15271,7 +15273,7 @@
       <c r="K793" s="6"/>
       <c r="L793" s="6"/>
     </row>
-    <row r="794" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A794" s="5"/>
       <c r="B794" s="5"/>
       <c r="C794" s="5"/>
@@ -15285,7 +15287,7 @@
       <c r="K794" s="6"/>
       <c r="L794" s="6"/>
     </row>
-    <row r="795" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A795" s="5"/>
       <c r="B795" s="5"/>
       <c r="C795" s="5"/>
@@ -15299,7 +15301,7 @@
       <c r="K795" s="6"/>
       <c r="L795" s="6"/>
     </row>
-    <row r="796" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A796" s="5"/>
       <c r="B796" s="5"/>
       <c r="C796" s="5"/>
@@ -15313,7 +15315,7 @@
       <c r="K796" s="6"/>
       <c r="L796" s="6"/>
     </row>
-    <row r="797" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A797" s="5"/>
       <c r="B797" s="5"/>
       <c r="C797" s="5"/>
@@ -15327,7 +15329,7 @@
       <c r="K797" s="6"/>
       <c r="L797" s="6"/>
     </row>
-    <row r="798" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A798" s="5"/>
       <c r="B798" s="5"/>
       <c r="C798" s="5"/>
@@ -15341,7 +15343,7 @@
       <c r="K798" s="6"/>
       <c r="L798" s="6"/>
     </row>
-    <row r="799" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A799" s="5"/>
       <c r="B799" s="5"/>
       <c r="C799" s="5"/>
@@ -15355,7 +15357,7 @@
       <c r="K799" s="6"/>
       <c r="L799" s="6"/>
     </row>
-    <row r="800" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A800" s="5"/>
       <c r="B800" s="5"/>
       <c r="C800" s="5"/>
@@ -15369,7 +15371,7 @@
       <c r="K800" s="6"/>
       <c r="L800" s="6"/>
     </row>
-    <row r="801" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A801" s="5"/>
       <c r="B801" s="5"/>
       <c r="C801" s="5"/>
@@ -15383,7 +15385,7 @@
       <c r="K801" s="6"/>
       <c r="L801" s="6"/>
     </row>
-    <row r="802" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A802" s="5"/>
       <c r="B802" s="5"/>
       <c r="C802" s="5"/>
@@ -15397,7 +15399,7 @@
       <c r="K802" s="6"/>
       <c r="L802" s="6"/>
     </row>
-    <row r="803" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A803" s="5"/>
       <c r="B803" s="5"/>
       <c r="C803" s="5"/>
@@ -15411,7 +15413,7 @@
       <c r="K803" s="6"/>
       <c r="L803" s="6"/>
     </row>
-    <row r="804" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A804" s="5"/>
       <c r="B804" s="5"/>
       <c r="C804" s="5"/>
@@ -15425,7 +15427,7 @@
       <c r="K804" s="6"/>
       <c r="L804" s="6"/>
     </row>
-    <row r="805" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A805" s="5"/>
       <c r="B805" s="5"/>
       <c r="C805" s="5"/>
@@ -15439,7 +15441,7 @@
       <c r="K805" s="6"/>
       <c r="L805" s="6"/>
     </row>
-    <row r="806" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A806" s="5"/>
       <c r="B806" s="5"/>
       <c r="C806" s="5"/>
@@ -15453,7 +15455,7 @@
       <c r="K806" s="6"/>
       <c r="L806" s="6"/>
     </row>
-    <row r="807" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A807" s="5"/>
       <c r="B807" s="5"/>
       <c r="C807" s="5"/>
@@ -15467,7 +15469,7 @@
       <c r="K807" s="6"/>
       <c r="L807" s="6"/>
     </row>
-    <row r="808" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A808" s="5"/>
       <c r="B808" s="5"/>
       <c r="C808" s="5"/>
@@ -15481,7 +15483,7 @@
       <c r="K808" s="6"/>
       <c r="L808" s="6"/>
     </row>
-    <row r="809" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A809" s="5"/>
       <c r="B809" s="5"/>
       <c r="C809" s="5"/>
@@ -15495,7 +15497,7 @@
       <c r="K809" s="6"/>
       <c r="L809" s="6"/>
     </row>
-    <row r="810" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A810" s="5"/>
       <c r="B810" s="5"/>
       <c r="C810" s="5"/>
@@ -15509,7 +15511,7 @@
       <c r="K810" s="6"/>
       <c r="L810" s="6"/>
     </row>
-    <row r="811" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A811" s="5"/>
       <c r="B811" s="5"/>
       <c r="C811" s="5"/>
@@ -15523,7 +15525,7 @@
       <c r="K811" s="6"/>
       <c r="L811" s="6"/>
     </row>
-    <row r="812" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A812" s="5"/>
       <c r="B812" s="5"/>
       <c r="C812" s="5"/>
@@ -15537,7 +15539,7 @@
       <c r="K812" s="6"/>
       <c r="L812" s="6"/>
     </row>
-    <row r="813" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A813" s="5"/>
       <c r="B813" s="5"/>
       <c r="C813" s="5"/>
@@ -15551,7 +15553,7 @@
       <c r="K813" s="6"/>
       <c r="L813" s="6"/>
     </row>
-    <row r="814" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A814" s="5"/>
       <c r="B814" s="5"/>
       <c r="C814" s="5"/>
@@ -15565,7 +15567,7 @@
       <c r="K814" s="6"/>
       <c r="L814" s="6"/>
     </row>
-    <row r="815" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A815" s="5"/>
       <c r="B815" s="5"/>
       <c r="C815" s="5"/>
@@ -15579,7 +15581,7 @@
       <c r="K815" s="6"/>
       <c r="L815" s="6"/>
     </row>
-    <row r="816" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A816" s="5"/>
       <c r="B816" s="5"/>
       <c r="C816" s="5"/>
@@ -15593,7 +15595,7 @@
       <c r="K816" s="6"/>
       <c r="L816" s="6"/>
     </row>
-    <row r="817" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A817" s="5"/>
       <c r="B817" s="5"/>
       <c r="C817" s="5"/>
@@ -15607,7 +15609,7 @@
       <c r="K817" s="6"/>
       <c r="L817" s="6"/>
     </row>
-    <row r="818" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A818" s="5"/>
       <c r="B818" s="5"/>
       <c r="C818" s="5"/>
@@ -15621,7 +15623,7 @@
       <c r="K818" s="6"/>
       <c r="L818" s="6"/>
     </row>
-    <row r="819" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A819" s="5"/>
       <c r="B819" s="5"/>
       <c r="C819" s="5"/>
@@ -15635,7 +15637,7 @@
       <c r="K819" s="6"/>
       <c r="L819" s="6"/>
     </row>
-    <row r="820" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A820" s="5"/>
       <c r="B820" s="5"/>
       <c r="C820" s="5"/>
@@ -15649,7 +15651,7 @@
       <c r="K820" s="6"/>
       <c r="L820" s="6"/>
     </row>
-    <row r="821" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A821" s="5"/>
       <c r="B821" s="5"/>
       <c r="C821" s="5"/>
@@ -15663,7 +15665,7 @@
       <c r="K821" s="6"/>
       <c r="L821" s="6"/>
     </row>
-    <row r="822" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A822" s="5"/>
       <c r="B822" s="5"/>
       <c r="C822" s="5"/>
@@ -15677,7 +15679,7 @@
       <c r="K822" s="6"/>
       <c r="L822" s="6"/>
     </row>
-    <row r="823" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A823" s="5"/>
       <c r="B823" s="5"/>
       <c r="C823" s="5"/>
@@ -15691,7 +15693,7 @@
       <c r="K823" s="6"/>
       <c r="L823" s="6"/>
     </row>
-    <row r="824" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A824" s="5"/>
       <c r="B824" s="5"/>
       <c r="C824" s="5"/>
@@ -15705,7 +15707,7 @@
       <c r="K824" s="6"/>
       <c r="L824" s="6"/>
     </row>
-    <row r="825" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A825" s="5"/>
       <c r="B825" s="5"/>
       <c r="C825" s="5"/>
@@ -15719,7 +15721,7 @@
       <c r="K825" s="6"/>
       <c r="L825" s="6"/>
     </row>
-    <row r="826" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A826" s="5"/>
       <c r="B826" s="5"/>
       <c r="C826" s="5"/>
@@ -15733,7 +15735,7 @@
       <c r="K826" s="6"/>
       <c r="L826" s="6"/>
     </row>
-    <row r="827" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A827" s="5"/>
       <c r="B827" s="5"/>
       <c r="C827" s="5"/>
@@ -15747,7 +15749,7 @@
       <c r="K827" s="6"/>
       <c r="L827" s="6"/>
     </row>
-    <row r="828" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A828" s="5"/>
       <c r="B828" s="5"/>
       <c r="C828" s="5"/>
@@ -15761,7 +15763,7 @@
       <c r="K828" s="6"/>
       <c r="L828" s="6"/>
     </row>
-    <row r="829" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A829" s="5"/>
       <c r="B829" s="5"/>
       <c r="C829" s="5"/>
@@ -15775,7 +15777,7 @@
       <c r="K829" s="6"/>
       <c r="L829" s="6"/>
     </row>
-    <row r="830" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A830" s="5"/>
       <c r="B830" s="5"/>
       <c r="C830" s="5"/>
@@ -15789,7 +15791,7 @@
       <c r="K830" s="6"/>
       <c r="L830" s="6"/>
     </row>
-    <row r="831" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A831" s="5"/>
       <c r="B831" s="5"/>
       <c r="C831" s="5"/>
@@ -15803,7 +15805,7 @@
       <c r="K831" s="6"/>
       <c r="L831" s="6"/>
     </row>
-    <row r="832" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A832" s="5"/>
       <c r="B832" s="5"/>
       <c r="C832" s="5"/>
@@ -15817,7 +15819,7 @@
       <c r="K832" s="6"/>
       <c r="L832" s="6"/>
     </row>
-    <row r="833" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A833" s="5"/>
       <c r="B833" s="5"/>
       <c r="C833" s="5"/>
@@ -15831,7 +15833,7 @@
       <c r="K833" s="6"/>
       <c r="L833" s="6"/>
     </row>
-    <row r="834" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A834" s="5"/>
       <c r="B834" s="5"/>
       <c r="C834" s="5"/>
@@ -15845,7 +15847,7 @@
       <c r="K834" s="6"/>
       <c r="L834" s="6"/>
     </row>
-    <row r="835" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A835" s="5"/>
       <c r="B835" s="5"/>
       <c r="C835" s="5"/>
@@ -15859,7 +15861,7 @@
       <c r="K835" s="6"/>
       <c r="L835" s="6"/>
     </row>
-    <row r="836" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A836" s="5"/>
       <c r="B836" s="5"/>
       <c r="C836" s="5"/>
@@ -15873,7 +15875,7 @@
       <c r="K836" s="6"/>
       <c r="L836" s="6"/>
     </row>
-    <row r="837" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A837" s="5"/>
       <c r="B837" s="5"/>
       <c r="C837" s="5"/>
@@ -15887,7 +15889,7 @@
       <c r="K837" s="6"/>
       <c r="L837" s="6"/>
     </row>
-    <row r="838" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A838" s="5"/>
       <c r="B838" s="5"/>
       <c r="C838" s="5"/>
@@ -15901,7 +15903,7 @@
       <c r="K838" s="6"/>
       <c r="L838" s="6"/>
     </row>
-    <row r="839" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A839" s="5"/>
       <c r="B839" s="5"/>
       <c r="C839" s="5"/>
@@ -15915,7 +15917,7 @@
       <c r="K839" s="6"/>
       <c r="L839" s="6"/>
     </row>
-    <row r="840" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A840" s="5"/>
       <c r="B840" s="5"/>
       <c r="C840" s="5"/>
@@ -15929,7 +15931,7 @@
       <c r="K840" s="6"/>
       <c r="L840" s="6"/>
     </row>
-    <row r="841" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A841" s="5"/>
       <c r="B841" s="5"/>
       <c r="C841" s="5"/>
@@ -15943,7 +15945,7 @@
       <c r="K841" s="6"/>
       <c r="L841" s="6"/>
     </row>
-    <row r="842" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A842" s="5"/>
       <c r="B842" s="5"/>
       <c r="C842" s="5"/>
@@ -15957,7 +15959,7 @@
       <c r="K842" s="6"/>
       <c r="L842" s="6"/>
     </row>
-    <row r="843" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A843" s="5"/>
       <c r="B843" s="5"/>
       <c r="C843" s="5"/>
@@ -15971,7 +15973,7 @@
       <c r="K843" s="6"/>
       <c r="L843" s="6"/>
     </row>
-    <row r="844" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A844" s="5"/>
       <c r="B844" s="5"/>
       <c r="C844" s="5"/>
@@ -15985,7 +15987,7 @@
       <c r="K844" s="6"/>
       <c r="L844" s="6"/>
     </row>
-    <row r="845" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A845" s="5"/>
       <c r="B845" s="5"/>
       <c r="C845" s="5"/>
@@ -15999,7 +16001,7 @@
       <c r="K845" s="6"/>
       <c r="L845" s="6"/>
     </row>
-    <row r="846" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A846" s="5"/>
       <c r="B846" s="5"/>
       <c r="C846" s="5"/>
@@ -16013,7 +16015,7 @@
       <c r="K846" s="6"/>
       <c r="L846" s="6"/>
     </row>
-    <row r="847" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A847" s="5"/>
       <c r="B847" s="5"/>
       <c r="C847" s="5"/>
@@ -16027,7 +16029,7 @@
       <c r="K847" s="6"/>
       <c r="L847" s="6"/>
     </row>
-    <row r="848" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A848" s="5"/>
       <c r="B848" s="5"/>
       <c r="C848" s="5"/>
@@ -16041,7 +16043,7 @@
       <c r="K848" s="6"/>
       <c r="L848" s="6"/>
     </row>
-    <row r="849" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A849" s="5"/>
       <c r="B849" s="5"/>
       <c r="C849" s="5"/>
@@ -16055,7 +16057,7 @@
       <c r="K849" s="6"/>
       <c r="L849" s="6"/>
     </row>
-    <row r="850" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A850" s="5"/>
       <c r="B850" s="5"/>
       <c r="C850" s="5"/>
@@ -16069,7 +16071,7 @@
       <c r="K850" s="6"/>
       <c r="L850" s="6"/>
     </row>
-    <row r="851" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A851" s="5"/>
       <c r="B851" s="5"/>
       <c r="C851" s="5"/>
@@ -16083,7 +16085,7 @@
       <c r="K851" s="6"/>
       <c r="L851" s="6"/>
     </row>
-    <row r="852" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A852" s="5"/>
       <c r="B852" s="5"/>
       <c r="C852" s="5"/>
@@ -16097,7 +16099,7 @@
       <c r="K852" s="6"/>
       <c r="L852" s="6"/>
     </row>
-    <row r="853" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A853" s="5"/>
       <c r="B853" s="5"/>
       <c r="C853" s="5"/>
@@ -16111,7 +16113,7 @@
       <c r="K853" s="6"/>
       <c r="L853" s="6"/>
     </row>
-    <row r="854" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A854" s="5"/>
       <c r="B854" s="5"/>
       <c r="C854" s="5"/>
@@ -16125,7 +16127,7 @@
       <c r="K854" s="6"/>
       <c r="L854" s="6"/>
     </row>
-    <row r="855" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A855" s="5"/>
       <c r="B855" s="5"/>
       <c r="C855" s="5"/>
@@ -16139,7 +16141,7 @@
       <c r="K855" s="6"/>
       <c r="L855" s="6"/>
     </row>
-    <row r="856" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A856" s="5"/>
       <c r="B856" s="5"/>
       <c r="C856" s="5"/>
@@ -16153,7 +16155,7 @@
       <c r="K856" s="6"/>
       <c r="L856" s="6"/>
     </row>
-    <row r="857" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A857" s="5"/>
       <c r="B857" s="5"/>
       <c r="C857" s="5"/>
@@ -16167,7 +16169,7 @@
       <c r="K857" s="6"/>
       <c r="L857" s="6"/>
     </row>
-    <row r="858" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A858" s="5"/>
       <c r="B858" s="5"/>
       <c r="C858" s="5"/>
@@ -16181,7 +16183,7 @@
       <c r="K858" s="6"/>
       <c r="L858" s="6"/>
     </row>
-    <row r="859" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A859" s="5"/>
       <c r="B859" s="5"/>
       <c r="C859" s="5"/>
@@ -16195,7 +16197,7 @@
       <c r="K859" s="6"/>
       <c r="L859" s="6"/>
     </row>
-    <row r="860" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A860" s="5"/>
       <c r="B860" s="5"/>
       <c r="C860" s="5"/>
@@ -16209,7 +16211,7 @@
       <c r="K860" s="6"/>
       <c r="L860" s="6"/>
     </row>
-    <row r="861" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A861" s="5"/>
       <c r="B861" s="5"/>
       <c r="C861" s="5"/>
@@ -16223,7 +16225,7 @@
       <c r="K861" s="6"/>
       <c r="L861" s="6"/>
     </row>
-    <row r="862" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A862" s="5"/>
       <c r="B862" s="5"/>
       <c r="C862" s="5"/>
@@ -16237,7 +16239,7 @@
       <c r="K862" s="6"/>
       <c r="L862" s="6"/>
     </row>
-    <row r="863" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A863" s="5"/>
       <c r="B863" s="5"/>
       <c r="C863" s="5"/>
@@ -16251,7 +16253,7 @@
       <c r="K863" s="6"/>
       <c r="L863" s="6"/>
     </row>
-    <row r="864" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A864" s="5"/>
       <c r="B864" s="5"/>
       <c r="C864" s="5"/>
@@ -16265,7 +16267,7 @@
       <c r="K864" s="6"/>
       <c r="L864" s="6"/>
     </row>
-    <row r="865" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A865" s="5"/>
       <c r="B865" s="5"/>
       <c r="C865" s="5"/>
@@ -16279,7 +16281,7 @@
       <c r="K865" s="6"/>
       <c r="L865" s="6"/>
     </row>
-    <row r="866" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A866" s="5"/>
       <c r="B866" s="5"/>
       <c r="C866" s="5"/>
@@ -16293,7 +16295,7 @@
       <c r="K866" s="6"/>
       <c r="L866" s="6"/>
     </row>
-    <row r="867" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A867" s="5"/>
       <c r="B867" s="5"/>
       <c r="C867" s="5"/>
@@ -16307,7 +16309,7 @@
       <c r="K867" s="6"/>
       <c r="L867" s="6"/>
     </row>
-    <row r="868" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A868" s="5"/>
       <c r="B868" s="5"/>
       <c r="C868" s="5"/>
@@ -16321,7 +16323,7 @@
       <c r="K868" s="6"/>
       <c r="L868" s="6"/>
     </row>
-    <row r="869" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A869" s="5"/>
       <c r="B869" s="5"/>
       <c r="C869" s="5"/>
@@ -16335,7 +16337,7 @@
       <c r="K869" s="6"/>
       <c r="L869" s="6"/>
     </row>
-    <row r="870" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A870" s="5"/>
       <c r="B870" s="5"/>
       <c r="C870" s="5"/>
@@ -16349,7 +16351,7 @@
       <c r="K870" s="6"/>
       <c r="L870" s="6"/>
     </row>
-    <row r="871" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A871" s="5"/>
       <c r="B871" s="5"/>
       <c r="C871" s="5"/>
@@ -16363,7 +16365,7 @@
       <c r="K871" s="6"/>
       <c r="L871" s="6"/>
     </row>
-    <row r="872" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A872" s="5"/>
       <c r="B872" s="5"/>
       <c r="C872" s="5"/>
@@ -16377,7 +16379,7 @@
       <c r="K872" s="6"/>
       <c r="L872" s="6"/>
     </row>
-    <row r="873" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A873" s="5"/>
       <c r="B873" s="5"/>
       <c r="C873" s="5"/>
@@ -16391,7 +16393,7 @@
       <c r="K873" s="6"/>
       <c r="L873" s="6"/>
     </row>
-    <row r="874" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A874" s="5"/>
       <c r="B874" s="5"/>
       <c r="C874" s="5"/>
@@ -16405,7 +16407,7 @@
       <c r="K874" s="6"/>
       <c r="L874" s="6"/>
     </row>
-    <row r="875" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A875" s="5"/>
       <c r="B875" s="5"/>
       <c r="C875" s="5"/>
@@ -16419,7 +16421,7 @@
       <c r="K875" s="6"/>
       <c r="L875" s="6"/>
     </row>
-    <row r="876" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A876" s="5"/>
       <c r="B876" s="5"/>
       <c r="C876" s="5"/>
@@ -16433,7 +16435,7 @@
       <c r="K876" s="6"/>
       <c r="L876" s="6"/>
     </row>
-    <row r="877" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A877" s="5"/>
       <c r="B877" s="5"/>
       <c r="C877" s="5"/>
@@ -16447,7 +16449,7 @@
       <c r="K877" s="6"/>
       <c r="L877" s="6"/>
     </row>
-    <row r="878" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A878" s="5"/>
       <c r="B878" s="5"/>
       <c r="C878" s="5"/>
@@ -16461,7 +16463,7 @@
       <c r="K878" s="6"/>
       <c r="L878" s="6"/>
     </row>
-    <row r="879" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A879" s="5"/>
       <c r="B879" s="5"/>
       <c r="C879" s="5"/>
@@ -16475,7 +16477,7 @@
       <c r="K879" s="6"/>
       <c r="L879" s="6"/>
     </row>
-    <row r="880" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A880" s="5"/>
       <c r="B880" s="5"/>
       <c r="C880" s="5"/>
@@ -16489,7 +16491,7 @@
       <c r="K880" s="6"/>
       <c r="L880" s="6"/>
     </row>
-    <row r="881" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A881" s="5"/>
       <c r="B881" s="5"/>
       <c r="C881" s="5"/>
@@ -16503,7 +16505,7 @@
       <c r="K881" s="6"/>
       <c r="L881" s="6"/>
     </row>
-    <row r="882" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A882" s="5"/>
       <c r="B882" s="5"/>
       <c r="C882" s="5"/>
@@ -16517,7 +16519,7 @@
       <c r="K882" s="6"/>
       <c r="L882" s="6"/>
     </row>
-    <row r="883" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A883" s="5"/>
       <c r="B883" s="5"/>
       <c r="C883" s="5"/>
@@ -16531,7 +16533,7 @@
       <c r="K883" s="6"/>
       <c r="L883" s="6"/>
     </row>
-    <row r="884" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A884" s="5"/>
       <c r="B884" s="5"/>
       <c r="C884" s="5"/>
@@ -16545,7 +16547,7 @@
       <c r="K884" s="6"/>
       <c r="L884" s="6"/>
     </row>
-    <row r="885" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A885" s="5"/>
       <c r="B885" s="5"/>
       <c r="C885" s="5"/>
@@ -16559,7 +16561,7 @@
       <c r="K885" s="6"/>
       <c r="L885" s="6"/>
     </row>
-    <row r="886" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A886" s="5"/>
       <c r="B886" s="5"/>
       <c r="C886" s="5"/>
@@ -16573,7 +16575,7 @@
       <c r="K886" s="6"/>
       <c r="L886" s="6"/>
     </row>
-    <row r="887" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A887" s="5"/>
       <c r="B887" s="5"/>
       <c r="C887" s="5"/>
@@ -16587,7 +16589,7 @@
       <c r="K887" s="6"/>
       <c r="L887" s="6"/>
     </row>
-    <row r="888" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A888" s="5"/>
       <c r="B888" s="5"/>
       <c r="C888" s="5"/>
@@ -16601,7 +16603,7 @@
       <c r="K888" s="6"/>
       <c r="L888" s="6"/>
     </row>
-    <row r="889" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A889" s="5"/>
       <c r="B889" s="5"/>
       <c r="C889" s="5"/>
@@ -16615,7 +16617,7 @@
       <c r="K889" s="6"/>
       <c r="L889" s="6"/>
     </row>
-    <row r="890" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A890" s="5"/>
       <c r="B890" s="5"/>
       <c r="C890" s="5"/>
@@ -16629,7 +16631,7 @@
       <c r="K890" s="6"/>
       <c r="L890" s="6"/>
     </row>
-    <row r="891" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A891" s="5"/>
       <c r="B891" s="5"/>
       <c r="C891" s="5"/>
@@ -16643,7 +16645,7 @@
       <c r="K891" s="6"/>
       <c r="L891" s="6"/>
     </row>
-    <row r="892" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A892" s="5"/>
       <c r="B892" s="5"/>
       <c r="C892" s="5"/>
@@ -16657,7 +16659,7 @@
       <c r="K892" s="6"/>
       <c r="L892" s="6"/>
     </row>
-    <row r="893" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A893" s="5"/>
       <c r="B893" s="5"/>
       <c r="C893" s="5"/>
@@ -16671,7 +16673,7 @@
       <c r="K893" s="6"/>
       <c r="L893" s="6"/>
     </row>
-    <row r="894" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A894" s="5"/>
       <c r="B894" s="5"/>
       <c r="C894" s="5"/>
@@ -16685,7 +16687,7 @@
       <c r="K894" s="6"/>
       <c r="L894" s="6"/>
     </row>
-    <row r="895" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A895" s="5"/>
       <c r="B895" s="5"/>
       <c r="C895" s="5"/>
@@ -16699,7 +16701,7 @@
       <c r="K895" s="6"/>
       <c r="L895" s="6"/>
     </row>
-    <row r="896" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A896" s="5"/>
       <c r="B896" s="5"/>
       <c r="C896" s="5"/>
@@ -16713,7 +16715,7 @@
       <c r="K896" s="6"/>
       <c r="L896" s="6"/>
     </row>
-    <row r="897" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A897" s="5"/>
       <c r="B897" s="5"/>
       <c r="C897" s="5"/>
@@ -16727,7 +16729,7 @@
       <c r="K897" s="6"/>
       <c r="L897" s="6"/>
     </row>
-    <row r="898" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A898" s="5"/>
       <c r="B898" s="5"/>
       <c r="C898" s="5"/>
@@ -16741,7 +16743,7 @@
       <c r="K898" s="6"/>
       <c r="L898" s="6"/>
     </row>
-    <row r="899" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A899" s="5"/>
       <c r="B899" s="5"/>
       <c r="C899" s="5"/>
@@ -16755,7 +16757,7 @@
       <c r="K899" s="6"/>
       <c r="L899" s="6"/>
     </row>
-    <row r="900" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A900" s="5"/>
       <c r="B900" s="5"/>
       <c r="C900" s="5"/>
@@ -16769,7 +16771,7 @@
       <c r="K900" s="6"/>
       <c r="L900" s="6"/>
     </row>
-    <row r="901" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A901" s="5"/>
       <c r="B901" s="5"/>
       <c r="C901" s="5"/>
@@ -16783,7 +16785,7 @@
       <c r="K901" s="6"/>
       <c r="L901" s="6"/>
     </row>
-    <row r="902" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A902" s="5"/>
       <c r="B902" s="5"/>
       <c r="C902" s="5"/>
@@ -16797,7 +16799,7 @@
       <c r="K902" s="6"/>
       <c r="L902" s="6"/>
     </row>
-    <row r="903" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A903" s="5"/>
       <c r="B903" s="5"/>
       <c r="C903" s="5"/>
@@ -16811,7 +16813,7 @@
       <c r="K903" s="6"/>
       <c r="L903" s="6"/>
     </row>
-    <row r="904" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A904" s="5"/>
       <c r="B904" s="5"/>
       <c r="C904" s="5"/>
@@ -16825,7 +16827,7 @@
       <c r="K904" s="6"/>
       <c r="L904" s="6"/>
     </row>
-    <row r="905" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A905" s="5"/>
       <c r="B905" s="5"/>
       <c r="C905" s="5"/>
@@ -16839,7 +16841,7 @@
       <c r="K905" s="6"/>
       <c r="L905" s="6"/>
     </row>
-    <row r="906" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A906" s="5"/>
       <c r="B906" s="5"/>
       <c r="C906" s="5"/>
@@ -16853,7 +16855,7 @@
       <c r="K906" s="6"/>
       <c r="L906" s="6"/>
     </row>
-    <row r="907" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A907" s="5"/>
       <c r="B907" s="5"/>
       <c r="C907" s="5"/>
@@ -16867,7 +16869,7 @@
       <c r="K907" s="6"/>
       <c r="L907" s="6"/>
     </row>
-    <row r="908" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A908" s="5"/>
       <c r="B908" s="5"/>
       <c r="C908" s="5"/>
@@ -16881,7 +16883,7 @@
       <c r="K908" s="6"/>
       <c r="L908" s="6"/>
     </row>
-    <row r="909" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A909" s="5"/>
       <c r="B909" s="5"/>
       <c r="C909" s="5"/>
@@ -16895,7 +16897,7 @@
       <c r="K909" s="6"/>
       <c r="L909" s="6"/>
     </row>
-    <row r="910" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A910" s="5"/>
       <c r="B910" s="5"/>
       <c r="C910" s="5"/>
@@ -16909,7 +16911,7 @@
       <c r="K910" s="6"/>
       <c r="L910" s="6"/>
     </row>
-    <row r="911" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A911" s="5"/>
       <c r="B911" s="5"/>
       <c r="C911" s="5"/>
@@ -16923,7 +16925,7 @@
       <c r="K911" s="6"/>
       <c r="L911" s="6"/>
     </row>
-    <row r="912" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A912" s="5"/>
       <c r="B912" s="5"/>
       <c r="C912" s="5"/>
@@ -16937,7 +16939,7 @@
       <c r="K912" s="6"/>
       <c r="L912" s="6"/>
     </row>
-    <row r="913" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A913" s="5"/>
       <c r="B913" s="5"/>
       <c r="C913" s="5"/>
@@ -16951,7 +16953,7 @@
       <c r="K913" s="6"/>
       <c r="L913" s="6"/>
     </row>
-    <row r="914" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A914" s="5"/>
       <c r="B914" s="5"/>
       <c r="C914" s="5"/>
@@ -16965,7 +16967,7 @@
       <c r="K914" s="6"/>
       <c r="L914" s="6"/>
     </row>
-    <row r="915" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A915" s="5"/>
       <c r="B915" s="5"/>
       <c r="C915" s="5"/>
@@ -16979,7 +16981,7 @@
       <c r="K915" s="6"/>
       <c r="L915" s="6"/>
     </row>
-    <row r="916" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A916" s="5"/>
       <c r="B916" s="5"/>
       <c r="C916" s="5"/>
@@ -16993,7 +16995,7 @@
       <c r="K916" s="6"/>
       <c r="L916" s="6"/>
     </row>
-    <row r="917" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A917" s="5"/>
       <c r="B917" s="5"/>
       <c r="C917" s="5"/>
@@ -17007,7 +17009,7 @@
       <c r="K917" s="6"/>
       <c r="L917" s="6"/>
     </row>
-    <row r="918" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A918" s="5"/>
       <c r="B918" s="5"/>
       <c r="C918" s="5"/>
@@ -17021,7 +17023,7 @@
       <c r="K918" s="6"/>
       <c r="L918" s="6"/>
     </row>
-    <row r="919" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A919" s="5"/>
       <c r="B919" s="5"/>
       <c r="C919" s="5"/>
@@ -17035,7 +17037,7 @@
       <c r="K919" s="6"/>
       <c r="L919" s="6"/>
     </row>
-    <row r="920" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A920" s="5"/>
       <c r="B920" s="5"/>
       <c r="C920" s="5"/>
@@ -17049,7 +17051,7 @@
       <c r="K920" s="6"/>
       <c r="L920" s="6"/>
     </row>
-    <row r="921" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A921" s="5"/>
       <c r="B921" s="5"/>
       <c r="C921" s="5"/>
@@ -17063,7 +17065,7 @@
       <c r="K921" s="6"/>
       <c r="L921" s="6"/>
     </row>
-    <row r="922" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A922" s="5"/>
       <c r="B922" s="5"/>
       <c r="C922" s="5"/>
@@ -17077,7 +17079,7 @@
       <c r="K922" s="6"/>
       <c r="L922" s="6"/>
     </row>
-    <row r="923" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A923" s="5"/>
       <c r="B923" s="5"/>
       <c r="C923" s="5"/>
@@ -17091,7 +17093,7 @@
       <c r="K923" s="6"/>
       <c r="L923" s="6"/>
     </row>
-    <row r="924" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A924" s="5"/>
       <c r="B924" s="5"/>
       <c r="C924" s="5"/>
@@ -17105,7 +17107,7 @@
       <c r="K924" s="6"/>
       <c r="L924" s="6"/>
     </row>
-    <row r="925" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A925" s="5"/>
       <c r="B925" s="5"/>
       <c r="C925" s="5"/>
@@ -17119,7 +17121,7 @@
       <c r="K925" s="6"/>
       <c r="L925" s="6"/>
     </row>
-    <row r="926" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A926" s="5"/>
       <c r="B926" s="5"/>
       <c r="C926" s="5"/>
@@ -17133,7 +17135,7 @@
       <c r="K926" s="6"/>
       <c r="L926" s="6"/>
     </row>
-    <row r="927" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A927" s="5"/>
       <c r="B927" s="5"/>
       <c r="C927" s="5"/>
@@ -17147,7 +17149,7 @@
       <c r="K927" s="6"/>
       <c r="L927" s="6"/>
     </row>
-    <row r="928" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A928" s="5"/>
       <c r="B928" s="5"/>
       <c r="C928" s="5"/>
@@ -17161,7 +17163,7 @@
       <c r="K928" s="6"/>
       <c r="L928" s="6"/>
     </row>
-    <row r="929" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A929" s="5"/>
       <c r="B929" s="5"/>
       <c r="C929" s="5"/>
@@ -17175,7 +17177,7 @@
       <c r="K929" s="6"/>
       <c r="L929" s="6"/>
     </row>
-    <row r="930" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A930" s="5"/>
       <c r="B930" s="5"/>
       <c r="C930" s="5"/>
@@ -17189,7 +17191,7 @@
       <c r="K930" s="6"/>
       <c r="L930" s="6"/>
     </row>
-    <row r="931" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A931" s="5"/>
       <c r="B931" s="5"/>
       <c r="C931" s="5"/>
@@ -17203,7 +17205,7 @@
       <c r="K931" s="6"/>
       <c r="L931" s="6"/>
     </row>
-    <row r="932" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A932" s="5"/>
       <c r="B932" s="5"/>
       <c r="C932" s="5"/>
@@ -17217,7 +17219,7 @@
       <c r="K932" s="6"/>
       <c r="L932" s="6"/>
     </row>
-    <row r="933" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A933" s="5"/>
       <c r="B933" s="5"/>
       <c r="C933" s="5"/>
@@ -17231,7 +17233,7 @@
       <c r="K933" s="6"/>
       <c r="L933" s="6"/>
     </row>
-    <row r="934" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A934" s="5"/>
       <c r="B934" s="5"/>
       <c r="C934" s="5"/>
@@ -17245,7 +17247,7 @@
       <c r="K934" s="6"/>
       <c r="L934" s="6"/>
     </row>
-    <row r="935" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A935" s="5"/>
       <c r="B935" s="5"/>
       <c r="C935" s="5"/>
@@ -17259,7 +17261,7 @@
       <c r="K935" s="6"/>
       <c r="L935" s="6"/>
     </row>
-    <row r="936" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A936" s="5"/>
       <c r="B936" s="5"/>
       <c r="C936" s="5"/>
@@ -17273,7 +17275,7 @@
       <c r="K936" s="6"/>
       <c r="L936" s="6"/>
     </row>
-    <row r="937" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A937" s="5"/>
       <c r="B937" s="5"/>
       <c r="C937" s="5"/>
@@ -17287,7 +17289,7 @@
       <c r="K937" s="6"/>
       <c r="L937" s="6"/>
     </row>
-    <row r="938" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A938" s="5"/>
       <c r="B938" s="5"/>
       <c r="C938" s="5"/>
@@ -17301,7 +17303,7 @@
       <c r="K938" s="6"/>
       <c r="L938" s="6"/>
     </row>
-    <row r="939" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A939" s="5"/>
       <c r="B939" s="5"/>
       <c r="C939" s="5"/>
@@ -17315,7 +17317,7 @@
       <c r="K939" s="6"/>
       <c r="L939" s="6"/>
     </row>
-    <row r="940" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A940" s="5"/>
       <c r="B940" s="5"/>
       <c r="C940" s="5"/>
@@ -17329,7 +17331,7 @@
       <c r="K940" s="6"/>
       <c r="L940" s="6"/>
     </row>
-    <row r="941" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A941" s="5"/>
       <c r="B941" s="5"/>
       <c r="C941" s="5"/>
@@ -17343,7 +17345,7 @@
       <c r="K941" s="6"/>
       <c r="L941" s="6"/>
     </row>
-    <row r="942" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A942" s="5"/>
       <c r="B942" s="5"/>
       <c r="C942" s="5"/>
@@ -17357,7 +17359,7 @@
       <c r="K942" s="6"/>
       <c r="L942" s="6"/>
     </row>
-    <row r="943" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A943" s="5"/>
       <c r="B943" s="5"/>
       <c r="C943" s="5"/>
@@ -17371,7 +17373,7 @@
       <c r="K943" s="6"/>
       <c r="L943" s="6"/>
     </row>
-    <row r="944" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A944" s="5"/>
       <c r="B944" s="5"/>
       <c r="C944" s="5"/>
@@ -17385,7 +17387,7 @@
       <c r="K944" s="6"/>
       <c r="L944" s="6"/>
     </row>
-    <row r="945" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A945" s="5"/>
       <c r="B945" s="5"/>
       <c r="C945" s="5"/>
@@ -17399,7 +17401,7 @@
       <c r="K945" s="6"/>
       <c r="L945" s="6"/>
     </row>
-    <row r="946" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A946" s="5"/>
       <c r="B946" s="5"/>
       <c r="C946" s="5"/>
@@ -17413,7 +17415,7 @@
       <c r="K946" s="6"/>
       <c r="L946" s="6"/>
     </row>
-    <row r="947" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A947" s="5"/>
       <c r="B947" s="5"/>
       <c r="C947" s="5"/>
@@ -17427,7 +17429,7 @@
       <c r="K947" s="6"/>
       <c r="L947" s="6"/>
     </row>
-    <row r="948" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A948" s="5"/>
       <c r="B948" s="5"/>
       <c r="C948" s="5"/>
@@ -17441,7 +17443,7 @@
       <c r="K948" s="6"/>
       <c r="L948" s="6"/>
     </row>
-    <row r="949" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A949" s="5"/>
       <c r="B949" s="5"/>
       <c r="C949" s="5"/>
@@ -17455,7 +17457,7 @@
       <c r="K949" s="6"/>
       <c r="L949" s="6"/>
     </row>
-    <row r="950" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A950" s="5"/>
       <c r="B950" s="5"/>
       <c r="C950" s="5"/>
@@ -17469,7 +17471,7 @@
       <c r="K950" s="6"/>
       <c r="L950" s="6"/>
     </row>
-    <row r="951" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A951" s="5"/>
       <c r="B951" s="5"/>
       <c r="C951" s="5"/>
@@ -17483,7 +17485,7 @@
       <c r="K951" s="6"/>
       <c r="L951" s="6"/>
     </row>
-    <row r="952" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A952" s="5"/>
       <c r="B952" s="5"/>
       <c r="C952" s="5"/>
@@ -17497,7 +17499,7 @@
       <c r="K952" s="6"/>
       <c r="L952" s="6"/>
     </row>
-    <row r="953" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A953" s="5"/>
       <c r="B953" s="5"/>
       <c r="C953" s="5"/>
@@ -17511,7 +17513,7 @@
       <c r="K953" s="6"/>
       <c r="L953" s="6"/>
     </row>
-    <row r="954" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A954" s="5"/>
       <c r="B954" s="5"/>
       <c r="C954" s="5"/>
@@ -17525,7 +17527,7 @@
       <c r="K954" s="6"/>
       <c r="L954" s="6"/>
     </row>
-    <row r="955" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A955" s="5"/>
       <c r="B955" s="5"/>
       <c r="C955" s="5"/>
@@ -17539,7 +17541,7 @@
       <c r="K955" s="6"/>
       <c r="L955" s="6"/>
     </row>
-    <row r="956" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A956" s="5"/>
       <c r="B956" s="5"/>
       <c r="C956" s="5"/>
@@ -17553,7 +17555,7 @@
       <c r="K956" s="6"/>
       <c r="L956" s="6"/>
     </row>
-    <row r="957" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A957" s="5"/>
       <c r="B957" s="5"/>
       <c r="C957" s="5"/>
@@ -17567,7 +17569,7 @@
       <c r="K957" s="6"/>
       <c r="L957" s="6"/>
     </row>
-    <row r="958" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A958" s="5"/>
       <c r="B958" s="5"/>
       <c r="C958" s="5"/>
@@ -17581,7 +17583,7 @@
       <c r="K958" s="6"/>
       <c r="L958" s="6"/>
     </row>
-    <row r="959" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A959" s="5"/>
       <c r="B959" s="5"/>
       <c r="C959" s="5"/>
@@ -17595,7 +17597,7 @@
       <c r="K959" s="6"/>
       <c r="L959" s="6"/>
     </row>
-    <row r="960" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A960" s="5"/>
       <c r="B960" s="5"/>
       <c r="C960" s="5"/>
@@ -17609,7 +17611,7 @@
       <c r="K960" s="6"/>
       <c r="L960" s="6"/>
     </row>
-    <row r="961" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A961" s="5"/>
       <c r="B961" s="5"/>
       <c r="C961" s="5"/>
@@ -17623,7 +17625,7 @@
       <c r="K961" s="6"/>
       <c r="L961" s="6"/>
     </row>
-    <row r="962" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A962" s="5"/>
       <c r="B962" s="5"/>
       <c r="C962" s="5"/>
@@ -17637,7 +17639,7 @@
       <c r="K962" s="6"/>
       <c r="L962" s="6"/>
     </row>
-    <row r="963" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A963" s="5"/>
       <c r="B963" s="5"/>
       <c r="C963" s="5"/>
@@ -17651,7 +17653,7 @@
       <c r="K963" s="6"/>
       <c r="L963" s="6"/>
     </row>
-    <row r="964" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A964" s="5"/>
       <c r="B964" s="5"/>
       <c r="C964" s="5"/>
@@ -17665,7 +17667,7 @@
       <c r="K964" s="6"/>
       <c r="L964" s="6"/>
     </row>
-    <row r="965" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A965" s="5"/>
       <c r="B965" s="5"/>
       <c r="C965" s="5"/>
@@ -17679,7 +17681,7 @@
       <c r="K965" s="6"/>
       <c r="L965" s="6"/>
     </row>
-    <row r="966" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A966" s="5"/>
       <c r="B966" s="5"/>
       <c r="C966" s="5"/>
@@ -17693,7 +17695,7 @@
       <c r="K966" s="6"/>
       <c r="L966" s="6"/>
     </row>
-    <row r="967" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A967" s="5"/>
       <c r="B967" s="5"/>
       <c r="C967" s="5"/>
@@ -17707,7 +17709,7 @@
       <c r="K967" s="6"/>
       <c r="L967" s="6"/>
     </row>
-    <row r="968" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A968" s="5"/>
       <c r="B968" s="5"/>
       <c r="C968" s="5"/>
@@ -17721,7 +17723,7 @@
       <c r="K968" s="6"/>
       <c r="L968" s="6"/>
     </row>
-    <row r="969" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A969" s="5"/>
       <c r="B969" s="5"/>
       <c r="C969" s="5"/>
@@ -17735,7 +17737,7 @@
       <c r="K969" s="6"/>
       <c r="L969" s="6"/>
     </row>
-    <row r="970" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A970" s="5"/>
       <c r="B970" s="5"/>
       <c r="C970" s="5"/>
@@ -17749,7 +17751,7 @@
       <c r="K970" s="6"/>
       <c r="L970" s="6"/>
     </row>
-    <row r="971" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A971" s="5"/>
       <c r="B971" s="5"/>
       <c r="C971" s="5"/>
@@ -17763,7 +17765,7 @@
       <c r="K971" s="6"/>
       <c r="L971" s="6"/>
     </row>
-    <row r="972" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A972" s="5"/>
       <c r="B972" s="5"/>
       <c r="C972" s="5"/>
@@ -17777,7 +17779,7 @@
       <c r="K972" s="6"/>
       <c r="L972" s="6"/>
     </row>
-    <row r="973" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A973" s="5"/>
       <c r="B973" s="5"/>
       <c r="C973" s="5"/>
@@ -17791,7 +17793,7 @@
       <c r="K973" s="6"/>
       <c r="L973" s="6"/>
     </row>
-    <row r="974" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A974" s="5"/>
       <c r="B974" s="5"/>
       <c r="C974" s="5"/>
@@ -17805,7 +17807,7 @@
       <c r="K974" s="6"/>
       <c r="L974" s="6"/>
     </row>
-    <row r="975" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A975" s="5"/>
       <c r="B975" s="5"/>
       <c r="C975" s="5"/>
@@ -17819,7 +17821,7 @@
       <c r="K975" s="6"/>
       <c r="L975" s="6"/>
     </row>
-    <row r="976" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A976" s="5"/>
       <c r="B976" s="5"/>
       <c r="C976" s="5"/>
@@ -17833,7 +17835,7 @@
       <c r="K976" s="6"/>
       <c r="L976" s="6"/>
     </row>
-    <row r="977" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A977" s="5"/>
       <c r="B977" s="5"/>
       <c r="C977" s="5"/>
@@ -17847,7 +17849,7 @@
       <c r="K977" s="6"/>
       <c r="L977" s="6"/>
     </row>
-    <row r="978" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A978" s="5"/>
       <c r="B978" s="5"/>
       <c r="C978" s="5"/>
@@ -17861,7 +17863,7 @@
       <c r="K978" s="6"/>
       <c r="L978" s="6"/>
     </row>
-    <row r="979" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A979" s="5"/>
       <c r="B979" s="5"/>
       <c r="C979" s="5"/>
@@ -17875,7 +17877,7 @@
       <c r="K979" s="6"/>
       <c r="L979" s="6"/>
     </row>
-    <row r="980" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A980" s="5"/>
       <c r="B980" s="5"/>
       <c r="C980" s="5"/>
@@ -17889,7 +17891,7 @@
       <c r="K980" s="6"/>
       <c r="L980" s="6"/>
     </row>
-    <row r="981" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A981" s="5"/>
       <c r="B981" s="5"/>
       <c r="C981" s="5"/>
@@ -17903,7 +17905,7 @@
       <c r="K981" s="6"/>
       <c r="L981" s="6"/>
     </row>
-    <row r="982" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A982" s="5"/>
       <c r="B982" s="5"/>
       <c r="C982" s="5"/>
@@ -17917,7 +17919,7 @@
       <c r="K982" s="6"/>
       <c r="L982" s="6"/>
     </row>
-    <row r="983" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A983" s="5"/>
       <c r="B983" s="5"/>
       <c r="C983" s="5"/>
@@ -17931,7 +17933,7 @@
       <c r="K983" s="6"/>
       <c r="L983" s="6"/>
     </row>
-    <row r="984" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A984" s="5"/>
       <c r="B984" s="5"/>
       <c r="C984" s="5"/>
@@ -17945,7 +17947,7 @@
       <c r="K984" s="6"/>
       <c r="L984" s="6"/>
     </row>
-    <row r="985" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A985" s="5"/>
       <c r="B985" s="5"/>
       <c r="C985" s="5"/>
@@ -17959,7 +17961,7 @@
       <c r="K985" s="6"/>
       <c r="L985" s="6"/>
     </row>
-    <row r="986" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A986" s="5"/>
       <c r="B986" s="5"/>
       <c r="C986" s="5"/>
@@ -17973,7 +17975,7 @@
       <c r="K986" s="6"/>
       <c r="L986" s="6"/>
     </row>
-    <row r="987" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A987" s="5"/>
       <c r="B987" s="5"/>
       <c r="C987" s="5"/>
@@ -17987,7 +17989,7 @@
       <c r="K987" s="6"/>
       <c r="L987" s="6"/>
     </row>
-    <row r="988" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A988" s="5"/>
       <c r="B988" s="5"/>
       <c r="C988" s="5"/>
@@ -18001,7 +18003,7 @@
       <c r="K988" s="6"/>
       <c r="L988" s="6"/>
     </row>
-    <row r="989" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A989" s="5"/>
       <c r="B989" s="5"/>
       <c r="C989" s="5"/>
@@ -18015,7 +18017,7 @@
       <c r="K989" s="6"/>
       <c r="L989" s="6"/>
     </row>
-    <row r="990" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A990" s="5"/>
       <c r="B990" s="5"/>
       <c r="C990" s="5"/>
@@ -18029,7 +18031,7 @@
       <c r="K990" s="6"/>
       <c r="L990" s="6"/>
     </row>
-    <row r="991" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A991" s="5"/>
       <c r="B991" s="5"/>
       <c r="C991" s="5"/>
@@ -18043,7 +18045,7 @@
       <c r="K991" s="6"/>
       <c r="L991" s="6"/>
     </row>
-    <row r="992" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A992" s="5"/>
       <c r="B992" s="5"/>
       <c r="C992" s="5"/>
@@ -18057,7 +18059,7 @@
       <c r="K992" s="6"/>
       <c r="L992" s="6"/>
     </row>
-    <row r="993" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A993" s="5"/>
       <c r="B993" s="5"/>
       <c r="C993" s="5"/>
@@ -18071,7 +18073,7 @@
       <c r="K993" s="6"/>
       <c r="L993" s="6"/>
     </row>
-    <row r="994" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A994" s="5"/>
       <c r="B994" s="5"/>
       <c r="C994" s="5"/>
@@ -18085,7 +18087,7 @@
       <c r="K994" s="6"/>
       <c r="L994" s="6"/>
     </row>
-    <row r="995" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A995" s="5"/>
       <c r="B995" s="5"/>
       <c r="C995" s="5"/>
@@ -18099,7 +18101,7 @@
       <c r="K995" s="6"/>
       <c r="L995" s="6"/>
     </row>
-    <row r="996" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A996" s="5"/>
       <c r="B996" s="5"/>
       <c r="C996" s="5"/>
@@ -18113,7 +18115,7 @@
       <c r="K996" s="6"/>
       <c r="L996" s="6"/>
     </row>
-    <row r="997" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A997" s="5"/>
       <c r="B997" s="5"/>
       <c r="C997" s="5"/>
@@ -18127,7 +18129,7 @@
       <c r="K997" s="6"/>
       <c r="L997" s="6"/>
     </row>
-    <row r="998" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A998" s="5"/>
       <c r="B998" s="5"/>
       <c r="C998" s="5"/>
@@ -18141,7 +18143,7 @@
       <c r="K998" s="6"/>
       <c r="L998" s="6"/>
     </row>
-    <row r="999" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A999" s="5"/>
       <c r="B999" s="5"/>
       <c r="C999" s="5"/>
@@ -18155,7 +18157,7 @@
       <c r="K999" s="6"/>
       <c r="L999" s="6"/>
     </row>
-    <row r="1000" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1000" s="5"/>
       <c r="B1000" s="5"/>
       <c r="C1000" s="5"/>
@@ -18169,7 +18171,7 @@
       <c r="K1000" s="6"/>
       <c r="L1000" s="6"/>
     </row>
-    <row r="1001" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1001" s="5"/>
       <c r="B1001" s="5"/>
       <c r="C1001" s="5"/>
@@ -18183,7 +18185,7 @@
       <c r="K1001" s="6"/>
       <c r="L1001" s="6"/>
     </row>
-    <row r="1002" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1002" s="5"/>
       <c r="B1002" s="5"/>
       <c r="C1002" s="5"/>
@@ -18197,7 +18199,7 @@
       <c r="K1002" s="6"/>
       <c r="L1002" s="6"/>
     </row>
-    <row r="1003" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1003" s="5"/>
       <c r="B1003" s="5"/>
       <c r="C1003" s="5"/>
@@ -18211,7 +18213,7 @@
       <c r="K1003" s="6"/>
       <c r="L1003" s="6"/>
     </row>
-    <row r="1004" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1004" s="5"/>
       <c r="B1004" s="5"/>
       <c r="C1004" s="5"/>
@@ -18225,7 +18227,7 @@
       <c r="K1004" s="6"/>
       <c r="L1004" s="6"/>
     </row>
-    <row r="1005" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1005" s="5"/>
       <c r="B1005" s="5"/>
       <c r="C1005" s="5"/>
@@ -18239,7 +18241,7 @@
       <c r="K1005" s="6"/>
       <c r="L1005" s="6"/>
     </row>
-    <row r="1006" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1006" s="5"/>
       <c r="B1006" s="5"/>
       <c r="C1006" s="5"/>
@@ -18253,7 +18255,7 @@
       <c r="K1006" s="6"/>
       <c r="L1006" s="6"/>
     </row>
-    <row r="1007" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1007" s="5"/>
       <c r="B1007" s="5"/>
       <c r="C1007" s="5"/>
@@ -18267,7 +18269,7 @@
       <c r="K1007" s="6"/>
       <c r="L1007" s="6"/>
     </row>
-    <row r="1008" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1008" s="5"/>
       <c r="B1008" s="5"/>
       <c r="C1008" s="5"/>
@@ -18281,7 +18283,7 @@
       <c r="K1008" s="6"/>
       <c r="L1008" s="6"/>
     </row>
-    <row r="1009" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1009" s="5"/>
       <c r="B1009" s="5"/>
       <c r="C1009" s="5"/>
@@ -18295,7 +18297,7 @@
       <c r="K1009" s="6"/>
       <c r="L1009" s="6"/>
     </row>
-    <row r="1010" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1010" s="5"/>
       <c r="B1010" s="5"/>
       <c r="C1010" s="5"/>
@@ -18309,7 +18311,7 @@
       <c r="K1010" s="6"/>
       <c r="L1010" s="6"/>
     </row>
-    <row r="1011" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1011" s="5"/>
       <c r="B1011" s="5"/>
       <c r="C1011" s="5"/>
@@ -18323,7 +18325,7 @@
       <c r="K1011" s="6"/>
       <c r="L1011" s="6"/>
     </row>
-    <row r="1012" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1012" s="5"/>
       <c r="B1012" s="5"/>
       <c r="C1012" s="5"/>
@@ -18337,7 +18339,7 @@
       <c r="K1012" s="6"/>
       <c r="L1012" s="6"/>
     </row>
-    <row r="1013" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1013" s="5"/>
       <c r="B1013" s="5"/>
       <c r="C1013" s="5"/>
@@ -18351,7 +18353,7 @@
       <c r="K1013" s="6"/>
       <c r="L1013" s="6"/>
     </row>
-    <row r="1014" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1014" s="5"/>
       <c r="B1014" s="5"/>
       <c r="C1014" s="5"/>
@@ -18365,7 +18367,7 @@
       <c r="K1014" s="6"/>
       <c r="L1014" s="6"/>
     </row>
-    <row r="1015" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1015" s="5"/>
       <c r="B1015" s="5"/>
       <c r="C1015" s="5"/>
@@ -18379,7 +18381,7 @@
       <c r="K1015" s="6"/>
       <c r="L1015" s="6"/>
     </row>
-    <row r="1016" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:12" ht="72" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1016" s="5" t="s">
         <v>602</v>
       </c>
@@ -18405,7 +18407,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="1017" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:12" ht="72" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1017" s="5" t="s">
         <v>608</v>
       </c>
@@ -18433,24 +18435,24 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K1017" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K1017" ns2:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Minor Repeatable,Minor Fire-Once,Major"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" ns2:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L1017" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" ns2:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation type="list" allowBlank="1" sqref="L2:L1017" ns2:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="R2:R16" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="R2:R16" ns2:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Implemented,New,In progress,Under review,Buggy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
+    <tablePart ns4:id="rId1"/>
+    <tablePart ns4:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Collapsing Soviet Union crisis with event-created republic focus trees, playable intervention boards, high-chaos successors, and the Civilian Factory of Russia Construction Directorate package.</t>
+          <t>Collapsing Soviet Union crisis with event-created republic focus trees, playable intervention boards, high-chaos successors, and CFR/MFR factory-state focus packages.</t>
         </is>
       </c>
       <c r="D6" s="6"/>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2544,7 +2544,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Collapsing Soviet Union crisis with event-created republic focus trees, playable intervention boards, high-chaos successors, and CFR/MFR factory-state focus packages.</t>
+          <t>Collapsing Soviet Union crisis with event-created republic focus trees, playable intervention boards, high-chaos successors, and CFR/MFR/OGB custom focus packages.</t>
         </is>
       </c>
       <c r="D6" s="6"/>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2271,13 +2271,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1C4587"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R1017"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" ns3:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
@@ -2296,7 +2296,7 @@
     <col min="18" max="18" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="99.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="111.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="90" customHeight="1" ns3:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>59</v>
       </c>
@@ -2544,21 +2544,51 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Collapsing Soviet Union crisis with event-created republic focus trees, playable intervention boards, high-chaos successors, and CFR/MFR/OGB custom focus packages.</t>
+          <t>Dynamic Soviet collapse crisis centered on Moscow authority, republic confidence, military obedience, depot vulnerability, foreign appetite, League cohesion, and high-chaos weirdness. The chain opens through chaos-scaled crisis values, releases event-created republics when their gates are met, gives every appearing republic or serious splinter starting guards and later reinforcement routes, activates capped Soviet goal missions, and adds breakaway and foreign-intervention decisions that spend equipment, XP, manpower, stability, war support, fuel, trains, convoys, support points, rail control, depot control, and local support rather than default political power. Ukraine, Belarus, Kazakhstan, regional republics, fallback breakaways, factory states, ancient restorations, and high-chaos custom successors receive runtime focus trees, ideas, decisions, localisation, assets, docs, and event-log/super-event wiring where specified.</t>
         </is>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>No Calm World evolution. Calm World is the base unlock; opening crisis pressure and ordinary stage reports are handled through crisis variables, missions, decisions, event details, and normal event history.</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>No baseline Rising Chaos evolution. Republic declarations, Soviet objective pressure, foreign aid, and League preparation remain crisis progression rather than evolution-log entries.</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>No baseline Chaos Tier evolution. Second-wave republics, intervention escalation, and League settlement pressure stay in missions, events, decisions, and focus branches unless a separate mutation track is explicitly selected.</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>High-chaos successor mutation: the first eligible tier-4 serious successor records one actor-linked Soviet Collapse evolution log. Later tier-4 successor notices remain normal reports to avoid duplicate evolution spam.</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Totalen Chaos successor mutation: the first eligible tier-5 serious successor records one actor-linked Soviet Collapse evolution log. Extreme successors can still spawn and fire reports, but only one tier-5 log is written.</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Reserved for future explicitly specified mutation tracks. Current implementation does not log ordinary Soviet Collapse stages as evolutions.</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>No dedicated Event 005 world-end scenario is currently implemented. Specified capstone routes fire super-event presentations such as The Black Banner Returns, The Dead Are Citizens, The World as One Factory, Every Port a Council, Steppe Federation, and The Union Unmade.</t>
+        </is>
+      </c>
       <c r="K6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>67</v>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Implemented - Final Audit Passed</t>
+        </is>
       </c>
       <c r="N6" s="7" t="s">
         <v>62</v>
@@ -2572,11 +2602,13 @@
       <c r="Q6" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="R6" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t>Final Audit Passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>64</v>
       </c>
@@ -2611,7 +2643,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>69</v>
       </c>
@@ -2648,7 +2680,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>74</v>
       </c>
@@ -2683,7 +2715,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>78</v>
       </c>
@@ -2718,7 +2750,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>82</v>
       </c>
@@ -2755,7 +2787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>87</v>
       </c>
@@ -2792,7 +2824,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>92</v>
       </c>
@@ -2827,7 +2859,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>96</v>
       </c>
@@ -2864,7 +2896,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>100</v>
       </c>
@@ -2901,7 +2933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>105</v>
       </c>
@@ -2934,7 +2966,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>108</v>
       </c>
@@ -2958,7 +2990,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>111</v>
       </c>
@@ -2982,7 +3014,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>114</v>
       </c>
@@ -3006,7 +3038,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>117</v>
       </c>
@@ -3030,7 +3062,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>120</v>
       </c>
@@ -3056,7 +3088,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>124</v>
       </c>
@@ -3083,7 +3115,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>128</v>
       </c>
@@ -3107,7 +3139,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>131</v>
       </c>
@@ -3131,7 +3163,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>134</v>
       </c>
@@ -3155,7 +3187,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>137</v>
       </c>
@@ -3179,7 +3211,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>140</v>
       </c>
@@ -3203,7 +3235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>143</v>
       </c>
@@ -3227,7 +3259,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>146</v>
       </c>
@@ -3251,7 +3283,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>149</v>
       </c>
@@ -3275,7 +3307,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>152</v>
       </c>
@@ -3301,7 +3333,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="32" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>156</v>
       </c>
@@ -3325,7 +3357,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>159</v>
       </c>
@@ -3349,7 +3381,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>162</v>
       </c>
@@ -3373,7 +3405,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>165</v>
       </c>
@@ -3397,7 +3429,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>168</v>
       </c>
@@ -3421,7 +3453,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>171</v>
       </c>
@@ -3445,7 +3477,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>174</v>
       </c>
@@ -3469,7 +3501,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>177</v>
       </c>
@@ -3495,7 +3527,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>181</v>
       </c>
@@ -3519,7 +3551,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>184</v>
       </c>
@@ -3543,7 +3575,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>187</v>
       </c>
@@ -3567,7 +3599,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>190</v>
       </c>
@@ -3591,7 +3623,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>193</v>
       </c>
@@ -3615,7 +3647,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>196</v>
       </c>
@@ -3639,7 +3671,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>199</v>
       </c>
@@ -3663,7 +3695,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>202</v>
       </c>
@@ -3687,7 +3719,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>205</v>
       </c>
@@ -3711,7 +3743,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>208</v>
       </c>
@@ -3735,7 +3767,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>211</v>
       </c>
@@ -3759,7 +3791,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>214</v>
       </c>
@@ -3783,7 +3815,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>217</v>
       </c>
@@ -3807,7 +3839,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>220</v>
       </c>
@@ -3831,7 +3863,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>223</v>
       </c>
@@ -3855,7 +3887,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>226</v>
       </c>
@@ -3879,7 +3911,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>229</v>
       </c>
@@ -3903,7 +3935,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>232</v>
       </c>
@@ -3927,7 +3959,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>235</v>
       </c>
@@ -3951,7 +3983,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>238</v>
       </c>
@@ -3975,7 +4007,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>241</v>
       </c>
@@ -3999,7 +4031,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>244</v>
       </c>
@@ -4023,7 +4055,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>247</v>
       </c>
@@ -4047,7 +4079,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>250</v>
       </c>
@@ -4071,7 +4103,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>253</v>
       </c>
@@ -4095,7 +4127,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>256</v>
       </c>
@@ -4119,7 +4151,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>259</v>
       </c>
@@ -4143,7 +4175,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>262</v>
       </c>
@@ -4167,7 +4199,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>265</v>
       </c>
@@ -4191,7 +4223,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>268</v>
       </c>
@@ -4217,7 +4249,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>272</v>
       </c>
@@ -4241,7 +4273,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>275</v>
       </c>
@@ -4265,7 +4297,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>278</v>
       </c>
@@ -4289,7 +4321,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>281</v>
       </c>
@@ -4313,7 +4345,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>284</v>
       </c>
@@ -4337,7 +4369,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>287</v>
       </c>
@@ -4361,7 +4393,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>290</v>
       </c>
@@ -4385,7 +4417,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>293</v>
       </c>
@@ -4409,7 +4441,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>296</v>
       </c>
@@ -4433,7 +4465,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>299</v>
       </c>
@@ -4457,7 +4489,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>302</v>
       </c>
@@ -4481,7 +4513,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>305</v>
       </c>
@@ -4505,7 +4537,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>308</v>
       </c>
@@ -4529,7 +4561,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>311</v>
       </c>
@@ -4553,7 +4585,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>314</v>
       </c>
@@ -4577,7 +4609,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>317</v>
       </c>
@@ -4601,7 +4633,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>320</v>
       </c>
@@ -4625,7 +4657,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>323</v>
       </c>
@@ -4649,7 +4681,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>326</v>
       </c>
@@ -4673,7 +4705,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>329</v>
       </c>
@@ -4697,7 +4729,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>332</v>
       </c>
@@ -4721,7 +4753,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>335</v>
       </c>
@@ -4745,7 +4777,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>338</v>
       </c>
@@ -4771,7 +4803,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>342</v>
       </c>
@@ -4795,7 +4827,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>345</v>
       </c>
@@ -4819,7 +4851,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>348</v>
       </c>
@@ -4843,7 +4875,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>351</v>
       </c>
@@ -4867,7 +4899,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>354</v>
       </c>
@@ -4891,7 +4923,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>357</v>
       </c>
@@ -4915,7 +4947,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>360</v>
       </c>
@@ -4939,7 +4971,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>363</v>
       </c>
@@ -4963,7 +4995,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>366</v>
       </c>
@@ -4985,7 +5017,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>369</v>
       </c>
@@ -5007,7 +5039,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>372</v>
       </c>
@@ -5029,7 +5061,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>375</v>
       </c>
@@ -5051,7 +5083,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>378</v>
       </c>
@@ -5073,7 +5105,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>381</v>
       </c>
@@ -5095,7 +5127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>384</v>
       </c>
@@ -5117,7 +5149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>387</v>
       </c>
@@ -5139,7 +5171,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>390</v>
       </c>
@@ -5161,7 +5193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>393</v>
       </c>
@@ -5183,7 +5215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>396</v>
       </c>
@@ -5205,7 +5237,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>399</v>
       </c>
@@ -5227,7 +5259,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>402</v>
       </c>
@@ -5249,7 +5281,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>405</v>
       </c>
@@ -5271,7 +5303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>408</v>
       </c>
@@ -5293,7 +5325,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>411</v>
       </c>
@@ -5315,7 +5347,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>414</v>
       </c>
@@ -5337,7 +5369,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>417</v>
       </c>
@@ -5359,7 +5391,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>420</v>
       </c>
@@ -5381,7 +5413,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>423</v>
       </c>
@@ -5403,7 +5435,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>426</v>
       </c>
@@ -5425,7 +5457,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>429</v>
       </c>
@@ -5447,7 +5479,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>432</v>
       </c>
@@ -5469,7 +5501,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>435</v>
       </c>
@@ -5491,7 +5523,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>438</v>
       </c>
@@ -5513,7 +5545,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>441</v>
       </c>
@@ -5535,7 +5567,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>444</v>
       </c>
@@ -5557,7 +5589,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>447</v>
       </c>
@@ -5579,7 +5611,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>450</v>
       </c>
@@ -5601,7 +5633,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>453</v>
       </c>
@@ -5623,7 +5655,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>456</v>
       </c>
@@ -5645,7 +5677,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="132" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>459</v>
       </c>
@@ -5667,7 +5699,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>462</v>
       </c>
@@ -5689,7 +5721,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>465</v>
       </c>
@@ -5711,7 +5743,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>468</v>
       </c>
@@ -5733,7 +5765,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>471</v>
       </c>
@@ -5755,7 +5787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>474</v>
       </c>
@@ -5777,7 +5809,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>477</v>
       </c>
@@ -5799,7 +5831,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>480</v>
       </c>
@@ -5821,7 +5853,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>483</v>
       </c>
@@ -5843,7 +5875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>486</v>
       </c>
@@ -5865,7 +5897,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>489</v>
       </c>
@@ -5887,7 +5919,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>492</v>
       </c>
@@ -5909,7 +5941,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>495</v>
       </c>
@@ -5931,7 +5963,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>498</v>
       </c>
@@ -5953,7 +5985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>501</v>
       </c>
@@ -5975,7 +6007,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>504</v>
       </c>
@@ -5997,7 +6029,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>507</v>
       </c>
@@ -6019,7 +6051,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>510</v>
       </c>
@@ -6041,7 +6073,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>513</v>
       </c>
@@ -6063,7 +6095,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>516</v>
       </c>
@@ -6085,7 +6117,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>519</v>
       </c>
@@ -6109,7 +6141,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="153" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>523</v>
       </c>
@@ -6131,7 +6163,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="154" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>526</v>
       </c>
@@ -6153,7 +6185,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="155" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>529</v>
       </c>
@@ -6175,7 +6207,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>532</v>
       </c>
@@ -6197,7 +6229,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="157" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>535</v>
       </c>
@@ -6219,7 +6251,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="158" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>538</v>
       </c>
@@ -6241,7 +6273,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>541</v>
       </c>
@@ -6263,7 +6295,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="160" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>544</v>
       </c>
@@ -6285,7 +6317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>547</v>
       </c>
@@ -6307,7 +6339,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="162" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>550</v>
       </c>
@@ -6331,7 +6363,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="163" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>554</v>
       </c>
@@ -6353,7 +6385,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="164" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>557</v>
       </c>
@@ -6375,7 +6407,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>560</v>
       </c>
@@ -6397,7 +6429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>563</v>
       </c>
@@ -6419,7 +6451,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>566</v>
       </c>
@@ -6443,7 +6475,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="168" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="5"/>
       <c r="B168" s="5" t="s">
         <v>569</v>
@@ -6461,7 +6493,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="169" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="5"/>
       <c r="B169" s="5" t="s">
         <v>571</v>
@@ -6479,7 +6511,7 @@
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
     </row>
-    <row r="170" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="170" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="5"/>
       <c r="B170" s="5" t="s">
         <v>573</v>
@@ -6497,7 +6529,7 @@
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
     </row>
-    <row r="171" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="171" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="5"/>
       <c r="B171" s="5" t="s">
         <v>575</v>
@@ -6515,7 +6547,7 @@
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
     </row>
-    <row r="172" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="172" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="5"/>
       <c r="B172" s="5" t="s">
         <v>577</v>
@@ -6533,7 +6565,7 @@
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
     </row>
-    <row r="173" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="173" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="5"/>
       <c r="B173" s="5" t="s">
         <v>579</v>
@@ -6553,7 +6585,7 @@
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
     </row>
-    <row r="174" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="174" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="5"/>
       <c r="B174" s="5" t="s">
         <v>582</v>
@@ -6571,7 +6603,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="175" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="5" t="s">
         <v>584</v>
@@ -6589,7 +6621,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="176" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="5" t="s">
         <v>586</v>
@@ -6607,7 +6639,7 @@
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
     </row>
-    <row r="177" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="177" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="5" t="s">
         <v>588</v>
@@ -6625,7 +6657,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="178" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="5" t="s">
         <v>590</v>
@@ -6643,7 +6675,7 @@
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
     </row>
-    <row r="179" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="179" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="5" t="s">
         <v>592</v>
@@ -6661,7 +6693,7 @@
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
     </row>
-    <row r="180" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="180" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="5" t="s">
         <v>594</v>
@@ -6679,7 +6711,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="181" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="5" t="s">
         <v>596</v>
@@ -6697,7 +6729,7 @@
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
     </row>
-    <row r="182" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="182" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="5" t="s">
         <v>598</v>
@@ -6715,7 +6747,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="183" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="5" t="s">
         <v>600</v>
@@ -6733,7 +6765,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="184" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -6747,7 +6779,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="185" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -6761,7 +6793,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="186" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -6775,7 +6807,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="187" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -6789,7 +6821,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="188" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -6803,7 +6835,7 @@
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
     </row>
-    <row r="189" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="189" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -6817,7 +6849,7 @@
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
     </row>
-    <row r="190" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="190" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -6831,7 +6863,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="191" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -6845,7 +6877,7 @@
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
     </row>
-    <row r="192" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="192" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -6859,7 +6891,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="193" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -6873,7 +6905,7 @@
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
     </row>
-    <row r="194" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="194" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -6887,7 +6919,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="195" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -6901,7 +6933,7 @@
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
     </row>
-    <row r="196" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="196" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -6915,7 +6947,7 @@
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
     </row>
-    <row r="197" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="197" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -6929,7 +6961,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="198" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -6943,7 +6975,7 @@
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
     </row>
-    <row r="199" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="199" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -6957,7 +6989,7 @@
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
     </row>
-    <row r="200" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="200" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -6971,7 +7003,7 @@
       <c r="K200" s="6"/>
       <c r="L200" s="6"/>
     </row>
-    <row r="201" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="201" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -6985,7 +7017,7 @@
       <c r="K201" s="6"/>
       <c r="L201" s="6"/>
     </row>
-    <row r="202" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="202" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -6999,7 +7031,7 @@
       <c r="K202" s="6"/>
       <c r="L202" s="6"/>
     </row>
-    <row r="203" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="203" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -7013,7 +7045,7 @@
       <c r="K203" s="6"/>
       <c r="L203" s="6"/>
     </row>
-    <row r="204" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="204" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -7027,7 +7059,7 @@
       <c r="K204" s="6"/>
       <c r="L204" s="6"/>
     </row>
-    <row r="205" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="205" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -7041,7 +7073,7 @@
       <c r="K205" s="6"/>
       <c r="L205" s="6"/>
     </row>
-    <row r="206" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="206" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -7055,7 +7087,7 @@
       <c r="K206" s="6"/>
       <c r="L206" s="6"/>
     </row>
-    <row r="207" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="207" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -7069,7 +7101,7 @@
       <c r="K207" s="6"/>
       <c r="L207" s="6"/>
     </row>
-    <row r="208" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="208" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -7083,7 +7115,7 @@
       <c r="K208" s="6"/>
       <c r="L208" s="6"/>
     </row>
-    <row r="209" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="209" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -7097,7 +7129,7 @@
       <c r="K209" s="6"/>
       <c r="L209" s="6"/>
     </row>
-    <row r="210" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="210" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -7111,7 +7143,7 @@
       <c r="K210" s="6"/>
       <c r="L210" s="6"/>
     </row>
-    <row r="211" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="211" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -7125,7 +7157,7 @@
       <c r="K211" s="6"/>
       <c r="L211" s="6"/>
     </row>
-    <row r="212" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="212" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -7139,7 +7171,7 @@
       <c r="K212" s="6"/>
       <c r="L212" s="6"/>
     </row>
-    <row r="213" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="213" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -7153,7 +7185,7 @@
       <c r="K213" s="6"/>
       <c r="L213" s="6"/>
     </row>
-    <row r="214" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="214" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -7167,7 +7199,7 @@
       <c r="K214" s="6"/>
       <c r="L214" s="6"/>
     </row>
-    <row r="215" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="215" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -7181,7 +7213,7 @@
       <c r="K215" s="6"/>
       <c r="L215" s="6"/>
     </row>
-    <row r="216" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="216" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -7195,7 +7227,7 @@
       <c r="K216" s="6"/>
       <c r="L216" s="6"/>
     </row>
-    <row r="217" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="217" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -7209,7 +7241,7 @@
       <c r="K217" s="6"/>
       <c r="L217" s="6"/>
     </row>
-    <row r="218" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="218" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -7223,7 +7255,7 @@
       <c r="K218" s="6"/>
       <c r="L218" s="6"/>
     </row>
-    <row r="219" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="219" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -7237,7 +7269,7 @@
       <c r="K219" s="6"/>
       <c r="L219" s="6"/>
     </row>
-    <row r="220" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="220" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -7251,7 +7283,7 @@
       <c r="K220" s="6"/>
       <c r="L220" s="6"/>
     </row>
-    <row r="221" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="221" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -7265,7 +7297,7 @@
       <c r="K221" s="6"/>
       <c r="L221" s="6"/>
     </row>
-    <row r="222" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="222" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -7279,7 +7311,7 @@
       <c r="K222" s="6"/>
       <c r="L222" s="6"/>
     </row>
-    <row r="223" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="223" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -7293,7 +7325,7 @@
       <c r="K223" s="6"/>
       <c r="L223" s="6"/>
     </row>
-    <row r="224" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="224" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -7307,7 +7339,7 @@
       <c r="K224" s="6"/>
       <c r="L224" s="6"/>
     </row>
-    <row r="225" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="225" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -7321,7 +7353,7 @@
       <c r="K225" s="6"/>
       <c r="L225" s="6"/>
     </row>
-    <row r="226" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="226" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -7335,7 +7367,7 @@
       <c r="K226" s="6"/>
       <c r="L226" s="6"/>
     </row>
-    <row r="227" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="227" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -7349,7 +7381,7 @@
       <c r="K227" s="6"/>
       <c r="L227" s="6"/>
     </row>
-    <row r="228" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="228" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -7363,7 +7395,7 @@
       <c r="K228" s="6"/>
       <c r="L228" s="6"/>
     </row>
-    <row r="229" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="229" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -7377,7 +7409,7 @@
       <c r="K229" s="6"/>
       <c r="L229" s="6"/>
     </row>
-    <row r="230" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="230" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -7391,7 +7423,7 @@
       <c r="K230" s="6"/>
       <c r="L230" s="6"/>
     </row>
-    <row r="231" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="231" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -7405,7 +7437,7 @@
       <c r="K231" s="6"/>
       <c r="L231" s="6"/>
     </row>
-    <row r="232" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="232" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -7419,7 +7451,7 @@
       <c r="K232" s="6"/>
       <c r="L232" s="6"/>
     </row>
-    <row r="233" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="233" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -7433,7 +7465,7 @@
       <c r="K233" s="6"/>
       <c r="L233" s="6"/>
     </row>
-    <row r="234" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="234" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -7447,7 +7479,7 @@
       <c r="K234" s="6"/>
       <c r="L234" s="6"/>
     </row>
-    <row r="235" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="235" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -7461,7 +7493,7 @@
       <c r="K235" s="6"/>
       <c r="L235" s="6"/>
     </row>
-    <row r="236" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="236" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -7475,7 +7507,7 @@
       <c r="K236" s="6"/>
       <c r="L236" s="6"/>
     </row>
-    <row r="237" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="237" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -7489,7 +7521,7 @@
       <c r="K237" s="6"/>
       <c r="L237" s="6"/>
     </row>
-    <row r="238" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="238" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -7503,7 +7535,7 @@
       <c r="K238" s="6"/>
       <c r="L238" s="6"/>
     </row>
-    <row r="239" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="239" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -7517,7 +7549,7 @@
       <c r="K239" s="6"/>
       <c r="L239" s="6"/>
     </row>
-    <row r="240" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="240" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -7531,7 +7563,7 @@
       <c r="K240" s="6"/>
       <c r="L240" s="6"/>
     </row>
-    <row r="241" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="241" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -7545,7 +7577,7 @@
       <c r="K241" s="6"/>
       <c r="L241" s="6"/>
     </row>
-    <row r="242" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="242" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -7559,7 +7591,7 @@
       <c r="K242" s="6"/>
       <c r="L242" s="6"/>
     </row>
-    <row r="243" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="243" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -7573,7 +7605,7 @@
       <c r="K243" s="6"/>
       <c r="L243" s="6"/>
     </row>
-    <row r="244" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="244" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -7587,7 +7619,7 @@
       <c r="K244" s="6"/>
       <c r="L244" s="6"/>
     </row>
-    <row r="245" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="245" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -7601,7 +7633,7 @@
       <c r="K245" s="6"/>
       <c r="L245" s="6"/>
     </row>
-    <row r="246" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="246" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -7615,7 +7647,7 @@
       <c r="K246" s="6"/>
       <c r="L246" s="6"/>
     </row>
-    <row r="247" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="247" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -7629,7 +7661,7 @@
       <c r="K247" s="6"/>
       <c r="L247" s="6"/>
     </row>
-    <row r="248" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="248" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -7643,7 +7675,7 @@
       <c r="K248" s="6"/>
       <c r="L248" s="6"/>
     </row>
-    <row r="249" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="249" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -7657,7 +7689,7 @@
       <c r="K249" s="6"/>
       <c r="L249" s="6"/>
     </row>
-    <row r="250" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="250" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -7671,7 +7703,7 @@
       <c r="K250" s="6"/>
       <c r="L250" s="6"/>
     </row>
-    <row r="251" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="251" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -7685,7 +7717,7 @@
       <c r="K251" s="6"/>
       <c r="L251" s="6"/>
     </row>
-    <row r="252" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="252" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -7699,7 +7731,7 @@
       <c r="K252" s="6"/>
       <c r="L252" s="6"/>
     </row>
-    <row r="253" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="253" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -7713,7 +7745,7 @@
       <c r="K253" s="6"/>
       <c r="L253" s="6"/>
     </row>
-    <row r="254" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="254" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -7727,7 +7759,7 @@
       <c r="K254" s="6"/>
       <c r="L254" s="6"/>
     </row>
-    <row r="255" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="255" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -7741,7 +7773,7 @@
       <c r="K255" s="6"/>
       <c r="L255" s="6"/>
     </row>
-    <row r="256" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="256" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -7755,7 +7787,7 @@
       <c r="K256" s="6"/>
       <c r="L256" s="6"/>
     </row>
-    <row r="257" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="257" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -7769,7 +7801,7 @@
       <c r="K257" s="6"/>
       <c r="L257" s="6"/>
     </row>
-    <row r="258" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="258" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -7783,7 +7815,7 @@
       <c r="K258" s="6"/>
       <c r="L258" s="6"/>
     </row>
-    <row r="259" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="259" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -7797,7 +7829,7 @@
       <c r="K259" s="6"/>
       <c r="L259" s="6"/>
     </row>
-    <row r="260" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="260" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -7811,7 +7843,7 @@
       <c r="K260" s="6"/>
       <c r="L260" s="6"/>
     </row>
-    <row r="261" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="261" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -7825,7 +7857,7 @@
       <c r="K261" s="6"/>
       <c r="L261" s="6"/>
     </row>
-    <row r="262" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="262" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -7839,7 +7871,7 @@
       <c r="K262" s="6"/>
       <c r="L262" s="6"/>
     </row>
-    <row r="263" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="263" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -7853,7 +7885,7 @@
       <c r="K263" s="6"/>
       <c r="L263" s="6"/>
     </row>
-    <row r="264" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="264" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -7867,7 +7899,7 @@
       <c r="K264" s="6"/>
       <c r="L264" s="6"/>
     </row>
-    <row r="265" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="265" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -7881,7 +7913,7 @@
       <c r="K265" s="6"/>
       <c r="L265" s="6"/>
     </row>
-    <row r="266" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="266" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -7895,7 +7927,7 @@
       <c r="K266" s="6"/>
       <c r="L266" s="6"/>
     </row>
-    <row r="267" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="267" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -7909,7 +7941,7 @@
       <c r="K267" s="6"/>
       <c r="L267" s="6"/>
     </row>
-    <row r="268" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="268" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -7923,7 +7955,7 @@
       <c r="K268" s="6"/>
       <c r="L268" s="6"/>
     </row>
-    <row r="269" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="269" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -7937,7 +7969,7 @@
       <c r="K269" s="6"/>
       <c r="L269" s="6"/>
     </row>
-    <row r="270" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="270" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -7951,7 +7983,7 @@
       <c r="K270" s="6"/>
       <c r="L270" s="6"/>
     </row>
-    <row r="271" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="271" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -7965,7 +7997,7 @@
       <c r="K271" s="6"/>
       <c r="L271" s="6"/>
     </row>
-    <row r="272" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="272" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -7979,7 +8011,7 @@
       <c r="K272" s="6"/>
       <c r="L272" s="6"/>
     </row>
-    <row r="273" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="273" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -7993,7 +8025,7 @@
       <c r="K273" s="6"/>
       <c r="L273" s="6"/>
     </row>
-    <row r="274" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="274" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -8007,7 +8039,7 @@
       <c r="K274" s="6"/>
       <c r="L274" s="6"/>
     </row>
-    <row r="275" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="275" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -8021,7 +8053,7 @@
       <c r="K275" s="6"/>
       <c r="L275" s="6"/>
     </row>
-    <row r="276" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="276" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -8035,7 +8067,7 @@
       <c r="K276" s="6"/>
       <c r="L276" s="6"/>
     </row>
-    <row r="277" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="277" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -8049,7 +8081,7 @@
       <c r="K277" s="6"/>
       <c r="L277" s="6"/>
     </row>
-    <row r="278" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="278" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -8063,7 +8095,7 @@
       <c r="K278" s="6"/>
       <c r="L278" s="6"/>
     </row>
-    <row r="279" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="279" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -8077,7 +8109,7 @@
       <c r="K279" s="6"/>
       <c r="L279" s="6"/>
     </row>
-    <row r="280" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="280" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -8091,7 +8123,7 @@
       <c r="K280" s="6"/>
       <c r="L280" s="6"/>
     </row>
-    <row r="281" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="281" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -8105,7 +8137,7 @@
       <c r="K281" s="6"/>
       <c r="L281" s="6"/>
     </row>
-    <row r="282" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="282" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -8119,7 +8151,7 @@
       <c r="K282" s="6"/>
       <c r="L282" s="6"/>
     </row>
-    <row r="283" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="283" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -8133,7 +8165,7 @@
       <c r="K283" s="6"/>
       <c r="L283" s="6"/>
     </row>
-    <row r="284" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="284" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -8147,7 +8179,7 @@
       <c r="K284" s="6"/>
       <c r="L284" s="6"/>
     </row>
-    <row r="285" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="285" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -8161,7 +8193,7 @@
       <c r="K285" s="6"/>
       <c r="L285" s="6"/>
     </row>
-    <row r="286" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="286" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -8175,7 +8207,7 @@
       <c r="K286" s="6"/>
       <c r="L286" s="6"/>
     </row>
-    <row r="287" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="287" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -8189,7 +8221,7 @@
       <c r="K287" s="6"/>
       <c r="L287" s="6"/>
     </row>
-    <row r="288" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="288" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -8203,7 +8235,7 @@
       <c r="K288" s="6"/>
       <c r="L288" s="6"/>
     </row>
-    <row r="289" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="289" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -8217,7 +8249,7 @@
       <c r="K289" s="6"/>
       <c r="L289" s="6"/>
     </row>
-    <row r="290" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="290" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -8231,7 +8263,7 @@
       <c r="K290" s="6"/>
       <c r="L290" s="6"/>
     </row>
-    <row r="291" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="291" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -8245,7 +8277,7 @@
       <c r="K291" s="6"/>
       <c r="L291" s="6"/>
     </row>
-    <row r="292" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="292" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -8259,7 +8291,7 @@
       <c r="K292" s="6"/>
       <c r="L292" s="6"/>
     </row>
-    <row r="293" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="293" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -8273,7 +8305,7 @@
       <c r="K293" s="6"/>
       <c r="L293" s="6"/>
     </row>
-    <row r="294" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="294" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -8287,7 +8319,7 @@
       <c r="K294" s="6"/>
       <c r="L294" s="6"/>
     </row>
-    <row r="295" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="295" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -8301,7 +8333,7 @@
       <c r="K295" s="6"/>
       <c r="L295" s="6"/>
     </row>
-    <row r="296" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="296" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -8315,7 +8347,7 @@
       <c r="K296" s="6"/>
       <c r="L296" s="6"/>
     </row>
-    <row r="297" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="297" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -8329,7 +8361,7 @@
       <c r="K297" s="6"/>
       <c r="L297" s="6"/>
     </row>
-    <row r="298" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="298" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -8343,7 +8375,7 @@
       <c r="K298" s="6"/>
       <c r="L298" s="6"/>
     </row>
-    <row r="299" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="299" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -8357,7 +8389,7 @@
       <c r="K299" s="6"/>
       <c r="L299" s="6"/>
     </row>
-    <row r="300" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="300" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -8371,7 +8403,7 @@
       <c r="K300" s="6"/>
       <c r="L300" s="6"/>
     </row>
-    <row r="301" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="301" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -8385,7 +8417,7 @@
       <c r="K301" s="6"/>
       <c r="L301" s="6"/>
     </row>
-    <row r="302" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="302" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -8399,7 +8431,7 @@
       <c r="K302" s="6"/>
       <c r="L302" s="6"/>
     </row>
-    <row r="303" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="303" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -8413,7 +8445,7 @@
       <c r="K303" s="6"/>
       <c r="L303" s="6"/>
     </row>
-    <row r="304" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="304" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -8427,7 +8459,7 @@
       <c r="K304" s="6"/>
       <c r="L304" s="6"/>
     </row>
-    <row r="305" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="305" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -8441,7 +8473,7 @@
       <c r="K305" s="6"/>
       <c r="L305" s="6"/>
     </row>
-    <row r="306" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="306" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -8455,7 +8487,7 @@
       <c r="K306" s="6"/>
       <c r="L306" s="6"/>
     </row>
-    <row r="307" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="307" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -8469,7 +8501,7 @@
       <c r="K307" s="6"/>
       <c r="L307" s="6"/>
     </row>
-    <row r="308" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="308" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -8483,7 +8515,7 @@
       <c r="K308" s="6"/>
       <c r="L308" s="6"/>
     </row>
-    <row r="309" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="309" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -8497,7 +8529,7 @@
       <c r="K309" s="6"/>
       <c r="L309" s="6"/>
     </row>
-    <row r="310" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="310" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -8511,7 +8543,7 @@
       <c r="K310" s="6"/>
       <c r="L310" s="6"/>
     </row>
-    <row r="311" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="311" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -8525,7 +8557,7 @@
       <c r="K311" s="6"/>
       <c r="L311" s="6"/>
     </row>
-    <row r="312" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="312" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -8539,7 +8571,7 @@
       <c r="K312" s="6"/>
       <c r="L312" s="6"/>
     </row>
-    <row r="313" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="313" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -8553,7 +8585,7 @@
       <c r="K313" s="6"/>
       <c r="L313" s="6"/>
     </row>
-    <row r="314" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="314" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -8567,7 +8599,7 @@
       <c r="K314" s="6"/>
       <c r="L314" s="6"/>
     </row>
-    <row r="315" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="315" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -8581,7 +8613,7 @@
       <c r="K315" s="6"/>
       <c r="L315" s="6"/>
     </row>
-    <row r="316" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="316" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -8595,7 +8627,7 @@
       <c r="K316" s="6"/>
       <c r="L316" s="6"/>
     </row>
-    <row r="317" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="317" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -8609,7 +8641,7 @@
       <c r="K317" s="6"/>
       <c r="L317" s="6"/>
     </row>
-    <row r="318" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="318" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -8623,7 +8655,7 @@
       <c r="K318" s="6"/>
       <c r="L318" s="6"/>
     </row>
-    <row r="319" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="319" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -8637,7 +8669,7 @@
       <c r="K319" s="6"/>
       <c r="L319" s="6"/>
     </row>
-    <row r="320" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="320" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -8651,7 +8683,7 @@
       <c r="K320" s="6"/>
       <c r="L320" s="6"/>
     </row>
-    <row r="321" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="321" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -8665,7 +8697,7 @@
       <c r="K321" s="6"/>
       <c r="L321" s="6"/>
     </row>
-    <row r="322" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="322" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -8679,7 +8711,7 @@
       <c r="K322" s="6"/>
       <c r="L322" s="6"/>
     </row>
-    <row r="323" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="323" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -8693,7 +8725,7 @@
       <c r="K323" s="6"/>
       <c r="L323" s="6"/>
     </row>
-    <row r="324" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="324" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -8707,7 +8739,7 @@
       <c r="K324" s="6"/>
       <c r="L324" s="6"/>
     </row>
-    <row r="325" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="325" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -8721,7 +8753,7 @@
       <c r="K325" s="6"/>
       <c r="L325" s="6"/>
     </row>
-    <row r="326" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="326" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -8735,7 +8767,7 @@
       <c r="K326" s="6"/>
       <c r="L326" s="6"/>
     </row>
-    <row r="327" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="327" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -8749,7 +8781,7 @@
       <c r="K327" s="6"/>
       <c r="L327" s="6"/>
     </row>
-    <row r="328" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="328" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -8763,7 +8795,7 @@
       <c r="K328" s="6"/>
       <c r="L328" s="6"/>
     </row>
-    <row r="329" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="329" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -8777,7 +8809,7 @@
       <c r="K329" s="6"/>
       <c r="L329" s="6"/>
     </row>
-    <row r="330" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="330" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -8791,7 +8823,7 @@
       <c r="K330" s="6"/>
       <c r="L330" s="6"/>
     </row>
-    <row r="331" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="331" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -8805,7 +8837,7 @@
       <c r="K331" s="6"/>
       <c r="L331" s="6"/>
     </row>
-    <row r="332" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="332" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -8819,7 +8851,7 @@
       <c r="K332" s="6"/>
       <c r="L332" s="6"/>
     </row>
-    <row r="333" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="333" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -8833,7 +8865,7 @@
       <c r="K333" s="6"/>
       <c r="L333" s="6"/>
     </row>
-    <row r="334" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="334" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -8847,7 +8879,7 @@
       <c r="K334" s="6"/>
       <c r="L334" s="6"/>
     </row>
-    <row r="335" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="335" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -8861,7 +8893,7 @@
       <c r="K335" s="6"/>
       <c r="L335" s="6"/>
     </row>
-    <row r="336" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="336" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -8875,7 +8907,7 @@
       <c r="K336" s="6"/>
       <c r="L336" s="6"/>
     </row>
-    <row r="337" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="337" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -8889,7 +8921,7 @@
       <c r="K337" s="6"/>
       <c r="L337" s="6"/>
     </row>
-    <row r="338" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="338" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -8903,7 +8935,7 @@
       <c r="K338" s="6"/>
       <c r="L338" s="6"/>
     </row>
-    <row r="339" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="339" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -8917,7 +8949,7 @@
       <c r="K339" s="6"/>
       <c r="L339" s="6"/>
     </row>
-    <row r="340" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="340" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -8931,7 +8963,7 @@
       <c r="K340" s="6"/>
       <c r="L340" s="6"/>
     </row>
-    <row r="341" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="341" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -8945,7 +8977,7 @@
       <c r="K341" s="6"/>
       <c r="L341" s="6"/>
     </row>
-    <row r="342" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="342" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -8959,7 +8991,7 @@
       <c r="K342" s="6"/>
       <c r="L342" s="6"/>
     </row>
-    <row r="343" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="343" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -8973,7 +9005,7 @@
       <c r="K343" s="6"/>
       <c r="L343" s="6"/>
     </row>
-    <row r="344" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="344" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -8987,7 +9019,7 @@
       <c r="K344" s="6"/>
       <c r="L344" s="6"/>
     </row>
-    <row r="345" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="345" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -9001,7 +9033,7 @@
       <c r="K345" s="6"/>
       <c r="L345" s="6"/>
     </row>
-    <row r="346" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="346" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -9015,7 +9047,7 @@
       <c r="K346" s="6"/>
       <c r="L346" s="6"/>
     </row>
-    <row r="347" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="347" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -9029,7 +9061,7 @@
       <c r="K347" s="6"/>
       <c r="L347" s="6"/>
     </row>
-    <row r="348" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="348" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -9043,7 +9075,7 @@
       <c r="K348" s="6"/>
       <c r="L348" s="6"/>
     </row>
-    <row r="349" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="349" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -9057,7 +9089,7 @@
       <c r="K349" s="6"/>
       <c r="L349" s="6"/>
     </row>
-    <row r="350" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="350" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -9071,7 +9103,7 @@
       <c r="K350" s="6"/>
       <c r="L350" s="6"/>
     </row>
-    <row r="351" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="351" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -9085,7 +9117,7 @@
       <c r="K351" s="6"/>
       <c r="L351" s="6"/>
     </row>
-    <row r="352" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="352" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -9099,7 +9131,7 @@
       <c r="K352" s="6"/>
       <c r="L352" s="6"/>
     </row>
-    <row r="353" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="353" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -9113,7 +9145,7 @@
       <c r="K353" s="6"/>
       <c r="L353" s="6"/>
     </row>
-    <row r="354" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="354" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -9127,7 +9159,7 @@
       <c r="K354" s="6"/>
       <c r="L354" s="6"/>
     </row>
-    <row r="355" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="355" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -9141,7 +9173,7 @@
       <c r="K355" s="6"/>
       <c r="L355" s="6"/>
     </row>
-    <row r="356" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="356" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -9155,7 +9187,7 @@
       <c r="K356" s="6"/>
       <c r="L356" s="6"/>
     </row>
-    <row r="357" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="357" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -9169,7 +9201,7 @@
       <c r="K357" s="6"/>
       <c r="L357" s="6"/>
     </row>
-    <row r="358" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="358" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -9183,7 +9215,7 @@
       <c r="K358" s="6"/>
       <c r="L358" s="6"/>
     </row>
-    <row r="359" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="359" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -9197,7 +9229,7 @@
       <c r="K359" s="6"/>
       <c r="L359" s="6"/>
     </row>
-    <row r="360" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="360" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -9211,7 +9243,7 @@
       <c r="K360" s="6"/>
       <c r="L360" s="6"/>
     </row>
-    <row r="361" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="361" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -9225,7 +9257,7 @@
       <c r="K361" s="6"/>
       <c r="L361" s="6"/>
     </row>
-    <row r="362" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="362" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -9239,7 +9271,7 @@
       <c r="K362" s="6"/>
       <c r="L362" s="6"/>
     </row>
-    <row r="363" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="363" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -9253,7 +9285,7 @@
       <c r="K363" s="6"/>
       <c r="L363" s="6"/>
     </row>
-    <row r="364" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="364" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -9267,7 +9299,7 @@
       <c r="K364" s="6"/>
       <c r="L364" s="6"/>
     </row>
-    <row r="365" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="365" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -9281,7 +9313,7 @@
       <c r="K365" s="6"/>
       <c r="L365" s="6"/>
     </row>
-    <row r="366" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="366" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -9295,7 +9327,7 @@
       <c r="K366" s="6"/>
       <c r="L366" s="6"/>
     </row>
-    <row r="367" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="367" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -9309,7 +9341,7 @@
       <c r="K367" s="6"/>
       <c r="L367" s="6"/>
     </row>
-    <row r="368" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="368" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -9323,7 +9355,7 @@
       <c r="K368" s="6"/>
       <c r="L368" s="6"/>
     </row>
-    <row r="369" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="369" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -9337,7 +9369,7 @@
       <c r="K369" s="6"/>
       <c r="L369" s="6"/>
     </row>
-    <row r="370" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="370" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -9351,7 +9383,7 @@
       <c r="K370" s="6"/>
       <c r="L370" s="6"/>
     </row>
-    <row r="371" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="371" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -9365,7 +9397,7 @@
       <c r="K371" s="6"/>
       <c r="L371" s="6"/>
     </row>
-    <row r="372" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="372" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -9379,7 +9411,7 @@
       <c r="K372" s="6"/>
       <c r="L372" s="6"/>
     </row>
-    <row r="373" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="373" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -9393,7 +9425,7 @@
       <c r="K373" s="6"/>
       <c r="L373" s="6"/>
     </row>
-    <row r="374" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="374" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -9407,7 +9439,7 @@
       <c r="K374" s="6"/>
       <c r="L374" s="6"/>
     </row>
-    <row r="375" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="375" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -9421,7 +9453,7 @@
       <c r="K375" s="6"/>
       <c r="L375" s="6"/>
     </row>
-    <row r="376" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="376" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -9435,7 +9467,7 @@
       <c r="K376" s="6"/>
       <c r="L376" s="6"/>
     </row>
-    <row r="377" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="377" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -9449,7 +9481,7 @@
       <c r="K377" s="6"/>
       <c r="L377" s="6"/>
     </row>
-    <row r="378" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="378" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -9463,7 +9495,7 @@
       <c r="K378" s="6"/>
       <c r="L378" s="6"/>
     </row>
-    <row r="379" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="379" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -9477,7 +9509,7 @@
       <c r="K379" s="6"/>
       <c r="L379" s="6"/>
     </row>
-    <row r="380" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="380" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -9491,7 +9523,7 @@
       <c r="K380" s="6"/>
       <c r="L380" s="6"/>
     </row>
-    <row r="381" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="381" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -9505,7 +9537,7 @@
       <c r="K381" s="6"/>
       <c r="L381" s="6"/>
     </row>
-    <row r="382" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="382" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -9519,7 +9551,7 @@
       <c r="K382" s="6"/>
       <c r="L382" s="6"/>
     </row>
-    <row r="383" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="383" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -9533,7 +9565,7 @@
       <c r="K383" s="6"/>
       <c r="L383" s="6"/>
     </row>
-    <row r="384" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="384" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -9547,7 +9579,7 @@
       <c r="K384" s="6"/>
       <c r="L384" s="6"/>
     </row>
-    <row r="385" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="385" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -9561,7 +9593,7 @@
       <c r="K385" s="6"/>
       <c r="L385" s="6"/>
     </row>
-    <row r="386" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="386" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -9575,7 +9607,7 @@
       <c r="K386" s="6"/>
       <c r="L386" s="6"/>
     </row>
-    <row r="387" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="387" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -9589,7 +9621,7 @@
       <c r="K387" s="6"/>
       <c r="L387" s="6"/>
     </row>
-    <row r="388" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="388" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -9603,7 +9635,7 @@
       <c r="K388" s="6"/>
       <c r="L388" s="6"/>
     </row>
-    <row r="389" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="389" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -9617,7 +9649,7 @@
       <c r="K389" s="6"/>
       <c r="L389" s="6"/>
     </row>
-    <row r="390" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="390" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -9631,7 +9663,7 @@
       <c r="K390" s="6"/>
       <c r="L390" s="6"/>
     </row>
-    <row r="391" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="391" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -9645,7 +9677,7 @@
       <c r="K391" s="6"/>
       <c r="L391" s="6"/>
     </row>
-    <row r="392" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="392" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -9659,7 +9691,7 @@
       <c r="K392" s="6"/>
       <c r="L392" s="6"/>
     </row>
-    <row r="393" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="393" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -9673,7 +9705,7 @@
       <c r="K393" s="6"/>
       <c r="L393" s="6"/>
     </row>
-    <row r="394" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="394" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -9687,7 +9719,7 @@
       <c r="K394" s="6"/>
       <c r="L394" s="6"/>
     </row>
-    <row r="395" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="395" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -9701,7 +9733,7 @@
       <c r="K395" s="6"/>
       <c r="L395" s="6"/>
     </row>
-    <row r="396" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="396" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -9715,7 +9747,7 @@
       <c r="K396" s="6"/>
       <c r="L396" s="6"/>
     </row>
-    <row r="397" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="397" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -9729,7 +9761,7 @@
       <c r="K397" s="6"/>
       <c r="L397" s="6"/>
     </row>
-    <row r="398" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="398" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -9743,7 +9775,7 @@
       <c r="K398" s="6"/>
       <c r="L398" s="6"/>
     </row>
-    <row r="399" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="399" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -9757,7 +9789,7 @@
       <c r="K399" s="6"/>
       <c r="L399" s="6"/>
     </row>
-    <row r="400" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="400" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -9771,7 +9803,7 @@
       <c r="K400" s="6"/>
       <c r="L400" s="6"/>
     </row>
-    <row r="401" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="401" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -9785,7 +9817,7 @@
       <c r="K401" s="6"/>
       <c r="L401" s="6"/>
     </row>
-    <row r="402" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="402" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -9799,7 +9831,7 @@
       <c r="K402" s="6"/>
       <c r="L402" s="6"/>
     </row>
-    <row r="403" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="403" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -9813,7 +9845,7 @@
       <c r="K403" s="6"/>
       <c r="L403" s="6"/>
     </row>
-    <row r="404" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="404" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -9827,7 +9859,7 @@
       <c r="K404" s="6"/>
       <c r="L404" s="6"/>
     </row>
-    <row r="405" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="405" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -9841,7 +9873,7 @@
       <c r="K405" s="6"/>
       <c r="L405" s="6"/>
     </row>
-    <row r="406" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="406" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -9855,7 +9887,7 @@
       <c r="K406" s="6"/>
       <c r="L406" s="6"/>
     </row>
-    <row r="407" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="407" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -9869,7 +9901,7 @@
       <c r="K407" s="6"/>
       <c r="L407" s="6"/>
     </row>
-    <row r="408" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="408" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -9883,7 +9915,7 @@
       <c r="K408" s="6"/>
       <c r="L408" s="6"/>
     </row>
-    <row r="409" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="409" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -9897,7 +9929,7 @@
       <c r="K409" s="6"/>
       <c r="L409" s="6"/>
     </row>
-    <row r="410" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="410" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -9911,7 +9943,7 @@
       <c r="K410" s="6"/>
       <c r="L410" s="6"/>
     </row>
-    <row r="411" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="411" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -9925,7 +9957,7 @@
       <c r="K411" s="6"/>
       <c r="L411" s="6"/>
     </row>
-    <row r="412" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="412" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -9939,7 +9971,7 @@
       <c r="K412" s="6"/>
       <c r="L412" s="6"/>
     </row>
-    <row r="413" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="413" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -9953,7 +9985,7 @@
       <c r="K413" s="6"/>
       <c r="L413" s="6"/>
     </row>
-    <row r="414" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="414" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -9967,7 +9999,7 @@
       <c r="K414" s="6"/>
       <c r="L414" s="6"/>
     </row>
-    <row r="415" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="415" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -9981,7 +10013,7 @@
       <c r="K415" s="6"/>
       <c r="L415" s="6"/>
     </row>
-    <row r="416" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="416" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -9995,7 +10027,7 @@
       <c r="K416" s="6"/>
       <c r="L416" s="6"/>
     </row>
-    <row r="417" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="417" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -10009,7 +10041,7 @@
       <c r="K417" s="6"/>
       <c r="L417" s="6"/>
     </row>
-    <row r="418" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="418" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -10023,7 +10055,7 @@
       <c r="K418" s="6"/>
       <c r="L418" s="6"/>
     </row>
-    <row r="419" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="419" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -10037,7 +10069,7 @@
       <c r="K419" s="6"/>
       <c r="L419" s="6"/>
     </row>
-    <row r="420" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="420" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -10051,7 +10083,7 @@
       <c r="K420" s="6"/>
       <c r="L420" s="6"/>
     </row>
-    <row r="421" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="421" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -10065,7 +10097,7 @@
       <c r="K421" s="6"/>
       <c r="L421" s="6"/>
     </row>
-    <row r="422" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="422" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -10079,7 +10111,7 @@
       <c r="K422" s="6"/>
       <c r="L422" s="6"/>
     </row>
-    <row r="423" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="423" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -10093,7 +10125,7 @@
       <c r="K423" s="6"/>
       <c r="L423" s="6"/>
     </row>
-    <row r="424" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="424" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -10107,7 +10139,7 @@
       <c r="K424" s="6"/>
       <c r="L424" s="6"/>
     </row>
-    <row r="425" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="425" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -10121,7 +10153,7 @@
       <c r="K425" s="6"/>
       <c r="L425" s="6"/>
     </row>
-    <row r="426" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="426" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -10135,7 +10167,7 @@
       <c r="K426" s="6"/>
       <c r="L426" s="6"/>
     </row>
-    <row r="427" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="427" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -10149,7 +10181,7 @@
       <c r="K427" s="6"/>
       <c r="L427" s="6"/>
     </row>
-    <row r="428" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="428" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -10163,7 +10195,7 @@
       <c r="K428" s="6"/>
       <c r="L428" s="6"/>
     </row>
-    <row r="429" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="429" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -10177,7 +10209,7 @@
       <c r="K429" s="6"/>
       <c r="L429" s="6"/>
     </row>
-    <row r="430" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="430" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -10191,7 +10223,7 @@
       <c r="K430" s="6"/>
       <c r="L430" s="6"/>
     </row>
-    <row r="431" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="431" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -10205,7 +10237,7 @@
       <c r="K431" s="6"/>
       <c r="L431" s="6"/>
     </row>
-    <row r="432" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="432" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -10219,7 +10251,7 @@
       <c r="K432" s="6"/>
       <c r="L432" s="6"/>
     </row>
-    <row r="433" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="433" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -10233,7 +10265,7 @@
       <c r="K433" s="6"/>
       <c r="L433" s="6"/>
     </row>
-    <row r="434" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="434" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -10247,7 +10279,7 @@
       <c r="K434" s="6"/>
       <c r="L434" s="6"/>
     </row>
-    <row r="435" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="435" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -10261,7 +10293,7 @@
       <c r="K435" s="6"/>
       <c r="L435" s="6"/>
     </row>
-    <row r="436" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="436" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -10275,7 +10307,7 @@
       <c r="K436" s="6"/>
       <c r="L436" s="6"/>
     </row>
-    <row r="437" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="437" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -10289,7 +10321,7 @@
       <c r="K437" s="6"/>
       <c r="L437" s="6"/>
     </row>
-    <row r="438" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="438" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -10303,7 +10335,7 @@
       <c r="K438" s="6"/>
       <c r="L438" s="6"/>
     </row>
-    <row r="439" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="439" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -10317,7 +10349,7 @@
       <c r="K439" s="6"/>
       <c r="L439" s="6"/>
     </row>
-    <row r="440" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="440" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -10331,7 +10363,7 @@
       <c r="K440" s="6"/>
       <c r="L440" s="6"/>
     </row>
-    <row r="441" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="441" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -10345,7 +10377,7 @@
       <c r="K441" s="6"/>
       <c r="L441" s="6"/>
     </row>
-    <row r="442" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="442" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -10359,7 +10391,7 @@
       <c r="K442" s="6"/>
       <c r="L442" s="6"/>
     </row>
-    <row r="443" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="443" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -10373,7 +10405,7 @@
       <c r="K443" s="6"/>
       <c r="L443" s="6"/>
     </row>
-    <row r="444" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="444" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -10387,7 +10419,7 @@
       <c r="K444" s="6"/>
       <c r="L444" s="6"/>
     </row>
-    <row r="445" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="445" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -10401,7 +10433,7 @@
       <c r="K445" s="6"/>
       <c r="L445" s="6"/>
     </row>
-    <row r="446" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="446" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -10415,7 +10447,7 @@
       <c r="K446" s="6"/>
       <c r="L446" s="6"/>
     </row>
-    <row r="447" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="447" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -10429,7 +10461,7 @@
       <c r="K447" s="6"/>
       <c r="L447" s="6"/>
     </row>
-    <row r="448" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="448" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="5"/>
       <c r="B448" s="5"/>
       <c r="C448" s="5"/>
@@ -10443,7 +10475,7 @@
       <c r="K448" s="6"/>
       <c r="L448" s="6"/>
     </row>
-    <row r="449" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="449" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="5"/>
       <c r="B449" s="5"/>
       <c r="C449" s="5"/>
@@ -10457,7 +10489,7 @@
       <c r="K449" s="6"/>
       <c r="L449" s="6"/>
     </row>
-    <row r="450" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="450" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="5"/>
       <c r="B450" s="5"/>
       <c r="C450" s="5"/>
@@ -10471,7 +10503,7 @@
       <c r="K450" s="6"/>
       <c r="L450" s="6"/>
     </row>
-    <row r="451" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="451" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="5"/>
       <c r="B451" s="5"/>
       <c r="C451" s="5"/>
@@ -10485,7 +10517,7 @@
       <c r="K451" s="6"/>
       <c r="L451" s="6"/>
     </row>
-    <row r="452" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="452" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="5"/>
       <c r="B452" s="5"/>
       <c r="C452" s="5"/>
@@ -10499,7 +10531,7 @@
       <c r="K452" s="6"/>
       <c r="L452" s="6"/>
     </row>
-    <row r="453" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="453" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="5"/>
       <c r="B453" s="5"/>
       <c r="C453" s="5"/>
@@ -10513,7 +10545,7 @@
       <c r="K453" s="6"/>
       <c r="L453" s="6"/>
     </row>
-    <row r="454" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="454" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="5"/>
       <c r="B454" s="5"/>
       <c r="C454" s="5"/>
@@ -10527,7 +10559,7 @@
       <c r="K454" s="6"/>
       <c r="L454" s="6"/>
     </row>
-    <row r="455" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="455" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="5"/>
       <c r="B455" s="5"/>
       <c r="C455" s="5"/>
@@ -10541,7 +10573,7 @@
       <c r="K455" s="6"/>
       <c r="L455" s="6"/>
     </row>
-    <row r="456" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="456" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="5"/>
       <c r="B456" s="5"/>
       <c r="C456" s="5"/>
@@ -10555,7 +10587,7 @@
       <c r="K456" s="6"/>
       <c r="L456" s="6"/>
     </row>
-    <row r="457" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="457" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="5"/>
       <c r="B457" s="5"/>
       <c r="C457" s="5"/>
@@ -10569,7 +10601,7 @@
       <c r="K457" s="6"/>
       <c r="L457" s="6"/>
     </row>
-    <row r="458" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="458" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="5"/>
       <c r="B458" s="5"/>
       <c r="C458" s="5"/>
@@ -10583,7 +10615,7 @@
       <c r="K458" s="6"/>
       <c r="L458" s="6"/>
     </row>
-    <row r="459" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="459" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="5"/>
       <c r="B459" s="5"/>
       <c r="C459" s="5"/>
@@ -10597,7 +10629,7 @@
       <c r="K459" s="6"/>
       <c r="L459" s="6"/>
     </row>
-    <row r="460" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="460" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="5"/>
       <c r="B460" s="5"/>
       <c r="C460" s="5"/>
@@ -10611,7 +10643,7 @@
       <c r="K460" s="6"/>
       <c r="L460" s="6"/>
     </row>
-    <row r="461" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="461" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="5"/>
       <c r="B461" s="5"/>
       <c r="C461" s="5"/>
@@ -10625,7 +10657,7 @@
       <c r="K461" s="6"/>
       <c r="L461" s="6"/>
     </row>
-    <row r="462" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="462" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="5"/>
       <c r="B462" s="5"/>
       <c r="C462" s="5"/>
@@ -10639,7 +10671,7 @@
       <c r="K462" s="6"/>
       <c r="L462" s="6"/>
     </row>
-    <row r="463" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="463" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="5"/>
       <c r="B463" s="5"/>
       <c r="C463" s="5"/>
@@ -10653,7 +10685,7 @@
       <c r="K463" s="6"/>
       <c r="L463" s="6"/>
     </row>
-    <row r="464" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="464" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="5"/>
       <c r="B464" s="5"/>
       <c r="C464" s="5"/>
@@ -10667,7 +10699,7 @@
       <c r="K464" s="6"/>
       <c r="L464" s="6"/>
     </row>
-    <row r="465" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="465" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="5"/>
       <c r="B465" s="5"/>
       <c r="C465" s="5"/>
@@ -10681,7 +10713,7 @@
       <c r="K465" s="6"/>
       <c r="L465" s="6"/>
     </row>
-    <row r="466" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="466" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="5"/>
       <c r="B466" s="5"/>
       <c r="C466" s="5"/>
@@ -10695,7 +10727,7 @@
       <c r="K466" s="6"/>
       <c r="L466" s="6"/>
     </row>
-    <row r="467" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="467" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="5"/>
       <c r="B467" s="5"/>
       <c r="C467" s="5"/>
@@ -10709,7 +10741,7 @@
       <c r="K467" s="6"/>
       <c r="L467" s="6"/>
     </row>
-    <row r="468" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="468" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="5"/>
       <c r="B468" s="5"/>
       <c r="C468" s="5"/>
@@ -10723,7 +10755,7 @@
       <c r="K468" s="6"/>
       <c r="L468" s="6"/>
     </row>
-    <row r="469" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="469" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="5"/>
       <c r="B469" s="5"/>
       <c r="C469" s="5"/>
@@ -10737,7 +10769,7 @@
       <c r="K469" s="6"/>
       <c r="L469" s="6"/>
     </row>
-    <row r="470" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="470" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="5"/>
       <c r="B470" s="5"/>
       <c r="C470" s="5"/>
@@ -10751,7 +10783,7 @@
       <c r="K470" s="6"/>
       <c r="L470" s="6"/>
     </row>
-    <row r="471" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="471" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="5"/>
       <c r="B471" s="5"/>
       <c r="C471" s="5"/>
@@ -10765,7 +10797,7 @@
       <c r="K471" s="6"/>
       <c r="L471" s="6"/>
     </row>
-    <row r="472" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="472" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="5"/>
       <c r="B472" s="5"/>
       <c r="C472" s="5"/>
@@ -10779,7 +10811,7 @@
       <c r="K472" s="6"/>
       <c r="L472" s="6"/>
     </row>
-    <row r="473" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="473" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="5"/>
       <c r="B473" s="5"/>
       <c r="C473" s="5"/>
@@ -10793,7 +10825,7 @@
       <c r="K473" s="6"/>
       <c r="L473" s="6"/>
     </row>
-    <row r="474" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="474" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="5"/>
       <c r="B474" s="5"/>
       <c r="C474" s="5"/>
@@ -10807,7 +10839,7 @@
       <c r="K474" s="6"/>
       <c r="L474" s="6"/>
     </row>
-    <row r="475" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="475" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="5"/>
       <c r="B475" s="5"/>
       <c r="C475" s="5"/>
@@ -10821,7 +10853,7 @@
       <c r="K475" s="6"/>
       <c r="L475" s="6"/>
     </row>
-    <row r="476" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="476" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="5"/>
       <c r="B476" s="5"/>
       <c r="C476" s="5"/>
@@ -10835,7 +10867,7 @@
       <c r="K476" s="6"/>
       <c r="L476" s="6"/>
     </row>
-    <row r="477" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="477" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="5"/>
       <c r="B477" s="5"/>
       <c r="C477" s="5"/>
@@ -10849,7 +10881,7 @@
       <c r="K477" s="6"/>
       <c r="L477" s="6"/>
     </row>
-    <row r="478" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="478" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="5"/>
       <c r="B478" s="5"/>
       <c r="C478" s="5"/>
@@ -10863,7 +10895,7 @@
       <c r="K478" s="6"/>
       <c r="L478" s="6"/>
     </row>
-    <row r="479" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="479" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="5"/>
       <c r="B479" s="5"/>
       <c r="C479" s="5"/>
@@ -10877,7 +10909,7 @@
       <c r="K479" s="6"/>
       <c r="L479" s="6"/>
     </row>
-    <row r="480" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="480" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="5"/>
       <c r="B480" s="5"/>
       <c r="C480" s="5"/>
@@ -10891,7 +10923,7 @@
       <c r="K480" s="6"/>
       <c r="L480" s="6"/>
     </row>
-    <row r="481" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="481" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="5"/>
       <c r="B481" s="5"/>
       <c r="C481" s="5"/>
@@ -10905,7 +10937,7 @@
       <c r="K481" s="6"/>
       <c r="L481" s="6"/>
     </row>
-    <row r="482" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="482" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="5"/>
       <c r="B482" s="5"/>
       <c r="C482" s="5"/>
@@ -10919,7 +10951,7 @@
       <c r="K482" s="6"/>
       <c r="L482" s="6"/>
     </row>
-    <row r="483" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="483" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="5"/>
       <c r="B483" s="5"/>
       <c r="C483" s="5"/>
@@ -10933,7 +10965,7 @@
       <c r="K483" s="6"/>
       <c r="L483" s="6"/>
     </row>
-    <row r="484" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="484" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="5"/>
       <c r="B484" s="5"/>
       <c r="C484" s="5"/>
@@ -10947,7 +10979,7 @@
       <c r="K484" s="6"/>
       <c r="L484" s="6"/>
     </row>
-    <row r="485" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="485" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="5"/>
       <c r="B485" s="5"/>
       <c r="C485" s="5"/>
@@ -10961,7 +10993,7 @@
       <c r="K485" s="6"/>
       <c r="L485" s="6"/>
     </row>
-    <row r="486" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="486" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="5"/>
       <c r="B486" s="5"/>
       <c r="C486" s="5"/>
@@ -10975,7 +11007,7 @@
       <c r="K486" s="6"/>
       <c r="L486" s="6"/>
     </row>
-    <row r="487" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="487" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="5"/>
       <c r="B487" s="5"/>
       <c r="C487" s="5"/>
@@ -10989,7 +11021,7 @@
       <c r="K487" s="6"/>
       <c r="L487" s="6"/>
     </row>
-    <row r="488" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="488" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="5"/>
       <c r="B488" s="5"/>
       <c r="C488" s="5"/>
@@ -11003,7 +11035,7 @@
       <c r="K488" s="6"/>
       <c r="L488" s="6"/>
     </row>
-    <row r="489" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="489" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="5"/>
       <c r="B489" s="5"/>
       <c r="C489" s="5"/>
@@ -11017,7 +11049,7 @@
       <c r="K489" s="6"/>
       <c r="L489" s="6"/>
     </row>
-    <row r="490" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="490" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="5"/>
       <c r="B490" s="5"/>
       <c r="C490" s="5"/>
@@ -11031,7 +11063,7 @@
       <c r="K490" s="6"/>
       <c r="L490" s="6"/>
     </row>
-    <row r="491" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="491" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="5"/>
       <c r="B491" s="5"/>
       <c r="C491" s="5"/>
@@ -11045,7 +11077,7 @@
       <c r="K491" s="6"/>
       <c r="L491" s="6"/>
     </row>
-    <row r="492" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="492" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="5"/>
       <c r="B492" s="5"/>
       <c r="C492" s="5"/>
@@ -11059,7 +11091,7 @@
       <c r="K492" s="6"/>
       <c r="L492" s="6"/>
     </row>
-    <row r="493" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="493" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="5"/>
       <c r="B493" s="5"/>
       <c r="C493" s="5"/>
@@ -11073,7 +11105,7 @@
       <c r="K493" s="6"/>
       <c r="L493" s="6"/>
     </row>
-    <row r="494" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="494" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="5"/>
       <c r="B494" s="5"/>
       <c r="C494" s="5"/>
@@ -11087,7 +11119,7 @@
       <c r="K494" s="6"/>
       <c r="L494" s="6"/>
     </row>
-    <row r="495" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="495" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="5"/>
       <c r="B495" s="5"/>
       <c r="C495" s="5"/>
@@ -11101,7 +11133,7 @@
       <c r="K495" s="6"/>
       <c r="L495" s="6"/>
     </row>
-    <row r="496" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="496" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="5"/>
       <c r="B496" s="5"/>
       <c r="C496" s="5"/>
@@ -11115,7 +11147,7 @@
       <c r="K496" s="6"/>
       <c r="L496" s="6"/>
     </row>
-    <row r="497" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="497" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="5"/>
       <c r="B497" s="5"/>
       <c r="C497" s="5"/>
@@ -11129,7 +11161,7 @@
       <c r="K497" s="6"/>
       <c r="L497" s="6"/>
     </row>
-    <row r="498" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="498" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="5"/>
       <c r="B498" s="5"/>
       <c r="C498" s="5"/>
@@ -11143,7 +11175,7 @@
       <c r="K498" s="6"/>
       <c r="L498" s="6"/>
     </row>
-    <row r="499" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="499" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="5"/>
       <c r="B499" s="5"/>
       <c r="C499" s="5"/>
@@ -11157,7 +11189,7 @@
       <c r="K499" s="6"/>
       <c r="L499" s="6"/>
     </row>
-    <row r="500" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="500" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="5"/>
       <c r="B500" s="5"/>
       <c r="C500" s="5"/>
@@ -11171,7 +11203,7 @@
       <c r="K500" s="6"/>
       <c r="L500" s="6"/>
     </row>
-    <row r="501" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="501" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="5"/>
       <c r="B501" s="5"/>
       <c r="C501" s="5"/>
@@ -11185,7 +11217,7 @@
       <c r="K501" s="6"/>
       <c r="L501" s="6"/>
     </row>
-    <row r="502" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="502" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="5"/>
       <c r="B502" s="5"/>
       <c r="C502" s="5"/>
@@ -11199,7 +11231,7 @@
       <c r="K502" s="6"/>
       <c r="L502" s="6"/>
     </row>
-    <row r="503" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="503" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="5"/>
       <c r="B503" s="5"/>
       <c r="C503" s="5"/>
@@ -11213,7 +11245,7 @@
       <c r="K503" s="6"/>
       <c r="L503" s="6"/>
     </row>
-    <row r="504" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="504" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="5"/>
       <c r="B504" s="5"/>
       <c r="C504" s="5"/>
@@ -11227,7 +11259,7 @@
       <c r="K504" s="6"/>
       <c r="L504" s="6"/>
     </row>
-    <row r="505" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="505" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="5"/>
       <c r="B505" s="5"/>
       <c r="C505" s="5"/>
@@ -11241,7 +11273,7 @@
       <c r="K505" s="6"/>
       <c r="L505" s="6"/>
     </row>
-    <row r="506" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="506" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="5"/>
       <c r="B506" s="5"/>
       <c r="C506" s="5"/>
@@ -11255,7 +11287,7 @@
       <c r="K506" s="6"/>
       <c r="L506" s="6"/>
     </row>
-    <row r="507" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="507" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="5"/>
       <c r="B507" s="5"/>
       <c r="C507" s="5"/>
@@ -11269,7 +11301,7 @@
       <c r="K507" s="6"/>
       <c r="L507" s="6"/>
     </row>
-    <row r="508" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="508" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="5"/>
       <c r="B508" s="5"/>
       <c r="C508" s="5"/>
@@ -11283,7 +11315,7 @@
       <c r="K508" s="6"/>
       <c r="L508" s="6"/>
     </row>
-    <row r="509" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="509" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="5"/>
       <c r="B509" s="5"/>
       <c r="C509" s="5"/>
@@ -11297,7 +11329,7 @@
       <c r="K509" s="6"/>
       <c r="L509" s="6"/>
     </row>
-    <row r="510" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="510" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="5"/>
       <c r="B510" s="5"/>
       <c r="C510" s="5"/>
@@ -11311,7 +11343,7 @@
       <c r="K510" s="6"/>
       <c r="L510" s="6"/>
     </row>
-    <row r="511" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="511" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="5"/>
       <c r="B511" s="5"/>
       <c r="C511" s="5"/>
@@ -11325,7 +11357,7 @@
       <c r="K511" s="6"/>
       <c r="L511" s="6"/>
     </row>
-    <row r="512" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="512" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="5"/>
       <c r="B512" s="5"/>
       <c r="C512" s="5"/>
@@ -11339,7 +11371,7 @@
       <c r="K512" s="6"/>
       <c r="L512" s="6"/>
     </row>
-    <row r="513" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="513" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="5"/>
       <c r="B513" s="5"/>
       <c r="C513" s="5"/>
@@ -11353,7 +11385,7 @@
       <c r="K513" s="6"/>
       <c r="L513" s="6"/>
     </row>
-    <row r="514" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="514" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="5"/>
       <c r="B514" s="5"/>
       <c r="C514" s="5"/>
@@ -11367,7 +11399,7 @@
       <c r="K514" s="6"/>
       <c r="L514" s="6"/>
     </row>
-    <row r="515" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="515" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="5"/>
       <c r="B515" s="5"/>
       <c r="C515" s="5"/>
@@ -11381,7 +11413,7 @@
       <c r="K515" s="6"/>
       <c r="L515" s="6"/>
     </row>
-    <row r="516" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="516" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="5"/>
       <c r="B516" s="5"/>
       <c r="C516" s="5"/>
@@ -11395,7 +11427,7 @@
       <c r="K516" s="6"/>
       <c r="L516" s="6"/>
     </row>
-    <row r="517" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="517" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="5"/>
       <c r="B517" s="5"/>
       <c r="C517" s="5"/>
@@ -11409,7 +11441,7 @@
       <c r="K517" s="6"/>
       <c r="L517" s="6"/>
     </row>
-    <row r="518" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="518" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="5"/>
       <c r="B518" s="5"/>
       <c r="C518" s="5"/>
@@ -11423,7 +11455,7 @@
       <c r="K518" s="6"/>
       <c r="L518" s="6"/>
     </row>
-    <row r="519" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="519" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="5"/>
       <c r="B519" s="5"/>
       <c r="C519" s="5"/>
@@ -11437,7 +11469,7 @@
       <c r="K519" s="6"/>
       <c r="L519" s="6"/>
     </row>
-    <row r="520" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="520" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="5"/>
       <c r="B520" s="5"/>
       <c r="C520" s="5"/>
@@ -11451,7 +11483,7 @@
       <c r="K520" s="6"/>
       <c r="L520" s="6"/>
     </row>
-    <row r="521" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="521" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="5"/>
       <c r="B521" s="5"/>
       <c r="C521" s="5"/>
@@ -11465,7 +11497,7 @@
       <c r="K521" s="6"/>
       <c r="L521" s="6"/>
     </row>
-    <row r="522" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="522" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="5"/>
       <c r="B522" s="5"/>
       <c r="C522" s="5"/>
@@ -11479,7 +11511,7 @@
       <c r="K522" s="6"/>
       <c r="L522" s="6"/>
     </row>
-    <row r="523" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="523" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="5"/>
       <c r="B523" s="5"/>
       <c r="C523" s="5"/>
@@ -11493,7 +11525,7 @@
       <c r="K523" s="6"/>
       <c r="L523" s="6"/>
     </row>
-    <row r="524" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="524" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="5"/>
       <c r="B524" s="5"/>
       <c r="C524" s="5"/>
@@ -11507,7 +11539,7 @@
       <c r="K524" s="6"/>
       <c r="L524" s="6"/>
     </row>
-    <row r="525" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="525" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="5"/>
       <c r="B525" s="5"/>
       <c r="C525" s="5"/>
@@ -11521,7 +11553,7 @@
       <c r="K525" s="6"/>
       <c r="L525" s="6"/>
     </row>
-    <row r="526" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="526" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="5"/>
       <c r="B526" s="5"/>
       <c r="C526" s="5"/>
@@ -11535,7 +11567,7 @@
       <c r="K526" s="6"/>
       <c r="L526" s="6"/>
     </row>
-    <row r="527" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="527" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="5"/>
       <c r="B527" s="5"/>
       <c r="C527" s="5"/>
@@ -11549,7 +11581,7 @@
       <c r="K527" s="6"/>
       <c r="L527" s="6"/>
     </row>
-    <row r="528" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="528" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="5"/>
       <c r="B528" s="5"/>
       <c r="C528" s="5"/>
@@ -11563,7 +11595,7 @@
       <c r="K528" s="6"/>
       <c r="L528" s="6"/>
     </row>
-    <row r="529" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="529" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="5"/>
       <c r="B529" s="5"/>
       <c r="C529" s="5"/>
@@ -11577,7 +11609,7 @@
       <c r="K529" s="6"/>
       <c r="L529" s="6"/>
     </row>
-    <row r="530" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="530" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="5"/>
       <c r="B530" s="5"/>
       <c r="C530" s="5"/>
@@ -11591,7 +11623,7 @@
       <c r="K530" s="6"/>
       <c r="L530" s="6"/>
     </row>
-    <row r="531" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="531" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="5"/>
       <c r="B531" s="5"/>
       <c r="C531" s="5"/>
@@ -11605,7 +11637,7 @@
       <c r="K531" s="6"/>
       <c r="L531" s="6"/>
     </row>
-    <row r="532" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="532" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="5"/>
       <c r="B532" s="5"/>
       <c r="C532" s="5"/>
@@ -11619,7 +11651,7 @@
       <c r="K532" s="6"/>
       <c r="L532" s="6"/>
     </row>
-    <row r="533" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="533" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="5"/>
       <c r="B533" s="5"/>
       <c r="C533" s="5"/>
@@ -11633,7 +11665,7 @@
       <c r="K533" s="6"/>
       <c r="L533" s="6"/>
     </row>
-    <row r="534" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="534" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="5"/>
       <c r="B534" s="5"/>
       <c r="C534" s="5"/>
@@ -11647,7 +11679,7 @@
       <c r="K534" s="6"/>
       <c r="L534" s="6"/>
     </row>
-    <row r="535" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="535" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="5"/>
       <c r="B535" s="5"/>
       <c r="C535" s="5"/>
@@ -11661,7 +11693,7 @@
       <c r="K535" s="6"/>
       <c r="L535" s="6"/>
     </row>
-    <row r="536" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="536" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="5"/>
       <c r="B536" s="5"/>
       <c r="C536" s="5"/>
@@ -11675,7 +11707,7 @@
       <c r="K536" s="6"/>
       <c r="L536" s="6"/>
     </row>
-    <row r="537" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="537" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="5"/>
       <c r="B537" s="5"/>
       <c r="C537" s="5"/>
@@ -11689,7 +11721,7 @@
       <c r="K537" s="6"/>
       <c r="L537" s="6"/>
     </row>
-    <row r="538" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="538" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="5"/>
       <c r="B538" s="5"/>
       <c r="C538" s="5"/>
@@ -11703,7 +11735,7 @@
       <c r="K538" s="6"/>
       <c r="L538" s="6"/>
     </row>
-    <row r="539" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="539" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="5"/>
       <c r="B539" s="5"/>
       <c r="C539" s="5"/>
@@ -11717,7 +11749,7 @@
       <c r="K539" s="6"/>
       <c r="L539" s="6"/>
     </row>
-    <row r="540" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="540" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="5"/>
       <c r="B540" s="5"/>
       <c r="C540" s="5"/>
@@ -11731,7 +11763,7 @@
       <c r="K540" s="6"/>
       <c r="L540" s="6"/>
     </row>
-    <row r="541" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="541" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="5"/>
       <c r="B541" s="5"/>
       <c r="C541" s="5"/>
@@ -11745,7 +11777,7 @@
       <c r="K541" s="6"/>
       <c r="L541" s="6"/>
     </row>
-    <row r="542" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="542" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="5"/>
       <c r="B542" s="5"/>
       <c r="C542" s="5"/>
@@ -11759,7 +11791,7 @@
       <c r="K542" s="6"/>
       <c r="L542" s="6"/>
     </row>
-    <row r="543" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="543" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="5"/>
       <c r="B543" s="5"/>
       <c r="C543" s="5"/>
@@ -11773,7 +11805,7 @@
       <c r="K543" s="6"/>
       <c r="L543" s="6"/>
     </row>
-    <row r="544" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="544" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="5"/>
       <c r="B544" s="5"/>
       <c r="C544" s="5"/>
@@ -11787,7 +11819,7 @@
       <c r="K544" s="6"/>
       <c r="L544" s="6"/>
     </row>
-    <row r="545" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="545" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="5"/>
       <c r="B545" s="5"/>
       <c r="C545" s="5"/>
@@ -11801,7 +11833,7 @@
       <c r="K545" s="6"/>
       <c r="L545" s="6"/>
     </row>
-    <row r="546" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="546" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="5"/>
       <c r="B546" s="5"/>
       <c r="C546" s="5"/>
@@ -11815,7 +11847,7 @@
       <c r="K546" s="6"/>
       <c r="L546" s="6"/>
     </row>
-    <row r="547" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="547" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="5"/>
       <c r="B547" s="5"/>
       <c r="C547" s="5"/>
@@ -11829,7 +11861,7 @@
       <c r="K547" s="6"/>
       <c r="L547" s="6"/>
     </row>
-    <row r="548" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="548" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="5"/>
       <c r="B548" s="5"/>
       <c r="C548" s="5"/>
@@ -11843,7 +11875,7 @@
       <c r="K548" s="6"/>
       <c r="L548" s="6"/>
     </row>
-    <row r="549" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="549" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="5"/>
       <c r="B549" s="5"/>
       <c r="C549" s="5"/>
@@ -11857,7 +11889,7 @@
       <c r="K549" s="6"/>
       <c r="L549" s="6"/>
     </row>
-    <row r="550" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="550" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="5"/>
       <c r="B550" s="5"/>
       <c r="C550" s="5"/>
@@ -11871,7 +11903,7 @@
       <c r="K550" s="6"/>
       <c r="L550" s="6"/>
     </row>
-    <row r="551" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="551" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="5"/>
       <c r="B551" s="5"/>
       <c r="C551" s="5"/>
@@ -11885,7 +11917,7 @@
       <c r="K551" s="6"/>
       <c r="L551" s="6"/>
     </row>
-    <row r="552" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="552" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="5"/>
       <c r="B552" s="5"/>
       <c r="C552" s="5"/>
@@ -11899,7 +11931,7 @@
       <c r="K552" s="6"/>
       <c r="L552" s="6"/>
     </row>
-    <row r="553" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="553" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="5"/>
       <c r="B553" s="5"/>
       <c r="C553" s="5"/>
@@ -11913,7 +11945,7 @@
       <c r="K553" s="6"/>
       <c r="L553" s="6"/>
     </row>
-    <row r="554" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="554" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="5"/>
       <c r="B554" s="5"/>
       <c r="C554" s="5"/>
@@ -11927,7 +11959,7 @@
       <c r="K554" s="6"/>
       <c r="L554" s="6"/>
     </row>
-    <row r="555" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="555" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="5"/>
       <c r="B555" s="5"/>
       <c r="C555" s="5"/>
@@ -11941,7 +11973,7 @@
       <c r="K555" s="6"/>
       <c r="L555" s="6"/>
     </row>
-    <row r="556" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="556" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="5"/>
       <c r="B556" s="5"/>
       <c r="C556" s="5"/>
@@ -11955,7 +11987,7 @@
       <c r="K556" s="6"/>
       <c r="L556" s="6"/>
     </row>
-    <row r="557" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="557" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="5"/>
       <c r="B557" s="5"/>
       <c r="C557" s="5"/>
@@ -11969,7 +12001,7 @@
       <c r="K557" s="6"/>
       <c r="L557" s="6"/>
     </row>
-    <row r="558" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="558" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="5"/>
       <c r="B558" s="5"/>
       <c r="C558" s="5"/>
@@ -11983,7 +12015,7 @@
       <c r="K558" s="6"/>
       <c r="L558" s="6"/>
     </row>
-    <row r="559" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="559" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="5"/>
       <c r="B559" s="5"/>
       <c r="C559" s="5"/>
@@ -11997,7 +12029,7 @@
       <c r="K559" s="6"/>
       <c r="L559" s="6"/>
     </row>
-    <row r="560" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="560" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="5"/>
       <c r="B560" s="5"/>
       <c r="C560" s="5"/>
@@ -12011,7 +12043,7 @@
       <c r="K560" s="6"/>
       <c r="L560" s="6"/>
     </row>
-    <row r="561" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="561" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="5"/>
       <c r="B561" s="5"/>
       <c r="C561" s="5"/>
@@ -12025,7 +12057,7 @@
       <c r="K561" s="6"/>
       <c r="L561" s="6"/>
     </row>
-    <row r="562" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="562" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="5"/>
       <c r="B562" s="5"/>
       <c r="C562" s="5"/>
@@ -12039,7 +12071,7 @@
       <c r="K562" s="6"/>
       <c r="L562" s="6"/>
     </row>
-    <row r="563" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="563" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="5"/>
       <c r="B563" s="5"/>
       <c r="C563" s="5"/>
@@ -12053,7 +12085,7 @@
       <c r="K563" s="6"/>
       <c r="L563" s="6"/>
     </row>
-    <row r="564" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="564" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="5"/>
       <c r="B564" s="5"/>
       <c r="C564" s="5"/>
@@ -12067,7 +12099,7 @@
       <c r="K564" s="6"/>
       <c r="L564" s="6"/>
     </row>
-    <row r="565" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="565" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="5"/>
       <c r="B565" s="5"/>
       <c r="C565" s="5"/>
@@ -12081,7 +12113,7 @@
       <c r="K565" s="6"/>
       <c r="L565" s="6"/>
     </row>
-    <row r="566" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="566" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="5"/>
       <c r="B566" s="5"/>
       <c r="C566" s="5"/>
@@ -12095,7 +12127,7 @@
       <c r="K566" s="6"/>
       <c r="L566" s="6"/>
     </row>
-    <row r="567" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="567" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="5"/>
       <c r="B567" s="5"/>
       <c r="C567" s="5"/>
@@ -12109,7 +12141,7 @@
       <c r="K567" s="6"/>
       <c r="L567" s="6"/>
     </row>
-    <row r="568" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="568" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="5"/>
       <c r="B568" s="5"/>
       <c r="C568" s="5"/>
@@ -12123,7 +12155,7 @@
       <c r="K568" s="6"/>
       <c r="L568" s="6"/>
     </row>
-    <row r="569" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="569" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="5"/>
       <c r="B569" s="5"/>
       <c r="C569" s="5"/>
@@ -12137,7 +12169,7 @@
       <c r="K569" s="6"/>
       <c r="L569" s="6"/>
     </row>
-    <row r="570" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="570" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="5"/>
       <c r="B570" s="5"/>
       <c r="C570" s="5"/>
@@ -12151,7 +12183,7 @@
       <c r="K570" s="6"/>
       <c r="L570" s="6"/>
     </row>
-    <row r="571" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="571" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="5"/>
       <c r="B571" s="5"/>
       <c r="C571" s="5"/>
@@ -12165,7 +12197,7 @@
       <c r="K571" s="6"/>
       <c r="L571" s="6"/>
     </row>
-    <row r="572" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="572" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="5"/>
       <c r="B572" s="5"/>
       <c r="C572" s="5"/>
@@ -12179,7 +12211,7 @@
       <c r="K572" s="6"/>
       <c r="L572" s="6"/>
     </row>
-    <row r="573" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="573" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="5"/>
       <c r="B573" s="5"/>
       <c r="C573" s="5"/>
@@ -12193,7 +12225,7 @@
       <c r="K573" s="6"/>
       <c r="L573" s="6"/>
     </row>
-    <row r="574" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="574" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="5"/>
       <c r="B574" s="5"/>
       <c r="C574" s="5"/>
@@ -12207,7 +12239,7 @@
       <c r="K574" s="6"/>
       <c r="L574" s="6"/>
     </row>
-    <row r="575" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="575" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="5"/>
       <c r="B575" s="5"/>
       <c r="C575" s="5"/>
@@ -12221,7 +12253,7 @@
       <c r="K575" s="6"/>
       <c r="L575" s="6"/>
     </row>
-    <row r="576" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="576" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="5"/>
       <c r="B576" s="5"/>
       <c r="C576" s="5"/>
@@ -12235,7 +12267,7 @@
       <c r="K576" s="6"/>
       <c r="L576" s="6"/>
     </row>
-    <row r="577" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="577" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="5"/>
       <c r="B577" s="5"/>
       <c r="C577" s="5"/>
@@ -12249,7 +12281,7 @@
       <c r="K577" s="6"/>
       <c r="L577" s="6"/>
     </row>
-    <row r="578" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="578" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="5"/>
       <c r="B578" s="5"/>
       <c r="C578" s="5"/>
@@ -12263,7 +12295,7 @@
       <c r="K578" s="6"/>
       <c r="L578" s="6"/>
     </row>
-    <row r="579" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="579" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="5"/>
       <c r="B579" s="5"/>
       <c r="C579" s="5"/>
@@ -12277,7 +12309,7 @@
       <c r="K579" s="6"/>
       <c r="L579" s="6"/>
     </row>
-    <row r="580" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="580" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="5"/>
       <c r="B580" s="5"/>
       <c r="C580" s="5"/>
@@ -12291,7 +12323,7 @@
       <c r="K580" s="6"/>
       <c r="L580" s="6"/>
     </row>
-    <row r="581" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="581" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="5"/>
       <c r="B581" s="5"/>
       <c r="C581" s="5"/>
@@ -12305,7 +12337,7 @@
       <c r="K581" s="6"/>
       <c r="L581" s="6"/>
     </row>
-    <row r="582" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="582" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="5"/>
       <c r="B582" s="5"/>
       <c r="C582" s="5"/>
@@ -12319,7 +12351,7 @@
       <c r="K582" s="6"/>
       <c r="L582" s="6"/>
     </row>
-    <row r="583" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="583" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="5"/>
       <c r="B583" s="5"/>
       <c r="C583" s="5"/>
@@ -12333,7 +12365,7 @@
       <c r="K583" s="6"/>
       <c r="L583" s="6"/>
     </row>
-    <row r="584" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="584" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="5"/>
       <c r="B584" s="5"/>
       <c r="C584" s="5"/>
@@ -12347,7 +12379,7 @@
       <c r="K584" s="6"/>
       <c r="L584" s="6"/>
     </row>
-    <row r="585" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="585" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="5"/>
       <c r="B585" s="5"/>
       <c r="C585" s="5"/>
@@ -12361,7 +12393,7 @@
       <c r="K585" s="6"/>
       <c r="L585" s="6"/>
     </row>
-    <row r="586" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="586" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="5"/>
       <c r="B586" s="5"/>
       <c r="C586" s="5"/>
@@ -12375,7 +12407,7 @@
       <c r="K586" s="6"/>
       <c r="L586" s="6"/>
     </row>
-    <row r="587" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="587" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="5"/>
       <c r="B587" s="5"/>
       <c r="C587" s="5"/>
@@ -12389,7 +12421,7 @@
       <c r="K587" s="6"/>
       <c r="L587" s="6"/>
     </row>
-    <row r="588" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="588" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="5"/>
       <c r="B588" s="5"/>
       <c r="C588" s="5"/>
@@ -12403,7 +12435,7 @@
       <c r="K588" s="6"/>
       <c r="L588" s="6"/>
     </row>
-    <row r="589" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="589" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="5"/>
       <c r="B589" s="5"/>
       <c r="C589" s="5"/>
@@ -12417,7 +12449,7 @@
       <c r="K589" s="6"/>
       <c r="L589" s="6"/>
     </row>
-    <row r="590" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="590" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="5"/>
       <c r="B590" s="5"/>
       <c r="C590" s="5"/>
@@ -12431,7 +12463,7 @@
       <c r="K590" s="6"/>
       <c r="L590" s="6"/>
     </row>
-    <row r="591" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="591" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="5"/>
       <c r="B591" s="5"/>
       <c r="C591" s="5"/>
@@ -12445,7 +12477,7 @@
       <c r="K591" s="6"/>
       <c r="L591" s="6"/>
     </row>
-    <row r="592" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="592" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="5"/>
       <c r="B592" s="5"/>
       <c r="C592" s="5"/>
@@ -12459,7 +12491,7 @@
       <c r="K592" s="6"/>
       <c r="L592" s="6"/>
     </row>
-    <row r="593" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="593" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="5"/>
       <c r="B593" s="5"/>
       <c r="C593" s="5"/>
@@ -12473,7 +12505,7 @@
       <c r="K593" s="6"/>
       <c r="L593" s="6"/>
     </row>
-    <row r="594" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="594" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="5"/>
       <c r="B594" s="5"/>
       <c r="C594" s="5"/>
@@ -12487,7 +12519,7 @@
       <c r="K594" s="6"/>
       <c r="L594" s="6"/>
     </row>
-    <row r="595" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="595" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="5"/>
       <c r="B595" s="5"/>
       <c r="C595" s="5"/>
@@ -12501,7 +12533,7 @@
       <c r="K595" s="6"/>
       <c r="L595" s="6"/>
     </row>
-    <row r="596" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="596" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="5"/>
       <c r="B596" s="5"/>
       <c r="C596" s="5"/>
@@ -12515,7 +12547,7 @@
       <c r="K596" s="6"/>
       <c r="L596" s="6"/>
     </row>
-    <row r="597" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="597" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="5"/>
       <c r="B597" s="5"/>
       <c r="C597" s="5"/>
@@ -12529,7 +12561,7 @@
       <c r="K597" s="6"/>
       <c r="L597" s="6"/>
     </row>
-    <row r="598" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="598" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="5"/>
       <c r="B598" s="5"/>
       <c r="C598" s="5"/>
@@ -12543,7 +12575,7 @@
       <c r="K598" s="6"/>
       <c r="L598" s="6"/>
     </row>
-    <row r="599" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="599" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="5"/>
       <c r="B599" s="5"/>
       <c r="C599" s="5"/>
@@ -12557,7 +12589,7 @@
       <c r="K599" s="6"/>
       <c r="L599" s="6"/>
     </row>
-    <row r="600" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="600" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="5"/>
       <c r="B600" s="5"/>
       <c r="C600" s="5"/>
@@ -12571,7 +12603,7 @@
       <c r="K600" s="6"/>
       <c r="L600" s="6"/>
     </row>
-    <row r="601" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="601" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="5"/>
       <c r="B601" s="5"/>
       <c r="C601" s="5"/>
@@ -12585,7 +12617,7 @@
       <c r="K601" s="6"/>
       <c r="L601" s="6"/>
     </row>
-    <row r="602" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="602" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="5"/>
       <c r="B602" s="5"/>
       <c r="C602" s="5"/>
@@ -12599,7 +12631,7 @@
       <c r="K602" s="6"/>
       <c r="L602" s="6"/>
     </row>
-    <row r="603" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="603" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="5"/>
       <c r="B603" s="5"/>
       <c r="C603" s="5"/>
@@ -12613,7 +12645,7 @@
       <c r="K603" s="6"/>
       <c r="L603" s="6"/>
     </row>
-    <row r="604" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="604" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="5"/>
       <c r="B604" s="5"/>
       <c r="C604" s="5"/>
@@ -12627,7 +12659,7 @@
       <c r="K604" s="6"/>
       <c r="L604" s="6"/>
     </row>
-    <row r="605" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="605" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="5"/>
       <c r="B605" s="5"/>
       <c r="C605" s="5"/>
@@ -12641,7 +12673,7 @@
       <c r="K605" s="6"/>
       <c r="L605" s="6"/>
     </row>
-    <row r="606" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="606" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="5"/>
       <c r="B606" s="5"/>
       <c r="C606" s="5"/>
@@ -12655,7 +12687,7 @@
       <c r="K606" s="6"/>
       <c r="L606" s="6"/>
     </row>
-    <row r="607" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="607" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="5"/>
       <c r="B607" s="5"/>
       <c r="C607" s="5"/>
@@ -12669,7 +12701,7 @@
       <c r="K607" s="6"/>
       <c r="L607" s="6"/>
     </row>
-    <row r="608" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="608" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="5"/>
       <c r="B608" s="5"/>
       <c r="C608" s="5"/>
@@ -12683,7 +12715,7 @@
       <c r="K608" s="6"/>
       <c r="L608" s="6"/>
     </row>
-    <row r="609" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="609" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="5"/>
       <c r="B609" s="5"/>
       <c r="C609" s="5"/>
@@ -12697,7 +12729,7 @@
       <c r="K609" s="6"/>
       <c r="L609" s="6"/>
     </row>
-    <row r="610" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="610" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="5"/>
       <c r="B610" s="5"/>
       <c r="C610" s="5"/>
@@ -12711,7 +12743,7 @@
       <c r="K610" s="6"/>
       <c r="L610" s="6"/>
     </row>
-    <row r="611" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="611" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="5"/>
       <c r="B611" s="5"/>
       <c r="C611" s="5"/>
@@ -12725,7 +12757,7 @@
       <c r="K611" s="6"/>
       <c r="L611" s="6"/>
     </row>
-    <row r="612" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="612" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="5"/>
       <c r="B612" s="5"/>
       <c r="C612" s="5"/>
@@ -12739,7 +12771,7 @@
       <c r="K612" s="6"/>
       <c r="L612" s="6"/>
     </row>
-    <row r="613" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="613" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="5"/>
       <c r="B613" s="5"/>
       <c r="C613" s="5"/>
@@ -12753,7 +12785,7 @@
       <c r="K613" s="6"/>
       <c r="L613" s="6"/>
     </row>
-    <row r="614" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="614" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="5"/>
       <c r="B614" s="5"/>
       <c r="C614" s="5"/>
@@ -12767,7 +12799,7 @@
       <c r="K614" s="6"/>
       <c r="L614" s="6"/>
     </row>
-    <row r="615" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="615" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="5"/>
       <c r="B615" s="5"/>
       <c r="C615" s="5"/>
@@ -12781,7 +12813,7 @@
       <c r="K615" s="6"/>
       <c r="L615" s="6"/>
     </row>
-    <row r="616" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="616" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="5"/>
       <c r="B616" s="5"/>
       <c r="C616" s="5"/>
@@ -12795,7 +12827,7 @@
       <c r="K616" s="6"/>
       <c r="L616" s="6"/>
     </row>
-    <row r="617" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="617" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="5"/>
       <c r="B617" s="5"/>
       <c r="C617" s="5"/>
@@ -12809,7 +12841,7 @@
       <c r="K617" s="6"/>
       <c r="L617" s="6"/>
     </row>
-    <row r="618" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="618" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="5"/>
       <c r="B618" s="5"/>
       <c r="C618" s="5"/>
@@ -12823,7 +12855,7 @@
       <c r="K618" s="6"/>
       <c r="L618" s="6"/>
     </row>
-    <row r="619" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="619" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="5"/>
       <c r="B619" s="5"/>
       <c r="C619" s="5"/>
@@ -12837,7 +12869,7 @@
       <c r="K619" s="6"/>
       <c r="L619" s="6"/>
     </row>
-    <row r="620" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="620" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="5"/>
       <c r="B620" s="5"/>
       <c r="C620" s="5"/>
@@ -12851,7 +12883,7 @@
       <c r="K620" s="6"/>
       <c r="L620" s="6"/>
     </row>
-    <row r="621" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="621" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="5"/>
       <c r="B621" s="5"/>
       <c r="C621" s="5"/>
@@ -12865,7 +12897,7 @@
       <c r="K621" s="6"/>
       <c r="L621" s="6"/>
     </row>
-    <row r="622" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="622" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="5"/>
       <c r="B622" s="5"/>
       <c r="C622" s="5"/>
@@ -12879,7 +12911,7 @@
       <c r="K622" s="6"/>
       <c r="L622" s="6"/>
     </row>
-    <row r="623" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="623" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="5"/>
       <c r="B623" s="5"/>
       <c r="C623" s="5"/>
@@ -12893,7 +12925,7 @@
       <c r="K623" s="6"/>
       <c r="L623" s="6"/>
     </row>
-    <row r="624" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="624" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="5"/>
       <c r="B624" s="5"/>
       <c r="C624" s="5"/>
@@ -12907,7 +12939,7 @@
       <c r="K624" s="6"/>
       <c r="L624" s="6"/>
     </row>
-    <row r="625" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="625" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="5"/>
       <c r="B625" s="5"/>
       <c r="C625" s="5"/>
@@ -12921,7 +12953,7 @@
       <c r="K625" s="6"/>
       <c r="L625" s="6"/>
     </row>
-    <row r="626" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="626" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="5"/>
       <c r="B626" s="5"/>
       <c r="C626" s="5"/>
@@ -12935,7 +12967,7 @@
       <c r="K626" s="6"/>
       <c r="L626" s="6"/>
     </row>
-    <row r="627" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="627" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="5"/>
       <c r="B627" s="5"/>
       <c r="C627" s="5"/>
@@ -12949,7 +12981,7 @@
       <c r="K627" s="6"/>
       <c r="L627" s="6"/>
     </row>
-    <row r="628" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="628" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="5"/>
       <c r="B628" s="5"/>
       <c r="C628" s="5"/>
@@ -12963,7 +12995,7 @@
       <c r="K628" s="6"/>
       <c r="L628" s="6"/>
     </row>
-    <row r="629" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="629" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="5"/>
       <c r="B629" s="5"/>
       <c r="C629" s="5"/>
@@ -12977,7 +13009,7 @@
       <c r="K629" s="6"/>
       <c r="L629" s="6"/>
     </row>
-    <row r="630" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="630" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="5"/>
       <c r="B630" s="5"/>
       <c r="C630" s="5"/>
@@ -12991,7 +13023,7 @@
       <c r="K630" s="6"/>
       <c r="L630" s="6"/>
     </row>
-    <row r="631" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="631" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="5"/>
       <c r="B631" s="5"/>
       <c r="C631" s="5"/>
@@ -13005,7 +13037,7 @@
       <c r="K631" s="6"/>
       <c r="L631" s="6"/>
     </row>
-    <row r="632" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="632" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="5"/>
       <c r="B632" s="5"/>
       <c r="C632" s="5"/>
@@ -13019,7 +13051,7 @@
       <c r="K632" s="6"/>
       <c r="L632" s="6"/>
     </row>
-    <row r="633" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="633" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="5"/>
       <c r="B633" s="5"/>
       <c r="C633" s="5"/>
@@ -13033,7 +13065,7 @@
       <c r="K633" s="6"/>
       <c r="L633" s="6"/>
     </row>
-    <row r="634" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="634" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="5"/>
       <c r="B634" s="5"/>
       <c r="C634" s="5"/>
@@ -13047,7 +13079,7 @@
       <c r="K634" s="6"/>
       <c r="L634" s="6"/>
     </row>
-    <row r="635" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="635" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="5"/>
       <c r="B635" s="5"/>
       <c r="C635" s="5"/>
@@ -13061,7 +13093,7 @@
       <c r="K635" s="6"/>
       <c r="L635" s="6"/>
     </row>
-    <row r="636" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="636" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="5"/>
       <c r="B636" s="5"/>
       <c r="C636" s="5"/>
@@ -13075,7 +13107,7 @@
       <c r="K636" s="6"/>
       <c r="L636" s="6"/>
     </row>
-    <row r="637" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="637" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="5"/>
       <c r="B637" s="5"/>
       <c r="C637" s="5"/>
@@ -13089,7 +13121,7 @@
       <c r="K637" s="6"/>
       <c r="L637" s="6"/>
     </row>
-    <row r="638" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="638" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="5"/>
       <c r="B638" s="5"/>
       <c r="C638" s="5"/>
@@ -13103,7 +13135,7 @@
       <c r="K638" s="6"/>
       <c r="L638" s="6"/>
     </row>
-    <row r="639" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="639" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="5"/>
       <c r="B639" s="5"/>
       <c r="C639" s="5"/>
@@ -13117,7 +13149,7 @@
       <c r="K639" s="6"/>
       <c r="L639" s="6"/>
     </row>
-    <row r="640" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="640" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="5"/>
       <c r="B640" s="5"/>
       <c r="C640" s="5"/>
@@ -13131,7 +13163,7 @@
       <c r="K640" s="6"/>
       <c r="L640" s="6"/>
     </row>
-    <row r="641" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="641" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="5"/>
       <c r="B641" s="5"/>
       <c r="C641" s="5"/>
@@ -13145,7 +13177,7 @@
       <c r="K641" s="6"/>
       <c r="L641" s="6"/>
     </row>
-    <row r="642" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="642" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="5"/>
       <c r="B642" s="5"/>
       <c r="C642" s="5"/>
@@ -13159,7 +13191,7 @@
       <c r="K642" s="6"/>
       <c r="L642" s="6"/>
     </row>
-    <row r="643" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="643" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="5"/>
       <c r="B643" s="5"/>
       <c r="C643" s="5"/>
@@ -13173,7 +13205,7 @@
       <c r="K643" s="6"/>
       <c r="L643" s="6"/>
     </row>
-    <row r="644" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="644" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="5"/>
       <c r="B644" s="5"/>
       <c r="C644" s="5"/>
@@ -13187,7 +13219,7 @@
       <c r="K644" s="6"/>
       <c r="L644" s="6"/>
     </row>
-    <row r="645" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="645" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="5"/>
       <c r="B645" s="5"/>
       <c r="C645" s="5"/>
@@ -13201,7 +13233,7 @@
       <c r="K645" s="6"/>
       <c r="L645" s="6"/>
     </row>
-    <row r="646" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="646" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="5"/>
       <c r="B646" s="5"/>
       <c r="C646" s="5"/>
@@ -13215,7 +13247,7 @@
       <c r="K646" s="6"/>
       <c r="L646" s="6"/>
     </row>
-    <row r="647" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="647" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="5"/>
       <c r="B647" s="5"/>
       <c r="C647" s="5"/>
@@ -13229,7 +13261,7 @@
       <c r="K647" s="6"/>
       <c r="L647" s="6"/>
     </row>
-    <row r="648" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="648" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="5"/>
       <c r="B648" s="5"/>
       <c r="C648" s="5"/>
@@ -13243,7 +13275,7 @@
       <c r="K648" s="6"/>
       <c r="L648" s="6"/>
     </row>
-    <row r="649" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="649" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="5"/>
       <c r="B649" s="5"/>
       <c r="C649" s="5"/>
@@ -13257,7 +13289,7 @@
       <c r="K649" s="6"/>
       <c r="L649" s="6"/>
     </row>
-    <row r="650" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="650" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="5"/>
       <c r="B650" s="5"/>
       <c r="C650" s="5"/>
@@ -13271,7 +13303,7 @@
       <c r="K650" s="6"/>
       <c r="L650" s="6"/>
     </row>
-    <row r="651" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="651" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="5"/>
       <c r="B651" s="5"/>
       <c r="C651" s="5"/>
@@ -13285,7 +13317,7 @@
       <c r="K651" s="6"/>
       <c r="L651" s="6"/>
     </row>
-    <row r="652" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="652" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="5"/>
       <c r="B652" s="5"/>
       <c r="C652" s="5"/>
@@ -13299,7 +13331,7 @@
       <c r="K652" s="6"/>
       <c r="L652" s="6"/>
     </row>
-    <row r="653" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="653" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="5"/>
       <c r="B653" s="5"/>
       <c r="C653" s="5"/>
@@ -13313,7 +13345,7 @@
       <c r="K653" s="6"/>
       <c r="L653" s="6"/>
     </row>
-    <row r="654" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="654" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="5"/>
       <c r="B654" s="5"/>
       <c r="C654" s="5"/>
@@ -13327,7 +13359,7 @@
       <c r="K654" s="6"/>
       <c r="L654" s="6"/>
     </row>
-    <row r="655" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="655" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="5"/>
       <c r="B655" s="5"/>
       <c r="C655" s="5"/>
@@ -13341,7 +13373,7 @@
       <c r="K655" s="6"/>
       <c r="L655" s="6"/>
     </row>
-    <row r="656" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="656" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="5"/>
       <c r="B656" s="5"/>
       <c r="C656" s="5"/>
@@ -13355,7 +13387,7 @@
       <c r="K656" s="6"/>
       <c r="L656" s="6"/>
     </row>
-    <row r="657" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="657" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="5"/>
       <c r="B657" s="5"/>
       <c r="C657" s="5"/>
@@ -13369,7 +13401,7 @@
       <c r="K657" s="6"/>
       <c r="L657" s="6"/>
     </row>
-    <row r="658" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="658" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="5"/>
       <c r="B658" s="5"/>
       <c r="C658" s="5"/>
@@ -13383,7 +13415,7 @@
       <c r="K658" s="6"/>
       <c r="L658" s="6"/>
     </row>
-    <row r="659" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="659" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="5"/>
       <c r="B659" s="5"/>
       <c r="C659" s="5"/>
@@ -13397,7 +13429,7 @@
       <c r="K659" s="6"/>
       <c r="L659" s="6"/>
     </row>
-    <row r="660" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="660" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="5"/>
       <c r="B660" s="5"/>
       <c r="C660" s="5"/>
@@ -13411,7 +13443,7 @@
       <c r="K660" s="6"/>
       <c r="L660" s="6"/>
     </row>
-    <row r="661" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="661" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="5"/>
       <c r="B661" s="5"/>
       <c r="C661" s="5"/>
@@ -13425,7 +13457,7 @@
       <c r="K661" s="6"/>
       <c r="L661" s="6"/>
     </row>
-    <row r="662" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="662" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="5"/>
       <c r="B662" s="5"/>
       <c r="C662" s="5"/>
@@ -13439,7 +13471,7 @@
       <c r="K662" s="6"/>
       <c r="L662" s="6"/>
     </row>
-    <row r="663" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="663" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="5"/>
       <c r="B663" s="5"/>
       <c r="C663" s="5"/>
@@ -13453,7 +13485,7 @@
       <c r="K663" s="6"/>
       <c r="L663" s="6"/>
     </row>
-    <row r="664" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="664" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="5"/>
       <c r="B664" s="5"/>
       <c r="C664" s="5"/>
@@ -13467,7 +13499,7 @@
       <c r="K664" s="6"/>
       <c r="L664" s="6"/>
     </row>
-    <row r="665" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="665" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="5"/>
       <c r="B665" s="5"/>
       <c r="C665" s="5"/>
@@ -13481,7 +13513,7 @@
       <c r="K665" s="6"/>
       <c r="L665" s="6"/>
     </row>
-    <row r="666" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="666" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="5"/>
       <c r="B666" s="5"/>
       <c r="C666" s="5"/>
@@ -13495,7 +13527,7 @@
       <c r="K666" s="6"/>
       <c r="L666" s="6"/>
     </row>
-    <row r="667" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="667" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="5"/>
       <c r="B667" s="5"/>
       <c r="C667" s="5"/>
@@ -13509,7 +13541,7 @@
       <c r="K667" s="6"/>
       <c r="L667" s="6"/>
     </row>
-    <row r="668" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="668" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="5"/>
       <c r="B668" s="5"/>
       <c r="C668" s="5"/>
@@ -13523,7 +13555,7 @@
       <c r="K668" s="6"/>
       <c r="L668" s="6"/>
     </row>
-    <row r="669" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="669" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="5"/>
       <c r="B669" s="5"/>
       <c r="C669" s="5"/>
@@ -13537,7 +13569,7 @@
       <c r="K669" s="6"/>
       <c r="L669" s="6"/>
     </row>
-    <row r="670" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="670" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="5"/>
       <c r="B670" s="5"/>
       <c r="C670" s="5"/>
@@ -13551,7 +13583,7 @@
       <c r="K670" s="6"/>
       <c r="L670" s="6"/>
     </row>
-    <row r="671" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="671" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="5"/>
       <c r="B671" s="5"/>
       <c r="C671" s="5"/>
@@ -13565,7 +13597,7 @@
       <c r="K671" s="6"/>
       <c r="L671" s="6"/>
     </row>
-    <row r="672" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="672" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="5"/>
       <c r="B672" s="5"/>
       <c r="C672" s="5"/>
@@ -13579,7 +13611,7 @@
       <c r="K672" s="6"/>
       <c r="L672" s="6"/>
     </row>
-    <row r="673" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="673" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="5"/>
       <c r="B673" s="5"/>
       <c r="C673" s="5"/>
@@ -13593,7 +13625,7 @@
       <c r="K673" s="6"/>
       <c r="L673" s="6"/>
     </row>
-    <row r="674" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="674" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="5"/>
       <c r="B674" s="5"/>
       <c r="C674" s="5"/>
@@ -13607,7 +13639,7 @@
       <c r="K674" s="6"/>
       <c r="L674" s="6"/>
     </row>
-    <row r="675" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="675" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="5"/>
       <c r="B675" s="5"/>
       <c r="C675" s="5"/>
@@ -13621,7 +13653,7 @@
       <c r="K675" s="6"/>
       <c r="L675" s="6"/>
     </row>
-    <row r="676" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="676" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="5"/>
       <c r="B676" s="5"/>
       <c r="C676" s="5"/>
@@ -13635,7 +13667,7 @@
       <c r="K676" s="6"/>
       <c r="L676" s="6"/>
     </row>
-    <row r="677" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="677" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="5"/>
       <c r="B677" s="5"/>
       <c r="C677" s="5"/>
@@ -13649,7 +13681,7 @@
       <c r="K677" s="6"/>
       <c r="L677" s="6"/>
     </row>
-    <row r="678" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="678" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="5"/>
       <c r="B678" s="5"/>
       <c r="C678" s="5"/>
@@ -13663,7 +13695,7 @@
       <c r="K678" s="6"/>
       <c r="L678" s="6"/>
     </row>
-    <row r="679" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="679" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="5"/>
       <c r="B679" s="5"/>
       <c r="C679" s="5"/>
@@ -13677,7 +13709,7 @@
       <c r="K679" s="6"/>
       <c r="L679" s="6"/>
     </row>
-    <row r="680" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="680" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="5"/>
       <c r="B680" s="5"/>
       <c r="C680" s="5"/>
@@ -13691,7 +13723,7 @@
       <c r="K680" s="6"/>
       <c r="L680" s="6"/>
     </row>
-    <row r="681" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="681" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="5"/>
       <c r="B681" s="5"/>
       <c r="C681" s="5"/>
@@ -13705,7 +13737,7 @@
       <c r="K681" s="6"/>
       <c r="L681" s="6"/>
     </row>
-    <row r="682" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="682" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="5"/>
       <c r="B682" s="5"/>
       <c r="C682" s="5"/>
@@ -13719,7 +13751,7 @@
       <c r="K682" s="6"/>
       <c r="L682" s="6"/>
     </row>
-    <row r="683" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="683" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="5"/>
       <c r="B683" s="5"/>
       <c r="C683" s="5"/>
@@ -13733,7 +13765,7 @@
       <c r="K683" s="6"/>
       <c r="L683" s="6"/>
     </row>
-    <row r="684" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="684" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="5"/>
       <c r="B684" s="5"/>
       <c r="C684" s="5"/>
@@ -13747,7 +13779,7 @@
       <c r="K684" s="6"/>
       <c r="L684" s="6"/>
     </row>
-    <row r="685" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="685" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="5"/>
       <c r="B685" s="5"/>
       <c r="C685" s="5"/>
@@ -13761,7 +13793,7 @@
       <c r="K685" s="6"/>
       <c r="L685" s="6"/>
     </row>
-    <row r="686" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="686" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="5"/>
       <c r="B686" s="5"/>
       <c r="C686" s="5"/>
@@ -13775,7 +13807,7 @@
       <c r="K686" s="6"/>
       <c r="L686" s="6"/>
     </row>
-    <row r="687" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="687" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="5"/>
       <c r="B687" s="5"/>
       <c r="C687" s="5"/>
@@ -13789,7 +13821,7 @@
       <c r="K687" s="6"/>
       <c r="L687" s="6"/>
     </row>
-    <row r="688" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="688" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="5"/>
       <c r="B688" s="5"/>
       <c r="C688" s="5"/>
@@ -13803,7 +13835,7 @@
       <c r="K688" s="6"/>
       <c r="L688" s="6"/>
     </row>
-    <row r="689" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="689" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="5"/>
       <c r="B689" s="5"/>
       <c r="C689" s="5"/>
@@ -13817,7 +13849,7 @@
       <c r="K689" s="6"/>
       <c r="L689" s="6"/>
     </row>
-    <row r="690" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="690" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="5"/>
       <c r="B690" s="5"/>
       <c r="C690" s="5"/>
@@ -13831,7 +13863,7 @@
       <c r="K690" s="6"/>
       <c r="L690" s="6"/>
     </row>
-    <row r="691" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="691" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="5"/>
       <c r="B691" s="5"/>
       <c r="C691" s="5"/>
@@ -13845,7 +13877,7 @@
       <c r="K691" s="6"/>
       <c r="L691" s="6"/>
     </row>
-    <row r="692" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="692" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="5"/>
       <c r="B692" s="5"/>
       <c r="C692" s="5"/>
@@ -13859,7 +13891,7 @@
       <c r="K692" s="6"/>
       <c r="L692" s="6"/>
     </row>
-    <row r="693" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="693" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="5"/>
       <c r="B693" s="5"/>
       <c r="C693" s="5"/>
@@ -13873,7 +13905,7 @@
       <c r="K693" s="6"/>
       <c r="L693" s="6"/>
     </row>
-    <row r="694" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="694" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="5"/>
       <c r="B694" s="5"/>
       <c r="C694" s="5"/>
@@ -13887,7 +13919,7 @@
       <c r="K694" s="6"/>
       <c r="L694" s="6"/>
     </row>
-    <row r="695" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="695" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="5"/>
       <c r="B695" s="5"/>
       <c r="C695" s="5"/>
@@ -13901,7 +13933,7 @@
       <c r="K695" s="6"/>
       <c r="L695" s="6"/>
     </row>
-    <row r="696" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="696" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="5"/>
       <c r="B696" s="5"/>
       <c r="C696" s="5"/>
@@ -13915,7 +13947,7 @@
       <c r="K696" s="6"/>
       <c r="L696" s="6"/>
     </row>
-    <row r="697" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="697" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="5"/>
       <c r="B697" s="5"/>
       <c r="C697" s="5"/>
@@ -13929,7 +13961,7 @@
       <c r="K697" s="6"/>
       <c r="L697" s="6"/>
     </row>
-    <row r="698" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="698" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="5"/>
       <c r="B698" s="5"/>
       <c r="C698" s="5"/>
@@ -13943,7 +13975,7 @@
       <c r="K698" s="6"/>
       <c r="L698" s="6"/>
     </row>
-    <row r="699" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="699" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="5"/>
       <c r="B699" s="5"/>
       <c r="C699" s="5"/>
@@ -13957,7 +13989,7 @@
       <c r="K699" s="6"/>
       <c r="L699" s="6"/>
     </row>
-    <row r="700" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="700" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="5"/>
       <c r="B700" s="5"/>
       <c r="C700" s="5"/>
@@ -13971,7 +14003,7 @@
       <c r="K700" s="6"/>
       <c r="L700" s="6"/>
     </row>
-    <row r="701" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="701" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="5"/>
       <c r="B701" s="5"/>
       <c r="C701" s="5"/>
@@ -13985,7 +14017,7 @@
       <c r="K701" s="6"/>
       <c r="L701" s="6"/>
     </row>
-    <row r="702" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="702" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="5"/>
       <c r="B702" s="5"/>
       <c r="C702" s="5"/>
@@ -13999,7 +14031,7 @@
       <c r="K702" s="6"/>
       <c r="L702" s="6"/>
     </row>
-    <row r="703" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="703" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="5"/>
       <c r="B703" s="5"/>
       <c r="C703" s="5"/>
@@ -14013,7 +14045,7 @@
       <c r="K703" s="6"/>
       <c r="L703" s="6"/>
     </row>
-    <row r="704" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="704" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="5"/>
       <c r="B704" s="5"/>
       <c r="C704" s="5"/>
@@ -14027,7 +14059,7 @@
       <c r="K704" s="6"/>
       <c r="L704" s="6"/>
     </row>
-    <row r="705" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="705" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="5"/>
       <c r="B705" s="5"/>
       <c r="C705" s="5"/>
@@ -14041,7 +14073,7 @@
       <c r="K705" s="6"/>
       <c r="L705" s="6"/>
     </row>
-    <row r="706" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="706" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="5"/>
       <c r="B706" s="5"/>
       <c r="C706" s="5"/>
@@ -14055,7 +14087,7 @@
       <c r="K706" s="6"/>
       <c r="L706" s="6"/>
     </row>
-    <row r="707" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="707" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="5"/>
       <c r="B707" s="5"/>
       <c r="C707" s="5"/>
@@ -14069,7 +14101,7 @@
       <c r="K707" s="6"/>
       <c r="L707" s="6"/>
     </row>
-    <row r="708" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="708" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="5"/>
       <c r="B708" s="5"/>
       <c r="C708" s="5"/>
@@ -14083,7 +14115,7 @@
       <c r="K708" s="6"/>
       <c r="L708" s="6"/>
     </row>
-    <row r="709" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="709" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="5"/>
       <c r="B709" s="5"/>
       <c r="C709" s="5"/>
@@ -14097,7 +14129,7 @@
       <c r="K709" s="6"/>
       <c r="L709" s="6"/>
     </row>
-    <row r="710" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="710" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="5"/>
       <c r="B710" s="5"/>
       <c r="C710" s="5"/>
@@ -14111,7 +14143,7 @@
       <c r="K710" s="6"/>
       <c r="L710" s="6"/>
     </row>
-    <row r="711" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="711" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="5"/>
       <c r="B711" s="5"/>
       <c r="C711" s="5"/>
@@ -14125,7 +14157,7 @@
       <c r="K711" s="6"/>
       <c r="L711" s="6"/>
     </row>
-    <row r="712" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="712" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="5"/>
       <c r="B712" s="5"/>
       <c r="C712" s="5"/>
@@ -14139,7 +14171,7 @@
       <c r="K712" s="6"/>
       <c r="L712" s="6"/>
     </row>
-    <row r="713" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="713" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="5"/>
       <c r="B713" s="5"/>
       <c r="C713" s="5"/>
@@ -14153,7 +14185,7 @@
       <c r="K713" s="6"/>
       <c r="L713" s="6"/>
     </row>
-    <row r="714" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="714" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="5"/>
       <c r="B714" s="5"/>
       <c r="C714" s="5"/>
@@ -14167,7 +14199,7 @@
       <c r="K714" s="6"/>
       <c r="L714" s="6"/>
     </row>
-    <row r="715" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="715" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="5"/>
       <c r="B715" s="5"/>
       <c r="C715" s="5"/>
@@ -14181,7 +14213,7 @@
       <c r="K715" s="6"/>
       <c r="L715" s="6"/>
     </row>
-    <row r="716" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="716" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="5"/>
       <c r="B716" s="5"/>
       <c r="C716" s="5"/>
@@ -14195,7 +14227,7 @@
       <c r="K716" s="6"/>
       <c r="L716" s="6"/>
     </row>
-    <row r="717" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="717" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="5"/>
       <c r="B717" s="5"/>
       <c r="C717" s="5"/>
@@ -14209,7 +14241,7 @@
       <c r="K717" s="6"/>
       <c r="L717" s="6"/>
     </row>
-    <row r="718" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="718" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="5"/>
       <c r="B718" s="5"/>
       <c r="C718" s="5"/>
@@ -14223,7 +14255,7 @@
       <c r="K718" s="6"/>
       <c r="L718" s="6"/>
     </row>
-    <row r="719" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="719" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="5"/>
       <c r="B719" s="5"/>
       <c r="C719" s="5"/>
@@ -14237,7 +14269,7 @@
       <c r="K719" s="6"/>
       <c r="L719" s="6"/>
     </row>
-    <row r="720" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="720" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="5"/>
       <c r="B720" s="5"/>
       <c r="C720" s="5"/>
@@ -14251,7 +14283,7 @@
       <c r="K720" s="6"/>
       <c r="L720" s="6"/>
     </row>
-    <row r="721" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="721" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="5"/>
       <c r="B721" s="5"/>
       <c r="C721" s="5"/>
@@ -14265,7 +14297,7 @@
       <c r="K721" s="6"/>
       <c r="L721" s="6"/>
     </row>
-    <row r="722" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="722" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="5"/>
       <c r="B722" s="5"/>
       <c r="C722" s="5"/>
@@ -14279,7 +14311,7 @@
       <c r="K722" s="6"/>
       <c r="L722" s="6"/>
     </row>
-    <row r="723" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="723" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="5"/>
       <c r="B723" s="5"/>
       <c r="C723" s="5"/>
@@ -14293,7 +14325,7 @@
       <c r="K723" s="6"/>
       <c r="L723" s="6"/>
     </row>
-    <row r="724" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="724" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="5"/>
       <c r="B724" s="5"/>
       <c r="C724" s="5"/>
@@ -14307,7 +14339,7 @@
       <c r="K724" s="6"/>
       <c r="L724" s="6"/>
     </row>
-    <row r="725" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="725" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="5"/>
       <c r="B725" s="5"/>
       <c r="C725" s="5"/>
@@ -14321,7 +14353,7 @@
       <c r="K725" s="6"/>
       <c r="L725" s="6"/>
     </row>
-    <row r="726" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="726" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="5"/>
       <c r="B726" s="5"/>
       <c r="C726" s="5"/>
@@ -14335,7 +14367,7 @@
       <c r="K726" s="6"/>
       <c r="L726" s="6"/>
     </row>
-    <row r="727" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="727" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="5"/>
       <c r="B727" s="5"/>
       <c r="C727" s="5"/>
@@ -14349,7 +14381,7 @@
       <c r="K727" s="6"/>
       <c r="L727" s="6"/>
     </row>
-    <row r="728" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="728" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="5"/>
       <c r="B728" s="5"/>
       <c r="C728" s="5"/>
@@ -14363,7 +14395,7 @@
       <c r="K728" s="6"/>
       <c r="L728" s="6"/>
     </row>
-    <row r="729" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="729" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A729" s="5"/>
       <c r="B729" s="5"/>
       <c r="C729" s="5"/>
@@ -14377,7 +14409,7 @@
       <c r="K729" s="6"/>
       <c r="L729" s="6"/>
     </row>
-    <row r="730" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="730" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="5"/>
       <c r="B730" s="5"/>
       <c r="C730" s="5"/>
@@ -14391,7 +14423,7 @@
       <c r="K730" s="6"/>
       <c r="L730" s="6"/>
     </row>
-    <row r="731" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="731" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="5"/>
       <c r="B731" s="5"/>
       <c r="C731" s="5"/>
@@ -14405,7 +14437,7 @@
       <c r="K731" s="6"/>
       <c r="L731" s="6"/>
     </row>
-    <row r="732" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="732" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="5"/>
       <c r="B732" s="5"/>
       <c r="C732" s="5"/>
@@ -14419,7 +14451,7 @@
       <c r="K732" s="6"/>
       <c r="L732" s="6"/>
     </row>
-    <row r="733" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="733" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="5"/>
       <c r="B733" s="5"/>
       <c r="C733" s="5"/>
@@ -14433,7 +14465,7 @@
       <c r="K733" s="6"/>
       <c r="L733" s="6"/>
     </row>
-    <row r="734" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="734" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="5"/>
       <c r="B734" s="5"/>
       <c r="C734" s="5"/>
@@ -14447,7 +14479,7 @@
       <c r="K734" s="6"/>
       <c r="L734" s="6"/>
     </row>
-    <row r="735" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="735" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="5"/>
       <c r="B735" s="5"/>
       <c r="C735" s="5"/>
@@ -14461,7 +14493,7 @@
       <c r="K735" s="6"/>
       <c r="L735" s="6"/>
     </row>
-    <row r="736" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="736" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="5"/>
       <c r="B736" s="5"/>
       <c r="C736" s="5"/>
@@ -14475,7 +14507,7 @@
       <c r="K736" s="6"/>
       <c r="L736" s="6"/>
     </row>
-    <row r="737" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="737" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="5"/>
       <c r="B737" s="5"/>
       <c r="C737" s="5"/>
@@ -14489,7 +14521,7 @@
       <c r="K737" s="6"/>
       <c r="L737" s="6"/>
     </row>
-    <row r="738" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="738" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A738" s="5"/>
       <c r="B738" s="5"/>
       <c r="C738" s="5"/>
@@ -14503,7 +14535,7 @@
       <c r="K738" s="6"/>
       <c r="L738" s="6"/>
     </row>
-    <row r="739" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="739" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="5"/>
       <c r="B739" s="5"/>
       <c r="C739" s="5"/>
@@ -14517,7 +14549,7 @@
       <c r="K739" s="6"/>
       <c r="L739" s="6"/>
     </row>
-    <row r="740" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="740" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="5"/>
       <c r="B740" s="5"/>
       <c r="C740" s="5"/>
@@ -14531,7 +14563,7 @@
       <c r="K740" s="6"/>
       <c r="L740" s="6"/>
     </row>
-    <row r="741" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="741" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="5"/>
       <c r="B741" s="5"/>
       <c r="C741" s="5"/>
@@ -14545,7 +14577,7 @@
       <c r="K741" s="6"/>
       <c r="L741" s="6"/>
     </row>
-    <row r="742" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="742" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="5"/>
       <c r="B742" s="5"/>
       <c r="C742" s="5"/>
@@ -14559,7 +14591,7 @@
       <c r="K742" s="6"/>
       <c r="L742" s="6"/>
     </row>
-    <row r="743" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="743" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="5"/>
       <c r="B743" s="5"/>
       <c r="C743" s="5"/>
@@ -14573,7 +14605,7 @@
       <c r="K743" s="6"/>
       <c r="L743" s="6"/>
     </row>
-    <row r="744" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="744" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A744" s="5"/>
       <c r="B744" s="5"/>
       <c r="C744" s="5"/>
@@ -14587,7 +14619,7 @@
       <c r="K744" s="6"/>
       <c r="L744" s="6"/>
     </row>
-    <row r="745" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="745" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A745" s="5"/>
       <c r="B745" s="5"/>
       <c r="C745" s="5"/>
@@ -14601,7 +14633,7 @@
       <c r="K745" s="6"/>
       <c r="L745" s="6"/>
     </row>
-    <row r="746" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="746" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A746" s="5"/>
       <c r="B746" s="5"/>
       <c r="C746" s="5"/>
@@ -14615,7 +14647,7 @@
       <c r="K746" s="6"/>
       <c r="L746" s="6"/>
     </row>
-    <row r="747" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="747" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A747" s="5"/>
       <c r="B747" s="5"/>
       <c r="C747" s="5"/>
@@ -14629,7 +14661,7 @@
       <c r="K747" s="6"/>
       <c r="L747" s="6"/>
     </row>
-    <row r="748" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="748" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A748" s="5"/>
       <c r="B748" s="5"/>
       <c r="C748" s="5"/>
@@ -14643,7 +14675,7 @@
       <c r="K748" s="6"/>
       <c r="L748" s="6"/>
     </row>
-    <row r="749" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="749" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="5"/>
       <c r="B749" s="5"/>
       <c r="C749" s="5"/>
@@ -14657,7 +14689,7 @@
       <c r="K749" s="6"/>
       <c r="L749" s="6"/>
     </row>
-    <row r="750" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="750" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="5"/>
       <c r="B750" s="5"/>
       <c r="C750" s="5"/>
@@ -14671,7 +14703,7 @@
       <c r="K750" s="6"/>
       <c r="L750" s="6"/>
     </row>
-    <row r="751" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="751" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="5"/>
       <c r="B751" s="5"/>
       <c r="C751" s="5"/>
@@ -14685,7 +14717,7 @@
       <c r="K751" s="6"/>
       <c r="L751" s="6"/>
     </row>
-    <row r="752" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="752" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="5"/>
       <c r="B752" s="5"/>
       <c r="C752" s="5"/>
@@ -14699,7 +14731,7 @@
       <c r="K752" s="6"/>
       <c r="L752" s="6"/>
     </row>
-    <row r="753" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="753" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="5"/>
       <c r="B753" s="5"/>
       <c r="C753" s="5"/>
@@ -14713,7 +14745,7 @@
       <c r="K753" s="6"/>
       <c r="L753" s="6"/>
     </row>
-    <row r="754" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="754" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="5"/>
       <c r="B754" s="5"/>
       <c r="C754" s="5"/>
@@ -14727,7 +14759,7 @@
       <c r="K754" s="6"/>
       <c r="L754" s="6"/>
     </row>
-    <row r="755" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="755" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="5"/>
       <c r="B755" s="5"/>
       <c r="C755" s="5"/>
@@ -14741,7 +14773,7 @@
       <c r="K755" s="6"/>
       <c r="L755" s="6"/>
     </row>
-    <row r="756" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="756" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="5"/>
       <c r="B756" s="5"/>
       <c r="C756" s="5"/>
@@ -14755,7 +14787,7 @@
       <c r="K756" s="6"/>
       <c r="L756" s="6"/>
     </row>
-    <row r="757" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="757" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="5"/>
       <c r="B757" s="5"/>
       <c r="C757" s="5"/>
@@ -14769,7 +14801,7 @@
       <c r="K757" s="6"/>
       <c r="L757" s="6"/>
     </row>
-    <row r="758" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="758" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="5"/>
       <c r="B758" s="5"/>
       <c r="C758" s="5"/>
@@ -14783,7 +14815,7 @@
       <c r="K758" s="6"/>
       <c r="L758" s="6"/>
     </row>
-    <row r="759" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="759" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="5"/>
       <c r="B759" s="5"/>
       <c r="C759" s="5"/>
@@ -14797,7 +14829,7 @@
       <c r="K759" s="6"/>
       <c r="L759" s="6"/>
     </row>
-    <row r="760" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="760" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="5"/>
       <c r="B760" s="5"/>
       <c r="C760" s="5"/>
@@ -14811,7 +14843,7 @@
       <c r="K760" s="6"/>
       <c r="L760" s="6"/>
     </row>
-    <row r="761" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="761" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="5"/>
       <c r="B761" s="5"/>
       <c r="C761" s="5"/>
@@ -14825,7 +14857,7 @@
       <c r="K761" s="6"/>
       <c r="L761" s="6"/>
     </row>
-    <row r="762" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="762" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="5"/>
       <c r="B762" s="5"/>
       <c r="C762" s="5"/>
@@ -14839,7 +14871,7 @@
       <c r="K762" s="6"/>
       <c r="L762" s="6"/>
     </row>
-    <row r="763" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="763" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="5"/>
       <c r="B763" s="5"/>
       <c r="C763" s="5"/>
@@ -14853,7 +14885,7 @@
       <c r="K763" s="6"/>
       <c r="L763" s="6"/>
     </row>
-    <row r="764" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="764" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="5"/>
       <c r="B764" s="5"/>
       <c r="C764" s="5"/>
@@ -14867,7 +14899,7 @@
       <c r="K764" s="6"/>
       <c r="L764" s="6"/>
     </row>
-    <row r="765" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="765" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="5"/>
       <c r="B765" s="5"/>
       <c r="C765" s="5"/>
@@ -14881,7 +14913,7 @@
       <c r="K765" s="6"/>
       <c r="L765" s="6"/>
     </row>
-    <row r="766" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="766" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="5"/>
       <c r="B766" s="5"/>
       <c r="C766" s="5"/>
@@ -14895,7 +14927,7 @@
       <c r="K766" s="6"/>
       <c r="L766" s="6"/>
     </row>
-    <row r="767" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="767" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="5"/>
       <c r="B767" s="5"/>
       <c r="C767" s="5"/>
@@ -14909,7 +14941,7 @@
       <c r="K767" s="6"/>
       <c r="L767" s="6"/>
     </row>
-    <row r="768" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="768" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="5"/>
       <c r="B768" s="5"/>
       <c r="C768" s="5"/>
@@ -14923,7 +14955,7 @@
       <c r="K768" s="6"/>
       <c r="L768" s="6"/>
     </row>
-    <row r="769" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="769" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="5"/>
       <c r="B769" s="5"/>
       <c r="C769" s="5"/>
@@ -14937,7 +14969,7 @@
       <c r="K769" s="6"/>
       <c r="L769" s="6"/>
     </row>
-    <row r="770" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="770" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="5"/>
       <c r="B770" s="5"/>
       <c r="C770" s="5"/>
@@ -14951,7 +14983,7 @@
       <c r="K770" s="6"/>
       <c r="L770" s="6"/>
     </row>
-    <row r="771" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="771" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="5"/>
       <c r="B771" s="5"/>
       <c r="C771" s="5"/>
@@ -14965,7 +14997,7 @@
       <c r="K771" s="6"/>
       <c r="L771" s="6"/>
     </row>
-    <row r="772" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="772" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="5"/>
       <c r="B772" s="5"/>
       <c r="C772" s="5"/>
@@ -14979,7 +15011,7 @@
       <c r="K772" s="6"/>
       <c r="L772" s="6"/>
     </row>
-    <row r="773" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="773" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="5"/>
       <c r="B773" s="5"/>
       <c r="C773" s="5"/>
@@ -14993,7 +15025,7 @@
       <c r="K773" s="6"/>
       <c r="L773" s="6"/>
     </row>
-    <row r="774" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="774" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="5"/>
       <c r="B774" s="5"/>
       <c r="C774" s="5"/>
@@ -15007,7 +15039,7 @@
       <c r="K774" s="6"/>
       <c r="L774" s="6"/>
     </row>
-    <row r="775" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="775" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A775" s="5"/>
       <c r="B775" s="5"/>
       <c r="C775" s="5"/>
@@ -15021,7 +15053,7 @@
       <c r="K775" s="6"/>
       <c r="L775" s="6"/>
     </row>
-    <row r="776" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="776" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="5"/>
       <c r="B776" s="5"/>
       <c r="C776" s="5"/>
@@ -15035,7 +15067,7 @@
       <c r="K776" s="6"/>
       <c r="L776" s="6"/>
     </row>
-    <row r="777" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="777" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="5"/>
       <c r="B777" s="5"/>
       <c r="C777" s="5"/>
@@ -15049,7 +15081,7 @@
       <c r="K777" s="6"/>
       <c r="L777" s="6"/>
     </row>
-    <row r="778" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="778" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="5"/>
       <c r="B778" s="5"/>
       <c r="C778" s="5"/>
@@ -15063,7 +15095,7 @@
       <c r="K778" s="6"/>
       <c r="L778" s="6"/>
     </row>
-    <row r="779" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="779" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="5"/>
       <c r="B779" s="5"/>
       <c r="C779" s="5"/>
@@ -15077,7 +15109,7 @@
       <c r="K779" s="6"/>
       <c r="L779" s="6"/>
     </row>
-    <row r="780" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="780" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="5"/>
       <c r="B780" s="5"/>
       <c r="C780" s="5"/>
@@ -15091,7 +15123,7 @@
       <c r="K780" s="6"/>
       <c r="L780" s="6"/>
     </row>
-    <row r="781" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="781" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="5"/>
       <c r="B781" s="5"/>
       <c r="C781" s="5"/>
@@ -15105,7 +15137,7 @@
       <c r="K781" s="6"/>
       <c r="L781" s="6"/>
     </row>
-    <row r="782" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="782" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="5"/>
       <c r="B782" s="5"/>
       <c r="C782" s="5"/>
@@ -15119,7 +15151,7 @@
       <c r="K782" s="6"/>
       <c r="L782" s="6"/>
     </row>
-    <row r="783" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="783" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="5"/>
       <c r="B783" s="5"/>
       <c r="C783" s="5"/>
@@ -15133,7 +15165,7 @@
       <c r="K783" s="6"/>
       <c r="L783" s="6"/>
     </row>
-    <row r="784" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="784" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="5"/>
       <c r="B784" s="5"/>
       <c r="C784" s="5"/>
@@ -15147,7 +15179,7 @@
       <c r="K784" s="6"/>
       <c r="L784" s="6"/>
     </row>
-    <row r="785" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="785" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="5"/>
       <c r="B785" s="5"/>
       <c r="C785" s="5"/>
@@ -15161,7 +15193,7 @@
       <c r="K785" s="6"/>
       <c r="L785" s="6"/>
     </row>
-    <row r="786" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="786" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="5"/>
       <c r="B786" s="5"/>
       <c r="C786" s="5"/>
@@ -15175,7 +15207,7 @@
       <c r="K786" s="6"/>
       <c r="L786" s="6"/>
     </row>
-    <row r="787" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="787" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="5"/>
       <c r="B787" s="5"/>
       <c r="C787" s="5"/>
@@ -15189,7 +15221,7 @@
       <c r="K787" s="6"/>
       <c r="L787" s="6"/>
     </row>
-    <row r="788" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="788" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="5"/>
       <c r="B788" s="5"/>
       <c r="C788" s="5"/>
@@ -15203,7 +15235,7 @@
       <c r="K788" s="6"/>
       <c r="L788" s="6"/>
     </row>
-    <row r="789" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="789" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="5"/>
       <c r="B789" s="5"/>
       <c r="C789" s="5"/>
@@ -15217,7 +15249,7 @@
       <c r="K789" s="6"/>
       <c r="L789" s="6"/>
     </row>
-    <row r="790" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="790" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="5"/>
       <c r="B790" s="5"/>
       <c r="C790" s="5"/>
@@ -15231,7 +15263,7 @@
       <c r="K790" s="6"/>
       <c r="L790" s="6"/>
     </row>
-    <row r="791" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="791" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="5"/>
       <c r="B791" s="5"/>
       <c r="C791" s="5"/>
@@ -15245,7 +15277,7 @@
       <c r="K791" s="6"/>
       <c r="L791" s="6"/>
     </row>
-    <row r="792" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="792" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="5"/>
       <c r="B792" s="5"/>
       <c r="C792" s="5"/>
@@ -15259,7 +15291,7 @@
       <c r="K792" s="6"/>
       <c r="L792" s="6"/>
     </row>
-    <row r="793" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="793" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="5"/>
       <c r="B793" s="5"/>
       <c r="C793" s="5"/>
@@ -15273,7 +15305,7 @@
       <c r="K793" s="6"/>
       <c r="L793" s="6"/>
     </row>
-    <row r="794" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="794" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="5"/>
       <c r="B794" s="5"/>
       <c r="C794" s="5"/>
@@ -15287,7 +15319,7 @@
       <c r="K794" s="6"/>
       <c r="L794" s="6"/>
     </row>
-    <row r="795" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="795" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="5"/>
       <c r="B795" s="5"/>
       <c r="C795" s="5"/>
@@ -15301,7 +15333,7 @@
       <c r="K795" s="6"/>
       <c r="L795" s="6"/>
     </row>
-    <row r="796" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="796" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="5"/>
       <c r="B796" s="5"/>
       <c r="C796" s="5"/>
@@ -15315,7 +15347,7 @@
       <c r="K796" s="6"/>
       <c r="L796" s="6"/>
     </row>
-    <row r="797" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="797" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="5"/>
       <c r="B797" s="5"/>
       <c r="C797" s="5"/>
@@ -15329,7 +15361,7 @@
       <c r="K797" s="6"/>
       <c r="L797" s="6"/>
     </row>
-    <row r="798" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="798" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="5"/>
       <c r="B798" s="5"/>
       <c r="C798" s="5"/>
@@ -15343,7 +15375,7 @@
       <c r="K798" s="6"/>
       <c r="L798" s="6"/>
     </row>
-    <row r="799" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="799" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="5"/>
       <c r="B799" s="5"/>
       <c r="C799" s="5"/>
@@ -15357,7 +15389,7 @@
       <c r="K799" s="6"/>
       <c r="L799" s="6"/>
     </row>
-    <row r="800" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="800" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="5"/>
       <c r="B800" s="5"/>
       <c r="C800" s="5"/>
@@ -15371,7 +15403,7 @@
       <c r="K800" s="6"/>
       <c r="L800" s="6"/>
     </row>
-    <row r="801" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="801" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="5"/>
       <c r="B801" s="5"/>
       <c r="C801" s="5"/>
@@ -15385,7 +15417,7 @@
       <c r="K801" s="6"/>
       <c r="L801" s="6"/>
     </row>
-    <row r="802" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="802" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="5"/>
       <c r="B802" s="5"/>
       <c r="C802" s="5"/>
@@ -15399,7 +15431,7 @@
       <c r="K802" s="6"/>
       <c r="L802" s="6"/>
     </row>
-    <row r="803" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="803" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="5"/>
       <c r="B803" s="5"/>
       <c r="C803" s="5"/>
@@ -15413,7 +15445,7 @@
       <c r="K803" s="6"/>
       <c r="L803" s="6"/>
     </row>
-    <row r="804" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="804" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="5"/>
       <c r="B804" s="5"/>
       <c r="C804" s="5"/>
@@ -15427,7 +15459,7 @@
       <c r="K804" s="6"/>
       <c r="L804" s="6"/>
     </row>
-    <row r="805" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="805" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="5"/>
       <c r="B805" s="5"/>
       <c r="C805" s="5"/>
@@ -15441,7 +15473,7 @@
       <c r="K805" s="6"/>
       <c r="L805" s="6"/>
     </row>
-    <row r="806" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="806" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="5"/>
       <c r="B806" s="5"/>
       <c r="C806" s="5"/>
@@ -15455,7 +15487,7 @@
       <c r="K806" s="6"/>
       <c r="L806" s="6"/>
     </row>
-    <row r="807" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="807" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="5"/>
       <c r="B807" s="5"/>
       <c r="C807" s="5"/>
@@ -15469,7 +15501,7 @@
       <c r="K807" s="6"/>
       <c r="L807" s="6"/>
     </row>
-    <row r="808" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="808" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="5"/>
       <c r="B808" s="5"/>
       <c r="C808" s="5"/>
@@ -15483,7 +15515,7 @@
       <c r="K808" s="6"/>
       <c r="L808" s="6"/>
     </row>
-    <row r="809" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="809" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="5"/>
       <c r="B809" s="5"/>
       <c r="C809" s="5"/>
@@ -15497,7 +15529,7 @@
       <c r="K809" s="6"/>
       <c r="L809" s="6"/>
     </row>
-    <row r="810" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="810" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="5"/>
       <c r="B810" s="5"/>
       <c r="C810" s="5"/>
@@ -15511,7 +15543,7 @@
       <c r="K810" s="6"/>
       <c r="L810" s="6"/>
     </row>
-    <row r="811" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="811" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="5"/>
       <c r="B811" s="5"/>
       <c r="C811" s="5"/>
@@ -15525,7 +15557,7 @@
       <c r="K811" s="6"/>
       <c r="L811" s="6"/>
     </row>
-    <row r="812" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="812" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="5"/>
       <c r="B812" s="5"/>
       <c r="C812" s="5"/>
@@ -15539,7 +15571,7 @@
       <c r="K812" s="6"/>
       <c r="L812" s="6"/>
     </row>
-    <row r="813" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="813" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="5"/>
       <c r="B813" s="5"/>
       <c r="C813" s="5"/>
@@ -15553,7 +15585,7 @@
       <c r="K813" s="6"/>
       <c r="L813" s="6"/>
     </row>
-    <row r="814" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="814" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="5"/>
       <c r="B814" s="5"/>
       <c r="C814" s="5"/>
@@ -15567,7 +15599,7 @@
       <c r="K814" s="6"/>
       <c r="L814" s="6"/>
     </row>
-    <row r="815" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="815" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A815" s="5"/>
       <c r="B815" s="5"/>
       <c r="C815" s="5"/>
@@ -15581,7 +15613,7 @@
       <c r="K815" s="6"/>
       <c r="L815" s="6"/>
     </row>
-    <row r="816" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="816" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A816" s="5"/>
       <c r="B816" s="5"/>
       <c r="C816" s="5"/>
@@ -15595,7 +15627,7 @@
       <c r="K816" s="6"/>
       <c r="L816" s="6"/>
     </row>
-    <row r="817" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="817" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A817" s="5"/>
       <c r="B817" s="5"/>
       <c r="C817" s="5"/>
@@ -15609,7 +15641,7 @@
       <c r="K817" s="6"/>
       <c r="L817" s="6"/>
     </row>
-    <row r="818" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="818" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A818" s="5"/>
       <c r="B818" s="5"/>
       <c r="C818" s="5"/>
@@ -15623,7 +15655,7 @@
       <c r="K818" s="6"/>
       <c r="L818" s="6"/>
     </row>
-    <row r="819" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="819" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A819" s="5"/>
       <c r="B819" s="5"/>
       <c r="C819" s="5"/>
@@ -15637,7 +15669,7 @@
       <c r="K819" s="6"/>
       <c r="L819" s="6"/>
     </row>
-    <row r="820" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="820" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A820" s="5"/>
       <c r="B820" s="5"/>
       <c r="C820" s="5"/>
@@ -15651,7 +15683,7 @@
       <c r="K820" s="6"/>
       <c r="L820" s="6"/>
     </row>
-    <row r="821" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="821" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A821" s="5"/>
       <c r="B821" s="5"/>
       <c r="C821" s="5"/>
@@ -15665,7 +15697,7 @@
       <c r="K821" s="6"/>
       <c r="L821" s="6"/>
     </row>
-    <row r="822" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="822" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A822" s="5"/>
       <c r="B822" s="5"/>
       <c r="C822" s="5"/>
@@ -15679,7 +15711,7 @@
       <c r="K822" s="6"/>
       <c r="L822" s="6"/>
     </row>
-    <row r="823" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="823" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A823" s="5"/>
       <c r="B823" s="5"/>
       <c r="C823" s="5"/>
@@ -15693,7 +15725,7 @@
       <c r="K823" s="6"/>
       <c r="L823" s="6"/>
     </row>
-    <row r="824" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="824" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A824" s="5"/>
       <c r="B824" s="5"/>
       <c r="C824" s="5"/>
@@ -15707,7 +15739,7 @@
       <c r="K824" s="6"/>
       <c r="L824" s="6"/>
     </row>
-    <row r="825" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="825" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A825" s="5"/>
       <c r="B825" s="5"/>
       <c r="C825" s="5"/>
@@ -15721,7 +15753,7 @@
       <c r="K825" s="6"/>
       <c r="L825" s="6"/>
     </row>
-    <row r="826" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="826" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A826" s="5"/>
       <c r="B826" s="5"/>
       <c r="C826" s="5"/>
@@ -15735,7 +15767,7 @@
       <c r="K826" s="6"/>
       <c r="L826" s="6"/>
     </row>
-    <row r="827" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="827" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A827" s="5"/>
       <c r="B827" s="5"/>
       <c r="C827" s="5"/>
@@ -15749,7 +15781,7 @@
       <c r="K827" s="6"/>
       <c r="L827" s="6"/>
     </row>
-    <row r="828" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="828" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A828" s="5"/>
       <c r="B828" s="5"/>
       <c r="C828" s="5"/>
@@ -15763,7 +15795,7 @@
       <c r="K828" s="6"/>
       <c r="L828" s="6"/>
     </row>
-    <row r="829" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="829" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A829" s="5"/>
       <c r="B829" s="5"/>
       <c r="C829" s="5"/>
@@ -15777,7 +15809,7 @@
       <c r="K829" s="6"/>
       <c r="L829" s="6"/>
     </row>
-    <row r="830" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="830" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A830" s="5"/>
       <c r="B830" s="5"/>
       <c r="C830" s="5"/>
@@ -15791,7 +15823,7 @@
       <c r="K830" s="6"/>
       <c r="L830" s="6"/>
     </row>
-    <row r="831" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="831" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A831" s="5"/>
       <c r="B831" s="5"/>
       <c r="C831" s="5"/>
@@ -15805,7 +15837,7 @@
       <c r="K831" s="6"/>
       <c r="L831" s="6"/>
     </row>
-    <row r="832" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="832" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A832" s="5"/>
       <c r="B832" s="5"/>
       <c r="C832" s="5"/>
@@ -15819,7 +15851,7 @@
       <c r="K832" s="6"/>
       <c r="L832" s="6"/>
     </row>
-    <row r="833" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="833" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A833" s="5"/>
       <c r="B833" s="5"/>
       <c r="C833" s="5"/>
@@ -15833,7 +15865,7 @@
       <c r="K833" s="6"/>
       <c r="L833" s="6"/>
     </row>
-    <row r="834" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="834" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A834" s="5"/>
       <c r="B834" s="5"/>
       <c r="C834" s="5"/>
@@ -15847,7 +15879,7 @@
       <c r="K834" s="6"/>
       <c r="L834" s="6"/>
     </row>
-    <row r="835" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="835" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A835" s="5"/>
       <c r="B835" s="5"/>
       <c r="C835" s="5"/>
@@ -15861,7 +15893,7 @@
       <c r="K835" s="6"/>
       <c r="L835" s="6"/>
     </row>
-    <row r="836" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="836" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A836" s="5"/>
       <c r="B836" s="5"/>
       <c r="C836" s="5"/>
@@ -15875,7 +15907,7 @@
       <c r="K836" s="6"/>
       <c r="L836" s="6"/>
     </row>
-    <row r="837" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="837" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A837" s="5"/>
       <c r="B837" s="5"/>
       <c r="C837" s="5"/>
@@ -15889,7 +15921,7 @@
       <c r="K837" s="6"/>
       <c r="L837" s="6"/>
     </row>
-    <row r="838" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="838" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A838" s="5"/>
       <c r="B838" s="5"/>
       <c r="C838" s="5"/>
@@ -15903,7 +15935,7 @@
       <c r="K838" s="6"/>
       <c r="L838" s="6"/>
     </row>
-    <row r="839" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="839" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A839" s="5"/>
       <c r="B839" s="5"/>
       <c r="C839" s="5"/>
@@ -15917,7 +15949,7 @@
       <c r="K839" s="6"/>
       <c r="L839" s="6"/>
     </row>
-    <row r="840" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="840" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A840" s="5"/>
       <c r="B840" s="5"/>
       <c r="C840" s="5"/>
@@ -15931,7 +15963,7 @@
       <c r="K840" s="6"/>
       <c r="L840" s="6"/>
     </row>
-    <row r="841" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="841" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A841" s="5"/>
       <c r="B841" s="5"/>
       <c r="C841" s="5"/>
@@ -15945,7 +15977,7 @@
       <c r="K841" s="6"/>
       <c r="L841" s="6"/>
     </row>
-    <row r="842" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="842" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A842" s="5"/>
       <c r="B842" s="5"/>
       <c r="C842" s="5"/>
@@ -15959,7 +15991,7 @@
       <c r="K842" s="6"/>
       <c r="L842" s="6"/>
     </row>
-    <row r="843" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="843" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A843" s="5"/>
       <c r="B843" s="5"/>
       <c r="C843" s="5"/>
@@ -15973,7 +16005,7 @@
       <c r="K843" s="6"/>
       <c r="L843" s="6"/>
     </row>
-    <row r="844" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="844" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A844" s="5"/>
       <c r="B844" s="5"/>
       <c r="C844" s="5"/>
@@ -15987,7 +16019,7 @@
       <c r="K844" s="6"/>
       <c r="L844" s="6"/>
     </row>
-    <row r="845" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="845" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A845" s="5"/>
       <c r="B845" s="5"/>
       <c r="C845" s="5"/>
@@ -16001,7 +16033,7 @@
       <c r="K845" s="6"/>
       <c r="L845" s="6"/>
     </row>
-    <row r="846" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="846" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A846" s="5"/>
       <c r="B846" s="5"/>
       <c r="C846" s="5"/>
@@ -16015,7 +16047,7 @@
       <c r="K846" s="6"/>
       <c r="L846" s="6"/>
     </row>
-    <row r="847" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="847" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A847" s="5"/>
       <c r="B847" s="5"/>
       <c r="C847" s="5"/>
@@ -16029,7 +16061,7 @@
       <c r="K847" s="6"/>
       <c r="L847" s="6"/>
     </row>
-    <row r="848" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="848" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A848" s="5"/>
       <c r="B848" s="5"/>
       <c r="C848" s="5"/>
@@ -16043,7 +16075,7 @@
       <c r="K848" s="6"/>
       <c r="L848" s="6"/>
     </row>
-    <row r="849" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="849" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A849" s="5"/>
       <c r="B849" s="5"/>
       <c r="C849" s="5"/>
@@ -16057,7 +16089,7 @@
       <c r="K849" s="6"/>
       <c r="L849" s="6"/>
     </row>
-    <row r="850" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="850" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A850" s="5"/>
       <c r="B850" s="5"/>
       <c r="C850" s="5"/>
@@ -16071,7 +16103,7 @@
       <c r="K850" s="6"/>
       <c r="L850" s="6"/>
     </row>
-    <row r="851" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="851" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A851" s="5"/>
       <c r="B851" s="5"/>
       <c r="C851" s="5"/>
@@ -16085,7 +16117,7 @@
       <c r="K851" s="6"/>
       <c r="L851" s="6"/>
     </row>
-    <row r="852" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="852" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A852" s="5"/>
       <c r="B852" s="5"/>
       <c r="C852" s="5"/>
@@ -16099,7 +16131,7 @@
       <c r="K852" s="6"/>
       <c r="L852" s="6"/>
     </row>
-    <row r="853" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="853" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A853" s="5"/>
       <c r="B853" s="5"/>
       <c r="C853" s="5"/>
@@ -16113,7 +16145,7 @@
       <c r="K853" s="6"/>
       <c r="L853" s="6"/>
     </row>
-    <row r="854" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="854" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A854" s="5"/>
       <c r="B854" s="5"/>
       <c r="C854" s="5"/>
@@ -16127,7 +16159,7 @@
       <c r="K854" s="6"/>
       <c r="L854" s="6"/>
     </row>
-    <row r="855" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="855" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A855" s="5"/>
       <c r="B855" s="5"/>
       <c r="C855" s="5"/>
@@ -16141,7 +16173,7 @@
       <c r="K855" s="6"/>
       <c r="L855" s="6"/>
     </row>
-    <row r="856" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="856" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A856" s="5"/>
       <c r="B856" s="5"/>
       <c r="C856" s="5"/>
@@ -16155,7 +16187,7 @@
       <c r="K856" s="6"/>
       <c r="L856" s="6"/>
     </row>
-    <row r="857" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="857" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A857" s="5"/>
       <c r="B857" s="5"/>
       <c r="C857" s="5"/>
@@ -16169,7 +16201,7 @@
       <c r="K857" s="6"/>
       <c r="L857" s="6"/>
     </row>
-    <row r="858" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="858" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A858" s="5"/>
       <c r="B858" s="5"/>
       <c r="C858" s="5"/>
@@ -16183,7 +16215,7 @@
       <c r="K858" s="6"/>
       <c r="L858" s="6"/>
     </row>
-    <row r="859" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="859" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A859" s="5"/>
       <c r="B859" s="5"/>
       <c r="C859" s="5"/>
@@ -16197,7 +16229,7 @@
       <c r="K859" s="6"/>
       <c r="L859" s="6"/>
     </row>
-    <row r="860" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="860" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A860" s="5"/>
       <c r="B860" s="5"/>
       <c r="C860" s="5"/>
@@ -16211,7 +16243,7 @@
       <c r="K860" s="6"/>
       <c r="L860" s="6"/>
     </row>
-    <row r="861" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="861" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A861" s="5"/>
       <c r="B861" s="5"/>
       <c r="C861" s="5"/>
@@ -16225,7 +16257,7 @@
       <c r="K861" s="6"/>
       <c r="L861" s="6"/>
     </row>
-    <row r="862" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="862" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A862" s="5"/>
       <c r="B862" s="5"/>
       <c r="C862" s="5"/>
@@ -16239,7 +16271,7 @@
       <c r="K862" s="6"/>
       <c r="L862" s="6"/>
     </row>
-    <row r="863" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="863" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A863" s="5"/>
       <c r="B863" s="5"/>
       <c r="C863" s="5"/>
@@ -16253,7 +16285,7 @@
       <c r="K863" s="6"/>
       <c r="L863" s="6"/>
     </row>
-    <row r="864" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="864" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A864" s="5"/>
       <c r="B864" s="5"/>
       <c r="C864" s="5"/>
@@ -16267,7 +16299,7 @@
       <c r="K864" s="6"/>
       <c r="L864" s="6"/>
     </row>
-    <row r="865" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="865" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A865" s="5"/>
       <c r="B865" s="5"/>
       <c r="C865" s="5"/>
@@ -16281,7 +16313,7 @@
       <c r="K865" s="6"/>
       <c r="L865" s="6"/>
     </row>
-    <row r="866" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="866" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A866" s="5"/>
       <c r="B866" s="5"/>
       <c r="C866" s="5"/>
@@ -16295,7 +16327,7 @@
       <c r="K866" s="6"/>
       <c r="L866" s="6"/>
     </row>
-    <row r="867" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="867" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A867" s="5"/>
       <c r="B867" s="5"/>
       <c r="C867" s="5"/>
@@ -16309,7 +16341,7 @@
       <c r="K867" s="6"/>
       <c r="L867" s="6"/>
     </row>
-    <row r="868" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="868" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A868" s="5"/>
       <c r="B868" s="5"/>
       <c r="C868" s="5"/>
@@ -16323,7 +16355,7 @@
       <c r="K868" s="6"/>
       <c r="L868" s="6"/>
     </row>
-    <row r="869" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="869" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A869" s="5"/>
       <c r="B869" s="5"/>
       <c r="C869" s="5"/>
@@ -16337,7 +16369,7 @@
       <c r="K869" s="6"/>
       <c r="L869" s="6"/>
     </row>
-    <row r="870" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="870" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A870" s="5"/>
       <c r="B870" s="5"/>
       <c r="C870" s="5"/>
@@ -16351,7 +16383,7 @@
       <c r="K870" s="6"/>
       <c r="L870" s="6"/>
     </row>
-    <row r="871" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="871" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A871" s="5"/>
       <c r="B871" s="5"/>
       <c r="C871" s="5"/>
@@ -16365,7 +16397,7 @@
       <c r="K871" s="6"/>
       <c r="L871" s="6"/>
     </row>
-    <row r="872" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="872" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A872" s="5"/>
       <c r="B872" s="5"/>
       <c r="C872" s="5"/>
@@ -16379,7 +16411,7 @@
       <c r="K872" s="6"/>
       <c r="L872" s="6"/>
     </row>
-    <row r="873" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="873" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A873" s="5"/>
       <c r="B873" s="5"/>
       <c r="C873" s="5"/>
@@ -16393,7 +16425,7 @@
       <c r="K873" s="6"/>
       <c r="L873" s="6"/>
     </row>
-    <row r="874" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="874" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A874" s="5"/>
       <c r="B874" s="5"/>
       <c r="C874" s="5"/>
@@ -16407,7 +16439,7 @@
       <c r="K874" s="6"/>
       <c r="L874" s="6"/>
     </row>
-    <row r="875" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="875" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A875" s="5"/>
       <c r="B875" s="5"/>
       <c r="C875" s="5"/>
@@ -16421,7 +16453,7 @@
       <c r="K875" s="6"/>
       <c r="L875" s="6"/>
     </row>
-    <row r="876" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="876" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A876" s="5"/>
       <c r="B876" s="5"/>
       <c r="C876" s="5"/>
@@ -16435,7 +16467,7 @@
       <c r="K876" s="6"/>
       <c r="L876" s="6"/>
     </row>
-    <row r="877" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="877" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A877" s="5"/>
       <c r="B877" s="5"/>
       <c r="C877" s="5"/>
@@ -16449,7 +16481,7 @@
       <c r="K877" s="6"/>
       <c r="L877" s="6"/>
     </row>
-    <row r="878" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="878" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A878" s="5"/>
       <c r="B878" s="5"/>
       <c r="C878" s="5"/>
@@ -16463,7 +16495,7 @@
       <c r="K878" s="6"/>
       <c r="L878" s="6"/>
     </row>
-    <row r="879" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="879" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A879" s="5"/>
       <c r="B879" s="5"/>
       <c r="C879" s="5"/>
@@ -16477,7 +16509,7 @@
       <c r="K879" s="6"/>
       <c r="L879" s="6"/>
     </row>
-    <row r="880" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="880" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A880" s="5"/>
       <c r="B880" s="5"/>
       <c r="C880" s="5"/>
@@ -16491,7 +16523,7 @@
       <c r="K880" s="6"/>
       <c r="L880" s="6"/>
     </row>
-    <row r="881" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="881" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A881" s="5"/>
       <c r="B881" s="5"/>
       <c r="C881" s="5"/>
@@ -16505,7 +16537,7 @@
       <c r="K881" s="6"/>
       <c r="L881" s="6"/>
     </row>
-    <row r="882" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="882" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A882" s="5"/>
       <c r="B882" s="5"/>
       <c r="C882" s="5"/>
@@ -16519,7 +16551,7 @@
       <c r="K882" s="6"/>
       <c r="L882" s="6"/>
     </row>
-    <row r="883" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="883" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A883" s="5"/>
       <c r="B883" s="5"/>
       <c r="C883" s="5"/>
@@ -16533,7 +16565,7 @@
       <c r="K883" s="6"/>
       <c r="L883" s="6"/>
     </row>
-    <row r="884" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="884" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A884" s="5"/>
       <c r="B884" s="5"/>
       <c r="C884" s="5"/>
@@ -16547,7 +16579,7 @@
       <c r="K884" s="6"/>
       <c r="L884" s="6"/>
     </row>
-    <row r="885" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="885" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A885" s="5"/>
       <c r="B885" s="5"/>
       <c r="C885" s="5"/>
@@ -16561,7 +16593,7 @@
       <c r="K885" s="6"/>
       <c r="L885" s="6"/>
     </row>
-    <row r="886" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="886" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A886" s="5"/>
       <c r="B886" s="5"/>
       <c r="C886" s="5"/>
@@ -16575,7 +16607,7 @@
       <c r="K886" s="6"/>
       <c r="L886" s="6"/>
     </row>
-    <row r="887" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="887" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A887" s="5"/>
       <c r="B887" s="5"/>
       <c r="C887" s="5"/>
@@ -16589,7 +16621,7 @@
       <c r="K887" s="6"/>
       <c r="L887" s="6"/>
     </row>
-    <row r="888" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="888" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A888" s="5"/>
       <c r="B888" s="5"/>
       <c r="C888" s="5"/>
@@ -16603,7 +16635,7 @@
       <c r="K888" s="6"/>
       <c r="L888" s="6"/>
     </row>
-    <row r="889" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="889" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A889" s="5"/>
       <c r="B889" s="5"/>
       <c r="C889" s="5"/>
@@ -16617,7 +16649,7 @@
       <c r="K889" s="6"/>
       <c r="L889" s="6"/>
     </row>
-    <row r="890" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="890" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A890" s="5"/>
       <c r="B890" s="5"/>
       <c r="C890" s="5"/>
@@ -16631,7 +16663,7 @@
       <c r="K890" s="6"/>
       <c r="L890" s="6"/>
     </row>
-    <row r="891" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="891" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A891" s="5"/>
       <c r="B891" s="5"/>
       <c r="C891" s="5"/>
@@ -16645,7 +16677,7 @@
       <c r="K891" s="6"/>
       <c r="L891" s="6"/>
     </row>
-    <row r="892" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="892" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A892" s="5"/>
       <c r="B892" s="5"/>
       <c r="C892" s="5"/>
@@ -16659,7 +16691,7 @@
       <c r="K892" s="6"/>
       <c r="L892" s="6"/>
     </row>
-    <row r="893" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="893" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A893" s="5"/>
       <c r="B893" s="5"/>
       <c r="C893" s="5"/>
@@ -16673,7 +16705,7 @@
       <c r="K893" s="6"/>
       <c r="L893" s="6"/>
     </row>
-    <row r="894" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="894" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A894" s="5"/>
       <c r="B894" s="5"/>
       <c r="C894" s="5"/>
@@ -16687,7 +16719,7 @@
       <c r="K894" s="6"/>
       <c r="L894" s="6"/>
     </row>
-    <row r="895" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="895" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A895" s="5"/>
       <c r="B895" s="5"/>
       <c r="C895" s="5"/>
@@ -16701,7 +16733,7 @@
       <c r="K895" s="6"/>
       <c r="L895" s="6"/>
     </row>
-    <row r="896" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="896" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A896" s="5"/>
       <c r="B896" s="5"/>
       <c r="C896" s="5"/>
@@ -16715,7 +16747,7 @@
       <c r="K896" s="6"/>
       <c r="L896" s="6"/>
     </row>
-    <row r="897" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="897" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A897" s="5"/>
       <c r="B897" s="5"/>
       <c r="C897" s="5"/>
@@ -16729,7 +16761,7 @@
       <c r="K897" s="6"/>
       <c r="L897" s="6"/>
     </row>
-    <row r="898" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="898" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A898" s="5"/>
       <c r="B898" s="5"/>
       <c r="C898" s="5"/>
@@ -16743,7 +16775,7 @@
       <c r="K898" s="6"/>
       <c r="L898" s="6"/>
     </row>
-    <row r="899" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="899" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A899" s="5"/>
       <c r="B899" s="5"/>
       <c r="C899" s="5"/>
@@ -16757,7 +16789,7 @@
       <c r="K899" s="6"/>
       <c r="L899" s="6"/>
     </row>
-    <row r="900" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="900" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A900" s="5"/>
       <c r="B900" s="5"/>
       <c r="C900" s="5"/>
@@ -16771,7 +16803,7 @@
       <c r="K900" s="6"/>
       <c r="L900" s="6"/>
     </row>
-    <row r="901" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="901" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A901" s="5"/>
       <c r="B901" s="5"/>
       <c r="C901" s="5"/>
@@ -16785,7 +16817,7 @@
       <c r="K901" s="6"/>
       <c r="L901" s="6"/>
     </row>
-    <row r="902" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="902" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A902" s="5"/>
       <c r="B902" s="5"/>
       <c r="C902" s="5"/>
@@ -16799,7 +16831,7 @@
       <c r="K902" s="6"/>
       <c r="L902" s="6"/>
     </row>
-    <row r="903" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="903" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A903" s="5"/>
       <c r="B903" s="5"/>
       <c r="C903" s="5"/>
@@ -16813,7 +16845,7 @@
       <c r="K903" s="6"/>
       <c r="L903" s="6"/>
     </row>
-    <row r="904" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="904" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A904" s="5"/>
       <c r="B904" s="5"/>
       <c r="C904" s="5"/>
@@ -16827,7 +16859,7 @@
       <c r="K904" s="6"/>
       <c r="L904" s="6"/>
     </row>
-    <row r="905" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="905" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A905" s="5"/>
       <c r="B905" s="5"/>
       <c r="C905" s="5"/>
@@ -16841,7 +16873,7 @@
       <c r="K905" s="6"/>
       <c r="L905" s="6"/>
     </row>
-    <row r="906" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="906" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A906" s="5"/>
       <c r="B906" s="5"/>
       <c r="C906" s="5"/>
@@ -16855,7 +16887,7 @@
       <c r="K906" s="6"/>
       <c r="L906" s="6"/>
     </row>
-    <row r="907" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="907" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A907" s="5"/>
       <c r="B907" s="5"/>
       <c r="C907" s="5"/>
@@ -16869,7 +16901,7 @@
       <c r="K907" s="6"/>
       <c r="L907" s="6"/>
     </row>
-    <row r="908" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="908" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A908" s="5"/>
       <c r="B908" s="5"/>
       <c r="C908" s="5"/>
@@ -16883,7 +16915,7 @@
       <c r="K908" s="6"/>
       <c r="L908" s="6"/>
     </row>
-    <row r="909" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="909" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A909" s="5"/>
       <c r="B909" s="5"/>
       <c r="C909" s="5"/>
@@ -16897,7 +16929,7 @@
       <c r="K909" s="6"/>
       <c r="L909" s="6"/>
     </row>
-    <row r="910" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="910" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A910" s="5"/>
       <c r="B910" s="5"/>
       <c r="C910" s="5"/>
@@ -16911,7 +16943,7 @@
       <c r="K910" s="6"/>
       <c r="L910" s="6"/>
     </row>
-    <row r="911" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="911" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A911" s="5"/>
       <c r="B911" s="5"/>
       <c r="C911" s="5"/>
@@ -16925,7 +16957,7 @@
       <c r="K911" s="6"/>
       <c r="L911" s="6"/>
     </row>
-    <row r="912" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="912" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A912" s="5"/>
       <c r="B912" s="5"/>
       <c r="C912" s="5"/>
@@ -16939,7 +16971,7 @@
       <c r="K912" s="6"/>
       <c r="L912" s="6"/>
     </row>
-    <row r="913" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="913" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A913" s="5"/>
       <c r="B913" s="5"/>
       <c r="C913" s="5"/>
@@ -16953,7 +16985,7 @@
       <c r="K913" s="6"/>
       <c r="L913" s="6"/>
     </row>
-    <row r="914" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="914" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A914" s="5"/>
       <c r="B914" s="5"/>
       <c r="C914" s="5"/>
@@ -16967,7 +16999,7 @@
       <c r="K914" s="6"/>
       <c r="L914" s="6"/>
     </row>
-    <row r="915" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="915" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A915" s="5"/>
       <c r="B915" s="5"/>
       <c r="C915" s="5"/>
@@ -16981,7 +17013,7 @@
       <c r="K915" s="6"/>
       <c r="L915" s="6"/>
     </row>
-    <row r="916" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="916" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A916" s="5"/>
       <c r="B916" s="5"/>
       <c r="C916" s="5"/>
@@ -16995,7 +17027,7 @@
       <c r="K916" s="6"/>
       <c r="L916" s="6"/>
     </row>
-    <row r="917" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="917" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A917" s="5"/>
       <c r="B917" s="5"/>
       <c r="C917" s="5"/>
@@ -17009,7 +17041,7 @@
       <c r="K917" s="6"/>
       <c r="L917" s="6"/>
     </row>
-    <row r="918" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="918" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A918" s="5"/>
       <c r="B918" s="5"/>
       <c r="C918" s="5"/>
@@ -17023,7 +17055,7 @@
       <c r="K918" s="6"/>
       <c r="L918" s="6"/>
     </row>
-    <row r="919" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="919" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A919" s="5"/>
       <c r="B919" s="5"/>
       <c r="C919" s="5"/>
@@ -17037,7 +17069,7 @@
       <c r="K919" s="6"/>
       <c r="L919" s="6"/>
     </row>
-    <row r="920" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="920" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A920" s="5"/>
       <c r="B920" s="5"/>
       <c r="C920" s="5"/>
@@ -17051,7 +17083,7 @@
       <c r="K920" s="6"/>
       <c r="L920" s="6"/>
     </row>
-    <row r="921" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="921" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A921" s="5"/>
       <c r="B921" s="5"/>
       <c r="C921" s="5"/>
@@ -17065,7 +17097,7 @@
       <c r="K921" s="6"/>
       <c r="L921" s="6"/>
     </row>
-    <row r="922" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="922" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A922" s="5"/>
       <c r="B922" s="5"/>
       <c r="C922" s="5"/>
@@ -17079,7 +17111,7 @@
       <c r="K922" s="6"/>
       <c r="L922" s="6"/>
     </row>
-    <row r="923" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="923" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A923" s="5"/>
       <c r="B923" s="5"/>
       <c r="C923" s="5"/>
@@ -17093,7 +17125,7 @@
       <c r="K923" s="6"/>
       <c r="L923" s="6"/>
     </row>
-    <row r="924" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="924" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A924" s="5"/>
       <c r="B924" s="5"/>
       <c r="C924" s="5"/>
@@ -17107,7 +17139,7 @@
       <c r="K924" s="6"/>
       <c r="L924" s="6"/>
     </row>
-    <row r="925" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="925" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A925" s="5"/>
       <c r="B925" s="5"/>
       <c r="C925" s="5"/>
@@ -17121,7 +17153,7 @@
       <c r="K925" s="6"/>
       <c r="L925" s="6"/>
     </row>
-    <row r="926" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="926" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A926" s="5"/>
       <c r="B926" s="5"/>
       <c r="C926" s="5"/>
@@ -17135,7 +17167,7 @@
       <c r="K926" s="6"/>
       <c r="L926" s="6"/>
     </row>
-    <row r="927" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="927" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A927" s="5"/>
       <c r="B927" s="5"/>
       <c r="C927" s="5"/>
@@ -17149,7 +17181,7 @@
       <c r="K927" s="6"/>
       <c r="L927" s="6"/>
     </row>
-    <row r="928" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="928" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A928" s="5"/>
       <c r="B928" s="5"/>
       <c r="C928" s="5"/>
@@ -17163,7 +17195,7 @@
       <c r="K928" s="6"/>
       <c r="L928" s="6"/>
     </row>
-    <row r="929" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="929" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A929" s="5"/>
       <c r="B929" s="5"/>
       <c r="C929" s="5"/>
@@ -17177,7 +17209,7 @@
       <c r="K929" s="6"/>
       <c r="L929" s="6"/>
     </row>
-    <row r="930" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="930" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A930" s="5"/>
       <c r="B930" s="5"/>
       <c r="C930" s="5"/>
@@ -17191,7 +17223,7 @@
       <c r="K930" s="6"/>
       <c r="L930" s="6"/>
     </row>
-    <row r="931" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="931" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A931" s="5"/>
       <c r="B931" s="5"/>
       <c r="C931" s="5"/>
@@ -17205,7 +17237,7 @@
       <c r="K931" s="6"/>
       <c r="L931" s="6"/>
     </row>
-    <row r="932" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="932" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A932" s="5"/>
       <c r="B932" s="5"/>
       <c r="C932" s="5"/>
@@ -17219,7 +17251,7 @@
       <c r="K932" s="6"/>
       <c r="L932" s="6"/>
     </row>
-    <row r="933" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="933" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A933" s="5"/>
       <c r="B933" s="5"/>
       <c r="C933" s="5"/>
@@ -17233,7 +17265,7 @@
       <c r="K933" s="6"/>
       <c r="L933" s="6"/>
     </row>
-    <row r="934" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="934" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A934" s="5"/>
       <c r="B934" s="5"/>
       <c r="C934" s="5"/>
@@ -17247,7 +17279,7 @@
       <c r="K934" s="6"/>
       <c r="L934" s="6"/>
     </row>
-    <row r="935" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="935" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A935" s="5"/>
       <c r="B935" s="5"/>
       <c r="C935" s="5"/>
@@ -17261,7 +17293,7 @@
       <c r="K935" s="6"/>
       <c r="L935" s="6"/>
     </row>
-    <row r="936" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="936" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A936" s="5"/>
       <c r="B936" s="5"/>
       <c r="C936" s="5"/>
@@ -17275,7 +17307,7 @@
       <c r="K936" s="6"/>
       <c r="L936" s="6"/>
     </row>
-    <row r="937" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="937" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A937" s="5"/>
       <c r="B937" s="5"/>
       <c r="C937" s="5"/>
@@ -17289,7 +17321,7 @@
       <c r="K937" s="6"/>
       <c r="L937" s="6"/>
     </row>
-    <row r="938" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="938" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A938" s="5"/>
       <c r="B938" s="5"/>
       <c r="C938" s="5"/>
@@ -17303,7 +17335,7 @@
       <c r="K938" s="6"/>
       <c r="L938" s="6"/>
     </row>
-    <row r="939" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="939" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A939" s="5"/>
       <c r="B939" s="5"/>
       <c r="C939" s="5"/>
@@ -17317,7 +17349,7 @@
       <c r="K939" s="6"/>
       <c r="L939" s="6"/>
     </row>
-    <row r="940" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="940" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A940" s="5"/>
       <c r="B940" s="5"/>
       <c r="C940" s="5"/>
@@ -17331,7 +17363,7 @@
       <c r="K940" s="6"/>
       <c r="L940" s="6"/>
     </row>
-    <row r="941" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="941" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A941" s="5"/>
       <c r="B941" s="5"/>
       <c r="C941" s="5"/>
@@ -17345,7 +17377,7 @@
       <c r="K941" s="6"/>
       <c r="L941" s="6"/>
     </row>
-    <row r="942" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="942" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A942" s="5"/>
       <c r="B942" s="5"/>
       <c r="C942" s="5"/>
@@ -17359,7 +17391,7 @@
       <c r="K942" s="6"/>
       <c r="L942" s="6"/>
     </row>
-    <row r="943" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="943" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A943" s="5"/>
       <c r="B943" s="5"/>
       <c r="C943" s="5"/>
@@ -17373,7 +17405,7 @@
       <c r="K943" s="6"/>
       <c r="L943" s="6"/>
     </row>
-    <row r="944" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="944" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A944" s="5"/>
       <c r="B944" s="5"/>
       <c r="C944" s="5"/>
@@ -17387,7 +17419,7 @@
       <c r="K944" s="6"/>
       <c r="L944" s="6"/>
     </row>
-    <row r="945" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="945" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A945" s="5"/>
       <c r="B945" s="5"/>
       <c r="C945" s="5"/>
@@ -17401,7 +17433,7 @@
       <c r="K945" s="6"/>
       <c r="L945" s="6"/>
     </row>
-    <row r="946" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="946" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A946" s="5"/>
       <c r="B946" s="5"/>
       <c r="C946" s="5"/>
@@ -17415,7 +17447,7 @@
       <c r="K946" s="6"/>
       <c r="L946" s="6"/>
     </row>
-    <row r="947" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="947" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A947" s="5"/>
       <c r="B947" s="5"/>
       <c r="C947" s="5"/>
@@ -17429,7 +17461,7 @@
       <c r="K947" s="6"/>
       <c r="L947" s="6"/>
     </row>
-    <row r="948" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="948" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A948" s="5"/>
       <c r="B948" s="5"/>
       <c r="C948" s="5"/>
@@ -17443,7 +17475,7 @@
       <c r="K948" s="6"/>
       <c r="L948" s="6"/>
     </row>
-    <row r="949" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="949" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A949" s="5"/>
       <c r="B949" s="5"/>
       <c r="C949" s="5"/>
@@ -17457,7 +17489,7 @@
       <c r="K949" s="6"/>
       <c r="L949" s="6"/>
     </row>
-    <row r="950" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="950" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A950" s="5"/>
       <c r="B950" s="5"/>
       <c r="C950" s="5"/>
@@ -17471,7 +17503,7 @@
       <c r="K950" s="6"/>
       <c r="L950" s="6"/>
     </row>
-    <row r="951" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="951" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A951" s="5"/>
       <c r="B951" s="5"/>
       <c r="C951" s="5"/>
@@ -17485,7 +17517,7 @@
       <c r="K951" s="6"/>
       <c r="L951" s="6"/>
     </row>
-    <row r="952" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="952" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A952" s="5"/>
       <c r="B952" s="5"/>
       <c r="C952" s="5"/>
@@ -17499,7 +17531,7 @@
       <c r="K952" s="6"/>
       <c r="L952" s="6"/>
     </row>
-    <row r="953" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="953" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A953" s="5"/>
       <c r="B953" s="5"/>
       <c r="C953" s="5"/>
@@ -17513,7 +17545,7 @@
       <c r="K953" s="6"/>
       <c r="L953" s="6"/>
     </row>
-    <row r="954" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="954" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A954" s="5"/>
       <c r="B954" s="5"/>
       <c r="C954" s="5"/>
@@ -17527,7 +17559,7 @@
       <c r="K954" s="6"/>
       <c r="L954" s="6"/>
     </row>
-    <row r="955" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="955" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A955" s="5"/>
       <c r="B955" s="5"/>
       <c r="C955" s="5"/>
@@ -17541,7 +17573,7 @@
       <c r="K955" s="6"/>
       <c r="L955" s="6"/>
     </row>
-    <row r="956" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="956" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A956" s="5"/>
       <c r="B956" s="5"/>
       <c r="C956" s="5"/>
@@ -17555,7 +17587,7 @@
       <c r="K956" s="6"/>
       <c r="L956" s="6"/>
     </row>
-    <row r="957" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="957" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A957" s="5"/>
       <c r="B957" s="5"/>
       <c r="C957" s="5"/>
@@ -17569,7 +17601,7 @@
       <c r="K957" s="6"/>
       <c r="L957" s="6"/>
     </row>
-    <row r="958" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="958" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A958" s="5"/>
       <c r="B958" s="5"/>
       <c r="C958" s="5"/>
@@ -17583,7 +17615,7 @@
       <c r="K958" s="6"/>
       <c r="L958" s="6"/>
     </row>
-    <row r="959" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="959" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A959" s="5"/>
       <c r="B959" s="5"/>
       <c r="C959" s="5"/>
@@ -17597,7 +17629,7 @@
       <c r="K959" s="6"/>
       <c r="L959" s="6"/>
     </row>
-    <row r="960" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="960" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A960" s="5"/>
       <c r="B960" s="5"/>
       <c r="C960" s="5"/>
@@ -17611,7 +17643,7 @@
       <c r="K960" s="6"/>
       <c r="L960" s="6"/>
     </row>
-    <row r="961" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="961" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A961" s="5"/>
       <c r="B961" s="5"/>
       <c r="C961" s="5"/>
@@ -17625,7 +17657,7 @@
       <c r="K961" s="6"/>
       <c r="L961" s="6"/>
     </row>
-    <row r="962" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="962" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A962" s="5"/>
       <c r="B962" s="5"/>
       <c r="C962" s="5"/>
@@ -17639,7 +17671,7 @@
       <c r="K962" s="6"/>
       <c r="L962" s="6"/>
     </row>
-    <row r="963" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="963" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A963" s="5"/>
       <c r="B963" s="5"/>
       <c r="C963" s="5"/>
@@ -17653,7 +17685,7 @@
       <c r="K963" s="6"/>
       <c r="L963" s="6"/>
     </row>
-    <row r="964" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="964" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A964" s="5"/>
       <c r="B964" s="5"/>
       <c r="C964" s="5"/>
@@ -17667,7 +17699,7 @@
       <c r="K964" s="6"/>
       <c r="L964" s="6"/>
     </row>
-    <row r="965" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="965" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A965" s="5"/>
       <c r="B965" s="5"/>
       <c r="C965" s="5"/>
@@ -17681,7 +17713,7 @@
       <c r="K965" s="6"/>
       <c r="L965" s="6"/>
     </row>
-    <row r="966" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="966" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A966" s="5"/>
       <c r="B966" s="5"/>
       <c r="C966" s="5"/>
@@ -17695,7 +17727,7 @@
       <c r="K966" s="6"/>
       <c r="L966" s="6"/>
     </row>
-    <row r="967" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="967" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A967" s="5"/>
       <c r="B967" s="5"/>
       <c r="C967" s="5"/>
@@ -17709,7 +17741,7 @@
       <c r="K967" s="6"/>
       <c r="L967" s="6"/>
     </row>
-    <row r="968" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="968" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A968" s="5"/>
       <c r="B968" s="5"/>
       <c r="C968" s="5"/>
@@ -17723,7 +17755,7 @@
       <c r="K968" s="6"/>
       <c r="L968" s="6"/>
     </row>
-    <row r="969" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="969" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A969" s="5"/>
       <c r="B969" s="5"/>
       <c r="C969" s="5"/>
@@ -17737,7 +17769,7 @@
       <c r="K969" s="6"/>
       <c r="L969" s="6"/>
     </row>
-    <row r="970" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="970" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A970" s="5"/>
       <c r="B970" s="5"/>
       <c r="C970" s="5"/>
@@ -17751,7 +17783,7 @@
       <c r="K970" s="6"/>
       <c r="L970" s="6"/>
     </row>
-    <row r="971" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="971" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A971" s="5"/>
       <c r="B971" s="5"/>
       <c r="C971" s="5"/>
@@ -17765,7 +17797,7 @@
       <c r="K971" s="6"/>
       <c r="L971" s="6"/>
     </row>
-    <row r="972" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="972" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A972" s="5"/>
       <c r="B972" s="5"/>
       <c r="C972" s="5"/>
@@ -17779,7 +17811,7 @@
       <c r="K972" s="6"/>
       <c r="L972" s="6"/>
     </row>
-    <row r="973" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="973" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A973" s="5"/>
       <c r="B973" s="5"/>
       <c r="C973" s="5"/>
@@ -17793,7 +17825,7 @@
       <c r="K973" s="6"/>
       <c r="L973" s="6"/>
     </row>
-    <row r="974" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="974" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A974" s="5"/>
       <c r="B974" s="5"/>
       <c r="C974" s="5"/>
@@ -17807,7 +17839,7 @@
       <c r="K974" s="6"/>
       <c r="L974" s="6"/>
     </row>
-    <row r="975" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="975" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A975" s="5"/>
       <c r="B975" s="5"/>
       <c r="C975" s="5"/>
@@ -17821,7 +17853,7 @@
       <c r="K975" s="6"/>
       <c r="L975" s="6"/>
     </row>
-    <row r="976" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="976" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A976" s="5"/>
       <c r="B976" s="5"/>
       <c r="C976" s="5"/>
@@ -17835,7 +17867,7 @@
       <c r="K976" s="6"/>
       <c r="L976" s="6"/>
     </row>
-    <row r="977" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="977" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A977" s="5"/>
       <c r="B977" s="5"/>
       <c r="C977" s="5"/>
@@ -17849,7 +17881,7 @@
       <c r="K977" s="6"/>
       <c r="L977" s="6"/>
     </row>
-    <row r="978" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="978" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A978" s="5"/>
       <c r="B978" s="5"/>
       <c r="C978" s="5"/>
@@ -17863,7 +17895,7 @@
       <c r="K978" s="6"/>
       <c r="L978" s="6"/>
     </row>
-    <row r="979" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="979" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A979" s="5"/>
       <c r="B979" s="5"/>
       <c r="C979" s="5"/>
@@ -17877,7 +17909,7 @@
       <c r="K979" s="6"/>
       <c r="L979" s="6"/>
     </row>
-    <row r="980" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="980" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A980" s="5"/>
       <c r="B980" s="5"/>
       <c r="C980" s="5"/>
@@ -17891,7 +17923,7 @@
       <c r="K980" s="6"/>
       <c r="L980" s="6"/>
     </row>
-    <row r="981" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="981" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A981" s="5"/>
       <c r="B981" s="5"/>
       <c r="C981" s="5"/>
@@ -17905,7 +17937,7 @@
       <c r="K981" s="6"/>
       <c r="L981" s="6"/>
     </row>
-    <row r="982" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="982" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A982" s="5"/>
       <c r="B982" s="5"/>
       <c r="C982" s="5"/>
@@ -17919,7 +17951,7 @@
       <c r="K982" s="6"/>
       <c r="L982" s="6"/>
     </row>
-    <row r="983" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="983" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A983" s="5"/>
       <c r="B983" s="5"/>
       <c r="C983" s="5"/>
@@ -17933,7 +17965,7 @@
       <c r="K983" s="6"/>
       <c r="L983" s="6"/>
     </row>
-    <row r="984" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="984" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A984" s="5"/>
       <c r="B984" s="5"/>
       <c r="C984" s="5"/>
@@ -17947,7 +17979,7 @@
       <c r="K984" s="6"/>
       <c r="L984" s="6"/>
     </row>
-    <row r="985" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="985" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A985" s="5"/>
       <c r="B985" s="5"/>
       <c r="C985" s="5"/>
@@ -17961,7 +17993,7 @@
       <c r="K985" s="6"/>
       <c r="L985" s="6"/>
     </row>
-    <row r="986" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="986" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A986" s="5"/>
       <c r="B986" s="5"/>
       <c r="C986" s="5"/>
@@ -17975,7 +18007,7 @@
       <c r="K986" s="6"/>
       <c r="L986" s="6"/>
     </row>
-    <row r="987" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="987" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A987" s="5"/>
       <c r="B987" s="5"/>
       <c r="C987" s="5"/>
@@ -17989,7 +18021,7 @@
       <c r="K987" s="6"/>
       <c r="L987" s="6"/>
     </row>
-    <row r="988" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="988" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A988" s="5"/>
       <c r="B988" s="5"/>
       <c r="C988" s="5"/>
@@ -18003,7 +18035,7 @@
       <c r="K988" s="6"/>
       <c r="L988" s="6"/>
     </row>
-    <row r="989" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="989" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A989" s="5"/>
       <c r="B989" s="5"/>
       <c r="C989" s="5"/>
@@ -18017,7 +18049,7 @@
       <c r="K989" s="6"/>
       <c r="L989" s="6"/>
     </row>
-    <row r="990" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="990" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A990" s="5"/>
       <c r="B990" s="5"/>
       <c r="C990" s="5"/>
@@ -18031,7 +18063,7 @@
       <c r="K990" s="6"/>
       <c r="L990" s="6"/>
     </row>
-    <row r="991" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="991" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A991" s="5"/>
       <c r="B991" s="5"/>
       <c r="C991" s="5"/>
@@ -18045,7 +18077,7 @@
       <c r="K991" s="6"/>
       <c r="L991" s="6"/>
     </row>
-    <row r="992" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="992" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A992" s="5"/>
       <c r="B992" s="5"/>
       <c r="C992" s="5"/>
@@ -18059,7 +18091,7 @@
       <c r="K992" s="6"/>
       <c r="L992" s="6"/>
     </row>
-    <row r="993" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="993" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A993" s="5"/>
       <c r="B993" s="5"/>
       <c r="C993" s="5"/>
@@ -18073,7 +18105,7 @@
       <c r="K993" s="6"/>
       <c r="L993" s="6"/>
     </row>
-    <row r="994" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="994" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A994" s="5"/>
       <c r="B994" s="5"/>
       <c r="C994" s="5"/>
@@ -18087,7 +18119,7 @@
       <c r="K994" s="6"/>
       <c r="L994" s="6"/>
     </row>
-    <row r="995" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="995" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A995" s="5"/>
       <c r="B995" s="5"/>
       <c r="C995" s="5"/>
@@ -18101,7 +18133,7 @@
       <c r="K995" s="6"/>
       <c r="L995" s="6"/>
     </row>
-    <row r="996" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="996" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A996" s="5"/>
       <c r="B996" s="5"/>
       <c r="C996" s="5"/>
@@ -18115,7 +18147,7 @@
       <c r="K996" s="6"/>
       <c r="L996" s="6"/>
     </row>
-    <row r="997" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="997" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A997" s="5"/>
       <c r="B997" s="5"/>
       <c r="C997" s="5"/>
@@ -18129,7 +18161,7 @@
       <c r="K997" s="6"/>
       <c r="L997" s="6"/>
     </row>
-    <row r="998" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="998" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A998" s="5"/>
       <c r="B998" s="5"/>
       <c r="C998" s="5"/>
@@ -18143,7 +18175,7 @@
       <c r="K998" s="6"/>
       <c r="L998" s="6"/>
     </row>
-    <row r="999" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="999" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A999" s="5"/>
       <c r="B999" s="5"/>
       <c r="C999" s="5"/>
@@ -18157,7 +18189,7 @@
       <c r="K999" s="6"/>
       <c r="L999" s="6"/>
     </row>
-    <row r="1000" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1000" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1000" s="5"/>
       <c r="B1000" s="5"/>
       <c r="C1000" s="5"/>
@@ -18171,7 +18203,7 @@
       <c r="K1000" s="6"/>
       <c r="L1000" s="6"/>
     </row>
-    <row r="1001" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1001" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1001" s="5"/>
       <c r="B1001" s="5"/>
       <c r="C1001" s="5"/>
@@ -18185,7 +18217,7 @@
       <c r="K1001" s="6"/>
       <c r="L1001" s="6"/>
     </row>
-    <row r="1002" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1002" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1002" s="5"/>
       <c r="B1002" s="5"/>
       <c r="C1002" s="5"/>
@@ -18199,7 +18231,7 @@
       <c r="K1002" s="6"/>
       <c r="L1002" s="6"/>
     </row>
-    <row r="1003" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1003" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1003" s="5"/>
       <c r="B1003" s="5"/>
       <c r="C1003" s="5"/>
@@ -18213,7 +18245,7 @@
       <c r="K1003" s="6"/>
       <c r="L1003" s="6"/>
     </row>
-    <row r="1004" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1004" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1004" s="5"/>
       <c r="B1004" s="5"/>
       <c r="C1004" s="5"/>
@@ -18227,7 +18259,7 @@
       <c r="K1004" s="6"/>
       <c r="L1004" s="6"/>
     </row>
-    <row r="1005" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1005" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1005" s="5"/>
       <c r="B1005" s="5"/>
       <c r="C1005" s="5"/>
@@ -18241,7 +18273,7 @@
       <c r="K1005" s="6"/>
       <c r="L1005" s="6"/>
     </row>
-    <row r="1006" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1006" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1006" s="5"/>
       <c r="B1006" s="5"/>
       <c r="C1006" s="5"/>
@@ -18255,7 +18287,7 @@
       <c r="K1006" s="6"/>
       <c r="L1006" s="6"/>
     </row>
-    <row r="1007" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1007" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1007" s="5"/>
       <c r="B1007" s="5"/>
       <c r="C1007" s="5"/>
@@ -18269,7 +18301,7 @@
       <c r="K1007" s="6"/>
       <c r="L1007" s="6"/>
     </row>
-    <row r="1008" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1008" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1008" s="5"/>
       <c r="B1008" s="5"/>
       <c r="C1008" s="5"/>
@@ -18283,7 +18315,7 @@
       <c r="K1008" s="6"/>
       <c r="L1008" s="6"/>
     </row>
-    <row r="1009" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1009" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1009" s="5"/>
       <c r="B1009" s="5"/>
       <c r="C1009" s="5"/>
@@ -18297,7 +18329,7 @@
       <c r="K1009" s="6"/>
       <c r="L1009" s="6"/>
     </row>
-    <row r="1010" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1010" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1010" s="5"/>
       <c r="B1010" s="5"/>
       <c r="C1010" s="5"/>
@@ -18311,7 +18343,7 @@
       <c r="K1010" s="6"/>
       <c r="L1010" s="6"/>
     </row>
-    <row r="1011" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1011" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1011" s="5"/>
       <c r="B1011" s="5"/>
       <c r="C1011" s="5"/>
@@ -18325,7 +18357,7 @@
       <c r="K1011" s="6"/>
       <c r="L1011" s="6"/>
     </row>
-    <row r="1012" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1012" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1012" s="5"/>
       <c r="B1012" s="5"/>
       <c r="C1012" s="5"/>
@@ -18339,7 +18371,7 @@
       <c r="K1012" s="6"/>
       <c r="L1012" s="6"/>
     </row>
-    <row r="1013" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1013" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1013" s="5"/>
       <c r="B1013" s="5"/>
       <c r="C1013" s="5"/>
@@ -18353,7 +18385,7 @@
       <c r="K1013" s="6"/>
       <c r="L1013" s="6"/>
     </row>
-    <row r="1014" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1014" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1014" s="5"/>
       <c r="B1014" s="5"/>
       <c r="C1014" s="5"/>
@@ -18367,7 +18399,7 @@
       <c r="K1014" s="6"/>
       <c r="L1014" s="6"/>
     </row>
-    <row r="1015" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1015" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1015" s="5"/>
       <c r="B1015" s="5"/>
       <c r="C1015" s="5"/>
@@ -18381,7 +18413,7 @@
       <c r="K1015" s="6"/>
       <c r="L1015" s="6"/>
     </row>
-    <row r="1016" spans="1:12" ht="72" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1016" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1016" s="5" t="s">
         <v>602</v>
       </c>
@@ -18407,7 +18439,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="1017" spans="1:12" ht="72" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1017" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1017" s="5" t="s">
         <v>608</v>
       </c>
@@ -18435,24 +18467,24 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K1017" ns2:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K1017" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Minor Repeatable,Minor Fire-Once,Major"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" ns2:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" ns2:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L1017" ns2:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation type="list" allowBlank="1" sqref="L2:L1017" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="R2:R16" ns2:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="R2:R16" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Implemented,New,In progress,Under review,Buggy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart ns4:id="rId1"/>
-    <tablePart ns4:id="rId2"/>
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2271,13 +2271,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1C4587"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R1017"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
@@ -2296,7 +2296,7 @@
     <col min="18" max="18" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="99.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="111.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="90" customHeight="1" ns3:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
@@ -2486,7 +2486,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>59</v>
       </c>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Implemented - Final Audit Passed</t>
+          <t>Implemented - Final Closure Blocked</t>
         </is>
       </c>
       <c r="N6" s="7" t="s">
@@ -2604,11 +2604,11 @@
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>Final Audit Passed</t>
+          <t>Blocked - Missing continuation spec/logs</t>
         </is>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>64</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>69</v>
       </c>
@@ -2680,7 +2680,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>74</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>78</v>
       </c>
@@ -2750,7 +2750,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>82</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>87</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>92</v>
       </c>
@@ -2859,7 +2859,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>96</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>100</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>105</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>108</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>111</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>114</v>
       </c>
@@ -3038,7 +3038,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>117</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>120</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>124</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>128</v>
       </c>
@@ -3139,7 +3139,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>131</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>134</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>137</v>
       </c>
@@ -3211,7 +3211,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>140</v>
       </c>
@@ -3235,7 +3235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>143</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>146</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>149</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>152</v>
       </c>
@@ -3333,7 +3333,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>156</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>159</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>162</v>
       </c>
@@ -3405,7 +3405,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>165</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>168</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>171</v>
       </c>
@@ -3477,7 +3477,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>174</v>
       </c>
@@ -3501,7 +3501,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>177</v>
       </c>
@@ -3527,7 +3527,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>181</v>
       </c>
@@ -3551,7 +3551,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>184</v>
       </c>
@@ -3575,7 +3575,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>187</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>190</v>
       </c>
@@ -3623,7 +3623,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>193</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>196</v>
       </c>
@@ -3671,7 +3671,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>199</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>202</v>
       </c>
@@ -3719,7 +3719,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>205</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>208</v>
       </c>
@@ -3767,7 +3767,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>211</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>214</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>217</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>220</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>223</v>
       </c>
@@ -3887,7 +3887,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>226</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>229</v>
       </c>
@@ -3935,7 +3935,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>232</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>235</v>
       </c>
@@ -3983,7 +3983,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>238</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>241</v>
       </c>
@@ -4031,7 +4031,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>244</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>247</v>
       </c>
@@ -4079,7 +4079,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>250</v>
       </c>
@@ -4103,7 +4103,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>253</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>256</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>259</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>262</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>265</v>
       </c>
@@ -4223,7 +4223,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>268</v>
       </c>
@@ -4249,7 +4249,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>272</v>
       </c>
@@ -4273,7 +4273,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>275</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>278</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>281</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>284</v>
       </c>
@@ -4369,7 +4369,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>287</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>290</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>293</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>296</v>
       </c>
@@ -4465,7 +4465,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>299</v>
       </c>
@@ -4489,7 +4489,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>302</v>
       </c>
@@ -4513,7 +4513,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>305</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>308</v>
       </c>
@@ -4561,7 +4561,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>311</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>314</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>317</v>
       </c>
@@ -4633,7 +4633,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>320</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>323</v>
       </c>
@@ -4681,7 +4681,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>326</v>
       </c>
@@ -4705,7 +4705,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>329</v>
       </c>
@@ -4729,7 +4729,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>332</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>335</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>338</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>342</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>345</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>348</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>351</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>354</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>357</v>
       </c>
@@ -4947,7 +4947,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>360</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>363</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>366</v>
       </c>
@@ -5017,7 +5017,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>369</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>372</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>375</v>
       </c>
@@ -5083,7 +5083,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>378</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>381</v>
       </c>
@@ -5127,7 +5127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>384</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>387</v>
       </c>
@@ -5171,7 +5171,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>390</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>393</v>
       </c>
@@ -5215,7 +5215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>396</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>399</v>
       </c>
@@ -5259,7 +5259,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>402</v>
       </c>
@@ -5281,7 +5281,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>405</v>
       </c>
@@ -5303,7 +5303,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>408</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>411</v>
       </c>
@@ -5347,7 +5347,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>414</v>
       </c>
@@ -5369,7 +5369,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>417</v>
       </c>
@@ -5391,7 +5391,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>420</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>423</v>
       </c>
@@ -5435,7 +5435,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>426</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>429</v>
       </c>
@@ -5479,7 +5479,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>432</v>
       </c>
@@ -5501,7 +5501,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>435</v>
       </c>
@@ -5523,7 +5523,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>438</v>
       </c>
@@ -5545,7 +5545,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>441</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>444</v>
       </c>
@@ -5589,7 +5589,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>447</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>450</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>453</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>456</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>459</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>462</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>465</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>468</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>471</v>
       </c>
@@ -5787,7 +5787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>474</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>477</v>
       </c>
@@ -5831,7 +5831,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>480</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>483</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>486</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>489</v>
       </c>
@@ -5919,7 +5919,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>492</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>495</v>
       </c>
@@ -5963,7 +5963,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>498</v>
       </c>
@@ -5985,7 +5985,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>501</v>
       </c>
@@ -6007,7 +6007,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>504</v>
       </c>
@@ -6029,7 +6029,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>507</v>
       </c>
@@ -6051,7 +6051,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>510</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>513</v>
       </c>
@@ -6095,7 +6095,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>516</v>
       </c>
@@ -6117,7 +6117,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>519</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>523</v>
       </c>
@@ -6163,7 +6163,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>526</v>
       </c>
@@ -6185,7 +6185,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>529</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>532</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>535</v>
       </c>
@@ -6251,7 +6251,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>538</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>541</v>
       </c>
@@ -6295,7 +6295,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>544</v>
       </c>
@@ -6317,7 +6317,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>547</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>550</v>
       </c>
@@ -6363,7 +6363,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>554</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>557</v>
       </c>
@@ -6407,7 +6407,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>560</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>563</v>
       </c>
@@ -6451,7 +6451,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>566</v>
       </c>
@@ -6475,7 +6475,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A168" s="5"/>
       <c r="B168" s="5" t="s">
         <v>569</v>
@@ -6493,7 +6493,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A169" s="5"/>
       <c r="B169" s="5" t="s">
         <v>571</v>
@@ -6511,7 +6511,7 @@
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
     </row>
-    <row r="170" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A170" s="5"/>
       <c r="B170" s="5" t="s">
         <v>573</v>
@@ -6529,7 +6529,7 @@
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
     </row>
-    <row r="171" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A171" s="5"/>
       <c r="B171" s="5" t="s">
         <v>575</v>
@@ -6547,7 +6547,7 @@
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
     </row>
-    <row r="172" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A172" s="5"/>
       <c r="B172" s="5" t="s">
         <v>577</v>
@@ -6565,7 +6565,7 @@
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
     </row>
-    <row r="173" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A173" s="5"/>
       <c r="B173" s="5" t="s">
         <v>579</v>
@@ -6585,7 +6585,7 @@
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
     </row>
-    <row r="174" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A174" s="5"/>
       <c r="B174" s="5" t="s">
         <v>582</v>
@@ -6603,7 +6603,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="5" t="s">
         <v>584</v>
@@ -6621,7 +6621,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="5" t="s">
         <v>586</v>
@@ -6639,7 +6639,7 @@
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
     </row>
-    <row r="177" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="5" t="s">
         <v>588</v>
@@ -6657,7 +6657,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="5" t="s">
         <v>590</v>
@@ -6675,7 +6675,7 @@
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
     </row>
-    <row r="179" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="5" t="s">
         <v>592</v>
@@ -6693,7 +6693,7 @@
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
     </row>
-    <row r="180" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="5" t="s">
         <v>594</v>
@@ -6711,7 +6711,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="5" t="s">
         <v>596</v>
@@ -6729,7 +6729,7 @@
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
     </row>
-    <row r="182" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="5" t="s">
         <v>598</v>
@@ -6747,7 +6747,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="5" t="s">
         <v>600</v>
@@ -6765,7 +6765,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -6779,7 +6779,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -6793,7 +6793,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -6807,7 +6807,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -6821,7 +6821,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -6835,7 +6835,7 @@
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
     </row>
-    <row r="189" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -6849,7 +6849,7 @@
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
     </row>
-    <row r="190" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -6863,7 +6863,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -6877,7 +6877,7 @@
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
     </row>
-    <row r="192" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -6891,7 +6891,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -6905,7 +6905,7 @@
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
     </row>
-    <row r="194" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -6919,7 +6919,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -6933,7 +6933,7 @@
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
     </row>
-    <row r="196" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -6947,7 +6947,7 @@
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
     </row>
-    <row r="197" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -6961,7 +6961,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -6975,7 +6975,7 @@
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
     </row>
-    <row r="199" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -6989,7 +6989,7 @@
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
     </row>
-    <row r="200" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -7003,7 +7003,7 @@
       <c r="K200" s="6"/>
       <c r="L200" s="6"/>
     </row>
-    <row r="201" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -7017,7 +7017,7 @@
       <c r="K201" s="6"/>
       <c r="L201" s="6"/>
     </row>
-    <row r="202" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -7031,7 +7031,7 @@
       <c r="K202" s="6"/>
       <c r="L202" s="6"/>
     </row>
-    <row r="203" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -7045,7 +7045,7 @@
       <c r="K203" s="6"/>
       <c r="L203" s="6"/>
     </row>
-    <row r="204" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -7059,7 +7059,7 @@
       <c r="K204" s="6"/>
       <c r="L204" s="6"/>
     </row>
-    <row r="205" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -7073,7 +7073,7 @@
       <c r="K205" s="6"/>
       <c r="L205" s="6"/>
     </row>
-    <row r="206" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -7087,7 +7087,7 @@
       <c r="K206" s="6"/>
       <c r="L206" s="6"/>
     </row>
-    <row r="207" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -7101,7 +7101,7 @@
       <c r="K207" s="6"/>
       <c r="L207" s="6"/>
     </row>
-    <row r="208" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -7115,7 +7115,7 @@
       <c r="K208" s="6"/>
       <c r="L208" s="6"/>
     </row>
-    <row r="209" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -7129,7 +7129,7 @@
       <c r="K209" s="6"/>
       <c r="L209" s="6"/>
     </row>
-    <row r="210" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -7143,7 +7143,7 @@
       <c r="K210" s="6"/>
       <c r="L210" s="6"/>
     </row>
-    <row r="211" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -7157,7 +7157,7 @@
       <c r="K211" s="6"/>
       <c r="L211" s="6"/>
     </row>
-    <row r="212" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -7171,7 +7171,7 @@
       <c r="K212" s="6"/>
       <c r="L212" s="6"/>
     </row>
-    <row r="213" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -7185,7 +7185,7 @@
       <c r="K213" s="6"/>
       <c r="L213" s="6"/>
     </row>
-    <row r="214" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -7199,7 +7199,7 @@
       <c r="K214" s="6"/>
       <c r="L214" s="6"/>
     </row>
-    <row r="215" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -7213,7 +7213,7 @@
       <c r="K215" s="6"/>
       <c r="L215" s="6"/>
     </row>
-    <row r="216" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -7227,7 +7227,7 @@
       <c r="K216" s="6"/>
       <c r="L216" s="6"/>
     </row>
-    <row r="217" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -7241,7 +7241,7 @@
       <c r="K217" s="6"/>
       <c r="L217" s="6"/>
     </row>
-    <row r="218" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -7255,7 +7255,7 @@
       <c r="K218" s="6"/>
       <c r="L218" s="6"/>
     </row>
-    <row r="219" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -7269,7 +7269,7 @@
       <c r="K219" s="6"/>
       <c r="L219" s="6"/>
     </row>
-    <row r="220" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -7283,7 +7283,7 @@
       <c r="K220" s="6"/>
       <c r="L220" s="6"/>
     </row>
-    <row r="221" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -7297,7 +7297,7 @@
       <c r="K221" s="6"/>
       <c r="L221" s="6"/>
     </row>
-    <row r="222" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -7311,7 +7311,7 @@
       <c r="K222" s="6"/>
       <c r="L222" s="6"/>
     </row>
-    <row r="223" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -7325,7 +7325,7 @@
       <c r="K223" s="6"/>
       <c r="L223" s="6"/>
     </row>
-    <row r="224" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -7339,7 +7339,7 @@
       <c r="K224" s="6"/>
       <c r="L224" s="6"/>
     </row>
-    <row r="225" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -7353,7 +7353,7 @@
       <c r="K225" s="6"/>
       <c r="L225" s="6"/>
     </row>
-    <row r="226" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -7367,7 +7367,7 @@
       <c r="K226" s="6"/>
       <c r="L226" s="6"/>
     </row>
-    <row r="227" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -7381,7 +7381,7 @@
       <c r="K227" s="6"/>
       <c r="L227" s="6"/>
     </row>
-    <row r="228" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -7395,7 +7395,7 @@
       <c r="K228" s="6"/>
       <c r="L228" s="6"/>
     </row>
-    <row r="229" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -7409,7 +7409,7 @@
       <c r="K229" s="6"/>
       <c r="L229" s="6"/>
     </row>
-    <row r="230" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -7423,7 +7423,7 @@
       <c r="K230" s="6"/>
       <c r="L230" s="6"/>
     </row>
-    <row r="231" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -7437,7 +7437,7 @@
       <c r="K231" s="6"/>
       <c r="L231" s="6"/>
     </row>
-    <row r="232" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -7451,7 +7451,7 @@
       <c r="K232" s="6"/>
       <c r="L232" s="6"/>
     </row>
-    <row r="233" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -7465,7 +7465,7 @@
       <c r="K233" s="6"/>
       <c r="L233" s="6"/>
     </row>
-    <row r="234" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -7479,7 +7479,7 @@
       <c r="K234" s="6"/>
       <c r="L234" s="6"/>
     </row>
-    <row r="235" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -7493,7 +7493,7 @@
       <c r="K235" s="6"/>
       <c r="L235" s="6"/>
     </row>
-    <row r="236" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -7507,7 +7507,7 @@
       <c r="K236" s="6"/>
       <c r="L236" s="6"/>
     </row>
-    <row r="237" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -7521,7 +7521,7 @@
       <c r="K237" s="6"/>
       <c r="L237" s="6"/>
     </row>
-    <row r="238" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -7535,7 +7535,7 @@
       <c r="K238" s="6"/>
       <c r="L238" s="6"/>
     </row>
-    <row r="239" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -7549,7 +7549,7 @@
       <c r="K239" s="6"/>
       <c r="L239" s="6"/>
     </row>
-    <row r="240" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -7563,7 +7563,7 @@
       <c r="K240" s="6"/>
       <c r="L240" s="6"/>
     </row>
-    <row r="241" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -7577,7 +7577,7 @@
       <c r="K241" s="6"/>
       <c r="L241" s="6"/>
     </row>
-    <row r="242" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -7591,7 +7591,7 @@
       <c r="K242" s="6"/>
       <c r="L242" s="6"/>
     </row>
-    <row r="243" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -7605,7 +7605,7 @@
       <c r="K243" s="6"/>
       <c r="L243" s="6"/>
     </row>
-    <row r="244" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -7619,7 +7619,7 @@
       <c r="K244" s="6"/>
       <c r="L244" s="6"/>
     </row>
-    <row r="245" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -7633,7 +7633,7 @@
       <c r="K245" s="6"/>
       <c r="L245" s="6"/>
     </row>
-    <row r="246" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -7647,7 +7647,7 @@
       <c r="K246" s="6"/>
       <c r="L246" s="6"/>
     </row>
-    <row r="247" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -7661,7 +7661,7 @@
       <c r="K247" s="6"/>
       <c r="L247" s="6"/>
     </row>
-    <row r="248" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -7675,7 +7675,7 @@
       <c r="K248" s="6"/>
       <c r="L248" s="6"/>
     </row>
-    <row r="249" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -7689,7 +7689,7 @@
       <c r="K249" s="6"/>
       <c r="L249" s="6"/>
     </row>
-    <row r="250" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -7703,7 +7703,7 @@
       <c r="K250" s="6"/>
       <c r="L250" s="6"/>
     </row>
-    <row r="251" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -7717,7 +7717,7 @@
       <c r="K251" s="6"/>
       <c r="L251" s="6"/>
     </row>
-    <row r="252" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -7731,7 +7731,7 @@
       <c r="K252" s="6"/>
       <c r="L252" s="6"/>
     </row>
-    <row r="253" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -7745,7 +7745,7 @@
       <c r="K253" s="6"/>
       <c r="L253" s="6"/>
     </row>
-    <row r="254" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -7759,7 +7759,7 @@
       <c r="K254" s="6"/>
       <c r="L254" s="6"/>
     </row>
-    <row r="255" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -7773,7 +7773,7 @@
       <c r="K255" s="6"/>
       <c r="L255" s="6"/>
     </row>
-    <row r="256" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -7787,7 +7787,7 @@
       <c r="K256" s="6"/>
       <c r="L256" s="6"/>
     </row>
-    <row r="257" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -7801,7 +7801,7 @@
       <c r="K257" s="6"/>
       <c r="L257" s="6"/>
     </row>
-    <row r="258" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -7815,7 +7815,7 @@
       <c r="K258" s="6"/>
       <c r="L258" s="6"/>
     </row>
-    <row r="259" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -7829,7 +7829,7 @@
       <c r="K259" s="6"/>
       <c r="L259" s="6"/>
     </row>
-    <row r="260" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -7843,7 +7843,7 @@
       <c r="K260" s="6"/>
       <c r="L260" s="6"/>
     </row>
-    <row r="261" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -7857,7 +7857,7 @@
       <c r="K261" s="6"/>
       <c r="L261" s="6"/>
     </row>
-    <row r="262" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -7871,7 +7871,7 @@
       <c r="K262" s="6"/>
       <c r="L262" s="6"/>
     </row>
-    <row r="263" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -7885,7 +7885,7 @@
       <c r="K263" s="6"/>
       <c r="L263" s="6"/>
     </row>
-    <row r="264" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -7899,7 +7899,7 @@
       <c r="K264" s="6"/>
       <c r="L264" s="6"/>
     </row>
-    <row r="265" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -7913,7 +7913,7 @@
       <c r="K265" s="6"/>
       <c r="L265" s="6"/>
     </row>
-    <row r="266" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -7927,7 +7927,7 @@
       <c r="K266" s="6"/>
       <c r="L266" s="6"/>
     </row>
-    <row r="267" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -7941,7 +7941,7 @@
       <c r="K267" s="6"/>
       <c r="L267" s="6"/>
     </row>
-    <row r="268" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -7955,7 +7955,7 @@
       <c r="K268" s="6"/>
       <c r="L268" s="6"/>
     </row>
-    <row r="269" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -7969,7 +7969,7 @@
       <c r="K269" s="6"/>
       <c r="L269" s="6"/>
     </row>
-    <row r="270" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -7983,7 +7983,7 @@
       <c r="K270" s="6"/>
       <c r="L270" s="6"/>
     </row>
-    <row r="271" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -7997,7 +7997,7 @@
       <c r="K271" s="6"/>
       <c r="L271" s="6"/>
     </row>
-    <row r="272" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -8011,7 +8011,7 @@
       <c r="K272" s="6"/>
       <c r="L272" s="6"/>
     </row>
-    <row r="273" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -8025,7 +8025,7 @@
       <c r="K273" s="6"/>
       <c r="L273" s="6"/>
     </row>
-    <row r="274" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -8039,7 +8039,7 @@
       <c r="K274" s="6"/>
       <c r="L274" s="6"/>
     </row>
-    <row r="275" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -8053,7 +8053,7 @@
       <c r="K275" s="6"/>
       <c r="L275" s="6"/>
     </row>
-    <row r="276" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -8067,7 +8067,7 @@
       <c r="K276" s="6"/>
       <c r="L276" s="6"/>
     </row>
-    <row r="277" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -8081,7 +8081,7 @@
       <c r="K277" s="6"/>
       <c r="L277" s="6"/>
     </row>
-    <row r="278" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -8095,7 +8095,7 @@
       <c r="K278" s="6"/>
       <c r="L278" s="6"/>
     </row>
-    <row r="279" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -8109,7 +8109,7 @@
       <c r="K279" s="6"/>
       <c r="L279" s="6"/>
     </row>
-    <row r="280" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -8123,7 +8123,7 @@
       <c r="K280" s="6"/>
       <c r="L280" s="6"/>
     </row>
-    <row r="281" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -8137,7 +8137,7 @@
       <c r="K281" s="6"/>
       <c r="L281" s="6"/>
     </row>
-    <row r="282" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -8151,7 +8151,7 @@
       <c r="K282" s="6"/>
       <c r="L282" s="6"/>
     </row>
-    <row r="283" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -8165,7 +8165,7 @@
       <c r="K283" s="6"/>
       <c r="L283" s="6"/>
     </row>
-    <row r="284" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -8179,7 +8179,7 @@
       <c r="K284" s="6"/>
       <c r="L284" s="6"/>
     </row>
-    <row r="285" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -8193,7 +8193,7 @@
       <c r="K285" s="6"/>
       <c r="L285" s="6"/>
     </row>
-    <row r="286" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -8207,7 +8207,7 @@
       <c r="K286" s="6"/>
       <c r="L286" s="6"/>
     </row>
-    <row r="287" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -8221,7 +8221,7 @@
       <c r="K287" s="6"/>
       <c r="L287" s="6"/>
     </row>
-    <row r="288" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -8235,7 +8235,7 @@
       <c r="K288" s="6"/>
       <c r="L288" s="6"/>
     </row>
-    <row r="289" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -8249,7 +8249,7 @@
       <c r="K289" s="6"/>
       <c r="L289" s="6"/>
     </row>
-    <row r="290" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -8263,7 +8263,7 @@
       <c r="K290" s="6"/>
       <c r="L290" s="6"/>
     </row>
-    <row r="291" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -8277,7 +8277,7 @@
       <c r="K291" s="6"/>
       <c r="L291" s="6"/>
     </row>
-    <row r="292" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -8291,7 +8291,7 @@
       <c r="K292" s="6"/>
       <c r="L292" s="6"/>
     </row>
-    <row r="293" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -8305,7 +8305,7 @@
       <c r="K293" s="6"/>
       <c r="L293" s="6"/>
     </row>
-    <row r="294" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -8319,7 +8319,7 @@
       <c r="K294" s="6"/>
       <c r="L294" s="6"/>
     </row>
-    <row r="295" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -8333,7 +8333,7 @@
       <c r="K295" s="6"/>
       <c r="L295" s="6"/>
     </row>
-    <row r="296" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -8347,7 +8347,7 @@
       <c r="K296" s="6"/>
       <c r="L296" s="6"/>
     </row>
-    <row r="297" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -8361,7 +8361,7 @@
       <c r="K297" s="6"/>
       <c r="L297" s="6"/>
     </row>
-    <row r="298" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -8375,7 +8375,7 @@
       <c r="K298" s="6"/>
       <c r="L298" s="6"/>
     </row>
-    <row r="299" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -8389,7 +8389,7 @@
       <c r="K299" s="6"/>
       <c r="L299" s="6"/>
     </row>
-    <row r="300" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -8403,7 +8403,7 @@
       <c r="K300" s="6"/>
       <c r="L300" s="6"/>
     </row>
-    <row r="301" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -8417,7 +8417,7 @@
       <c r="K301" s="6"/>
       <c r="L301" s="6"/>
     </row>
-    <row r="302" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -8431,7 +8431,7 @@
       <c r="K302" s="6"/>
       <c r="L302" s="6"/>
     </row>
-    <row r="303" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -8445,7 +8445,7 @@
       <c r="K303" s="6"/>
       <c r="L303" s="6"/>
     </row>
-    <row r="304" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -8459,7 +8459,7 @@
       <c r="K304" s="6"/>
       <c r="L304" s="6"/>
     </row>
-    <row r="305" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -8473,7 +8473,7 @@
       <c r="K305" s="6"/>
       <c r="L305" s="6"/>
     </row>
-    <row r="306" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -8487,7 +8487,7 @@
       <c r="K306" s="6"/>
       <c r="L306" s="6"/>
     </row>
-    <row r="307" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -8501,7 +8501,7 @@
       <c r="K307" s="6"/>
       <c r="L307" s="6"/>
     </row>
-    <row r="308" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -8515,7 +8515,7 @@
       <c r="K308" s="6"/>
       <c r="L308" s="6"/>
     </row>
-    <row r="309" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -8529,7 +8529,7 @@
       <c r="K309" s="6"/>
       <c r="L309" s="6"/>
     </row>
-    <row r="310" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -8543,7 +8543,7 @@
       <c r="K310" s="6"/>
       <c r="L310" s="6"/>
     </row>
-    <row r="311" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -8557,7 +8557,7 @@
       <c r="K311" s="6"/>
       <c r="L311" s="6"/>
     </row>
-    <row r="312" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -8571,7 +8571,7 @@
       <c r="K312" s="6"/>
       <c r="L312" s="6"/>
     </row>
-    <row r="313" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -8585,7 +8585,7 @@
       <c r="K313" s="6"/>
       <c r="L313" s="6"/>
     </row>
-    <row r="314" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -8599,7 +8599,7 @@
       <c r="K314" s="6"/>
       <c r="L314" s="6"/>
     </row>
-    <row r="315" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -8613,7 +8613,7 @@
       <c r="K315" s="6"/>
       <c r="L315" s="6"/>
     </row>
-    <row r="316" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -8627,7 +8627,7 @@
       <c r="K316" s="6"/>
       <c r="L316" s="6"/>
     </row>
-    <row r="317" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -8641,7 +8641,7 @@
       <c r="K317" s="6"/>
       <c r="L317" s="6"/>
     </row>
-    <row r="318" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -8655,7 +8655,7 @@
       <c r="K318" s="6"/>
       <c r="L318" s="6"/>
     </row>
-    <row r="319" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -8669,7 +8669,7 @@
       <c r="K319" s="6"/>
       <c r="L319" s="6"/>
     </row>
-    <row r="320" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -8683,7 +8683,7 @@
       <c r="K320" s="6"/>
       <c r="L320" s="6"/>
     </row>
-    <row r="321" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -8697,7 +8697,7 @@
       <c r="K321" s="6"/>
       <c r="L321" s="6"/>
     </row>
-    <row r="322" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -8711,7 +8711,7 @@
       <c r="K322" s="6"/>
       <c r="L322" s="6"/>
     </row>
-    <row r="323" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -8725,7 +8725,7 @@
       <c r="K323" s="6"/>
       <c r="L323" s="6"/>
     </row>
-    <row r="324" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -8739,7 +8739,7 @@
       <c r="K324" s="6"/>
       <c r="L324" s="6"/>
     </row>
-    <row r="325" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -8753,7 +8753,7 @@
       <c r="K325" s="6"/>
       <c r="L325" s="6"/>
     </row>
-    <row r="326" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -8767,7 +8767,7 @@
       <c r="K326" s="6"/>
       <c r="L326" s="6"/>
     </row>
-    <row r="327" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -8781,7 +8781,7 @@
       <c r="K327" s="6"/>
       <c r="L327" s="6"/>
     </row>
-    <row r="328" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -8795,7 +8795,7 @@
       <c r="K328" s="6"/>
       <c r="L328" s="6"/>
     </row>
-    <row r="329" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -8809,7 +8809,7 @@
       <c r="K329" s="6"/>
       <c r="L329" s="6"/>
     </row>
-    <row r="330" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -8823,7 +8823,7 @@
       <c r="K330" s="6"/>
       <c r="L330" s="6"/>
     </row>
-    <row r="331" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -8837,7 +8837,7 @@
       <c r="K331" s="6"/>
       <c r="L331" s="6"/>
     </row>
-    <row r="332" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -8851,7 +8851,7 @@
       <c r="K332" s="6"/>
       <c r="L332" s="6"/>
     </row>
-    <row r="333" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -8865,7 +8865,7 @@
       <c r="K333" s="6"/>
       <c r="L333" s="6"/>
     </row>
-    <row r="334" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -8879,7 +8879,7 @@
       <c r="K334" s="6"/>
       <c r="L334" s="6"/>
     </row>
-    <row r="335" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -8893,7 +8893,7 @@
       <c r="K335" s="6"/>
       <c r="L335" s="6"/>
     </row>
-    <row r="336" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -8907,7 +8907,7 @@
       <c r="K336" s="6"/>
       <c r="L336" s="6"/>
     </row>
-    <row r="337" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -8921,7 +8921,7 @@
       <c r="K337" s="6"/>
       <c r="L337" s="6"/>
     </row>
-    <row r="338" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -8935,7 +8935,7 @@
       <c r="K338" s="6"/>
       <c r="L338" s="6"/>
     </row>
-    <row r="339" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -8949,7 +8949,7 @@
       <c r="K339" s="6"/>
       <c r="L339" s="6"/>
     </row>
-    <row r="340" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -8963,7 +8963,7 @@
       <c r="K340" s="6"/>
       <c r="L340" s="6"/>
     </row>
-    <row r="341" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -8977,7 +8977,7 @@
       <c r="K341" s="6"/>
       <c r="L341" s="6"/>
     </row>
-    <row r="342" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -8991,7 +8991,7 @@
       <c r="K342" s="6"/>
       <c r="L342" s="6"/>
     </row>
-    <row r="343" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -9005,7 +9005,7 @@
       <c r="K343" s="6"/>
       <c r="L343" s="6"/>
     </row>
-    <row r="344" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -9019,7 +9019,7 @@
       <c r="K344" s="6"/>
       <c r="L344" s="6"/>
     </row>
-    <row r="345" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -9033,7 +9033,7 @@
       <c r="K345" s="6"/>
       <c r="L345" s="6"/>
     </row>
-    <row r="346" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -9047,7 +9047,7 @@
       <c r="K346" s="6"/>
       <c r="L346" s="6"/>
     </row>
-    <row r="347" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -9061,7 +9061,7 @@
       <c r="K347" s="6"/>
       <c r="L347" s="6"/>
     </row>
-    <row r="348" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -9075,7 +9075,7 @@
       <c r="K348" s="6"/>
       <c r="L348" s="6"/>
     </row>
-    <row r="349" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -9089,7 +9089,7 @@
       <c r="K349" s="6"/>
       <c r="L349" s="6"/>
     </row>
-    <row r="350" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -9103,7 +9103,7 @@
       <c r="K350" s="6"/>
       <c r="L350" s="6"/>
     </row>
-    <row r="351" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -9117,7 +9117,7 @@
       <c r="K351" s="6"/>
       <c r="L351" s="6"/>
     </row>
-    <row r="352" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -9131,7 +9131,7 @@
       <c r="K352" s="6"/>
       <c r="L352" s="6"/>
     </row>
-    <row r="353" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -9145,7 +9145,7 @@
       <c r="K353" s="6"/>
       <c r="L353" s="6"/>
     </row>
-    <row r="354" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -9159,7 +9159,7 @@
       <c r="K354" s="6"/>
       <c r="L354" s="6"/>
     </row>
-    <row r="355" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -9173,7 +9173,7 @@
       <c r="K355" s="6"/>
       <c r="L355" s="6"/>
     </row>
-    <row r="356" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -9187,7 +9187,7 @@
       <c r="K356" s="6"/>
       <c r="L356" s="6"/>
     </row>
-    <row r="357" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -9201,7 +9201,7 @@
       <c r="K357" s="6"/>
       <c r="L357" s="6"/>
     </row>
-    <row r="358" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -9215,7 +9215,7 @@
       <c r="K358" s="6"/>
       <c r="L358" s="6"/>
     </row>
-    <row r="359" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -9229,7 +9229,7 @@
       <c r="K359" s="6"/>
       <c r="L359" s="6"/>
     </row>
-    <row r="360" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -9243,7 +9243,7 @@
       <c r="K360" s="6"/>
       <c r="L360" s="6"/>
     </row>
-    <row r="361" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -9257,7 +9257,7 @@
       <c r="K361" s="6"/>
       <c r="L361" s="6"/>
     </row>
-    <row r="362" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -9271,7 +9271,7 @@
       <c r="K362" s="6"/>
       <c r="L362" s="6"/>
     </row>
-    <row r="363" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -9285,7 +9285,7 @@
       <c r="K363" s="6"/>
       <c r="L363" s="6"/>
     </row>
-    <row r="364" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -9299,7 +9299,7 @@
       <c r="K364" s="6"/>
       <c r="L364" s="6"/>
     </row>
-    <row r="365" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -9313,7 +9313,7 @@
       <c r="K365" s="6"/>
       <c r="L365" s="6"/>
     </row>
-    <row r="366" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -9327,7 +9327,7 @@
       <c r="K366" s="6"/>
       <c r="L366" s="6"/>
     </row>
-    <row r="367" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -9341,7 +9341,7 @@
       <c r="K367" s="6"/>
       <c r="L367" s="6"/>
     </row>
-    <row r="368" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -9355,7 +9355,7 @@
       <c r="K368" s="6"/>
       <c r="L368" s="6"/>
     </row>
-    <row r="369" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -9369,7 +9369,7 @@
       <c r="K369" s="6"/>
       <c r="L369" s="6"/>
     </row>
-    <row r="370" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -9383,7 +9383,7 @@
       <c r="K370" s="6"/>
       <c r="L370" s="6"/>
     </row>
-    <row r="371" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -9397,7 +9397,7 @@
       <c r="K371" s="6"/>
       <c r="L371" s="6"/>
     </row>
-    <row r="372" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -9411,7 +9411,7 @@
       <c r="K372" s="6"/>
       <c r="L372" s="6"/>
     </row>
-    <row r="373" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -9425,7 +9425,7 @@
       <c r="K373" s="6"/>
       <c r="L373" s="6"/>
     </row>
-    <row r="374" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -9439,7 +9439,7 @@
       <c r="K374" s="6"/>
       <c r="L374" s="6"/>
     </row>
-    <row r="375" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -9453,7 +9453,7 @@
       <c r="K375" s="6"/>
       <c r="L375" s="6"/>
     </row>
-    <row r="376" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -9467,7 +9467,7 @@
       <c r="K376" s="6"/>
       <c r="L376" s="6"/>
     </row>
-    <row r="377" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -9481,7 +9481,7 @@
       <c r="K377" s="6"/>
       <c r="L377" s="6"/>
     </row>
-    <row r="378" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -9495,7 +9495,7 @@
       <c r="K378" s="6"/>
       <c r="L378" s="6"/>
     </row>
-    <row r="379" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -9509,7 +9509,7 @@
       <c r="K379" s="6"/>
       <c r="L379" s="6"/>
     </row>
-    <row r="380" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -9523,7 +9523,7 @@
       <c r="K380" s="6"/>
       <c r="L380" s="6"/>
     </row>
-    <row r="381" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -9537,7 +9537,7 @@
       <c r="K381" s="6"/>
       <c r="L381" s="6"/>
     </row>
-    <row r="382" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -9551,7 +9551,7 @@
       <c r="K382" s="6"/>
       <c r="L382" s="6"/>
     </row>
-    <row r="383" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -9565,7 +9565,7 @@
       <c r="K383" s="6"/>
       <c r="L383" s="6"/>
     </row>
-    <row r="384" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -9579,7 +9579,7 @@
       <c r="K384" s="6"/>
       <c r="L384" s="6"/>
     </row>
-    <row r="385" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -9593,7 +9593,7 @@
       <c r="K385" s="6"/>
       <c r="L385" s="6"/>
     </row>
-    <row r="386" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -9607,7 +9607,7 @@
       <c r="K386" s="6"/>
       <c r="L386" s="6"/>
     </row>
-    <row r="387" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -9621,7 +9621,7 @@
       <c r="K387" s="6"/>
       <c r="L387" s="6"/>
     </row>
-    <row r="388" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -9635,7 +9635,7 @@
       <c r="K388" s="6"/>
       <c r="L388" s="6"/>
     </row>
-    <row r="389" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -9649,7 +9649,7 @@
       <c r="K389" s="6"/>
       <c r="L389" s="6"/>
     </row>
-    <row r="390" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -9663,7 +9663,7 @@
       <c r="K390" s="6"/>
       <c r="L390" s="6"/>
     </row>
-    <row r="391" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -9677,7 +9677,7 @@
       <c r="K391" s="6"/>
       <c r="L391" s="6"/>
     </row>
-    <row r="392" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -9691,7 +9691,7 @@
       <c r="K392" s="6"/>
       <c r="L392" s="6"/>
     </row>
-    <row r="393" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -9705,7 +9705,7 @@
       <c r="K393" s="6"/>
       <c r="L393" s="6"/>
     </row>
-    <row r="394" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -9719,7 +9719,7 @@
       <c r="K394" s="6"/>
       <c r="L394" s="6"/>
     </row>
-    <row r="395" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -9733,7 +9733,7 @@
       <c r="K395" s="6"/>
       <c r="L395" s="6"/>
     </row>
-    <row r="396" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -9747,7 +9747,7 @@
       <c r="K396" s="6"/>
       <c r="L396" s="6"/>
     </row>
-    <row r="397" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -9761,7 +9761,7 @@
       <c r="K397" s="6"/>
       <c r="L397" s="6"/>
     </row>
-    <row r="398" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -9775,7 +9775,7 @@
       <c r="K398" s="6"/>
       <c r="L398" s="6"/>
     </row>
-    <row r="399" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -9789,7 +9789,7 @@
       <c r="K399" s="6"/>
       <c r="L399" s="6"/>
     </row>
-    <row r="400" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -9803,7 +9803,7 @@
       <c r="K400" s="6"/>
       <c r="L400" s="6"/>
     </row>
-    <row r="401" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -9817,7 +9817,7 @@
       <c r="K401" s="6"/>
       <c r="L401" s="6"/>
     </row>
-    <row r="402" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -9831,7 +9831,7 @@
       <c r="K402" s="6"/>
       <c r="L402" s="6"/>
     </row>
-    <row r="403" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -9845,7 +9845,7 @@
       <c r="K403" s="6"/>
       <c r="L403" s="6"/>
     </row>
-    <row r="404" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -9859,7 +9859,7 @@
       <c r="K404" s="6"/>
       <c r="L404" s="6"/>
     </row>
-    <row r="405" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -9873,7 +9873,7 @@
       <c r="K405" s="6"/>
       <c r="L405" s="6"/>
     </row>
-    <row r="406" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -9887,7 +9887,7 @@
       <c r="K406" s="6"/>
       <c r="L406" s="6"/>
     </row>
-    <row r="407" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -9901,7 +9901,7 @@
       <c r="K407" s="6"/>
       <c r="L407" s="6"/>
     </row>
-    <row r="408" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -9915,7 +9915,7 @@
       <c r="K408" s="6"/>
       <c r="L408" s="6"/>
     </row>
-    <row r="409" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -9929,7 +9929,7 @@
       <c r="K409" s="6"/>
       <c r="L409" s="6"/>
     </row>
-    <row r="410" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -9943,7 +9943,7 @@
       <c r="K410" s="6"/>
       <c r="L410" s="6"/>
     </row>
-    <row r="411" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -9957,7 +9957,7 @@
       <c r="K411" s="6"/>
       <c r="L411" s="6"/>
     </row>
-    <row r="412" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -9971,7 +9971,7 @@
       <c r="K412" s="6"/>
       <c r="L412" s="6"/>
     </row>
-    <row r="413" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -9985,7 +9985,7 @@
       <c r="K413" s="6"/>
       <c r="L413" s="6"/>
     </row>
-    <row r="414" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -9999,7 +9999,7 @@
       <c r="K414" s="6"/>
       <c r="L414" s="6"/>
     </row>
-    <row r="415" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -10013,7 +10013,7 @@
       <c r="K415" s="6"/>
       <c r="L415" s="6"/>
     </row>
-    <row r="416" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -10027,7 +10027,7 @@
       <c r="K416" s="6"/>
       <c r="L416" s="6"/>
     </row>
-    <row r="417" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -10041,7 +10041,7 @@
       <c r="K417" s="6"/>
       <c r="L417" s="6"/>
     </row>
-    <row r="418" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -10055,7 +10055,7 @@
       <c r="K418" s="6"/>
       <c r="L418" s="6"/>
     </row>
-    <row r="419" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -10069,7 +10069,7 @@
       <c r="K419" s="6"/>
       <c r="L419" s="6"/>
     </row>
-    <row r="420" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -10083,7 +10083,7 @@
       <c r="K420" s="6"/>
       <c r="L420" s="6"/>
     </row>
-    <row r="421" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -10097,7 +10097,7 @@
       <c r="K421" s="6"/>
       <c r="L421" s="6"/>
     </row>
-    <row r="422" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -10111,7 +10111,7 @@
       <c r="K422" s="6"/>
       <c r="L422" s="6"/>
     </row>
-    <row r="423" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -10125,7 +10125,7 @@
       <c r="K423" s="6"/>
       <c r="L423" s="6"/>
     </row>
-    <row r="424" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -10139,7 +10139,7 @@
       <c r="K424" s="6"/>
       <c r="L424" s="6"/>
     </row>
-    <row r="425" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -10153,7 +10153,7 @@
       <c r="K425" s="6"/>
       <c r="L425" s="6"/>
     </row>
-    <row r="426" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -10167,7 +10167,7 @@
       <c r="K426" s="6"/>
       <c r="L426" s="6"/>
     </row>
-    <row r="427" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -10181,7 +10181,7 @@
       <c r="K427" s="6"/>
       <c r="L427" s="6"/>
     </row>
-    <row r="428" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -10195,7 +10195,7 @@
       <c r="K428" s="6"/>
       <c r="L428" s="6"/>
     </row>
-    <row r="429" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -10209,7 +10209,7 @@
       <c r="K429" s="6"/>
       <c r="L429" s="6"/>
     </row>
-    <row r="430" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -10223,7 +10223,7 @@
       <c r="K430" s="6"/>
       <c r="L430" s="6"/>
     </row>
-    <row r="431" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -10237,7 +10237,7 @@
       <c r="K431" s="6"/>
       <c r="L431" s="6"/>
     </row>
-    <row r="432" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -10251,7 +10251,7 @@
       <c r="K432" s="6"/>
       <c r="L432" s="6"/>
     </row>
-    <row r="433" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -10265,7 +10265,7 @@
       <c r="K433" s="6"/>
       <c r="L433" s="6"/>
     </row>
-    <row r="434" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -10279,7 +10279,7 @@
       <c r="K434" s="6"/>
       <c r="L434" s="6"/>
     </row>
-    <row r="435" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -10293,7 +10293,7 @@
       <c r="K435" s="6"/>
       <c r="L435" s="6"/>
     </row>
-    <row r="436" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -10307,7 +10307,7 @@
       <c r="K436" s="6"/>
       <c r="L436" s="6"/>
     </row>
-    <row r="437" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -10321,7 +10321,7 @@
       <c r="K437" s="6"/>
       <c r="L437" s="6"/>
     </row>
-    <row r="438" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -10335,7 +10335,7 @@
       <c r="K438" s="6"/>
       <c r="L438" s="6"/>
     </row>
-    <row r="439" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -10349,7 +10349,7 @@
       <c r="K439" s="6"/>
       <c r="L439" s="6"/>
     </row>
-    <row r="440" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -10363,7 +10363,7 @@
       <c r="K440" s="6"/>
       <c r="L440" s="6"/>
     </row>
-    <row r="441" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -10377,7 +10377,7 @@
       <c r="K441" s="6"/>
       <c r="L441" s="6"/>
     </row>
-    <row r="442" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -10391,7 +10391,7 @@
       <c r="K442" s="6"/>
       <c r="L442" s="6"/>
     </row>
-    <row r="443" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -10405,7 +10405,7 @@
       <c r="K443" s="6"/>
       <c r="L443" s="6"/>
     </row>
-    <row r="444" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -10419,7 +10419,7 @@
       <c r="K444" s="6"/>
       <c r="L444" s="6"/>
     </row>
-    <row r="445" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -10433,7 +10433,7 @@
       <c r="K445" s="6"/>
       <c r="L445" s="6"/>
     </row>
-    <row r="446" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -10447,7 +10447,7 @@
       <c r="K446" s="6"/>
       <c r="L446" s="6"/>
     </row>
-    <row r="447" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -10461,7 +10461,7 @@
       <c r="K447" s="6"/>
       <c r="L447" s="6"/>
     </row>
-    <row r="448" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A448" s="5"/>
       <c r="B448" s="5"/>
       <c r="C448" s="5"/>
@@ -10475,7 +10475,7 @@
       <c r="K448" s="6"/>
       <c r="L448" s="6"/>
     </row>
-    <row r="449" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A449" s="5"/>
       <c r="B449" s="5"/>
       <c r="C449" s="5"/>
@@ -10489,7 +10489,7 @@
       <c r="K449" s="6"/>
       <c r="L449" s="6"/>
     </row>
-    <row r="450" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A450" s="5"/>
       <c r="B450" s="5"/>
       <c r="C450" s="5"/>
@@ -10503,7 +10503,7 @@
       <c r="K450" s="6"/>
       <c r="L450" s="6"/>
     </row>
-    <row r="451" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A451" s="5"/>
       <c r="B451" s="5"/>
       <c r="C451" s="5"/>
@@ -10517,7 +10517,7 @@
       <c r="K451" s="6"/>
       <c r="L451" s="6"/>
     </row>
-    <row r="452" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A452" s="5"/>
       <c r="B452" s="5"/>
       <c r="C452" s="5"/>
@@ -10531,7 +10531,7 @@
       <c r="K452" s="6"/>
       <c r="L452" s="6"/>
     </row>
-    <row r="453" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A453" s="5"/>
       <c r="B453" s="5"/>
       <c r="C453" s="5"/>
@@ -10545,7 +10545,7 @@
       <c r="K453" s="6"/>
       <c r="L453" s="6"/>
     </row>
-    <row r="454" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A454" s="5"/>
       <c r="B454" s="5"/>
       <c r="C454" s="5"/>
@@ -10559,7 +10559,7 @@
       <c r="K454" s="6"/>
       <c r="L454" s="6"/>
     </row>
-    <row r="455" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A455" s="5"/>
       <c r="B455" s="5"/>
       <c r="C455" s="5"/>
@@ -10573,7 +10573,7 @@
       <c r="K455" s="6"/>
       <c r="L455" s="6"/>
     </row>
-    <row r="456" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A456" s="5"/>
       <c r="B456" s="5"/>
       <c r="C456" s="5"/>
@@ -10587,7 +10587,7 @@
       <c r="K456" s="6"/>
       <c r="L456" s="6"/>
     </row>
-    <row r="457" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A457" s="5"/>
       <c r="B457" s="5"/>
       <c r="C457" s="5"/>
@@ -10601,7 +10601,7 @@
       <c r="K457" s="6"/>
       <c r="L457" s="6"/>
     </row>
-    <row r="458" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A458" s="5"/>
       <c r="B458" s="5"/>
       <c r="C458" s="5"/>
@@ -10615,7 +10615,7 @@
       <c r="K458" s="6"/>
       <c r="L458" s="6"/>
     </row>
-    <row r="459" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A459" s="5"/>
       <c r="B459" s="5"/>
       <c r="C459" s="5"/>
@@ -10629,7 +10629,7 @@
       <c r="K459" s="6"/>
       <c r="L459" s="6"/>
     </row>
-    <row r="460" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A460" s="5"/>
       <c r="B460" s="5"/>
       <c r="C460" s="5"/>
@@ -10643,7 +10643,7 @@
       <c r="K460" s="6"/>
       <c r="L460" s="6"/>
     </row>
-    <row r="461" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A461" s="5"/>
       <c r="B461" s="5"/>
       <c r="C461" s="5"/>
@@ -10657,7 +10657,7 @@
       <c r="K461" s="6"/>
       <c r="L461" s="6"/>
     </row>
-    <row r="462" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A462" s="5"/>
       <c r="B462" s="5"/>
       <c r="C462" s="5"/>
@@ -10671,7 +10671,7 @@
       <c r="K462" s="6"/>
       <c r="L462" s="6"/>
     </row>
-    <row r="463" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A463" s="5"/>
       <c r="B463" s="5"/>
       <c r="C463" s="5"/>
@@ -10685,7 +10685,7 @@
       <c r="K463" s="6"/>
       <c r="L463" s="6"/>
     </row>
-    <row r="464" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A464" s="5"/>
       <c r="B464" s="5"/>
       <c r="C464" s="5"/>
@@ -10699,7 +10699,7 @@
       <c r="K464" s="6"/>
       <c r="L464" s="6"/>
     </row>
-    <row r="465" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A465" s="5"/>
       <c r="B465" s="5"/>
       <c r="C465" s="5"/>
@@ -10713,7 +10713,7 @@
       <c r="K465" s="6"/>
       <c r="L465" s="6"/>
     </row>
-    <row r="466" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A466" s="5"/>
       <c r="B466" s="5"/>
       <c r="C466" s="5"/>
@@ -10727,7 +10727,7 @@
       <c r="K466" s="6"/>
       <c r="L466" s="6"/>
     </row>
-    <row r="467" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A467" s="5"/>
       <c r="B467" s="5"/>
       <c r="C467" s="5"/>
@@ -10741,7 +10741,7 @@
       <c r="K467" s="6"/>
       <c r="L467" s="6"/>
     </row>
-    <row r="468" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A468" s="5"/>
       <c r="B468" s="5"/>
       <c r="C468" s="5"/>
@@ -10755,7 +10755,7 @@
       <c r="K468" s="6"/>
       <c r="L468" s="6"/>
     </row>
-    <row r="469" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A469" s="5"/>
       <c r="B469" s="5"/>
       <c r="C469" s="5"/>
@@ -10769,7 +10769,7 @@
       <c r="K469" s="6"/>
       <c r="L469" s="6"/>
     </row>
-    <row r="470" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A470" s="5"/>
       <c r="B470" s="5"/>
       <c r="C470" s="5"/>
@@ -10783,7 +10783,7 @@
       <c r="K470" s="6"/>
       <c r="L470" s="6"/>
     </row>
-    <row r="471" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A471" s="5"/>
       <c r="B471" s="5"/>
       <c r="C471" s="5"/>
@@ -10797,7 +10797,7 @@
       <c r="K471" s="6"/>
       <c r="L471" s="6"/>
     </row>
-    <row r="472" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A472" s="5"/>
       <c r="B472" s="5"/>
       <c r="C472" s="5"/>
@@ -10811,7 +10811,7 @@
       <c r="K472" s="6"/>
       <c r="L472" s="6"/>
     </row>
-    <row r="473" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A473" s="5"/>
       <c r="B473" s="5"/>
       <c r="C473" s="5"/>
@@ -10825,7 +10825,7 @@
       <c r="K473" s="6"/>
       <c r="L473" s="6"/>
     </row>
-    <row r="474" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A474" s="5"/>
       <c r="B474" s="5"/>
       <c r="C474" s="5"/>
@@ -10839,7 +10839,7 @@
       <c r="K474" s="6"/>
       <c r="L474" s="6"/>
     </row>
-    <row r="475" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A475" s="5"/>
       <c r="B475" s="5"/>
       <c r="C475" s="5"/>
@@ -10853,7 +10853,7 @@
       <c r="K475" s="6"/>
       <c r="L475" s="6"/>
     </row>
-    <row r="476" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A476" s="5"/>
       <c r="B476" s="5"/>
       <c r="C476" s="5"/>
@@ -10867,7 +10867,7 @@
       <c r="K476" s="6"/>
       <c r="L476" s="6"/>
     </row>
-    <row r="477" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A477" s="5"/>
       <c r="B477" s="5"/>
       <c r="C477" s="5"/>
@@ -10881,7 +10881,7 @@
       <c r="K477" s="6"/>
       <c r="L477" s="6"/>
     </row>
-    <row r="478" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A478" s="5"/>
       <c r="B478" s="5"/>
       <c r="C478" s="5"/>
@@ -10895,7 +10895,7 @@
       <c r="K478" s="6"/>
       <c r="L478" s="6"/>
     </row>
-    <row r="479" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A479" s="5"/>
       <c r="B479" s="5"/>
       <c r="C479" s="5"/>
@@ -10909,7 +10909,7 @@
       <c r="K479" s="6"/>
       <c r="L479" s="6"/>
     </row>
-    <row r="480" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A480" s="5"/>
       <c r="B480" s="5"/>
       <c r="C480" s="5"/>
@@ -10923,7 +10923,7 @@
       <c r="K480" s="6"/>
       <c r="L480" s="6"/>
     </row>
-    <row r="481" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A481" s="5"/>
       <c r="B481" s="5"/>
       <c r="C481" s="5"/>
@@ -10937,7 +10937,7 @@
       <c r="K481" s="6"/>
       <c r="L481" s="6"/>
     </row>
-    <row r="482" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A482" s="5"/>
       <c r="B482" s="5"/>
       <c r="C482" s="5"/>
@@ -10951,7 +10951,7 @@
       <c r="K482" s="6"/>
       <c r="L482" s="6"/>
     </row>
-    <row r="483" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A483" s="5"/>
       <c r="B483" s="5"/>
       <c r="C483" s="5"/>
@@ -10965,7 +10965,7 @@
       <c r="K483" s="6"/>
       <c r="L483" s="6"/>
     </row>
-    <row r="484" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A484" s="5"/>
       <c r="B484" s="5"/>
       <c r="C484" s="5"/>
@@ -10979,7 +10979,7 @@
       <c r="K484" s="6"/>
       <c r="L484" s="6"/>
     </row>
-    <row r="485" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A485" s="5"/>
       <c r="B485" s="5"/>
       <c r="C485" s="5"/>
@@ -10993,7 +10993,7 @@
       <c r="K485" s="6"/>
       <c r="L485" s="6"/>
     </row>
-    <row r="486" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A486" s="5"/>
       <c r="B486" s="5"/>
       <c r="C486" s="5"/>
@@ -11007,7 +11007,7 @@
       <c r="K486" s="6"/>
       <c r="L486" s="6"/>
     </row>
-    <row r="487" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A487" s="5"/>
       <c r="B487" s="5"/>
       <c r="C487" s="5"/>
@@ -11021,7 +11021,7 @@
       <c r="K487" s="6"/>
       <c r="L487" s="6"/>
     </row>
-    <row r="488" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A488" s="5"/>
       <c r="B488" s="5"/>
       <c r="C488" s="5"/>
@@ -11035,7 +11035,7 @@
       <c r="K488" s="6"/>
       <c r="L488" s="6"/>
     </row>
-    <row r="489" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A489" s="5"/>
       <c r="B489" s="5"/>
       <c r="C489" s="5"/>
@@ -11049,7 +11049,7 @@
       <c r="K489" s="6"/>
       <c r="L489" s="6"/>
     </row>
-    <row r="490" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A490" s="5"/>
       <c r="B490" s="5"/>
       <c r="C490" s="5"/>
@@ -11063,7 +11063,7 @@
       <c r="K490" s="6"/>
       <c r="L490" s="6"/>
     </row>
-    <row r="491" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A491" s="5"/>
       <c r="B491" s="5"/>
       <c r="C491" s="5"/>
@@ -11077,7 +11077,7 @@
       <c r="K491" s="6"/>
       <c r="L491" s="6"/>
     </row>
-    <row r="492" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A492" s="5"/>
       <c r="B492" s="5"/>
       <c r="C492" s="5"/>
@@ -11091,7 +11091,7 @@
       <c r="K492" s="6"/>
       <c r="L492" s="6"/>
     </row>
-    <row r="493" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A493" s="5"/>
       <c r="B493" s="5"/>
       <c r="C493" s="5"/>
@@ -11105,7 +11105,7 @@
       <c r="K493" s="6"/>
       <c r="L493" s="6"/>
     </row>
-    <row r="494" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A494" s="5"/>
       <c r="B494" s="5"/>
       <c r="C494" s="5"/>
@@ -11119,7 +11119,7 @@
       <c r="K494" s="6"/>
       <c r="L494" s="6"/>
     </row>
-    <row r="495" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A495" s="5"/>
       <c r="B495" s="5"/>
       <c r="C495" s="5"/>
@@ -11133,7 +11133,7 @@
       <c r="K495" s="6"/>
       <c r="L495" s="6"/>
     </row>
-    <row r="496" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A496" s="5"/>
       <c r="B496" s="5"/>
       <c r="C496" s="5"/>
@@ -11147,7 +11147,7 @@
       <c r="K496" s="6"/>
       <c r="L496" s="6"/>
     </row>
-    <row r="497" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A497" s="5"/>
       <c r="B497" s="5"/>
       <c r="C497" s="5"/>
@@ -11161,7 +11161,7 @@
       <c r="K497" s="6"/>
       <c r="L497" s="6"/>
     </row>
-    <row r="498" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A498" s="5"/>
       <c r="B498" s="5"/>
       <c r="C498" s="5"/>
@@ -11175,7 +11175,7 @@
       <c r="K498" s="6"/>
       <c r="L498" s="6"/>
     </row>
-    <row r="499" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A499" s="5"/>
       <c r="B499" s="5"/>
       <c r="C499" s="5"/>
@@ -11189,7 +11189,7 @@
       <c r="K499" s="6"/>
       <c r="L499" s="6"/>
     </row>
-    <row r="500" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A500" s="5"/>
       <c r="B500" s="5"/>
       <c r="C500" s="5"/>
@@ -11203,7 +11203,7 @@
       <c r="K500" s="6"/>
       <c r="L500" s="6"/>
     </row>
-    <row r="501" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A501" s="5"/>
       <c r="B501" s="5"/>
       <c r="C501" s="5"/>
@@ -11217,7 +11217,7 @@
       <c r="K501" s="6"/>
       <c r="L501" s="6"/>
     </row>
-    <row r="502" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A502" s="5"/>
       <c r="B502" s="5"/>
       <c r="C502" s="5"/>
@@ -11231,7 +11231,7 @@
       <c r="K502" s="6"/>
       <c r="L502" s="6"/>
     </row>
-    <row r="503" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A503" s="5"/>
       <c r="B503" s="5"/>
       <c r="C503" s="5"/>
@@ -11245,7 +11245,7 @@
       <c r="K503" s="6"/>
       <c r="L503" s="6"/>
     </row>
-    <row r="504" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A504" s="5"/>
       <c r="B504" s="5"/>
       <c r="C504" s="5"/>
@@ -11259,7 +11259,7 @@
       <c r="K504" s="6"/>
       <c r="L504" s="6"/>
     </row>
-    <row r="505" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A505" s="5"/>
       <c r="B505" s="5"/>
       <c r="C505" s="5"/>
@@ -11273,7 +11273,7 @@
       <c r="K505" s="6"/>
       <c r="L505" s="6"/>
     </row>
-    <row r="506" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A506" s="5"/>
       <c r="B506" s="5"/>
       <c r="C506" s="5"/>
@@ -11287,7 +11287,7 @@
       <c r="K506" s="6"/>
       <c r="L506" s="6"/>
     </row>
-    <row r="507" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A507" s="5"/>
       <c r="B507" s="5"/>
       <c r="C507" s="5"/>
@@ -11301,7 +11301,7 @@
       <c r="K507" s="6"/>
       <c r="L507" s="6"/>
     </row>
-    <row r="508" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A508" s="5"/>
       <c r="B508" s="5"/>
       <c r="C508" s="5"/>
@@ -11315,7 +11315,7 @@
       <c r="K508" s="6"/>
       <c r="L508" s="6"/>
     </row>
-    <row r="509" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A509" s="5"/>
       <c r="B509" s="5"/>
       <c r="C509" s="5"/>
@@ -11329,7 +11329,7 @@
       <c r="K509" s="6"/>
       <c r="L509" s="6"/>
     </row>
-    <row r="510" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A510" s="5"/>
       <c r="B510" s="5"/>
       <c r="C510" s="5"/>
@@ -11343,7 +11343,7 @@
       <c r="K510" s="6"/>
       <c r="L510" s="6"/>
     </row>
-    <row r="511" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A511" s="5"/>
       <c r="B511" s="5"/>
       <c r="C511" s="5"/>
@@ -11357,7 +11357,7 @@
       <c r="K511" s="6"/>
       <c r="L511" s="6"/>
     </row>
-    <row r="512" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A512" s="5"/>
       <c r="B512" s="5"/>
       <c r="C512" s="5"/>
@@ -11371,7 +11371,7 @@
       <c r="K512" s="6"/>
       <c r="L512" s="6"/>
     </row>
-    <row r="513" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A513" s="5"/>
       <c r="B513" s="5"/>
       <c r="C513" s="5"/>
@@ -11385,7 +11385,7 @@
       <c r="K513" s="6"/>
       <c r="L513" s="6"/>
     </row>
-    <row r="514" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A514" s="5"/>
       <c r="B514" s="5"/>
       <c r="C514" s="5"/>
@@ -11399,7 +11399,7 @@
       <c r="K514" s="6"/>
       <c r="L514" s="6"/>
     </row>
-    <row r="515" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A515" s="5"/>
       <c r="B515" s="5"/>
       <c r="C515" s="5"/>
@@ -11413,7 +11413,7 @@
       <c r="K515" s="6"/>
       <c r="L515" s="6"/>
     </row>
-    <row r="516" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A516" s="5"/>
       <c r="B516" s="5"/>
       <c r="C516" s="5"/>
@@ -11427,7 +11427,7 @@
       <c r="K516" s="6"/>
       <c r="L516" s="6"/>
     </row>
-    <row r="517" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A517" s="5"/>
       <c r="B517" s="5"/>
       <c r="C517" s="5"/>
@@ -11441,7 +11441,7 @@
       <c r="K517" s="6"/>
       <c r="L517" s="6"/>
     </row>
-    <row r="518" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A518" s="5"/>
       <c r="B518" s="5"/>
       <c r="C518" s="5"/>
@@ -11455,7 +11455,7 @@
       <c r="K518" s="6"/>
       <c r="L518" s="6"/>
     </row>
-    <row r="519" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A519" s="5"/>
       <c r="B519" s="5"/>
       <c r="C519" s="5"/>
@@ -11469,7 +11469,7 @@
       <c r="K519" s="6"/>
       <c r="L519" s="6"/>
     </row>
-    <row r="520" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A520" s="5"/>
       <c r="B520" s="5"/>
       <c r="C520" s="5"/>
@@ -11483,7 +11483,7 @@
       <c r="K520" s="6"/>
       <c r="L520" s="6"/>
     </row>
-    <row r="521" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A521" s="5"/>
       <c r="B521" s="5"/>
       <c r="C521" s="5"/>
@@ -11497,7 +11497,7 @@
       <c r="K521" s="6"/>
       <c r="L521" s="6"/>
     </row>
-    <row r="522" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A522" s="5"/>
       <c r="B522" s="5"/>
       <c r="C522" s="5"/>
@@ -11511,7 +11511,7 @@
       <c r="K522" s="6"/>
       <c r="L522" s="6"/>
     </row>
-    <row r="523" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A523" s="5"/>
       <c r="B523" s="5"/>
       <c r="C523" s="5"/>
@@ -11525,7 +11525,7 @@
       <c r="K523" s="6"/>
       <c r="L523" s="6"/>
     </row>
-    <row r="524" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A524" s="5"/>
       <c r="B524" s="5"/>
       <c r="C524" s="5"/>
@@ -11539,7 +11539,7 @@
       <c r="K524" s="6"/>
       <c r="L524" s="6"/>
     </row>
-    <row r="525" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A525" s="5"/>
       <c r="B525" s="5"/>
       <c r="C525" s="5"/>
@@ -11553,7 +11553,7 @@
       <c r="K525" s="6"/>
       <c r="L525" s="6"/>
     </row>
-    <row r="526" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A526" s="5"/>
       <c r="B526" s="5"/>
       <c r="C526" s="5"/>
@@ -11567,7 +11567,7 @@
       <c r="K526" s="6"/>
       <c r="L526" s="6"/>
     </row>
-    <row r="527" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A527" s="5"/>
       <c r="B527" s="5"/>
       <c r="C527" s="5"/>
@@ -11581,7 +11581,7 @@
       <c r="K527" s="6"/>
       <c r="L527" s="6"/>
     </row>
-    <row r="528" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A528" s="5"/>
       <c r="B528" s="5"/>
       <c r="C528" s="5"/>
@@ -11595,7 +11595,7 @@
       <c r="K528" s="6"/>
       <c r="L528" s="6"/>
     </row>
-    <row r="529" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A529" s="5"/>
       <c r="B529" s="5"/>
       <c r="C529" s="5"/>
@@ -11609,7 +11609,7 @@
       <c r="K529" s="6"/>
       <c r="L529" s="6"/>
     </row>
-    <row r="530" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A530" s="5"/>
       <c r="B530" s="5"/>
       <c r="C530" s="5"/>
@@ -11623,7 +11623,7 @@
       <c r="K530" s="6"/>
       <c r="L530" s="6"/>
     </row>
-    <row r="531" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A531" s="5"/>
       <c r="B531" s="5"/>
       <c r="C531" s="5"/>
@@ -11637,7 +11637,7 @@
       <c r="K531" s="6"/>
       <c r="L531" s="6"/>
     </row>
-    <row r="532" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A532" s="5"/>
       <c r="B532" s="5"/>
       <c r="C532" s="5"/>
@@ -11651,7 +11651,7 @@
       <c r="K532" s="6"/>
       <c r="L532" s="6"/>
     </row>
-    <row r="533" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A533" s="5"/>
       <c r="B533" s="5"/>
       <c r="C533" s="5"/>
@@ -11665,7 +11665,7 @@
       <c r="K533" s="6"/>
       <c r="L533" s="6"/>
     </row>
-    <row r="534" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A534" s="5"/>
       <c r="B534" s="5"/>
       <c r="C534" s="5"/>
@@ -11679,7 +11679,7 @@
       <c r="K534" s="6"/>
       <c r="L534" s="6"/>
     </row>
-    <row r="535" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A535" s="5"/>
       <c r="B535" s="5"/>
       <c r="C535" s="5"/>
@@ -11693,7 +11693,7 @@
       <c r="K535" s="6"/>
       <c r="L535" s="6"/>
     </row>
-    <row r="536" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A536" s="5"/>
       <c r="B536" s="5"/>
       <c r="C536" s="5"/>
@@ -11707,7 +11707,7 @@
       <c r="K536" s="6"/>
       <c r="L536" s="6"/>
     </row>
-    <row r="537" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A537" s="5"/>
       <c r="B537" s="5"/>
       <c r="C537" s="5"/>
@@ -11721,7 +11721,7 @@
       <c r="K537" s="6"/>
       <c r="L537" s="6"/>
     </row>
-    <row r="538" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A538" s="5"/>
       <c r="B538" s="5"/>
       <c r="C538" s="5"/>
@@ -11735,7 +11735,7 @@
       <c r="K538" s="6"/>
       <c r="L538" s="6"/>
     </row>
-    <row r="539" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A539" s="5"/>
       <c r="B539" s="5"/>
       <c r="C539" s="5"/>
@@ -11749,7 +11749,7 @@
       <c r="K539" s="6"/>
       <c r="L539" s="6"/>
     </row>
-    <row r="540" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A540" s="5"/>
       <c r="B540" s="5"/>
       <c r="C540" s="5"/>
@@ -11763,7 +11763,7 @@
       <c r="K540" s="6"/>
       <c r="L540" s="6"/>
     </row>
-    <row r="541" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A541" s="5"/>
       <c r="B541" s="5"/>
       <c r="C541" s="5"/>
@@ -11777,7 +11777,7 @@
       <c r="K541" s="6"/>
       <c r="L541" s="6"/>
     </row>
-    <row r="542" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A542" s="5"/>
       <c r="B542" s="5"/>
       <c r="C542" s="5"/>
@@ -11791,7 +11791,7 @@
       <c r="K542" s="6"/>
       <c r="L542" s="6"/>
     </row>
-    <row r="543" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A543" s="5"/>
       <c r="B543" s="5"/>
       <c r="C543" s="5"/>
@@ -11805,7 +11805,7 @@
       <c r="K543" s="6"/>
       <c r="L543" s="6"/>
     </row>
-    <row r="544" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A544" s="5"/>
       <c r="B544" s="5"/>
       <c r="C544" s="5"/>
@@ -11819,7 +11819,7 @@
       <c r="K544" s="6"/>
       <c r="L544" s="6"/>
     </row>
-    <row r="545" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A545" s="5"/>
       <c r="B545" s="5"/>
       <c r="C545" s="5"/>
@@ -11833,7 +11833,7 @@
       <c r="K545" s="6"/>
       <c r="L545" s="6"/>
     </row>
-    <row r="546" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A546" s="5"/>
       <c r="B546" s="5"/>
       <c r="C546" s="5"/>
@@ -11847,7 +11847,7 @@
       <c r="K546" s="6"/>
       <c r="L546" s="6"/>
     </row>
-    <row r="547" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A547" s="5"/>
       <c r="B547" s="5"/>
       <c r="C547" s="5"/>
@@ -11861,7 +11861,7 @@
       <c r="K547" s="6"/>
       <c r="L547" s="6"/>
     </row>
-    <row r="548" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A548" s="5"/>
       <c r="B548" s="5"/>
       <c r="C548" s="5"/>
@@ -11875,7 +11875,7 @@
       <c r="K548" s="6"/>
       <c r="L548" s="6"/>
     </row>
-    <row r="549" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A549" s="5"/>
       <c r="B549" s="5"/>
       <c r="C549" s="5"/>
@@ -11889,7 +11889,7 @@
       <c r="K549" s="6"/>
       <c r="L549" s="6"/>
     </row>
-    <row r="550" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A550" s="5"/>
       <c r="B550" s="5"/>
       <c r="C550" s="5"/>
@@ -11903,7 +11903,7 @@
       <c r="K550" s="6"/>
       <c r="L550" s="6"/>
     </row>
-    <row r="551" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A551" s="5"/>
       <c r="B551" s="5"/>
       <c r="C551" s="5"/>
@@ -11917,7 +11917,7 @@
       <c r="K551" s="6"/>
       <c r="L551" s="6"/>
     </row>
-    <row r="552" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A552" s="5"/>
       <c r="B552" s="5"/>
       <c r="C552" s="5"/>
@@ -11931,7 +11931,7 @@
       <c r="K552" s="6"/>
       <c r="L552" s="6"/>
     </row>
-    <row r="553" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A553" s="5"/>
       <c r="B553" s="5"/>
       <c r="C553" s="5"/>
@@ -11945,7 +11945,7 @@
       <c r="K553" s="6"/>
       <c r="L553" s="6"/>
     </row>
-    <row r="554" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A554" s="5"/>
       <c r="B554" s="5"/>
       <c r="C554" s="5"/>
@@ -11959,7 +11959,7 @@
       <c r="K554" s="6"/>
       <c r="L554" s="6"/>
     </row>
-    <row r="555" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A555" s="5"/>
       <c r="B555" s="5"/>
       <c r="C555" s="5"/>
@@ -11973,7 +11973,7 @@
       <c r="K555" s="6"/>
       <c r="L555" s="6"/>
     </row>
-    <row r="556" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A556" s="5"/>
       <c r="B556" s="5"/>
       <c r="C556" s="5"/>
@@ -11987,7 +11987,7 @@
       <c r="K556" s="6"/>
       <c r="L556" s="6"/>
     </row>
-    <row r="557" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A557" s="5"/>
       <c r="B557" s="5"/>
       <c r="C557" s="5"/>
@@ -12001,7 +12001,7 @@
       <c r="K557" s="6"/>
       <c r="L557" s="6"/>
     </row>
-    <row r="558" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A558" s="5"/>
       <c r="B558" s="5"/>
       <c r="C558" s="5"/>
@@ -12015,7 +12015,7 @@
       <c r="K558" s="6"/>
       <c r="L558" s="6"/>
     </row>
-    <row r="559" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A559" s="5"/>
       <c r="B559" s="5"/>
       <c r="C559" s="5"/>
@@ -12029,7 +12029,7 @@
       <c r="K559" s="6"/>
       <c r="L559" s="6"/>
     </row>
-    <row r="560" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A560" s="5"/>
       <c r="B560" s="5"/>
       <c r="C560" s="5"/>
@@ -12043,7 +12043,7 @@
       <c r="K560" s="6"/>
       <c r="L560" s="6"/>
     </row>
-    <row r="561" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A561" s="5"/>
       <c r="B561" s="5"/>
       <c r="C561" s="5"/>
@@ -12057,7 +12057,7 @@
       <c r="K561" s="6"/>
       <c r="L561" s="6"/>
     </row>
-    <row r="562" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A562" s="5"/>
       <c r="B562" s="5"/>
       <c r="C562" s="5"/>
@@ -12071,7 +12071,7 @@
       <c r="K562" s="6"/>
       <c r="L562" s="6"/>
     </row>
-    <row r="563" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A563" s="5"/>
       <c r="B563" s="5"/>
       <c r="C563" s="5"/>
@@ -12085,7 +12085,7 @@
       <c r="K563" s="6"/>
       <c r="L563" s="6"/>
     </row>
-    <row r="564" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A564" s="5"/>
       <c r="B564" s="5"/>
       <c r="C564" s="5"/>
@@ -12099,7 +12099,7 @@
       <c r="K564" s="6"/>
       <c r="L564" s="6"/>
     </row>
-    <row r="565" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A565" s="5"/>
       <c r="B565" s="5"/>
       <c r="C565" s="5"/>
@@ -12113,7 +12113,7 @@
       <c r="K565" s="6"/>
       <c r="L565" s="6"/>
     </row>
-    <row r="566" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A566" s="5"/>
       <c r="B566" s="5"/>
       <c r="C566" s="5"/>
@@ -12127,7 +12127,7 @@
       <c r="K566" s="6"/>
       <c r="L566" s="6"/>
     </row>
-    <row r="567" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A567" s="5"/>
       <c r="B567" s="5"/>
       <c r="C567" s="5"/>
@@ -12141,7 +12141,7 @@
       <c r="K567" s="6"/>
       <c r="L567" s="6"/>
     </row>
-    <row r="568" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A568" s="5"/>
       <c r="B568" s="5"/>
       <c r="C568" s="5"/>
@@ -12155,7 +12155,7 @@
       <c r="K568" s="6"/>
       <c r="L568" s="6"/>
     </row>
-    <row r="569" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A569" s="5"/>
       <c r="B569" s="5"/>
       <c r="C569" s="5"/>
@@ -12169,7 +12169,7 @@
       <c r="K569" s="6"/>
       <c r="L569" s="6"/>
     </row>
-    <row r="570" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A570" s="5"/>
       <c r="B570" s="5"/>
       <c r="C570" s="5"/>
@@ -12183,7 +12183,7 @@
       <c r="K570" s="6"/>
       <c r="L570" s="6"/>
     </row>
-    <row r="571" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A571" s="5"/>
       <c r="B571" s="5"/>
       <c r="C571" s="5"/>
@@ -12197,7 +12197,7 @@
       <c r="K571" s="6"/>
       <c r="L571" s="6"/>
     </row>
-    <row r="572" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A572" s="5"/>
       <c r="B572" s="5"/>
       <c r="C572" s="5"/>
@@ -12211,7 +12211,7 @@
       <c r="K572" s="6"/>
       <c r="L572" s="6"/>
     </row>
-    <row r="573" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A573" s="5"/>
       <c r="B573" s="5"/>
       <c r="C573" s="5"/>
@@ -12225,7 +12225,7 @@
       <c r="K573" s="6"/>
       <c r="L573" s="6"/>
     </row>
-    <row r="574" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A574" s="5"/>
       <c r="B574" s="5"/>
       <c r="C574" s="5"/>
@@ -12239,7 +12239,7 @@
       <c r="K574" s="6"/>
       <c r="L574" s="6"/>
     </row>
-    <row r="575" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A575" s="5"/>
       <c r="B575" s="5"/>
       <c r="C575" s="5"/>
@@ -12253,7 +12253,7 @@
       <c r="K575" s="6"/>
       <c r="L575" s="6"/>
     </row>
-    <row r="576" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A576" s="5"/>
       <c r="B576" s="5"/>
       <c r="C576" s="5"/>
@@ -12267,7 +12267,7 @@
       <c r="K576" s="6"/>
       <c r="L576" s="6"/>
     </row>
-    <row r="577" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A577" s="5"/>
       <c r="B577" s="5"/>
       <c r="C577" s="5"/>
@@ -12281,7 +12281,7 @@
       <c r="K577" s="6"/>
       <c r="L577" s="6"/>
     </row>
-    <row r="578" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A578" s="5"/>
       <c r="B578" s="5"/>
       <c r="C578" s="5"/>
@@ -12295,7 +12295,7 @@
       <c r="K578" s="6"/>
       <c r="L578" s="6"/>
     </row>
-    <row r="579" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A579" s="5"/>
       <c r="B579" s="5"/>
       <c r="C579" s="5"/>
@@ -12309,7 +12309,7 @@
       <c r="K579" s="6"/>
       <c r="L579" s="6"/>
     </row>
-    <row r="580" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A580" s="5"/>
       <c r="B580" s="5"/>
       <c r="C580" s="5"/>
@@ -12323,7 +12323,7 @@
       <c r="K580" s="6"/>
       <c r="L580" s="6"/>
     </row>
-    <row r="581" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A581" s="5"/>
       <c r="B581" s="5"/>
       <c r="C581" s="5"/>
@@ -12337,7 +12337,7 @@
       <c r="K581" s="6"/>
       <c r="L581" s="6"/>
     </row>
-    <row r="582" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A582" s="5"/>
       <c r="B582" s="5"/>
       <c r="C582" s="5"/>
@@ -12351,7 +12351,7 @@
       <c r="K582" s="6"/>
       <c r="L582" s="6"/>
     </row>
-    <row r="583" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A583" s="5"/>
       <c r="B583" s="5"/>
       <c r="C583" s="5"/>
@@ -12365,7 +12365,7 @@
       <c r="K583" s="6"/>
       <c r="L583" s="6"/>
     </row>
-    <row r="584" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A584" s="5"/>
       <c r="B584" s="5"/>
       <c r="C584" s="5"/>
@@ -12379,7 +12379,7 @@
       <c r="K584" s="6"/>
       <c r="L584" s="6"/>
     </row>
-    <row r="585" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A585" s="5"/>
       <c r="B585" s="5"/>
       <c r="C585" s="5"/>
@@ -12393,7 +12393,7 @@
       <c r="K585" s="6"/>
       <c r="L585" s="6"/>
     </row>
-    <row r="586" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A586" s="5"/>
       <c r="B586" s="5"/>
       <c r="C586" s="5"/>
@@ -12407,7 +12407,7 @@
       <c r="K586" s="6"/>
       <c r="L586" s="6"/>
     </row>
-    <row r="587" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A587" s="5"/>
       <c r="B587" s="5"/>
       <c r="C587" s="5"/>
@@ -12421,7 +12421,7 @@
       <c r="K587" s="6"/>
       <c r="L587" s="6"/>
     </row>
-    <row r="588" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A588" s="5"/>
       <c r="B588" s="5"/>
       <c r="C588" s="5"/>
@@ -12435,7 +12435,7 @@
       <c r="K588" s="6"/>
       <c r="L588" s="6"/>
     </row>
-    <row r="589" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A589" s="5"/>
       <c r="B589" s="5"/>
       <c r="C589" s="5"/>
@@ -12449,7 +12449,7 @@
       <c r="K589" s="6"/>
       <c r="L589" s="6"/>
     </row>
-    <row r="590" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A590" s="5"/>
       <c r="B590" s="5"/>
       <c r="C590" s="5"/>
@@ -12463,7 +12463,7 @@
       <c r="K590" s="6"/>
       <c r="L590" s="6"/>
     </row>
-    <row r="591" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A591" s="5"/>
       <c r="B591" s="5"/>
       <c r="C591" s="5"/>
@@ -12477,7 +12477,7 @@
       <c r="K591" s="6"/>
       <c r="L591" s="6"/>
     </row>
-    <row r="592" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A592" s="5"/>
       <c r="B592" s="5"/>
       <c r="C592" s="5"/>
@@ -12491,7 +12491,7 @@
       <c r="K592" s="6"/>
       <c r="L592" s="6"/>
     </row>
-    <row r="593" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A593" s="5"/>
       <c r="B593" s="5"/>
       <c r="C593" s="5"/>
@@ -12505,7 +12505,7 @@
       <c r="K593" s="6"/>
       <c r="L593" s="6"/>
     </row>
-    <row r="594" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A594" s="5"/>
       <c r="B594" s="5"/>
       <c r="C594" s="5"/>
@@ -12519,7 +12519,7 @@
       <c r="K594" s="6"/>
       <c r="L594" s="6"/>
     </row>
-    <row r="595" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A595" s="5"/>
       <c r="B595" s="5"/>
       <c r="C595" s="5"/>
@@ -12533,7 +12533,7 @@
       <c r="K595" s="6"/>
       <c r="L595" s="6"/>
     </row>
-    <row r="596" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A596" s="5"/>
       <c r="B596" s="5"/>
       <c r="C596" s="5"/>
@@ -12547,7 +12547,7 @@
       <c r="K596" s="6"/>
       <c r="L596" s="6"/>
     </row>
-    <row r="597" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A597" s="5"/>
       <c r="B597" s="5"/>
       <c r="C597" s="5"/>
@@ -12561,7 +12561,7 @@
       <c r="K597" s="6"/>
       <c r="L597" s="6"/>
     </row>
-    <row r="598" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A598" s="5"/>
       <c r="B598" s="5"/>
       <c r="C598" s="5"/>
@@ -12575,7 +12575,7 @@
       <c r="K598" s="6"/>
       <c r="L598" s="6"/>
     </row>
-    <row r="599" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A599" s="5"/>
       <c r="B599" s="5"/>
       <c r="C599" s="5"/>
@@ -12589,7 +12589,7 @@
       <c r="K599" s="6"/>
       <c r="L599" s="6"/>
     </row>
-    <row r="600" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A600" s="5"/>
       <c r="B600" s="5"/>
       <c r="C600" s="5"/>
@@ -12603,7 +12603,7 @@
       <c r="K600" s="6"/>
       <c r="L600" s="6"/>
     </row>
-    <row r="601" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A601" s="5"/>
       <c r="B601" s="5"/>
       <c r="C601" s="5"/>
@@ -12617,7 +12617,7 @@
       <c r="K601" s="6"/>
       <c r="L601" s="6"/>
     </row>
-    <row r="602" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A602" s="5"/>
       <c r="B602" s="5"/>
       <c r="C602" s="5"/>
@@ -12631,7 +12631,7 @@
       <c r="K602" s="6"/>
       <c r="L602" s="6"/>
     </row>
-    <row r="603" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A603" s="5"/>
       <c r="B603" s="5"/>
       <c r="C603" s="5"/>
@@ -12645,7 +12645,7 @@
       <c r="K603" s="6"/>
       <c r="L603" s="6"/>
     </row>
-    <row r="604" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A604" s="5"/>
       <c r="B604" s="5"/>
       <c r="C604" s="5"/>
@@ -12659,7 +12659,7 @@
       <c r="K604" s="6"/>
       <c r="L604" s="6"/>
     </row>
-    <row r="605" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A605" s="5"/>
       <c r="B605" s="5"/>
       <c r="C605" s="5"/>
@@ -12673,7 +12673,7 @@
       <c r="K605" s="6"/>
       <c r="L605" s="6"/>
     </row>
-    <row r="606" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A606" s="5"/>
       <c r="B606" s="5"/>
       <c r="C606" s="5"/>
@@ -12687,7 +12687,7 @@
       <c r="K606" s="6"/>
       <c r="L606" s="6"/>
     </row>
-    <row r="607" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A607" s="5"/>
       <c r="B607" s="5"/>
       <c r="C607" s="5"/>
@@ -12701,7 +12701,7 @@
       <c r="K607" s="6"/>
       <c r="L607" s="6"/>
     </row>
-    <row r="608" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A608" s="5"/>
       <c r="B608" s="5"/>
       <c r="C608" s="5"/>
@@ -12715,7 +12715,7 @@
       <c r="K608" s="6"/>
       <c r="L608" s="6"/>
     </row>
-    <row r="609" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A609" s="5"/>
       <c r="B609" s="5"/>
       <c r="C609" s="5"/>
@@ -12729,7 +12729,7 @@
       <c r="K609" s="6"/>
       <c r="L609" s="6"/>
     </row>
-    <row r="610" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A610" s="5"/>
       <c r="B610" s="5"/>
       <c r="C610" s="5"/>
@@ -12743,7 +12743,7 @@
       <c r="K610" s="6"/>
       <c r="L610" s="6"/>
     </row>
-    <row r="611" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A611" s="5"/>
       <c r="B611" s="5"/>
       <c r="C611" s="5"/>
@@ -12757,7 +12757,7 @@
       <c r="K611" s="6"/>
       <c r="L611" s="6"/>
     </row>
-    <row r="612" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A612" s="5"/>
       <c r="B612" s="5"/>
       <c r="C612" s="5"/>
@@ -12771,7 +12771,7 @@
       <c r="K612" s="6"/>
       <c r="L612" s="6"/>
     </row>
-    <row r="613" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A613" s="5"/>
       <c r="B613" s="5"/>
       <c r="C613" s="5"/>
@@ -12785,7 +12785,7 @@
       <c r="K613" s="6"/>
       <c r="L613" s="6"/>
     </row>
-    <row r="614" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A614" s="5"/>
       <c r="B614" s="5"/>
       <c r="C614" s="5"/>
@@ -12799,7 +12799,7 @@
       <c r="K614" s="6"/>
       <c r="L614" s="6"/>
     </row>
-    <row r="615" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A615" s="5"/>
       <c r="B615" s="5"/>
       <c r="C615" s="5"/>
@@ -12813,7 +12813,7 @@
       <c r="K615" s="6"/>
       <c r="L615" s="6"/>
     </row>
-    <row r="616" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A616" s="5"/>
       <c r="B616" s="5"/>
       <c r="C616" s="5"/>
@@ -12827,7 +12827,7 @@
       <c r="K616" s="6"/>
       <c r="L616" s="6"/>
     </row>
-    <row r="617" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A617" s="5"/>
       <c r="B617" s="5"/>
       <c r="C617" s="5"/>
@@ -12841,7 +12841,7 @@
       <c r="K617" s="6"/>
       <c r="L617" s="6"/>
     </row>
-    <row r="618" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A618" s="5"/>
       <c r="B618" s="5"/>
       <c r="C618" s="5"/>
@@ -12855,7 +12855,7 @@
       <c r="K618" s="6"/>
       <c r="L618" s="6"/>
     </row>
-    <row r="619" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A619" s="5"/>
       <c r="B619" s="5"/>
       <c r="C619" s="5"/>
@@ -12869,7 +12869,7 @@
       <c r="K619" s="6"/>
       <c r="L619" s="6"/>
     </row>
-    <row r="620" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A620" s="5"/>
       <c r="B620" s="5"/>
       <c r="C620" s="5"/>
@@ -12883,7 +12883,7 @@
       <c r="K620" s="6"/>
       <c r="L620" s="6"/>
     </row>
-    <row r="621" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A621" s="5"/>
       <c r="B621" s="5"/>
       <c r="C621" s="5"/>
@@ -12897,7 +12897,7 @@
       <c r="K621" s="6"/>
       <c r="L621" s="6"/>
     </row>
-    <row r="622" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A622" s="5"/>
       <c r="B622" s="5"/>
       <c r="C622" s="5"/>
@@ -12911,7 +12911,7 @@
       <c r="K622" s="6"/>
       <c r="L622" s="6"/>
     </row>
-    <row r="623" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A623" s="5"/>
       <c r="B623" s="5"/>
       <c r="C623" s="5"/>
@@ -12925,7 +12925,7 @@
       <c r="K623" s="6"/>
       <c r="L623" s="6"/>
     </row>
-    <row r="624" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A624" s="5"/>
       <c r="B624" s="5"/>
       <c r="C624" s="5"/>
@@ -12939,7 +12939,7 @@
       <c r="K624" s="6"/>
       <c r="L624" s="6"/>
     </row>
-    <row r="625" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A625" s="5"/>
       <c r="B625" s="5"/>
       <c r="C625" s="5"/>
@@ -12953,7 +12953,7 @@
       <c r="K625" s="6"/>
       <c r="L625" s="6"/>
     </row>
-    <row r="626" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A626" s="5"/>
       <c r="B626" s="5"/>
       <c r="C626" s="5"/>
@@ -12967,7 +12967,7 @@
       <c r="K626" s="6"/>
       <c r="L626" s="6"/>
     </row>
-    <row r="627" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A627" s="5"/>
       <c r="B627" s="5"/>
       <c r="C627" s="5"/>
@@ -12981,7 +12981,7 @@
       <c r="K627" s="6"/>
       <c r="L627" s="6"/>
     </row>
-    <row r="628" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A628" s="5"/>
       <c r="B628" s="5"/>
       <c r="C628" s="5"/>
@@ -12995,7 +12995,7 @@
       <c r="K628" s="6"/>
       <c r="L628" s="6"/>
     </row>
-    <row r="629" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A629" s="5"/>
       <c r="B629" s="5"/>
       <c r="C629" s="5"/>
@@ -13009,7 +13009,7 @@
       <c r="K629" s="6"/>
       <c r="L629" s="6"/>
     </row>
-    <row r="630" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A630" s="5"/>
       <c r="B630" s="5"/>
       <c r="C630" s="5"/>
@@ -13023,7 +13023,7 @@
       <c r="K630" s="6"/>
       <c r="L630" s="6"/>
     </row>
-    <row r="631" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A631" s="5"/>
       <c r="B631" s="5"/>
       <c r="C631" s="5"/>
@@ -13037,7 +13037,7 @@
       <c r="K631" s="6"/>
       <c r="L631" s="6"/>
     </row>
-    <row r="632" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A632" s="5"/>
       <c r="B632" s="5"/>
       <c r="C632" s="5"/>
@@ -13051,7 +13051,7 @@
       <c r="K632" s="6"/>
       <c r="L632" s="6"/>
     </row>
-    <row r="633" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A633" s="5"/>
       <c r="B633" s="5"/>
       <c r="C633" s="5"/>
@@ -13065,7 +13065,7 @@
       <c r="K633" s="6"/>
       <c r="L633" s="6"/>
     </row>
-    <row r="634" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A634" s="5"/>
       <c r="B634" s="5"/>
       <c r="C634" s="5"/>
@@ -13079,7 +13079,7 @@
       <c r="K634" s="6"/>
       <c r="L634" s="6"/>
     </row>
-    <row r="635" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A635" s="5"/>
       <c r="B635" s="5"/>
       <c r="C635" s="5"/>
@@ -13093,7 +13093,7 @@
       <c r="K635" s="6"/>
       <c r="L635" s="6"/>
     </row>
-    <row r="636" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A636" s="5"/>
       <c r="B636" s="5"/>
       <c r="C636" s="5"/>
@@ -13107,7 +13107,7 @@
       <c r="K636" s="6"/>
       <c r="L636" s="6"/>
     </row>
-    <row r="637" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A637" s="5"/>
       <c r="B637" s="5"/>
       <c r="C637" s="5"/>
@@ -13121,7 +13121,7 @@
       <c r="K637" s="6"/>
       <c r="L637" s="6"/>
     </row>
-    <row r="638" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A638" s="5"/>
       <c r="B638" s="5"/>
       <c r="C638" s="5"/>
@@ -13135,7 +13135,7 @@
       <c r="K638" s="6"/>
       <c r="L638" s="6"/>
     </row>
-    <row r="639" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A639" s="5"/>
       <c r="B639" s="5"/>
       <c r="C639" s="5"/>
@@ -13149,7 +13149,7 @@
       <c r="K639" s="6"/>
       <c r="L639" s="6"/>
     </row>
-    <row r="640" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A640" s="5"/>
       <c r="B640" s="5"/>
       <c r="C640" s="5"/>
@@ -13163,7 +13163,7 @@
       <c r="K640" s="6"/>
       <c r="L640" s="6"/>
     </row>
-    <row r="641" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A641" s="5"/>
       <c r="B641" s="5"/>
       <c r="C641" s="5"/>
@@ -13177,7 +13177,7 @@
       <c r="K641" s="6"/>
       <c r="L641" s="6"/>
     </row>
-    <row r="642" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A642" s="5"/>
       <c r="B642" s="5"/>
       <c r="C642" s="5"/>
@@ -13191,7 +13191,7 @@
       <c r="K642" s="6"/>
       <c r="L642" s="6"/>
     </row>
-    <row r="643" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A643" s="5"/>
       <c r="B643" s="5"/>
       <c r="C643" s="5"/>
@@ -13205,7 +13205,7 @@
       <c r="K643" s="6"/>
       <c r="L643" s="6"/>
     </row>
-    <row r="644" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A644" s="5"/>
       <c r="B644" s="5"/>
       <c r="C644" s="5"/>
@@ -13219,7 +13219,7 @@
       <c r="K644" s="6"/>
       <c r="L644" s="6"/>
     </row>
-    <row r="645" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A645" s="5"/>
       <c r="B645" s="5"/>
       <c r="C645" s="5"/>
@@ -13233,7 +13233,7 @@
       <c r="K645" s="6"/>
       <c r="L645" s="6"/>
     </row>
-    <row r="646" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A646" s="5"/>
       <c r="B646" s="5"/>
       <c r="C646" s="5"/>
@@ -13247,7 +13247,7 @@
       <c r="K646" s="6"/>
       <c r="L646" s="6"/>
     </row>
-    <row r="647" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A647" s="5"/>
       <c r="B647" s="5"/>
       <c r="C647" s="5"/>
@@ -13261,7 +13261,7 @@
       <c r="K647" s="6"/>
       <c r="L647" s="6"/>
     </row>
-    <row r="648" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A648" s="5"/>
       <c r="B648" s="5"/>
       <c r="C648" s="5"/>
@@ -13275,7 +13275,7 @@
       <c r="K648" s="6"/>
       <c r="L648" s="6"/>
     </row>
-    <row r="649" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A649" s="5"/>
       <c r="B649" s="5"/>
       <c r="C649" s="5"/>
@@ -13289,7 +13289,7 @@
       <c r="K649" s="6"/>
       <c r="L649" s="6"/>
     </row>
-    <row r="650" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A650" s="5"/>
       <c r="B650" s="5"/>
       <c r="C650" s="5"/>
@@ -13303,7 +13303,7 @@
       <c r="K650" s="6"/>
       <c r="L650" s="6"/>
     </row>
-    <row r="651" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A651" s="5"/>
       <c r="B651" s="5"/>
       <c r="C651" s="5"/>
@@ -13317,7 +13317,7 @@
       <c r="K651" s="6"/>
       <c r="L651" s="6"/>
     </row>
-    <row r="652" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A652" s="5"/>
       <c r="B652" s="5"/>
       <c r="C652" s="5"/>
@@ -13331,7 +13331,7 @@
       <c r="K652" s="6"/>
       <c r="L652" s="6"/>
     </row>
-    <row r="653" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A653" s="5"/>
       <c r="B653" s="5"/>
       <c r="C653" s="5"/>
@@ -13345,7 +13345,7 @@
       <c r="K653" s="6"/>
       <c r="L653" s="6"/>
     </row>
-    <row r="654" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A654" s="5"/>
       <c r="B654" s="5"/>
       <c r="C654" s="5"/>
@@ -13359,7 +13359,7 @@
       <c r="K654" s="6"/>
       <c r="L654" s="6"/>
     </row>
-    <row r="655" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A655" s="5"/>
       <c r="B655" s="5"/>
       <c r="C655" s="5"/>
@@ -13373,7 +13373,7 @@
       <c r="K655" s="6"/>
       <c r="L655" s="6"/>
     </row>
-    <row r="656" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A656" s="5"/>
       <c r="B656" s="5"/>
       <c r="C656" s="5"/>
@@ -13387,7 +13387,7 @@
       <c r="K656" s="6"/>
       <c r="L656" s="6"/>
     </row>
-    <row r="657" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A657" s="5"/>
       <c r="B657" s="5"/>
       <c r="C657" s="5"/>
@@ -13401,7 +13401,7 @@
       <c r="K657" s="6"/>
       <c r="L657" s="6"/>
     </row>
-    <row r="658" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A658" s="5"/>
       <c r="B658" s="5"/>
       <c r="C658" s="5"/>
@@ -13415,7 +13415,7 @@
       <c r="K658" s="6"/>
       <c r="L658" s="6"/>
     </row>
-    <row r="659" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A659" s="5"/>
       <c r="B659" s="5"/>
       <c r="C659" s="5"/>
@@ -13429,7 +13429,7 @@
       <c r="K659" s="6"/>
       <c r="L659" s="6"/>
     </row>
-    <row r="660" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A660" s="5"/>
       <c r="B660" s="5"/>
       <c r="C660" s="5"/>
@@ -13443,7 +13443,7 @@
       <c r="K660" s="6"/>
       <c r="L660" s="6"/>
     </row>
-    <row r="661" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A661" s="5"/>
       <c r="B661" s="5"/>
       <c r="C661" s="5"/>
@@ -13457,7 +13457,7 @@
       <c r="K661" s="6"/>
       <c r="L661" s="6"/>
     </row>
-    <row r="662" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A662" s="5"/>
       <c r="B662" s="5"/>
       <c r="C662" s="5"/>
@@ -13471,7 +13471,7 @@
       <c r="K662" s="6"/>
       <c r="L662" s="6"/>
     </row>
-    <row r="663" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A663" s="5"/>
       <c r="B663" s="5"/>
       <c r="C663" s="5"/>
@@ -13485,7 +13485,7 @@
       <c r="K663" s="6"/>
       <c r="L663" s="6"/>
     </row>
-    <row r="664" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A664" s="5"/>
       <c r="B664" s="5"/>
       <c r="C664" s="5"/>
@@ -13499,7 +13499,7 @@
       <c r="K664" s="6"/>
       <c r="L664" s="6"/>
     </row>
-    <row r="665" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A665" s="5"/>
       <c r="B665" s="5"/>
       <c r="C665" s="5"/>
@@ -13513,7 +13513,7 @@
       <c r="K665" s="6"/>
       <c r="L665" s="6"/>
     </row>
-    <row r="666" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A666" s="5"/>
       <c r="B666" s="5"/>
       <c r="C666" s="5"/>
@@ -13527,7 +13527,7 @@
       <c r="K666" s="6"/>
       <c r="L666" s="6"/>
     </row>
-    <row r="667" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A667" s="5"/>
       <c r="B667" s="5"/>
       <c r="C667" s="5"/>
@@ -13541,7 +13541,7 @@
       <c r="K667" s="6"/>
       <c r="L667" s="6"/>
     </row>
-    <row r="668" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A668" s="5"/>
       <c r="B668" s="5"/>
       <c r="C668" s="5"/>
@@ -13555,7 +13555,7 @@
       <c r="K668" s="6"/>
       <c r="L668" s="6"/>
     </row>
-    <row r="669" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A669" s="5"/>
       <c r="B669" s="5"/>
       <c r="C669" s="5"/>
@@ -13569,7 +13569,7 @@
       <c r="K669" s="6"/>
       <c r="L669" s="6"/>
     </row>
-    <row r="670" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A670" s="5"/>
       <c r="B670" s="5"/>
       <c r="C670" s="5"/>
@@ -13583,7 +13583,7 @@
       <c r="K670" s="6"/>
       <c r="L670" s="6"/>
     </row>
-    <row r="671" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A671" s="5"/>
       <c r="B671" s="5"/>
       <c r="C671" s="5"/>
@@ -13597,7 +13597,7 @@
       <c r="K671" s="6"/>
       <c r="L671" s="6"/>
     </row>
-    <row r="672" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A672" s="5"/>
       <c r="B672" s="5"/>
       <c r="C672" s="5"/>
@@ -13611,7 +13611,7 @@
       <c r="K672" s="6"/>
       <c r="L672" s="6"/>
     </row>
-    <row r="673" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A673" s="5"/>
       <c r="B673" s="5"/>
       <c r="C673" s="5"/>
@@ -13625,7 +13625,7 @@
       <c r="K673" s="6"/>
       <c r="L673" s="6"/>
     </row>
-    <row r="674" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A674" s="5"/>
       <c r="B674" s="5"/>
       <c r="C674" s="5"/>
@@ -13639,7 +13639,7 @@
       <c r="K674" s="6"/>
       <c r="L674" s="6"/>
     </row>
-    <row r="675" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A675" s="5"/>
       <c r="B675" s="5"/>
       <c r="C675" s="5"/>
@@ -13653,7 +13653,7 @@
       <c r="K675" s="6"/>
       <c r="L675" s="6"/>
     </row>
-    <row r="676" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A676" s="5"/>
       <c r="B676" s="5"/>
       <c r="C676" s="5"/>
@@ -13667,7 +13667,7 @@
       <c r="K676" s="6"/>
       <c r="L676" s="6"/>
     </row>
-    <row r="677" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A677" s="5"/>
       <c r="B677" s="5"/>
       <c r="C677" s="5"/>
@@ -13681,7 +13681,7 @@
       <c r="K677" s="6"/>
       <c r="L677" s="6"/>
     </row>
-    <row r="678" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A678" s="5"/>
       <c r="B678" s="5"/>
       <c r="C678" s="5"/>
@@ -13695,7 +13695,7 @@
       <c r="K678" s="6"/>
       <c r="L678" s="6"/>
     </row>
-    <row r="679" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A679" s="5"/>
       <c r="B679" s="5"/>
       <c r="C679" s="5"/>
@@ -13709,7 +13709,7 @@
       <c r="K679" s="6"/>
       <c r="L679" s="6"/>
     </row>
-    <row r="680" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A680" s="5"/>
       <c r="B680" s="5"/>
       <c r="C680" s="5"/>
@@ -13723,7 +13723,7 @@
       <c r="K680" s="6"/>
       <c r="L680" s="6"/>
     </row>
-    <row r="681" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A681" s="5"/>
       <c r="B681" s="5"/>
       <c r="C681" s="5"/>
@@ -13737,7 +13737,7 @@
       <c r="K681" s="6"/>
       <c r="L681" s="6"/>
     </row>
-    <row r="682" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A682" s="5"/>
       <c r="B682" s="5"/>
       <c r="C682" s="5"/>
@@ -13751,7 +13751,7 @@
       <c r="K682" s="6"/>
       <c r="L682" s="6"/>
     </row>
-    <row r="683" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A683" s="5"/>
       <c r="B683" s="5"/>
       <c r="C683" s="5"/>
@@ -13765,7 +13765,7 @@
       <c r="K683" s="6"/>
       <c r="L683" s="6"/>
     </row>
-    <row r="684" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A684" s="5"/>
       <c r="B684" s="5"/>
       <c r="C684" s="5"/>
@@ -13779,7 +13779,7 @@
       <c r="K684" s="6"/>
       <c r="L684" s="6"/>
     </row>
-    <row r="685" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A685" s="5"/>
       <c r="B685" s="5"/>
       <c r="C685" s="5"/>
@@ -13793,7 +13793,7 @@
       <c r="K685" s="6"/>
       <c r="L685" s="6"/>
     </row>
-    <row r="686" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A686" s="5"/>
       <c r="B686" s="5"/>
       <c r="C686" s="5"/>
@@ -13807,7 +13807,7 @@
       <c r="K686" s="6"/>
       <c r="L686" s="6"/>
     </row>
-    <row r="687" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A687" s="5"/>
       <c r="B687" s="5"/>
       <c r="C687" s="5"/>
@@ -13821,7 +13821,7 @@
       <c r="K687" s="6"/>
       <c r="L687" s="6"/>
     </row>
-    <row r="688" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A688" s="5"/>
       <c r="B688" s="5"/>
       <c r="C688" s="5"/>
@@ -13835,7 +13835,7 @@
       <c r="K688" s="6"/>
       <c r="L688" s="6"/>
     </row>
-    <row r="689" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A689" s="5"/>
       <c r="B689" s="5"/>
       <c r="C689" s="5"/>
@@ -13849,7 +13849,7 @@
       <c r="K689" s="6"/>
       <c r="L689" s="6"/>
     </row>
-    <row r="690" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A690" s="5"/>
       <c r="B690" s="5"/>
       <c r="C690" s="5"/>
@@ -13863,7 +13863,7 @@
       <c r="K690" s="6"/>
       <c r="L690" s="6"/>
     </row>
-    <row r="691" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A691" s="5"/>
       <c r="B691" s="5"/>
       <c r="C691" s="5"/>
@@ -13877,7 +13877,7 @@
       <c r="K691" s="6"/>
       <c r="L691" s="6"/>
     </row>
-    <row r="692" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A692" s="5"/>
       <c r="B692" s="5"/>
       <c r="C692" s="5"/>
@@ -13891,7 +13891,7 @@
       <c r="K692" s="6"/>
       <c r="L692" s="6"/>
     </row>
-    <row r="693" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A693" s="5"/>
       <c r="B693" s="5"/>
       <c r="C693" s="5"/>
@@ -13905,7 +13905,7 @@
       <c r="K693" s="6"/>
       <c r="L693" s="6"/>
     </row>
-    <row r="694" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A694" s="5"/>
       <c r="B694" s="5"/>
       <c r="C694" s="5"/>
@@ -13919,7 +13919,7 @@
       <c r="K694" s="6"/>
       <c r="L694" s="6"/>
     </row>
-    <row r="695" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A695" s="5"/>
       <c r="B695" s="5"/>
       <c r="C695" s="5"/>
@@ -13933,7 +13933,7 @@
       <c r="K695" s="6"/>
       <c r="L695" s="6"/>
     </row>
-    <row r="696" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A696" s="5"/>
       <c r="B696" s="5"/>
       <c r="C696" s="5"/>
@@ -13947,7 +13947,7 @@
       <c r="K696" s="6"/>
       <c r="L696" s="6"/>
     </row>
-    <row r="697" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A697" s="5"/>
       <c r="B697" s="5"/>
       <c r="C697" s="5"/>
@@ -13961,7 +13961,7 @@
       <c r="K697" s="6"/>
       <c r="L697" s="6"/>
     </row>
-    <row r="698" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A698" s="5"/>
       <c r="B698" s="5"/>
       <c r="C698" s="5"/>
@@ -13975,7 +13975,7 @@
       <c r="K698" s="6"/>
       <c r="L698" s="6"/>
     </row>
-    <row r="699" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A699" s="5"/>
       <c r="B699" s="5"/>
       <c r="C699" s="5"/>
@@ -13989,7 +13989,7 @@
       <c r="K699" s="6"/>
       <c r="L699" s="6"/>
     </row>
-    <row r="700" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A700" s="5"/>
       <c r="B700" s="5"/>
       <c r="C700" s="5"/>
@@ -14003,7 +14003,7 @@
       <c r="K700" s="6"/>
       <c r="L700" s="6"/>
     </row>
-    <row r="701" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A701" s="5"/>
       <c r="B701" s="5"/>
       <c r="C701" s="5"/>
@@ -14017,7 +14017,7 @@
       <c r="K701" s="6"/>
       <c r="L701" s="6"/>
     </row>
-    <row r="702" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A702" s="5"/>
       <c r="B702" s="5"/>
       <c r="C702" s="5"/>
@@ -14031,7 +14031,7 @@
       <c r="K702" s="6"/>
       <c r="L702" s="6"/>
     </row>
-    <row r="703" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A703" s="5"/>
       <c r="B703" s="5"/>
       <c r="C703" s="5"/>
@@ -14045,7 +14045,7 @@
       <c r="K703" s="6"/>
       <c r="L703" s="6"/>
     </row>
-    <row r="704" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A704" s="5"/>
       <c r="B704" s="5"/>
       <c r="C704" s="5"/>
@@ -14059,7 +14059,7 @@
       <c r="K704" s="6"/>
       <c r="L704" s="6"/>
     </row>
-    <row r="705" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A705" s="5"/>
       <c r="B705" s="5"/>
       <c r="C705" s="5"/>
@@ -14073,7 +14073,7 @@
       <c r="K705" s="6"/>
       <c r="L705" s="6"/>
     </row>
-    <row r="706" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A706" s="5"/>
       <c r="B706" s="5"/>
       <c r="C706" s="5"/>
@@ -14087,7 +14087,7 @@
       <c r="K706" s="6"/>
       <c r="L706" s="6"/>
     </row>
-    <row r="707" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A707" s="5"/>
       <c r="B707" s="5"/>
       <c r="C707" s="5"/>
@@ -14101,7 +14101,7 @@
       <c r="K707" s="6"/>
       <c r="L707" s="6"/>
     </row>
-    <row r="708" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A708" s="5"/>
       <c r="B708" s="5"/>
       <c r="C708" s="5"/>
@@ -14115,7 +14115,7 @@
       <c r="K708" s="6"/>
       <c r="L708" s="6"/>
     </row>
-    <row r="709" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A709" s="5"/>
       <c r="B709" s="5"/>
       <c r="C709" s="5"/>
@@ -14129,7 +14129,7 @@
       <c r="K709" s="6"/>
       <c r="L709" s="6"/>
     </row>
-    <row r="710" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A710" s="5"/>
       <c r="B710" s="5"/>
       <c r="C710" s="5"/>
@@ -14143,7 +14143,7 @@
       <c r="K710" s="6"/>
       <c r="L710" s="6"/>
     </row>
-    <row r="711" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A711" s="5"/>
       <c r="B711" s="5"/>
       <c r="C711" s="5"/>
@@ -14157,7 +14157,7 @@
       <c r="K711" s="6"/>
       <c r="L711" s="6"/>
     </row>
-    <row r="712" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A712" s="5"/>
       <c r="B712" s="5"/>
       <c r="C712" s="5"/>
@@ -14171,7 +14171,7 @@
       <c r="K712" s="6"/>
       <c r="L712" s="6"/>
     </row>
-    <row r="713" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A713" s="5"/>
       <c r="B713" s="5"/>
       <c r="C713" s="5"/>
@@ -14185,7 +14185,7 @@
       <c r="K713" s="6"/>
       <c r="L713" s="6"/>
     </row>
-    <row r="714" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A714" s="5"/>
       <c r="B714" s="5"/>
       <c r="C714" s="5"/>
@@ -14199,7 +14199,7 @@
       <c r="K714" s="6"/>
       <c r="L714" s="6"/>
     </row>
-    <row r="715" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A715" s="5"/>
       <c r="B715" s="5"/>
       <c r="C715" s="5"/>
@@ -14213,7 +14213,7 @@
       <c r="K715" s="6"/>
       <c r="L715" s="6"/>
     </row>
-    <row r="716" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A716" s="5"/>
       <c r="B716" s="5"/>
       <c r="C716" s="5"/>
@@ -14227,7 +14227,7 @@
       <c r="K716" s="6"/>
       <c r="L716" s="6"/>
     </row>
-    <row r="717" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A717" s="5"/>
       <c r="B717" s="5"/>
       <c r="C717" s="5"/>
@@ -14241,7 +14241,7 @@
       <c r="K717" s="6"/>
       <c r="L717" s="6"/>
     </row>
-    <row r="718" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A718" s="5"/>
       <c r="B718" s="5"/>
       <c r="C718" s="5"/>
@@ -14255,7 +14255,7 @@
       <c r="K718" s="6"/>
       <c r="L718" s="6"/>
     </row>
-    <row r="719" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A719" s="5"/>
       <c r="B719" s="5"/>
       <c r="C719" s="5"/>
@@ -14269,7 +14269,7 @@
       <c r="K719" s="6"/>
       <c r="L719" s="6"/>
     </row>
-    <row r="720" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A720" s="5"/>
       <c r="B720" s="5"/>
       <c r="C720" s="5"/>
@@ -14283,7 +14283,7 @@
       <c r="K720" s="6"/>
       <c r="L720" s="6"/>
     </row>
-    <row r="721" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A721" s="5"/>
       <c r="B721" s="5"/>
       <c r="C721" s="5"/>
@@ -14297,7 +14297,7 @@
       <c r="K721" s="6"/>
       <c r="L721" s="6"/>
     </row>
-    <row r="722" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A722" s="5"/>
       <c r="B722" s="5"/>
       <c r="C722" s="5"/>
@@ -14311,7 +14311,7 @@
       <c r="K722" s="6"/>
       <c r="L722" s="6"/>
     </row>
-    <row r="723" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A723" s="5"/>
       <c r="B723" s="5"/>
       <c r="C723" s="5"/>
@@ -14325,7 +14325,7 @@
       <c r="K723" s="6"/>
       <c r="L723" s="6"/>
     </row>
-    <row r="724" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A724" s="5"/>
       <c r="B724" s="5"/>
       <c r="C724" s="5"/>
@@ -14339,7 +14339,7 @@
       <c r="K724" s="6"/>
       <c r="L724" s="6"/>
     </row>
-    <row r="725" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A725" s="5"/>
       <c r="B725" s="5"/>
       <c r="C725" s="5"/>
@@ -14353,7 +14353,7 @@
       <c r="K725" s="6"/>
       <c r="L725" s="6"/>
     </row>
-    <row r="726" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A726" s="5"/>
       <c r="B726" s="5"/>
       <c r="C726" s="5"/>
@@ -14367,7 +14367,7 @@
       <c r="K726" s="6"/>
       <c r="L726" s="6"/>
     </row>
-    <row r="727" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A727" s="5"/>
       <c r="B727" s="5"/>
       <c r="C727" s="5"/>
@@ -14381,7 +14381,7 @@
       <c r="K727" s="6"/>
       <c r="L727" s="6"/>
     </row>
-    <row r="728" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A728" s="5"/>
       <c r="B728" s="5"/>
       <c r="C728" s="5"/>
@@ -14395,7 +14395,7 @@
       <c r="K728" s="6"/>
       <c r="L728" s="6"/>
     </row>
-    <row r="729" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A729" s="5"/>
       <c r="B729" s="5"/>
       <c r="C729" s="5"/>
@@ -14409,7 +14409,7 @@
       <c r="K729" s="6"/>
       <c r="L729" s="6"/>
     </row>
-    <row r="730" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A730" s="5"/>
       <c r="B730" s="5"/>
       <c r="C730" s="5"/>
@@ -14423,7 +14423,7 @@
       <c r="K730" s="6"/>
       <c r="L730" s="6"/>
     </row>
-    <row r="731" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A731" s="5"/>
       <c r="B731" s="5"/>
       <c r="C731" s="5"/>
@@ -14437,7 +14437,7 @@
       <c r="K731" s="6"/>
       <c r="L731" s="6"/>
     </row>
-    <row r="732" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A732" s="5"/>
       <c r="B732" s="5"/>
       <c r="C732" s="5"/>
@@ -14451,7 +14451,7 @@
       <c r="K732" s="6"/>
       <c r="L732" s="6"/>
     </row>
-    <row r="733" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A733" s="5"/>
       <c r="B733" s="5"/>
       <c r="C733" s="5"/>
@@ -14465,7 +14465,7 @@
       <c r="K733" s="6"/>
       <c r="L733" s="6"/>
     </row>
-    <row r="734" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A734" s="5"/>
       <c r="B734" s="5"/>
       <c r="C734" s="5"/>
@@ -14479,7 +14479,7 @@
       <c r="K734" s="6"/>
       <c r="L734" s="6"/>
     </row>
-    <row r="735" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A735" s="5"/>
       <c r="B735" s="5"/>
       <c r="C735" s="5"/>
@@ -14493,7 +14493,7 @@
       <c r="K735" s="6"/>
       <c r="L735" s="6"/>
     </row>
-    <row r="736" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A736" s="5"/>
       <c r="B736" s="5"/>
       <c r="C736" s="5"/>
@@ -14507,7 +14507,7 @@
       <c r="K736" s="6"/>
       <c r="L736" s="6"/>
     </row>
-    <row r="737" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A737" s="5"/>
       <c r="B737" s="5"/>
       <c r="C737" s="5"/>
@@ -14521,7 +14521,7 @@
       <c r="K737" s="6"/>
       <c r="L737" s="6"/>
     </row>
-    <row r="738" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A738" s="5"/>
       <c r="B738" s="5"/>
       <c r="C738" s="5"/>
@@ -14535,7 +14535,7 @@
       <c r="K738" s="6"/>
       <c r="L738" s="6"/>
     </row>
-    <row r="739" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A739" s="5"/>
       <c r="B739" s="5"/>
       <c r="C739" s="5"/>
@@ -14549,7 +14549,7 @@
       <c r="K739" s="6"/>
       <c r="L739" s="6"/>
     </row>
-    <row r="740" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A740" s="5"/>
       <c r="B740" s="5"/>
       <c r="C740" s="5"/>
@@ -14563,7 +14563,7 @@
       <c r="K740" s="6"/>
       <c r="L740" s="6"/>
     </row>
-    <row r="741" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A741" s="5"/>
       <c r="B741" s="5"/>
       <c r="C741" s="5"/>
@@ -14577,7 +14577,7 @@
       <c r="K741" s="6"/>
       <c r="L741" s="6"/>
     </row>
-    <row r="742" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A742" s="5"/>
       <c r="B742" s="5"/>
       <c r="C742" s="5"/>
@@ -14591,7 +14591,7 @@
       <c r="K742" s="6"/>
       <c r="L742" s="6"/>
     </row>
-    <row r="743" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A743" s="5"/>
       <c r="B743" s="5"/>
       <c r="C743" s="5"/>
@@ -14605,7 +14605,7 @@
       <c r="K743" s="6"/>
       <c r="L743" s="6"/>
     </row>
-    <row r="744" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A744" s="5"/>
       <c r="B744" s="5"/>
       <c r="C744" s="5"/>
@@ -14619,7 +14619,7 @@
       <c r="K744" s="6"/>
       <c r="L744" s="6"/>
     </row>
-    <row r="745" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A745" s="5"/>
       <c r="B745" s="5"/>
       <c r="C745" s="5"/>
@@ -14633,7 +14633,7 @@
       <c r="K745" s="6"/>
       <c r="L745" s="6"/>
     </row>
-    <row r="746" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A746" s="5"/>
       <c r="B746" s="5"/>
       <c r="C746" s="5"/>
@@ -14647,7 +14647,7 @@
       <c r="K746" s="6"/>
       <c r="L746" s="6"/>
     </row>
-    <row r="747" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A747" s="5"/>
       <c r="B747" s="5"/>
       <c r="C747" s="5"/>
@@ -14661,7 +14661,7 @@
       <c r="K747" s="6"/>
       <c r="L747" s="6"/>
     </row>
-    <row r="748" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A748" s="5"/>
       <c r="B748" s="5"/>
       <c r="C748" s="5"/>
@@ -14675,7 +14675,7 @@
       <c r="K748" s="6"/>
       <c r="L748" s="6"/>
     </row>
-    <row r="749" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A749" s="5"/>
       <c r="B749" s="5"/>
       <c r="C749" s="5"/>
@@ -14689,7 +14689,7 @@
       <c r="K749" s="6"/>
       <c r="L749" s="6"/>
     </row>
-    <row r="750" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A750" s="5"/>
       <c r="B750" s="5"/>
       <c r="C750" s="5"/>
@@ -14703,7 +14703,7 @@
       <c r="K750" s="6"/>
       <c r="L750" s="6"/>
     </row>
-    <row r="751" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A751" s="5"/>
       <c r="B751" s="5"/>
       <c r="C751" s="5"/>
@@ -14717,7 +14717,7 @@
       <c r="K751" s="6"/>
       <c r="L751" s="6"/>
     </row>
-    <row r="752" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A752" s="5"/>
       <c r="B752" s="5"/>
       <c r="C752" s="5"/>
@@ -14731,7 +14731,7 @@
       <c r="K752" s="6"/>
       <c r="L752" s="6"/>
     </row>
-    <row r="753" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A753" s="5"/>
       <c r="B753" s="5"/>
       <c r="C753" s="5"/>
@@ -14745,7 +14745,7 @@
       <c r="K753" s="6"/>
       <c r="L753" s="6"/>
     </row>
-    <row r="754" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A754" s="5"/>
       <c r="B754" s="5"/>
       <c r="C754" s="5"/>
@@ -14759,7 +14759,7 @@
       <c r="K754" s="6"/>
       <c r="L754" s="6"/>
     </row>
-    <row r="755" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A755" s="5"/>
       <c r="B755" s="5"/>
       <c r="C755" s="5"/>
@@ -14773,7 +14773,7 @@
       <c r="K755" s="6"/>
       <c r="L755" s="6"/>
     </row>
-    <row r="756" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A756" s="5"/>
       <c r="B756" s="5"/>
       <c r="C756" s="5"/>
@@ -14787,7 +14787,7 @@
       <c r="K756" s="6"/>
       <c r="L756" s="6"/>
     </row>
-    <row r="757" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A757" s="5"/>
       <c r="B757" s="5"/>
       <c r="C757" s="5"/>
@@ -14801,7 +14801,7 @@
       <c r="K757" s="6"/>
       <c r="L757" s="6"/>
     </row>
-    <row r="758" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A758" s="5"/>
       <c r="B758" s="5"/>
       <c r="C758" s="5"/>
@@ -14815,7 +14815,7 @@
       <c r="K758" s="6"/>
       <c r="L758" s="6"/>
     </row>
-    <row r="759" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A759" s="5"/>
       <c r="B759" s="5"/>
       <c r="C759" s="5"/>
@@ -14829,7 +14829,7 @@
       <c r="K759" s="6"/>
       <c r="L759" s="6"/>
     </row>
-    <row r="760" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A760" s="5"/>
       <c r="B760" s="5"/>
       <c r="C760" s="5"/>
@@ -14843,7 +14843,7 @@
       <c r="K760" s="6"/>
       <c r="L760" s="6"/>
     </row>
-    <row r="761" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A761" s="5"/>
       <c r="B761" s="5"/>
       <c r="C761" s="5"/>
@@ -14857,7 +14857,7 @@
       <c r="K761" s="6"/>
       <c r="L761" s="6"/>
     </row>
-    <row r="762" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A762" s="5"/>
       <c r="B762" s="5"/>
       <c r="C762" s="5"/>
@@ -14871,7 +14871,7 @@
       <c r="K762" s="6"/>
       <c r="L762" s="6"/>
     </row>
-    <row r="763" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A763" s="5"/>
       <c r="B763" s="5"/>
       <c r="C763" s="5"/>
@@ -14885,7 +14885,7 @@
       <c r="K763" s="6"/>
       <c r="L763" s="6"/>
     </row>
-    <row r="764" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A764" s="5"/>
       <c r="B764" s="5"/>
       <c r="C764" s="5"/>
@@ -14899,7 +14899,7 @@
       <c r="K764" s="6"/>
       <c r="L764" s="6"/>
     </row>
-    <row r="765" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A765" s="5"/>
       <c r="B765" s="5"/>
       <c r="C765" s="5"/>
@@ -14913,7 +14913,7 @@
       <c r="K765" s="6"/>
       <c r="L765" s="6"/>
     </row>
-    <row r="766" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A766" s="5"/>
       <c r="B766" s="5"/>
       <c r="C766" s="5"/>
@@ -14927,7 +14927,7 @@
       <c r="K766" s="6"/>
       <c r="L766" s="6"/>
     </row>
-    <row r="767" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A767" s="5"/>
       <c r="B767" s="5"/>
       <c r="C767" s="5"/>
@@ -14941,7 +14941,7 @@
       <c r="K767" s="6"/>
       <c r="L767" s="6"/>
     </row>
-    <row r="768" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A768" s="5"/>
       <c r="B768" s="5"/>
       <c r="C768" s="5"/>
@@ -14955,7 +14955,7 @@
       <c r="K768" s="6"/>
       <c r="L768" s="6"/>
     </row>
-    <row r="769" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A769" s="5"/>
       <c r="B769" s="5"/>
       <c r="C769" s="5"/>
@@ -14969,7 +14969,7 @@
       <c r="K769" s="6"/>
       <c r="L769" s="6"/>
     </row>
-    <row r="770" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A770" s="5"/>
       <c r="B770" s="5"/>
       <c r="C770" s="5"/>
@@ -14983,7 +14983,7 @@
       <c r="K770" s="6"/>
       <c r="L770" s="6"/>
     </row>
-    <row r="771" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A771" s="5"/>
       <c r="B771" s="5"/>
       <c r="C771" s="5"/>
@@ -14997,7 +14997,7 @@
       <c r="K771" s="6"/>
       <c r="L771" s="6"/>
     </row>
-    <row r="772" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A772" s="5"/>
       <c r="B772" s="5"/>
       <c r="C772" s="5"/>
@@ -15011,7 +15011,7 @@
       <c r="K772" s="6"/>
       <c r="L772" s="6"/>
     </row>
-    <row r="773" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A773" s="5"/>
       <c r="B773" s="5"/>
       <c r="C773" s="5"/>
@@ -15025,7 +15025,7 @@
       <c r="K773" s="6"/>
       <c r="L773" s="6"/>
     </row>
-    <row r="774" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A774" s="5"/>
       <c r="B774" s="5"/>
       <c r="C774" s="5"/>
@@ -15039,7 +15039,7 @@
       <c r="K774" s="6"/>
       <c r="L774" s="6"/>
     </row>
-    <row r="775" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A775" s="5"/>
       <c r="B775" s="5"/>
       <c r="C775" s="5"/>
@@ -15053,7 +15053,7 @@
       <c r="K775" s="6"/>
       <c r="L775" s="6"/>
     </row>
-    <row r="776" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A776" s="5"/>
       <c r="B776" s="5"/>
       <c r="C776" s="5"/>
@@ -15067,7 +15067,7 @@
       <c r="K776" s="6"/>
       <c r="L776" s="6"/>
     </row>
-    <row r="777" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A777" s="5"/>
       <c r="B777" s="5"/>
       <c r="C777" s="5"/>
@@ -15081,7 +15081,7 @@
       <c r="K777" s="6"/>
       <c r="L777" s="6"/>
     </row>
-    <row r="778" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A778" s="5"/>
       <c r="B778" s="5"/>
       <c r="C778" s="5"/>
@@ -15095,7 +15095,7 @@
       <c r="K778" s="6"/>
       <c r="L778" s="6"/>
     </row>
-    <row r="779" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A779" s="5"/>
       <c r="B779" s="5"/>
       <c r="C779" s="5"/>
@@ -15109,7 +15109,7 @@
       <c r="K779" s="6"/>
       <c r="L779" s="6"/>
     </row>
-    <row r="780" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A780" s="5"/>
       <c r="B780" s="5"/>
       <c r="C780" s="5"/>
@@ -15123,7 +15123,7 @@
       <c r="K780" s="6"/>
       <c r="L780" s="6"/>
     </row>
-    <row r="781" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A781" s="5"/>
       <c r="B781" s="5"/>
       <c r="C781" s="5"/>
@@ -15137,7 +15137,7 @@
       <c r="K781" s="6"/>
       <c r="L781" s="6"/>
     </row>
-    <row r="782" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A782" s="5"/>
       <c r="B782" s="5"/>
       <c r="C782" s="5"/>
@@ -15151,7 +15151,7 @@
       <c r="K782" s="6"/>
       <c r="L782" s="6"/>
     </row>
-    <row r="783" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A783" s="5"/>
       <c r="B783" s="5"/>
       <c r="C783" s="5"/>
@@ -15165,7 +15165,7 @@
       <c r="K783" s="6"/>
       <c r="L783" s="6"/>
     </row>
-    <row r="784" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A784" s="5"/>
       <c r="B784" s="5"/>
       <c r="C784" s="5"/>
@@ -15179,7 +15179,7 @@
       <c r="K784" s="6"/>
       <c r="L784" s="6"/>
     </row>
-    <row r="785" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A785" s="5"/>
       <c r="B785" s="5"/>
       <c r="C785" s="5"/>
@@ -15193,7 +15193,7 @@
       <c r="K785" s="6"/>
       <c r="L785" s="6"/>
     </row>
-    <row r="786" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A786" s="5"/>
       <c r="B786" s="5"/>
       <c r="C786" s="5"/>
@@ -15207,7 +15207,7 @@
       <c r="K786" s="6"/>
       <c r="L786" s="6"/>
     </row>
-    <row r="787" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A787" s="5"/>
       <c r="B787" s="5"/>
       <c r="C787" s="5"/>
@@ -15221,7 +15221,7 @@
       <c r="K787" s="6"/>
       <c r="L787" s="6"/>
     </row>
-    <row r="788" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A788" s="5"/>
       <c r="B788" s="5"/>
       <c r="C788" s="5"/>
@@ -15235,7 +15235,7 @@
       <c r="K788" s="6"/>
       <c r="L788" s="6"/>
     </row>
-    <row r="789" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A789" s="5"/>
       <c r="B789" s="5"/>
       <c r="C789" s="5"/>
@@ -15249,7 +15249,7 @@
       <c r="K789" s="6"/>
       <c r="L789" s="6"/>
     </row>
-    <row r="790" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A790" s="5"/>
       <c r="B790" s="5"/>
       <c r="C790" s="5"/>
@@ -15263,7 +15263,7 @@
       <c r="K790" s="6"/>
       <c r="L790" s="6"/>
     </row>
-    <row r="791" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A791" s="5"/>
       <c r="B791" s="5"/>
       <c r="C791" s="5"/>
@@ -15277,7 +15277,7 @@
       <c r="K791" s="6"/>
       <c r="L791" s="6"/>
     </row>
-    <row r="792" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A792" s="5"/>
       <c r="B792" s="5"/>
       <c r="C792" s="5"/>
@@ -15291,7 +15291,7 @@
       <c r="K792" s="6"/>
       <c r="L792" s="6"/>
     </row>
-    <row r="793" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A793" s="5"/>
       <c r="B793" s="5"/>
       <c r="C793" s="5"/>
@@ -15305,7 +15305,7 @@
       <c r="K793" s="6"/>
       <c r="L793" s="6"/>
     </row>
-    <row r="794" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A794" s="5"/>
       <c r="B794" s="5"/>
       <c r="C794" s="5"/>
@@ -15319,7 +15319,7 @@
       <c r="K794" s="6"/>
       <c r="L794" s="6"/>
     </row>
-    <row r="795" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A795" s="5"/>
       <c r="B795" s="5"/>
       <c r="C795" s="5"/>
@@ -15333,7 +15333,7 @@
       <c r="K795" s="6"/>
       <c r="L795" s="6"/>
     </row>
-    <row r="796" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A796" s="5"/>
       <c r="B796" s="5"/>
       <c r="C796" s="5"/>
@@ -15347,7 +15347,7 @@
       <c r="K796" s="6"/>
       <c r="L796" s="6"/>
     </row>
-    <row r="797" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A797" s="5"/>
       <c r="B797" s="5"/>
       <c r="C797" s="5"/>
@@ -15361,7 +15361,7 @@
       <c r="K797" s="6"/>
       <c r="L797" s="6"/>
     </row>
-    <row r="798" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A798" s="5"/>
       <c r="B798" s="5"/>
       <c r="C798" s="5"/>
@@ -15375,7 +15375,7 @@
       <c r="K798" s="6"/>
       <c r="L798" s="6"/>
     </row>
-    <row r="799" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A799" s="5"/>
       <c r="B799" s="5"/>
       <c r="C799" s="5"/>
@@ -15389,7 +15389,7 @@
       <c r="K799" s="6"/>
       <c r="L799" s="6"/>
     </row>
-    <row r="800" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A800" s="5"/>
       <c r="B800" s="5"/>
       <c r="C800" s="5"/>
@@ -15403,7 +15403,7 @@
       <c r="K800" s="6"/>
       <c r="L800" s="6"/>
     </row>
-    <row r="801" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A801" s="5"/>
       <c r="B801" s="5"/>
       <c r="C801" s="5"/>
@@ -15417,7 +15417,7 @@
       <c r="K801" s="6"/>
       <c r="L801" s="6"/>
     </row>
-    <row r="802" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A802" s="5"/>
       <c r="B802" s="5"/>
       <c r="C802" s="5"/>
@@ -15431,7 +15431,7 @@
       <c r="K802" s="6"/>
       <c r="L802" s="6"/>
     </row>
-    <row r="803" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A803" s="5"/>
       <c r="B803" s="5"/>
       <c r="C803" s="5"/>
@@ -15445,7 +15445,7 @@
       <c r="K803" s="6"/>
       <c r="L803" s="6"/>
     </row>
-    <row r="804" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A804" s="5"/>
       <c r="B804" s="5"/>
       <c r="C804" s="5"/>
@@ -15459,7 +15459,7 @@
       <c r="K804" s="6"/>
       <c r="L804" s="6"/>
     </row>
-    <row r="805" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A805" s="5"/>
       <c r="B805" s="5"/>
       <c r="C805" s="5"/>
@@ -15473,7 +15473,7 @@
       <c r="K805" s="6"/>
       <c r="L805" s="6"/>
     </row>
-    <row r="806" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A806" s="5"/>
       <c r="B806" s="5"/>
       <c r="C806" s="5"/>
@@ -15487,7 +15487,7 @@
       <c r="K806" s="6"/>
       <c r="L806" s="6"/>
     </row>
-    <row r="807" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A807" s="5"/>
       <c r="B807" s="5"/>
       <c r="C807" s="5"/>
@@ -15501,7 +15501,7 @@
       <c r="K807" s="6"/>
       <c r="L807" s="6"/>
     </row>
-    <row r="808" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A808" s="5"/>
       <c r="B808" s="5"/>
       <c r="C808" s="5"/>
@@ -15515,7 +15515,7 @@
       <c r="K808" s="6"/>
       <c r="L808" s="6"/>
     </row>
-    <row r="809" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A809" s="5"/>
       <c r="B809" s="5"/>
       <c r="C809" s="5"/>
@@ -15529,7 +15529,7 @@
       <c r="K809" s="6"/>
       <c r="L809" s="6"/>
     </row>
-    <row r="810" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A810" s="5"/>
       <c r="B810" s="5"/>
       <c r="C810" s="5"/>
@@ -15543,7 +15543,7 @@
       <c r="K810" s="6"/>
       <c r="L810" s="6"/>
     </row>
-    <row r="811" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A811" s="5"/>
       <c r="B811" s="5"/>
       <c r="C811" s="5"/>
@@ -15557,7 +15557,7 @@
       <c r="K811" s="6"/>
       <c r="L811" s="6"/>
     </row>
-    <row r="812" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A812" s="5"/>
       <c r="B812" s="5"/>
       <c r="C812" s="5"/>
@@ -15571,7 +15571,7 @@
       <c r="K812" s="6"/>
       <c r="L812" s="6"/>
     </row>
-    <row r="813" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A813" s="5"/>
       <c r="B813" s="5"/>
       <c r="C813" s="5"/>
@@ -15585,7 +15585,7 @@
       <c r="K813" s="6"/>
       <c r="L813" s="6"/>
     </row>
-    <row r="814" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A814" s="5"/>
       <c r="B814" s="5"/>
       <c r="C814" s="5"/>
@@ -15599,7 +15599,7 @@
       <c r="K814" s="6"/>
       <c r="L814" s="6"/>
     </row>
-    <row r="815" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A815" s="5"/>
       <c r="B815" s="5"/>
       <c r="C815" s="5"/>
@@ -15613,7 +15613,7 @@
       <c r="K815" s="6"/>
       <c r="L815" s="6"/>
     </row>
-    <row r="816" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A816" s="5"/>
       <c r="B816" s="5"/>
       <c r="C816" s="5"/>
@@ -15627,7 +15627,7 @@
       <c r="K816" s="6"/>
       <c r="L816" s="6"/>
     </row>
-    <row r="817" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A817" s="5"/>
       <c r="B817" s="5"/>
       <c r="C817" s="5"/>
@@ -15641,7 +15641,7 @@
       <c r="K817" s="6"/>
       <c r="L817" s="6"/>
     </row>
-    <row r="818" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A818" s="5"/>
       <c r="B818" s="5"/>
       <c r="C818" s="5"/>
@@ -15655,7 +15655,7 @@
       <c r="K818" s="6"/>
       <c r="L818" s="6"/>
     </row>
-    <row r="819" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A819" s="5"/>
       <c r="B819" s="5"/>
       <c r="C819" s="5"/>
@@ -15669,7 +15669,7 @@
       <c r="K819" s="6"/>
       <c r="L819" s="6"/>
     </row>
-    <row r="820" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A820" s="5"/>
       <c r="B820" s="5"/>
       <c r="C820" s="5"/>
@@ -15683,7 +15683,7 @@
       <c r="K820" s="6"/>
       <c r="L820" s="6"/>
     </row>
-    <row r="821" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A821" s="5"/>
       <c r="B821" s="5"/>
       <c r="C821" s="5"/>
@@ -15697,7 +15697,7 @@
       <c r="K821" s="6"/>
       <c r="L821" s="6"/>
     </row>
-    <row r="822" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A822" s="5"/>
       <c r="B822" s="5"/>
       <c r="C822" s="5"/>
@@ -15711,7 +15711,7 @@
       <c r="K822" s="6"/>
       <c r="L822" s="6"/>
     </row>
-    <row r="823" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A823" s="5"/>
       <c r="B823" s="5"/>
       <c r="C823" s="5"/>
@@ -15725,7 +15725,7 @@
       <c r="K823" s="6"/>
       <c r="L823" s="6"/>
     </row>
-    <row r="824" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A824" s="5"/>
       <c r="B824" s="5"/>
       <c r="C824" s="5"/>
@@ -15739,7 +15739,7 @@
       <c r="K824" s="6"/>
       <c r="L824" s="6"/>
     </row>
-    <row r="825" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A825" s="5"/>
       <c r="B825" s="5"/>
       <c r="C825" s="5"/>
@@ -15753,7 +15753,7 @@
       <c r="K825" s="6"/>
       <c r="L825" s="6"/>
     </row>
-    <row r="826" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A826" s="5"/>
       <c r="B826" s="5"/>
       <c r="C826" s="5"/>
@@ -15767,7 +15767,7 @@
       <c r="K826" s="6"/>
       <c r="L826" s="6"/>
     </row>
-    <row r="827" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A827" s="5"/>
       <c r="B827" s="5"/>
       <c r="C827" s="5"/>
@@ -15781,7 +15781,7 @@
       <c r="K827" s="6"/>
       <c r="L827" s="6"/>
     </row>
-    <row r="828" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A828" s="5"/>
       <c r="B828" s="5"/>
       <c r="C828" s="5"/>
@@ -15795,7 +15795,7 @@
       <c r="K828" s="6"/>
       <c r="L828" s="6"/>
     </row>
-    <row r="829" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A829" s="5"/>
       <c r="B829" s="5"/>
       <c r="C829" s="5"/>
@@ -15809,7 +15809,7 @@
       <c r="K829" s="6"/>
       <c r="L829" s="6"/>
     </row>
-    <row r="830" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A830" s="5"/>
       <c r="B830" s="5"/>
       <c r="C830" s="5"/>
@@ -15823,7 +15823,7 @@
       <c r="K830" s="6"/>
       <c r="L830" s="6"/>
     </row>
-    <row r="831" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A831" s="5"/>
       <c r="B831" s="5"/>
       <c r="C831" s="5"/>
@@ -15837,7 +15837,7 @@
       <c r="K831" s="6"/>
       <c r="L831" s="6"/>
     </row>
-    <row r="832" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A832" s="5"/>
       <c r="B832" s="5"/>
       <c r="C832" s="5"/>
@@ -15851,7 +15851,7 @@
       <c r="K832" s="6"/>
       <c r="L832" s="6"/>
     </row>
-    <row r="833" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A833" s="5"/>
       <c r="B833" s="5"/>
       <c r="C833" s="5"/>
@@ -15865,7 +15865,7 @@
       <c r="K833" s="6"/>
       <c r="L833" s="6"/>
     </row>
-    <row r="834" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A834" s="5"/>
       <c r="B834" s="5"/>
       <c r="C834" s="5"/>
@@ -15879,7 +15879,7 @@
       <c r="K834" s="6"/>
       <c r="L834" s="6"/>
     </row>
-    <row r="835" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A835" s="5"/>
       <c r="B835" s="5"/>
       <c r="C835" s="5"/>
@@ -15893,7 +15893,7 @@
       <c r="K835" s="6"/>
       <c r="L835" s="6"/>
     </row>
-    <row r="836" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A836" s="5"/>
       <c r="B836" s="5"/>
       <c r="C836" s="5"/>
@@ -15907,7 +15907,7 @@
       <c r="K836" s="6"/>
       <c r="L836" s="6"/>
     </row>
-    <row r="837" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A837" s="5"/>
       <c r="B837" s="5"/>
       <c r="C837" s="5"/>
@@ -15921,7 +15921,7 @@
       <c r="K837" s="6"/>
       <c r="L837" s="6"/>
     </row>
-    <row r="838" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A838" s="5"/>
       <c r="B838" s="5"/>
       <c r="C838" s="5"/>
@@ -15935,7 +15935,7 @@
       <c r="K838" s="6"/>
       <c r="L838" s="6"/>
     </row>
-    <row r="839" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A839" s="5"/>
       <c r="B839" s="5"/>
       <c r="C839" s="5"/>
@@ -15949,7 +15949,7 @@
       <c r="K839" s="6"/>
       <c r="L839" s="6"/>
     </row>
-    <row r="840" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A840" s="5"/>
       <c r="B840" s="5"/>
       <c r="C840" s="5"/>
@@ -15963,7 +15963,7 @@
       <c r="K840" s="6"/>
       <c r="L840" s="6"/>
     </row>
-    <row r="841" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A841" s="5"/>
       <c r="B841" s="5"/>
       <c r="C841" s="5"/>
@@ -15977,7 +15977,7 @@
       <c r="K841" s="6"/>
       <c r="L841" s="6"/>
     </row>
-    <row r="842" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A842" s="5"/>
       <c r="B842" s="5"/>
       <c r="C842" s="5"/>
@@ -15991,7 +15991,7 @@
       <c r="K842" s="6"/>
       <c r="L842" s="6"/>
     </row>
-    <row r="843" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A843" s="5"/>
       <c r="B843" s="5"/>
       <c r="C843" s="5"/>
@@ -16005,7 +16005,7 @@
       <c r="K843" s="6"/>
       <c r="L843" s="6"/>
     </row>
-    <row r="844" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A844" s="5"/>
       <c r="B844" s="5"/>
       <c r="C844" s="5"/>
@@ -16019,7 +16019,7 @@
       <c r="K844" s="6"/>
       <c r="L844" s="6"/>
     </row>
-    <row r="845" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A845" s="5"/>
       <c r="B845" s="5"/>
       <c r="C845" s="5"/>
@@ -16033,7 +16033,7 @@
       <c r="K845" s="6"/>
       <c r="L845" s="6"/>
     </row>
-    <row r="846" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A846" s="5"/>
       <c r="B846" s="5"/>
       <c r="C846" s="5"/>
@@ -16047,7 +16047,7 @@
       <c r="K846" s="6"/>
       <c r="L846" s="6"/>
     </row>
-    <row r="847" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A847" s="5"/>
       <c r="B847" s="5"/>
       <c r="C847" s="5"/>
@@ -16061,7 +16061,7 @@
       <c r="K847" s="6"/>
       <c r="L847" s="6"/>
     </row>
-    <row r="848" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A848" s="5"/>
       <c r="B848" s="5"/>
       <c r="C848" s="5"/>
@@ -16075,7 +16075,7 @@
       <c r="K848" s="6"/>
       <c r="L848" s="6"/>
     </row>
-    <row r="849" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A849" s="5"/>
       <c r="B849" s="5"/>
       <c r="C849" s="5"/>
@@ -16089,7 +16089,7 @@
       <c r="K849" s="6"/>
       <c r="L849" s="6"/>
     </row>
-    <row r="850" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A850" s="5"/>
       <c r="B850" s="5"/>
       <c r="C850" s="5"/>
@@ -16103,7 +16103,7 @@
       <c r="K850" s="6"/>
       <c r="L850" s="6"/>
     </row>
-    <row r="851" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A851" s="5"/>
       <c r="B851" s="5"/>
       <c r="C851" s="5"/>
@@ -16117,7 +16117,7 @@
       <c r="K851" s="6"/>
       <c r="L851" s="6"/>
     </row>
-    <row r="852" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A852" s="5"/>
       <c r="B852" s="5"/>
       <c r="C852" s="5"/>
@@ -16131,7 +16131,7 @@
       <c r="K852" s="6"/>
       <c r="L852" s="6"/>
     </row>
-    <row r="853" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A853" s="5"/>
       <c r="B853" s="5"/>
       <c r="C853" s="5"/>
@@ -16145,7 +16145,7 @@
       <c r="K853" s="6"/>
       <c r="L853" s="6"/>
     </row>
-    <row r="854" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A854" s="5"/>
       <c r="B854" s="5"/>
       <c r="C854" s="5"/>
@@ -16159,7 +16159,7 @@
       <c r="K854" s="6"/>
       <c r="L854" s="6"/>
     </row>
-    <row r="855" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A855" s="5"/>
       <c r="B855" s="5"/>
       <c r="C855" s="5"/>
@@ -16173,7 +16173,7 @@
       <c r="K855" s="6"/>
       <c r="L855" s="6"/>
     </row>
-    <row r="856" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A856" s="5"/>
       <c r="B856" s="5"/>
       <c r="C856" s="5"/>
@@ -16187,7 +16187,7 @@
       <c r="K856" s="6"/>
       <c r="L856" s="6"/>
     </row>
-    <row r="857" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A857" s="5"/>
       <c r="B857" s="5"/>
       <c r="C857" s="5"/>
@@ -16201,7 +16201,7 @@
       <c r="K857" s="6"/>
       <c r="L857" s="6"/>
     </row>
-    <row r="858" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A858" s="5"/>
       <c r="B858" s="5"/>
       <c r="C858" s="5"/>
@@ -16215,7 +16215,7 @@
       <c r="K858" s="6"/>
       <c r="L858" s="6"/>
     </row>
-    <row r="859" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A859" s="5"/>
       <c r="B859" s="5"/>
       <c r="C859" s="5"/>
@@ -16229,7 +16229,7 @@
       <c r="K859" s="6"/>
       <c r="L859" s="6"/>
     </row>
-    <row r="860" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A860" s="5"/>
       <c r="B860" s="5"/>
       <c r="C860" s="5"/>
@@ -16243,7 +16243,7 @@
       <c r="K860" s="6"/>
       <c r="L860" s="6"/>
     </row>
-    <row r="861" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A861" s="5"/>
       <c r="B861" s="5"/>
       <c r="C861" s="5"/>
@@ -16257,7 +16257,7 @@
       <c r="K861" s="6"/>
       <c r="L861" s="6"/>
     </row>
-    <row r="862" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A862" s="5"/>
       <c r="B862" s="5"/>
       <c r="C862" s="5"/>
@@ -16271,7 +16271,7 @@
       <c r="K862" s="6"/>
       <c r="L862" s="6"/>
     </row>
-    <row r="863" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A863" s="5"/>
       <c r="B863" s="5"/>
       <c r="C863" s="5"/>
@@ -16285,7 +16285,7 @@
       <c r="K863" s="6"/>
       <c r="L863" s="6"/>
     </row>
-    <row r="864" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A864" s="5"/>
       <c r="B864" s="5"/>
       <c r="C864" s="5"/>
@@ -16299,7 +16299,7 @@
       <c r="K864" s="6"/>
       <c r="L864" s="6"/>
     </row>
-    <row r="865" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A865" s="5"/>
       <c r="B865" s="5"/>
       <c r="C865" s="5"/>
@@ -16313,7 +16313,7 @@
       <c r="K865" s="6"/>
       <c r="L865" s="6"/>
     </row>
-    <row r="866" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A866" s="5"/>
       <c r="B866" s="5"/>
       <c r="C866" s="5"/>
@@ -16327,7 +16327,7 @@
       <c r="K866" s="6"/>
       <c r="L866" s="6"/>
     </row>
-    <row r="867" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A867" s="5"/>
       <c r="B867" s="5"/>
       <c r="C867" s="5"/>
@@ -16341,7 +16341,7 @@
       <c r="K867" s="6"/>
       <c r="L867" s="6"/>
     </row>
-    <row r="868" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A868" s="5"/>
       <c r="B868" s="5"/>
       <c r="C868" s="5"/>
@@ -16355,7 +16355,7 @@
       <c r="K868" s="6"/>
       <c r="L868" s="6"/>
     </row>
-    <row r="869" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A869" s="5"/>
       <c r="B869" s="5"/>
       <c r="C869" s="5"/>
@@ -16369,7 +16369,7 @@
       <c r="K869" s="6"/>
       <c r="L869" s="6"/>
     </row>
-    <row r="870" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A870" s="5"/>
       <c r="B870" s="5"/>
       <c r="C870" s="5"/>
@@ -16383,7 +16383,7 @@
       <c r="K870" s="6"/>
       <c r="L870" s="6"/>
     </row>
-    <row r="871" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A871" s="5"/>
       <c r="B871" s="5"/>
       <c r="C871" s="5"/>
@@ -16397,7 +16397,7 @@
       <c r="K871" s="6"/>
       <c r="L871" s="6"/>
     </row>
-    <row r="872" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A872" s="5"/>
       <c r="B872" s="5"/>
       <c r="C872" s="5"/>
@@ -16411,7 +16411,7 @@
       <c r="K872" s="6"/>
       <c r="L872" s="6"/>
     </row>
-    <row r="873" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A873" s="5"/>
       <c r="B873" s="5"/>
       <c r="C873" s="5"/>
@@ -16425,7 +16425,7 @@
       <c r="K873" s="6"/>
       <c r="L873" s="6"/>
     </row>
-    <row r="874" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A874" s="5"/>
       <c r="B874" s="5"/>
       <c r="C874" s="5"/>
@@ -16439,7 +16439,7 @@
       <c r="K874" s="6"/>
       <c r="L874" s="6"/>
     </row>
-    <row r="875" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A875" s="5"/>
       <c r="B875" s="5"/>
       <c r="C875" s="5"/>
@@ -16453,7 +16453,7 @@
       <c r="K875" s="6"/>
       <c r="L875" s="6"/>
     </row>
-    <row r="876" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A876" s="5"/>
       <c r="B876" s="5"/>
       <c r="C876" s="5"/>
@@ -16467,7 +16467,7 @@
       <c r="K876" s="6"/>
       <c r="L876" s="6"/>
     </row>
-    <row r="877" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A877" s="5"/>
       <c r="B877" s="5"/>
       <c r="C877" s="5"/>
@@ -16481,7 +16481,7 @@
       <c r="K877" s="6"/>
       <c r="L877" s="6"/>
     </row>
-    <row r="878" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A878" s="5"/>
       <c r="B878" s="5"/>
       <c r="C878" s="5"/>
@@ -16495,7 +16495,7 @@
       <c r="K878" s="6"/>
       <c r="L878" s="6"/>
     </row>
-    <row r="879" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A879" s="5"/>
       <c r="B879" s="5"/>
       <c r="C879" s="5"/>
@@ -16509,7 +16509,7 @@
       <c r="K879" s="6"/>
       <c r="L879" s="6"/>
     </row>
-    <row r="880" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A880" s="5"/>
       <c r="B880" s="5"/>
       <c r="C880" s="5"/>
@@ -16523,7 +16523,7 @@
       <c r="K880" s="6"/>
       <c r="L880" s="6"/>
     </row>
-    <row r="881" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A881" s="5"/>
       <c r="B881" s="5"/>
       <c r="C881" s="5"/>
@@ -16537,7 +16537,7 @@
       <c r="K881" s="6"/>
       <c r="L881" s="6"/>
     </row>
-    <row r="882" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A882" s="5"/>
       <c r="B882" s="5"/>
       <c r="C882" s="5"/>
@@ -16551,7 +16551,7 @@
       <c r="K882" s="6"/>
       <c r="L882" s="6"/>
     </row>
-    <row r="883" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A883" s="5"/>
       <c r="B883" s="5"/>
       <c r="C883" s="5"/>
@@ -16565,7 +16565,7 @@
       <c r="K883" s="6"/>
       <c r="L883" s="6"/>
     </row>
-    <row r="884" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A884" s="5"/>
       <c r="B884" s="5"/>
       <c r="C884" s="5"/>
@@ -16579,7 +16579,7 @@
       <c r="K884" s="6"/>
       <c r="L884" s="6"/>
     </row>
-    <row r="885" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A885" s="5"/>
       <c r="B885" s="5"/>
       <c r="C885" s="5"/>
@@ -16593,7 +16593,7 @@
       <c r="K885" s="6"/>
       <c r="L885" s="6"/>
     </row>
-    <row r="886" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A886" s="5"/>
       <c r="B886" s="5"/>
       <c r="C886" s="5"/>
@@ -16607,7 +16607,7 @@
       <c r="K886" s="6"/>
       <c r="L886" s="6"/>
     </row>
-    <row r="887" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A887" s="5"/>
       <c r="B887" s="5"/>
       <c r="C887" s="5"/>
@@ -16621,7 +16621,7 @@
       <c r="K887" s="6"/>
       <c r="L887" s="6"/>
     </row>
-    <row r="888" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A888" s="5"/>
       <c r="B888" s="5"/>
       <c r="C888" s="5"/>
@@ -16635,7 +16635,7 @@
       <c r="K888" s="6"/>
       <c r="L888" s="6"/>
     </row>
-    <row r="889" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A889" s="5"/>
       <c r="B889" s="5"/>
       <c r="C889" s="5"/>
@@ -16649,7 +16649,7 @@
       <c r="K889" s="6"/>
       <c r="L889" s="6"/>
     </row>
-    <row r="890" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A890" s="5"/>
       <c r="B890" s="5"/>
       <c r="C890" s="5"/>
@@ -16663,7 +16663,7 @@
       <c r="K890" s="6"/>
       <c r="L890" s="6"/>
     </row>
-    <row r="891" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A891" s="5"/>
       <c r="B891" s="5"/>
       <c r="C891" s="5"/>
@@ -16677,7 +16677,7 @@
       <c r="K891" s="6"/>
       <c r="L891" s="6"/>
     </row>
-    <row r="892" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A892" s="5"/>
       <c r="B892" s="5"/>
       <c r="C892" s="5"/>
@@ -16691,7 +16691,7 @@
       <c r="K892" s="6"/>
       <c r="L892" s="6"/>
     </row>
-    <row r="893" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A893" s="5"/>
       <c r="B893" s="5"/>
       <c r="C893" s="5"/>
@@ -16705,7 +16705,7 @@
       <c r="K893" s="6"/>
       <c r="L893" s="6"/>
     </row>
-    <row r="894" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A894" s="5"/>
       <c r="B894" s="5"/>
       <c r="C894" s="5"/>
@@ -16719,7 +16719,7 @@
       <c r="K894" s="6"/>
       <c r="L894" s="6"/>
     </row>
-    <row r="895" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A895" s="5"/>
       <c r="B895" s="5"/>
       <c r="C895" s="5"/>
@@ -16733,7 +16733,7 @@
       <c r="K895" s="6"/>
       <c r="L895" s="6"/>
     </row>
-    <row r="896" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A896" s="5"/>
       <c r="B896" s="5"/>
       <c r="C896" s="5"/>
@@ -16747,7 +16747,7 @@
       <c r="K896" s="6"/>
       <c r="L896" s="6"/>
     </row>
-    <row r="897" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A897" s="5"/>
       <c r="B897" s="5"/>
       <c r="C897" s="5"/>
@@ -16761,7 +16761,7 @@
       <c r="K897" s="6"/>
       <c r="L897" s="6"/>
     </row>
-    <row r="898" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A898" s="5"/>
       <c r="B898" s="5"/>
       <c r="C898" s="5"/>
@@ -16775,7 +16775,7 @@
       <c r="K898" s="6"/>
       <c r="L898" s="6"/>
     </row>
-    <row r="899" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A899" s="5"/>
       <c r="B899" s="5"/>
       <c r="C899" s="5"/>
@@ -16789,7 +16789,7 @@
       <c r="K899" s="6"/>
       <c r="L899" s="6"/>
     </row>
-    <row r="900" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A900" s="5"/>
       <c r="B900" s="5"/>
       <c r="C900" s="5"/>
@@ -16803,7 +16803,7 @@
       <c r="K900" s="6"/>
       <c r="L900" s="6"/>
     </row>
-    <row r="901" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A901" s="5"/>
       <c r="B901" s="5"/>
       <c r="C901" s="5"/>
@@ -16817,7 +16817,7 @@
       <c r="K901" s="6"/>
       <c r="L901" s="6"/>
     </row>
-    <row r="902" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A902" s="5"/>
       <c r="B902" s="5"/>
       <c r="C902" s="5"/>
@@ -16831,7 +16831,7 @@
       <c r="K902" s="6"/>
       <c r="L902" s="6"/>
     </row>
-    <row r="903" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A903" s="5"/>
       <c r="B903" s="5"/>
       <c r="C903" s="5"/>
@@ -16845,7 +16845,7 @@
       <c r="K903" s="6"/>
       <c r="L903" s="6"/>
     </row>
-    <row r="904" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A904" s="5"/>
       <c r="B904" s="5"/>
       <c r="C904" s="5"/>
@@ -16859,7 +16859,7 @@
       <c r="K904" s="6"/>
       <c r="L904" s="6"/>
     </row>
-    <row r="905" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A905" s="5"/>
       <c r="B905" s="5"/>
       <c r="C905" s="5"/>
@@ -16873,7 +16873,7 @@
       <c r="K905" s="6"/>
       <c r="L905" s="6"/>
     </row>
-    <row r="906" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A906" s="5"/>
       <c r="B906" s="5"/>
       <c r="C906" s="5"/>
@@ -16887,7 +16887,7 @@
       <c r="K906" s="6"/>
       <c r="L906" s="6"/>
     </row>
-    <row r="907" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A907" s="5"/>
       <c r="B907" s="5"/>
       <c r="C907" s="5"/>
@@ -16901,7 +16901,7 @@
       <c r="K907" s="6"/>
       <c r="L907" s="6"/>
     </row>
-    <row r="908" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A908" s="5"/>
       <c r="B908" s="5"/>
       <c r="C908" s="5"/>
@@ -16915,7 +16915,7 @@
       <c r="K908" s="6"/>
       <c r="L908" s="6"/>
     </row>
-    <row r="909" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A909" s="5"/>
       <c r="B909" s="5"/>
       <c r="C909" s="5"/>
@@ -16929,7 +16929,7 @@
       <c r="K909" s="6"/>
       <c r="L909" s="6"/>
     </row>
-    <row r="910" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A910" s="5"/>
       <c r="B910" s="5"/>
       <c r="C910" s="5"/>
@@ -16943,7 +16943,7 @@
       <c r="K910" s="6"/>
       <c r="L910" s="6"/>
     </row>
-    <row r="911" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A911" s="5"/>
       <c r="B911" s="5"/>
       <c r="C911" s="5"/>
@@ -16957,7 +16957,7 @@
       <c r="K911" s="6"/>
       <c r="L911" s="6"/>
     </row>
-    <row r="912" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A912" s="5"/>
       <c r="B912" s="5"/>
       <c r="C912" s="5"/>
@@ -16971,7 +16971,7 @@
       <c r="K912" s="6"/>
       <c r="L912" s="6"/>
     </row>
-    <row r="913" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A913" s="5"/>
       <c r="B913" s="5"/>
       <c r="C913" s="5"/>
@@ -16985,7 +16985,7 @@
       <c r="K913" s="6"/>
       <c r="L913" s="6"/>
     </row>
-    <row r="914" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A914" s="5"/>
       <c r="B914" s="5"/>
       <c r="C914" s="5"/>
@@ -16999,7 +16999,7 @@
       <c r="K914" s="6"/>
       <c r="L914" s="6"/>
     </row>
-    <row r="915" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A915" s="5"/>
       <c r="B915" s="5"/>
       <c r="C915" s="5"/>
@@ -17013,7 +17013,7 @@
       <c r="K915" s="6"/>
       <c r="L915" s="6"/>
     </row>
-    <row r="916" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A916" s="5"/>
       <c r="B916" s="5"/>
       <c r="C916" s="5"/>
@@ -17027,7 +17027,7 @@
       <c r="K916" s="6"/>
       <c r="L916" s="6"/>
     </row>
-    <row r="917" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A917" s="5"/>
       <c r="B917" s="5"/>
       <c r="C917" s="5"/>
@@ -17041,7 +17041,7 @@
       <c r="K917" s="6"/>
       <c r="L917" s="6"/>
     </row>
-    <row r="918" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A918" s="5"/>
       <c r="B918" s="5"/>
       <c r="C918" s="5"/>
@@ -17055,7 +17055,7 @@
       <c r="K918" s="6"/>
       <c r="L918" s="6"/>
     </row>
-    <row r="919" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A919" s="5"/>
       <c r="B919" s="5"/>
       <c r="C919" s="5"/>
@@ -17069,7 +17069,7 @@
       <c r="K919" s="6"/>
       <c r="L919" s="6"/>
     </row>
-    <row r="920" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A920" s="5"/>
       <c r="B920" s="5"/>
       <c r="C920" s="5"/>
@@ -17083,7 +17083,7 @@
       <c r="K920" s="6"/>
       <c r="L920" s="6"/>
     </row>
-    <row r="921" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A921" s="5"/>
       <c r="B921" s="5"/>
       <c r="C921" s="5"/>
@@ -17097,7 +17097,7 @@
       <c r="K921" s="6"/>
       <c r="L921" s="6"/>
     </row>
-    <row r="922" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A922" s="5"/>
       <c r="B922" s="5"/>
       <c r="C922" s="5"/>
@@ -17111,7 +17111,7 @@
       <c r="K922" s="6"/>
       <c r="L922" s="6"/>
     </row>
-    <row r="923" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A923" s="5"/>
       <c r="B923" s="5"/>
       <c r="C923" s="5"/>
@@ -17125,7 +17125,7 @@
       <c r="K923" s="6"/>
       <c r="L923" s="6"/>
     </row>
-    <row r="924" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A924" s="5"/>
       <c r="B924" s="5"/>
       <c r="C924" s="5"/>
@@ -17139,7 +17139,7 @@
       <c r="K924" s="6"/>
       <c r="L924" s="6"/>
     </row>
-    <row r="925" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A925" s="5"/>
       <c r="B925" s="5"/>
       <c r="C925" s="5"/>
@@ -17153,7 +17153,7 @@
       <c r="K925" s="6"/>
       <c r="L925" s="6"/>
     </row>
-    <row r="926" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A926" s="5"/>
       <c r="B926" s="5"/>
       <c r="C926" s="5"/>
@@ -17167,7 +17167,7 @@
       <c r="K926" s="6"/>
       <c r="L926" s="6"/>
     </row>
-    <row r="927" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A927" s="5"/>
       <c r="B927" s="5"/>
       <c r="C927" s="5"/>
@@ -17181,7 +17181,7 @@
       <c r="K927" s="6"/>
       <c r="L927" s="6"/>
     </row>
-    <row r="928" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A928" s="5"/>
       <c r="B928" s="5"/>
       <c r="C928" s="5"/>
@@ -17195,7 +17195,7 @@
       <c r="K928" s="6"/>
       <c r="L928" s="6"/>
     </row>
-    <row r="929" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A929" s="5"/>
       <c r="B929" s="5"/>
       <c r="C929" s="5"/>
@@ -17209,7 +17209,7 @@
       <c r="K929" s="6"/>
       <c r="L929" s="6"/>
     </row>
-    <row r="930" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A930" s="5"/>
       <c r="B930" s="5"/>
       <c r="C930" s="5"/>
@@ -17223,7 +17223,7 @@
       <c r="K930" s="6"/>
       <c r="L930" s="6"/>
     </row>
-    <row r="931" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A931" s="5"/>
       <c r="B931" s="5"/>
       <c r="C931" s="5"/>
@@ -17237,7 +17237,7 @@
       <c r="K931" s="6"/>
       <c r="L931" s="6"/>
     </row>
-    <row r="932" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A932" s="5"/>
       <c r="B932" s="5"/>
       <c r="C932" s="5"/>
@@ -17251,7 +17251,7 @@
       <c r="K932" s="6"/>
       <c r="L932" s="6"/>
     </row>
-    <row r="933" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A933" s="5"/>
       <c r="B933" s="5"/>
       <c r="C933" s="5"/>
@@ -17265,7 +17265,7 @@
       <c r="K933" s="6"/>
       <c r="L933" s="6"/>
     </row>
-    <row r="934" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A934" s="5"/>
       <c r="B934" s="5"/>
       <c r="C934" s="5"/>
@@ -17279,7 +17279,7 @@
       <c r="K934" s="6"/>
       <c r="L934" s="6"/>
     </row>
-    <row r="935" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A935" s="5"/>
       <c r="B935" s="5"/>
       <c r="C935" s="5"/>
@@ -17293,7 +17293,7 @@
       <c r="K935" s="6"/>
       <c r="L935" s="6"/>
     </row>
-    <row r="936" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A936" s="5"/>
       <c r="B936" s="5"/>
       <c r="C936" s="5"/>
@@ -17307,7 +17307,7 @@
       <c r="K936" s="6"/>
       <c r="L936" s="6"/>
     </row>
-    <row r="937" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A937" s="5"/>
       <c r="B937" s="5"/>
       <c r="C937" s="5"/>
@@ -17321,7 +17321,7 @@
       <c r="K937" s="6"/>
       <c r="L937" s="6"/>
     </row>
-    <row r="938" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A938" s="5"/>
       <c r="B938" s="5"/>
       <c r="C938" s="5"/>
@@ -17335,7 +17335,7 @@
       <c r="K938" s="6"/>
       <c r="L938" s="6"/>
     </row>
-    <row r="939" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A939" s="5"/>
       <c r="B939" s="5"/>
       <c r="C939" s="5"/>
@@ -17349,7 +17349,7 @@
       <c r="K939" s="6"/>
       <c r="L939" s="6"/>
     </row>
-    <row r="940" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A940" s="5"/>
       <c r="B940" s="5"/>
       <c r="C940" s="5"/>
@@ -17363,7 +17363,7 @@
       <c r="K940" s="6"/>
       <c r="L940" s="6"/>
     </row>
-    <row r="941" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A941" s="5"/>
       <c r="B941" s="5"/>
       <c r="C941" s="5"/>
@@ -17377,7 +17377,7 @@
       <c r="K941" s="6"/>
       <c r="L941" s="6"/>
     </row>
-    <row r="942" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A942" s="5"/>
       <c r="B942" s="5"/>
       <c r="C942" s="5"/>
@@ -17391,7 +17391,7 @@
       <c r="K942" s="6"/>
       <c r="L942" s="6"/>
     </row>
-    <row r="943" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A943" s="5"/>
       <c r="B943" s="5"/>
       <c r="C943" s="5"/>
@@ -17405,7 +17405,7 @@
       <c r="K943" s="6"/>
       <c r="L943" s="6"/>
     </row>
-    <row r="944" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A944" s="5"/>
       <c r="B944" s="5"/>
       <c r="C944" s="5"/>
@@ -17419,7 +17419,7 @@
       <c r="K944" s="6"/>
       <c r="L944" s="6"/>
     </row>
-    <row r="945" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A945" s="5"/>
       <c r="B945" s="5"/>
       <c r="C945" s="5"/>
@@ -17433,7 +17433,7 @@
       <c r="K945" s="6"/>
       <c r="L945" s="6"/>
     </row>
-    <row r="946" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A946" s="5"/>
       <c r="B946" s="5"/>
       <c r="C946" s="5"/>
@@ -17447,7 +17447,7 @@
       <c r="K946" s="6"/>
       <c r="L946" s="6"/>
     </row>
-    <row r="947" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A947" s="5"/>
       <c r="B947" s="5"/>
       <c r="C947" s="5"/>
@@ -17461,7 +17461,7 @@
       <c r="K947" s="6"/>
       <c r="L947" s="6"/>
     </row>
-    <row r="948" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A948" s="5"/>
       <c r="B948" s="5"/>
       <c r="C948" s="5"/>
@@ -17475,7 +17475,7 @@
       <c r="K948" s="6"/>
       <c r="L948" s="6"/>
     </row>
-    <row r="949" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A949" s="5"/>
       <c r="B949" s="5"/>
       <c r="C949" s="5"/>
@@ -17489,7 +17489,7 @@
       <c r="K949" s="6"/>
       <c r="L949" s="6"/>
     </row>
-    <row r="950" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A950" s="5"/>
       <c r="B950" s="5"/>
       <c r="C950" s="5"/>
@@ -17503,7 +17503,7 @@
       <c r="K950" s="6"/>
       <c r="L950" s="6"/>
     </row>
-    <row r="951" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A951" s="5"/>
       <c r="B951" s="5"/>
       <c r="C951" s="5"/>
@@ -17517,7 +17517,7 @@
       <c r="K951" s="6"/>
       <c r="L951" s="6"/>
     </row>
-    <row r="952" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A952" s="5"/>
       <c r="B952" s="5"/>
       <c r="C952" s="5"/>
@@ -17531,7 +17531,7 @@
       <c r="K952" s="6"/>
       <c r="L952" s="6"/>
     </row>
-    <row r="953" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A953" s="5"/>
       <c r="B953" s="5"/>
       <c r="C953" s="5"/>
@@ -17545,7 +17545,7 @@
       <c r="K953" s="6"/>
       <c r="L953" s="6"/>
     </row>
-    <row r="954" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A954" s="5"/>
       <c r="B954" s="5"/>
       <c r="C954" s="5"/>
@@ -17559,7 +17559,7 @@
       <c r="K954" s="6"/>
       <c r="L954" s="6"/>
     </row>
-    <row r="955" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A955" s="5"/>
       <c r="B955" s="5"/>
       <c r="C955" s="5"/>
@@ -17573,7 +17573,7 @@
       <c r="K955" s="6"/>
       <c r="L955" s="6"/>
     </row>
-    <row r="956" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A956" s="5"/>
       <c r="B956" s="5"/>
       <c r="C956" s="5"/>
@@ -17587,7 +17587,7 @@
       <c r="K956" s="6"/>
       <c r="L956" s="6"/>
     </row>
-    <row r="957" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A957" s="5"/>
       <c r="B957" s="5"/>
       <c r="C957" s="5"/>
@@ -17601,7 +17601,7 @@
       <c r="K957" s="6"/>
       <c r="L957" s="6"/>
     </row>
-    <row r="958" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A958" s="5"/>
       <c r="B958" s="5"/>
       <c r="C958" s="5"/>
@@ -17615,7 +17615,7 @@
       <c r="K958" s="6"/>
       <c r="L958" s="6"/>
     </row>
-    <row r="959" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A959" s="5"/>
       <c r="B959" s="5"/>
       <c r="C959" s="5"/>
@@ -17629,7 +17629,7 @@
       <c r="K959" s="6"/>
       <c r="L959" s="6"/>
     </row>
-    <row r="960" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A960" s="5"/>
       <c r="B960" s="5"/>
       <c r="C960" s="5"/>
@@ -17643,7 +17643,7 @@
       <c r="K960" s="6"/>
       <c r="L960" s="6"/>
     </row>
-    <row r="961" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A961" s="5"/>
       <c r="B961" s="5"/>
       <c r="C961" s="5"/>
@@ -17657,7 +17657,7 @@
       <c r="K961" s="6"/>
       <c r="L961" s="6"/>
     </row>
-    <row r="962" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A962" s="5"/>
       <c r="B962" s="5"/>
       <c r="C962" s="5"/>
@@ -17671,7 +17671,7 @@
       <c r="K962" s="6"/>
       <c r="L962" s="6"/>
     </row>
-    <row r="963" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A963" s="5"/>
       <c r="B963" s="5"/>
       <c r="C963" s="5"/>
@@ -17685,7 +17685,7 @@
       <c r="K963" s="6"/>
       <c r="L963" s="6"/>
     </row>
-    <row r="964" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A964" s="5"/>
       <c r="B964" s="5"/>
       <c r="C964" s="5"/>
@@ -17699,7 +17699,7 @@
       <c r="K964" s="6"/>
       <c r="L964" s="6"/>
     </row>
-    <row r="965" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A965" s="5"/>
       <c r="B965" s="5"/>
       <c r="C965" s="5"/>
@@ -17713,7 +17713,7 @@
       <c r="K965" s="6"/>
       <c r="L965" s="6"/>
     </row>
-    <row r="966" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A966" s="5"/>
       <c r="B966" s="5"/>
       <c r="C966" s="5"/>
@@ -17727,7 +17727,7 @@
       <c r="K966" s="6"/>
       <c r="L966" s="6"/>
     </row>
-    <row r="967" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A967" s="5"/>
       <c r="B967" s="5"/>
       <c r="C967" s="5"/>
@@ -17741,7 +17741,7 @@
       <c r="K967" s="6"/>
       <c r="L967" s="6"/>
     </row>
-    <row r="968" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A968" s="5"/>
       <c r="B968" s="5"/>
       <c r="C968" s="5"/>
@@ -17755,7 +17755,7 @@
       <c r="K968" s="6"/>
       <c r="L968" s="6"/>
     </row>
-    <row r="969" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A969" s="5"/>
       <c r="B969" s="5"/>
       <c r="C969" s="5"/>
@@ -17769,7 +17769,7 @@
       <c r="K969" s="6"/>
       <c r="L969" s="6"/>
     </row>
-    <row r="970" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A970" s="5"/>
       <c r="B970" s="5"/>
       <c r="C970" s="5"/>
@@ -17783,7 +17783,7 @@
       <c r="K970" s="6"/>
       <c r="L970" s="6"/>
     </row>
-    <row r="971" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A971" s="5"/>
       <c r="B971" s="5"/>
       <c r="C971" s="5"/>
@@ -17797,7 +17797,7 @@
       <c r="K971" s="6"/>
       <c r="L971" s="6"/>
     </row>
-    <row r="972" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A972" s="5"/>
       <c r="B972" s="5"/>
       <c r="C972" s="5"/>
@@ -17811,7 +17811,7 @@
       <c r="K972" s="6"/>
       <c r="L972" s="6"/>
     </row>
-    <row r="973" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A973" s="5"/>
       <c r="B973" s="5"/>
       <c r="C973" s="5"/>
@@ -17825,7 +17825,7 @@
       <c r="K973" s="6"/>
       <c r="L973" s="6"/>
     </row>
-    <row r="974" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A974" s="5"/>
       <c r="B974" s="5"/>
       <c r="C974" s="5"/>
@@ -17839,7 +17839,7 @@
       <c r="K974" s="6"/>
       <c r="L974" s="6"/>
     </row>
-    <row r="975" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A975" s="5"/>
       <c r="B975" s="5"/>
       <c r="C975" s="5"/>
@@ -17853,7 +17853,7 @@
       <c r="K975" s="6"/>
       <c r="L975" s="6"/>
     </row>
-    <row r="976" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A976" s="5"/>
       <c r="B976" s="5"/>
       <c r="C976" s="5"/>
@@ -17867,7 +17867,7 @@
       <c r="K976" s="6"/>
       <c r="L976" s="6"/>
     </row>
-    <row r="977" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A977" s="5"/>
       <c r="B977" s="5"/>
       <c r="C977" s="5"/>
@@ -17881,7 +17881,7 @@
       <c r="K977" s="6"/>
       <c r="L977" s="6"/>
     </row>
-    <row r="978" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A978" s="5"/>
       <c r="B978" s="5"/>
       <c r="C978" s="5"/>
@@ -17895,7 +17895,7 @@
       <c r="K978" s="6"/>
       <c r="L978" s="6"/>
     </row>
-    <row r="979" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A979" s="5"/>
       <c r="B979" s="5"/>
       <c r="C979" s="5"/>
@@ -17909,7 +17909,7 @@
       <c r="K979" s="6"/>
       <c r="L979" s="6"/>
     </row>
-    <row r="980" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A980" s="5"/>
       <c r="B980" s="5"/>
       <c r="C980" s="5"/>
@@ -17923,7 +17923,7 @@
       <c r="K980" s="6"/>
       <c r="L980" s="6"/>
     </row>
-    <row r="981" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A981" s="5"/>
       <c r="B981" s="5"/>
       <c r="C981" s="5"/>
@@ -17937,7 +17937,7 @@
       <c r="K981" s="6"/>
       <c r="L981" s="6"/>
     </row>
-    <row r="982" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A982" s="5"/>
       <c r="B982" s="5"/>
       <c r="C982" s="5"/>
@@ -17951,7 +17951,7 @@
       <c r="K982" s="6"/>
       <c r="L982" s="6"/>
     </row>
-    <row r="983" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A983" s="5"/>
       <c r="B983" s="5"/>
       <c r="C983" s="5"/>
@@ -17965,7 +17965,7 @@
       <c r="K983" s="6"/>
       <c r="L983" s="6"/>
     </row>
-    <row r="984" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A984" s="5"/>
       <c r="B984" s="5"/>
       <c r="C984" s="5"/>
@@ -17979,7 +17979,7 @@
       <c r="K984" s="6"/>
       <c r="L984" s="6"/>
     </row>
-    <row r="985" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A985" s="5"/>
       <c r="B985" s="5"/>
       <c r="C985" s="5"/>
@@ -17993,7 +17993,7 @@
       <c r="K985" s="6"/>
       <c r="L985" s="6"/>
     </row>
-    <row r="986" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A986" s="5"/>
       <c r="B986" s="5"/>
       <c r="C986" s="5"/>
@@ -18007,7 +18007,7 @@
       <c r="K986" s="6"/>
       <c r="L986" s="6"/>
     </row>
-    <row r="987" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A987" s="5"/>
       <c r="B987" s="5"/>
       <c r="C987" s="5"/>
@@ -18021,7 +18021,7 @@
       <c r="K987" s="6"/>
       <c r="L987" s="6"/>
     </row>
-    <row r="988" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A988" s="5"/>
       <c r="B988" s="5"/>
       <c r="C988" s="5"/>
@@ -18035,7 +18035,7 @@
       <c r="K988" s="6"/>
       <c r="L988" s="6"/>
     </row>
-    <row r="989" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A989" s="5"/>
       <c r="B989" s="5"/>
       <c r="C989" s="5"/>
@@ -18049,7 +18049,7 @@
       <c r="K989" s="6"/>
       <c r="L989" s="6"/>
     </row>
-    <row r="990" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A990" s="5"/>
       <c r="B990" s="5"/>
       <c r="C990" s="5"/>
@@ -18063,7 +18063,7 @@
       <c r="K990" s="6"/>
       <c r="L990" s="6"/>
     </row>
-    <row r="991" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A991" s="5"/>
       <c r="B991" s="5"/>
       <c r="C991" s="5"/>
@@ -18077,7 +18077,7 @@
       <c r="K991" s="6"/>
       <c r="L991" s="6"/>
     </row>
-    <row r="992" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A992" s="5"/>
       <c r="B992" s="5"/>
       <c r="C992" s="5"/>
@@ -18091,7 +18091,7 @@
       <c r="K992" s="6"/>
       <c r="L992" s="6"/>
     </row>
-    <row r="993" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A993" s="5"/>
       <c r="B993" s="5"/>
       <c r="C993" s="5"/>
@@ -18105,7 +18105,7 @@
       <c r="K993" s="6"/>
       <c r="L993" s="6"/>
     </row>
-    <row r="994" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A994" s="5"/>
       <c r="B994" s="5"/>
       <c r="C994" s="5"/>
@@ -18119,7 +18119,7 @@
       <c r="K994" s="6"/>
       <c r="L994" s="6"/>
     </row>
-    <row r="995" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A995" s="5"/>
       <c r="B995" s="5"/>
       <c r="C995" s="5"/>
@@ -18133,7 +18133,7 @@
       <c r="K995" s="6"/>
       <c r="L995" s="6"/>
     </row>
-    <row r="996" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A996" s="5"/>
       <c r="B996" s="5"/>
       <c r="C996" s="5"/>
@@ -18147,7 +18147,7 @@
       <c r="K996" s="6"/>
       <c r="L996" s="6"/>
     </row>
-    <row r="997" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A997" s="5"/>
       <c r="B997" s="5"/>
       <c r="C997" s="5"/>
@@ -18161,7 +18161,7 @@
       <c r="K997" s="6"/>
       <c r="L997" s="6"/>
     </row>
-    <row r="998" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A998" s="5"/>
       <c r="B998" s="5"/>
       <c r="C998" s="5"/>
@@ -18175,7 +18175,7 @@
       <c r="K998" s="6"/>
       <c r="L998" s="6"/>
     </row>
-    <row r="999" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A999" s="5"/>
       <c r="B999" s="5"/>
       <c r="C999" s="5"/>
@@ -18189,7 +18189,7 @@
       <c r="K999" s="6"/>
       <c r="L999" s="6"/>
     </row>
-    <row r="1000" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1000" s="5"/>
       <c r="B1000" s="5"/>
       <c r="C1000" s="5"/>
@@ -18203,7 +18203,7 @@
       <c r="K1000" s="6"/>
       <c r="L1000" s="6"/>
     </row>
-    <row r="1001" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1001" s="5"/>
       <c r="B1001" s="5"/>
       <c r="C1001" s="5"/>
@@ -18217,7 +18217,7 @@
       <c r="K1001" s="6"/>
       <c r="L1001" s="6"/>
     </row>
-    <row r="1002" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1002" s="5"/>
       <c r="B1002" s="5"/>
       <c r="C1002" s="5"/>
@@ -18231,7 +18231,7 @@
       <c r="K1002" s="6"/>
       <c r="L1002" s="6"/>
     </row>
-    <row r="1003" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1003" s="5"/>
       <c r="B1003" s="5"/>
       <c r="C1003" s="5"/>
@@ -18245,7 +18245,7 @@
       <c r="K1003" s="6"/>
       <c r="L1003" s="6"/>
     </row>
-    <row r="1004" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1004" s="5"/>
       <c r="B1004" s="5"/>
       <c r="C1004" s="5"/>
@@ -18259,7 +18259,7 @@
       <c r="K1004" s="6"/>
       <c r="L1004" s="6"/>
     </row>
-    <row r="1005" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1005" s="5"/>
       <c r="B1005" s="5"/>
       <c r="C1005" s="5"/>
@@ -18273,7 +18273,7 @@
       <c r="K1005" s="6"/>
       <c r="L1005" s="6"/>
     </row>
-    <row r="1006" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1006" s="5"/>
       <c r="B1006" s="5"/>
       <c r="C1006" s="5"/>
@@ -18287,7 +18287,7 @@
       <c r="K1006" s="6"/>
       <c r="L1006" s="6"/>
     </row>
-    <row r="1007" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1007" s="5"/>
       <c r="B1007" s="5"/>
       <c r="C1007" s="5"/>
@@ -18301,7 +18301,7 @@
       <c r="K1007" s="6"/>
       <c r="L1007" s="6"/>
     </row>
-    <row r="1008" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1008" s="5"/>
       <c r="B1008" s="5"/>
       <c r="C1008" s="5"/>
@@ -18315,7 +18315,7 @@
       <c r="K1008" s="6"/>
       <c r="L1008" s="6"/>
     </row>
-    <row r="1009" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1009" s="5"/>
       <c r="B1009" s="5"/>
       <c r="C1009" s="5"/>
@@ -18329,7 +18329,7 @@
       <c r="K1009" s="6"/>
       <c r="L1009" s="6"/>
     </row>
-    <row r="1010" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1010" s="5"/>
       <c r="B1010" s="5"/>
       <c r="C1010" s="5"/>
@@ -18343,7 +18343,7 @@
       <c r="K1010" s="6"/>
       <c r="L1010" s="6"/>
     </row>
-    <row r="1011" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1011" s="5"/>
       <c r="B1011" s="5"/>
       <c r="C1011" s="5"/>
@@ -18357,7 +18357,7 @@
       <c r="K1011" s="6"/>
       <c r="L1011" s="6"/>
     </row>
-    <row r="1012" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1012" s="5"/>
       <c r="B1012" s="5"/>
       <c r="C1012" s="5"/>
@@ -18371,7 +18371,7 @@
       <c r="K1012" s="6"/>
       <c r="L1012" s="6"/>
     </row>
-    <row r="1013" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1013" s="5"/>
       <c r="B1013" s="5"/>
       <c r="C1013" s="5"/>
@@ -18385,7 +18385,7 @@
       <c r="K1013" s="6"/>
       <c r="L1013" s="6"/>
     </row>
-    <row r="1014" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1014" s="5"/>
       <c r="B1014" s="5"/>
       <c r="C1014" s="5"/>
@@ -18399,7 +18399,7 @@
       <c r="K1014" s="6"/>
       <c r="L1014" s="6"/>
     </row>
-    <row r="1015" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1015" s="5"/>
       <c r="B1015" s="5"/>
       <c r="C1015" s="5"/>
@@ -18413,7 +18413,7 @@
       <c r="K1015" s="6"/>
       <c r="L1015" s="6"/>
     </row>
-    <row r="1016" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:12" ht="72" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1016" s="5" t="s">
         <v>602</v>
       </c>
@@ -18439,7 +18439,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="1017" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:12" ht="72" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1017" s="5" t="s">
         <v>608</v>
       </c>
@@ -18467,17 +18467,17 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K1017" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K1017" ns2:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Minor Repeatable,Minor Fire-Once,Major"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" ns2:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L1017" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" ns2:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation type="list" allowBlank="1" sqref="L2:L1017" ns2:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="R2:R16" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="R2:R16" ns2:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Implemented,New,In progress,Under review,Buggy"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>Blocked - Missing continuation spec/logs</t>
+          <t>Blocked - Missing continuation spec</t>
         </is>
       </c>
     </row>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>Implemented - Final Closure Blocked</t>
+          <t>Implemented - Verified</t>
         </is>
       </c>
       <c r="N6" s="7" t="s">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t>Blocked - Missing continuation spec</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\klim\projects\chaos_redux\docs\spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{5A89095B-1873-4272-9EFE-4205D8C33EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B352B940-7C08-401C-AE0E-13C7D4A3A9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,11 @@
     <sheet name="Info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="620" uniqueCount="620">
   <si>
     <t>ID</t>
   </si>
@@ -1866,6 +1865,25 @@
   </si>
   <si>
     <t>In progress</t>
+  </si>
+  <si>
+    <t>Gathering Storm: First republic declarations begin once at least one breakaway ministry, garrison, or depot network stops obeying Moscow. The stage records the first durable republic release and opens the chain for follow-on republics instead of treating the crisis as a single scripted split.</t>
+  </si>
+  <si>
+    <t>Rising Chaos: Regional cascades begin once several republics are free. Release pressure starts feeding on visible breakaways, foreign attention, depot vulnerability, and League coordination, so additional republics can appear without waiting for a fixed low-threat gate.</t>
+  </si>
+  <si>
+    <t>Chaos Tier: Union Unmade begins once Moscow authority has failed as a Union-wide command. Ordinary remaining republics are forced out of the old center, terminal collapse rules take over, and the crisis becomes an open war over the former Union.</t>
+  </si>
+  <si>
+    <t>World Collapse: every remaining republic and eligible special splinter is allowed to break from the former Union once terminal collapse meets maximum chaos. The crisis stops being a managed secession sequence and becomes a full map-wide rupture.</t>
+  </si>
+  <si>
+    <t>Terminal Rupture: every remaining republic and eligible special splinter is allowed to break from the former Union once terminal collapse meets maximum chaos. The crisis stops being a managed secession sequence and becomes a full map-wide rupture.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-chaos successor mutation: serious successor authorities can appear outside the ordinary republic cascade when chaos is high enough. The first qualifying high-chaos successor records an actor-linked Soviet Collapse evolution entry.
+Extreme successor mutation: at maximum collapse pressure, fringe and special successor authorities can also break away. These entries mark the first qualifying extreme successor without duplicating every later report.</t>
   </si>
 </sst>
 </file>
@@ -2281,13 +2299,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <tabColor rgb="FF1C4587"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:R1017"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
@@ -2306,7 +2324,7 @@
     <col min="18" max="18" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2359,7 +2377,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="99.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" ht="99.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>15</v>
       </c>
@@ -2404,7 +2422,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="111.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -2447,7 +2465,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="90" customHeight="1" ns3:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>36</v>
       </c>
@@ -2496,7 +2514,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>47</v>
       </c>
@@ -2545,7 +2563,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>59</v>
       </c>
@@ -2555,24 +2573,27 @@
       <c r="C6" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>616</v>
+      </c>
       <c r="G6" s="6" t="s">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="I6" s="6"/>
+        <v>619</v>
+      </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="6" t="inlineStr">
-        <is>
-          <t>Implemented - Verified</t>
-        </is>
+      <c r="L6" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>61</v>
@@ -2586,13 +2607,11 @@
       <c r="Q6" s="8">
         <v>1</v>
       </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="R6" s="8" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>63</v>
       </c>
@@ -2627,7 +2646,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>68</v>
       </c>
@@ -2664,7 +2683,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>73</v>
       </c>
@@ -2699,7 +2718,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>77</v>
       </c>
@@ -2734,7 +2753,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>81</v>
       </c>
@@ -2771,7 +2790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>86</v>
       </c>
@@ -2808,7 +2827,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>91</v>
       </c>
@@ -2843,7 +2862,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>95</v>
       </c>
@@ -2880,7 +2899,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>99</v>
       </c>
@@ -2917,7 +2936,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>104</v>
       </c>
@@ -2950,7 +2969,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>107</v>
       </c>
@@ -2974,7 +2993,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>110</v>
       </c>
@@ -2998,7 +3017,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>113</v>
       </c>
@@ -3022,7 +3041,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>116</v>
       </c>
@@ -3046,7 +3065,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>119</v>
       </c>
@@ -3072,7 +3091,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>123</v>
       </c>
@@ -3099,7 +3118,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>127</v>
       </c>
@@ -3123,7 +3142,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>130</v>
       </c>
@@ -3147,7 +3166,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>133</v>
       </c>
@@ -3171,7 +3190,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>136</v>
       </c>
@@ -3195,7 +3214,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>139</v>
       </c>
@@ -3219,7 +3238,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>142</v>
       </c>
@@ -3243,7 +3262,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>145</v>
       </c>
@@ -3267,7 +3286,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>148</v>
       </c>
@@ -3291,7 +3310,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>151</v>
       </c>
@@ -3317,7 +3336,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:17" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>155</v>
       </c>
@@ -3341,7 +3360,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>158</v>
       </c>
@@ -3365,7 +3384,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>161</v>
       </c>
@@ -3389,7 +3408,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>164</v>
       </c>
@@ -3413,7 +3432,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>167</v>
       </c>
@@ -3437,7 +3456,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>170</v>
       </c>
@@ -3461,7 +3480,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>173</v>
       </c>
@@ -3485,7 +3504,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>176</v>
       </c>
@@ -3511,7 +3530,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>180</v>
       </c>
@@ -3535,7 +3554,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>183</v>
       </c>
@@ -3559,7 +3578,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>186</v>
       </c>
@@ -3583,7 +3602,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>189</v>
       </c>
@@ -3607,7 +3626,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>192</v>
       </c>
@@ -3631,7 +3650,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>195</v>
       </c>
@@ -3655,7 +3674,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>198</v>
       </c>
@@ -3679,7 +3698,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>201</v>
       </c>
@@ -3703,7 +3722,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>204</v>
       </c>
@@ -3727,7 +3746,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>207</v>
       </c>
@@ -3751,7 +3770,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>210</v>
       </c>
@@ -3775,7 +3794,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>213</v>
       </c>
@@ -3799,7 +3818,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>216</v>
       </c>
@@ -3823,7 +3842,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>219</v>
       </c>
@@ -3847,7 +3866,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>222</v>
       </c>
@@ -3871,7 +3890,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>225</v>
       </c>
@@ -3895,7 +3914,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>228</v>
       </c>
@@ -3919,7 +3938,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>231</v>
       </c>
@@ -3943,7 +3962,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>234</v>
       </c>
@@ -3967,7 +3986,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>237</v>
       </c>
@@ -3991,7 +4010,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>240</v>
       </c>
@@ -4015,7 +4034,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A61" s="4" t="s">
         <v>243</v>
       </c>
@@ -4039,7 +4058,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>246</v>
       </c>
@@ -4063,7 +4082,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A63" s="4" t="s">
         <v>249</v>
       </c>
@@ -4087,7 +4106,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>252</v>
       </c>
@@ -4111,7 +4130,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A65" s="4" t="s">
         <v>255</v>
       </c>
@@ -4135,7 +4154,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>258</v>
       </c>
@@ -4159,7 +4178,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A67" s="4" t="s">
         <v>261</v>
       </c>
@@ -4183,7 +4202,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>264</v>
       </c>
@@ -4207,7 +4226,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A69" s="4" t="s">
         <v>267</v>
       </c>
@@ -4233,7 +4252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>271</v>
       </c>
@@ -4257,7 +4276,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>274</v>
       </c>
@@ -4281,7 +4300,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A72" s="4" t="s">
         <v>277</v>
       </c>
@@ -4305,7 +4324,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>280</v>
       </c>
@@ -4329,7 +4348,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A74" s="4" t="s">
         <v>283</v>
       </c>
@@ -4353,7 +4372,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>286</v>
       </c>
@@ -4377,7 +4396,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A76" s="4" t="s">
         <v>289</v>
       </c>
@@ -4401,7 +4420,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>292</v>
       </c>
@@ -4425,7 +4444,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A78" s="4" t="s">
         <v>295</v>
       </c>
@@ -4449,7 +4468,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>298</v>
       </c>
@@ -4473,7 +4492,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A80" s="4" t="s">
         <v>301</v>
       </c>
@@ -4497,7 +4516,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>304</v>
       </c>
@@ -4521,7 +4540,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A82" s="4" t="s">
         <v>307</v>
       </c>
@@ -4545,7 +4564,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>310</v>
       </c>
@@ -4569,7 +4588,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A84" s="4" t="s">
         <v>313</v>
       </c>
@@ -4593,7 +4612,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>316</v>
       </c>
@@ -4617,7 +4636,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A86" s="4" t="s">
         <v>319</v>
       </c>
@@ -4641,7 +4660,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A87" s="4" t="s">
         <v>322</v>
       </c>
@@ -4665,7 +4684,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A88" s="4" t="s">
         <v>325</v>
       </c>
@@ -4689,7 +4708,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>328</v>
       </c>
@@ -4713,7 +4732,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A90" s="4" t="s">
         <v>331</v>
       </c>
@@ -4737,7 +4756,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>334</v>
       </c>
@@ -4761,7 +4780,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A92" s="4" t="s">
         <v>337</v>
       </c>
@@ -4787,7 +4806,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>341</v>
       </c>
@@ -4811,7 +4830,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A94" s="4" t="s">
         <v>344</v>
       </c>
@@ -4835,7 +4854,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>347</v>
       </c>
@@ -4859,7 +4878,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A96" s="4" t="s">
         <v>350</v>
       </c>
@@ -4883,7 +4902,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>353</v>
       </c>
@@ -4907,7 +4926,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A98" s="4" t="s">
         <v>356</v>
       </c>
@@ -4931,7 +4950,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>359</v>
       </c>
@@ -4955,7 +4974,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A100" s="4" t="s">
         <v>362</v>
       </c>
@@ -4979,7 +4998,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>365</v>
       </c>
@@ -5001,7 +5020,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A102" s="4" t="s">
         <v>368</v>
       </c>
@@ -5023,7 +5042,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>371</v>
       </c>
@@ -5045,7 +5064,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A104" s="4" t="s">
         <v>374</v>
       </c>
@@ -5067,7 +5086,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>377</v>
       </c>
@@ -5089,7 +5108,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A106" s="4" t="s">
         <v>380</v>
       </c>
@@ -5111,7 +5130,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>383</v>
       </c>
@@ -5133,7 +5152,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A108" s="4" t="s">
         <v>386</v>
       </c>
@@ -5155,7 +5174,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>389</v>
       </c>
@@ -5177,7 +5196,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A110" s="4" t="s">
         <v>392</v>
       </c>
@@ -5199,7 +5218,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>395</v>
       </c>
@@ -5221,7 +5240,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A112" s="4" t="s">
         <v>398</v>
       </c>
@@ -5243,7 +5262,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>401</v>
       </c>
@@ -5265,7 +5284,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A114" s="4" t="s">
         <v>404</v>
       </c>
@@ -5287,7 +5306,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>407</v>
       </c>
@@ -5309,7 +5328,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A116" s="4" t="s">
         <v>410</v>
       </c>
@@ -5331,7 +5350,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>413</v>
       </c>
@@ -5353,7 +5372,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A118" s="4" t="s">
         <v>416</v>
       </c>
@@ -5375,7 +5394,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>419</v>
       </c>
@@ -5397,7 +5416,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A120" s="4" t="s">
         <v>422</v>
       </c>
@@ -5419,7 +5438,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>425</v>
       </c>
@@ -5441,7 +5460,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A122" s="4" t="s">
         <v>428</v>
       </c>
@@ -5463,7 +5482,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>431</v>
       </c>
@@ -5485,7 +5504,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A124" s="4" t="s">
         <v>434</v>
       </c>
@@ -5507,7 +5526,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>437</v>
       </c>
@@ -5529,7 +5548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A126" s="4" t="s">
         <v>440</v>
       </c>
@@ -5551,7 +5570,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>443</v>
       </c>
@@ -5573,7 +5592,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A128" s="4" t="s">
         <v>446</v>
       </c>
@@ -5595,7 +5614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>449</v>
       </c>
@@ -5617,7 +5636,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A130" s="4" t="s">
         <v>452</v>
       </c>
@@ -5639,7 +5658,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A131" s="4" t="s">
         <v>455</v>
       </c>
@@ -5661,7 +5680,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A132" s="4" t="s">
         <v>458</v>
       </c>
@@ -5683,7 +5702,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>461</v>
       </c>
@@ -5705,7 +5724,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A134" s="4" t="s">
         <v>464</v>
       </c>
@@ -5727,7 +5746,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>467</v>
       </c>
@@ -5749,7 +5768,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A136" s="4" t="s">
         <v>470</v>
       </c>
@@ -5771,7 +5790,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>473</v>
       </c>
@@ -5793,7 +5812,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A138" s="4" t="s">
         <v>476</v>
       </c>
@@ -5815,7 +5834,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>479</v>
       </c>
@@ -5837,7 +5856,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A140" s="4" t="s">
         <v>482</v>
       </c>
@@ -5859,7 +5878,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>485</v>
       </c>
@@ -5881,7 +5900,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A142" s="4" t="s">
         <v>488</v>
       </c>
@@ -5903,7 +5922,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>491</v>
       </c>
@@ -5925,7 +5944,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A144" s="4" t="s">
         <v>494</v>
       </c>
@@ -5947,7 +5966,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>497</v>
       </c>
@@ -5969,7 +5988,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A146" s="4" t="s">
         <v>500</v>
       </c>
@@ -5991,7 +6010,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>503</v>
       </c>
@@ -6013,7 +6032,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A148" s="4" t="s">
         <v>506</v>
       </c>
@@ -6035,7 +6054,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>509</v>
       </c>
@@ -6057,7 +6076,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A150" s="4" t="s">
         <v>512</v>
       </c>
@@ -6079,7 +6098,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>515</v>
       </c>
@@ -6101,7 +6120,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A152" s="4" t="s">
         <v>518</v>
       </c>
@@ -6125,7 +6144,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A153" s="4" t="s">
         <v>522</v>
       </c>
@@ -6147,7 +6166,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A154" s="4" t="s">
         <v>525</v>
       </c>
@@ -6169,7 +6188,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>528</v>
       </c>
@@ -6191,7 +6210,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A156" s="4" t="s">
         <v>531</v>
       </c>
@@ -6213,7 +6232,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>534</v>
       </c>
@@ -6235,7 +6254,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A158" s="4" t="s">
         <v>537</v>
       </c>
@@ -6257,7 +6276,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>540</v>
       </c>
@@ -6279,7 +6298,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A160" s="4" t="s">
         <v>543</v>
       </c>
@@ -6301,7 +6320,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>546</v>
       </c>
@@ -6323,7 +6342,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A162" s="4" t="s">
         <v>549</v>
       </c>
@@ -6347,7 +6366,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>553</v>
       </c>
@@ -6369,7 +6388,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A164" s="4" t="s">
         <v>556</v>
       </c>
@@ -6391,7 +6410,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>559</v>
       </c>
@@ -6413,7 +6432,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A166" s="4" t="s">
         <v>562</v>
       </c>
@@ -6435,7 +6454,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>565</v>
       </c>
@@ -6459,7 +6478,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A168" s="5"/>
       <c r="B168" s="5" t="s">
         <v>568</v>
@@ -6477,7 +6496,7 @@
       <c r="K168" s="6"/>
       <c r="L168" s="6"/>
     </row>
-    <row r="169" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A169" s="5"/>
       <c r="B169" s="5" t="s">
         <v>570</v>
@@ -6495,7 +6514,7 @@
       <c r="K169" s="6"/>
       <c r="L169" s="6"/>
     </row>
-    <row r="170" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A170" s="5"/>
       <c r="B170" s="5" t="s">
         <v>572</v>
@@ -6513,7 +6532,7 @@
       <c r="K170" s="6"/>
       <c r="L170" s="6"/>
     </row>
-    <row r="171" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A171" s="5"/>
       <c r="B171" s="5" t="s">
         <v>574</v>
@@ -6531,7 +6550,7 @@
       <c r="K171" s="6"/>
       <c r="L171" s="6"/>
     </row>
-    <row r="172" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A172" s="5"/>
       <c r="B172" s="5" t="s">
         <v>576</v>
@@ -6549,7 +6568,7 @@
       <c r="K172" s="6"/>
       <c r="L172" s="6"/>
     </row>
-    <row r="173" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A173" s="5"/>
       <c r="B173" s="5" t="s">
         <v>578</v>
@@ -6569,7 +6588,7 @@
       <c r="K173" s="6"/>
       <c r="L173" s="6"/>
     </row>
-    <row r="174" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A174" s="5"/>
       <c r="B174" s="5" t="s">
         <v>581</v>
@@ -6587,7 +6606,7 @@
       <c r="K174" s="6"/>
       <c r="L174" s="6"/>
     </row>
-    <row r="175" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A175" s="5"/>
       <c r="B175" s="5" t="s">
         <v>583</v>
@@ -6605,7 +6624,7 @@
       <c r="K175" s="6"/>
       <c r="L175" s="6"/>
     </row>
-    <row r="176" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A176" s="5"/>
       <c r="B176" s="5" t="s">
         <v>585</v>
@@ -6623,7 +6642,7 @@
       <c r="K176" s="6"/>
       <c r="L176" s="6"/>
     </row>
-    <row r="177" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A177" s="5"/>
       <c r="B177" s="5" t="s">
         <v>587</v>
@@ -6641,7 +6660,7 @@
       <c r="K177" s="6"/>
       <c r="L177" s="6"/>
     </row>
-    <row r="178" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A178" s="5"/>
       <c r="B178" s="5" t="s">
         <v>589</v>
@@ -6659,7 +6678,7 @@
       <c r="K178" s="6"/>
       <c r="L178" s="6"/>
     </row>
-    <row r="179" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A179" s="5"/>
       <c r="B179" s="5" t="s">
         <v>591</v>
@@ -6677,7 +6696,7 @@
       <c r="K179" s="6"/>
       <c r="L179" s="6"/>
     </row>
-    <row r="180" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A180" s="5"/>
       <c r="B180" s="5" t="s">
         <v>593</v>
@@ -6695,7 +6714,7 @@
       <c r="K180" s="6"/>
       <c r="L180" s="6"/>
     </row>
-    <row r="181" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A181" s="5"/>
       <c r="B181" s="5" t="s">
         <v>595</v>
@@ -6713,7 +6732,7 @@
       <c r="K181" s="6"/>
       <c r="L181" s="6"/>
     </row>
-    <row r="182" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A182" s="5"/>
       <c r="B182" s="5" t="s">
         <v>597</v>
@@ -6731,7 +6750,7 @@
       <c r="K182" s="6"/>
       <c r="L182" s="6"/>
     </row>
-    <row r="183" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A183" s="5"/>
       <c r="B183" s="5" t="s">
         <v>599</v>
@@ -6749,7 +6768,7 @@
       <c r="K183" s="6"/>
       <c r="L183" s="6"/>
     </row>
-    <row r="184" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A184" s="5"/>
       <c r="B184" s="5"/>
       <c r="C184" s="5"/>
@@ -6763,7 +6782,7 @@
       <c r="K184" s="6"/>
       <c r="L184" s="6"/>
     </row>
-    <row r="185" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A185" s="5"/>
       <c r="B185" s="5"/>
       <c r="C185" s="5"/>
@@ -6777,7 +6796,7 @@
       <c r="K185" s="6"/>
       <c r="L185" s="6"/>
     </row>
-    <row r="186" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A186" s="5"/>
       <c r="B186" s="5"/>
       <c r="C186" s="5"/>
@@ -6791,7 +6810,7 @@
       <c r="K186" s="6"/>
       <c r="L186" s="6"/>
     </row>
-    <row r="187" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A187" s="5"/>
       <c r="B187" s="5"/>
       <c r="C187" s="5"/>
@@ -6805,7 +6824,7 @@
       <c r="K187" s="6"/>
       <c r="L187" s="6"/>
     </row>
-    <row r="188" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A188" s="5"/>
       <c r="B188" s="5"/>
       <c r="C188" s="5"/>
@@ -6819,7 +6838,7 @@
       <c r="K188" s="6"/>
       <c r="L188" s="6"/>
     </row>
-    <row r="189" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A189" s="5"/>
       <c r="B189" s="5"/>
       <c r="C189" s="5"/>
@@ -6833,7 +6852,7 @@
       <c r="K189" s="6"/>
       <c r="L189" s="6"/>
     </row>
-    <row r="190" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A190" s="5"/>
       <c r="B190" s="5"/>
       <c r="C190" s="5"/>
@@ -6847,7 +6866,7 @@
       <c r="K190" s="6"/>
       <c r="L190" s="6"/>
     </row>
-    <row r="191" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A191" s="5"/>
       <c r="B191" s="5"/>
       <c r="C191" s="5"/>
@@ -6861,7 +6880,7 @@
       <c r="K191" s="6"/>
       <c r="L191" s="6"/>
     </row>
-    <row r="192" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A192" s="5"/>
       <c r="B192" s="5"/>
       <c r="C192" s="5"/>
@@ -6875,7 +6894,7 @@
       <c r="K192" s="6"/>
       <c r="L192" s="6"/>
     </row>
-    <row r="193" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A193" s="5"/>
       <c r="B193" s="5"/>
       <c r="C193" s="5"/>
@@ -6889,7 +6908,7 @@
       <c r="K193" s="6"/>
       <c r="L193" s="6"/>
     </row>
-    <row r="194" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A194" s="5"/>
       <c r="B194" s="5"/>
       <c r="C194" s="5"/>
@@ -6903,7 +6922,7 @@
       <c r="K194" s="6"/>
       <c r="L194" s="6"/>
     </row>
-    <row r="195" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A195" s="5"/>
       <c r="B195" s="5"/>
       <c r="C195" s="5"/>
@@ -6917,7 +6936,7 @@
       <c r="K195" s="6"/>
       <c r="L195" s="6"/>
     </row>
-    <row r="196" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A196" s="5"/>
       <c r="B196" s="5"/>
       <c r="C196" s="5"/>
@@ -6931,7 +6950,7 @@
       <c r="K196" s="6"/>
       <c r="L196" s="6"/>
     </row>
-    <row r="197" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A197" s="5"/>
       <c r="B197" s="5"/>
       <c r="C197" s="5"/>
@@ -6945,7 +6964,7 @@
       <c r="K197" s="6"/>
       <c r="L197" s="6"/>
     </row>
-    <row r="198" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A198" s="5"/>
       <c r="B198" s="5"/>
       <c r="C198" s="5"/>
@@ -6959,7 +6978,7 @@
       <c r="K198" s="6"/>
       <c r="L198" s="6"/>
     </row>
-    <row r="199" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A199" s="5"/>
       <c r="B199" s="5"/>
       <c r="C199" s="5"/>
@@ -6973,7 +6992,7 @@
       <c r="K199" s="6"/>
       <c r="L199" s="6"/>
     </row>
-    <row r="200" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A200" s="5"/>
       <c r="B200" s="5"/>
       <c r="C200" s="5"/>
@@ -6987,7 +7006,7 @@
       <c r="K200" s="6"/>
       <c r="L200" s="6"/>
     </row>
-    <row r="201" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A201" s="5"/>
       <c r="B201" s="5"/>
       <c r="C201" s="5"/>
@@ -7001,7 +7020,7 @@
       <c r="K201" s="6"/>
       <c r="L201" s="6"/>
     </row>
-    <row r="202" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A202" s="5"/>
       <c r="B202" s="5"/>
       <c r="C202" s="5"/>
@@ -7015,7 +7034,7 @@
       <c r="K202" s="6"/>
       <c r="L202" s="6"/>
     </row>
-    <row r="203" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A203" s="5"/>
       <c r="B203" s="5"/>
       <c r="C203" s="5"/>
@@ -7029,7 +7048,7 @@
       <c r="K203" s="6"/>
       <c r="L203" s="6"/>
     </row>
-    <row r="204" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A204" s="5"/>
       <c r="B204" s="5"/>
       <c r="C204" s="5"/>
@@ -7043,7 +7062,7 @@
       <c r="K204" s="6"/>
       <c r="L204" s="6"/>
     </row>
-    <row r="205" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A205" s="5"/>
       <c r="B205" s="5"/>
       <c r="C205" s="5"/>
@@ -7057,7 +7076,7 @@
       <c r="K205" s="6"/>
       <c r="L205" s="6"/>
     </row>
-    <row r="206" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A206" s="5"/>
       <c r="B206" s="5"/>
       <c r="C206" s="5"/>
@@ -7071,7 +7090,7 @@
       <c r="K206" s="6"/>
       <c r="L206" s="6"/>
     </row>
-    <row r="207" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A207" s="5"/>
       <c r="B207" s="5"/>
       <c r="C207" s="5"/>
@@ -7085,7 +7104,7 @@
       <c r="K207" s="6"/>
       <c r="L207" s="6"/>
     </row>
-    <row r="208" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A208" s="5"/>
       <c r="B208" s="5"/>
       <c r="C208" s="5"/>
@@ -7099,7 +7118,7 @@
       <c r="K208" s="6"/>
       <c r="L208" s="6"/>
     </row>
-    <row r="209" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A209" s="5"/>
       <c r="B209" s="5"/>
       <c r="C209" s="5"/>
@@ -7113,7 +7132,7 @@
       <c r="K209" s="6"/>
       <c r="L209" s="6"/>
     </row>
-    <row r="210" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A210" s="5"/>
       <c r="B210" s="5"/>
       <c r="C210" s="5"/>
@@ -7127,7 +7146,7 @@
       <c r="K210" s="6"/>
       <c r="L210" s="6"/>
     </row>
-    <row r="211" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A211" s="5"/>
       <c r="B211" s="5"/>
       <c r="C211" s="5"/>
@@ -7141,7 +7160,7 @@
       <c r="K211" s="6"/>
       <c r="L211" s="6"/>
     </row>
-    <row r="212" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A212" s="5"/>
       <c r="B212" s="5"/>
       <c r="C212" s="5"/>
@@ -7155,7 +7174,7 @@
       <c r="K212" s="6"/>
       <c r="L212" s="6"/>
     </row>
-    <row r="213" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A213" s="5"/>
       <c r="B213" s="5"/>
       <c r="C213" s="5"/>
@@ -7169,7 +7188,7 @@
       <c r="K213" s="6"/>
       <c r="L213" s="6"/>
     </row>
-    <row r="214" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A214" s="5"/>
       <c r="B214" s="5"/>
       <c r="C214" s="5"/>
@@ -7183,7 +7202,7 @@
       <c r="K214" s="6"/>
       <c r="L214" s="6"/>
     </row>
-    <row r="215" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A215" s="5"/>
       <c r="B215" s="5"/>
       <c r="C215" s="5"/>
@@ -7197,7 +7216,7 @@
       <c r="K215" s="6"/>
       <c r="L215" s="6"/>
     </row>
-    <row r="216" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A216" s="5"/>
       <c r="B216" s="5"/>
       <c r="C216" s="5"/>
@@ -7211,7 +7230,7 @@
       <c r="K216" s="6"/>
       <c r="L216" s="6"/>
     </row>
-    <row r="217" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A217" s="5"/>
       <c r="B217" s="5"/>
       <c r="C217" s="5"/>
@@ -7225,7 +7244,7 @@
       <c r="K217" s="6"/>
       <c r="L217" s="6"/>
     </row>
-    <row r="218" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A218" s="5"/>
       <c r="B218" s="5"/>
       <c r="C218" s="5"/>
@@ -7239,7 +7258,7 @@
       <c r="K218" s="6"/>
       <c r="L218" s="6"/>
     </row>
-    <row r="219" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A219" s="5"/>
       <c r="B219" s="5"/>
       <c r="C219" s="5"/>
@@ -7253,7 +7272,7 @@
       <c r="K219" s="6"/>
       <c r="L219" s="6"/>
     </row>
-    <row r="220" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A220" s="5"/>
       <c r="B220" s="5"/>
       <c r="C220" s="5"/>
@@ -7267,7 +7286,7 @@
       <c r="K220" s="6"/>
       <c r="L220" s="6"/>
     </row>
-    <row r="221" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A221" s="5"/>
       <c r="B221" s="5"/>
       <c r="C221" s="5"/>
@@ -7281,7 +7300,7 @@
       <c r="K221" s="6"/>
       <c r="L221" s="6"/>
     </row>
-    <row r="222" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A222" s="5"/>
       <c r="B222" s="5"/>
       <c r="C222" s="5"/>
@@ -7295,7 +7314,7 @@
       <c r="K222" s="6"/>
       <c r="L222" s="6"/>
     </row>
-    <row r="223" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A223" s="5"/>
       <c r="B223" s="5"/>
       <c r="C223" s="5"/>
@@ -7309,7 +7328,7 @@
       <c r="K223" s="6"/>
       <c r="L223" s="6"/>
     </row>
-    <row r="224" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A224" s="5"/>
       <c r="B224" s="5"/>
       <c r="C224" s="5"/>
@@ -7323,7 +7342,7 @@
       <c r="K224" s="6"/>
       <c r="L224" s="6"/>
     </row>
-    <row r="225" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A225" s="5"/>
       <c r="B225" s="5"/>
       <c r="C225" s="5"/>
@@ -7337,7 +7356,7 @@
       <c r="K225" s="6"/>
       <c r="L225" s="6"/>
     </row>
-    <row r="226" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A226" s="5"/>
       <c r="B226" s="5"/>
       <c r="C226" s="5"/>
@@ -7351,7 +7370,7 @@
       <c r="K226" s="6"/>
       <c r="L226" s="6"/>
     </row>
-    <row r="227" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A227" s="5"/>
       <c r="B227" s="5"/>
       <c r="C227" s="5"/>
@@ -7365,7 +7384,7 @@
       <c r="K227" s="6"/>
       <c r="L227" s="6"/>
     </row>
-    <row r="228" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A228" s="5"/>
       <c r="B228" s="5"/>
       <c r="C228" s="5"/>
@@ -7379,7 +7398,7 @@
       <c r="K228" s="6"/>
       <c r="L228" s="6"/>
     </row>
-    <row r="229" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A229" s="5"/>
       <c r="B229" s="5"/>
       <c r="C229" s="5"/>
@@ -7393,7 +7412,7 @@
       <c r="K229" s="6"/>
       <c r="L229" s="6"/>
     </row>
-    <row r="230" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A230" s="5"/>
       <c r="B230" s="5"/>
       <c r="C230" s="5"/>
@@ -7407,7 +7426,7 @@
       <c r="K230" s="6"/>
       <c r="L230" s="6"/>
     </row>
-    <row r="231" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A231" s="5"/>
       <c r="B231" s="5"/>
       <c r="C231" s="5"/>
@@ -7421,7 +7440,7 @@
       <c r="K231" s="6"/>
       <c r="L231" s="6"/>
     </row>
-    <row r="232" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A232" s="5"/>
       <c r="B232" s="5"/>
       <c r="C232" s="5"/>
@@ -7435,7 +7454,7 @@
       <c r="K232" s="6"/>
       <c r="L232" s="6"/>
     </row>
-    <row r="233" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A233" s="5"/>
       <c r="B233" s="5"/>
       <c r="C233" s="5"/>
@@ -7449,7 +7468,7 @@
       <c r="K233" s="6"/>
       <c r="L233" s="6"/>
     </row>
-    <row r="234" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A234" s="5"/>
       <c r="B234" s="5"/>
       <c r="C234" s="5"/>
@@ -7463,7 +7482,7 @@
       <c r="K234" s="6"/>
       <c r="L234" s="6"/>
     </row>
-    <row r="235" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A235" s="5"/>
       <c r="B235" s="5"/>
       <c r="C235" s="5"/>
@@ -7477,7 +7496,7 @@
       <c r="K235" s="6"/>
       <c r="L235" s="6"/>
     </row>
-    <row r="236" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A236" s="5"/>
       <c r="B236" s="5"/>
       <c r="C236" s="5"/>
@@ -7491,7 +7510,7 @@
       <c r="K236" s="6"/>
       <c r="L236" s="6"/>
     </row>
-    <row r="237" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A237" s="5"/>
       <c r="B237" s="5"/>
       <c r="C237" s="5"/>
@@ -7505,7 +7524,7 @@
       <c r="K237" s="6"/>
       <c r="L237" s="6"/>
     </row>
-    <row r="238" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A238" s="5"/>
       <c r="B238" s="5"/>
       <c r="C238" s="5"/>
@@ -7519,7 +7538,7 @@
       <c r="K238" s="6"/>
       <c r="L238" s="6"/>
     </row>
-    <row r="239" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A239" s="5"/>
       <c r="B239" s="5"/>
       <c r="C239" s="5"/>
@@ -7533,7 +7552,7 @@
       <c r="K239" s="6"/>
       <c r="L239" s="6"/>
     </row>
-    <row r="240" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A240" s="5"/>
       <c r="B240" s="5"/>
       <c r="C240" s="5"/>
@@ -7547,7 +7566,7 @@
       <c r="K240" s="6"/>
       <c r="L240" s="6"/>
     </row>
-    <row r="241" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A241" s="5"/>
       <c r="B241" s="5"/>
       <c r="C241" s="5"/>
@@ -7561,7 +7580,7 @@
       <c r="K241" s="6"/>
       <c r="L241" s="6"/>
     </row>
-    <row r="242" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A242" s="5"/>
       <c r="B242" s="5"/>
       <c r="C242" s="5"/>
@@ -7575,7 +7594,7 @@
       <c r="K242" s="6"/>
       <c r="L242" s="6"/>
     </row>
-    <row r="243" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A243" s="5"/>
       <c r="B243" s="5"/>
       <c r="C243" s="5"/>
@@ -7589,7 +7608,7 @@
       <c r="K243" s="6"/>
       <c r="L243" s="6"/>
     </row>
-    <row r="244" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A244" s="5"/>
       <c r="B244" s="5"/>
       <c r="C244" s="5"/>
@@ -7603,7 +7622,7 @@
       <c r="K244" s="6"/>
       <c r="L244" s="6"/>
     </row>
-    <row r="245" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A245" s="5"/>
       <c r="B245" s="5"/>
       <c r="C245" s="5"/>
@@ -7617,7 +7636,7 @@
       <c r="K245" s="6"/>
       <c r="L245" s="6"/>
     </row>
-    <row r="246" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A246" s="5"/>
       <c r="B246" s="5"/>
       <c r="C246" s="5"/>
@@ -7631,7 +7650,7 @@
       <c r="K246" s="6"/>
       <c r="L246" s="6"/>
     </row>
-    <row r="247" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A247" s="5"/>
       <c r="B247" s="5"/>
       <c r="C247" s="5"/>
@@ -7645,7 +7664,7 @@
       <c r="K247" s="6"/>
       <c r="L247" s="6"/>
     </row>
-    <row r="248" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A248" s="5"/>
       <c r="B248" s="5"/>
       <c r="C248" s="5"/>
@@ -7659,7 +7678,7 @@
       <c r="K248" s="6"/>
       <c r="L248" s="6"/>
     </row>
-    <row r="249" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A249" s="5"/>
       <c r="B249" s="5"/>
       <c r="C249" s="5"/>
@@ -7673,7 +7692,7 @@
       <c r="K249" s="6"/>
       <c r="L249" s="6"/>
     </row>
-    <row r="250" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A250" s="5"/>
       <c r="B250" s="5"/>
       <c r="C250" s="5"/>
@@ -7687,7 +7706,7 @@
       <c r="K250" s="6"/>
       <c r="L250" s="6"/>
     </row>
-    <row r="251" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A251" s="5"/>
       <c r="B251" s="5"/>
       <c r="C251" s="5"/>
@@ -7701,7 +7720,7 @@
       <c r="K251" s="6"/>
       <c r="L251" s="6"/>
     </row>
-    <row r="252" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A252" s="5"/>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -7715,7 +7734,7 @@
       <c r="K252" s="6"/>
       <c r="L252" s="6"/>
     </row>
-    <row r="253" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A253" s="5"/>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -7729,7 +7748,7 @@
       <c r="K253" s="6"/>
       <c r="L253" s="6"/>
     </row>
-    <row r="254" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A254" s="5"/>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -7743,7 +7762,7 @@
       <c r="K254" s="6"/>
       <c r="L254" s="6"/>
     </row>
-    <row r="255" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A255" s="5"/>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
@@ -7757,7 +7776,7 @@
       <c r="K255" s="6"/>
       <c r="L255" s="6"/>
     </row>
-    <row r="256" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A256" s="5"/>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -7771,7 +7790,7 @@
       <c r="K256" s="6"/>
       <c r="L256" s="6"/>
     </row>
-    <row r="257" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A257" s="5"/>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -7785,7 +7804,7 @@
       <c r="K257" s="6"/>
       <c r="L257" s="6"/>
     </row>
-    <row r="258" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A258" s="5"/>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -7799,7 +7818,7 @@
       <c r="K258" s="6"/>
       <c r="L258" s="6"/>
     </row>
-    <row r="259" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A259" s="5"/>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -7813,7 +7832,7 @@
       <c r="K259" s="6"/>
       <c r="L259" s="6"/>
     </row>
-    <row r="260" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A260" s="5"/>
       <c r="B260" s="5"/>
       <c r="C260" s="5"/>
@@ -7827,7 +7846,7 @@
       <c r="K260" s="6"/>
       <c r="L260" s="6"/>
     </row>
-    <row r="261" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A261" s="5"/>
       <c r="B261" s="5"/>
       <c r="C261" s="5"/>
@@ -7841,7 +7860,7 @@
       <c r="K261" s="6"/>
       <c r="L261" s="6"/>
     </row>
-    <row r="262" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A262" s="5"/>
       <c r="B262" s="5"/>
       <c r="C262" s="5"/>
@@ -7855,7 +7874,7 @@
       <c r="K262" s="6"/>
       <c r="L262" s="6"/>
     </row>
-    <row r="263" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A263" s="5"/>
       <c r="B263" s="5"/>
       <c r="C263" s="5"/>
@@ -7869,7 +7888,7 @@
       <c r="K263" s="6"/>
       <c r="L263" s="6"/>
     </row>
-    <row r="264" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A264" s="5"/>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -7883,7 +7902,7 @@
       <c r="K264" s="6"/>
       <c r="L264" s="6"/>
     </row>
-    <row r="265" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A265" s="5"/>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -7897,7 +7916,7 @@
       <c r="K265" s="6"/>
       <c r="L265" s="6"/>
     </row>
-    <row r="266" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A266" s="5"/>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -7911,7 +7930,7 @@
       <c r="K266" s="6"/>
       <c r="L266" s="6"/>
     </row>
-    <row r="267" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A267" s="5"/>
       <c r="B267" s="5"/>
       <c r="C267" s="5"/>
@@ -7925,7 +7944,7 @@
       <c r="K267" s="6"/>
       <c r="L267" s="6"/>
     </row>
-    <row r="268" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A268" s="5"/>
       <c r="B268" s="5"/>
       <c r="C268" s="5"/>
@@ -7939,7 +7958,7 @@
       <c r="K268" s="6"/>
       <c r="L268" s="6"/>
     </row>
-    <row r="269" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A269" s="5"/>
       <c r="B269" s="5"/>
       <c r="C269" s="5"/>
@@ -7953,7 +7972,7 @@
       <c r="K269" s="6"/>
       <c r="L269" s="6"/>
     </row>
-    <row r="270" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A270" s="5"/>
       <c r="B270" s="5"/>
       <c r="C270" s="5"/>
@@ -7967,7 +7986,7 @@
       <c r="K270" s="6"/>
       <c r="L270" s="6"/>
     </row>
-    <row r="271" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A271" s="5"/>
       <c r="B271" s="5"/>
       <c r="C271" s="5"/>
@@ -7981,7 +8000,7 @@
       <c r="K271" s="6"/>
       <c r="L271" s="6"/>
     </row>
-    <row r="272" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A272" s="5"/>
       <c r="B272" s="5"/>
       <c r="C272" s="5"/>
@@ -7995,7 +8014,7 @@
       <c r="K272" s="6"/>
       <c r="L272" s="6"/>
     </row>
-    <row r="273" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A273" s="5"/>
       <c r="B273" s="5"/>
       <c r="C273" s="5"/>
@@ -8009,7 +8028,7 @@
       <c r="K273" s="6"/>
       <c r="L273" s="6"/>
     </row>
-    <row r="274" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A274" s="5"/>
       <c r="B274" s="5"/>
       <c r="C274" s="5"/>
@@ -8023,7 +8042,7 @@
       <c r="K274" s="6"/>
       <c r="L274" s="6"/>
     </row>
-    <row r="275" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A275" s="5"/>
       <c r="B275" s="5"/>
       <c r="C275" s="5"/>
@@ -8037,7 +8056,7 @@
       <c r="K275" s="6"/>
       <c r="L275" s="6"/>
     </row>
-    <row r="276" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A276" s="5"/>
       <c r="B276" s="5"/>
       <c r="C276" s="5"/>
@@ -8051,7 +8070,7 @@
       <c r="K276" s="6"/>
       <c r="L276" s="6"/>
     </row>
-    <row r="277" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A277" s="5"/>
       <c r="B277" s="5"/>
       <c r="C277" s="5"/>
@@ -8065,7 +8084,7 @@
       <c r="K277" s="6"/>
       <c r="L277" s="6"/>
     </row>
-    <row r="278" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A278" s="5"/>
       <c r="B278" s="5"/>
       <c r="C278" s="5"/>
@@ -8079,7 +8098,7 @@
       <c r="K278" s="6"/>
       <c r="L278" s="6"/>
     </row>
-    <row r="279" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A279" s="5"/>
       <c r="B279" s="5"/>
       <c r="C279" s="5"/>
@@ -8093,7 +8112,7 @@
       <c r="K279" s="6"/>
       <c r="L279" s="6"/>
     </row>
-    <row r="280" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A280" s="5"/>
       <c r="B280" s="5"/>
       <c r="C280" s="5"/>
@@ -8107,7 +8126,7 @@
       <c r="K280" s="6"/>
       <c r="L280" s="6"/>
     </row>
-    <row r="281" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A281" s="5"/>
       <c r="B281" s="5"/>
       <c r="C281" s="5"/>
@@ -8121,7 +8140,7 @@
       <c r="K281" s="6"/>
       <c r="L281" s="6"/>
     </row>
-    <row r="282" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A282" s="5"/>
       <c r="B282" s="5"/>
       <c r="C282" s="5"/>
@@ -8135,7 +8154,7 @@
       <c r="K282" s="6"/>
       <c r="L282" s="6"/>
     </row>
-    <row r="283" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A283" s="5"/>
       <c r="B283" s="5"/>
       <c r="C283" s="5"/>
@@ -8149,7 +8168,7 @@
       <c r="K283" s="6"/>
       <c r="L283" s="6"/>
     </row>
-    <row r="284" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A284" s="5"/>
       <c r="B284" s="5"/>
       <c r="C284" s="5"/>
@@ -8163,7 +8182,7 @@
       <c r="K284" s="6"/>
       <c r="L284" s="6"/>
     </row>
-    <row r="285" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A285" s="5"/>
       <c r="B285" s="5"/>
       <c r="C285" s="5"/>
@@ -8177,7 +8196,7 @@
       <c r="K285" s="6"/>
       <c r="L285" s="6"/>
     </row>
-    <row r="286" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A286" s="5"/>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
@@ -8191,7 +8210,7 @@
       <c r="K286" s="6"/>
       <c r="L286" s="6"/>
     </row>
-    <row r="287" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A287" s="5"/>
       <c r="B287" s="5"/>
       <c r="C287" s="5"/>
@@ -8205,7 +8224,7 @@
       <c r="K287" s="6"/>
       <c r="L287" s="6"/>
     </row>
-    <row r="288" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A288" s="5"/>
       <c r="B288" s="5"/>
       <c r="C288" s="5"/>
@@ -8219,7 +8238,7 @@
       <c r="K288" s="6"/>
       <c r="L288" s="6"/>
     </row>
-    <row r="289" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A289" s="5"/>
       <c r="B289" s="5"/>
       <c r="C289" s="5"/>
@@ -8233,7 +8252,7 @@
       <c r="K289" s="6"/>
       <c r="L289" s="6"/>
     </row>
-    <row r="290" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A290" s="5"/>
       <c r="B290" s="5"/>
       <c r="C290" s="5"/>
@@ -8247,7 +8266,7 @@
       <c r="K290" s="6"/>
       <c r="L290" s="6"/>
     </row>
-    <row r="291" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A291" s="5"/>
       <c r="B291" s="5"/>
       <c r="C291" s="5"/>
@@ -8261,7 +8280,7 @@
       <c r="K291" s="6"/>
       <c r="L291" s="6"/>
     </row>
-    <row r="292" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A292" s="5"/>
       <c r="B292" s="5"/>
       <c r="C292" s="5"/>
@@ -8275,7 +8294,7 @@
       <c r="K292" s="6"/>
       <c r="L292" s="6"/>
     </row>
-    <row r="293" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A293" s="5"/>
       <c r="B293" s="5"/>
       <c r="C293" s="5"/>
@@ -8289,7 +8308,7 @@
       <c r="K293" s="6"/>
       <c r="L293" s="6"/>
     </row>
-    <row r="294" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A294" s="5"/>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
@@ -8303,7 +8322,7 @@
       <c r="K294" s="6"/>
       <c r="L294" s="6"/>
     </row>
-    <row r="295" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A295" s="5"/>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
@@ -8317,7 +8336,7 @@
       <c r="K295" s="6"/>
       <c r="L295" s="6"/>
     </row>
-    <row r="296" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A296" s="5"/>
       <c r="B296" s="5"/>
       <c r="C296" s="5"/>
@@ -8331,7 +8350,7 @@
       <c r="K296" s="6"/>
       <c r="L296" s="6"/>
     </row>
-    <row r="297" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A297" s="5"/>
       <c r="B297" s="5"/>
       <c r="C297" s="5"/>
@@ -8345,7 +8364,7 @@
       <c r="K297" s="6"/>
       <c r="L297" s="6"/>
     </row>
-    <row r="298" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A298" s="5"/>
       <c r="B298" s="5"/>
       <c r="C298" s="5"/>
@@ -8359,7 +8378,7 @@
       <c r="K298" s="6"/>
       <c r="L298" s="6"/>
     </row>
-    <row r="299" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A299" s="5"/>
       <c r="B299" s="5"/>
       <c r="C299" s="5"/>
@@ -8373,7 +8392,7 @@
       <c r="K299" s="6"/>
       <c r="L299" s="6"/>
     </row>
-    <row r="300" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A300" s="5"/>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
@@ -8387,7 +8406,7 @@
       <c r="K300" s="6"/>
       <c r="L300" s="6"/>
     </row>
-    <row r="301" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A301" s="5"/>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
@@ -8401,7 +8420,7 @@
       <c r="K301" s="6"/>
       <c r="L301" s="6"/>
     </row>
-    <row r="302" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A302" s="5"/>
       <c r="B302" s="5"/>
       <c r="C302" s="5"/>
@@ -8415,7 +8434,7 @@
       <c r="K302" s="6"/>
       <c r="L302" s="6"/>
     </row>
-    <row r="303" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A303" s="5"/>
       <c r="B303" s="5"/>
       <c r="C303" s="5"/>
@@ -8429,7 +8448,7 @@
       <c r="K303" s="6"/>
       <c r="L303" s="6"/>
     </row>
-    <row r="304" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A304" s="5"/>
       <c r="B304" s="5"/>
       <c r="C304" s="5"/>
@@ -8443,7 +8462,7 @@
       <c r="K304" s="6"/>
       <c r="L304" s="6"/>
     </row>
-    <row r="305" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A305" s="5"/>
       <c r="B305" s="5"/>
       <c r="C305" s="5"/>
@@ -8457,7 +8476,7 @@
       <c r="K305" s="6"/>
       <c r="L305" s="6"/>
     </row>
-    <row r="306" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A306" s="5"/>
       <c r="B306" s="5"/>
       <c r="C306" s="5"/>
@@ -8471,7 +8490,7 @@
       <c r="K306" s="6"/>
       <c r="L306" s="6"/>
     </row>
-    <row r="307" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A307" s="5"/>
       <c r="B307" s="5"/>
       <c r="C307" s="5"/>
@@ -8485,7 +8504,7 @@
       <c r="K307" s="6"/>
       <c r="L307" s="6"/>
     </row>
-    <row r="308" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A308" s="5"/>
       <c r="B308" s="5"/>
       <c r="C308" s="5"/>
@@ -8499,7 +8518,7 @@
       <c r="K308" s="6"/>
       <c r="L308" s="6"/>
     </row>
-    <row r="309" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A309" s="5"/>
       <c r="B309" s="5"/>
       <c r="C309" s="5"/>
@@ -8513,7 +8532,7 @@
       <c r="K309" s="6"/>
       <c r="L309" s="6"/>
     </row>
-    <row r="310" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A310" s="5"/>
       <c r="B310" s="5"/>
       <c r="C310" s="5"/>
@@ -8527,7 +8546,7 @@
       <c r="K310" s="6"/>
       <c r="L310" s="6"/>
     </row>
-    <row r="311" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A311" s="5"/>
       <c r="B311" s="5"/>
       <c r="C311" s="5"/>
@@ -8541,7 +8560,7 @@
       <c r="K311" s="6"/>
       <c r="L311" s="6"/>
     </row>
-    <row r="312" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A312" s="5"/>
       <c r="B312" s="5"/>
       <c r="C312" s="5"/>
@@ -8555,7 +8574,7 @@
       <c r="K312" s="6"/>
       <c r="L312" s="6"/>
     </row>
-    <row r="313" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A313" s="5"/>
       <c r="B313" s="5"/>
       <c r="C313" s="5"/>
@@ -8569,7 +8588,7 @@
       <c r="K313" s="6"/>
       <c r="L313" s="6"/>
     </row>
-    <row r="314" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A314" s="5"/>
       <c r="B314" s="5"/>
       <c r="C314" s="5"/>
@@ -8583,7 +8602,7 @@
       <c r="K314" s="6"/>
       <c r="L314" s="6"/>
     </row>
-    <row r="315" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A315" s="5"/>
       <c r="B315" s="5"/>
       <c r="C315" s="5"/>
@@ -8597,7 +8616,7 @@
       <c r="K315" s="6"/>
       <c r="L315" s="6"/>
     </row>
-    <row r="316" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A316" s="5"/>
       <c r="B316" s="5"/>
       <c r="C316" s="5"/>
@@ -8611,7 +8630,7 @@
       <c r="K316" s="6"/>
       <c r="L316" s="6"/>
     </row>
-    <row r="317" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A317" s="5"/>
       <c r="B317" s="5"/>
       <c r="C317" s="5"/>
@@ -8625,7 +8644,7 @@
       <c r="K317" s="6"/>
       <c r="L317" s="6"/>
     </row>
-    <row r="318" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A318" s="5"/>
       <c r="B318" s="5"/>
       <c r="C318" s="5"/>
@@ -8639,7 +8658,7 @@
       <c r="K318" s="6"/>
       <c r="L318" s="6"/>
     </row>
-    <row r="319" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A319" s="5"/>
       <c r="B319" s="5"/>
       <c r="C319" s="5"/>
@@ -8653,7 +8672,7 @@
       <c r="K319" s="6"/>
       <c r="L319" s="6"/>
     </row>
-    <row r="320" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A320" s="5"/>
       <c r="B320" s="5"/>
       <c r="C320" s="5"/>
@@ -8667,7 +8686,7 @@
       <c r="K320" s="6"/>
       <c r="L320" s="6"/>
     </row>
-    <row r="321" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A321" s="5"/>
       <c r="B321" s="5"/>
       <c r="C321" s="5"/>
@@ -8681,7 +8700,7 @@
       <c r="K321" s="6"/>
       <c r="L321" s="6"/>
     </row>
-    <row r="322" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A322" s="5"/>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
@@ -8695,7 +8714,7 @@
       <c r="K322" s="6"/>
       <c r="L322" s="6"/>
     </row>
-    <row r="323" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A323" s="5"/>
       <c r="B323" s="5"/>
       <c r="C323" s="5"/>
@@ -8709,7 +8728,7 @@
       <c r="K323" s="6"/>
       <c r="L323" s="6"/>
     </row>
-    <row r="324" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A324" s="5"/>
       <c r="B324" s="5"/>
       <c r="C324" s="5"/>
@@ -8723,7 +8742,7 @@
       <c r="K324" s="6"/>
       <c r="L324" s="6"/>
     </row>
-    <row r="325" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A325" s="5"/>
       <c r="B325" s="5"/>
       <c r="C325" s="5"/>
@@ -8737,7 +8756,7 @@
       <c r="K325" s="6"/>
       <c r="L325" s="6"/>
     </row>
-    <row r="326" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A326" s="5"/>
       <c r="B326" s="5"/>
       <c r="C326" s="5"/>
@@ -8751,7 +8770,7 @@
       <c r="K326" s="6"/>
       <c r="L326" s="6"/>
     </row>
-    <row r="327" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A327" s="5"/>
       <c r="B327" s="5"/>
       <c r="C327" s="5"/>
@@ -8765,7 +8784,7 @@
       <c r="K327" s="6"/>
       <c r="L327" s="6"/>
     </row>
-    <row r="328" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A328" s="5"/>
       <c r="B328" s="5"/>
       <c r="C328" s="5"/>
@@ -8779,7 +8798,7 @@
       <c r="K328" s="6"/>
       <c r="L328" s="6"/>
     </row>
-    <row r="329" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A329" s="5"/>
       <c r="B329" s="5"/>
       <c r="C329" s="5"/>
@@ -8793,7 +8812,7 @@
       <c r="K329" s="6"/>
       <c r="L329" s="6"/>
     </row>
-    <row r="330" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A330" s="5"/>
       <c r="B330" s="5"/>
       <c r="C330" s="5"/>
@@ -8807,7 +8826,7 @@
       <c r="K330" s="6"/>
       <c r="L330" s="6"/>
     </row>
-    <row r="331" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A331" s="5"/>
       <c r="B331" s="5"/>
       <c r="C331" s="5"/>
@@ -8821,7 +8840,7 @@
       <c r="K331" s="6"/>
       <c r="L331" s="6"/>
     </row>
-    <row r="332" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A332" s="5"/>
       <c r="B332" s="5"/>
       <c r="C332" s="5"/>
@@ -8835,7 +8854,7 @@
       <c r="K332" s="6"/>
       <c r="L332" s="6"/>
     </row>
-    <row r="333" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A333" s="5"/>
       <c r="B333" s="5"/>
       <c r="C333" s="5"/>
@@ -8849,7 +8868,7 @@
       <c r="K333" s="6"/>
       <c r="L333" s="6"/>
     </row>
-    <row r="334" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A334" s="5"/>
       <c r="B334" s="5"/>
       <c r="C334" s="5"/>
@@ -8863,7 +8882,7 @@
       <c r="K334" s="6"/>
       <c r="L334" s="6"/>
     </row>
-    <row r="335" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A335" s="5"/>
       <c r="B335" s="5"/>
       <c r="C335" s="5"/>
@@ -8877,7 +8896,7 @@
       <c r="K335" s="6"/>
       <c r="L335" s="6"/>
     </row>
-    <row r="336" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A336" s="5"/>
       <c r="B336" s="5"/>
       <c r="C336" s="5"/>
@@ -8891,7 +8910,7 @@
       <c r="K336" s="6"/>
       <c r="L336" s="6"/>
     </row>
-    <row r="337" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A337" s="5"/>
       <c r="B337" s="5"/>
       <c r="C337" s="5"/>
@@ -8905,7 +8924,7 @@
       <c r="K337" s="6"/>
       <c r="L337" s="6"/>
     </row>
-    <row r="338" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A338" s="5"/>
       <c r="B338" s="5"/>
       <c r="C338" s="5"/>
@@ -8919,7 +8938,7 @@
       <c r="K338" s="6"/>
       <c r="L338" s="6"/>
     </row>
-    <row r="339" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A339" s="5"/>
       <c r="B339" s="5"/>
       <c r="C339" s="5"/>
@@ -8933,7 +8952,7 @@
       <c r="K339" s="6"/>
       <c r="L339" s="6"/>
     </row>
-    <row r="340" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A340" s="5"/>
       <c r="B340" s="5"/>
       <c r="C340" s="5"/>
@@ -8947,7 +8966,7 @@
       <c r="K340" s="6"/>
       <c r="L340" s="6"/>
     </row>
-    <row r="341" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A341" s="5"/>
       <c r="B341" s="5"/>
       <c r="C341" s="5"/>
@@ -8961,7 +8980,7 @@
       <c r="K341" s="6"/>
       <c r="L341" s="6"/>
     </row>
-    <row r="342" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A342" s="5"/>
       <c r="B342" s="5"/>
       <c r="C342" s="5"/>
@@ -8975,7 +8994,7 @@
       <c r="K342" s="6"/>
       <c r="L342" s="6"/>
     </row>
-    <row r="343" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A343" s="5"/>
       <c r="B343" s="5"/>
       <c r="C343" s="5"/>
@@ -8989,7 +9008,7 @@
       <c r="K343" s="6"/>
       <c r="L343" s="6"/>
     </row>
-    <row r="344" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A344" s="5"/>
       <c r="B344" s="5"/>
       <c r="C344" s="5"/>
@@ -9003,7 +9022,7 @@
       <c r="K344" s="6"/>
       <c r="L344" s="6"/>
     </row>
-    <row r="345" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A345" s="5"/>
       <c r="B345" s="5"/>
       <c r="C345" s="5"/>
@@ -9017,7 +9036,7 @@
       <c r="K345" s="6"/>
       <c r="L345" s="6"/>
     </row>
-    <row r="346" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A346" s="5"/>
       <c r="B346" s="5"/>
       <c r="C346" s="5"/>
@@ -9031,7 +9050,7 @@
       <c r="K346" s="6"/>
       <c r="L346" s="6"/>
     </row>
-    <row r="347" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A347" s="5"/>
       <c r="B347" s="5"/>
       <c r="C347" s="5"/>
@@ -9045,7 +9064,7 @@
       <c r="K347" s="6"/>
       <c r="L347" s="6"/>
     </row>
-    <row r="348" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A348" s="5"/>
       <c r="B348" s="5"/>
       <c r="C348" s="5"/>
@@ -9059,7 +9078,7 @@
       <c r="K348" s="6"/>
       <c r="L348" s="6"/>
     </row>
-    <row r="349" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A349" s="5"/>
       <c r="B349" s="5"/>
       <c r="C349" s="5"/>
@@ -9073,7 +9092,7 @@
       <c r="K349" s="6"/>
       <c r="L349" s="6"/>
     </row>
-    <row r="350" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A350" s="5"/>
       <c r="B350" s="5"/>
       <c r="C350" s="5"/>
@@ -9087,7 +9106,7 @@
       <c r="K350" s="6"/>
       <c r="L350" s="6"/>
     </row>
-    <row r="351" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A351" s="5"/>
       <c r="B351" s="5"/>
       <c r="C351" s="5"/>
@@ -9101,7 +9120,7 @@
       <c r="K351" s="6"/>
       <c r="L351" s="6"/>
     </row>
-    <row r="352" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A352" s="5"/>
       <c r="B352" s="5"/>
       <c r="C352" s="5"/>
@@ -9115,7 +9134,7 @@
       <c r="K352" s="6"/>
       <c r="L352" s="6"/>
     </row>
-    <row r="353" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A353" s="5"/>
       <c r="B353" s="5"/>
       <c r="C353" s="5"/>
@@ -9129,7 +9148,7 @@
       <c r="K353" s="6"/>
       <c r="L353" s="6"/>
     </row>
-    <row r="354" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A354" s="5"/>
       <c r="B354" s="5"/>
       <c r="C354" s="5"/>
@@ -9143,7 +9162,7 @@
       <c r="K354" s="6"/>
       <c r="L354" s="6"/>
     </row>
-    <row r="355" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A355" s="5"/>
       <c r="B355" s="5"/>
       <c r="C355" s="5"/>
@@ -9157,7 +9176,7 @@
       <c r="K355" s="6"/>
       <c r="L355" s="6"/>
     </row>
-    <row r="356" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A356" s="5"/>
       <c r="B356" s="5"/>
       <c r="C356" s="5"/>
@@ -9171,7 +9190,7 @@
       <c r="K356" s="6"/>
       <c r="L356" s="6"/>
     </row>
-    <row r="357" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A357" s="5"/>
       <c r="B357" s="5"/>
       <c r="C357" s="5"/>
@@ -9185,7 +9204,7 @@
       <c r="K357" s="6"/>
       <c r="L357" s="6"/>
     </row>
-    <row r="358" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A358" s="5"/>
       <c r="B358" s="5"/>
       <c r="C358" s="5"/>
@@ -9199,7 +9218,7 @@
       <c r="K358" s="6"/>
       <c r="L358" s="6"/>
     </row>
-    <row r="359" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A359" s="5"/>
       <c r="B359" s="5"/>
       <c r="C359" s="5"/>
@@ -9213,7 +9232,7 @@
       <c r="K359" s="6"/>
       <c r="L359" s="6"/>
     </row>
-    <row r="360" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A360" s="5"/>
       <c r="B360" s="5"/>
       <c r="C360" s="5"/>
@@ -9227,7 +9246,7 @@
       <c r="K360" s="6"/>
       <c r="L360" s="6"/>
     </row>
-    <row r="361" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A361" s="5"/>
       <c r="B361" s="5"/>
       <c r="C361" s="5"/>
@@ -9241,7 +9260,7 @@
       <c r="K361" s="6"/>
       <c r="L361" s="6"/>
     </row>
-    <row r="362" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A362" s="5"/>
       <c r="B362" s="5"/>
       <c r="C362" s="5"/>
@@ -9255,7 +9274,7 @@
       <c r="K362" s="6"/>
       <c r="L362" s="6"/>
     </row>
-    <row r="363" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A363" s="5"/>
       <c r="B363" s="5"/>
       <c r="C363" s="5"/>
@@ -9269,7 +9288,7 @@
       <c r="K363" s="6"/>
       <c r="L363" s="6"/>
     </row>
-    <row r="364" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A364" s="5"/>
       <c r="B364" s="5"/>
       <c r="C364" s="5"/>
@@ -9283,7 +9302,7 @@
       <c r="K364" s="6"/>
       <c r="L364" s="6"/>
     </row>
-    <row r="365" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A365" s="5"/>
       <c r="B365" s="5"/>
       <c r="C365" s="5"/>
@@ -9297,7 +9316,7 @@
       <c r="K365" s="6"/>
       <c r="L365" s="6"/>
     </row>
-    <row r="366" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A366" s="5"/>
       <c r="B366" s="5"/>
       <c r="C366" s="5"/>
@@ -9311,7 +9330,7 @@
       <c r="K366" s="6"/>
       <c r="L366" s="6"/>
     </row>
-    <row r="367" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A367" s="5"/>
       <c r="B367" s="5"/>
       <c r="C367" s="5"/>
@@ -9325,7 +9344,7 @@
       <c r="K367" s="6"/>
       <c r="L367" s="6"/>
     </row>
-    <row r="368" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A368" s="5"/>
       <c r="B368" s="5"/>
       <c r="C368" s="5"/>
@@ -9339,7 +9358,7 @@
       <c r="K368" s="6"/>
       <c r="L368" s="6"/>
     </row>
-    <row r="369" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A369" s="5"/>
       <c r="B369" s="5"/>
       <c r="C369" s="5"/>
@@ -9353,7 +9372,7 @@
       <c r="K369" s="6"/>
       <c r="L369" s="6"/>
     </row>
-    <row r="370" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A370" s="5"/>
       <c r="B370" s="5"/>
       <c r="C370" s="5"/>
@@ -9367,7 +9386,7 @@
       <c r="K370" s="6"/>
       <c r="L370" s="6"/>
     </row>
-    <row r="371" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A371" s="5"/>
       <c r="B371" s="5"/>
       <c r="C371" s="5"/>
@@ -9381,7 +9400,7 @@
       <c r="K371" s="6"/>
       <c r="L371" s="6"/>
     </row>
-    <row r="372" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A372" s="5"/>
       <c r="B372" s="5"/>
       <c r="C372" s="5"/>
@@ -9395,7 +9414,7 @@
       <c r="K372" s="6"/>
       <c r="L372" s="6"/>
     </row>
-    <row r="373" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A373" s="5"/>
       <c r="B373" s="5"/>
       <c r="C373" s="5"/>
@@ -9409,7 +9428,7 @@
       <c r="K373" s="6"/>
       <c r="L373" s="6"/>
     </row>
-    <row r="374" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A374" s="5"/>
       <c r="B374" s="5"/>
       <c r="C374" s="5"/>
@@ -9423,7 +9442,7 @@
       <c r="K374" s="6"/>
       <c r="L374" s="6"/>
     </row>
-    <row r="375" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A375" s="5"/>
       <c r="B375" s="5"/>
       <c r="C375" s="5"/>
@@ -9437,7 +9456,7 @@
       <c r="K375" s="6"/>
       <c r="L375" s="6"/>
     </row>
-    <row r="376" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A376" s="5"/>
       <c r="B376" s="5"/>
       <c r="C376" s="5"/>
@@ -9451,7 +9470,7 @@
       <c r="K376" s="6"/>
       <c r="L376" s="6"/>
     </row>
-    <row r="377" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A377" s="5"/>
       <c r="B377" s="5"/>
       <c r="C377" s="5"/>
@@ -9465,7 +9484,7 @@
       <c r="K377" s="6"/>
       <c r="L377" s="6"/>
     </row>
-    <row r="378" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A378" s="5"/>
       <c r="B378" s="5"/>
       <c r="C378" s="5"/>
@@ -9479,7 +9498,7 @@
       <c r="K378" s="6"/>
       <c r="L378" s="6"/>
     </row>
-    <row r="379" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A379" s="5"/>
       <c r="B379" s="5"/>
       <c r="C379" s="5"/>
@@ -9493,7 +9512,7 @@
       <c r="K379" s="6"/>
       <c r="L379" s="6"/>
     </row>
-    <row r="380" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A380" s="5"/>
       <c r="B380" s="5"/>
       <c r="C380" s="5"/>
@@ -9507,7 +9526,7 @@
       <c r="K380" s="6"/>
       <c r="L380" s="6"/>
     </row>
-    <row r="381" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A381" s="5"/>
       <c r="B381" s="5"/>
       <c r="C381" s="5"/>
@@ -9521,7 +9540,7 @@
       <c r="K381" s="6"/>
       <c r="L381" s="6"/>
     </row>
-    <row r="382" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A382" s="5"/>
       <c r="B382" s="5"/>
       <c r="C382" s="5"/>
@@ -9535,7 +9554,7 @@
       <c r="K382" s="6"/>
       <c r="L382" s="6"/>
     </row>
-    <row r="383" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A383" s="5"/>
       <c r="B383" s="5"/>
       <c r="C383" s="5"/>
@@ -9549,7 +9568,7 @@
       <c r="K383" s="6"/>
       <c r="L383" s="6"/>
     </row>
-    <row r="384" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A384" s="5"/>
       <c r="B384" s="5"/>
       <c r="C384" s="5"/>
@@ -9563,7 +9582,7 @@
       <c r="K384" s="6"/>
       <c r="L384" s="6"/>
     </row>
-    <row r="385" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A385" s="5"/>
       <c r="B385" s="5"/>
       <c r="C385" s="5"/>
@@ -9577,7 +9596,7 @@
       <c r="K385" s="6"/>
       <c r="L385" s="6"/>
     </row>
-    <row r="386" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A386" s="5"/>
       <c r="B386" s="5"/>
       <c r="C386" s="5"/>
@@ -9591,7 +9610,7 @@
       <c r="K386" s="6"/>
       <c r="L386" s="6"/>
     </row>
-    <row r="387" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A387" s="5"/>
       <c r="B387" s="5"/>
       <c r="C387" s="5"/>
@@ -9605,7 +9624,7 @@
       <c r="K387" s="6"/>
       <c r="L387" s="6"/>
     </row>
-    <row r="388" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A388" s="5"/>
       <c r="B388" s="5"/>
       <c r="C388" s="5"/>
@@ -9619,7 +9638,7 @@
       <c r="K388" s="6"/>
       <c r="L388" s="6"/>
     </row>
-    <row r="389" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A389" s="5"/>
       <c r="B389" s="5"/>
       <c r="C389" s="5"/>
@@ -9633,7 +9652,7 @@
       <c r="K389" s="6"/>
       <c r="L389" s="6"/>
     </row>
-    <row r="390" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A390" s="5"/>
       <c r="B390" s="5"/>
       <c r="C390" s="5"/>
@@ -9647,7 +9666,7 @@
       <c r="K390" s="6"/>
       <c r="L390" s="6"/>
     </row>
-    <row r="391" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A391" s="5"/>
       <c r="B391" s="5"/>
       <c r="C391" s="5"/>
@@ -9661,7 +9680,7 @@
       <c r="K391" s="6"/>
       <c r="L391" s="6"/>
     </row>
-    <row r="392" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A392" s="5"/>
       <c r="B392" s="5"/>
       <c r="C392" s="5"/>
@@ -9675,7 +9694,7 @@
       <c r="K392" s="6"/>
       <c r="L392" s="6"/>
     </row>
-    <row r="393" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A393" s="5"/>
       <c r="B393" s="5"/>
       <c r="C393" s="5"/>
@@ -9689,7 +9708,7 @@
       <c r="K393" s="6"/>
       <c r="L393" s="6"/>
     </row>
-    <row r="394" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A394" s="5"/>
       <c r="B394" s="5"/>
       <c r="C394" s="5"/>
@@ -9703,7 +9722,7 @@
       <c r="K394" s="6"/>
       <c r="L394" s="6"/>
     </row>
-    <row r="395" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A395" s="5"/>
       <c r="B395" s="5"/>
       <c r="C395" s="5"/>
@@ -9717,7 +9736,7 @@
       <c r="K395" s="6"/>
       <c r="L395" s="6"/>
     </row>
-    <row r="396" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A396" s="5"/>
       <c r="B396" s="5"/>
       <c r="C396" s="5"/>
@@ -9731,7 +9750,7 @@
       <c r="K396" s="6"/>
       <c r="L396" s="6"/>
     </row>
-    <row r="397" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A397" s="5"/>
       <c r="B397" s="5"/>
       <c r="C397" s="5"/>
@@ -9745,7 +9764,7 @@
       <c r="K397" s="6"/>
       <c r="L397" s="6"/>
     </row>
-    <row r="398" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A398" s="5"/>
       <c r="B398" s="5"/>
       <c r="C398" s="5"/>
@@ -9759,7 +9778,7 @@
       <c r="K398" s="6"/>
       <c r="L398" s="6"/>
     </row>
-    <row r="399" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A399" s="5"/>
       <c r="B399" s="5"/>
       <c r="C399" s="5"/>
@@ -9773,7 +9792,7 @@
       <c r="K399" s="6"/>
       <c r="L399" s="6"/>
     </row>
-    <row r="400" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A400" s="5"/>
       <c r="B400" s="5"/>
       <c r="C400" s="5"/>
@@ -9787,7 +9806,7 @@
       <c r="K400" s="6"/>
       <c r="L400" s="6"/>
     </row>
-    <row r="401" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A401" s="5"/>
       <c r="B401" s="5"/>
       <c r="C401" s="5"/>
@@ -9801,7 +9820,7 @@
       <c r="K401" s="6"/>
       <c r="L401" s="6"/>
     </row>
-    <row r="402" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A402" s="5"/>
       <c r="B402" s="5"/>
       <c r="C402" s="5"/>
@@ -9815,7 +9834,7 @@
       <c r="K402" s="6"/>
       <c r="L402" s="6"/>
     </row>
-    <row r="403" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A403" s="5"/>
       <c r="B403" s="5"/>
       <c r="C403" s="5"/>
@@ -9829,7 +9848,7 @@
       <c r="K403" s="6"/>
       <c r="L403" s="6"/>
     </row>
-    <row r="404" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A404" s="5"/>
       <c r="B404" s="5"/>
       <c r="C404" s="5"/>
@@ -9843,7 +9862,7 @@
       <c r="K404" s="6"/>
       <c r="L404" s="6"/>
     </row>
-    <row r="405" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A405" s="5"/>
       <c r="B405" s="5"/>
       <c r="C405" s="5"/>
@@ -9857,7 +9876,7 @@
       <c r="K405" s="6"/>
       <c r="L405" s="6"/>
     </row>
-    <row r="406" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A406" s="5"/>
       <c r="B406" s="5"/>
       <c r="C406" s="5"/>
@@ -9871,7 +9890,7 @@
       <c r="K406" s="6"/>
       <c r="L406" s="6"/>
     </row>
-    <row r="407" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A407" s="5"/>
       <c r="B407" s="5"/>
       <c r="C407" s="5"/>
@@ -9885,7 +9904,7 @@
       <c r="K407" s="6"/>
       <c r="L407" s="6"/>
     </row>
-    <row r="408" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A408" s="5"/>
       <c r="B408" s="5"/>
       <c r="C408" s="5"/>
@@ -9899,7 +9918,7 @@
       <c r="K408" s="6"/>
       <c r="L408" s="6"/>
     </row>
-    <row r="409" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A409" s="5"/>
       <c r="B409" s="5"/>
       <c r="C409" s="5"/>
@@ -9913,7 +9932,7 @@
       <c r="K409" s="6"/>
       <c r="L409" s="6"/>
     </row>
-    <row r="410" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A410" s="5"/>
       <c r="B410" s="5"/>
       <c r="C410" s="5"/>
@@ -9927,7 +9946,7 @@
       <c r="K410" s="6"/>
       <c r="L410" s="6"/>
     </row>
-    <row r="411" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A411" s="5"/>
       <c r="B411" s="5"/>
       <c r="C411" s="5"/>
@@ -9941,7 +9960,7 @@
       <c r="K411" s="6"/>
       <c r="L411" s="6"/>
     </row>
-    <row r="412" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A412" s="5"/>
       <c r="B412" s="5"/>
       <c r="C412" s="5"/>
@@ -9955,7 +9974,7 @@
       <c r="K412" s="6"/>
       <c r="L412" s="6"/>
     </row>
-    <row r="413" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A413" s="5"/>
       <c r="B413" s="5"/>
       <c r="C413" s="5"/>
@@ -9969,7 +9988,7 @@
       <c r="K413" s="6"/>
       <c r="L413" s="6"/>
     </row>
-    <row r="414" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A414" s="5"/>
       <c r="B414" s="5"/>
       <c r="C414" s="5"/>
@@ -9983,7 +10002,7 @@
       <c r="K414" s="6"/>
       <c r="L414" s="6"/>
     </row>
-    <row r="415" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A415" s="5"/>
       <c r="B415" s="5"/>
       <c r="C415" s="5"/>
@@ -9997,7 +10016,7 @@
       <c r="K415" s="6"/>
       <c r="L415" s="6"/>
     </row>
-    <row r="416" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A416" s="5"/>
       <c r="B416" s="5"/>
       <c r="C416" s="5"/>
@@ -10011,7 +10030,7 @@
       <c r="K416" s="6"/>
       <c r="L416" s="6"/>
     </row>
-    <row r="417" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A417" s="5"/>
       <c r="B417" s="5"/>
       <c r="C417" s="5"/>
@@ -10025,7 +10044,7 @@
       <c r="K417" s="6"/>
       <c r="L417" s="6"/>
     </row>
-    <row r="418" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A418" s="5"/>
       <c r="B418" s="5"/>
       <c r="C418" s="5"/>
@@ -10039,7 +10058,7 @@
       <c r="K418" s="6"/>
       <c r="L418" s="6"/>
     </row>
-    <row r="419" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A419" s="5"/>
       <c r="B419" s="5"/>
       <c r="C419" s="5"/>
@@ -10053,7 +10072,7 @@
       <c r="K419" s="6"/>
       <c r="L419" s="6"/>
     </row>
-    <row r="420" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A420" s="5"/>
       <c r="B420" s="5"/>
       <c r="C420" s="5"/>
@@ -10067,7 +10086,7 @@
       <c r="K420" s="6"/>
       <c r="L420" s="6"/>
     </row>
-    <row r="421" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A421" s="5"/>
       <c r="B421" s="5"/>
       <c r="C421" s="5"/>
@@ -10081,7 +10100,7 @@
       <c r="K421" s="6"/>
       <c r="L421" s="6"/>
     </row>
-    <row r="422" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A422" s="5"/>
       <c r="B422" s="5"/>
       <c r="C422" s="5"/>
@@ -10095,7 +10114,7 @@
       <c r="K422" s="6"/>
       <c r="L422" s="6"/>
     </row>
-    <row r="423" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A423" s="5"/>
       <c r="B423" s="5"/>
       <c r="C423" s="5"/>
@@ -10109,7 +10128,7 @@
       <c r="K423" s="6"/>
       <c r="L423" s="6"/>
     </row>
-    <row r="424" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A424" s="5"/>
       <c r="B424" s="5"/>
       <c r="C424" s="5"/>
@@ -10123,7 +10142,7 @@
       <c r="K424" s="6"/>
       <c r="L424" s="6"/>
     </row>
-    <row r="425" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A425" s="5"/>
       <c r="B425" s="5"/>
       <c r="C425" s="5"/>
@@ -10137,7 +10156,7 @@
       <c r="K425" s="6"/>
       <c r="L425" s="6"/>
     </row>
-    <row r="426" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A426" s="5"/>
       <c r="B426" s="5"/>
       <c r="C426" s="5"/>
@@ -10151,7 +10170,7 @@
       <c r="K426" s="6"/>
       <c r="L426" s="6"/>
     </row>
-    <row r="427" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A427" s="5"/>
       <c r="B427" s="5"/>
       <c r="C427" s="5"/>
@@ -10165,7 +10184,7 @@
       <c r="K427" s="6"/>
       <c r="L427" s="6"/>
     </row>
-    <row r="428" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A428" s="5"/>
       <c r="B428" s="5"/>
       <c r="C428" s="5"/>
@@ -10179,7 +10198,7 @@
       <c r="K428" s="6"/>
       <c r="L428" s="6"/>
     </row>
-    <row r="429" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A429" s="5"/>
       <c r="B429" s="5"/>
       <c r="C429" s="5"/>
@@ -10193,7 +10212,7 @@
       <c r="K429" s="6"/>
       <c r="L429" s="6"/>
     </row>
-    <row r="430" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A430" s="5"/>
       <c r="B430" s="5"/>
       <c r="C430" s="5"/>
@@ -10207,7 +10226,7 @@
       <c r="K430" s="6"/>
       <c r="L430" s="6"/>
     </row>
-    <row r="431" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A431" s="5"/>
       <c r="B431" s="5"/>
       <c r="C431" s="5"/>
@@ -10221,7 +10240,7 @@
       <c r="K431" s="6"/>
       <c r="L431" s="6"/>
     </row>
-    <row r="432" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A432" s="5"/>
       <c r="B432" s="5"/>
       <c r="C432" s="5"/>
@@ -10235,7 +10254,7 @@
       <c r="K432" s="6"/>
       <c r="L432" s="6"/>
     </row>
-    <row r="433" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A433" s="5"/>
       <c r="B433" s="5"/>
       <c r="C433" s="5"/>
@@ -10249,7 +10268,7 @@
       <c r="K433" s="6"/>
       <c r="L433" s="6"/>
     </row>
-    <row r="434" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A434" s="5"/>
       <c r="B434" s="5"/>
       <c r="C434" s="5"/>
@@ -10263,7 +10282,7 @@
       <c r="K434" s="6"/>
       <c r="L434" s="6"/>
     </row>
-    <row r="435" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A435" s="5"/>
       <c r="B435" s="5"/>
       <c r="C435" s="5"/>
@@ -10277,7 +10296,7 @@
       <c r="K435" s="6"/>
       <c r="L435" s="6"/>
     </row>
-    <row r="436" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A436" s="5"/>
       <c r="B436" s="5"/>
       <c r="C436" s="5"/>
@@ -10291,7 +10310,7 @@
       <c r="K436" s="6"/>
       <c r="L436" s="6"/>
     </row>
-    <row r="437" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A437" s="5"/>
       <c r="B437" s="5"/>
       <c r="C437" s="5"/>
@@ -10305,7 +10324,7 @@
       <c r="K437" s="6"/>
       <c r="L437" s="6"/>
     </row>
-    <row r="438" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A438" s="5"/>
       <c r="B438" s="5"/>
       <c r="C438" s="5"/>
@@ -10319,7 +10338,7 @@
       <c r="K438" s="6"/>
       <c r="L438" s="6"/>
     </row>
-    <row r="439" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A439" s="5"/>
       <c r="B439" s="5"/>
       <c r="C439" s="5"/>
@@ -10333,7 +10352,7 @@
       <c r="K439" s="6"/>
       <c r="L439" s="6"/>
     </row>
-    <row r="440" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A440" s="5"/>
       <c r="B440" s="5"/>
       <c r="C440" s="5"/>
@@ -10347,7 +10366,7 @@
       <c r="K440" s="6"/>
       <c r="L440" s="6"/>
     </row>
-    <row r="441" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A441" s="5"/>
       <c r="B441" s="5"/>
       <c r="C441" s="5"/>
@@ -10361,7 +10380,7 @@
       <c r="K441" s="6"/>
       <c r="L441" s="6"/>
     </row>
-    <row r="442" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A442" s="5"/>
       <c r="B442" s="5"/>
       <c r="C442" s="5"/>
@@ -10375,7 +10394,7 @@
       <c r="K442" s="6"/>
       <c r="L442" s="6"/>
     </row>
-    <row r="443" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A443" s="5"/>
       <c r="B443" s="5"/>
       <c r="C443" s="5"/>
@@ -10389,7 +10408,7 @@
       <c r="K443" s="6"/>
       <c r="L443" s="6"/>
     </row>
-    <row r="444" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A444" s="5"/>
       <c r="B444" s="5"/>
       <c r="C444" s="5"/>
@@ -10403,7 +10422,7 @@
       <c r="K444" s="6"/>
       <c r="L444" s="6"/>
     </row>
-    <row r="445" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A445" s="5"/>
       <c r="B445" s="5"/>
       <c r="C445" s="5"/>
@@ -10417,7 +10436,7 @@
       <c r="K445" s="6"/>
       <c r="L445" s="6"/>
     </row>
-    <row r="446" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A446" s="5"/>
       <c r="B446" s="5"/>
       <c r="C446" s="5"/>
@@ -10431,7 +10450,7 @@
       <c r="K446" s="6"/>
       <c r="L446" s="6"/>
     </row>
-    <row r="447" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A447" s="5"/>
       <c r="B447" s="5"/>
       <c r="C447" s="5"/>
@@ -10445,7 +10464,7 @@
       <c r="K447" s="6"/>
       <c r="L447" s="6"/>
     </row>
-    <row r="448" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A448" s="5"/>
       <c r="B448" s="5"/>
       <c r="C448" s="5"/>
@@ -10459,7 +10478,7 @@
       <c r="K448" s="6"/>
       <c r="L448" s="6"/>
     </row>
-    <row r="449" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A449" s="5"/>
       <c r="B449" s="5"/>
       <c r="C449" s="5"/>
@@ -10473,7 +10492,7 @@
       <c r="K449" s="6"/>
       <c r="L449" s="6"/>
     </row>
-    <row r="450" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A450" s="5"/>
       <c r="B450" s="5"/>
       <c r="C450" s="5"/>
@@ -10487,7 +10506,7 @@
       <c r="K450" s="6"/>
       <c r="L450" s="6"/>
     </row>
-    <row r="451" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A451" s="5"/>
       <c r="B451" s="5"/>
       <c r="C451" s="5"/>
@@ -10501,7 +10520,7 @@
       <c r="K451" s="6"/>
       <c r="L451" s="6"/>
     </row>
-    <row r="452" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A452" s="5"/>
       <c r="B452" s="5"/>
       <c r="C452" s="5"/>
@@ -10515,7 +10534,7 @@
       <c r="K452" s="6"/>
       <c r="L452" s="6"/>
     </row>
-    <row r="453" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A453" s="5"/>
       <c r="B453" s="5"/>
       <c r="C453" s="5"/>
@@ -10529,7 +10548,7 @@
       <c r="K453" s="6"/>
       <c r="L453" s="6"/>
     </row>
-    <row r="454" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A454" s="5"/>
       <c r="B454" s="5"/>
       <c r="C454" s="5"/>
@@ -10543,7 +10562,7 @@
       <c r="K454" s="6"/>
       <c r="L454" s="6"/>
     </row>
-    <row r="455" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A455" s="5"/>
       <c r="B455" s="5"/>
       <c r="C455" s="5"/>
@@ -10557,7 +10576,7 @@
       <c r="K455" s="6"/>
       <c r="L455" s="6"/>
     </row>
-    <row r="456" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A456" s="5"/>
       <c r="B456" s="5"/>
       <c r="C456" s="5"/>
@@ -10571,7 +10590,7 @@
       <c r="K456" s="6"/>
       <c r="L456" s="6"/>
     </row>
-    <row r="457" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A457" s="5"/>
       <c r="B457" s="5"/>
       <c r="C457" s="5"/>
@@ -10585,7 +10604,7 @@
       <c r="K457" s="6"/>
       <c r="L457" s="6"/>
     </row>
-    <row r="458" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A458" s="5"/>
       <c r="B458" s="5"/>
       <c r="C458" s="5"/>
@@ -10599,7 +10618,7 @@
       <c r="K458" s="6"/>
       <c r="L458" s="6"/>
     </row>
-    <row r="459" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A459" s="5"/>
       <c r="B459" s="5"/>
       <c r="C459" s="5"/>
@@ -10613,7 +10632,7 @@
       <c r="K459" s="6"/>
       <c r="L459" s="6"/>
     </row>
-    <row r="460" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A460" s="5"/>
       <c r="B460" s="5"/>
       <c r="C460" s="5"/>
@@ -10627,7 +10646,7 @@
       <c r="K460" s="6"/>
       <c r="L460" s="6"/>
     </row>
-    <row r="461" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A461" s="5"/>
       <c r="B461" s="5"/>
       <c r="C461" s="5"/>
@@ -10641,7 +10660,7 @@
       <c r="K461" s="6"/>
       <c r="L461" s="6"/>
     </row>
-    <row r="462" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A462" s="5"/>
       <c r="B462" s="5"/>
       <c r="C462" s="5"/>
@@ -10655,7 +10674,7 @@
       <c r="K462" s="6"/>
       <c r="L462" s="6"/>
     </row>
-    <row r="463" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A463" s="5"/>
       <c r="B463" s="5"/>
       <c r="C463" s="5"/>
@@ -10669,7 +10688,7 @@
       <c r="K463" s="6"/>
       <c r="L463" s="6"/>
     </row>
-    <row r="464" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A464" s="5"/>
       <c r="B464" s="5"/>
       <c r="C464" s="5"/>
@@ -10683,7 +10702,7 @@
       <c r="K464" s="6"/>
       <c r="L464" s="6"/>
     </row>
-    <row r="465" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A465" s="5"/>
       <c r="B465" s="5"/>
       <c r="C465" s="5"/>
@@ -10697,7 +10716,7 @@
       <c r="K465" s="6"/>
       <c r="L465" s="6"/>
     </row>
-    <row r="466" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A466" s="5"/>
       <c r="B466" s="5"/>
       <c r="C466" s="5"/>
@@ -10711,7 +10730,7 @@
       <c r="K466" s="6"/>
       <c r="L466" s="6"/>
     </row>
-    <row r="467" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A467" s="5"/>
       <c r="B467" s="5"/>
       <c r="C467" s="5"/>
@@ -10725,7 +10744,7 @@
       <c r="K467" s="6"/>
       <c r="L467" s="6"/>
     </row>
-    <row r="468" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A468" s="5"/>
       <c r="B468" s="5"/>
       <c r="C468" s="5"/>
@@ -10739,7 +10758,7 @@
       <c r="K468" s="6"/>
       <c r="L468" s="6"/>
     </row>
-    <row r="469" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A469" s="5"/>
       <c r="B469" s="5"/>
       <c r="C469" s="5"/>
@@ -10753,7 +10772,7 @@
       <c r="K469" s="6"/>
       <c r="L469" s="6"/>
     </row>
-    <row r="470" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A470" s="5"/>
       <c r="B470" s="5"/>
       <c r="C470" s="5"/>
@@ -10767,7 +10786,7 @@
       <c r="K470" s="6"/>
       <c r="L470" s="6"/>
     </row>
-    <row r="471" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A471" s="5"/>
       <c r="B471" s="5"/>
       <c r="C471" s="5"/>
@@ -10781,7 +10800,7 @@
       <c r="K471" s="6"/>
       <c r="L471" s="6"/>
     </row>
-    <row r="472" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A472" s="5"/>
       <c r="B472" s="5"/>
       <c r="C472" s="5"/>
@@ -10795,7 +10814,7 @@
       <c r="K472" s="6"/>
       <c r="L472" s="6"/>
     </row>
-    <row r="473" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A473" s="5"/>
       <c r="B473" s="5"/>
       <c r="C473" s="5"/>
@@ -10809,7 +10828,7 @@
       <c r="K473" s="6"/>
       <c r="L473" s="6"/>
     </row>
-    <row r="474" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A474" s="5"/>
       <c r="B474" s="5"/>
       <c r="C474" s="5"/>
@@ -10823,7 +10842,7 @@
       <c r="K474" s="6"/>
       <c r="L474" s="6"/>
     </row>
-    <row r="475" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A475" s="5"/>
       <c r="B475" s="5"/>
       <c r="C475" s="5"/>
@@ -10837,7 +10856,7 @@
       <c r="K475" s="6"/>
       <c r="L475" s="6"/>
     </row>
-    <row r="476" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A476" s="5"/>
       <c r="B476" s="5"/>
       <c r="C476" s="5"/>
@@ -10851,7 +10870,7 @@
       <c r="K476" s="6"/>
       <c r="L476" s="6"/>
     </row>
-    <row r="477" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A477" s="5"/>
       <c r="B477" s="5"/>
       <c r="C477" s="5"/>
@@ -10865,7 +10884,7 @@
       <c r="K477" s="6"/>
       <c r="L477" s="6"/>
     </row>
-    <row r="478" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A478" s="5"/>
       <c r="B478" s="5"/>
       <c r="C478" s="5"/>
@@ -10879,7 +10898,7 @@
       <c r="K478" s="6"/>
       <c r="L478" s="6"/>
     </row>
-    <row r="479" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A479" s="5"/>
       <c r="B479" s="5"/>
       <c r="C479" s="5"/>
@@ -10893,7 +10912,7 @@
       <c r="K479" s="6"/>
       <c r="L479" s="6"/>
     </row>
-    <row r="480" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A480" s="5"/>
       <c r="B480" s="5"/>
       <c r="C480" s="5"/>
@@ -10907,7 +10926,7 @@
       <c r="K480" s="6"/>
       <c r="L480" s="6"/>
     </row>
-    <row r="481" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A481" s="5"/>
       <c r="B481" s="5"/>
       <c r="C481" s="5"/>
@@ -10921,7 +10940,7 @@
       <c r="K481" s="6"/>
       <c r="L481" s="6"/>
     </row>
-    <row r="482" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A482" s="5"/>
       <c r="B482" s="5"/>
       <c r="C482" s="5"/>
@@ -10935,7 +10954,7 @@
       <c r="K482" s="6"/>
       <c r="L482" s="6"/>
     </row>
-    <row r="483" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A483" s="5"/>
       <c r="B483" s="5"/>
       <c r="C483" s="5"/>
@@ -10949,7 +10968,7 @@
       <c r="K483" s="6"/>
       <c r="L483" s="6"/>
     </row>
-    <row r="484" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A484" s="5"/>
       <c r="B484" s="5"/>
       <c r="C484" s="5"/>
@@ -10963,7 +10982,7 @@
       <c r="K484" s="6"/>
       <c r="L484" s="6"/>
     </row>
-    <row r="485" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A485" s="5"/>
       <c r="B485" s="5"/>
       <c r="C485" s="5"/>
@@ -10977,7 +10996,7 @@
       <c r="K485" s="6"/>
       <c r="L485" s="6"/>
     </row>
-    <row r="486" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A486" s="5"/>
       <c r="B486" s="5"/>
       <c r="C486" s="5"/>
@@ -10991,7 +11010,7 @@
       <c r="K486" s="6"/>
       <c r="L486" s="6"/>
     </row>
-    <row r="487" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A487" s="5"/>
       <c r="B487" s="5"/>
       <c r="C487" s="5"/>
@@ -11005,7 +11024,7 @@
       <c r="K487" s="6"/>
       <c r="L487" s="6"/>
     </row>
-    <row r="488" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A488" s="5"/>
       <c r="B488" s="5"/>
       <c r="C488" s="5"/>
@@ -11019,7 +11038,7 @@
       <c r="K488" s="6"/>
       <c r="L488" s="6"/>
     </row>
-    <row r="489" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A489" s="5"/>
       <c r="B489" s="5"/>
       <c r="C489" s="5"/>
@@ -11033,7 +11052,7 @@
       <c r="K489" s="6"/>
       <c r="L489" s="6"/>
     </row>
-    <row r="490" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A490" s="5"/>
       <c r="B490" s="5"/>
       <c r="C490" s="5"/>
@@ -11047,7 +11066,7 @@
       <c r="K490" s="6"/>
       <c r="L490" s="6"/>
     </row>
-    <row r="491" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A491" s="5"/>
       <c r="B491" s="5"/>
       <c r="C491" s="5"/>
@@ -11061,7 +11080,7 @@
       <c r="K491" s="6"/>
       <c r="L491" s="6"/>
     </row>
-    <row r="492" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A492" s="5"/>
       <c r="B492" s="5"/>
       <c r="C492" s="5"/>
@@ -11075,7 +11094,7 @@
       <c r="K492" s="6"/>
       <c r="L492" s="6"/>
     </row>
-    <row r="493" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A493" s="5"/>
       <c r="B493" s="5"/>
       <c r="C493" s="5"/>
@@ -11089,7 +11108,7 @@
       <c r="K493" s="6"/>
       <c r="L493" s="6"/>
     </row>
-    <row r="494" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A494" s="5"/>
       <c r="B494" s="5"/>
       <c r="C494" s="5"/>
@@ -11103,7 +11122,7 @@
       <c r="K494" s="6"/>
       <c r="L494" s="6"/>
     </row>
-    <row r="495" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A495" s="5"/>
       <c r="B495" s="5"/>
       <c r="C495" s="5"/>
@@ -11117,7 +11136,7 @@
       <c r="K495" s="6"/>
       <c r="L495" s="6"/>
     </row>
-    <row r="496" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A496" s="5"/>
       <c r="B496" s="5"/>
       <c r="C496" s="5"/>
@@ -11131,7 +11150,7 @@
       <c r="K496" s="6"/>
       <c r="L496" s="6"/>
     </row>
-    <row r="497" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A497" s="5"/>
       <c r="B497" s="5"/>
       <c r="C497" s="5"/>
@@ -11145,7 +11164,7 @@
       <c r="K497" s="6"/>
       <c r="L497" s="6"/>
     </row>
-    <row r="498" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A498" s="5"/>
       <c r="B498" s="5"/>
       <c r="C498" s="5"/>
@@ -11159,7 +11178,7 @@
       <c r="K498" s="6"/>
       <c r="L498" s="6"/>
     </row>
-    <row r="499" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A499" s="5"/>
       <c r="B499" s="5"/>
       <c r="C499" s="5"/>
@@ -11173,7 +11192,7 @@
       <c r="K499" s="6"/>
       <c r="L499" s="6"/>
     </row>
-    <row r="500" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A500" s="5"/>
       <c r="B500" s="5"/>
       <c r="C500" s="5"/>
@@ -11187,7 +11206,7 @@
       <c r="K500" s="6"/>
       <c r="L500" s="6"/>
     </row>
-    <row r="501" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A501" s="5"/>
       <c r="B501" s="5"/>
       <c r="C501" s="5"/>
@@ -11201,7 +11220,7 @@
       <c r="K501" s="6"/>
       <c r="L501" s="6"/>
     </row>
-    <row r="502" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A502" s="5"/>
       <c r="B502" s="5"/>
       <c r="C502" s="5"/>
@@ -11215,7 +11234,7 @@
       <c r="K502" s="6"/>
       <c r="L502" s="6"/>
     </row>
-    <row r="503" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A503" s="5"/>
       <c r="B503" s="5"/>
       <c r="C503" s="5"/>
@@ -11229,7 +11248,7 @@
       <c r="K503" s="6"/>
       <c r="L503" s="6"/>
     </row>
-    <row r="504" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A504" s="5"/>
       <c r="B504" s="5"/>
       <c r="C504" s="5"/>
@@ -11243,7 +11262,7 @@
       <c r="K504" s="6"/>
       <c r="L504" s="6"/>
     </row>
-    <row r="505" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A505" s="5"/>
       <c r="B505" s="5"/>
       <c r="C505" s="5"/>
@@ -11257,7 +11276,7 @@
       <c r="K505" s="6"/>
       <c r="L505" s="6"/>
     </row>
-    <row r="506" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A506" s="5"/>
       <c r="B506" s="5"/>
       <c r="C506" s="5"/>
@@ -11271,7 +11290,7 @@
       <c r="K506" s="6"/>
       <c r="L506" s="6"/>
     </row>
-    <row r="507" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A507" s="5"/>
       <c r="B507" s="5"/>
       <c r="C507" s="5"/>
@@ -11285,7 +11304,7 @@
       <c r="K507" s="6"/>
       <c r="L507" s="6"/>
     </row>
-    <row r="508" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A508" s="5"/>
       <c r="B508" s="5"/>
       <c r="C508" s="5"/>
@@ -11299,7 +11318,7 @@
       <c r="K508" s="6"/>
       <c r="L508" s="6"/>
     </row>
-    <row r="509" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A509" s="5"/>
       <c r="B509" s="5"/>
       <c r="C509" s="5"/>
@@ -11313,7 +11332,7 @@
       <c r="K509" s="6"/>
       <c r="L509" s="6"/>
     </row>
-    <row r="510" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A510" s="5"/>
       <c r="B510" s="5"/>
       <c r="C510" s="5"/>
@@ -11327,7 +11346,7 @@
       <c r="K510" s="6"/>
       <c r="L510" s="6"/>
     </row>
-    <row r="511" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A511" s="5"/>
       <c r="B511" s="5"/>
       <c r="C511" s="5"/>
@@ -11341,7 +11360,7 @@
       <c r="K511" s="6"/>
       <c r="L511" s="6"/>
     </row>
-    <row r="512" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A512" s="5"/>
       <c r="B512" s="5"/>
       <c r="C512" s="5"/>
@@ -11355,7 +11374,7 @@
       <c r="K512" s="6"/>
       <c r="L512" s="6"/>
     </row>
-    <row r="513" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A513" s="5"/>
       <c r="B513" s="5"/>
       <c r="C513" s="5"/>
@@ -11369,7 +11388,7 @@
       <c r="K513" s="6"/>
       <c r="L513" s="6"/>
     </row>
-    <row r="514" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A514" s="5"/>
       <c r="B514" s="5"/>
       <c r="C514" s="5"/>
@@ -11383,7 +11402,7 @@
       <c r="K514" s="6"/>
       <c r="L514" s="6"/>
     </row>
-    <row r="515" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A515" s="5"/>
       <c r="B515" s="5"/>
       <c r="C515" s="5"/>
@@ -11397,7 +11416,7 @@
       <c r="K515" s="6"/>
       <c r="L515" s="6"/>
     </row>
-    <row r="516" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A516" s="5"/>
       <c r="B516" s="5"/>
       <c r="C516" s="5"/>
@@ -11411,7 +11430,7 @@
       <c r="K516" s="6"/>
       <c r="L516" s="6"/>
     </row>
-    <row r="517" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A517" s="5"/>
       <c r="B517" s="5"/>
       <c r="C517" s="5"/>
@@ -11425,7 +11444,7 @@
       <c r="K517" s="6"/>
       <c r="L517" s="6"/>
     </row>
-    <row r="518" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A518" s="5"/>
       <c r="B518" s="5"/>
       <c r="C518" s="5"/>
@@ -11439,7 +11458,7 @@
       <c r="K518" s="6"/>
       <c r="L518" s="6"/>
     </row>
-    <row r="519" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A519" s="5"/>
       <c r="B519" s="5"/>
       <c r="C519" s="5"/>
@@ -11453,7 +11472,7 @@
       <c r="K519" s="6"/>
       <c r="L519" s="6"/>
     </row>
-    <row r="520" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A520" s="5"/>
       <c r="B520" s="5"/>
       <c r="C520" s="5"/>
@@ -11467,7 +11486,7 @@
       <c r="K520" s="6"/>
       <c r="L520" s="6"/>
     </row>
-    <row r="521" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A521" s="5"/>
       <c r="B521" s="5"/>
       <c r="C521" s="5"/>
@@ -11481,7 +11500,7 @@
       <c r="K521" s="6"/>
       <c r="L521" s="6"/>
     </row>
-    <row r="522" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A522" s="5"/>
       <c r="B522" s="5"/>
       <c r="C522" s="5"/>
@@ -11495,7 +11514,7 @@
       <c r="K522" s="6"/>
       <c r="L522" s="6"/>
     </row>
-    <row r="523" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A523" s="5"/>
       <c r="B523" s="5"/>
       <c r="C523" s="5"/>
@@ -11509,7 +11528,7 @@
       <c r="K523" s="6"/>
       <c r="L523" s="6"/>
     </row>
-    <row r="524" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A524" s="5"/>
       <c r="B524" s="5"/>
       <c r="C524" s="5"/>
@@ -11523,7 +11542,7 @@
       <c r="K524" s="6"/>
       <c r="L524" s="6"/>
     </row>
-    <row r="525" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A525" s="5"/>
       <c r="B525" s="5"/>
       <c r="C525" s="5"/>
@@ -11537,7 +11556,7 @@
       <c r="K525" s="6"/>
       <c r="L525" s="6"/>
     </row>
-    <row r="526" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A526" s="5"/>
       <c r="B526" s="5"/>
       <c r="C526" s="5"/>
@@ -11551,7 +11570,7 @@
       <c r="K526" s="6"/>
       <c r="L526" s="6"/>
     </row>
-    <row r="527" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A527" s="5"/>
       <c r="B527" s="5"/>
       <c r="C527" s="5"/>
@@ -11565,7 +11584,7 @@
       <c r="K527" s="6"/>
       <c r="L527" s="6"/>
     </row>
-    <row r="528" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A528" s="5"/>
       <c r="B528" s="5"/>
       <c r="C528" s="5"/>
@@ -11579,7 +11598,7 @@
       <c r="K528" s="6"/>
       <c r="L528" s="6"/>
     </row>
-    <row r="529" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A529" s="5"/>
       <c r="B529" s="5"/>
       <c r="C529" s="5"/>
@@ -11593,7 +11612,7 @@
       <c r="K529" s="6"/>
       <c r="L529" s="6"/>
     </row>
-    <row r="530" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A530" s="5"/>
       <c r="B530" s="5"/>
       <c r="C530" s="5"/>
@@ -11607,7 +11626,7 @@
       <c r="K530" s="6"/>
       <c r="L530" s="6"/>
     </row>
-    <row r="531" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A531" s="5"/>
       <c r="B531" s="5"/>
       <c r="C531" s="5"/>
@@ -11621,7 +11640,7 @@
       <c r="K531" s="6"/>
       <c r="L531" s="6"/>
     </row>
-    <row r="532" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A532" s="5"/>
       <c r="B532" s="5"/>
       <c r="C532" s="5"/>
@@ -11635,7 +11654,7 @@
       <c r="K532" s="6"/>
       <c r="L532" s="6"/>
     </row>
-    <row r="533" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A533" s="5"/>
       <c r="B533" s="5"/>
       <c r="C533" s="5"/>
@@ -11649,7 +11668,7 @@
       <c r="K533" s="6"/>
       <c r="L533" s="6"/>
     </row>
-    <row r="534" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A534" s="5"/>
       <c r="B534" s="5"/>
       <c r="C534" s="5"/>
@@ -11663,7 +11682,7 @@
       <c r="K534" s="6"/>
       <c r="L534" s="6"/>
     </row>
-    <row r="535" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A535" s="5"/>
       <c r="B535" s="5"/>
       <c r="C535" s="5"/>
@@ -11677,7 +11696,7 @@
       <c r="K535" s="6"/>
       <c r="L535" s="6"/>
     </row>
-    <row r="536" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A536" s="5"/>
       <c r="B536" s="5"/>
       <c r="C536" s="5"/>
@@ -11691,7 +11710,7 @@
       <c r="K536" s="6"/>
       <c r="L536" s="6"/>
     </row>
-    <row r="537" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A537" s="5"/>
       <c r="B537" s="5"/>
       <c r="C537" s="5"/>
@@ -11705,7 +11724,7 @@
       <c r="K537" s="6"/>
       <c r="L537" s="6"/>
     </row>
-    <row r="538" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A538" s="5"/>
       <c r="B538" s="5"/>
       <c r="C538" s="5"/>
@@ -11719,7 +11738,7 @@
       <c r="K538" s="6"/>
       <c r="L538" s="6"/>
     </row>
-    <row r="539" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A539" s="5"/>
       <c r="B539" s="5"/>
       <c r="C539" s="5"/>
@@ -11733,7 +11752,7 @@
       <c r="K539" s="6"/>
       <c r="L539" s="6"/>
     </row>
-    <row r="540" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A540" s="5"/>
       <c r="B540" s="5"/>
       <c r="C540" s="5"/>
@@ -11747,7 +11766,7 @@
       <c r="K540" s="6"/>
       <c r="L540" s="6"/>
     </row>
-    <row r="541" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A541" s="5"/>
       <c r="B541" s="5"/>
       <c r="C541" s="5"/>
@@ -11761,7 +11780,7 @@
       <c r="K541" s="6"/>
       <c r="L541" s="6"/>
     </row>
-    <row r="542" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A542" s="5"/>
       <c r="B542" s="5"/>
       <c r="C542" s="5"/>
@@ -11775,7 +11794,7 @@
       <c r="K542" s="6"/>
       <c r="L542" s="6"/>
     </row>
-    <row r="543" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A543" s="5"/>
       <c r="B543" s="5"/>
       <c r="C543" s="5"/>
@@ -11789,7 +11808,7 @@
       <c r="K543" s="6"/>
       <c r="L543" s="6"/>
     </row>
-    <row r="544" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A544" s="5"/>
       <c r="B544" s="5"/>
       <c r="C544" s="5"/>
@@ -11803,7 +11822,7 @@
       <c r="K544" s="6"/>
       <c r="L544" s="6"/>
     </row>
-    <row r="545" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A545" s="5"/>
       <c r="B545" s="5"/>
       <c r="C545" s="5"/>
@@ -11817,7 +11836,7 @@
       <c r="K545" s="6"/>
       <c r="L545" s="6"/>
     </row>
-    <row r="546" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A546" s="5"/>
       <c r="B546" s="5"/>
       <c r="C546" s="5"/>
@@ -11831,7 +11850,7 @@
       <c r="K546" s="6"/>
       <c r="L546" s="6"/>
     </row>
-    <row r="547" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A547" s="5"/>
       <c r="B547" s="5"/>
       <c r="C547" s="5"/>
@@ -11845,7 +11864,7 @@
       <c r="K547" s="6"/>
       <c r="L547" s="6"/>
     </row>
-    <row r="548" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A548" s="5"/>
       <c r="B548" s="5"/>
       <c r="C548" s="5"/>
@@ -11859,7 +11878,7 @@
       <c r="K548" s="6"/>
       <c r="L548" s="6"/>
     </row>
-    <row r="549" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A549" s="5"/>
       <c r="B549" s="5"/>
       <c r="C549" s="5"/>
@@ -11873,7 +11892,7 @@
       <c r="K549" s="6"/>
       <c r="L549" s="6"/>
     </row>
-    <row r="550" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A550" s="5"/>
       <c r="B550" s="5"/>
       <c r="C550" s="5"/>
@@ -11887,7 +11906,7 @@
       <c r="K550" s="6"/>
       <c r="L550" s="6"/>
     </row>
-    <row r="551" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A551" s="5"/>
       <c r="B551" s="5"/>
       <c r="C551" s="5"/>
@@ -11901,7 +11920,7 @@
       <c r="K551" s="6"/>
       <c r="L551" s="6"/>
     </row>
-    <row r="552" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A552" s="5"/>
       <c r="B552" s="5"/>
       <c r="C552" s="5"/>
@@ -11915,7 +11934,7 @@
       <c r="K552" s="6"/>
       <c r="L552" s="6"/>
     </row>
-    <row r="553" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A553" s="5"/>
       <c r="B553" s="5"/>
       <c r="C553" s="5"/>
@@ -11929,7 +11948,7 @@
       <c r="K553" s="6"/>
       <c r="L553" s="6"/>
     </row>
-    <row r="554" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A554" s="5"/>
       <c r="B554" s="5"/>
       <c r="C554" s="5"/>
@@ -11943,7 +11962,7 @@
       <c r="K554" s="6"/>
       <c r="L554" s="6"/>
     </row>
-    <row r="555" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A555" s="5"/>
       <c r="B555" s="5"/>
       <c r="C555" s="5"/>
@@ -11957,7 +11976,7 @@
       <c r="K555" s="6"/>
       <c r="L555" s="6"/>
     </row>
-    <row r="556" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A556" s="5"/>
       <c r="B556" s="5"/>
       <c r="C556" s="5"/>
@@ -11971,7 +11990,7 @@
       <c r="K556" s="6"/>
       <c r="L556" s="6"/>
     </row>
-    <row r="557" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A557" s="5"/>
       <c r="B557" s="5"/>
       <c r="C557" s="5"/>
@@ -11985,7 +12004,7 @@
       <c r="K557" s="6"/>
       <c r="L557" s="6"/>
     </row>
-    <row r="558" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A558" s="5"/>
       <c r="B558" s="5"/>
       <c r="C558" s="5"/>
@@ -11999,7 +12018,7 @@
       <c r="K558" s="6"/>
       <c r="L558" s="6"/>
     </row>
-    <row r="559" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A559" s="5"/>
       <c r="B559" s="5"/>
       <c r="C559" s="5"/>
@@ -12013,7 +12032,7 @@
       <c r="K559" s="6"/>
       <c r="L559" s="6"/>
     </row>
-    <row r="560" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A560" s="5"/>
       <c r="B560" s="5"/>
       <c r="C560" s="5"/>
@@ -12027,7 +12046,7 @@
       <c r="K560" s="6"/>
       <c r="L560" s="6"/>
     </row>
-    <row r="561" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A561" s="5"/>
       <c r="B561" s="5"/>
       <c r="C561" s="5"/>
@@ -12041,7 +12060,7 @@
       <c r="K561" s="6"/>
       <c r="L561" s="6"/>
     </row>
-    <row r="562" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A562" s="5"/>
       <c r="B562" s="5"/>
       <c r="C562" s="5"/>
@@ -12055,7 +12074,7 @@
       <c r="K562" s="6"/>
       <c r="L562" s="6"/>
     </row>
-    <row r="563" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A563" s="5"/>
       <c r="B563" s="5"/>
       <c r="C563" s="5"/>
@@ -12069,7 +12088,7 @@
       <c r="K563" s="6"/>
       <c r="L563" s="6"/>
     </row>
-    <row r="564" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A564" s="5"/>
       <c r="B564" s="5"/>
       <c r="C564" s="5"/>
@@ -12083,7 +12102,7 @@
       <c r="K564" s="6"/>
       <c r="L564" s="6"/>
     </row>
-    <row r="565" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A565" s="5"/>
       <c r="B565" s="5"/>
       <c r="C565" s="5"/>
@@ -12097,7 +12116,7 @@
       <c r="K565" s="6"/>
       <c r="L565" s="6"/>
     </row>
-    <row r="566" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A566" s="5"/>
       <c r="B566" s="5"/>
       <c r="C566" s="5"/>
@@ -12111,7 +12130,7 @@
       <c r="K566" s="6"/>
       <c r="L566" s="6"/>
     </row>
-    <row r="567" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A567" s="5"/>
       <c r="B567" s="5"/>
       <c r="C567" s="5"/>
@@ -12125,7 +12144,7 @@
       <c r="K567" s="6"/>
       <c r="L567" s="6"/>
     </row>
-    <row r="568" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A568" s="5"/>
       <c r="B568" s="5"/>
       <c r="C568" s="5"/>
@@ -12139,7 +12158,7 @@
       <c r="K568" s="6"/>
       <c r="L568" s="6"/>
     </row>
-    <row r="569" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A569" s="5"/>
       <c r="B569" s="5"/>
       <c r="C569" s="5"/>
@@ -12153,7 +12172,7 @@
       <c r="K569" s="6"/>
       <c r="L569" s="6"/>
     </row>
-    <row r="570" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A570" s="5"/>
       <c r="B570" s="5"/>
       <c r="C570" s="5"/>
@@ -12167,7 +12186,7 @@
       <c r="K570" s="6"/>
       <c r="L570" s="6"/>
     </row>
-    <row r="571" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A571" s="5"/>
       <c r="B571" s="5"/>
       <c r="C571" s="5"/>
@@ -12181,7 +12200,7 @@
       <c r="K571" s="6"/>
       <c r="L571" s="6"/>
     </row>
-    <row r="572" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A572" s="5"/>
       <c r="B572" s="5"/>
       <c r="C572" s="5"/>
@@ -12195,7 +12214,7 @@
       <c r="K572" s="6"/>
       <c r="L572" s="6"/>
     </row>
-    <row r="573" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A573" s="5"/>
       <c r="B573" s="5"/>
       <c r="C573" s="5"/>
@@ -12209,7 +12228,7 @@
       <c r="K573" s="6"/>
       <c r="L573" s="6"/>
     </row>
-    <row r="574" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A574" s="5"/>
       <c r="B574" s="5"/>
       <c r="C574" s="5"/>
@@ -12223,7 +12242,7 @@
       <c r="K574" s="6"/>
       <c r="L574" s="6"/>
     </row>
-    <row r="575" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A575" s="5"/>
       <c r="B575" s="5"/>
       <c r="C575" s="5"/>
@@ -12237,7 +12256,7 @@
       <c r="K575" s="6"/>
       <c r="L575" s="6"/>
     </row>
-    <row r="576" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A576" s="5"/>
       <c r="B576" s="5"/>
       <c r="C576" s="5"/>
@@ -12251,7 +12270,7 @@
       <c r="K576" s="6"/>
       <c r="L576" s="6"/>
     </row>
-    <row r="577" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A577" s="5"/>
       <c r="B577" s="5"/>
       <c r="C577" s="5"/>
@@ -12265,7 +12284,7 @@
       <c r="K577" s="6"/>
       <c r="L577" s="6"/>
     </row>
-    <row r="578" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A578" s="5"/>
       <c r="B578" s="5"/>
       <c r="C578" s="5"/>
@@ -12279,7 +12298,7 @@
       <c r="K578" s="6"/>
       <c r="L578" s="6"/>
     </row>
-    <row r="579" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A579" s="5"/>
       <c r="B579" s="5"/>
       <c r="C579" s="5"/>
@@ -12293,7 +12312,7 @@
       <c r="K579" s="6"/>
       <c r="L579" s="6"/>
     </row>
-    <row r="580" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A580" s="5"/>
       <c r="B580" s="5"/>
       <c r="C580" s="5"/>
@@ -12307,7 +12326,7 @@
       <c r="K580" s="6"/>
       <c r="L580" s="6"/>
     </row>
-    <row r="581" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A581" s="5"/>
       <c r="B581" s="5"/>
       <c r="C581" s="5"/>
@@ -12321,7 +12340,7 @@
       <c r="K581" s="6"/>
       <c r="L581" s="6"/>
     </row>
-    <row r="582" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A582" s="5"/>
       <c r="B582" s="5"/>
       <c r="C582" s="5"/>
@@ -12335,7 +12354,7 @@
       <c r="K582" s="6"/>
       <c r="L582" s="6"/>
     </row>
-    <row r="583" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A583" s="5"/>
       <c r="B583" s="5"/>
       <c r="C583" s="5"/>
@@ -12349,7 +12368,7 @@
       <c r="K583" s="6"/>
       <c r="L583" s="6"/>
     </row>
-    <row r="584" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A584" s="5"/>
       <c r="B584" s="5"/>
       <c r="C584" s="5"/>
@@ -12363,7 +12382,7 @@
       <c r="K584" s="6"/>
       <c r="L584" s="6"/>
     </row>
-    <row r="585" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A585" s="5"/>
       <c r="B585" s="5"/>
       <c r="C585" s="5"/>
@@ -12377,7 +12396,7 @@
       <c r="K585" s="6"/>
       <c r="L585" s="6"/>
     </row>
-    <row r="586" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A586" s="5"/>
       <c r="B586" s="5"/>
       <c r="C586" s="5"/>
@@ -12391,7 +12410,7 @@
       <c r="K586" s="6"/>
       <c r="L586" s="6"/>
     </row>
-    <row r="587" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A587" s="5"/>
       <c r="B587" s="5"/>
       <c r="C587" s="5"/>
@@ -12405,7 +12424,7 @@
       <c r="K587" s="6"/>
       <c r="L587" s="6"/>
     </row>
-    <row r="588" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A588" s="5"/>
       <c r="B588" s="5"/>
       <c r="C588" s="5"/>
@@ -12419,7 +12438,7 @@
       <c r="K588" s="6"/>
       <c r="L588" s="6"/>
     </row>
-    <row r="589" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A589" s="5"/>
       <c r="B589" s="5"/>
       <c r="C589" s="5"/>
@@ -12433,7 +12452,7 @@
       <c r="K589" s="6"/>
       <c r="L589" s="6"/>
     </row>
-    <row r="590" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A590" s="5"/>
       <c r="B590" s="5"/>
       <c r="C590" s="5"/>
@@ -12447,7 +12466,7 @@
       <c r="K590" s="6"/>
       <c r="L590" s="6"/>
     </row>
-    <row r="591" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A591" s="5"/>
       <c r="B591" s="5"/>
       <c r="C591" s="5"/>
@@ -12461,7 +12480,7 @@
       <c r="K591" s="6"/>
       <c r="L591" s="6"/>
     </row>
-    <row r="592" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A592" s="5"/>
       <c r="B592" s="5"/>
       <c r="C592" s="5"/>
@@ -12475,7 +12494,7 @@
       <c r="K592" s="6"/>
       <c r="L592" s="6"/>
     </row>
-    <row r="593" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A593" s="5"/>
       <c r="B593" s="5"/>
       <c r="C593" s="5"/>
@@ -12489,7 +12508,7 @@
       <c r="K593" s="6"/>
       <c r="L593" s="6"/>
     </row>
-    <row r="594" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A594" s="5"/>
       <c r="B594" s="5"/>
       <c r="C594" s="5"/>
@@ -12503,7 +12522,7 @@
       <c r="K594" s="6"/>
       <c r="L594" s="6"/>
     </row>
-    <row r="595" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A595" s="5"/>
       <c r="B595" s="5"/>
       <c r="C595" s="5"/>
@@ -12517,7 +12536,7 @@
       <c r="K595" s="6"/>
       <c r="L595" s="6"/>
     </row>
-    <row r="596" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A596" s="5"/>
       <c r="B596" s="5"/>
       <c r="C596" s="5"/>
@@ -12531,7 +12550,7 @@
       <c r="K596" s="6"/>
       <c r="L596" s="6"/>
     </row>
-    <row r="597" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A597" s="5"/>
       <c r="B597" s="5"/>
       <c r="C597" s="5"/>
@@ -12545,7 +12564,7 @@
       <c r="K597" s="6"/>
       <c r="L597" s="6"/>
     </row>
-    <row r="598" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A598" s="5"/>
       <c r="B598" s="5"/>
       <c r="C598" s="5"/>
@@ -12559,7 +12578,7 @@
       <c r="K598" s="6"/>
       <c r="L598" s="6"/>
     </row>
-    <row r="599" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A599" s="5"/>
       <c r="B599" s="5"/>
       <c r="C599" s="5"/>
@@ -12573,7 +12592,7 @@
       <c r="K599" s="6"/>
       <c r="L599" s="6"/>
     </row>
-    <row r="600" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A600" s="5"/>
       <c r="B600" s="5"/>
       <c r="C600" s="5"/>
@@ -12587,7 +12606,7 @@
       <c r="K600" s="6"/>
       <c r="L600" s="6"/>
     </row>
-    <row r="601" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A601" s="5"/>
       <c r="B601" s="5"/>
       <c r="C601" s="5"/>
@@ -12601,7 +12620,7 @@
       <c r="K601" s="6"/>
       <c r="L601" s="6"/>
     </row>
-    <row r="602" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A602" s="5"/>
       <c r="B602" s="5"/>
       <c r="C602" s="5"/>
@@ -12615,7 +12634,7 @@
       <c r="K602" s="6"/>
       <c r="L602" s="6"/>
     </row>
-    <row r="603" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A603" s="5"/>
       <c r="B603" s="5"/>
       <c r="C603" s="5"/>
@@ -12629,7 +12648,7 @@
       <c r="K603" s="6"/>
       <c r="L603" s="6"/>
     </row>
-    <row r="604" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A604" s="5"/>
       <c r="B604" s="5"/>
       <c r="C604" s="5"/>
@@ -12643,7 +12662,7 @@
       <c r="K604" s="6"/>
       <c r="L604" s="6"/>
     </row>
-    <row r="605" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A605" s="5"/>
       <c r="B605" s="5"/>
       <c r="C605" s="5"/>
@@ -12657,7 +12676,7 @@
       <c r="K605" s="6"/>
       <c r="L605" s="6"/>
     </row>
-    <row r="606" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A606" s="5"/>
       <c r="B606" s="5"/>
       <c r="C606" s="5"/>
@@ -12671,7 +12690,7 @@
       <c r="K606" s="6"/>
       <c r="L606" s="6"/>
     </row>
-    <row r="607" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A607" s="5"/>
       <c r="B607" s="5"/>
       <c r="C607" s="5"/>
@@ -12685,7 +12704,7 @@
       <c r="K607" s="6"/>
       <c r="L607" s="6"/>
     </row>
-    <row r="608" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A608" s="5"/>
       <c r="B608" s="5"/>
       <c r="C608" s="5"/>
@@ -12699,7 +12718,7 @@
       <c r="K608" s="6"/>
       <c r="L608" s="6"/>
     </row>
-    <row r="609" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A609" s="5"/>
       <c r="B609" s="5"/>
       <c r="C609" s="5"/>
@@ -12713,7 +12732,7 @@
       <c r="K609" s="6"/>
       <c r="L609" s="6"/>
     </row>
-    <row r="610" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A610" s="5"/>
       <c r="B610" s="5"/>
       <c r="C610" s="5"/>
@@ -12727,7 +12746,7 @@
       <c r="K610" s="6"/>
       <c r="L610" s="6"/>
     </row>
-    <row r="611" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A611" s="5"/>
       <c r="B611" s="5"/>
       <c r="C611" s="5"/>
@@ -12741,7 +12760,7 @@
       <c r="K611" s="6"/>
       <c r="L611" s="6"/>
     </row>
-    <row r="612" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A612" s="5"/>
       <c r="B612" s="5"/>
       <c r="C612" s="5"/>
@@ -12755,7 +12774,7 @@
       <c r="K612" s="6"/>
       <c r="L612" s="6"/>
     </row>
-    <row r="613" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A613" s="5"/>
       <c r="B613" s="5"/>
       <c r="C613" s="5"/>
@@ -12769,7 +12788,7 @@
       <c r="K613" s="6"/>
       <c r="L613" s="6"/>
     </row>
-    <row r="614" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A614" s="5"/>
       <c r="B614" s="5"/>
       <c r="C614" s="5"/>
@@ -12783,7 +12802,7 @@
       <c r="K614" s="6"/>
       <c r="L614" s="6"/>
     </row>
-    <row r="615" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A615" s="5"/>
       <c r="B615" s="5"/>
       <c r="C615" s="5"/>
@@ -12797,7 +12816,7 @@
       <c r="K615" s="6"/>
       <c r="L615" s="6"/>
     </row>
-    <row r="616" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A616" s="5"/>
       <c r="B616" s="5"/>
       <c r="C616" s="5"/>
@@ -12811,7 +12830,7 @@
       <c r="K616" s="6"/>
       <c r="L616" s="6"/>
     </row>
-    <row r="617" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A617" s="5"/>
       <c r="B617" s="5"/>
       <c r="C617" s="5"/>
@@ -12825,7 +12844,7 @@
       <c r="K617" s="6"/>
       <c r="L617" s="6"/>
     </row>
-    <row r="618" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A618" s="5"/>
       <c r="B618" s="5"/>
       <c r="C618" s="5"/>
@@ -12839,7 +12858,7 @@
       <c r="K618" s="6"/>
       <c r="L618" s="6"/>
     </row>
-    <row r="619" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A619" s="5"/>
       <c r="B619" s="5"/>
       <c r="C619" s="5"/>
@@ -12853,7 +12872,7 @@
       <c r="K619" s="6"/>
       <c r="L619" s="6"/>
     </row>
-    <row r="620" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A620" s="5"/>
       <c r="B620" s="5"/>
       <c r="C620" s="5"/>
@@ -12867,7 +12886,7 @@
       <c r="K620" s="6"/>
       <c r="L620" s="6"/>
     </row>
-    <row r="621" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A621" s="5"/>
       <c r="B621" s="5"/>
       <c r="C621" s="5"/>
@@ -12881,7 +12900,7 @@
       <c r="K621" s="6"/>
       <c r="L621" s="6"/>
     </row>
-    <row r="622" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A622" s="5"/>
       <c r="B622" s="5"/>
       <c r="C622" s="5"/>
@@ -12895,7 +12914,7 @@
       <c r="K622" s="6"/>
       <c r="L622" s="6"/>
     </row>
-    <row r="623" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A623" s="5"/>
       <c r="B623" s="5"/>
       <c r="C623" s="5"/>
@@ -12909,7 +12928,7 @@
       <c r="K623" s="6"/>
       <c r="L623" s="6"/>
     </row>
-    <row r="624" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A624" s="5"/>
       <c r="B624" s="5"/>
       <c r="C624" s="5"/>
@@ -12923,7 +12942,7 @@
       <c r="K624" s="6"/>
       <c r="L624" s="6"/>
     </row>
-    <row r="625" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A625" s="5"/>
       <c r="B625" s="5"/>
       <c r="C625" s="5"/>
@@ -12937,7 +12956,7 @@
       <c r="K625" s="6"/>
       <c r="L625" s="6"/>
     </row>
-    <row r="626" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A626" s="5"/>
       <c r="B626" s="5"/>
       <c r="C626" s="5"/>
@@ -12951,7 +12970,7 @@
       <c r="K626" s="6"/>
       <c r="L626" s="6"/>
     </row>
-    <row r="627" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A627" s="5"/>
       <c r="B627" s="5"/>
       <c r="C627" s="5"/>
@@ -12965,7 +12984,7 @@
       <c r="K627" s="6"/>
       <c r="L627" s="6"/>
     </row>
-    <row r="628" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A628" s="5"/>
       <c r="B628" s="5"/>
       <c r="C628" s="5"/>
@@ -12979,7 +12998,7 @@
       <c r="K628" s="6"/>
       <c r="L628" s="6"/>
     </row>
-    <row r="629" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A629" s="5"/>
       <c r="B629" s="5"/>
       <c r="C629" s="5"/>
@@ -12993,7 +13012,7 @@
       <c r="K629" s="6"/>
       <c r="L629" s="6"/>
     </row>
-    <row r="630" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A630" s="5"/>
       <c r="B630" s="5"/>
       <c r="C630" s="5"/>
@@ -13007,7 +13026,7 @@
       <c r="K630" s="6"/>
       <c r="L630" s="6"/>
     </row>
-    <row r="631" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A631" s="5"/>
       <c r="B631" s="5"/>
       <c r="C631" s="5"/>
@@ -13021,7 +13040,7 @@
       <c r="K631" s="6"/>
       <c r="L631" s="6"/>
     </row>
-    <row r="632" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A632" s="5"/>
       <c r="B632" s="5"/>
       <c r="C632" s="5"/>
@@ -13035,7 +13054,7 @@
       <c r="K632" s="6"/>
       <c r="L632" s="6"/>
     </row>
-    <row r="633" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A633" s="5"/>
       <c r="B633" s="5"/>
       <c r="C633" s="5"/>
@@ -13049,7 +13068,7 @@
       <c r="K633" s="6"/>
       <c r="L633" s="6"/>
     </row>
-    <row r="634" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A634" s="5"/>
       <c r="B634" s="5"/>
       <c r="C634" s="5"/>
@@ -13063,7 +13082,7 @@
       <c r="K634" s="6"/>
       <c r="L634" s="6"/>
     </row>
-    <row r="635" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A635" s="5"/>
       <c r="B635" s="5"/>
       <c r="C635" s="5"/>
@@ -13077,7 +13096,7 @@
       <c r="K635" s="6"/>
       <c r="L635" s="6"/>
     </row>
-    <row r="636" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A636" s="5"/>
       <c r="B636" s="5"/>
       <c r="C636" s="5"/>
@@ -13091,7 +13110,7 @@
       <c r="K636" s="6"/>
       <c r="L636" s="6"/>
     </row>
-    <row r="637" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A637" s="5"/>
       <c r="B637" s="5"/>
       <c r="C637" s="5"/>
@@ -13105,7 +13124,7 @@
       <c r="K637" s="6"/>
       <c r="L637" s="6"/>
     </row>
-    <row r="638" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A638" s="5"/>
       <c r="B638" s="5"/>
       <c r="C638" s="5"/>
@@ -13119,7 +13138,7 @@
       <c r="K638" s="6"/>
       <c r="L638" s="6"/>
     </row>
-    <row r="639" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A639" s="5"/>
       <c r="B639" s="5"/>
       <c r="C639" s="5"/>
@@ -13133,7 +13152,7 @@
       <c r="K639" s="6"/>
       <c r="L639" s="6"/>
     </row>
-    <row r="640" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A640" s="5"/>
       <c r="B640" s="5"/>
       <c r="C640" s="5"/>
@@ -13147,7 +13166,7 @@
       <c r="K640" s="6"/>
       <c r="L640" s="6"/>
     </row>
-    <row r="641" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A641" s="5"/>
       <c r="B641" s="5"/>
       <c r="C641" s="5"/>
@@ -13161,7 +13180,7 @@
       <c r="K641" s="6"/>
       <c r="L641" s="6"/>
     </row>
-    <row r="642" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A642" s="5"/>
       <c r="B642" s="5"/>
       <c r="C642" s="5"/>
@@ -13175,7 +13194,7 @@
       <c r="K642" s="6"/>
       <c r="L642" s="6"/>
     </row>
-    <row r="643" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A643" s="5"/>
       <c r="B643" s="5"/>
       <c r="C643" s="5"/>
@@ -13189,7 +13208,7 @@
       <c r="K643" s="6"/>
       <c r="L643" s="6"/>
     </row>
-    <row r="644" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A644" s="5"/>
       <c r="B644" s="5"/>
       <c r="C644" s="5"/>
@@ -13203,7 +13222,7 @@
       <c r="K644" s="6"/>
       <c r="L644" s="6"/>
     </row>
-    <row r="645" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A645" s="5"/>
       <c r="B645" s="5"/>
       <c r="C645" s="5"/>
@@ -13217,7 +13236,7 @@
       <c r="K645" s="6"/>
       <c r="L645" s="6"/>
     </row>
-    <row r="646" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A646" s="5"/>
       <c r="B646" s="5"/>
       <c r="C646" s="5"/>
@@ -13231,7 +13250,7 @@
       <c r="K646" s="6"/>
       <c r="L646" s="6"/>
     </row>
-    <row r="647" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A647" s="5"/>
       <c r="B647" s="5"/>
       <c r="C647" s="5"/>
@@ -13245,7 +13264,7 @@
       <c r="K647" s="6"/>
       <c r="L647" s="6"/>
     </row>
-    <row r="648" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A648" s="5"/>
       <c r="B648" s="5"/>
       <c r="C648" s="5"/>
@@ -13259,7 +13278,7 @@
       <c r="K648" s="6"/>
       <c r="L648" s="6"/>
     </row>
-    <row r="649" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A649" s="5"/>
       <c r="B649" s="5"/>
       <c r="C649" s="5"/>
@@ -13273,7 +13292,7 @@
       <c r="K649" s="6"/>
       <c r="L649" s="6"/>
     </row>
-    <row r="650" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A650" s="5"/>
       <c r="B650" s="5"/>
       <c r="C650" s="5"/>
@@ -13287,7 +13306,7 @@
       <c r="K650" s="6"/>
       <c r="L650" s="6"/>
     </row>
-    <row r="651" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A651" s="5"/>
       <c r="B651" s="5"/>
       <c r="C651" s="5"/>
@@ -13301,7 +13320,7 @@
       <c r="K651" s="6"/>
       <c r="L651" s="6"/>
     </row>
-    <row r="652" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A652" s="5"/>
       <c r="B652" s="5"/>
       <c r="C652" s="5"/>
@@ -13315,7 +13334,7 @@
       <c r="K652" s="6"/>
       <c r="L652" s="6"/>
     </row>
-    <row r="653" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A653" s="5"/>
       <c r="B653" s="5"/>
       <c r="C653" s="5"/>
@@ -13329,7 +13348,7 @@
       <c r="K653" s="6"/>
       <c r="L653" s="6"/>
     </row>
-    <row r="654" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A654" s="5"/>
       <c r="B654" s="5"/>
       <c r="C654" s="5"/>
@@ -13343,7 +13362,7 @@
       <c r="K654" s="6"/>
       <c r="L654" s="6"/>
     </row>
-    <row r="655" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A655" s="5"/>
       <c r="B655" s="5"/>
       <c r="C655" s="5"/>
@@ -13357,7 +13376,7 @@
       <c r="K655" s="6"/>
       <c r="L655" s="6"/>
     </row>
-    <row r="656" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A656" s="5"/>
       <c r="B656" s="5"/>
       <c r="C656" s="5"/>
@@ -13371,7 +13390,7 @@
       <c r="K656" s="6"/>
       <c r="L656" s="6"/>
     </row>
-    <row r="657" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A657" s="5"/>
       <c r="B657" s="5"/>
       <c r="C657" s="5"/>
@@ -13385,7 +13404,7 @@
       <c r="K657" s="6"/>
       <c r="L657" s="6"/>
     </row>
-    <row r="658" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A658" s="5"/>
       <c r="B658" s="5"/>
       <c r="C658" s="5"/>
@@ -13399,7 +13418,7 @@
       <c r="K658" s="6"/>
       <c r="L658" s="6"/>
     </row>
-    <row r="659" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A659" s="5"/>
       <c r="B659" s="5"/>
       <c r="C659" s="5"/>
@@ -13413,7 +13432,7 @@
       <c r="K659" s="6"/>
       <c r="L659" s="6"/>
     </row>
-    <row r="660" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A660" s="5"/>
       <c r="B660" s="5"/>
       <c r="C660" s="5"/>
@@ -13427,7 +13446,7 @@
       <c r="K660" s="6"/>
       <c r="L660" s="6"/>
     </row>
-    <row r="661" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A661" s="5"/>
       <c r="B661" s="5"/>
       <c r="C661" s="5"/>
@@ -13441,7 +13460,7 @@
       <c r="K661" s="6"/>
       <c r="L661" s="6"/>
     </row>
-    <row r="662" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A662" s="5"/>
       <c r="B662" s="5"/>
       <c r="C662" s="5"/>
@@ -13455,7 +13474,7 @@
       <c r="K662" s="6"/>
       <c r="L662" s="6"/>
     </row>
-    <row r="663" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A663" s="5"/>
       <c r="B663" s="5"/>
       <c r="C663" s="5"/>
@@ -13469,7 +13488,7 @@
       <c r="K663" s="6"/>
       <c r="L663" s="6"/>
     </row>
-    <row r="664" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A664" s="5"/>
       <c r="B664" s="5"/>
       <c r="C664" s="5"/>
@@ -13483,7 +13502,7 @@
       <c r="K664" s="6"/>
       <c r="L664" s="6"/>
     </row>
-    <row r="665" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A665" s="5"/>
       <c r="B665" s="5"/>
       <c r="C665" s="5"/>
@@ -13497,7 +13516,7 @@
       <c r="K665" s="6"/>
       <c r="L665" s="6"/>
     </row>
-    <row r="666" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A666" s="5"/>
       <c r="B666" s="5"/>
       <c r="C666" s="5"/>
@@ -13511,7 +13530,7 @@
       <c r="K666" s="6"/>
       <c r="L666" s="6"/>
     </row>
-    <row r="667" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A667" s="5"/>
       <c r="B667" s="5"/>
       <c r="C667" s="5"/>
@@ -13525,7 +13544,7 @@
       <c r="K667" s="6"/>
       <c r="L667" s="6"/>
     </row>
-    <row r="668" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A668" s="5"/>
       <c r="B668" s="5"/>
       <c r="C668" s="5"/>
@@ -13539,7 +13558,7 @@
       <c r="K668" s="6"/>
       <c r="L668" s="6"/>
     </row>
-    <row r="669" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A669" s="5"/>
       <c r="B669" s="5"/>
       <c r="C669" s="5"/>
@@ -13553,7 +13572,7 @@
       <c r="K669" s="6"/>
       <c r="L669" s="6"/>
     </row>
-    <row r="670" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A670" s="5"/>
       <c r="B670" s="5"/>
       <c r="C670" s="5"/>
@@ -13567,7 +13586,7 @@
       <c r="K670" s="6"/>
       <c r="L670" s="6"/>
     </row>
-    <row r="671" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A671" s="5"/>
       <c r="B671" s="5"/>
       <c r="C671" s="5"/>
@@ -13581,7 +13600,7 @@
       <c r="K671" s="6"/>
       <c r="L671" s="6"/>
     </row>
-    <row r="672" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A672" s="5"/>
       <c r="B672" s="5"/>
       <c r="C672" s="5"/>
@@ -13595,7 +13614,7 @@
       <c r="K672" s="6"/>
       <c r="L672" s="6"/>
     </row>
-    <row r="673" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A673" s="5"/>
       <c r="B673" s="5"/>
       <c r="C673" s="5"/>
@@ -13609,7 +13628,7 @@
       <c r="K673" s="6"/>
       <c r="L673" s="6"/>
     </row>
-    <row r="674" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A674" s="5"/>
       <c r="B674" s="5"/>
       <c r="C674" s="5"/>
@@ -13623,7 +13642,7 @@
       <c r="K674" s="6"/>
       <c r="L674" s="6"/>
     </row>
-    <row r="675" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A675" s="5"/>
       <c r="B675" s="5"/>
       <c r="C675" s="5"/>
@@ -13637,7 +13656,7 @@
       <c r="K675" s="6"/>
       <c r="L675" s="6"/>
     </row>
-    <row r="676" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A676" s="5"/>
       <c r="B676" s="5"/>
       <c r="C676" s="5"/>
@@ -13651,7 +13670,7 @@
       <c r="K676" s="6"/>
       <c r="L676" s="6"/>
     </row>
-    <row r="677" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A677" s="5"/>
       <c r="B677" s="5"/>
       <c r="C677" s="5"/>
@@ -13665,7 +13684,7 @@
       <c r="K677" s="6"/>
       <c r="L677" s="6"/>
     </row>
-    <row r="678" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A678" s="5"/>
       <c r="B678" s="5"/>
       <c r="C678" s="5"/>
@@ -13679,7 +13698,7 @@
       <c r="K678" s="6"/>
       <c r="L678" s="6"/>
     </row>
-    <row r="679" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A679" s="5"/>
       <c r="B679" s="5"/>
       <c r="C679" s="5"/>
@@ -13693,7 +13712,7 @@
       <c r="K679" s="6"/>
       <c r="L679" s="6"/>
     </row>
-    <row r="680" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A680" s="5"/>
       <c r="B680" s="5"/>
       <c r="C680" s="5"/>
@@ -13707,7 +13726,7 @@
       <c r="K680" s="6"/>
       <c r="L680" s="6"/>
     </row>
-    <row r="681" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A681" s="5"/>
       <c r="B681" s="5"/>
       <c r="C681" s="5"/>
@@ -13721,7 +13740,7 @@
       <c r="K681" s="6"/>
       <c r="L681" s="6"/>
     </row>
-    <row r="682" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A682" s="5"/>
       <c r="B682" s="5"/>
       <c r="C682" s="5"/>
@@ -13735,7 +13754,7 @@
       <c r="K682" s="6"/>
       <c r="L682" s="6"/>
     </row>
-    <row r="683" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A683" s="5"/>
       <c r="B683" s="5"/>
       <c r="C683" s="5"/>
@@ -13749,7 +13768,7 @@
       <c r="K683" s="6"/>
       <c r="L683" s="6"/>
     </row>
-    <row r="684" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A684" s="5"/>
       <c r="B684" s="5"/>
       <c r="C684" s="5"/>
@@ -13763,7 +13782,7 @@
       <c r="K684" s="6"/>
       <c r="L684" s="6"/>
     </row>
-    <row r="685" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A685" s="5"/>
       <c r="B685" s="5"/>
       <c r="C685" s="5"/>
@@ -13777,7 +13796,7 @@
       <c r="K685" s="6"/>
       <c r="L685" s="6"/>
     </row>
-    <row r="686" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A686" s="5"/>
       <c r="B686" s="5"/>
       <c r="C686" s="5"/>
@@ -13791,7 +13810,7 @@
       <c r="K686" s="6"/>
       <c r="L686" s="6"/>
     </row>
-    <row r="687" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A687" s="5"/>
       <c r="B687" s="5"/>
       <c r="C687" s="5"/>
@@ -13805,7 +13824,7 @@
       <c r="K687" s="6"/>
       <c r="L687" s="6"/>
     </row>
-    <row r="688" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A688" s="5"/>
       <c r="B688" s="5"/>
       <c r="C688" s="5"/>
@@ -13819,7 +13838,7 @@
       <c r="K688" s="6"/>
       <c r="L688" s="6"/>
     </row>
-    <row r="689" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A689" s="5"/>
       <c r="B689" s="5"/>
       <c r="C689" s="5"/>
@@ -13833,7 +13852,7 @@
       <c r="K689" s="6"/>
       <c r="L689" s="6"/>
     </row>
-    <row r="690" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A690" s="5"/>
       <c r="B690" s="5"/>
       <c r="C690" s="5"/>
@@ -13847,7 +13866,7 @@
       <c r="K690" s="6"/>
       <c r="L690" s="6"/>
     </row>
-    <row r="691" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A691" s="5"/>
       <c r="B691" s="5"/>
       <c r="C691" s="5"/>
@@ -13861,7 +13880,7 @@
       <c r="K691" s="6"/>
       <c r="L691" s="6"/>
     </row>
-    <row r="692" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A692" s="5"/>
       <c r="B692" s="5"/>
       <c r="C692" s="5"/>
@@ -13875,7 +13894,7 @@
       <c r="K692" s="6"/>
       <c r="L692" s="6"/>
     </row>
-    <row r="693" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A693" s="5"/>
       <c r="B693" s="5"/>
       <c r="C693" s="5"/>
@@ -13889,7 +13908,7 @@
       <c r="K693" s="6"/>
       <c r="L693" s="6"/>
     </row>
-    <row r="694" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A694" s="5"/>
       <c r="B694" s="5"/>
       <c r="C694" s="5"/>
@@ -13903,7 +13922,7 @@
       <c r="K694" s="6"/>
       <c r="L694" s="6"/>
     </row>
-    <row r="695" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A695" s="5"/>
       <c r="B695" s="5"/>
       <c r="C695" s="5"/>
@@ -13917,7 +13936,7 @@
       <c r="K695" s="6"/>
       <c r="L695" s="6"/>
     </row>
-    <row r="696" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A696" s="5"/>
       <c r="B696" s="5"/>
       <c r="C696" s="5"/>
@@ -13931,7 +13950,7 @@
       <c r="K696" s="6"/>
       <c r="L696" s="6"/>
     </row>
-    <row r="697" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A697" s="5"/>
       <c r="B697" s="5"/>
       <c r="C697" s="5"/>
@@ -13945,7 +13964,7 @@
       <c r="K697" s="6"/>
       <c r="L697" s="6"/>
     </row>
-    <row r="698" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A698" s="5"/>
       <c r="B698" s="5"/>
       <c r="C698" s="5"/>
@@ -13959,7 +13978,7 @@
       <c r="K698" s="6"/>
       <c r="L698" s="6"/>
     </row>
-    <row r="699" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A699" s="5"/>
       <c r="B699" s="5"/>
       <c r="C699" s="5"/>
@@ -13973,7 +13992,7 @@
       <c r="K699" s="6"/>
       <c r="L699" s="6"/>
     </row>
-    <row r="700" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A700" s="5"/>
       <c r="B700" s="5"/>
       <c r="C700" s="5"/>
@@ -13987,7 +14006,7 @@
       <c r="K700" s="6"/>
       <c r="L700" s="6"/>
     </row>
-    <row r="701" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A701" s="5"/>
       <c r="B701" s="5"/>
       <c r="C701" s="5"/>
@@ -14001,7 +14020,7 @@
       <c r="K701" s="6"/>
       <c r="L701" s="6"/>
     </row>
-    <row r="702" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A702" s="5"/>
       <c r="B702" s="5"/>
       <c r="C702" s="5"/>
@@ -14015,7 +14034,7 @@
       <c r="K702" s="6"/>
       <c r="L702" s="6"/>
     </row>
-    <row r="703" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A703" s="5"/>
       <c r="B703" s="5"/>
       <c r="C703" s="5"/>
@@ -14029,7 +14048,7 @@
       <c r="K703" s="6"/>
       <c r="L703" s="6"/>
     </row>
-    <row r="704" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A704" s="5"/>
       <c r="B704" s="5"/>
       <c r="C704" s="5"/>
@@ -14043,7 +14062,7 @@
       <c r="K704" s="6"/>
       <c r="L704" s="6"/>
     </row>
-    <row r="705" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A705" s="5"/>
       <c r="B705" s="5"/>
       <c r="C705" s="5"/>
@@ -14057,7 +14076,7 @@
       <c r="K705" s="6"/>
       <c r="L705" s="6"/>
     </row>
-    <row r="706" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A706" s="5"/>
       <c r="B706" s="5"/>
       <c r="C706" s="5"/>
@@ -14071,7 +14090,7 @@
       <c r="K706" s="6"/>
       <c r="L706" s="6"/>
     </row>
-    <row r="707" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A707" s="5"/>
       <c r="B707" s="5"/>
       <c r="C707" s="5"/>
@@ -14085,7 +14104,7 @@
       <c r="K707" s="6"/>
       <c r="L707" s="6"/>
     </row>
-    <row r="708" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A708" s="5"/>
       <c r="B708" s="5"/>
       <c r="C708" s="5"/>
@@ -14099,7 +14118,7 @@
       <c r="K708" s="6"/>
       <c r="L708" s="6"/>
     </row>
-    <row r="709" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A709" s="5"/>
       <c r="B709" s="5"/>
       <c r="C709" s="5"/>
@@ -14113,7 +14132,7 @@
       <c r="K709" s="6"/>
       <c r="L709" s="6"/>
     </row>
-    <row r="710" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A710" s="5"/>
       <c r="B710" s="5"/>
       <c r="C710" s="5"/>
@@ -14127,7 +14146,7 @@
       <c r="K710" s="6"/>
       <c r="L710" s="6"/>
     </row>
-    <row r="711" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A711" s="5"/>
       <c r="B711" s="5"/>
       <c r="C711" s="5"/>
@@ -14141,7 +14160,7 @@
       <c r="K711" s="6"/>
       <c r="L711" s="6"/>
     </row>
-    <row r="712" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A712" s="5"/>
       <c r="B712" s="5"/>
       <c r="C712" s="5"/>
@@ -14155,7 +14174,7 @@
       <c r="K712" s="6"/>
       <c r="L712" s="6"/>
     </row>
-    <row r="713" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A713" s="5"/>
       <c r="B713" s="5"/>
       <c r="C713" s="5"/>
@@ -14169,7 +14188,7 @@
       <c r="K713" s="6"/>
       <c r="L713" s="6"/>
     </row>
-    <row r="714" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A714" s="5"/>
       <c r="B714" s="5"/>
       <c r="C714" s="5"/>
@@ -14183,7 +14202,7 @@
       <c r="K714" s="6"/>
       <c r="L714" s="6"/>
     </row>
-    <row r="715" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A715" s="5"/>
       <c r="B715" s="5"/>
       <c r="C715" s="5"/>
@@ -14197,7 +14216,7 @@
       <c r="K715" s="6"/>
       <c r="L715" s="6"/>
     </row>
-    <row r="716" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A716" s="5"/>
       <c r="B716" s="5"/>
       <c r="C716" s="5"/>
@@ -14211,7 +14230,7 @@
       <c r="K716" s="6"/>
       <c r="L716" s="6"/>
     </row>
-    <row r="717" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A717" s="5"/>
       <c r="B717" s="5"/>
       <c r="C717" s="5"/>
@@ -14225,7 +14244,7 @@
       <c r="K717" s="6"/>
       <c r="L717" s="6"/>
     </row>
-    <row r="718" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A718" s="5"/>
       <c r="B718" s="5"/>
       <c r="C718" s="5"/>
@@ -14239,7 +14258,7 @@
       <c r="K718" s="6"/>
       <c r="L718" s="6"/>
     </row>
-    <row r="719" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A719" s="5"/>
       <c r="B719" s="5"/>
       <c r="C719" s="5"/>
@@ -14253,7 +14272,7 @@
       <c r="K719" s="6"/>
       <c r="L719" s="6"/>
     </row>
-    <row r="720" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A720" s="5"/>
       <c r="B720" s="5"/>
       <c r="C720" s="5"/>
@@ -14267,7 +14286,7 @@
       <c r="K720" s="6"/>
       <c r="L720" s="6"/>
     </row>
-    <row r="721" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A721" s="5"/>
       <c r="B721" s="5"/>
       <c r="C721" s="5"/>
@@ -14281,7 +14300,7 @@
       <c r="K721" s="6"/>
       <c r="L721" s="6"/>
     </row>
-    <row r="722" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A722" s="5"/>
       <c r="B722" s="5"/>
       <c r="C722" s="5"/>
@@ -14295,7 +14314,7 @@
       <c r="K722" s="6"/>
       <c r="L722" s="6"/>
     </row>
-    <row r="723" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A723" s="5"/>
       <c r="B723" s="5"/>
       <c r="C723" s="5"/>
@@ -14309,7 +14328,7 @@
       <c r="K723" s="6"/>
       <c r="L723" s="6"/>
     </row>
-    <row r="724" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A724" s="5"/>
       <c r="B724" s="5"/>
       <c r="C724" s="5"/>
@@ -14323,7 +14342,7 @@
       <c r="K724" s="6"/>
       <c r="L724" s="6"/>
     </row>
-    <row r="725" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A725" s="5"/>
       <c r="B725" s="5"/>
       <c r="C725" s="5"/>
@@ -14337,7 +14356,7 @@
       <c r="K725" s="6"/>
       <c r="L725" s="6"/>
     </row>
-    <row r="726" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A726" s="5"/>
       <c r="B726" s="5"/>
       <c r="C726" s="5"/>
@@ -14351,7 +14370,7 @@
       <c r="K726" s="6"/>
       <c r="L726" s="6"/>
     </row>
-    <row r="727" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A727" s="5"/>
       <c r="B727" s="5"/>
       <c r="C727" s="5"/>
@@ -14365,7 +14384,7 @@
       <c r="K727" s="6"/>
       <c r="L727" s="6"/>
     </row>
-    <row r="728" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A728" s="5"/>
       <c r="B728" s="5"/>
       <c r="C728" s="5"/>
@@ -14379,7 +14398,7 @@
       <c r="K728" s="6"/>
       <c r="L728" s="6"/>
     </row>
-    <row r="729" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A729" s="5"/>
       <c r="B729" s="5"/>
       <c r="C729" s="5"/>
@@ -14393,7 +14412,7 @@
       <c r="K729" s="6"/>
       <c r="L729" s="6"/>
     </row>
-    <row r="730" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A730" s="5"/>
       <c r="B730" s="5"/>
       <c r="C730" s="5"/>
@@ -14407,7 +14426,7 @@
       <c r="K730" s="6"/>
       <c r="L730" s="6"/>
     </row>
-    <row r="731" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A731" s="5"/>
       <c r="B731" s="5"/>
       <c r="C731" s="5"/>
@@ -14421,7 +14440,7 @@
       <c r="K731" s="6"/>
       <c r="L731" s="6"/>
     </row>
-    <row r="732" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A732" s="5"/>
       <c r="B732" s="5"/>
       <c r="C732" s="5"/>
@@ -14435,7 +14454,7 @@
       <c r="K732" s="6"/>
       <c r="L732" s="6"/>
     </row>
-    <row r="733" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A733" s="5"/>
       <c r="B733" s="5"/>
       <c r="C733" s="5"/>
@@ -14449,7 +14468,7 @@
       <c r="K733" s="6"/>
       <c r="L733" s="6"/>
     </row>
-    <row r="734" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A734" s="5"/>
       <c r="B734" s="5"/>
       <c r="C734" s="5"/>
@@ -14463,7 +14482,7 @@
       <c r="K734" s="6"/>
       <c r="L734" s="6"/>
     </row>
-    <row r="735" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A735" s="5"/>
       <c r="B735" s="5"/>
       <c r="C735" s="5"/>
@@ -14477,7 +14496,7 @@
       <c r="K735" s="6"/>
       <c r="L735" s="6"/>
     </row>
-    <row r="736" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A736" s="5"/>
       <c r="B736" s="5"/>
       <c r="C736" s="5"/>
@@ -14491,7 +14510,7 @@
       <c r="K736" s="6"/>
       <c r="L736" s="6"/>
     </row>
-    <row r="737" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A737" s="5"/>
       <c r="B737" s="5"/>
       <c r="C737" s="5"/>
@@ -14505,7 +14524,7 @@
       <c r="K737" s="6"/>
       <c r="L737" s="6"/>
     </row>
-    <row r="738" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A738" s="5"/>
       <c r="B738" s="5"/>
       <c r="C738" s="5"/>
@@ -14519,7 +14538,7 @@
       <c r="K738" s="6"/>
       <c r="L738" s="6"/>
     </row>
-    <row r="739" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A739" s="5"/>
       <c r="B739" s="5"/>
       <c r="C739" s="5"/>
@@ -14533,7 +14552,7 @@
       <c r="K739" s="6"/>
       <c r="L739" s="6"/>
     </row>
-    <row r="740" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A740" s="5"/>
       <c r="B740" s="5"/>
       <c r="C740" s="5"/>
@@ -14547,7 +14566,7 @@
       <c r="K740" s="6"/>
       <c r="L740" s="6"/>
     </row>
-    <row r="741" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A741" s="5"/>
       <c r="B741" s="5"/>
       <c r="C741" s="5"/>
@@ -14561,7 +14580,7 @@
       <c r="K741" s="6"/>
       <c r="L741" s="6"/>
     </row>
-    <row r="742" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A742" s="5"/>
       <c r="B742" s="5"/>
       <c r="C742" s="5"/>
@@ -14575,7 +14594,7 @@
       <c r="K742" s="6"/>
       <c r="L742" s="6"/>
     </row>
-    <row r="743" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A743" s="5"/>
       <c r="B743" s="5"/>
       <c r="C743" s="5"/>
@@ -14589,7 +14608,7 @@
       <c r="K743" s="6"/>
       <c r="L743" s="6"/>
     </row>
-    <row r="744" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A744" s="5"/>
       <c r="B744" s="5"/>
       <c r="C744" s="5"/>
@@ -14603,7 +14622,7 @@
       <c r="K744" s="6"/>
       <c r="L744" s="6"/>
     </row>
-    <row r="745" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A745" s="5"/>
       <c r="B745" s="5"/>
       <c r="C745" s="5"/>
@@ -14617,7 +14636,7 @@
       <c r="K745" s="6"/>
       <c r="L745" s="6"/>
     </row>
-    <row r="746" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A746" s="5"/>
       <c r="B746" s="5"/>
       <c r="C746" s="5"/>
@@ -14631,7 +14650,7 @@
       <c r="K746" s="6"/>
       <c r="L746" s="6"/>
     </row>
-    <row r="747" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A747" s="5"/>
       <c r="B747" s="5"/>
       <c r="C747" s="5"/>
@@ -14645,7 +14664,7 @@
       <c r="K747" s="6"/>
       <c r="L747" s="6"/>
     </row>
-    <row r="748" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A748" s="5"/>
       <c r="B748" s="5"/>
       <c r="C748" s="5"/>
@@ -14659,7 +14678,7 @@
       <c r="K748" s="6"/>
       <c r="L748" s="6"/>
     </row>
-    <row r="749" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A749" s="5"/>
       <c r="B749" s="5"/>
       <c r="C749" s="5"/>
@@ -14673,7 +14692,7 @@
       <c r="K749" s="6"/>
       <c r="L749" s="6"/>
     </row>
-    <row r="750" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A750" s="5"/>
       <c r="B750" s="5"/>
       <c r="C750" s="5"/>
@@ -14687,7 +14706,7 @@
       <c r="K750" s="6"/>
       <c r="L750" s="6"/>
     </row>
-    <row r="751" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A751" s="5"/>
       <c r="B751" s="5"/>
       <c r="C751" s="5"/>
@@ -14701,7 +14720,7 @@
       <c r="K751" s="6"/>
       <c r="L751" s="6"/>
     </row>
-    <row r="752" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A752" s="5"/>
       <c r="B752" s="5"/>
       <c r="C752" s="5"/>
@@ -14715,7 +14734,7 @@
       <c r="K752" s="6"/>
       <c r="L752" s="6"/>
     </row>
-    <row r="753" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A753" s="5"/>
       <c r="B753" s="5"/>
       <c r="C753" s="5"/>
@@ -14729,7 +14748,7 @@
       <c r="K753" s="6"/>
       <c r="L753" s="6"/>
     </row>
-    <row r="754" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A754" s="5"/>
       <c r="B754" s="5"/>
       <c r="C754" s="5"/>
@@ -14743,7 +14762,7 @@
       <c r="K754" s="6"/>
       <c r="L754" s="6"/>
     </row>
-    <row r="755" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A755" s="5"/>
       <c r="B755" s="5"/>
       <c r="C755" s="5"/>
@@ -14757,7 +14776,7 @@
       <c r="K755" s="6"/>
       <c r="L755" s="6"/>
     </row>
-    <row r="756" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A756" s="5"/>
       <c r="B756" s="5"/>
       <c r="C756" s="5"/>
@@ -14771,7 +14790,7 @@
       <c r="K756" s="6"/>
       <c r="L756" s="6"/>
     </row>
-    <row r="757" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A757" s="5"/>
       <c r="B757" s="5"/>
       <c r="C757" s="5"/>
@@ -14785,7 +14804,7 @@
       <c r="K757" s="6"/>
       <c r="L757" s="6"/>
     </row>
-    <row r="758" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A758" s="5"/>
       <c r="B758" s="5"/>
       <c r="C758" s="5"/>
@@ -14799,7 +14818,7 @@
       <c r="K758" s="6"/>
       <c r="L758" s="6"/>
     </row>
-    <row r="759" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A759" s="5"/>
       <c r="B759" s="5"/>
       <c r="C759" s="5"/>
@@ -14813,7 +14832,7 @@
       <c r="K759" s="6"/>
       <c r="L759" s="6"/>
     </row>
-    <row r="760" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A760" s="5"/>
       <c r="B760" s="5"/>
       <c r="C760" s="5"/>
@@ -14827,7 +14846,7 @@
       <c r="K760" s="6"/>
       <c r="L760" s="6"/>
     </row>
-    <row r="761" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A761" s="5"/>
       <c r="B761" s="5"/>
       <c r="C761" s="5"/>
@@ -14841,7 +14860,7 @@
       <c r="K761" s="6"/>
       <c r="L761" s="6"/>
     </row>
-    <row r="762" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A762" s="5"/>
       <c r="B762" s="5"/>
       <c r="C762" s="5"/>
@@ -14855,7 +14874,7 @@
       <c r="K762" s="6"/>
       <c r="L762" s="6"/>
     </row>
-    <row r="763" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A763" s="5"/>
       <c r="B763" s="5"/>
       <c r="C763" s="5"/>
@@ -14869,7 +14888,7 @@
       <c r="K763" s="6"/>
       <c r="L763" s="6"/>
     </row>
-    <row r="764" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A764" s="5"/>
       <c r="B764" s="5"/>
       <c r="C764" s="5"/>
@@ -14883,7 +14902,7 @@
       <c r="K764" s="6"/>
       <c r="L764" s="6"/>
     </row>
-    <row r="765" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A765" s="5"/>
       <c r="B765" s="5"/>
       <c r="C765" s="5"/>
@@ -14897,7 +14916,7 @@
       <c r="K765" s="6"/>
       <c r="L765" s="6"/>
     </row>
-    <row r="766" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A766" s="5"/>
       <c r="B766" s="5"/>
       <c r="C766" s="5"/>
@@ -14911,7 +14930,7 @@
       <c r="K766" s="6"/>
       <c r="L766" s="6"/>
     </row>
-    <row r="767" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A767" s="5"/>
       <c r="B767" s="5"/>
       <c r="C767" s="5"/>
@@ -14925,7 +14944,7 @@
       <c r="K767" s="6"/>
       <c r="L767" s="6"/>
     </row>
-    <row r="768" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A768" s="5"/>
       <c r="B768" s="5"/>
       <c r="C768" s="5"/>
@@ -14939,7 +14958,7 @@
       <c r="K768" s="6"/>
       <c r="L768" s="6"/>
     </row>
-    <row r="769" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A769" s="5"/>
       <c r="B769" s="5"/>
       <c r="C769" s="5"/>
@@ -14953,7 +14972,7 @@
       <c r="K769" s="6"/>
       <c r="L769" s="6"/>
     </row>
-    <row r="770" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A770" s="5"/>
       <c r="B770" s="5"/>
       <c r="C770" s="5"/>
@@ -14967,7 +14986,7 @@
       <c r="K770" s="6"/>
       <c r="L770" s="6"/>
     </row>
-    <row r="771" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A771" s="5"/>
       <c r="B771" s="5"/>
       <c r="C771" s="5"/>
@@ -14981,7 +15000,7 @@
       <c r="K771" s="6"/>
       <c r="L771" s="6"/>
     </row>
-    <row r="772" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A772" s="5"/>
       <c r="B772" s="5"/>
       <c r="C772" s="5"/>
@@ -14995,7 +15014,7 @@
       <c r="K772" s="6"/>
       <c r="L772" s="6"/>
     </row>
-    <row r="773" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A773" s="5"/>
       <c r="B773" s="5"/>
       <c r="C773" s="5"/>
@@ -15009,7 +15028,7 @@
       <c r="K773" s="6"/>
       <c r="L773" s="6"/>
     </row>
-    <row r="774" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A774" s="5"/>
       <c r="B774" s="5"/>
       <c r="C774" s="5"/>
@@ -15023,7 +15042,7 @@
       <c r="K774" s="6"/>
       <c r="L774" s="6"/>
     </row>
-    <row r="775" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A775" s="5"/>
       <c r="B775" s="5"/>
       <c r="C775" s="5"/>
@@ -15037,7 +15056,7 @@
       <c r="K775" s="6"/>
       <c r="L775" s="6"/>
     </row>
-    <row r="776" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A776" s="5"/>
       <c r="B776" s="5"/>
       <c r="C776" s="5"/>
@@ -15051,7 +15070,7 @@
       <c r="K776" s="6"/>
       <c r="L776" s="6"/>
     </row>
-    <row r="777" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A777" s="5"/>
       <c r="B777" s="5"/>
       <c r="C777" s="5"/>
@@ -15065,7 +15084,7 @@
       <c r="K777" s="6"/>
       <c r="L777" s="6"/>
     </row>
-    <row r="778" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A778" s="5"/>
       <c r="B778" s="5"/>
       <c r="C778" s="5"/>
@@ -15079,7 +15098,7 @@
       <c r="K778" s="6"/>
       <c r="L778" s="6"/>
     </row>
-    <row r="779" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A779" s="5"/>
       <c r="B779" s="5"/>
       <c r="C779" s="5"/>
@@ -15093,7 +15112,7 @@
       <c r="K779" s="6"/>
       <c r="L779" s="6"/>
     </row>
-    <row r="780" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A780" s="5"/>
       <c r="B780" s="5"/>
       <c r="C780" s="5"/>
@@ -15107,7 +15126,7 @@
       <c r="K780" s="6"/>
       <c r="L780" s="6"/>
     </row>
-    <row r="781" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A781" s="5"/>
       <c r="B781" s="5"/>
       <c r="C781" s="5"/>
@@ -15121,7 +15140,7 @@
       <c r="K781" s="6"/>
       <c r="L781" s="6"/>
     </row>
-    <row r="782" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A782" s="5"/>
       <c r="B782" s="5"/>
       <c r="C782" s="5"/>
@@ -15135,7 +15154,7 @@
       <c r="K782" s="6"/>
       <c r="L782" s="6"/>
     </row>
-    <row r="783" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A783" s="5"/>
       <c r="B783" s="5"/>
       <c r="C783" s="5"/>
@@ -15149,7 +15168,7 @@
       <c r="K783" s="6"/>
       <c r="L783" s="6"/>
     </row>
-    <row r="784" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A784" s="5"/>
       <c r="B784" s="5"/>
       <c r="C784" s="5"/>
@@ -15163,7 +15182,7 @@
       <c r="K784" s="6"/>
       <c r="L784" s="6"/>
     </row>
-    <row r="785" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A785" s="5"/>
       <c r="B785" s="5"/>
       <c r="C785" s="5"/>
@@ -15177,7 +15196,7 @@
       <c r="K785" s="6"/>
       <c r="L785" s="6"/>
     </row>
-    <row r="786" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A786" s="5"/>
       <c r="B786" s="5"/>
       <c r="C786" s="5"/>
@@ -15191,7 +15210,7 @@
       <c r="K786" s="6"/>
       <c r="L786" s="6"/>
     </row>
-    <row r="787" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A787" s="5"/>
       <c r="B787" s="5"/>
       <c r="C787" s="5"/>
@@ -15205,7 +15224,7 @@
       <c r="K787" s="6"/>
       <c r="L787" s="6"/>
     </row>
-    <row r="788" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A788" s="5"/>
       <c r="B788" s="5"/>
       <c r="C788" s="5"/>
@@ -15219,7 +15238,7 @@
       <c r="K788" s="6"/>
       <c r="L788" s="6"/>
     </row>
-    <row r="789" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A789" s="5"/>
       <c r="B789" s="5"/>
       <c r="C789" s="5"/>
@@ -15233,7 +15252,7 @@
       <c r="K789" s="6"/>
       <c r="L789" s="6"/>
     </row>
-    <row r="790" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A790" s="5"/>
       <c r="B790" s="5"/>
       <c r="C790" s="5"/>
@@ -15247,7 +15266,7 @@
       <c r="K790" s="6"/>
       <c r="L790" s="6"/>
     </row>
-    <row r="791" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A791" s="5"/>
       <c r="B791" s="5"/>
       <c r="C791" s="5"/>
@@ -15261,7 +15280,7 @@
       <c r="K791" s="6"/>
       <c r="L791" s="6"/>
     </row>
-    <row r="792" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A792" s="5"/>
       <c r="B792" s="5"/>
       <c r="C792" s="5"/>
@@ -15275,7 +15294,7 @@
       <c r="K792" s="6"/>
       <c r="L792" s="6"/>
     </row>
-    <row r="793" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A793" s="5"/>
       <c r="B793" s="5"/>
       <c r="C793" s="5"/>
@@ -15289,7 +15308,7 @@
       <c r="K793" s="6"/>
       <c r="L793" s="6"/>
     </row>
-    <row r="794" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A794" s="5"/>
       <c r="B794" s="5"/>
       <c r="C794" s="5"/>
@@ -15303,7 +15322,7 @@
       <c r="K794" s="6"/>
       <c r="L794" s="6"/>
     </row>
-    <row r="795" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A795" s="5"/>
       <c r="B795" s="5"/>
       <c r="C795" s="5"/>
@@ -15317,7 +15336,7 @@
       <c r="K795" s="6"/>
       <c r="L795" s="6"/>
     </row>
-    <row r="796" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A796" s="5"/>
       <c r="B796" s="5"/>
       <c r="C796" s="5"/>
@@ -15331,7 +15350,7 @@
       <c r="K796" s="6"/>
       <c r="L796" s="6"/>
     </row>
-    <row r="797" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A797" s="5"/>
       <c r="B797" s="5"/>
       <c r="C797" s="5"/>
@@ -15345,7 +15364,7 @@
       <c r="K797" s="6"/>
       <c r="L797" s="6"/>
     </row>
-    <row r="798" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A798" s="5"/>
       <c r="B798" s="5"/>
       <c r="C798" s="5"/>
@@ -15359,7 +15378,7 @@
       <c r="K798" s="6"/>
       <c r="L798" s="6"/>
     </row>
-    <row r="799" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A799" s="5"/>
       <c r="B799" s="5"/>
       <c r="C799" s="5"/>
@@ -15373,7 +15392,7 @@
       <c r="K799" s="6"/>
       <c r="L799" s="6"/>
     </row>
-    <row r="800" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A800" s="5"/>
       <c r="B800" s="5"/>
       <c r="C800" s="5"/>
@@ -15387,7 +15406,7 @@
       <c r="K800" s="6"/>
       <c r="L800" s="6"/>
     </row>
-    <row r="801" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A801" s="5"/>
       <c r="B801" s="5"/>
       <c r="C801" s="5"/>
@@ -15401,7 +15420,7 @@
       <c r="K801" s="6"/>
       <c r="L801" s="6"/>
     </row>
-    <row r="802" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A802" s="5"/>
       <c r="B802" s="5"/>
       <c r="C802" s="5"/>
@@ -15415,7 +15434,7 @@
       <c r="K802" s="6"/>
       <c r="L802" s="6"/>
     </row>
-    <row r="803" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A803" s="5"/>
       <c r="B803" s="5"/>
       <c r="C803" s="5"/>
@@ -15429,7 +15448,7 @@
       <c r="K803" s="6"/>
       <c r="L803" s="6"/>
     </row>
-    <row r="804" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A804" s="5"/>
       <c r="B804" s="5"/>
       <c r="C804" s="5"/>
@@ -15443,7 +15462,7 @@
       <c r="K804" s="6"/>
       <c r="L804" s="6"/>
     </row>
-    <row r="805" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A805" s="5"/>
       <c r="B805" s="5"/>
       <c r="C805" s="5"/>
@@ -15457,7 +15476,7 @@
       <c r="K805" s="6"/>
       <c r="L805" s="6"/>
     </row>
-    <row r="806" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A806" s="5"/>
       <c r="B806" s="5"/>
       <c r="C806" s="5"/>
@@ -15471,7 +15490,7 @@
       <c r="K806" s="6"/>
       <c r="L806" s="6"/>
     </row>
-    <row r="807" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A807" s="5"/>
       <c r="B807" s="5"/>
       <c r="C807" s="5"/>
@@ -15485,7 +15504,7 @@
       <c r="K807" s="6"/>
       <c r="L807" s="6"/>
     </row>
-    <row r="808" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A808" s="5"/>
       <c r="B808" s="5"/>
       <c r="C808" s="5"/>
@@ -15499,7 +15518,7 @@
       <c r="K808" s="6"/>
       <c r="L808" s="6"/>
     </row>
-    <row r="809" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A809" s="5"/>
       <c r="B809" s="5"/>
       <c r="C809" s="5"/>
@@ -15513,7 +15532,7 @@
       <c r="K809" s="6"/>
       <c r="L809" s="6"/>
     </row>
-    <row r="810" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A810" s="5"/>
       <c r="B810" s="5"/>
       <c r="C810" s="5"/>
@@ -15527,7 +15546,7 @@
       <c r="K810" s="6"/>
       <c r="L810" s="6"/>
     </row>
-    <row r="811" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A811" s="5"/>
       <c r="B811" s="5"/>
       <c r="C811" s="5"/>
@@ -15541,7 +15560,7 @@
       <c r="K811" s="6"/>
       <c r="L811" s="6"/>
     </row>
-    <row r="812" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A812" s="5"/>
       <c r="B812" s="5"/>
       <c r="C812" s="5"/>
@@ -15555,7 +15574,7 @@
       <c r="K812" s="6"/>
       <c r="L812" s="6"/>
     </row>
-    <row r="813" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A813" s="5"/>
       <c r="B813" s="5"/>
       <c r="C813" s="5"/>
@@ -15569,7 +15588,7 @@
       <c r="K813" s="6"/>
       <c r="L813" s="6"/>
     </row>
-    <row r="814" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A814" s="5"/>
       <c r="B814" s="5"/>
       <c r="C814" s="5"/>
@@ -15583,7 +15602,7 @@
       <c r="K814" s="6"/>
       <c r="L814" s="6"/>
     </row>
-    <row r="815" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A815" s="5"/>
       <c r="B815" s="5"/>
       <c r="C815" s="5"/>
@@ -15597,7 +15616,7 @@
       <c r="K815" s="6"/>
       <c r="L815" s="6"/>
     </row>
-    <row r="816" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A816" s="5"/>
       <c r="B816" s="5"/>
       <c r="C816" s="5"/>
@@ -15611,7 +15630,7 @@
       <c r="K816" s="6"/>
       <c r="L816" s="6"/>
     </row>
-    <row r="817" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A817" s="5"/>
       <c r="B817" s="5"/>
       <c r="C817" s="5"/>
@@ -15625,7 +15644,7 @@
       <c r="K817" s="6"/>
       <c r="L817" s="6"/>
     </row>
-    <row r="818" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A818" s="5"/>
       <c r="B818" s="5"/>
       <c r="C818" s="5"/>
@@ -15639,7 +15658,7 @@
       <c r="K818" s="6"/>
       <c r="L818" s="6"/>
     </row>
-    <row r="819" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A819" s="5"/>
       <c r="B819" s="5"/>
       <c r="C819" s="5"/>
@@ -15653,7 +15672,7 @@
       <c r="K819" s="6"/>
       <c r="L819" s="6"/>
     </row>
-    <row r="820" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A820" s="5"/>
       <c r="B820" s="5"/>
       <c r="C820" s="5"/>
@@ -15667,7 +15686,7 @@
       <c r="K820" s="6"/>
       <c r="L820" s="6"/>
     </row>
-    <row r="821" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A821" s="5"/>
       <c r="B821" s="5"/>
       <c r="C821" s="5"/>
@@ -15681,7 +15700,7 @@
       <c r="K821" s="6"/>
       <c r="L821" s="6"/>
     </row>
-    <row r="822" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A822" s="5"/>
       <c r="B822" s="5"/>
       <c r="C822" s="5"/>
@@ -15695,7 +15714,7 @@
       <c r="K822" s="6"/>
       <c r="L822" s="6"/>
     </row>
-    <row r="823" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A823" s="5"/>
       <c r="B823" s="5"/>
       <c r="C823" s="5"/>
@@ -15709,7 +15728,7 @@
       <c r="K823" s="6"/>
       <c r="L823" s="6"/>
     </row>
-    <row r="824" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A824" s="5"/>
       <c r="B824" s="5"/>
       <c r="C824" s="5"/>
@@ -15723,7 +15742,7 @@
       <c r="K824" s="6"/>
       <c r="L824" s="6"/>
     </row>
-    <row r="825" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A825" s="5"/>
       <c r="B825" s="5"/>
       <c r="C825" s="5"/>
@@ -15737,7 +15756,7 @@
       <c r="K825" s="6"/>
       <c r="L825" s="6"/>
     </row>
-    <row r="826" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A826" s="5"/>
       <c r="B826" s="5"/>
       <c r="C826" s="5"/>
@@ -15751,7 +15770,7 @@
       <c r="K826" s="6"/>
       <c r="L826" s="6"/>
     </row>
-    <row r="827" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A827" s="5"/>
       <c r="B827" s="5"/>
       <c r="C827" s="5"/>
@@ -15765,7 +15784,7 @@
       <c r="K827" s="6"/>
       <c r="L827" s="6"/>
     </row>
-    <row r="828" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A828" s="5"/>
       <c r="B828" s="5"/>
       <c r="C828" s="5"/>
@@ -15779,7 +15798,7 @@
       <c r="K828" s="6"/>
       <c r="L828" s="6"/>
     </row>
-    <row r="829" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A829" s="5"/>
       <c r="B829" s="5"/>
       <c r="C829" s="5"/>
@@ -15793,7 +15812,7 @@
       <c r="K829" s="6"/>
       <c r="L829" s="6"/>
     </row>
-    <row r="830" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A830" s="5"/>
       <c r="B830" s="5"/>
       <c r="C830" s="5"/>
@@ -15807,7 +15826,7 @@
       <c r="K830" s="6"/>
       <c r="L830" s="6"/>
     </row>
-    <row r="831" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A831" s="5"/>
       <c r="B831" s="5"/>
       <c r="C831" s="5"/>
@@ -15821,7 +15840,7 @@
       <c r="K831" s="6"/>
       <c r="L831" s="6"/>
     </row>
-    <row r="832" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A832" s="5"/>
       <c r="B832" s="5"/>
       <c r="C832" s="5"/>
@@ -15835,7 +15854,7 @@
       <c r="K832" s="6"/>
       <c r="L832" s="6"/>
     </row>
-    <row r="833" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A833" s="5"/>
       <c r="B833" s="5"/>
       <c r="C833" s="5"/>
@@ -15849,7 +15868,7 @@
       <c r="K833" s="6"/>
       <c r="L833" s="6"/>
     </row>
-    <row r="834" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A834" s="5"/>
       <c r="B834" s="5"/>
       <c r="C834" s="5"/>
@@ -15863,7 +15882,7 @@
       <c r="K834" s="6"/>
       <c r="L834" s="6"/>
     </row>
-    <row r="835" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A835" s="5"/>
       <c r="B835" s="5"/>
       <c r="C835" s="5"/>
@@ -15877,7 +15896,7 @@
       <c r="K835" s="6"/>
       <c r="L835" s="6"/>
     </row>
-    <row r="836" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A836" s="5"/>
       <c r="B836" s="5"/>
       <c r="C836" s="5"/>
@@ -15891,7 +15910,7 @@
       <c r="K836" s="6"/>
       <c r="L836" s="6"/>
     </row>
-    <row r="837" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A837" s="5"/>
       <c r="B837" s="5"/>
       <c r="C837" s="5"/>
@@ -15905,7 +15924,7 @@
       <c r="K837" s="6"/>
       <c r="L837" s="6"/>
     </row>
-    <row r="838" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A838" s="5"/>
       <c r="B838" s="5"/>
       <c r="C838" s="5"/>
@@ -15919,7 +15938,7 @@
       <c r="K838" s="6"/>
       <c r="L838" s="6"/>
     </row>
-    <row r="839" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A839" s="5"/>
       <c r="B839" s="5"/>
       <c r="C839" s="5"/>
@@ -15933,7 +15952,7 @@
       <c r="K839" s="6"/>
       <c r="L839" s="6"/>
     </row>
-    <row r="840" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A840" s="5"/>
       <c r="B840" s="5"/>
       <c r="C840" s="5"/>
@@ -15947,7 +15966,7 @@
       <c r="K840" s="6"/>
       <c r="L840" s="6"/>
     </row>
-    <row r="841" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A841" s="5"/>
       <c r="B841" s="5"/>
       <c r="C841" s="5"/>
@@ -15961,7 +15980,7 @@
       <c r="K841" s="6"/>
       <c r="L841" s="6"/>
     </row>
-    <row r="842" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A842" s="5"/>
       <c r="B842" s="5"/>
       <c r="C842" s="5"/>
@@ -15975,7 +15994,7 @@
       <c r="K842" s="6"/>
       <c r="L842" s="6"/>
     </row>
-    <row r="843" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A843" s="5"/>
       <c r="B843" s="5"/>
       <c r="C843" s="5"/>
@@ -15989,7 +16008,7 @@
       <c r="K843" s="6"/>
       <c r="L843" s="6"/>
     </row>
-    <row r="844" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A844" s="5"/>
       <c r="B844" s="5"/>
       <c r="C844" s="5"/>
@@ -16003,7 +16022,7 @@
       <c r="K844" s="6"/>
       <c r="L844" s="6"/>
     </row>
-    <row r="845" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A845" s="5"/>
       <c r="B845" s="5"/>
       <c r="C845" s="5"/>
@@ -16017,7 +16036,7 @@
       <c r="K845" s="6"/>
       <c r="L845" s="6"/>
     </row>
-    <row r="846" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A846" s="5"/>
       <c r="B846" s="5"/>
       <c r="C846" s="5"/>
@@ -16031,7 +16050,7 @@
       <c r="K846" s="6"/>
       <c r="L846" s="6"/>
     </row>
-    <row r="847" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A847" s="5"/>
       <c r="B847" s="5"/>
       <c r="C847" s="5"/>
@@ -16045,7 +16064,7 @@
       <c r="K847" s="6"/>
       <c r="L847" s="6"/>
     </row>
-    <row r="848" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A848" s="5"/>
       <c r="B848" s="5"/>
       <c r="C848" s="5"/>
@@ -16059,7 +16078,7 @@
       <c r="K848" s="6"/>
       <c r="L848" s="6"/>
     </row>
-    <row r="849" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A849" s="5"/>
       <c r="B849" s="5"/>
       <c r="C849" s="5"/>
@@ -16073,7 +16092,7 @@
       <c r="K849" s="6"/>
       <c r="L849" s="6"/>
     </row>
-    <row r="850" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A850" s="5"/>
       <c r="B850" s="5"/>
       <c r="C850" s="5"/>
@@ -16087,7 +16106,7 @@
       <c r="K850" s="6"/>
       <c r="L850" s="6"/>
     </row>
-    <row r="851" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A851" s="5"/>
       <c r="B851" s="5"/>
       <c r="C851" s="5"/>
@@ -16101,7 +16120,7 @@
       <c r="K851" s="6"/>
       <c r="L851" s="6"/>
     </row>
-    <row r="852" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A852" s="5"/>
       <c r="B852" s="5"/>
       <c r="C852" s="5"/>
@@ -16115,7 +16134,7 @@
       <c r="K852" s="6"/>
       <c r="L852" s="6"/>
     </row>
-    <row r="853" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A853" s="5"/>
       <c r="B853" s="5"/>
       <c r="C853" s="5"/>
@@ -16129,7 +16148,7 @@
       <c r="K853" s="6"/>
       <c r="L853" s="6"/>
     </row>
-    <row r="854" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A854" s="5"/>
       <c r="B854" s="5"/>
       <c r="C854" s="5"/>
@@ -16143,7 +16162,7 @@
       <c r="K854" s="6"/>
       <c r="L854" s="6"/>
     </row>
-    <row r="855" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A855" s="5"/>
       <c r="B855" s="5"/>
       <c r="C855" s="5"/>
@@ -16157,7 +16176,7 @@
       <c r="K855" s="6"/>
       <c r="L855" s="6"/>
     </row>
-    <row r="856" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A856" s="5"/>
       <c r="B856" s="5"/>
       <c r="C856" s="5"/>
@@ -16171,7 +16190,7 @@
       <c r="K856" s="6"/>
       <c r="L856" s="6"/>
     </row>
-    <row r="857" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A857" s="5"/>
       <c r="B857" s="5"/>
       <c r="C857" s="5"/>
@@ -16185,7 +16204,7 @@
       <c r="K857" s="6"/>
       <c r="L857" s="6"/>
     </row>
-    <row r="858" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A858" s="5"/>
       <c r="B858" s="5"/>
       <c r="C858" s="5"/>
@@ -16199,7 +16218,7 @@
       <c r="K858" s="6"/>
       <c r="L858" s="6"/>
     </row>
-    <row r="859" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A859" s="5"/>
       <c r="B859" s="5"/>
       <c r="C859" s="5"/>
@@ -16213,7 +16232,7 @@
       <c r="K859" s="6"/>
       <c r="L859" s="6"/>
     </row>
-    <row r="860" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A860" s="5"/>
       <c r="B860" s="5"/>
       <c r="C860" s="5"/>
@@ -16227,7 +16246,7 @@
       <c r="K860" s="6"/>
       <c r="L860" s="6"/>
     </row>
-    <row r="861" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A861" s="5"/>
       <c r="B861" s="5"/>
       <c r="C861" s="5"/>
@@ -16241,7 +16260,7 @@
       <c r="K861" s="6"/>
       <c r="L861" s="6"/>
     </row>
-    <row r="862" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A862" s="5"/>
       <c r="B862" s="5"/>
       <c r="C862" s="5"/>
@@ -16255,7 +16274,7 @@
       <c r="K862" s="6"/>
       <c r="L862" s="6"/>
     </row>
-    <row r="863" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A863" s="5"/>
       <c r="B863" s="5"/>
       <c r="C863" s="5"/>
@@ -16269,7 +16288,7 @@
       <c r="K863" s="6"/>
       <c r="L863" s="6"/>
     </row>
-    <row r="864" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A864" s="5"/>
       <c r="B864" s="5"/>
       <c r="C864" s="5"/>
@@ -16283,7 +16302,7 @@
       <c r="K864" s="6"/>
       <c r="L864" s="6"/>
     </row>
-    <row r="865" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A865" s="5"/>
       <c r="B865" s="5"/>
       <c r="C865" s="5"/>
@@ -16297,7 +16316,7 @@
       <c r="K865" s="6"/>
       <c r="L865" s="6"/>
     </row>
-    <row r="866" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A866" s="5"/>
       <c r="B866" s="5"/>
       <c r="C866" s="5"/>
@@ -16311,7 +16330,7 @@
       <c r="K866" s="6"/>
       <c r="L866" s="6"/>
     </row>
-    <row r="867" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A867" s="5"/>
       <c r="B867" s="5"/>
       <c r="C867" s="5"/>
@@ -16325,7 +16344,7 @@
       <c r="K867" s="6"/>
       <c r="L867" s="6"/>
     </row>
-    <row r="868" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A868" s="5"/>
       <c r="B868" s="5"/>
       <c r="C868" s="5"/>
@@ -16339,7 +16358,7 @@
       <c r="K868" s="6"/>
       <c r="L868" s="6"/>
     </row>
-    <row r="869" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A869" s="5"/>
       <c r="B869" s="5"/>
       <c r="C869" s="5"/>
@@ -16353,7 +16372,7 @@
       <c r="K869" s="6"/>
       <c r="L869" s="6"/>
     </row>
-    <row r="870" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A870" s="5"/>
       <c r="B870" s="5"/>
       <c r="C870" s="5"/>
@@ -16367,7 +16386,7 @@
       <c r="K870" s="6"/>
       <c r="L870" s="6"/>
     </row>
-    <row r="871" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A871" s="5"/>
       <c r="B871" s="5"/>
       <c r="C871" s="5"/>
@@ -16381,7 +16400,7 @@
       <c r="K871" s="6"/>
       <c r="L871" s="6"/>
     </row>
-    <row r="872" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A872" s="5"/>
       <c r="B872" s="5"/>
       <c r="C872" s="5"/>
@@ -16395,7 +16414,7 @@
       <c r="K872" s="6"/>
       <c r="L872" s="6"/>
     </row>
-    <row r="873" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A873" s="5"/>
       <c r="B873" s="5"/>
       <c r="C873" s="5"/>
@@ -16409,7 +16428,7 @@
       <c r="K873" s="6"/>
       <c r="L873" s="6"/>
     </row>
-    <row r="874" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A874" s="5"/>
       <c r="B874" s="5"/>
       <c r="C874" s="5"/>
@@ -16423,7 +16442,7 @@
       <c r="K874" s="6"/>
       <c r="L874" s="6"/>
     </row>
-    <row r="875" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A875" s="5"/>
       <c r="B875" s="5"/>
       <c r="C875" s="5"/>
@@ -16437,7 +16456,7 @@
       <c r="K875" s="6"/>
       <c r="L875" s="6"/>
     </row>
-    <row r="876" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A876" s="5"/>
       <c r="B876" s="5"/>
       <c r="C876" s="5"/>
@@ -16451,7 +16470,7 @@
       <c r="K876" s="6"/>
       <c r="L876" s="6"/>
     </row>
-    <row r="877" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A877" s="5"/>
       <c r="B877" s="5"/>
       <c r="C877" s="5"/>
@@ -16465,7 +16484,7 @@
       <c r="K877" s="6"/>
       <c r="L877" s="6"/>
     </row>
-    <row r="878" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A878" s="5"/>
       <c r="B878" s="5"/>
       <c r="C878" s="5"/>
@@ -16479,7 +16498,7 @@
       <c r="K878" s="6"/>
       <c r="L878" s="6"/>
     </row>
-    <row r="879" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A879" s="5"/>
       <c r="B879" s="5"/>
       <c r="C879" s="5"/>
@@ -16493,7 +16512,7 @@
       <c r="K879" s="6"/>
       <c r="L879" s="6"/>
     </row>
-    <row r="880" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A880" s="5"/>
       <c r="B880" s="5"/>
       <c r="C880" s="5"/>
@@ -16507,7 +16526,7 @@
       <c r="K880" s="6"/>
       <c r="L880" s="6"/>
     </row>
-    <row r="881" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A881" s="5"/>
       <c r="B881" s="5"/>
       <c r="C881" s="5"/>
@@ -16521,7 +16540,7 @@
       <c r="K881" s="6"/>
       <c r="L881" s="6"/>
     </row>
-    <row r="882" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A882" s="5"/>
       <c r="B882" s="5"/>
       <c r="C882" s="5"/>
@@ -16535,7 +16554,7 @@
       <c r="K882" s="6"/>
       <c r="L882" s="6"/>
     </row>
-    <row r="883" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A883" s="5"/>
       <c r="B883" s="5"/>
       <c r="C883" s="5"/>
@@ -16549,7 +16568,7 @@
       <c r="K883" s="6"/>
       <c r="L883" s="6"/>
     </row>
-    <row r="884" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A884" s="5"/>
       <c r="B884" s="5"/>
       <c r="C884" s="5"/>
@@ -16563,7 +16582,7 @@
       <c r="K884" s="6"/>
       <c r="L884" s="6"/>
     </row>
-    <row r="885" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A885" s="5"/>
       <c r="B885" s="5"/>
       <c r="C885" s="5"/>
@@ -16577,7 +16596,7 @@
       <c r="K885" s="6"/>
       <c r="L885" s="6"/>
     </row>
-    <row r="886" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A886" s="5"/>
       <c r="B886" s="5"/>
       <c r="C886" s="5"/>
@@ -16591,7 +16610,7 @@
       <c r="K886" s="6"/>
       <c r="L886" s="6"/>
     </row>
-    <row r="887" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A887" s="5"/>
       <c r="B887" s="5"/>
       <c r="C887" s="5"/>
@@ -16605,7 +16624,7 @@
       <c r="K887" s="6"/>
       <c r="L887" s="6"/>
     </row>
-    <row r="888" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A888" s="5"/>
       <c r="B888" s="5"/>
       <c r="C888" s="5"/>
@@ -16619,7 +16638,7 @@
       <c r="K888" s="6"/>
       <c r="L888" s="6"/>
     </row>
-    <row r="889" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A889" s="5"/>
       <c r="B889" s="5"/>
       <c r="C889" s="5"/>
@@ -16633,7 +16652,7 @@
       <c r="K889" s="6"/>
       <c r="L889" s="6"/>
     </row>
-    <row r="890" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A890" s="5"/>
       <c r="B890" s="5"/>
       <c r="C890" s="5"/>
@@ -16647,7 +16666,7 @@
       <c r="K890" s="6"/>
       <c r="L890" s="6"/>
     </row>
-    <row r="891" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A891" s="5"/>
       <c r="B891" s="5"/>
       <c r="C891" s="5"/>
@@ -16661,7 +16680,7 @@
       <c r="K891" s="6"/>
       <c r="L891" s="6"/>
     </row>
-    <row r="892" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A892" s="5"/>
       <c r="B892" s="5"/>
       <c r="C892" s="5"/>
@@ -16675,7 +16694,7 @@
       <c r="K892" s="6"/>
       <c r="L892" s="6"/>
     </row>
-    <row r="893" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A893" s="5"/>
       <c r="B893" s="5"/>
       <c r="C893" s="5"/>
@@ -16689,7 +16708,7 @@
       <c r="K893" s="6"/>
       <c r="L893" s="6"/>
     </row>
-    <row r="894" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A894" s="5"/>
       <c r="B894" s="5"/>
       <c r="C894" s="5"/>
@@ -16703,7 +16722,7 @@
       <c r="K894" s="6"/>
       <c r="L894" s="6"/>
     </row>
-    <row r="895" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A895" s="5"/>
       <c r="B895" s="5"/>
       <c r="C895" s="5"/>
@@ -16717,7 +16736,7 @@
       <c r="K895" s="6"/>
       <c r="L895" s="6"/>
     </row>
-    <row r="896" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A896" s="5"/>
       <c r="B896" s="5"/>
       <c r="C896" s="5"/>
@@ -16731,7 +16750,7 @@
       <c r="K896" s="6"/>
       <c r="L896" s="6"/>
     </row>
-    <row r="897" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A897" s="5"/>
       <c r="B897" s="5"/>
       <c r="C897" s="5"/>
@@ -16745,7 +16764,7 @@
       <c r="K897" s="6"/>
       <c r="L897" s="6"/>
     </row>
-    <row r="898" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A898" s="5"/>
       <c r="B898" s="5"/>
       <c r="C898" s="5"/>
@@ -16759,7 +16778,7 @@
       <c r="K898" s="6"/>
       <c r="L898" s="6"/>
     </row>
-    <row r="899" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A899" s="5"/>
       <c r="B899" s="5"/>
       <c r="C899" s="5"/>
@@ -16773,7 +16792,7 @@
       <c r="K899" s="6"/>
       <c r="L899" s="6"/>
     </row>
-    <row r="900" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A900" s="5"/>
       <c r="B900" s="5"/>
       <c r="C900" s="5"/>
@@ -16787,7 +16806,7 @@
       <c r="K900" s="6"/>
       <c r="L900" s="6"/>
     </row>
-    <row r="901" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A901" s="5"/>
       <c r="B901" s="5"/>
       <c r="C901" s="5"/>
@@ -16801,7 +16820,7 @@
       <c r="K901" s="6"/>
       <c r="L901" s="6"/>
     </row>
-    <row r="902" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A902" s="5"/>
       <c r="B902" s="5"/>
       <c r="C902" s="5"/>
@@ -16815,7 +16834,7 @@
       <c r="K902" s="6"/>
       <c r="L902" s="6"/>
     </row>
-    <row r="903" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A903" s="5"/>
       <c r="B903" s="5"/>
       <c r="C903" s="5"/>
@@ -16829,7 +16848,7 @@
       <c r="K903" s="6"/>
       <c r="L903" s="6"/>
     </row>
-    <row r="904" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A904" s="5"/>
       <c r="B904" s="5"/>
       <c r="C904" s="5"/>
@@ -16843,7 +16862,7 @@
       <c r="K904" s="6"/>
       <c r="L904" s="6"/>
     </row>
-    <row r="905" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A905" s="5"/>
       <c r="B905" s="5"/>
       <c r="C905" s="5"/>
@@ -16857,7 +16876,7 @@
       <c r="K905" s="6"/>
       <c r="L905" s="6"/>
     </row>
-    <row r="906" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A906" s="5"/>
       <c r="B906" s="5"/>
       <c r="C906" s="5"/>
@@ -16871,7 +16890,7 @@
       <c r="K906" s="6"/>
       <c r="L906" s="6"/>
     </row>
-    <row r="907" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A907" s="5"/>
       <c r="B907" s="5"/>
       <c r="C907" s="5"/>
@@ -16885,7 +16904,7 @@
       <c r="K907" s="6"/>
       <c r="L907" s="6"/>
     </row>
-    <row r="908" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A908" s="5"/>
       <c r="B908" s="5"/>
       <c r="C908" s="5"/>
@@ -16899,7 +16918,7 @@
       <c r="K908" s="6"/>
       <c r="L908" s="6"/>
     </row>
-    <row r="909" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A909" s="5"/>
       <c r="B909" s="5"/>
       <c r="C909" s="5"/>
@@ -16913,7 +16932,7 @@
       <c r="K909" s="6"/>
       <c r="L909" s="6"/>
     </row>
-    <row r="910" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A910" s="5"/>
       <c r="B910" s="5"/>
       <c r="C910" s="5"/>
@@ -16927,7 +16946,7 @@
       <c r="K910" s="6"/>
       <c r="L910" s="6"/>
     </row>
-    <row r="911" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A911" s="5"/>
       <c r="B911" s="5"/>
       <c r="C911" s="5"/>
@@ -16941,7 +16960,7 @@
       <c r="K911" s="6"/>
       <c r="L911" s="6"/>
     </row>
-    <row r="912" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A912" s="5"/>
       <c r="B912" s="5"/>
       <c r="C912" s="5"/>
@@ -16955,7 +16974,7 @@
       <c r="K912" s="6"/>
       <c r="L912" s="6"/>
     </row>
-    <row r="913" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A913" s="5"/>
       <c r="B913" s="5"/>
       <c r="C913" s="5"/>
@@ -16969,7 +16988,7 @@
       <c r="K913" s="6"/>
       <c r="L913" s="6"/>
     </row>
-    <row r="914" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A914" s="5"/>
       <c r="B914" s="5"/>
       <c r="C914" s="5"/>
@@ -16983,7 +17002,7 @@
       <c r="K914" s="6"/>
       <c r="L914" s="6"/>
     </row>
-    <row r="915" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A915" s="5"/>
       <c r="B915" s="5"/>
       <c r="C915" s="5"/>
@@ -16997,7 +17016,7 @@
       <c r="K915" s="6"/>
       <c r="L915" s="6"/>
     </row>
-    <row r="916" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A916" s="5"/>
       <c r="B916" s="5"/>
       <c r="C916" s="5"/>
@@ -17011,7 +17030,7 @@
       <c r="K916" s="6"/>
       <c r="L916" s="6"/>
     </row>
-    <row r="917" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A917" s="5"/>
       <c r="B917" s="5"/>
       <c r="C917" s="5"/>
@@ -17025,7 +17044,7 @@
       <c r="K917" s="6"/>
       <c r="L917" s="6"/>
     </row>
-    <row r="918" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A918" s="5"/>
       <c r="B918" s="5"/>
       <c r="C918" s="5"/>
@@ -17039,7 +17058,7 @@
       <c r="K918" s="6"/>
       <c r="L918" s="6"/>
     </row>
-    <row r="919" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A919" s="5"/>
       <c r="B919" s="5"/>
       <c r="C919" s="5"/>
@@ -17053,7 +17072,7 @@
       <c r="K919" s="6"/>
       <c r="L919" s="6"/>
     </row>
-    <row r="920" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A920" s="5"/>
       <c r="B920" s="5"/>
       <c r="C920" s="5"/>
@@ -17067,7 +17086,7 @@
       <c r="K920" s="6"/>
       <c r="L920" s="6"/>
     </row>
-    <row r="921" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A921" s="5"/>
       <c r="B921" s="5"/>
       <c r="C921" s="5"/>
@@ -17081,7 +17100,7 @@
       <c r="K921" s="6"/>
       <c r="L921" s="6"/>
     </row>
-    <row r="922" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A922" s="5"/>
       <c r="B922" s="5"/>
       <c r="C922" s="5"/>
@@ -17095,7 +17114,7 @@
       <c r="K922" s="6"/>
       <c r="L922" s="6"/>
     </row>
-    <row r="923" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A923" s="5"/>
       <c r="B923" s="5"/>
       <c r="C923" s="5"/>
@@ -17109,7 +17128,7 @@
       <c r="K923" s="6"/>
       <c r="L923" s="6"/>
     </row>
-    <row r="924" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A924" s="5"/>
       <c r="B924" s="5"/>
       <c r="C924" s="5"/>
@@ -17123,7 +17142,7 @@
       <c r="K924" s="6"/>
       <c r="L924" s="6"/>
     </row>
-    <row r="925" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A925" s="5"/>
       <c r="B925" s="5"/>
       <c r="C925" s="5"/>
@@ -17137,7 +17156,7 @@
       <c r="K925" s="6"/>
       <c r="L925" s="6"/>
     </row>
-    <row r="926" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A926" s="5"/>
       <c r="B926" s="5"/>
       <c r="C926" s="5"/>
@@ -17151,7 +17170,7 @@
       <c r="K926" s="6"/>
       <c r="L926" s="6"/>
     </row>
-    <row r="927" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A927" s="5"/>
       <c r="B927" s="5"/>
       <c r="C927" s="5"/>
@@ -17165,7 +17184,7 @@
       <c r="K927" s="6"/>
       <c r="L927" s="6"/>
     </row>
-    <row r="928" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A928" s="5"/>
       <c r="B928" s="5"/>
       <c r="C928" s="5"/>
@@ -17179,7 +17198,7 @@
       <c r="K928" s="6"/>
       <c r="L928" s="6"/>
     </row>
-    <row r="929" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A929" s="5"/>
       <c r="B929" s="5"/>
       <c r="C929" s="5"/>
@@ -17193,7 +17212,7 @@
       <c r="K929" s="6"/>
       <c r="L929" s="6"/>
     </row>
-    <row r="930" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A930" s="5"/>
       <c r="B930" s="5"/>
       <c r="C930" s="5"/>
@@ -17207,7 +17226,7 @@
       <c r="K930" s="6"/>
       <c r="L930" s="6"/>
     </row>
-    <row r="931" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A931" s="5"/>
       <c r="B931" s="5"/>
       <c r="C931" s="5"/>
@@ -17221,7 +17240,7 @@
       <c r="K931" s="6"/>
       <c r="L931" s="6"/>
     </row>
-    <row r="932" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A932" s="5"/>
       <c r="B932" s="5"/>
       <c r="C932" s="5"/>
@@ -17235,7 +17254,7 @@
       <c r="K932" s="6"/>
       <c r="L932" s="6"/>
     </row>
-    <row r="933" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A933" s="5"/>
       <c r="B933" s="5"/>
       <c r="C933" s="5"/>
@@ -17249,7 +17268,7 @@
       <c r="K933" s="6"/>
       <c r="L933" s="6"/>
     </row>
-    <row r="934" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A934" s="5"/>
       <c r="B934" s="5"/>
       <c r="C934" s="5"/>
@@ -17263,7 +17282,7 @@
       <c r="K934" s="6"/>
       <c r="L934" s="6"/>
     </row>
-    <row r="935" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A935" s="5"/>
       <c r="B935" s="5"/>
       <c r="C935" s="5"/>
@@ -17277,7 +17296,7 @@
       <c r="K935" s="6"/>
       <c r="L935" s="6"/>
     </row>
-    <row r="936" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A936" s="5"/>
       <c r="B936" s="5"/>
       <c r="C936" s="5"/>
@@ -17291,7 +17310,7 @@
       <c r="K936" s="6"/>
       <c r="L936" s="6"/>
     </row>
-    <row r="937" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A937" s="5"/>
       <c r="B937" s="5"/>
       <c r="C937" s="5"/>
@@ -17305,7 +17324,7 @@
       <c r="K937" s="6"/>
       <c r="L937" s="6"/>
     </row>
-    <row r="938" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A938" s="5"/>
       <c r="B938" s="5"/>
       <c r="C938" s="5"/>
@@ -17319,7 +17338,7 @@
       <c r="K938" s="6"/>
       <c r="L938" s="6"/>
     </row>
-    <row r="939" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A939" s="5"/>
       <c r="B939" s="5"/>
       <c r="C939" s="5"/>
@@ -17333,7 +17352,7 @@
       <c r="K939" s="6"/>
       <c r="L939" s="6"/>
     </row>
-    <row r="940" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A940" s="5"/>
       <c r="B940" s="5"/>
       <c r="C940" s="5"/>
@@ -17347,7 +17366,7 @@
       <c r="K940" s="6"/>
       <c r="L940" s="6"/>
     </row>
-    <row r="941" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A941" s="5"/>
       <c r="B941" s="5"/>
       <c r="C941" s="5"/>
@@ -17361,7 +17380,7 @@
       <c r="K941" s="6"/>
       <c r="L941" s="6"/>
     </row>
-    <row r="942" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A942" s="5"/>
       <c r="B942" s="5"/>
       <c r="C942" s="5"/>
@@ -17375,7 +17394,7 @@
       <c r="K942" s="6"/>
       <c r="L942" s="6"/>
     </row>
-    <row r="943" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A943" s="5"/>
       <c r="B943" s="5"/>
       <c r="C943" s="5"/>
@@ -17389,7 +17408,7 @@
       <c r="K943" s="6"/>
       <c r="L943" s="6"/>
     </row>
-    <row r="944" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A944" s="5"/>
       <c r="B944" s="5"/>
       <c r="C944" s="5"/>
@@ -17403,7 +17422,7 @@
       <c r="K944" s="6"/>
       <c r="L944" s="6"/>
     </row>
-    <row r="945" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A945" s="5"/>
       <c r="B945" s="5"/>
       <c r="C945" s="5"/>
@@ -17417,7 +17436,7 @@
       <c r="K945" s="6"/>
       <c r="L945" s="6"/>
     </row>
-    <row r="946" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A946" s="5"/>
       <c r="B946" s="5"/>
       <c r="C946" s="5"/>
@@ -17431,7 +17450,7 @@
       <c r="K946" s="6"/>
       <c r="L946" s="6"/>
     </row>
-    <row r="947" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A947" s="5"/>
       <c r="B947" s="5"/>
       <c r="C947" s="5"/>
@@ -17445,7 +17464,7 @@
       <c r="K947" s="6"/>
       <c r="L947" s="6"/>
     </row>
-    <row r="948" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A948" s="5"/>
       <c r="B948" s="5"/>
       <c r="C948" s="5"/>
@@ -17459,7 +17478,7 @@
       <c r="K948" s="6"/>
       <c r="L948" s="6"/>
     </row>
-    <row r="949" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A949" s="5"/>
       <c r="B949" s="5"/>
       <c r="C949" s="5"/>
@@ -17473,7 +17492,7 @@
       <c r="K949" s="6"/>
       <c r="L949" s="6"/>
     </row>
-    <row r="950" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A950" s="5"/>
       <c r="B950" s="5"/>
       <c r="C950" s="5"/>
@@ -17487,7 +17506,7 @@
       <c r="K950" s="6"/>
       <c r="L950" s="6"/>
     </row>
-    <row r="951" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A951" s="5"/>
       <c r="B951" s="5"/>
       <c r="C951" s="5"/>
@@ -17501,7 +17520,7 @@
       <c r="K951" s="6"/>
       <c r="L951" s="6"/>
     </row>
-    <row r="952" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A952" s="5"/>
       <c r="B952" s="5"/>
       <c r="C952" s="5"/>
@@ -17515,7 +17534,7 @@
       <c r="K952" s="6"/>
       <c r="L952" s="6"/>
     </row>
-    <row r="953" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A953" s="5"/>
       <c r="B953" s="5"/>
       <c r="C953" s="5"/>
@@ -17529,7 +17548,7 @@
       <c r="K953" s="6"/>
       <c r="L953" s="6"/>
     </row>
-    <row r="954" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A954" s="5"/>
       <c r="B954" s="5"/>
       <c r="C954" s="5"/>
@@ -17543,7 +17562,7 @@
       <c r="K954" s="6"/>
       <c r="L954" s="6"/>
     </row>
-    <row r="955" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A955" s="5"/>
       <c r="B955" s="5"/>
       <c r="C955" s="5"/>
@@ -17557,7 +17576,7 @@
       <c r="K955" s="6"/>
       <c r="L955" s="6"/>
     </row>
-    <row r="956" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A956" s="5"/>
       <c r="B956" s="5"/>
       <c r="C956" s="5"/>
@@ -17571,7 +17590,7 @@
       <c r="K956" s="6"/>
       <c r="L956" s="6"/>
     </row>
-    <row r="957" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A957" s="5"/>
       <c r="B957" s="5"/>
       <c r="C957" s="5"/>
@@ -17585,7 +17604,7 @@
       <c r="K957" s="6"/>
       <c r="L957" s="6"/>
     </row>
-    <row r="958" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A958" s="5"/>
       <c r="B958" s="5"/>
       <c r="C958" s="5"/>
@@ -17599,7 +17618,7 @@
       <c r="K958" s="6"/>
       <c r="L958" s="6"/>
     </row>
-    <row r="959" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A959" s="5"/>
       <c r="B959" s="5"/>
       <c r="C959" s="5"/>
@@ -17613,7 +17632,7 @@
       <c r="K959" s="6"/>
       <c r="L959" s="6"/>
     </row>
-    <row r="960" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A960" s="5"/>
       <c r="B960" s="5"/>
       <c r="C960" s="5"/>
@@ -17627,7 +17646,7 @@
       <c r="K960" s="6"/>
       <c r="L960" s="6"/>
     </row>
-    <row r="961" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A961" s="5"/>
       <c r="B961" s="5"/>
       <c r="C961" s="5"/>
@@ -17641,7 +17660,7 @@
       <c r="K961" s="6"/>
       <c r="L961" s="6"/>
     </row>
-    <row r="962" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A962" s="5"/>
       <c r="B962" s="5"/>
       <c r="C962" s="5"/>
@@ -17655,7 +17674,7 @@
       <c r="K962" s="6"/>
       <c r="L962" s="6"/>
     </row>
-    <row r="963" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A963" s="5"/>
       <c r="B963" s="5"/>
       <c r="C963" s="5"/>
@@ -17669,7 +17688,7 @@
       <c r="K963" s="6"/>
       <c r="L963" s="6"/>
     </row>
-    <row r="964" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A964" s="5"/>
       <c r="B964" s="5"/>
       <c r="C964" s="5"/>
@@ -17683,7 +17702,7 @@
       <c r="K964" s="6"/>
       <c r="L964" s="6"/>
     </row>
-    <row r="965" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A965" s="5"/>
       <c r="B965" s="5"/>
       <c r="C965" s="5"/>
@@ -17697,7 +17716,7 @@
       <c r="K965" s="6"/>
       <c r="L965" s="6"/>
     </row>
-    <row r="966" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A966" s="5"/>
       <c r="B966" s="5"/>
       <c r="C966" s="5"/>
@@ -17711,7 +17730,7 @@
       <c r="K966" s="6"/>
       <c r="L966" s="6"/>
     </row>
-    <row r="967" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A967" s="5"/>
       <c r="B967" s="5"/>
       <c r="C967" s="5"/>
@@ -17725,7 +17744,7 @@
       <c r="K967" s="6"/>
       <c r="L967" s="6"/>
     </row>
-    <row r="968" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A968" s="5"/>
       <c r="B968" s="5"/>
       <c r="C968" s="5"/>
@@ -17739,7 +17758,7 @@
       <c r="K968" s="6"/>
       <c r="L968" s="6"/>
     </row>
-    <row r="969" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A969" s="5"/>
       <c r="B969" s="5"/>
       <c r="C969" s="5"/>
@@ -17753,7 +17772,7 @@
       <c r="K969" s="6"/>
       <c r="L969" s="6"/>
     </row>
-    <row r="970" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A970" s="5"/>
       <c r="B970" s="5"/>
       <c r="C970" s="5"/>
@@ -17767,7 +17786,7 @@
       <c r="K970" s="6"/>
       <c r="L970" s="6"/>
     </row>
-    <row r="971" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A971" s="5"/>
       <c r="B971" s="5"/>
       <c r="C971" s="5"/>
@@ -17781,7 +17800,7 @@
       <c r="K971" s="6"/>
       <c r="L971" s="6"/>
     </row>
-    <row r="972" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A972" s="5"/>
       <c r="B972" s="5"/>
       <c r="C972" s="5"/>
@@ -17795,7 +17814,7 @@
       <c r="K972" s="6"/>
       <c r="L972" s="6"/>
     </row>
-    <row r="973" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A973" s="5"/>
       <c r="B973" s="5"/>
       <c r="C973" s="5"/>
@@ -17809,7 +17828,7 @@
       <c r="K973" s="6"/>
       <c r="L973" s="6"/>
     </row>
-    <row r="974" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A974" s="5"/>
       <c r="B974" s="5"/>
       <c r="C974" s="5"/>
@@ -17823,7 +17842,7 @@
       <c r="K974" s="6"/>
       <c r="L974" s="6"/>
     </row>
-    <row r="975" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A975" s="5"/>
       <c r="B975" s="5"/>
       <c r="C975" s="5"/>
@@ -17837,7 +17856,7 @@
       <c r="K975" s="6"/>
       <c r="L975" s="6"/>
     </row>
-    <row r="976" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A976" s="5"/>
       <c r="B976" s="5"/>
       <c r="C976" s="5"/>
@@ -17851,7 +17870,7 @@
       <c r="K976" s="6"/>
       <c r="L976" s="6"/>
     </row>
-    <row r="977" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A977" s="5"/>
       <c r="B977" s="5"/>
       <c r="C977" s="5"/>
@@ -17865,7 +17884,7 @@
       <c r="K977" s="6"/>
       <c r="L977" s="6"/>
     </row>
-    <row r="978" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A978" s="5"/>
       <c r="B978" s="5"/>
       <c r="C978" s="5"/>
@@ -17879,7 +17898,7 @@
       <c r="K978" s="6"/>
       <c r="L978" s="6"/>
     </row>
-    <row r="979" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A979" s="5"/>
       <c r="B979" s="5"/>
       <c r="C979" s="5"/>
@@ -17893,7 +17912,7 @@
       <c r="K979" s="6"/>
       <c r="L979" s="6"/>
     </row>
-    <row r="980" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A980" s="5"/>
       <c r="B980" s="5"/>
       <c r="C980" s="5"/>
@@ -17907,7 +17926,7 @@
       <c r="K980" s="6"/>
       <c r="L980" s="6"/>
     </row>
-    <row r="981" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A981" s="5"/>
       <c r="B981" s="5"/>
       <c r="C981" s="5"/>
@@ -17921,7 +17940,7 @@
       <c r="K981" s="6"/>
       <c r="L981" s="6"/>
     </row>
-    <row r="982" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A982" s="5"/>
       <c r="B982" s="5"/>
       <c r="C982" s="5"/>
@@ -17935,7 +17954,7 @@
       <c r="K982" s="6"/>
       <c r="L982" s="6"/>
     </row>
-    <row r="983" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A983" s="5"/>
       <c r="B983" s="5"/>
       <c r="C983" s="5"/>
@@ -17949,7 +17968,7 @@
       <c r="K983" s="6"/>
       <c r="L983" s="6"/>
     </row>
-    <row r="984" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A984" s="5"/>
       <c r="B984" s="5"/>
       <c r="C984" s="5"/>
@@ -17963,7 +17982,7 @@
       <c r="K984" s="6"/>
       <c r="L984" s="6"/>
     </row>
-    <row r="985" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A985" s="5"/>
       <c r="B985" s="5"/>
       <c r="C985" s="5"/>
@@ -17977,7 +17996,7 @@
       <c r="K985" s="6"/>
       <c r="L985" s="6"/>
     </row>
-    <row r="986" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A986" s="5"/>
       <c r="B986" s="5"/>
       <c r="C986" s="5"/>
@@ -17991,7 +18010,7 @@
       <c r="K986" s="6"/>
       <c r="L986" s="6"/>
     </row>
-    <row r="987" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A987" s="5"/>
       <c r="B987" s="5"/>
       <c r="C987" s="5"/>
@@ -18005,7 +18024,7 @@
       <c r="K987" s="6"/>
       <c r="L987" s="6"/>
     </row>
-    <row r="988" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A988" s="5"/>
       <c r="B988" s="5"/>
       <c r="C988" s="5"/>
@@ -18019,7 +18038,7 @@
       <c r="K988" s="6"/>
       <c r="L988" s="6"/>
     </row>
-    <row r="989" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A989" s="5"/>
       <c r="B989" s="5"/>
       <c r="C989" s="5"/>
@@ -18033,7 +18052,7 @@
       <c r="K989" s="6"/>
       <c r="L989" s="6"/>
     </row>
-    <row r="990" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A990" s="5"/>
       <c r="B990" s="5"/>
       <c r="C990" s="5"/>
@@ -18047,7 +18066,7 @@
       <c r="K990" s="6"/>
       <c r="L990" s="6"/>
     </row>
-    <row r="991" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A991" s="5"/>
       <c r="B991" s="5"/>
       <c r="C991" s="5"/>
@@ -18061,7 +18080,7 @@
       <c r="K991" s="6"/>
       <c r="L991" s="6"/>
     </row>
-    <row r="992" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A992" s="5"/>
       <c r="B992" s="5"/>
       <c r="C992" s="5"/>
@@ -18075,7 +18094,7 @@
       <c r="K992" s="6"/>
       <c r="L992" s="6"/>
     </row>
-    <row r="993" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A993" s="5"/>
       <c r="B993" s="5"/>
       <c r="C993" s="5"/>
@@ -18089,7 +18108,7 @@
       <c r="K993" s="6"/>
       <c r="L993" s="6"/>
     </row>
-    <row r="994" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A994" s="5"/>
       <c r="B994" s="5"/>
       <c r="C994" s="5"/>
@@ -18103,7 +18122,7 @@
       <c r="K994" s="6"/>
       <c r="L994" s="6"/>
     </row>
-    <row r="995" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A995" s="5"/>
       <c r="B995" s="5"/>
       <c r="C995" s="5"/>
@@ -18117,7 +18136,7 @@
       <c r="K995" s="6"/>
       <c r="L995" s="6"/>
     </row>
-    <row r="996" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A996" s="5"/>
       <c r="B996" s="5"/>
       <c r="C996" s="5"/>
@@ -18131,7 +18150,7 @@
       <c r="K996" s="6"/>
       <c r="L996" s="6"/>
     </row>
-    <row r="997" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A997" s="5"/>
       <c r="B997" s="5"/>
       <c r="C997" s="5"/>
@@ -18145,7 +18164,7 @@
       <c r="K997" s="6"/>
       <c r="L997" s="6"/>
     </row>
-    <row r="998" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="998" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A998" s="5"/>
       <c r="B998" s="5"/>
       <c r="C998" s="5"/>
@@ -18159,7 +18178,7 @@
       <c r="K998" s="6"/>
       <c r="L998" s="6"/>
     </row>
-    <row r="999" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="999" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A999" s="5"/>
       <c r="B999" s="5"/>
       <c r="C999" s="5"/>
@@ -18173,7 +18192,7 @@
       <c r="K999" s="6"/>
       <c r="L999" s="6"/>
     </row>
-    <row r="1000" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1000" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1000" s="5"/>
       <c r="B1000" s="5"/>
       <c r="C1000" s="5"/>
@@ -18187,7 +18206,7 @@
       <c r="K1000" s="6"/>
       <c r="L1000" s="6"/>
     </row>
-    <row r="1001" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1001" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1001" s="5"/>
       <c r="B1001" s="5"/>
       <c r="C1001" s="5"/>
@@ -18201,7 +18220,7 @@
       <c r="K1001" s="6"/>
       <c r="L1001" s="6"/>
     </row>
-    <row r="1002" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1002" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1002" s="5"/>
       <c r="B1002" s="5"/>
       <c r="C1002" s="5"/>
@@ -18215,7 +18234,7 @@
       <c r="K1002" s="6"/>
       <c r="L1002" s="6"/>
     </row>
-    <row r="1003" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1003" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1003" s="5"/>
       <c r="B1003" s="5"/>
       <c r="C1003" s="5"/>
@@ -18229,7 +18248,7 @@
       <c r="K1003" s="6"/>
       <c r="L1003" s="6"/>
     </row>
-    <row r="1004" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1004" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1004" s="5"/>
       <c r="B1004" s="5"/>
       <c r="C1004" s="5"/>
@@ -18243,7 +18262,7 @@
       <c r="K1004" s="6"/>
       <c r="L1004" s="6"/>
     </row>
-    <row r="1005" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1005" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1005" s="5"/>
       <c r="B1005" s="5"/>
       <c r="C1005" s="5"/>
@@ -18257,7 +18276,7 @@
       <c r="K1005" s="6"/>
       <c r="L1005" s="6"/>
     </row>
-    <row r="1006" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1006" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1006" s="5"/>
       <c r="B1006" s="5"/>
       <c r="C1006" s="5"/>
@@ -18271,7 +18290,7 @@
       <c r="K1006" s="6"/>
       <c r="L1006" s="6"/>
     </row>
-    <row r="1007" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1007" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1007" s="5"/>
       <c r="B1007" s="5"/>
       <c r="C1007" s="5"/>
@@ -18285,7 +18304,7 @@
       <c r="K1007" s="6"/>
       <c r="L1007" s="6"/>
     </row>
-    <row r="1008" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1008" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1008" s="5"/>
       <c r="B1008" s="5"/>
       <c r="C1008" s="5"/>
@@ -18299,7 +18318,7 @@
       <c r="K1008" s="6"/>
       <c r="L1008" s="6"/>
     </row>
-    <row r="1009" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1009" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1009" s="5"/>
       <c r="B1009" s="5"/>
       <c r="C1009" s="5"/>
@@ -18313,7 +18332,7 @@
       <c r="K1009" s="6"/>
       <c r="L1009" s="6"/>
     </row>
-    <row r="1010" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1010" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1010" s="5"/>
       <c r="B1010" s="5"/>
       <c r="C1010" s="5"/>
@@ -18327,7 +18346,7 @@
       <c r="K1010" s="6"/>
       <c r="L1010" s="6"/>
     </row>
-    <row r="1011" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1011" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1011" s="5"/>
       <c r="B1011" s="5"/>
       <c r="C1011" s="5"/>
@@ -18341,7 +18360,7 @@
       <c r="K1011" s="6"/>
       <c r="L1011" s="6"/>
     </row>
-    <row r="1012" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1012" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1012" s="5"/>
       <c r="B1012" s="5"/>
       <c r="C1012" s="5"/>
@@ -18355,7 +18374,7 @@
       <c r="K1012" s="6"/>
       <c r="L1012" s="6"/>
     </row>
-    <row r="1013" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1013" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1013" s="5"/>
       <c r="B1013" s="5"/>
       <c r="C1013" s="5"/>
@@ -18369,7 +18388,7 @@
       <c r="K1013" s="6"/>
       <c r="L1013" s="6"/>
     </row>
-    <row r="1014" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1014" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1014" s="5"/>
       <c r="B1014" s="5"/>
       <c r="C1014" s="5"/>
@@ -18383,7 +18402,7 @@
       <c r="K1014" s="6"/>
       <c r="L1014" s="6"/>
     </row>
-    <row r="1015" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1015" spans="1:12" ht="22.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1015" s="5"/>
       <c r="B1015" s="5"/>
       <c r="C1015" s="5"/>
@@ -18397,7 +18416,7 @@
       <c r="K1015" s="6"/>
       <c r="L1015" s="6"/>
     </row>
-    <row r="1016" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1016" spans="1:12" ht="72" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1016" s="5" t="s">
         <v>601</v>
       </c>
@@ -18423,7 +18442,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="1017" spans="1:12" ht="72" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1017" spans="1:12" ht="72" customHeight="1" ns3:dyDescent="0.2">
       <c r="A1017" s="5" t="s">
         <v>607</v>
       </c>
@@ -18451,24 +18470,24 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" sqref="K2:K1017" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="K2:K1017" ns2:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Minor Repeatable,Minor Fire-Once,Major"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="Q2:Q16" ns2:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L1017" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:C1017 N2:N16" ns2:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation type="list" allowBlank="1" sqref="L2:L1017" ns2:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="R2:R16" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="R2:R16" ns2:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"Implemented,New,In progress,Under review,Buggy"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="2">
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
+    <tablePart ns4:id="rId1"/>
+    <tablePart ns4:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2321,7 +2321,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="25">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2457,7 +2457,101 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF5B3F86"/>
+          <bgColor rgb="FF5B3F86"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9B3642"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9B3642"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9B3642"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9B3642"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9B3642"/>
+          <bgColor rgb="FF9B3642"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF9B3642"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF9B3642"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF9B3642"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF9B3642"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Main Sheet-style" pivot="0" count="4">
+      <tableStyleElement type="wholeTable" dxfId="24" size="0"/>
+      <tableStyleElement type="headerRow" dxfId="23"/>
+      <tableStyleElement type="firstRowStripe" dxfId="22"/>
+      <tableStyleElement type="secondRowStripe" dxfId="21"/>
+    </tableStyle>
+    <tableStyle name="Main Sheet-style 2" pivot="0" count="4">
+      <tableStyleElement type="wholeTable" dxfId="20" size="0"/>
+      <tableStyleElement type="headerRow" dxfId="19"/>
+      <tableStyleElement type="firstRowStripe" dxfId="18"/>
+      <tableStyleElement type="secondRowStripe" dxfId="17"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -2533,6 +2627,7 @@
     <tableColumn id="7" name="Chaos level"/>
     <tableColumn id="8" name="Status"/>
   </tableColumns>
+  <tableStyleInfo name="Main Sheet-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2553,6 +2648,7 @@
     <tableColumn id="12" name="Severity"/>
     <tableColumn id="13" name="Status"/>
   </tableColumns>
+  <tableStyleInfo name="Main Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2825,7 +2825,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1C4587"/>
     <pageSetUpPr fitToPage="false"/>
@@ -3103,7 +3103,7 @@
       <c r="J5" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="20" t="s">
+      <c r="K5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="L5" s="12" t="s">
@@ -3112,7 +3112,7 @@
       <c r="M5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="21" t="s">
+      <c r="O5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="P5" s="14" t="s">
@@ -3166,7 +3166,7 @@
       <c r="J6" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L6" s="23" t="s">
@@ -3175,7 +3175,7 @@
       <c r="M6" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="O6" s="21" t="s">
+      <c r="O6" s="2" t="s">
         <v>29</v>
       </c>
       <c r="P6" s="14" t="s">
@@ -3229,7 +3229,7 @@
       <c r="J7" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="K7" s="20" t="s">
+      <c r="K7" s="2" t="s">
         <v>29</v>
       </c>
       <c r="L7" s="12" t="s">
@@ -18129,8 +18129,8 @@
     <oddFooter/>
   </headerFooter>
   <tableParts>
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
+    <tablePart ns1:id="rId1"/>
+    <tablePart ns1:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -18099,26 +18099,27 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:K1017" type="list">
-      <formula1>"Minor Repeatable,Minor Fire-Once,Major"</formula1>
-      <formula2>0</formula2>
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J1017">
+      <formula1>"Minor Repeatable,Minor Fire-Once,Major,Manual Scenario"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P16" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="L2:L1017">
+      <formula1>"Low,Medium,High,Severe"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="M2:M1017">
+      <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="S2:S14">
+      <formula1>"Minor Repeatable,Minor Fire-Once,Major,Manual Scenario"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="T2:T14">
+      <formula1>"Low,Medium,High,Severe"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="U2:U14">
       <formula1>"1,2,3,4,5"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="true" showErrorMessage="false" showInputMessage="false" sqref="A2:C1017 M2:M16" type="none">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L1017" type="list">
-      <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q2:Q16" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="V2:V14">
       <formula1>"Implemented,New,In progress,Under review,Buggy"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2632,7 +2632,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Events" displayName="Events" ref="A1:M1017" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Events" displayName="Events" ref="A1:M1015" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="13">
     <tableColumn id="1" name="ID"/>
     <tableColumn id="2" name="Event Name"/>
@@ -2649,6 +2649,22 @@
     <tableColumn id="13" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="Main Sheet-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Manual_Scenarios" displayName="Manual_Scenarios" ref="W1:AD5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="8">
+    <tableColumn id="1" name="Scenario ID"/>
+    <tableColumn id="2" name="Scenario Name"/>
+    <tableColumn id="3" name="Details"/>
+    <tableColumn id="4" name="Source Event"/>
+    <tableColumn id="5" name="Type Options"/>
+    <tableColumn id="6" name="Intensity Scaling"/>
+    <tableColumn id="7" name="Launch Gate"/>
+    <tableColumn id="8" name="Status"/>
+  </tableColumns>
+  <tableStyleInfo name="Main Sheet-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2825,12 +2841,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1C4587"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V1017"/>
+  <dimension ref="A1:AD1015"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.15"/>
@@ -2854,6 +2870,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
+    <col min="23" max="23" width="12" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
+    <col min="25" max="25" width="68" customWidth="1"/>
+    <col min="26" max="26" width="24" customWidth="1"/>
+    <col min="27" max="27" width="46" customWidth="1"/>
+    <col min="28" max="28" width="52" customWidth="1"/>
+    <col min="29" max="29" width="44" customWidth="1"/>
+    <col min="30" max="30" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2920,6 +2944,46 @@
       <c r="V1" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Scenario ID</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Scenario Name</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>Source Event</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>Type Options</t>
+        </is>
+      </c>
+      <c r="AB1" s="3" t="inlineStr">
+        <is>
+          <t>Intensity Scaling</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>Launch Gate</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="99.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
@@ -2971,6 +3035,46 @@
       <c r="V2" s="17" t="s">
         <v>28</v>
       </c>
+      <c r="W2" s="14" t="inlineStr">
+        <is>
+          <t>SCN-001</t>
+        </is>
+      </c>
+      <c r="X2" s="14" t="inlineStr">
+        <is>
+          <t>Zombie Apocalypse</t>
+        </is>
+      </c>
+      <c r="Y2" s="14" t="inlineStr">
+        <is>
+          <t>Manual setup launched from the Chaos Redux scenario window. Creates hostile zombie outbreaks from selected outbreak profile and structure.</t>
+        </is>
+      </c>
+      <c r="Z2" s="14" t="inlineStr">
+        <is>
+          <t>Event 002 Zombie Outbreak</t>
+        </is>
+      </c>
+      <c r="AA2" s="14" t="inlineStr">
+        <is>
+          <t>Diverse, Random, Standard, Rabid, Parasitic, Mutant, Undead, Necrotic, Demonic, Wendigo, Connected</t>
+        </is>
+      </c>
+      <c r="AB2" s="14" t="inlineStr">
+        <is>
+          <t>Low/Medium/High/Maximum controls outbreak count, starting states, spawned divisions, and early pressure.</t>
+        </is>
+      </c>
+      <c r="AC2" s="14" t="inlineStr">
+        <is>
+          <t>Available unless the launch is impossible or conflicts with an active terminal state.</t>
+        </is>
+      </c>
+      <c r="AD2" s="19" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="111.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
@@ -3020,6 +3124,46 @@
       <c r="V3" s="17" t="s">
         <v>28</v>
       </c>
+      <c r="W3" s="14" t="inlineStr">
+        <is>
+          <t>SCN-002</t>
+        </is>
+      </c>
+      <c r="X3" s="14" t="inlineStr">
+        <is>
+          <t>Army of Clones</t>
+        </is>
+      </c>
+      <c r="Y3" s="14" t="inlineStr">
+        <is>
+          <t>Manual setup launched from the Chaos Redux scenario window. Creates a hostile artificial army in Eastern Europe and the western Soviet borderlands.</t>
+        </is>
+      </c>
+      <c r="Z3" s="14" t="inlineStr">
+        <is>
+          <t>Mengele Clone Army scenario</t>
+        </is>
+      </c>
+      <c r="AA3" s="14" t="inlineStr">
+        <is>
+          <t>Standard clone army or stronger Aryan variant</t>
+        </is>
+      </c>
+      <c r="AB3" s="14" t="inlineStr">
+        <is>
+          <t>Low/Medium/High/Maximum controls starting territory, divisions, army experience, equipment stockpiles, and pressure on neighboring countries.</t>
+        </is>
+      </c>
+      <c r="AC3" s="14" t="inlineStr">
+        <is>
+          <t>Available unless the launch is impossible or conflicts with an active terminal state.</t>
+        </is>
+      </c>
+      <c r="AD3" s="19" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -3073,6 +3217,46 @@
       <c r="V4" s="17" t="s">
         <v>28</v>
       </c>
+      <c r="W4" s="14" t="inlineStr">
+        <is>
+          <t>SCN-003</t>
+        </is>
+      </c>
+      <c r="X4" s="14" t="inlineStr">
+        <is>
+          <t>Soviet Collapse</t>
+        </is>
+      </c>
+      <c r="Y4" s="14" t="inlineStr">
+        <is>
+          <t>Manual setup launched from the Chaos Redux scenario window. Forces the Event 005 Union Unmade terminal collapse immediately and releases the Soviet breakaways.</t>
+        </is>
+      </c>
+      <c r="Z4" s="14" t="inlineStr">
+        <is>
+          <t>Event 005 Soviet Collapse</t>
+        </is>
+      </c>
+      <c r="AA4" s="14" t="inlineStr">
+        <is>
+          <t>Ordinary republics or chaos republics</t>
+        </is>
+      </c>
+      <c r="AB4" s="14" t="inlineStr">
+        <is>
+          <t>Low/Medium/High/Maximum adds scaled extra breakaway armies, manpower, infantry equipment, support equipment, artillery, and motorized equipment.</t>
+        </is>
+      </c>
+      <c r="AC4" s="14" t="inlineStr">
+        <is>
+          <t>Requires a valid Soviet collapse launch state; bypasses normal chaos, evolution, and prior-super-event gates during setup.</t>
+        </is>
+      </c>
+      <c r="AD4" s="19" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
@@ -3135,6 +3319,46 @@
       </c>
       <c r="V5" s="22" t="s">
         <v>60</v>
+      </c>
+      <c r="W5" s="14" t="inlineStr">
+        <is>
+          <t>SCN-004</t>
+        </is>
+      </c>
+      <c r="X5" s="14" t="inlineStr">
+        <is>
+          <t>Final Silence</t>
+        </is>
+      </c>
+      <c r="Y5" s="14" t="inlineStr">
+        <is>
+          <t>Manual setup launched from the Chaos Redux scenario window. Starts the Holy Realm Final Silence world-end sequence from the current player country.</t>
+        </is>
+      </c>
+      <c r="Z5" s="14" t="inlineStr">
+        <is>
+          <t>Event 003 The Holy Realm</t>
+        </is>
+      </c>
+      <c r="AA5" s="14" t="inlineStr">
+        <is>
+          <t>Nuclear or thermonuclear payload</t>
+        </is>
+      </c>
+      <c r="AB5" s="14" t="inlineStr">
+        <is>
+          <t>Intensity is fixed; the scenario keeps the canonical four-wave Final Silence sequence.</t>
+        </is>
+      </c>
+      <c r="AC5" s="14" t="inlineStr">
+        <is>
+          <t>Blocked if another terminal world-end is already active or the launch is otherwise impossible.</t>
+        </is>
+      </c>
+      <c r="AD5" s="19" t="inlineStr">
+        <is>
+          <t>Implemented</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18048,65 +18272,15 @@
       <c r="J1015" s="29"/>
       <c r="M1015" s="29"/>
     </row>
-    <row r="1016" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1016" s="31" t="s">
-        <v>614</v>
-      </c>
-      <c r="B1016" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="C1016" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="D1016" s="6"/>
-      <c r="E1016" s="7"/>
-      <c r="F1016" s="8"/>
-      <c r="G1016" s="9"/>
-      <c r="H1016" s="10"/>
-      <c r="I1016" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="J1016" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="M1016" s="19" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="1017" customFormat="false" ht="72" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1017" s="31" t="s">
-        <v>620</v>
-      </c>
-      <c r="B1017" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="C1017" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="D1017" s="6"/>
-      <c r="E1017" s="7"/>
-      <c r="F1017" s="8"/>
-      <c r="G1017" s="9"/>
-      <c r="H1017" s="10"/>
-      <c r="I1017" s="11" t="s">
-        <v>617</v>
-      </c>
-      <c r="J1017" s="20" t="s">
-        <v>618</v>
-      </c>
-      <c r="M1017" s="19" t="s">
-        <v>619</v>
-      </c>
-    </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="J2:J1017">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J1015">
       <formula1>"Minor Repeatable,Minor Fire-Once,Major,Manual Scenario"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="L2:L1017">
+    <dataValidation type="list" allowBlank="1" sqref="L2:L1015">
       <formula1>"Low,Medium,High,Severe"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="M2:M1017">
+    <dataValidation type="list" allowBlank="1" sqref="M2:M1015">
       <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="S2:S14">
@@ -18121,6 +18295,9 @@
     <dataValidation type="list" allowBlank="1" sqref="V2:V14">
       <formula1>"Implemented,New,In progress,Under review,Buggy"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="AD2:AD5">
+      <formula1>"Implemented,New,In progress,To Be Reworked,Buggy,Needs Testing"</formula1>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -18129,9 +18306,10 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <tableParts>
-    <tablePart ns1:id="rId1"/>
-    <tablePart ns1:id="rId2"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2047,7 +2047,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2144,6 +2144,36 @@
         <bgColor rgb="FFF4CCCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE5E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB3B3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9999"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF8080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
@@ -2179,7 +2209,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2310,6 +2340,26 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false" applyFill="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false" applyFill="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="19" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false" applyFill="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="20" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false" applyFill="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="21" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false" applyFill="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2616,16 +2666,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Event_Clusters" displayName="Event_Clusters" ref="O1:V14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Event_Clusters" displayName="Event_Clusters" ref="O1:U14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <tableColumns count="7">
     <tableColumn id="1" name="Cluster ID"/>
     <tableColumn id="2" name="Cluster Name"/>
     <tableColumn id="3" name="Details"/>
     <tableColumn id="4" name="Events (ID)"/>
     <tableColumn id="5" name="Type"/>
-    <tableColumn id="6" name="Severity"/>
-    <tableColumn id="7" name="Chaos level"/>
-    <tableColumn id="8" name="Status"/>
+    <tableColumn id="6" name="Chaos level"/>
+    <tableColumn id="7" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="Main Sheet-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2936,12 +2985,9 @@
         <v>9</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="W1" s="3" t="inlineStr">
@@ -3015,7 +3061,7 @@
       <c r="M2" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="14"/>
+      <c r="O2" s="4"/>
       <c r="P2" s="14" t="s">
         <v>25</v>
       </c>
@@ -3026,13 +3072,10 @@
       <c r="S2" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T2" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="U2" s="14" t="s">
+      <c r="T2" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="V2" s="17" t="s">
+      <c r="U2" s="17" t="s">
         <v>28</v>
       </c>
       <c r="W2" s="14" t="inlineStr">
@@ -3106,7 +3149,7 @@
       <c r="M3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="14"/>
+      <c r="O3" s="4"/>
       <c r="P3" s="14" t="s">
         <v>37</v>
       </c>
@@ -3115,13 +3158,10 @@
       <c r="S3" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="U3" s="14" t="s">
+      <c r="T3" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="V3" s="17" t="s">
+      <c r="U3" s="17" t="s">
         <v>28</v>
       </c>
       <c r="W3" s="14" t="inlineStr">
@@ -3199,7 +3239,7 @@
       <c r="M4" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="14"/>
+      <c r="O4" s="4"/>
       <c r="P4" s="14" t="s">
         <v>47</v>
       </c>
@@ -3208,13 +3248,10 @@
       <c r="S4" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T4" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="U4" s="14" t="s">
+      <c r="T4" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="U4" s="17" t="s">
         <v>28</v>
       </c>
       <c r="W4" s="14" t="inlineStr">
@@ -3296,7 +3333,7 @@
       <c r="M5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="4" t="s">
         <v>16</v>
       </c>
       <c r="P5" s="14" t="s">
@@ -3311,13 +3348,10 @@
       <c r="S5" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="T5" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="U5" s="14" t="s">
+      <c r="T5" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="V5" s="22" t="s">
+      <c r="U5" s="22" t="s">
         <v>60</v>
       </c>
       <c r="W5" s="14" t="inlineStr">
@@ -3399,7 +3433,7 @@
       <c r="M6" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="4" t="s">
         <v>29</v>
       </c>
       <c r="P6" s="14" t="s">
@@ -3414,13 +3448,10 @@
       <c r="S6" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="T6" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="U6" s="14" t="s">
+      <c r="T6" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="V6" s="22" t="s">
+      <c r="U6" s="22" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3462,7 +3493,7 @@
       <c r="M7" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="O7" s="14"/>
+      <c r="O7" s="4"/>
       <c r="P7" s="14" t="s">
         <v>81</v>
       </c>
@@ -3473,13 +3504,10 @@
       <c r="S7" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T7" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="U7" s="14" t="s">
+      <c r="T7" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="V7" s="17" t="s">
+      <c r="U7" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3507,7 +3535,7 @@
       <c r="M8" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="O8" s="14"/>
+      <c r="O8" s="4"/>
       <c r="P8" s="14" t="s">
         <v>88</v>
       </c>
@@ -3516,13 +3544,10 @@
       <c r="S8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T8" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="U8" s="14" t="s">
+      <c r="T8" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="V8" s="17" t="s">
+      <c r="U8" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3548,7 +3573,7 @@
       <c r="M9" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="O9" s="14"/>
+      <c r="O9" s="4"/>
       <c r="P9" s="14" t="s">
         <v>92</v>
       </c>
@@ -3557,13 +3582,10 @@
       <c r="S9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T9" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="U9" s="14" t="s">
+      <c r="T9" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="V9" s="17" t="s">
+      <c r="U9" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3589,7 +3611,7 @@
       <c r="M10" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="O10" s="14"/>
+      <c r="O10" s="4"/>
       <c r="P10" s="14" t="s">
         <v>96</v>
       </c>
@@ -3600,13 +3622,10 @@
       <c r="S10" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T10" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="U10" s="14" t="s">
+      <c r="T10" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="V10" s="17" t="s">
+      <c r="U10" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3632,7 +3651,7 @@
       <c r="M11" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="O11" s="14"/>
+      <c r="O11" s="4"/>
       <c r="P11" s="14" t="s">
         <v>101</v>
       </c>
@@ -3643,13 +3662,10 @@
       <c r="S11" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T11" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="U11" s="14" t="s">
+      <c r="T11" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="V11" s="17" t="s">
+      <c r="U11" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3675,7 +3691,7 @@
       <c r="M12" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="O12" s="14"/>
+      <c r="O12" s="4"/>
       <c r="P12" s="14" t="s">
         <v>106</v>
       </c>
@@ -3684,13 +3700,10 @@
       <c r="S12" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T12" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="U12" s="14" t="s">
+      <c r="T12" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="V12" s="17" t="s">
+      <c r="U12" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3716,7 +3729,7 @@
       <c r="M13" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="O13" s="14"/>
+      <c r="O13" s="4"/>
       <c r="P13" s="14" t="s">
         <v>110</v>
       </c>
@@ -3725,13 +3738,10 @@
       <c r="S13" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="T13" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="U13" s="14" t="s">
+      <c r="T13" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="V13" s="17" t="s">
+      <c r="U13" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -3759,7 +3769,7 @@
       <c r="M14" s="27" t="s">
         <v>87</v>
       </c>
-      <c r="O14" s="14"/>
+      <c r="O14" s="4"/>
       <c r="P14" s="14" t="s">
         <v>114</v>
       </c>
@@ -3770,13 +3780,10 @@
       <c r="S14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="T14" s="25" t="s">
-        <v>69</v>
-      </c>
-      <c r="U14" s="14" t="s">
+      <c r="T14" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="V14" s="17" t="s">
+      <c r="U14" s="17" t="s">
         <v>28</v>
       </c>
     </row>
@@ -18273,7 +18280,7 @@
       <c r="M1015" s="29"/>
     </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="7">
     <dataValidation type="list" allowBlank="1" sqref="J2:J1015">
       <formula1>"Minor Repeatable,Minor Fire-Once,Major,Manual Scenario"</formula1>
     </dataValidation>
@@ -18287,12 +18294,9 @@
       <formula1>"Minor Repeatable,Minor Fire-Once,Major,Manual Scenario"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="T2:T14">
-      <formula1>"Low,Medium,High,Severe"</formula1>
+      <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="U2:U14">
-      <formula1>"1,2,3,4,5"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="V2:V14">
       <formula1>"Implemented,New,In progress,Under review,Buggy"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="AD2:AD5">

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -3434,7 +3434,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFE699"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFFFE699"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3442,7 +3442,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3450,7 +3450,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF4CCCC"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3458,7 +3458,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFDDEBF7"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFDDEBF7"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3466,7 +3466,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFE7E6E6"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFE7E6E6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3474,7 +3474,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFCFE2F3"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFCFE2F3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3482,7 +3482,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFCE4D6"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3490,7 +3490,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8CBAD"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFF8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3498,7 +3498,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3506,7 +3506,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF4CCCC"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3514,7 +3514,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9D2E9"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFD9D2E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3522,7 +3522,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFC6EFCE"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3530,7 +3530,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFE699"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFFFE699"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3538,7 +3538,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF4CCCC"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFF4CCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3546,7 +3546,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFD9D2E9"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFD9D2E9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3554,7 +3554,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFE5E5"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFFFE5E5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3562,7 +3562,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFCCCC"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3570,7 +3570,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFB3B3"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFFFB3B3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3578,7 +3578,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF9999"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFFF9999"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3586,7 +3586,7 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFF8080"/>
-          <bgColor indexed="64"/>
+          <bgColor rgb="FFFF8080"/>
         </patternFill>
       </fill>
     </dxf>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{0E38D6A2-8B35-4B26-95DB-FB44AF7250B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main Sheet" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="Legend" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -21347,11 +21346,11 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <tableParts count="3">
-    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Y6" s="61" t="inlineStr">
         <is>
-          <t>Creates AI Fury actors from safe eligible minors, loads their Fury package, and starts the expansion loop without turning the player into Fury.</t>
+          <t>Creates dispersed AI Fury actors from safe eligible minors, loads their Fury package, and starts the expansion loop without turning the player into Fury.</t>
         </is>
       </c>
       <c r="Z6" s="47" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AA6" s="47" t="inlineStr">
         <is>
-          <t>Low/Medium/High/Maximum targets 1/3/6/10 Fury actors, capped by safe eligible countries. Maximum records the ten-fires challenge state when ten actors spawn.</t>
+          <t>Low/Medium/High/Maximum targets 2/5/9/16 dispersed Fury actors, capped by safe eligible countries. Maximum records the full-spread challenge state when the maximum actor count or every safe candidate is used.</t>
         </is>
       </c>
       <c r="AB6" s="50" t="inlineStr">

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -3238,7 +3238,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="false">
     <tabColor rgb="FF1C4587"/>
     <pageSetUpPr fitToPage="false"/>
@@ -3500,26 +3500,40 @@
       <c r="B4" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>61</v>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Transforms Tibet first, falling back to Bhutan or Nepal only if Tibet is gone and the fallback exists and is not a special chaos country. All origins use the shared Holy Realm/THR identity. The 112-focus tree builds a defensive refuge into Buddhahood play through Bodhi, Dhyana, Teaching Successes, Meditation Charge, Defilements, World Suffering, Sangha Cohesion, the Sangha Compact, anti-chaos Buddha powers, hidden False Buddha Schism outcomes, and the split Final Silence route. Twelve Holy Realm achievements and DDS icon triplets are registered.</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Mountain Refuge: forms The Holy Realm, initializes Mandala and Buddhahood counters, applies fragile refuge ideas, opens the Mandala GUI/category, loads the focus tree, and starts shelter, road, refugee, early teaching, and defensive play.</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Bodhisattva Teaching and Meditation: Send Dhamma Envoys, Guard the Pilgrimage Route, Translate the Wheel, teaching-under-fire, and the concentration-vow sequence raise Bodhi, Compassion, Dhyana Depth, and Meditation Charge while tracking clean-route and Defilement risks.</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Governance, Sanctuary, Guardian, and Sangha Compact routes: Council/Regent/Assembly choices, infrastructure and supply works, Temple Guard and pilgrimage escort systems, compact admission, aid, anti-puppet clauses, and AI weights support defensive humanitarian play against special chaos countries.</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>The Unshaken Seat and Powers: Buddhahood requires 108 Bodhi, Fourth Dhyana, low Defilements, teaching successes, crisis teaching, and the focus marker. Success changes leader/stage, fires The Awakened One, unlocks the Buddha powers category, and the first anti-chaos power display fires Powers of the Awakened.</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Final Silence and Schism: the hidden False Buddha branch supports debate, exile, suppression, and absorption outcomes. Extinction of Defilements, Witnesses Gather, and the final doctrine balance gate non-terminal Empty Seat aftermath versus terminal Final Silence.</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Terminal Final Silence requires Buddhahood, Dhyana 4, low Defilements, Meditation Charge, a prior anti-chaos power display, final doctrine/focus gates, controlled capital, no active schism, no other world-end, and chaos above 1000. Completion sets world_end/world_end_final_silence and runs the strike-wave sequence; otherwise the non-terminal Empty Seat aftermath remains playable.</t>
+        </is>
       </c>
       <c r="J4" s="16" t="s">
         <v>27</v>
@@ -20746,9 +20760,9 @@
     <oddFooter/>
   </headerFooter>
   <tableParts>
-    <tablePart r:id="rId1"/>
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
+    <tablePart ns1:id="rId1"/>
+    <tablePart ns1:id="rId2"/>
+    <tablePart ns1:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -191,7 +191,7 @@
     <t xml:space="preserve">The Holy Realm</t>
   </si>
   <si>
-    <t xml:space="preserve">Transforms Tibet or a Tibet-centered Himalayan state into the Holy Realm. The route begins as a defensive mountain refuge, develops into a Bodhisattva-led state, and layers Bodhi, Dhyana, Teaching Successes, Meditation Charge, Defilements, World Suffering, and Sangha Cohesion onto the older Mandala counters. The Unshaken Seat tests whether the Bodhisattva realizes Buddhahood or builds False Buddha Schism pressure; a realized Buddha unlocks Powers of the Awakened and a split Final Silence that can end as the Empty Seat aftermath or the terminal world-end.</t>
+    <t xml:space="preserve">Transforms Tibet first, falling back to Bhutan or Nepal only if Tibet is gone and the fallback exists as a valid normal country. All origins use the shared Holy Realm/THR identity. The route begins as a defensive mountain refuge, develops into a Bodhisattva-led state, and layers Bodhi, Dhyana, Teaching Successes, Meditation Charge, Defilements, World Suffering, and Sangha Cohesion onto the older Mandala counters. The Unshaken Seat tests whether the Bodhisattva realizes Buddhahood or builds False Buddha Schism pressure; a realized Buddha unlocks Powers of the Awakened and a split Final Silence that can end as the Empty Seat aftermath or the terminal world-end.</t>
   </si>
   <si>
     <t xml:space="preserve">Mountain Refuge: forms the Holy Realm, loads the Holy Realm focus tree, initializes the Mandala and Buddhahood counters, and opens defensive refuge, high-pass, shelter, and refugee policy content.</t>
@@ -3502,7 +3502,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Transforms Tibet first, falling back to Bhutan or Nepal only if Tibet is gone and the fallback exists and is not a special chaos country. All origins use the shared Holy Realm/THR identity. The 112-focus tree builds a defensive refuge into Buddhahood play through Bodhi, Dhyana, Teaching Successes, Meditation Charge, Defilements, World Suffering, Sangha Cohesion, the Sangha Compact, anti-chaos Buddha powers, hidden False Buddha Schism outcomes, and the split Final Silence route. Twelve Holy Realm achievements and DDS icon triplets are registered.</t>
+          <t>Transforms Tibet first, falling back to Bhutan or Nepal only if Tibet is gone and the fallback exists and is not a special chaos country. All origins use the shared Holy Realm/THR identity. The 111-focus tree builds a defensive refuge into Buddhahood play through Bodhi, Dhyana, Teaching Successes, Meditation Charge, Defilements, World Suffering, Sangha Cohesion, the Sangha Compact, anti-chaos Buddha powers, hidden False Buddha Schism outcomes, and the split Final Silence route. Twelve Holy Realm achievements and DDS icon triplets are registered.</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -3541,7 +3541,7 @@
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
       <c r="M4" s="18" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="O4" s="19" t="s">
         <v>29</v>

--- a/docs/spreadsheets/chaos_redux_events_catalog.xlsx
+++ b/docs/spreadsheets/chaos_redux_events_catalog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Main Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -2031,33 +2031,34 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Tensions Rising is a repeatable diplomatic pressure event. In a calm world it adds +10 world tension and is blocked at full world tension. Higher chaos tiers let it fire even at 100% world tension, adding direct chaos, larger world-tension packets, capped temporary timer pressure, timed relation shocks, delayed reports, event-log and evolution-detail wiring, AI posture hooks, achievement tracking, and cataloged asset hooks, with Stage IV ending in a one-time non-terminal super-event.</t>
+          <t>Tensions Rising is a repeatable diplomatic-pressure incident. In calm conditions it adds world tension and stops once world tension is full. At higher chaos levels it can still fire at maximum world tension, adding indirect pressure through timer pacing, timed opinion penalties, AI readiness ideas, delayed reports, and achievement tracking.
+It does not create war goals, countries, cores, focus trees, formables, or a world-end scenario.</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Gathering Storm: Cable Traffic Flood. Adds +10 chaos and +10 world tension, can fire at full world tension, opens light timed relation shocks, a capped timer pulse, delayed diplomatic reports, and the first wired evolution and event-log detail updates.</t>
+          <t>Cable Traffic Increase. The first evolved stage moves the incident beyond a simple world-tension increase. Relation shocks begin, and later incidents can briefly gather pace.</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Rising Chaos: The Accusation Market. Adds +15 chaos and +20 world tension, selects more relation pairs and AI posture targets, and expands the delayed-report and evolution-detail pressure.</t>
+          <t>Competing Accusations. The second stage reaches more capitals. Timed relation damage can affect additional pairs, delayed reports become more likely, and some governments take short-lived readiness postures.</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Chaos Tier: General Staffs Stop Sleeping. Adds +25 chaos and +50 world tension, applies heavier relation shocks, stronger timer pressure, broader AI posture hooks, and opens the Thin Wire full-tension peace watch.</t>
+          <t>Staff Readiness. The third stage treats the pattern as a planning concern. Relation shocks last longer, diplomatic aftershocks remain temporary, and peaceful players can begin the Thin Wire watch while world tension remains full.</t>
         </is>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Totalen Chaos: The Permanent Alert. Adds +50 chaos and +100 world tension, applies the strongest timed diplomatic shock, and fires the one-time non-terminal super-event The Red Line Disappears.</t>
+          <t>Extended Alert. The fourth stage is the strongest non-terminal form of the incident. It keeps pressure indirect and does not create a direct conflict branch.</t>
         </is>
       </c>
       <c r="H9" s="14" t="n"/>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>No world-end scenario. Stage IV is a one-time non-terminal super-event only; Event 8 never creates direct war goals, countries, focus trees, cores, or formables.</t>
+          <t>No world-end scenario. Event 8 never creates direct war goals, countries, focus trees, cores, or formables; Stage IV remains a normal event-log and evolution stage.</t>
         </is>
       </c>
       <c r="J9" s="28" t="inlineStr">
@@ -2468,7 +2469,7 @@
       </c>
       <c r="Q15" s="20" t="inlineStr">
         <is>
-          <t>Repeatable diplomatic-panic cluster. Current implemented member is Event 8, which pushes world tension and chaos through capped timer pressure, timed relation shocks, delayed reports, event-log and evolution-detail wiring, AI posture hooks, achievement tracking, and cataloged asset hooks without direct war goals, new countries, focus trees, cores, formables, or a world-end scenario.</t>
+          <t>Diplomatic panic pushes world tension, relation damage, ministries, newspapers, and staff offices into a shared crisis pattern without creating direct war goals or new countries.</t>
         </is>
       </c>
       <c r="R15" s="20" t="inlineStr">
@@ -2483,7 +2484,7 @@
       </c>
       <c r="T15" s="27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Calm World</t>
         </is>
       </c>
       <c r="U15" s="31" t="inlineStr">
